--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="66">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,34 +178,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>50.3 → 48.4</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.3</t>
-  </si>
-  <si>
-    <t>48.4</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -407,15 +380,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -930,10 +902,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1357.6</v>
+        <v>1339.8</v>
       </c>
       <c r="D2">
-        <v>-0.38</v>
+        <v>-1.31</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -942,46 +914,46 @@
         <v>1247.38</v>
       </c>
       <c r="G2">
-        <v>-28.65</v>
+        <v>-29.58</v>
       </c>
       <c r="H2">
-        <v>8.84</v>
+        <v>7.41</v>
       </c>
       <c r="I2">
-        <v>-2.89</v>
+        <v>-3.24</v>
       </c>
       <c r="J2">
-        <v>-1.94</v>
+        <v>-2.83</v>
       </c>
       <c r="K2">
-        <v>1.37</v>
+        <v>-1.38</v>
       </c>
       <c r="L2">
-        <v>-23.73</v>
+        <v>-25.21</v>
       </c>
       <c r="M2">
-        <v>-9.17</v>
+        <v>-9.24</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="P2">
-        <v>1375.5</v>
+        <v>1366.52</v>
       </c>
       <c r="Q2">
-        <v>1367.96</v>
+        <v>1366.86</v>
       </c>
       <c r="R2">
-        <v>1355.07</v>
+        <v>1354.82</v>
       </c>
       <c r="S2">
-        <v>1543.12</v>
+        <v>1540.63</v>
       </c>
       <c r="T2">
-        <v>-12.02</v>
+        <v>-13.04</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -996,34 +968,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>47.82</v>
+        <v>43.91</v>
       </c>
       <c r="Z2">
-        <v>2.95</v>
+        <v>0.37</v>
       </c>
       <c r="AA2">
-        <v>3.28</v>
+        <v>2.7</v>
       </c>
       <c r="AB2">
-        <v>-0.33</v>
+        <v>-2.33</v>
       </c>
       <c r="AC2">
-        <v>45.61</v>
+        <v>26.15</v>
       </c>
       <c r="AD2">
-        <v>62.76</v>
+        <v>45.59</v>
       </c>
       <c r="AE2">
-        <v>28.91</v>
+        <v>28.56</v>
       </c>
       <c r="AF2">
-        <v>-22.06</v>
+        <v>-34.82</v>
       </c>
       <c r="AG2">
-        <v>1403.72</v>
+        <v>1404.71</v>
       </c>
       <c r="AH2">
-        <v>1332.2</v>
+        <v>1329</v>
       </c>
       <c r="AI2">
         <v>1318.07</v>
@@ -1032,7 +1004,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>16.72</v>
+        <v>17.55</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,10 +1015,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3010</v>
+        <v>2995.5</v>
       </c>
       <c r="D3">
-        <v>-0.33</v>
+        <v>-0.48</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1055,46 +1027,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-6.29</v>
+        <v>-6.74</v>
       </c>
       <c r="H3">
-        <v>71.22</v>
+        <v>70.39</v>
       </c>
       <c r="I3">
-        <v>-1.89</v>
+        <v>-1.79</v>
       </c>
       <c r="J3">
-        <v>-4.67</v>
+        <v>-5.73</v>
       </c>
       <c r="K3">
-        <v>25.2</v>
+        <v>19.97</v>
       </c>
       <c r="L3">
-        <v>27.41</v>
+        <v>28.72</v>
       </c>
       <c r="M3">
-        <v>15.84</v>
+        <v>15.88</v>
       </c>
       <c r="N3">
         <v>88</v>
       </c>
       <c r="O3">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="P3">
-        <v>3031.2</v>
+        <v>3020.3</v>
       </c>
       <c r="Q3">
-        <v>3077.38</v>
+        <v>3067.72</v>
       </c>
       <c r="R3">
-        <v>3048.04</v>
+        <v>3049.79</v>
       </c>
       <c r="S3">
-        <v>2459.06</v>
+        <v>2461.29</v>
       </c>
       <c r="T3">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1109,34 +1081,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>44.94</v>
+        <v>43.34</v>
       </c>
       <c r="Z3">
-        <v>-8.130000000000001</v>
+        <v>-11.31</v>
       </c>
       <c r="AA3">
-        <v>4.03</v>
+        <v>0.96</v>
       </c>
       <c r="AB3">
-        <v>-12.16</v>
+        <v>-12.27</v>
       </c>
       <c r="AC3">
-        <v>12.92</v>
+        <v>7.37</v>
       </c>
       <c r="AD3">
-        <v>19.78</v>
+        <v>13.51</v>
       </c>
       <c r="AE3">
-        <v>65.73999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AF3">
-        <v>-30.02</v>
+        <v>29.85</v>
       </c>
       <c r="AG3">
-        <v>3216.69</v>
+        <v>3201.15</v>
       </c>
       <c r="AH3">
-        <v>2938.08</v>
+        <v>2934.28</v>
       </c>
       <c r="AI3">
         <v>2959.69</v>
@@ -1145,7 +1117,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>29.37</v>
+        <v>27.31</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1128,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1369</v>
+        <v>1366</v>
       </c>
       <c r="D4">
-        <v>-0.25</v>
+        <v>-0.22</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1168,46 +1140,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-14.68</v>
+        <v>-14.86</v>
       </c>
       <c r="H4">
-        <v>77.15000000000001</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="I4">
-        <v>-1.86</v>
+        <v>-1.3</v>
       </c>
       <c r="J4">
-        <v>-10.91</v>
+        <v>-11.67</v>
       </c>
       <c r="K4">
-        <v>4.66</v>
+        <v>-0.05</v>
       </c>
       <c r="L4">
-        <v>38.31</v>
+        <v>40.57</v>
       </c>
       <c r="M4">
-        <v>8.550000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="N4">
         <v>77</v>
       </c>
       <c r="O4">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="P4">
-        <v>1375.38</v>
+        <v>1371.78</v>
       </c>
       <c r="Q4">
-        <v>1435.05</v>
+        <v>1423.12</v>
       </c>
       <c r="R4">
-        <v>1475.16</v>
+        <v>1473.55</v>
       </c>
       <c r="S4">
-        <v>1154.02</v>
+        <v>1155.65</v>
       </c>
       <c r="T4">
-        <v>18.63</v>
+        <v>18.2</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1222,34 +1194,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>37.75</v>
+        <v>37.29</v>
       </c>
       <c r="Z4">
-        <v>-33.82</v>
+        <v>-33.55</v>
       </c>
       <c r="AA4">
-        <v>-28.49</v>
+        <v>-29.5</v>
       </c>
       <c r="AB4">
-        <v>-5.33</v>
+        <v>-4.05</v>
       </c>
       <c r="AC4">
-        <v>22.8</v>
+        <v>31.18</v>
       </c>
       <c r="AD4">
-        <v>21.58</v>
+        <v>24.63</v>
       </c>
       <c r="AE4">
-        <v>42.52</v>
+        <v>43.91</v>
       </c>
       <c r="AF4">
-        <v>-74.78</v>
+        <v>23.53</v>
       </c>
       <c r="AG4">
-        <v>1596.71</v>
+        <v>1566.28</v>
       </c>
       <c r="AH4">
-        <v>1273.38</v>
+        <v>1279.96</v>
       </c>
       <c r="AI4">
         <v>1493.56</v>
@@ -1258,7 +1230,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>29.48</v>
+        <v>26.45</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1241,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1681</v>
+        <v>1668.2</v>
       </c>
       <c r="D5">
-        <v>-0.74</v>
+        <v>-0.76</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1281,46 +1253,46 @@
         <v>1294.84</v>
       </c>
       <c r="G5">
-        <v>-10.74</v>
+        <v>-11.42</v>
       </c>
       <c r="H5">
-        <v>29.82</v>
+        <v>28.83</v>
       </c>
       <c r="I5">
-        <v>-1.18</v>
+        <v>-2.26</v>
       </c>
       <c r="J5">
-        <v>-8.050000000000001</v>
+        <v>-7.85</v>
       </c>
       <c r="K5">
-        <v>-0.01</v>
+        <v>-3.6</v>
       </c>
       <c r="L5">
-        <v>21.54</v>
+        <v>23.35</v>
       </c>
       <c r="M5">
-        <v>20.04</v>
+        <v>19.64</v>
       </c>
       <c r="N5">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="O5">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P5">
-        <v>1695.24</v>
+        <v>1687.54</v>
       </c>
       <c r="Q5">
-        <v>1758.7</v>
+        <v>1751.02</v>
       </c>
       <c r="R5">
-        <v>1792.98</v>
+        <v>1790.83</v>
       </c>
       <c r="S5">
-        <v>1580.39</v>
+        <v>1581.4</v>
       </c>
       <c r="T5">
-        <v>6.37</v>
+        <v>5.49</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1335,34 +1307,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>33.43</v>
+        <v>31.56</v>
       </c>
       <c r="Z5">
-        <v>-33.43</v>
+        <v>-34.92</v>
       </c>
       <c r="AA5">
-        <v>-25.5</v>
+        <v>-27.39</v>
       </c>
       <c r="AB5">
-        <v>-7.93</v>
+        <v>-7.53</v>
       </c>
       <c r="AC5">
-        <v>27.35</v>
+        <v>27.19</v>
       </c>
       <c r="AD5">
-        <v>28.98</v>
+        <v>27.75</v>
       </c>
       <c r="AE5">
-        <v>35.51</v>
+        <v>35.94</v>
       </c>
       <c r="AF5">
-        <v>4.08</v>
+        <v>6.49</v>
       </c>
       <c r="AG5">
-        <v>1886.39</v>
+        <v>1881.17</v>
       </c>
       <c r="AH5">
-        <v>1631.02</v>
+        <v>1620.87</v>
       </c>
       <c r="AI5">
         <v>1788.08</v>
@@ -1371,7 +1343,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>56.8</v>
+        <v>55.17</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,10 +1354,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>210.65</v>
+        <v>209</v>
       </c>
       <c r="D6">
-        <v>0.79</v>
+        <v>-0.78</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1394,46 +1366,46 @@
         <v>113.49</v>
       </c>
       <c r="G6">
-        <v>-15.37</v>
+        <v>-16.03</v>
       </c>
       <c r="H6">
-        <v>85.61</v>
+        <v>84.16</v>
       </c>
       <c r="I6">
-        <v>-1.4</v>
+        <v>-0.45</v>
       </c>
       <c r="J6">
-        <v>-3.57</v>
+        <v>-3</v>
       </c>
       <c r="K6">
-        <v>0.49</v>
+        <v>-2.28</v>
       </c>
       <c r="L6">
-        <v>80.34999999999999</v>
+        <v>80.33</v>
       </c>
       <c r="M6">
-        <v>65.12</v>
+        <v>65.81</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P6">
-        <v>209.34</v>
+        <v>209.15</v>
       </c>
       <c r="Q6">
-        <v>213.59</v>
+        <v>212.73</v>
       </c>
       <c r="R6">
-        <v>220.5</v>
+        <v>220.03</v>
       </c>
       <c r="S6">
-        <v>178.17</v>
+        <v>178.36</v>
       </c>
       <c r="T6">
-        <v>18.23</v>
+        <v>17.18</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1448,34 +1420,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>44.02</v>
+        <v>41.86</v>
       </c>
       <c r="Z6">
-        <v>-3.16</v>
+        <v>-3.1</v>
       </c>
       <c r="AA6">
-        <v>-3.16</v>
+        <v>-3.15</v>
       </c>
       <c r="AB6">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="AC6">
-        <v>42.64</v>
+        <v>53.68</v>
       </c>
       <c r="AD6">
-        <v>31.77</v>
+        <v>40.64</v>
       </c>
       <c r="AE6">
-        <v>5.32</v>
+        <v>5.34</v>
       </c>
       <c r="AF6">
-        <v>-46.11</v>
+        <v>-26.61</v>
       </c>
       <c r="AG6">
-        <v>223.45</v>
+        <v>220.81</v>
       </c>
       <c r="AH6">
-        <v>203.72</v>
+        <v>204.64</v>
       </c>
       <c r="AI6">
         <v>225</v>
@@ -1484,7 +1456,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>24.17</v>
+        <v>20.94</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1495,58 +1467,58 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>430.85</v>
+        <v>424</v>
       </c>
       <c r="D7">
-        <v>-0.73</v>
+        <v>-1.59</v>
       </c>
       <c r="E7">
-        <v>599.73</v>
+        <v>589.48</v>
       </c>
       <c r="F7">
         <v>393.4</v>
       </c>
       <c r="G7">
-        <v>-28.16</v>
+        <v>-28.07</v>
       </c>
       <c r="H7">
-        <v>9.52</v>
+        <v>7.78</v>
       </c>
       <c r="I7">
-        <v>-2.96</v>
+        <v>-2.76</v>
       </c>
       <c r="J7">
-        <v>-1.28</v>
+        <v>-1.89</v>
       </c>
       <c r="K7">
-        <v>1.41</v>
+        <v>-2.81</v>
       </c>
       <c r="L7">
-        <v>-28.46</v>
+        <v>-29.3</v>
       </c>
       <c r="M7">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="N7">
         <v>23</v>
       </c>
       <c r="O7">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="P7">
-        <v>436.48</v>
+        <v>434.07</v>
       </c>
       <c r="Q7">
-        <v>434.02</v>
+        <v>433.73</v>
       </c>
       <c r="R7">
-        <v>428.76</v>
+        <v>428.59</v>
       </c>
       <c r="S7">
-        <v>482.54</v>
+        <v>481.84</v>
       </c>
       <c r="T7">
-        <v>-10.71</v>
+        <v>-12</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1561,34 +1533,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>48.36</v>
+        <v>44.3</v>
       </c>
       <c r="Z7">
-        <v>1.42</v>
+        <v>0.46</v>
       </c>
       <c r="AA7">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="AB7">
-        <v>-0.1</v>
+        <v>-0.86</v>
       </c>
       <c r="AC7">
-        <v>39.77</v>
+        <v>22.24</v>
       </c>
       <c r="AD7">
-        <v>56.95</v>
+        <v>41.61</v>
       </c>
       <c r="AE7">
-        <v>10.37</v>
+        <v>10.45</v>
       </c>
       <c r="AF7">
-        <v>-29.72</v>
+        <v>-42.07</v>
       </c>
       <c r="AG7">
-        <v>445.43</v>
+        <v>445.86</v>
       </c>
       <c r="AH7">
-        <v>422.61</v>
+        <v>421.59</v>
       </c>
       <c r="AI7">
         <v>411.2</v>
@@ -1597,7 +1569,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>14.81</v>
+        <v>16.08</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1608,10 +1580,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>660.1</v>
+        <v>666.15</v>
       </c>
       <c r="D8">
-        <v>0.39</v>
+        <v>0.92</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1620,46 +1592,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-18.33</v>
+        <v>-17.58</v>
       </c>
       <c r="H8">
-        <v>41.13</v>
+        <v>42.42</v>
       </c>
       <c r="I8">
-        <v>-1.12</v>
+        <v>-0.12</v>
       </c>
       <c r="J8">
-        <v>-8.81</v>
+        <v>-7.6</v>
       </c>
       <c r="K8">
-        <v>11.68</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="L8">
-        <v>8.949999999999999</v>
+        <v>11.84</v>
       </c>
       <c r="M8">
-        <v>-5.7</v>
+        <v>-5.82</v>
       </c>
       <c r="N8">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="O8">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P8">
-        <v>661.04</v>
+        <v>660.88</v>
       </c>
       <c r="Q8">
-        <v>674.9</v>
+        <v>672.13</v>
       </c>
       <c r="R8">
-        <v>705.1900000000001</v>
+        <v>703.84</v>
       </c>
       <c r="S8">
-        <v>612.0700000000001</v>
+        <v>612.28</v>
       </c>
       <c r="T8">
-        <v>7.85</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="U8" t="s">
         <v>48</v>
@@ -1674,34 +1646,34 @@
         <v>2</v>
       </c>
       <c r="Y8">
-        <v>40.86</v>
+        <v>44.23</v>
       </c>
       <c r="Z8">
-        <v>-13.22</v>
+        <v>-12.12</v>
       </c>
       <c r="AA8">
-        <v>-13.38</v>
+        <v>-13.13</v>
       </c>
       <c r="AB8">
-        <v>0.16</v>
+        <v>1.01</v>
       </c>
       <c r="AC8">
-        <v>64.7</v>
+        <v>81.34</v>
       </c>
       <c r="AD8">
-        <v>57.57</v>
+        <v>66.61</v>
       </c>
       <c r="AE8">
-        <v>18.19</v>
+        <v>17.87</v>
       </c>
       <c r="AF8">
-        <v>-64.14</v>
+        <v>-7.77</v>
       </c>
       <c r="AG8">
-        <v>725.86</v>
+        <v>718.1799999999999</v>
       </c>
       <c r="AH8">
-        <v>623.9400000000001</v>
+        <v>626.0700000000001</v>
       </c>
       <c r="AI8">
         <v>713.42</v>
@@ -1710,7 +1682,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>29.74</v>
+        <v>26.14</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1721,10 +1693,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>196.13</v>
+        <v>192.86</v>
       </c>
       <c r="D9">
-        <v>-0.6899999999999999</v>
+        <v>-1.67</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1733,46 +1705,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-29.35</v>
+        <v>-30.53</v>
       </c>
       <c r="H9">
-        <v>13.83</v>
+        <v>11.93</v>
       </c>
       <c r="I9">
-        <v>3.06</v>
+        <v>1.19</v>
       </c>
       <c r="J9">
-        <v>3.23</v>
+        <v>1.84</v>
       </c>
       <c r="K9">
-        <v>-1.04</v>
+        <v>-1.67</v>
       </c>
       <c r="L9">
-        <v>-23.77</v>
+        <v>-23.92</v>
       </c>
       <c r="M9">
-        <v>-6.72</v>
+        <v>-7.06</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P9">
-        <v>195.03</v>
+        <v>195.48</v>
       </c>
       <c r="Q9">
-        <v>190.58</v>
+        <v>190.76</v>
       </c>
       <c r="R9">
-        <v>188.84</v>
+        <v>188.89</v>
       </c>
       <c r="S9">
-        <v>210.78</v>
+        <v>210.43</v>
       </c>
       <c r="T9">
-        <v>-6.95</v>
+        <v>-8.35</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1787,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>60.57</v>
+        <v>53.71</v>
       </c>
       <c r="Z9">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="AA9">
-        <v>0.84</v>
+        <v>1.02</v>
       </c>
       <c r="AB9">
-        <v>0.98</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AC9">
-        <v>94.13</v>
+        <v>75.53</v>
       </c>
       <c r="AD9">
-        <v>92.48</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="AE9">
-        <v>5.12</v>
+        <v>5.04</v>
       </c>
       <c r="AF9">
-        <v>-68.81999999999999</v>
+        <v>-62.63</v>
       </c>
       <c r="AG9">
-        <v>197.24</v>
+        <v>197.46</v>
       </c>
       <c r="AH9">
-        <v>183.93</v>
+        <v>184.07</v>
       </c>
       <c r="AI9">
         <v>197.85</v>
@@ -1823,7 +1795,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>50.56</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1834,10 +1806,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>76.14</v>
+        <v>76.95</v>
       </c>
       <c r="D10">
-        <v>-0.95</v>
+        <v>1.06</v>
       </c>
       <c r="E10">
         <v>150.86</v>
@@ -1846,46 +1818,46 @@
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-49.53</v>
+        <v>-48.99</v>
       </c>
       <c r="H10">
-        <v>28.44</v>
+        <v>29.81</v>
       </c>
       <c r="I10">
-        <v>-1.62</v>
+        <v>0.38</v>
       </c>
       <c r="J10">
-        <v>-8.220000000000001</v>
+        <v>-6.49</v>
       </c>
       <c r="K10">
-        <v>3.06</v>
+        <v>3.5</v>
       </c>
       <c r="L10">
-        <v>-44.54</v>
+        <v>-43.52</v>
       </c>
       <c r="M10">
-        <v>0.44</v>
+        <v>-0.77</v>
       </c>
       <c r="N10">
         <v>12</v>
       </c>
       <c r="O10">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P10">
-        <v>76.84</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="Q10">
-        <v>77.88</v>
+        <v>77.62</v>
       </c>
       <c r="R10">
-        <v>79.98999999999999</v>
+        <v>79.89</v>
       </c>
       <c r="S10">
-        <v>82.47</v>
+        <v>82.38</v>
       </c>
       <c r="T10">
-        <v>-7.67</v>
+        <v>-6.59</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1900,34 +1872,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>39.65</v>
+        <v>44.19</v>
       </c>
       <c r="Z10">
-        <v>-1</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AA10">
-        <v>-1</v>
+        <v>-0.99</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AC10">
-        <v>71.54000000000001</v>
+        <v>74.58</v>
       </c>
       <c r="AD10">
-        <v>73.37</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="AE10">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AF10">
-        <v>-54.73</v>
+        <v>-25.61</v>
       </c>
       <c r="AG10">
-        <v>81.86</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="AH10">
-        <v>73.89</v>
+        <v>74.14</v>
       </c>
       <c r="AI10">
         <v>74.97</v>
@@ -1936,7 +1908,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>16.55</v>
+        <v>15.94</v>
       </c>
     </row>
   </sheetData>
@@ -2097,47 +2069,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -2145,1278 +2082,1278 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="B6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-1.94</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-2.83</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-4.67</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-5.73</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-10.91</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-11.67</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-8.050000000000001</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-7.85</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-3.57</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-3</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-1.28</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-1.89</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-8.81</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-7.6</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="5">
+        <v>3.23</v>
+      </c>
+      <c r="D14" s="5">
+        <v>1.84</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-1.39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-8.220000000000001</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-6.49</v>
+      </c>
+      <c r="E15" s="7">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-2.89</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-3.24</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-1.89</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-1.79</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-1.86</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-1.3</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-1.18</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-2.26</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-1.08</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-1.4</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-0.45</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-2.96</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-2.76</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-1.12</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-0.12</v>
+      </c>
+      <c r="E22" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="5">
+        <v>3.06</v>
+      </c>
+      <c r="D23" s="5">
+        <v>1.19</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-1.87</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-1.62</v>
+      </c>
+      <c r="D24" s="5">
+        <v>0.38</v>
+      </c>
+      <c r="E24" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-23.73</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-25.21</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-1.48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>27.41</v>
+      </c>
+      <c r="D26" s="5">
+        <v>28.72</v>
+      </c>
+      <c r="E26" s="7">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>38.31</v>
+      </c>
+      <c r="D27" s="5">
+        <v>40.57</v>
+      </c>
+      <c r="E27" s="7">
+        <v>2.26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="5">
+        <v>21.54</v>
+      </c>
+      <c r="D28" s="5">
+        <v>23.35</v>
+      </c>
+      <c r="E28" s="7">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="5">
+        <v>80.34999999999999</v>
+      </c>
+      <c r="D29" s="5">
+        <v>80.33</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-28.46</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-29.3</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="5">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="D31" s="5">
+        <v>11.84</v>
+      </c>
+      <c r="E31" s="7">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-23.77</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-23.92</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="5">
+        <v>-44.54</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-43.52</v>
+      </c>
+      <c r="E33" s="7">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>1.37</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-1.38</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-2.75</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="5">
+        <v>25.2</v>
+      </c>
+      <c r="D35" s="5">
+        <v>19.97</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-5.23</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="5">
+        <v>4.66</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-0.05</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-4.71</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-0.01</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-3.6</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-3.59</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5">
+        <v>0.49</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-2.28</v>
+      </c>
+      <c r="E38" s="6">
+        <v>-2.77</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="5">
+        <v>1.41</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-2.81</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-4.22</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="5">
+        <v>11.68</v>
+      </c>
+      <c r="D40" s="5">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-1.81</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-1.04</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-1.67</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="5">
+        <v>3.06</v>
+      </c>
+      <c r="D42" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="E42" s="7">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-28.65</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-29.58</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-6.29</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-6.74</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-14.68</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-14.86</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="5">
+        <v>-10.74</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-11.42</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="5">
+        <v>-15.37</v>
+      </c>
+      <c r="D47" s="5">
+        <v>-16.03</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-0.66</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="5">
+        <v>-28.16</v>
+      </c>
+      <c r="D48" s="5">
+        <v>-28.07</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="5">
+        <v>-18.33</v>
+      </c>
+      <c r="D49" s="5">
+        <v>-17.58</v>
+      </c>
+      <c r="E49" s="7">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="5">
+        <v>-29.35</v>
+      </c>
+      <c r="D50" s="5">
+        <v>-30.53</v>
+      </c>
+      <c r="E50" s="6">
+        <v>-1.18</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="5">
+        <v>-49.53</v>
+      </c>
+      <c r="D51" s="5">
+        <v>-48.99</v>
+      </c>
+      <c r="E51" s="7">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="5">
+        <v>1357.6</v>
+      </c>
+      <c r="D52" s="5">
+        <v>1339.8</v>
+      </c>
+      <c r="E52" s="6">
+        <v>-17.8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="5">
+        <v>3010</v>
+      </c>
+      <c r="D53" s="5">
+        <v>2995.5</v>
+      </c>
+      <c r="E53" s="6">
+        <v>-14.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="5">
+        <v>1369</v>
+      </c>
+      <c r="D54" s="5">
+        <v>1366</v>
+      </c>
+      <c r="E54" s="6">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="5">
+        <v>1681</v>
+      </c>
+      <c r="D55" s="5">
+        <v>1668.2</v>
+      </c>
+      <c r="E55" s="6">
+        <v>-12.8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="5">
+        <v>210.65</v>
+      </c>
+      <c r="D56" s="5">
+        <v>209</v>
+      </c>
+      <c r="E56" s="6">
+        <v>-1.65</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="5">
+        <v>430.85</v>
+      </c>
+      <c r="D57" s="5">
+        <v>424</v>
+      </c>
+      <c r="E57" s="6">
+        <v>-6.85</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="5">
+        <v>660.1</v>
+      </c>
+      <c r="D58" s="5">
+        <v>666.15</v>
+      </c>
+      <c r="E58" s="7">
+        <v>6.05</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="5">
+        <v>196.13</v>
+      </c>
+      <c r="D59" s="5">
+        <v>192.86</v>
+      </c>
+      <c r="E59" s="6">
+        <v>-3.27</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="5">
+        <v>76.14</v>
+      </c>
+      <c r="D60" s="5">
+        <v>76.95</v>
+      </c>
+      <c r="E60" s="7">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="5">
         <v>66</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="D61" s="5">
+        <v>55</v>
+      </c>
+      <c r="E61" s="6">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="5">
+        <v>55</v>
+      </c>
+      <c r="D62" s="5">
+        <v>66</v>
+      </c>
+      <c r="E62" s="7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0.04</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-1.94</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-1.98</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="B63" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="5">
+        <v>47.82</v>
+      </c>
+      <c r="D63" s="5">
+        <v>43.91</v>
+      </c>
+      <c r="E63" s="6">
+        <v>-3.91</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-2.06</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-4.67</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-2.61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B64" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="5">
+        <v>44.94</v>
+      </c>
+      <c r="D64" s="5">
+        <v>43.34</v>
+      </c>
+      <c r="E64" s="6">
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-7.68</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-10.91</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-3.23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B65" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="5">
+        <v>37.75</v>
+      </c>
+      <c r="D65" s="5">
+        <v>37.29</v>
+      </c>
+      <c r="E65" s="6">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-5.92</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-8.050000000000001</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-2.13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B66" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="5">
+        <v>33.43</v>
+      </c>
+      <c r="D66" s="5">
+        <v>31.56</v>
+      </c>
+      <c r="E66" s="6">
+        <v>-1.87</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-3.38</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-3.57</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B67" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="5">
+        <v>44.02</v>
+      </c>
+      <c r="D67" s="5">
+        <v>41.86</v>
+      </c>
+      <c r="E67" s="6">
+        <v>-2.16</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>1.37</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-1.28</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-2.65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B68" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="5">
+        <v>48.36</v>
+      </c>
+      <c r="D68" s="5">
+        <v>44.3</v>
+      </c>
+      <c r="E68" s="6">
+        <v>-4.06</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-6.15</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-8.81</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-2.66</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B69" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="5">
+        <v>40.86</v>
+      </c>
+      <c r="D69" s="5">
+        <v>44.23</v>
+      </c>
+      <c r="E69" s="7">
+        <v>3.37</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>6.37</v>
-      </c>
-      <c r="D14" s="6">
-        <v>3.23</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-3.14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B70" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="5">
+        <v>60.57</v>
+      </c>
+      <c r="D70" s="5">
+        <v>53.71</v>
+      </c>
+      <c r="E70" s="6">
+        <v>-6.86</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-7.05</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-8.220000000000001</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-1.17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B71" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="5">
+        <v>39.65</v>
+      </c>
+      <c r="D71" s="5">
+        <v>44.19</v>
+      </c>
+      <c r="E71" s="7">
+        <v>4.54</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0.4</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-2.89</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-3.29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B72" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="5">
+        <v>-22.06</v>
+      </c>
+      <c r="D72" s="5">
+        <v>-34.82</v>
+      </c>
+      <c r="E72" s="6">
+        <v>-12.76</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0.35</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-1.89</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-2.24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B73" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="5">
+        <v>-30.02</v>
+      </c>
+      <c r="D73" s="5">
+        <v>29.85</v>
+      </c>
+      <c r="E73" s="7">
+        <v>59.87</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-0.77</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-1.86</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-1.09</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B74" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="5">
+        <v>-74.78</v>
+      </c>
+      <c r="D74" s="5">
+        <v>23.53</v>
+      </c>
+      <c r="E74" s="7">
+        <v>98.31</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-0.18</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-1.18</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B75" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="5">
+        <v>4.08</v>
+      </c>
+      <c r="D75" s="5">
+        <v>6.49</v>
+      </c>
+      <c r="E75" s="7">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-1.09</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-1.4</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B76" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="5">
+        <v>-46.11</v>
+      </c>
+      <c r="D76" s="5">
+        <v>-26.61</v>
+      </c>
+      <c r="E76" s="7">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>0.42</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-2.96</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-3.38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B77" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="5">
+        <v>-29.72</v>
+      </c>
+      <c r="D77" s="5">
+        <v>-42.07</v>
+      </c>
+      <c r="E77" s="6">
+        <v>-12.35</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-1.12</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-2.06</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B78" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="5">
+        <v>-64.14</v>
+      </c>
+      <c r="D78" s="5">
+        <v>-7.77</v>
+      </c>
+      <c r="E78" s="7">
+        <v>56.37</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>4.25</v>
-      </c>
-      <c r="D23" s="6">
-        <v>3.06</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-1.19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B79" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="5">
+        <v>-68.81999999999999</v>
+      </c>
+      <c r="D79" s="5">
+        <v>-62.63</v>
+      </c>
+      <c r="E79" s="7">
+        <v>6.19</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-0.3</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-1.62</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-1.32</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-23.62</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-23.73</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>28.52</v>
-      </c>
-      <c r="D26" s="6">
-        <v>27.41</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-1.11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>41.11</v>
-      </c>
-      <c r="D27" s="6">
-        <v>38.31</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-2.8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>26.24</v>
-      </c>
-      <c r="D28" s="6">
-        <v>21.54</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-4.7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>84.3</v>
-      </c>
-      <c r="D29" s="6">
-        <v>80.34999999999999</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-3.95</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-28.26</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-28.46</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>10.48</v>
-      </c>
-      <c r="D31" s="6">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-1.53</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-23.24</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-23.77</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-0.53</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-43.41</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-44.54</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-1.13</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="D34" s="6">
-        <v>1.37</v>
-      </c>
-      <c r="E34" s="8">
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>20.84</v>
-      </c>
-      <c r="D35" s="6">
-        <v>25.2</v>
-      </c>
-      <c r="E35" s="8">
-        <v>4.36</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-1.1</v>
-      </c>
-      <c r="D36" s="6">
-        <v>4.66</v>
-      </c>
-      <c r="E36" s="8">
-        <v>5.76</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-3.77</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-0.01</v>
-      </c>
-      <c r="E37" s="8">
-        <v>3.76</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-5.87</v>
-      </c>
-      <c r="D38" s="6">
-        <v>0.49</v>
-      </c>
-      <c r="E38" s="8">
-        <v>6.36</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-0.01</v>
-      </c>
-      <c r="D39" s="6">
-        <v>1.41</v>
-      </c>
-      <c r="E39" s="8">
-        <v>1.42</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>6.01</v>
-      </c>
-      <c r="D40" s="6">
-        <v>11.68</v>
-      </c>
-      <c r="E40" s="8">
-        <v>5.67</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-3.63</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-1.04</v>
-      </c>
-      <c r="E41" s="8">
-        <v>2.59</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-0.5</v>
-      </c>
-      <c r="D42" s="6">
-        <v>3.06</v>
-      </c>
-      <c r="E42" s="8">
-        <v>3.56</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-28.38</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-28.65</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-5.98</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-6.29</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-0.31</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-14.47</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-14.68</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-0.21</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-10.07</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-10.74</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-0.67</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-16.03</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-15.37</v>
-      </c>
-      <c r="E47" s="8">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-27.94</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-28.16</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-0.22</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-18.65</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-18.33</v>
-      </c>
-      <c r="E49" s="8">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-28.85</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-29.35</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-49.05</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-49.53</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-0.48</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="6">
-        <v>1362.8</v>
-      </c>
-      <c r="D52" s="6">
-        <v>1357.6</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-5.2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>3020</v>
-      </c>
-      <c r="D53" s="6">
-        <v>3010</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>1372.4</v>
-      </c>
-      <c r="D54" s="6">
-        <v>1369</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-3.4</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>1693.5</v>
-      </c>
-      <c r="D55" s="6">
-        <v>1681</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-12.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>209</v>
-      </c>
-      <c r="D56" s="6">
-        <v>210.65</v>
-      </c>
-      <c r="E56" s="8">
-        <v>1.65</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>434</v>
-      </c>
-      <c r="D57" s="6">
-        <v>430.85</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-3.15</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>657.55</v>
-      </c>
-      <c r="D58" s="6">
-        <v>660.1</v>
-      </c>
-      <c r="E58" s="8">
-        <v>2.55</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>197.5</v>
-      </c>
-      <c r="D59" s="6">
-        <v>196.13</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-1.37</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="6">
-        <v>76.87</v>
-      </c>
-      <c r="D60" s="6">
-        <v>76.14</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-0.73</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" s="6">
-        <v>45</v>
-      </c>
-      <c r="D61" s="6">
-        <v>34</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="6">
-        <v>34</v>
-      </c>
-      <c r="D62" s="6">
-        <v>45</v>
-      </c>
-      <c r="E62" s="8">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="6">
-        <v>49</v>
-      </c>
-      <c r="D63" s="6">
-        <v>47.82</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="6">
-        <v>46.03</v>
-      </c>
-      <c r="D64" s="6">
-        <v>44.94</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-1.09</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>38.24</v>
-      </c>
-      <c r="D65" s="6">
-        <v>37.75</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-0.49</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>35.33</v>
-      </c>
-      <c r="D66" s="6">
-        <v>33.43</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-1.9</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>41.21</v>
-      </c>
-      <c r="D67" s="6">
-        <v>44.02</v>
-      </c>
-      <c r="E67" s="8">
-        <v>2.81</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>50.33</v>
-      </c>
-      <c r="D68" s="6">
-        <v>48.36</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-1.97</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="6">
-        <v>39.43</v>
-      </c>
-      <c r="D69" s="6">
-        <v>40.86</v>
-      </c>
-      <c r="E69" s="8">
-        <v>1.43</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="6">
-        <v>63.73</v>
-      </c>
-      <c r="D70" s="6">
-        <v>60.57</v>
-      </c>
-      <c r="E70" s="7">
-        <v>-3.16</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="6">
-        <v>42.54</v>
-      </c>
-      <c r="D71" s="6">
-        <v>39.65</v>
-      </c>
-      <c r="E71" s="7">
-        <v>-2.89</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B72" s="5" t="s">
+      <c r="B80" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C72" s="6">
-        <v>-19.54</v>
-      </c>
-      <c r="D72" s="6">
-        <v>-22.06</v>
-      </c>
-      <c r="E72" s="7">
-        <v>-2.52</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="6">
-        <v>-36.68</v>
-      </c>
-      <c r="D73" s="6">
-        <v>-30.02</v>
-      </c>
-      <c r="E73" s="8">
-        <v>6.66</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="6">
-        <v>-52.84</v>
-      </c>
-      <c r="D74" s="6">
-        <v>-74.78</v>
-      </c>
-      <c r="E74" s="7">
-        <v>-21.94</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="6">
-        <v>17.56</v>
-      </c>
-      <c r="D75" s="6">
-        <v>4.08</v>
-      </c>
-      <c r="E75" s="7">
-        <v>-13.48</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>-41.84</v>
-      </c>
-      <c r="D76" s="6">
-        <v>-46.11</v>
-      </c>
-      <c r="E76" s="7">
-        <v>-4.27</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>-19.52</v>
-      </c>
-      <c r="D77" s="6">
-        <v>-29.72</v>
-      </c>
-      <c r="E77" s="7">
-        <v>-10.2</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>-69.69</v>
-      </c>
-      <c r="D78" s="6">
-        <v>-64.14</v>
-      </c>
-      <c r="E78" s="8">
-        <v>5.55</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>6.72</v>
-      </c>
-      <c r="D79" s="6">
-        <v>-68.81999999999999</v>
-      </c>
-      <c r="E79" s="7">
-        <v>-75.54000000000001</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>-76.91</v>
-      </c>
-      <c r="D80" s="6">
+      <c r="C80" s="5">
         <v>-54.73</v>
       </c>
-      <c r="E80" s="8">
-        <v>22.18</v>
+      <c r="D80" s="5">
+        <v>-25.61</v>
+      </c>
+      <c r="E80" s="7">
+        <v>29.12</v>
       </c>
     </row>
   </sheetData>
@@ -3442,60 +3379,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>74</v>
+      <c r="B1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>56.16</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
-        <v>44.2</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>42.7</v>
+      </c>
+      <c r="E2" s="10">
         <v>60</v>
       </c>
-      <c r="F2" s="11">
-        <v>-4.9</v>
-      </c>
-      <c r="G2" s="11">
-        <v>5.2</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-5</v>
+      </c>
+      <c r="G2" s="10">
+        <v>2.4</v>
+      </c>
+      <c r="H2" s="10">
         <v>55.4</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>10</v>
       </c>
     </row>
@@ -3597,61 +3534,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>0.6512</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.2004</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1584</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.08550000000000001</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.0225</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.0044</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.057</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.0672</v>
-      </c>
-      <c r="I2" s="14">
-        <v>-0.0917</v>
+      <c r="A2" s="13">
+        <v>0.6581</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.1964</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.1588</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.0867</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.0204</v>
+      </c>
+      <c r="F2" s="13">
+        <v>-0.0077</v>
+      </c>
+      <c r="G2" s="13">
+        <v>-0.0582</v>
+      </c>
+      <c r="H2" s="13">
+        <v>-0.0706</v>
+      </c>
+      <c r="I2" s="13">
+        <v>-0.0924</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="66">
   <si>
     <t>Symbol</t>
   </si>
@@ -264,14 +264,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -304,13 +304,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -902,10 +902,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1339.8</v>
+        <v>1332.8</v>
       </c>
       <c r="D2">
-        <v>-1.31</v>
+        <v>-0.52</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -914,46 +914,46 @@
         <v>1247.38</v>
       </c>
       <c r="G2">
-        <v>-29.58</v>
+        <v>-29.95</v>
       </c>
       <c r="H2">
-        <v>7.41</v>
+        <v>6.85</v>
       </c>
       <c r="I2">
-        <v>-3.24</v>
+        <v>-4.39</v>
       </c>
       <c r="J2">
-        <v>-2.83</v>
+        <v>-2.14</v>
       </c>
       <c r="K2">
-        <v>-1.38</v>
+        <v>-2.73</v>
       </c>
       <c r="L2">
-        <v>-25.21</v>
+        <v>-26.76</v>
       </c>
       <c r="M2">
-        <v>-9.24</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="P2">
-        <v>1366.52</v>
+        <v>1354.28</v>
       </c>
       <c r="Q2">
-        <v>1366.86</v>
+        <v>1364.34</v>
       </c>
       <c r="R2">
-        <v>1354.82</v>
+        <v>1354.24</v>
       </c>
       <c r="S2">
-        <v>1540.63</v>
+        <v>1538.07</v>
       </c>
       <c r="T2">
-        <v>-13.04</v>
+        <v>-13.35</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -968,34 +968,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>43.91</v>
+        <v>42.43</v>
       </c>
       <c r="Z2">
-        <v>0.37</v>
+        <v>-2.21</v>
       </c>
       <c r="AA2">
-        <v>2.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB2">
-        <v>-2.33</v>
+        <v>-3.93</v>
       </c>
       <c r="AC2">
-        <v>26.15</v>
+        <v>12.77</v>
       </c>
       <c r="AD2">
-        <v>45.59</v>
+        <v>28.18</v>
       </c>
       <c r="AE2">
-        <v>28.56</v>
+        <v>28.3</v>
       </c>
       <c r="AF2">
-        <v>-34.82</v>
+        <v>-33.52</v>
       </c>
       <c r="AG2">
-        <v>1404.71</v>
+        <v>1404.26</v>
       </c>
       <c r="AH2">
-        <v>1329</v>
+        <v>1324.41</v>
       </c>
       <c r="AI2">
         <v>1318.07</v>
@@ -1004,7 +1004,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>17.55</v>
+        <v>19.89</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1015,10 +1015,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2995.5</v>
+        <v>2985.7</v>
       </c>
       <c r="D3">
-        <v>-0.48</v>
+        <v>-0.33</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1027,46 +1027,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-6.74</v>
+        <v>-7.05</v>
       </c>
       <c r="H3">
-        <v>70.39</v>
+        <v>69.83</v>
       </c>
       <c r="I3">
-        <v>-1.79</v>
+        <v>-2.11</v>
       </c>
       <c r="J3">
-        <v>-5.73</v>
+        <v>-6.37</v>
       </c>
       <c r="K3">
-        <v>19.97</v>
+        <v>10.1</v>
       </c>
       <c r="L3">
-        <v>28.72</v>
+        <v>29.85</v>
       </c>
       <c r="M3">
-        <v>15.88</v>
+        <v>15.71</v>
       </c>
       <c r="N3">
         <v>88</v>
       </c>
       <c r="O3">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="P3">
-        <v>3020.3</v>
+        <v>3007.44</v>
       </c>
       <c r="Q3">
-        <v>3067.72</v>
+        <v>3059.47</v>
       </c>
       <c r="R3">
-        <v>3049.79</v>
+        <v>3050.17</v>
       </c>
       <c r="S3">
-        <v>2461.29</v>
+        <v>2463.5</v>
       </c>
       <c r="T3">
-        <v>21.7</v>
+        <v>21.2</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1081,34 +1081,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>43.34</v>
+        <v>42.25</v>
       </c>
       <c r="Z3">
-        <v>-11.31</v>
+        <v>-14.46</v>
       </c>
       <c r="AA3">
-        <v>0.96</v>
+        <v>-2.12</v>
       </c>
       <c r="AB3">
-        <v>-12.27</v>
+        <v>-12.33</v>
       </c>
       <c r="AC3">
-        <v>7.37</v>
+        <v>3</v>
       </c>
       <c r="AD3">
-        <v>13.51</v>
+        <v>7.76</v>
       </c>
       <c r="AE3">
-        <v>66.90000000000001</v>
+        <v>67.62</v>
       </c>
       <c r="AF3">
-        <v>29.85</v>
+        <v>6.7</v>
       </c>
       <c r="AG3">
-        <v>3201.15</v>
+        <v>3191.72</v>
       </c>
       <c r="AH3">
-        <v>2934.28</v>
+        <v>2927.22</v>
       </c>
       <c r="AI3">
         <v>2959.69</v>
@@ -1117,7 +1117,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>27.31</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1128,10 +1128,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1366</v>
+        <v>1332.3</v>
       </c>
       <c r="D4">
-        <v>-0.22</v>
+        <v>-2.47</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1140,46 +1140,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-14.86</v>
+        <v>-16.96</v>
       </c>
       <c r="H4">
-        <v>76.76000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I4">
-        <v>-1.3</v>
+        <v>-3.46</v>
       </c>
       <c r="J4">
-        <v>-11.67</v>
+        <v>-16.96</v>
       </c>
       <c r="K4">
-        <v>-0.05</v>
+        <v>-5.84</v>
       </c>
       <c r="L4">
-        <v>40.57</v>
+        <v>39.14</v>
       </c>
       <c r="M4">
-        <v>8.67</v>
+        <v>7.84</v>
       </c>
       <c r="N4">
         <v>77</v>
       </c>
       <c r="O4">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="P4">
-        <v>1371.78</v>
+        <v>1362.24</v>
       </c>
       <c r="Q4">
-        <v>1423.12</v>
+        <v>1411.97</v>
       </c>
       <c r="R4">
-        <v>1473.55</v>
+        <v>1471.2</v>
       </c>
       <c r="S4">
-        <v>1155.65</v>
+        <v>1157.08</v>
       </c>
       <c r="T4">
-        <v>18.2</v>
+        <v>15.14</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1194,43 +1194,43 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>37.29</v>
+        <v>32.53</v>
       </c>
       <c r="Z4">
-        <v>-33.55</v>
+        <v>-35.65</v>
       </c>
       <c r="AA4">
-        <v>-29.5</v>
+        <v>-30.73</v>
       </c>
       <c r="AB4">
-        <v>-4.05</v>
+        <v>-4.92</v>
       </c>
       <c r="AC4">
-        <v>31.18</v>
+        <v>24.94</v>
       </c>
       <c r="AD4">
-        <v>24.63</v>
+        <v>26.3</v>
       </c>
       <c r="AE4">
-        <v>43.91</v>
+        <v>44.77</v>
       </c>
       <c r="AF4">
-        <v>23.53</v>
+        <v>-18.24</v>
       </c>
       <c r="AG4">
-        <v>1566.28</v>
+        <v>1546.22</v>
       </c>
       <c r="AH4">
-        <v>1279.96</v>
+        <v>1277.71</v>
       </c>
       <c r="AI4">
-        <v>1493.56</v>
+        <v>1477.32</v>
       </c>
       <c r="AJ4" t="s">
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>26.45</v>
+        <v>25.53</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1241,10 +1241,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1668.2</v>
+        <v>1665</v>
       </c>
       <c r="D5">
-        <v>-0.76</v>
+        <v>-0.19</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1253,46 +1253,46 @@
         <v>1294.84</v>
       </c>
       <c r="G5">
-        <v>-11.42</v>
+        <v>-11.59</v>
       </c>
       <c r="H5">
-        <v>28.83</v>
+        <v>28.59</v>
       </c>
       <c r="I5">
-        <v>-2.26</v>
+        <v>-2.06</v>
       </c>
       <c r="J5">
-        <v>-7.85</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="K5">
-        <v>-3.6</v>
+        <v>-5.72</v>
       </c>
       <c r="L5">
-        <v>23.35</v>
+        <v>22.3</v>
       </c>
       <c r="M5">
-        <v>19.64</v>
+        <v>19.43</v>
       </c>
       <c r="N5">
         <v>55</v>
       </c>
       <c r="O5">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="P5">
-        <v>1687.54</v>
+        <v>1680.54</v>
       </c>
       <c r="Q5">
-        <v>1751.02</v>
+        <v>1742.81</v>
       </c>
       <c r="R5">
-        <v>1790.83</v>
+        <v>1787.99</v>
       </c>
       <c r="S5">
-        <v>1581.4</v>
+        <v>1582.49</v>
       </c>
       <c r="T5">
-        <v>5.49</v>
+        <v>5.21</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1307,43 +1307,43 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>31.56</v>
+        <v>31.1</v>
       </c>
       <c r="Z5">
-        <v>-34.92</v>
+        <v>-35.94</v>
       </c>
       <c r="AA5">
-        <v>-27.39</v>
+        <v>-29.1</v>
       </c>
       <c r="AB5">
-        <v>-7.53</v>
+        <v>-6.84</v>
       </c>
       <c r="AC5">
-        <v>27.19</v>
+        <v>26.26</v>
       </c>
       <c r="AD5">
-        <v>27.75</v>
+        <v>26.93</v>
       </c>
       <c r="AE5">
-        <v>35.94</v>
+        <v>35.68</v>
       </c>
       <c r="AF5">
-        <v>6.49</v>
+        <v>-31.38</v>
       </c>
       <c r="AG5">
-        <v>1881.17</v>
+        <v>1872.92</v>
       </c>
       <c r="AH5">
-        <v>1620.87</v>
+        <v>1612.71</v>
       </c>
       <c r="AI5">
-        <v>1788.08</v>
+        <v>1763.6</v>
       </c>
       <c r="AJ5" t="s">
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>55.17</v>
+        <v>55.4</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1354,58 +1354,58 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>209</v>
+        <v>206.99</v>
       </c>
       <c r="D6">
-        <v>-0.78</v>
+        <v>-0.96</v>
       </c>
       <c r="E6">
         <v>248.91</v>
       </c>
       <c r="F6">
-        <v>113.49</v>
+        <v>115.38</v>
       </c>
       <c r="G6">
-        <v>-16.03</v>
+        <v>-16.84</v>
       </c>
       <c r="H6">
-        <v>84.16</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I6">
-        <v>-0.45</v>
+        <v>-0.96</v>
       </c>
       <c r="J6">
-        <v>-3</v>
+        <v>-8.48</v>
       </c>
       <c r="K6">
-        <v>-2.28</v>
+        <v>-7.8</v>
       </c>
       <c r="L6">
-        <v>80.33</v>
+        <v>82.39</v>
       </c>
       <c r="M6">
-        <v>65.81</v>
+        <v>64.87</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P6">
-        <v>209.15</v>
+        <v>208.75</v>
       </c>
       <c r="Q6">
-        <v>212.73</v>
+        <v>212.13</v>
       </c>
       <c r="R6">
-        <v>220.03</v>
+        <v>219.45</v>
       </c>
       <c r="S6">
-        <v>178.36</v>
+        <v>178.57</v>
       </c>
       <c r="T6">
-        <v>17.18</v>
+        <v>15.92</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1420,43 +1420,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>41.86</v>
+        <v>39.34</v>
       </c>
       <c r="Z6">
-        <v>-3.1</v>
+        <v>-3.17</v>
       </c>
       <c r="AA6">
         <v>-3.15</v>
       </c>
       <c r="AB6">
-        <v>0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="AC6">
-        <v>53.68</v>
+        <v>49.84</v>
       </c>
       <c r="AD6">
-        <v>40.64</v>
+        <v>48.72</v>
       </c>
       <c r="AE6">
-        <v>5.34</v>
+        <v>5.29</v>
       </c>
       <c r="AF6">
-        <v>-26.61</v>
+        <v>-40.56</v>
       </c>
       <c r="AG6">
-        <v>220.81</v>
+        <v>220.04</v>
       </c>
       <c r="AH6">
-        <v>204.64</v>
+        <v>204.22</v>
       </c>
       <c r="AI6">
-        <v>225</v>
+        <v>223.23</v>
       </c>
       <c r="AJ6" t="s">
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>20.94</v>
+        <v>21.12</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1467,10 +1467,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="D7">
-        <v>-1.59</v>
+        <v>-0.71</v>
       </c>
       <c r="E7">
         <v>589.48</v>
@@ -1479,46 +1479,46 @@
         <v>393.4</v>
       </c>
       <c r="G7">
-        <v>-28.07</v>
+        <v>-28.58</v>
       </c>
       <c r="H7">
-        <v>7.78</v>
+        <v>7.02</v>
       </c>
       <c r="I7">
-        <v>-2.76</v>
+        <v>-5.39</v>
       </c>
       <c r="J7">
-        <v>-1.89</v>
+        <v>-2.05</v>
       </c>
       <c r="K7">
-        <v>-2.81</v>
+        <v>-4.69</v>
       </c>
       <c r="L7">
-        <v>-29.3</v>
+        <v>-28.28</v>
       </c>
       <c r="M7">
-        <v>2.04</v>
+        <v>1.82</v>
       </c>
       <c r="N7">
         <v>23</v>
       </c>
       <c r="O7">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="P7">
-        <v>434.07</v>
+        <v>429.27</v>
       </c>
       <c r="Q7">
-        <v>433.73</v>
+        <v>433.01</v>
       </c>
       <c r="R7">
-        <v>428.59</v>
+        <v>428.27</v>
       </c>
       <c r="S7">
-        <v>481.84</v>
+        <v>481.14</v>
       </c>
       <c r="T7">
-        <v>-12</v>
+        <v>-12.5</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1533,34 +1533,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>44.3</v>
+        <v>42.61</v>
       </c>
       <c r="Z7">
-        <v>0.46</v>
+        <v>-0.55</v>
       </c>
       <c r="AA7">
-        <v>1.31</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AB7">
-        <v>-0.86</v>
+        <v>-1.49</v>
       </c>
       <c r="AC7">
-        <v>22.24</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="AD7">
-        <v>41.61</v>
+        <v>23.55</v>
       </c>
       <c r="AE7">
-        <v>10.45</v>
+        <v>10.32</v>
       </c>
       <c r="AF7">
-        <v>-42.07</v>
+        <v>114.39</v>
       </c>
       <c r="AG7">
-        <v>445.86</v>
+        <v>446.38</v>
       </c>
       <c r="AH7">
-        <v>421.59</v>
+        <v>419.65</v>
       </c>
       <c r="AI7">
         <v>411.2</v>
@@ -1569,7 +1569,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>16.08</v>
+        <v>18.67</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1580,10 +1580,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>666.15</v>
+        <v>660.35</v>
       </c>
       <c r="D8">
-        <v>0.92</v>
+        <v>-0.87</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1592,46 +1592,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-17.58</v>
+        <v>-18.3</v>
       </c>
       <c r="H8">
-        <v>42.42</v>
+        <v>41.18</v>
       </c>
       <c r="I8">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>-7.6</v>
+        <v>-8.49</v>
       </c>
       <c r="K8">
-        <v>9.869999999999999</v>
+        <v>7.83</v>
       </c>
       <c r="L8">
-        <v>11.84</v>
+        <v>12.15</v>
       </c>
       <c r="M8">
-        <v>-5.82</v>
+        <v>-6.14</v>
       </c>
       <c r="N8">
         <v>66</v>
       </c>
       <c r="O8">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="P8">
         <v>660.88</v>
       </c>
       <c r="Q8">
-        <v>672.13</v>
+        <v>669.37</v>
       </c>
       <c r="R8">
-        <v>703.84</v>
+        <v>702.29</v>
       </c>
       <c r="S8">
-        <v>612.28</v>
+        <v>612.47</v>
       </c>
       <c r="T8">
-        <v>8.800000000000001</v>
+        <v>7.82</v>
       </c>
       <c r="U8" t="s">
         <v>48</v>
@@ -1646,34 +1646,34 @@
         <v>2</v>
       </c>
       <c r="Y8">
-        <v>44.23</v>
+        <v>41.78</v>
       </c>
       <c r="Z8">
-        <v>-12.12</v>
+        <v>-11.57</v>
       </c>
       <c r="AA8">
-        <v>-13.13</v>
+        <v>-12.82</v>
       </c>
       <c r="AB8">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AC8">
-        <v>81.34</v>
+        <v>88</v>
       </c>
       <c r="AD8">
-        <v>66.61</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="AE8">
-        <v>17.87</v>
+        <v>17.55</v>
       </c>
       <c r="AF8">
-        <v>-7.77</v>
+        <v>-15.28</v>
       </c>
       <c r="AG8">
-        <v>718.1799999999999</v>
+        <v>710.9</v>
       </c>
       <c r="AH8">
-        <v>626.0700000000001</v>
+        <v>627.85</v>
       </c>
       <c r="AI8">
         <v>713.42</v>
@@ -1682,7 +1682,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>26.14</v>
+        <v>24.97</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1693,10 +1693,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>192.86</v>
+        <v>194.24</v>
       </c>
       <c r="D9">
-        <v>-1.67</v>
+        <v>0.72</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1705,46 +1705,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-30.53</v>
+        <v>-30.03</v>
       </c>
       <c r="H9">
-        <v>11.93</v>
+        <v>12.73</v>
       </c>
       <c r="I9">
-        <v>1.19</v>
+        <v>0.36</v>
       </c>
       <c r="J9">
-        <v>1.84</v>
+        <v>2.63</v>
       </c>
       <c r="K9">
-        <v>-1.67</v>
+        <v>-3.27</v>
       </c>
       <c r="L9">
-        <v>-23.92</v>
+        <v>-23.19</v>
       </c>
       <c r="M9">
-        <v>-7.06</v>
+        <v>-6.91</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P9">
-        <v>195.48</v>
+        <v>195.62</v>
       </c>
       <c r="Q9">
-        <v>190.76</v>
+        <v>191.03</v>
       </c>
       <c r="R9">
-        <v>188.89</v>
+        <v>188.96</v>
       </c>
       <c r="S9">
-        <v>210.43</v>
+        <v>210.1</v>
       </c>
       <c r="T9">
-        <v>-8.35</v>
+        <v>-7.55</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>53.71</v>
+        <v>55.97</v>
       </c>
       <c r="Z9">
         <v>1.71</v>
       </c>
       <c r="AA9">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="AB9">
-        <v>0.6899999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="AC9">
-        <v>75.53</v>
+        <v>61.14</v>
       </c>
       <c r="AD9">
-        <v>89.40000000000001</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="AE9">
-        <v>5.04</v>
+        <v>4.95</v>
       </c>
       <c r="AF9">
-        <v>-62.63</v>
+        <v>-48.2</v>
       </c>
       <c r="AG9">
-        <v>197.46</v>
+        <v>197.84</v>
       </c>
       <c r="AH9">
-        <v>184.07</v>
+        <v>184.22</v>
       </c>
       <c r="AI9">
         <v>197.85</v>
@@ -1795,7 +1795,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>49.3</v>
+        <v>47.12</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1806,10 +1806,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>76.95</v>
+        <v>76.11</v>
       </c>
       <c r="D10">
-        <v>1.06</v>
+        <v>-1.09</v>
       </c>
       <c r="E10">
         <v>150.86</v>
@@ -1818,46 +1818,46 @@
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-48.99</v>
+        <v>-49.55</v>
       </c>
       <c r="H10">
-        <v>29.81</v>
+        <v>28.39</v>
       </c>
       <c r="I10">
-        <v>0.38</v>
+        <v>-1.37</v>
       </c>
       <c r="J10">
-        <v>-6.49</v>
+        <v>-7.23</v>
       </c>
       <c r="K10">
-        <v>3.5</v>
+        <v>-1.76</v>
       </c>
       <c r="L10">
-        <v>-43.52</v>
+        <v>-42.99</v>
       </c>
       <c r="M10">
-        <v>-0.77</v>
+        <v>-1.15</v>
       </c>
       <c r="N10">
         <v>12</v>
       </c>
       <c r="O10">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="P10">
-        <v>76.90000000000001</v>
+        <v>76.69</v>
       </c>
       <c r="Q10">
-        <v>77.62</v>
+        <v>77.36</v>
       </c>
       <c r="R10">
-        <v>79.89</v>
+        <v>79.77</v>
       </c>
       <c r="S10">
-        <v>82.38</v>
+        <v>82.28</v>
       </c>
       <c r="T10">
-        <v>-6.59</v>
+        <v>-7.5</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1872,34 +1872,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>44.19</v>
+        <v>40.76</v>
       </c>
       <c r="Z10">
-        <v>-0.9399999999999999</v>
+        <v>-0.95</v>
       </c>
       <c r="AA10">
-        <v>-0.99</v>
+        <v>-0.98</v>
       </c>
       <c r="AB10">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="AC10">
-        <v>74.58</v>
+        <v>63.8</v>
       </c>
       <c r="AD10">
-        <v>74.81999999999999</v>
+        <v>69.97</v>
       </c>
       <c r="AE10">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AF10">
-        <v>-25.61</v>
+        <v>-23.76</v>
       </c>
       <c r="AG10">
-        <v>81.09999999999999</v>
+        <v>80.41</v>
       </c>
       <c r="AH10">
-        <v>74.14</v>
+        <v>74.3</v>
       </c>
       <c r="AI10">
         <v>74.97</v>
@@ -1908,7 +1908,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>15.94</v>
+        <v>14.99</v>
       </c>
     </row>
   </sheetData>
@@ -2049,7 +2049,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2106,13 +2106,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-1.94</v>
+        <v>-2.83</v>
       </c>
       <c r="D7" s="5">
-        <v>-2.83</v>
+        <v>-2.14</v>
       </c>
       <c r="E7" s="6">
-        <v>-0.89</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2123,13 +2123,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-4.67</v>
+        <v>-5.73</v>
       </c>
       <c r="D8" s="5">
-        <v>-5.73</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-1.06</v>
+        <v>-6.37</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-0.64</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2140,13 +2140,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-10.91</v>
+        <v>-11.67</v>
       </c>
       <c r="D9" s="5">
-        <v>-11.67</v>
-      </c>
-      <c r="E9" s="6">
-        <v>-0.76</v>
+        <v>-16.96</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-5.29</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2157,13 +2157,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-8.050000000000001</v>
+        <v>-7.85</v>
       </c>
       <c r="D10" s="5">
-        <v>-7.85</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="E10" s="7">
-        <v>0.2</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2174,13 +2174,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-3.57</v>
+        <v>-3</v>
       </c>
       <c r="D11" s="5">
-        <v>-3</v>
+        <v>-8.48</v>
       </c>
       <c r="E11" s="7">
-        <v>0.57</v>
+        <v>-5.48</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2191,13 +2191,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="5">
-        <v>-1.28</v>
+        <v>-1.89</v>
       </c>
       <c r="D12" s="5">
-        <v>-1.89</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-0.61</v>
+        <v>-2.05</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2208,13 +2208,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="5">
-        <v>-8.81</v>
+        <v>-7.6</v>
       </c>
       <c r="D13" s="5">
-        <v>-7.6</v>
+        <v>-8.49</v>
       </c>
       <c r="E13" s="7">
-        <v>1.21</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2225,13 +2225,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="5">
-        <v>3.23</v>
+        <v>1.84</v>
       </c>
       <c r="D14" s="5">
-        <v>1.84</v>
+        <v>2.63</v>
       </c>
       <c r="E14" s="6">
-        <v>-1.39</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2242,13 +2242,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="5">
-        <v>-8.220000000000001</v>
+        <v>-6.49</v>
       </c>
       <c r="D15" s="5">
-        <v>-6.49</v>
+        <v>-7.23</v>
       </c>
       <c r="E15" s="7">
-        <v>1.73</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2259,13 +2259,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>-2.89</v>
+        <v>-3.24</v>
       </c>
       <c r="D16" s="5">
-        <v>-3.24</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-0.35</v>
+        <v>-4.39</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-1.15</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2276,13 +2276,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="5">
-        <v>-1.89</v>
+        <v>-1.79</v>
       </c>
       <c r="D17" s="5">
-        <v>-1.79</v>
+        <v>-2.11</v>
       </c>
       <c r="E17" s="7">
-        <v>0.1</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2293,13 +2293,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="5">
-        <v>-1.86</v>
+        <v>-1.3</v>
       </c>
       <c r="D18" s="5">
-        <v>-1.3</v>
+        <v>-3.46</v>
       </c>
       <c r="E18" s="7">
-        <v>0.5600000000000001</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2310,13 +2310,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="5">
-        <v>-1.18</v>
+        <v>-2.26</v>
       </c>
       <c r="D19" s="5">
-        <v>-2.26</v>
+        <v>-2.06</v>
       </c>
       <c r="E19" s="6">
-        <v>-1.08</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2327,13 +2327,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="5">
-        <v>-1.4</v>
+        <v>-0.45</v>
       </c>
       <c r="D20" s="5">
-        <v>-0.45</v>
+        <v>-0.96</v>
       </c>
       <c r="E20" s="7">
-        <v>0.95</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2344,13 +2344,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="5">
-        <v>-2.96</v>
+        <v>-2.76</v>
       </c>
       <c r="D21" s="5">
-        <v>-2.76</v>
+        <v>-5.39</v>
       </c>
       <c r="E21" s="7">
-        <v>0.2</v>
+        <v>-2.63</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2361,13 +2361,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="5">
-        <v>-1.12</v>
+        <v>-0.12</v>
       </c>
       <c r="D22" s="5">
-        <v>-0.12</v>
-      </c>
-      <c r="E22" s="7">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E22" s="6">
+        <v>0.12</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2378,13 +2378,13 @@
         <v>8</v>
       </c>
       <c r="C23" s="5">
-        <v>3.06</v>
+        <v>1.19</v>
       </c>
       <c r="D23" s="5">
-        <v>1.19</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-1.87</v>
+        <v>0.36</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.83</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2395,13 +2395,13 @@
         <v>8</v>
       </c>
       <c r="C24" s="5">
-        <v>-1.62</v>
+        <v>0.38</v>
       </c>
       <c r="D24" s="5">
-        <v>0.38</v>
+        <v>-1.37</v>
       </c>
       <c r="E24" s="7">
-        <v>2</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2412,13 +2412,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="5">
-        <v>-23.73</v>
+        <v>-25.21</v>
       </c>
       <c r="D25" s="5">
-        <v>-25.21</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-1.48</v>
+        <v>-26.76</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1.55</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2429,13 +2429,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="5">
-        <v>27.41</v>
+        <v>28.72</v>
       </c>
       <c r="D26" s="5">
-        <v>28.72</v>
-      </c>
-      <c r="E26" s="7">
-        <v>1.31</v>
+        <v>29.85</v>
+      </c>
+      <c r="E26" s="6">
+        <v>1.13</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2446,13 +2446,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="5">
-        <v>38.31</v>
+        <v>40.57</v>
       </c>
       <c r="D27" s="5">
-        <v>40.57</v>
+        <v>39.14</v>
       </c>
       <c r="E27" s="7">
-        <v>2.26</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2463,13 +2463,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="5">
-        <v>21.54</v>
+        <v>23.35</v>
       </c>
       <c r="D28" s="5">
-        <v>23.35</v>
+        <v>22.3</v>
       </c>
       <c r="E28" s="7">
-        <v>1.81</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2480,13 +2480,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="5">
-        <v>80.34999999999999</v>
+        <v>80.33</v>
       </c>
       <c r="D29" s="5">
-        <v>80.33</v>
+        <v>82.39</v>
       </c>
       <c r="E29" s="6">
-        <v>-0.02</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2497,13 +2497,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="5">
-        <v>-28.46</v>
+        <v>-29.3</v>
       </c>
       <c r="D30" s="5">
-        <v>-29.3</v>
+        <v>-28.28</v>
       </c>
       <c r="E30" s="6">
-        <v>-0.84</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2514,13 +2514,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="5">
-        <v>8.949999999999999</v>
+        <v>11.84</v>
       </c>
       <c r="D31" s="5">
-        <v>11.84</v>
-      </c>
-      <c r="E31" s="7">
-        <v>2.89</v>
+        <v>12.15</v>
+      </c>
+      <c r="E31" s="6">
+        <v>0.31</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2531,13 +2531,13 @@
         <v>11</v>
       </c>
       <c r="C32" s="5">
-        <v>-23.77</v>
+        <v>-23.92</v>
       </c>
       <c r="D32" s="5">
-        <v>-23.92</v>
+        <v>-23.19</v>
       </c>
       <c r="E32" s="6">
-        <v>-0.15</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2548,13 +2548,13 @@
         <v>11</v>
       </c>
       <c r="C33" s="5">
-        <v>-44.54</v>
+        <v>-43.52</v>
       </c>
       <c r="D33" s="5">
-        <v>-43.52</v>
-      </c>
-      <c r="E33" s="7">
-        <v>1.02</v>
+        <v>-42.99</v>
+      </c>
+      <c r="E33" s="6">
+        <v>0.53</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2565,13 +2565,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="5">
-        <v>1.37</v>
+        <v>-1.38</v>
       </c>
       <c r="D34" s="5">
-        <v>-1.38</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-2.75</v>
+        <v>-2.73</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-1.35</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2582,13 +2582,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="5">
-        <v>25.2</v>
+        <v>19.97</v>
       </c>
       <c r="D35" s="5">
-        <v>19.97</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-5.23</v>
+        <v>10.1</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-9.869999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2599,13 +2599,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="5">
-        <v>4.66</v>
+        <v>-0.05</v>
       </c>
       <c r="D36" s="5">
-        <v>-0.05</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-4.71</v>
+        <v>-5.84</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-5.79</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2616,13 +2616,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="5">
-        <v>-0.01</v>
+        <v>-3.6</v>
       </c>
       <c r="D37" s="5">
-        <v>-3.6</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-3.59</v>
+        <v>-5.72</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-2.12</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2633,13 +2633,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="5">
-        <v>0.49</v>
+        <v>-2.28</v>
       </c>
       <c r="D38" s="5">
-        <v>-2.28</v>
-      </c>
-      <c r="E38" s="6">
-        <v>-2.77</v>
+        <v>-7.8</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-5.52</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2650,13 +2650,13 @@
         <v>10</v>
       </c>
       <c r="C39" s="5">
-        <v>1.41</v>
+        <v>-2.81</v>
       </c>
       <c r="D39" s="5">
-        <v>-2.81</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-4.22</v>
+        <v>-4.69</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-1.88</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2667,13 +2667,13 @@
         <v>10</v>
       </c>
       <c r="C40" s="5">
-        <v>11.68</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="D40" s="5">
-        <v>9.869999999999999</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-1.81</v>
+        <v>7.83</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-2.04</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2684,13 +2684,13 @@
         <v>10</v>
       </c>
       <c r="C41" s="5">
-        <v>-1.04</v>
+        <v>-1.67</v>
       </c>
       <c r="D41" s="5">
-        <v>-1.67</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-0.63</v>
+        <v>-3.27</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-1.6</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2701,13 +2701,13 @@
         <v>10</v>
       </c>
       <c r="C42" s="5">
-        <v>3.06</v>
+        <v>3.5</v>
       </c>
       <c r="D42" s="5">
-        <v>3.5</v>
+        <v>-1.76</v>
       </c>
       <c r="E42" s="7">
-        <v>0.44</v>
+        <v>-5.26</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2718,13 +2718,13 @@
         <v>6</v>
       </c>
       <c r="C43" s="5">
-        <v>-28.65</v>
+        <v>-29.58</v>
       </c>
       <c r="D43" s="5">
-        <v>-29.58</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-0.93</v>
+        <v>-29.95</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-0.37</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2735,13 +2735,13 @@
         <v>6</v>
       </c>
       <c r="C44" s="5">
-        <v>-6.29</v>
+        <v>-6.74</v>
       </c>
       <c r="D44" s="5">
-        <v>-6.74</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-0.45</v>
+        <v>-7.05</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2752,13 +2752,13 @@
         <v>6</v>
       </c>
       <c r="C45" s="5">
-        <v>-14.68</v>
+        <v>-14.86</v>
       </c>
       <c r="D45" s="5">
-        <v>-14.86</v>
-      </c>
-      <c r="E45" s="6">
-        <v>-0.18</v>
+        <v>-16.96</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-2.1</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2769,13 +2769,13 @@
         <v>6</v>
       </c>
       <c r="C46" s="5">
-        <v>-10.74</v>
+        <v>-11.42</v>
       </c>
       <c r="D46" s="5">
-        <v>-11.42</v>
-      </c>
-      <c r="E46" s="6">
-        <v>-0.68</v>
+        <v>-11.59</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-0.17</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2786,13 +2786,13 @@
         <v>6</v>
       </c>
       <c r="C47" s="5">
-        <v>-15.37</v>
+        <v>-16.03</v>
       </c>
       <c r="D47" s="5">
-        <v>-16.03</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-0.66</v>
+        <v>-16.84</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2803,13 +2803,13 @@
         <v>6</v>
       </c>
       <c r="C48" s="5">
-        <v>-28.16</v>
+        <v>-28.07</v>
       </c>
       <c r="D48" s="5">
-        <v>-28.07</v>
+        <v>-28.58</v>
       </c>
       <c r="E48" s="7">
-        <v>0.09</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2820,13 +2820,13 @@
         <v>6</v>
       </c>
       <c r="C49" s="5">
-        <v>-18.33</v>
+        <v>-17.58</v>
       </c>
       <c r="D49" s="5">
-        <v>-17.58</v>
+        <v>-18.3</v>
       </c>
       <c r="E49" s="7">
-        <v>0.75</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2837,13 +2837,13 @@
         <v>6</v>
       </c>
       <c r="C50" s="5">
-        <v>-29.35</v>
+        <v>-30.53</v>
       </c>
       <c r="D50" s="5">
-        <v>-30.53</v>
+        <v>-30.03</v>
       </c>
       <c r="E50" s="6">
-        <v>-1.18</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2854,13 +2854,13 @@
         <v>6</v>
       </c>
       <c r="C51" s="5">
-        <v>-49.53</v>
+        <v>-48.99</v>
       </c>
       <c r="D51" s="5">
-        <v>-48.99</v>
+        <v>-49.55</v>
       </c>
       <c r="E51" s="7">
-        <v>0.54</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2871,13 +2871,13 @@
         <v>2</v>
       </c>
       <c r="C52" s="5">
-        <v>1357.6</v>
+        <v>1339.8</v>
       </c>
       <c r="D52" s="5">
-        <v>1339.8</v>
-      </c>
-      <c r="E52" s="6">
-        <v>-17.8</v>
+        <v>1332.8</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-7</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2888,13 +2888,13 @@
         <v>2</v>
       </c>
       <c r="C53" s="5">
-        <v>3010</v>
+        <v>2995.5</v>
       </c>
       <c r="D53" s="5">
-        <v>2995.5</v>
-      </c>
-      <c r="E53" s="6">
-        <v>-14.5</v>
+        <v>2985.7</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-9.800000000000001</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2905,13 +2905,13 @@
         <v>2</v>
       </c>
       <c r="C54" s="5">
-        <v>1369</v>
+        <v>1366</v>
       </c>
       <c r="D54" s="5">
-        <v>1366</v>
-      </c>
-      <c r="E54" s="6">
-        <v>-3</v>
+        <v>1332.3</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-33.7</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2922,13 +2922,13 @@
         <v>2</v>
       </c>
       <c r="C55" s="5">
-        <v>1681</v>
+        <v>1668.2</v>
       </c>
       <c r="D55" s="5">
-        <v>1668.2</v>
-      </c>
-      <c r="E55" s="6">
-        <v>-12.8</v>
+        <v>1665</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-3.2</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2939,13 +2939,13 @@
         <v>2</v>
       </c>
       <c r="C56" s="5">
-        <v>210.65</v>
+        <v>209</v>
       </c>
       <c r="D56" s="5">
-        <v>209</v>
-      </c>
-      <c r="E56" s="6">
-        <v>-1.65</v>
+        <v>206.99</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-2.01</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2956,13 +2956,13 @@
         <v>2</v>
       </c>
       <c r="C57" s="5">
-        <v>430.85</v>
+        <v>424</v>
       </c>
       <c r="D57" s="5">
-        <v>424</v>
-      </c>
-      <c r="E57" s="6">
-        <v>-6.85</v>
+        <v>421</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-3</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2973,13 +2973,13 @@
         <v>2</v>
       </c>
       <c r="C58" s="5">
-        <v>660.1</v>
+        <v>666.15</v>
       </c>
       <c r="D58" s="5">
-        <v>666.15</v>
+        <v>660.35</v>
       </c>
       <c r="E58" s="7">
-        <v>6.05</v>
+        <v>-5.8</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2990,13 +2990,13 @@
         <v>2</v>
       </c>
       <c r="C59" s="5">
-        <v>196.13</v>
+        <v>192.86</v>
       </c>
       <c r="D59" s="5">
-        <v>192.86</v>
+        <v>194.24</v>
       </c>
       <c r="E59" s="6">
-        <v>-3.27</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -3007,353 +3007,319 @@
         <v>2</v>
       </c>
       <c r="C60" s="5">
-        <v>76.14</v>
+        <v>76.95</v>
       </c>
       <c r="D60" s="5">
-        <v>76.95</v>
+        <v>76.11</v>
       </c>
       <c r="E60" s="7">
-        <v>0.8100000000000001</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C61" s="5">
-        <v>66</v>
+        <v>43.91</v>
       </c>
       <c r="D61" s="5">
-        <v>55</v>
-      </c>
-      <c r="E61" s="6">
-        <v>-11</v>
+        <v>42.43</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-1.48</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C62" s="5">
-        <v>55</v>
+        <v>43.34</v>
       </c>
       <c r="D62" s="5">
-        <v>66</v>
+        <v>42.25</v>
       </c>
       <c r="E62" s="7">
-        <v>11</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C63" s="5">
-        <v>47.82</v>
+        <v>37.29</v>
       </c>
       <c r="D63" s="5">
-        <v>43.91</v>
-      </c>
-      <c r="E63" s="6">
-        <v>-3.91</v>
+        <v>32.53</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-4.76</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C64" s="5">
-        <v>44.94</v>
+        <v>31.56</v>
       </c>
       <c r="D64" s="5">
-        <v>43.34</v>
-      </c>
-      <c r="E64" s="6">
-        <v>-1.6</v>
+        <v>31.1</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-0.46</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C65" s="5">
-        <v>37.75</v>
+        <v>41.86</v>
       </c>
       <c r="D65" s="5">
-        <v>37.29</v>
-      </c>
-      <c r="E65" s="6">
-        <v>-0.46</v>
+        <v>39.34</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-2.52</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="5">
-        <v>33.43</v>
+        <v>44.3</v>
       </c>
       <c r="D66" s="5">
-        <v>31.56</v>
-      </c>
-      <c r="E66" s="6">
-        <v>-1.87</v>
+        <v>42.61</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-1.69</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="5">
-        <v>44.02</v>
+        <v>44.23</v>
       </c>
       <c r="D67" s="5">
-        <v>41.86</v>
-      </c>
-      <c r="E67" s="6">
-        <v>-2.16</v>
+        <v>41.78</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-2.45</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="5">
-        <v>48.36</v>
+        <v>53.71</v>
       </c>
       <c r="D68" s="5">
-        <v>44.3</v>
+        <v>55.97</v>
       </c>
       <c r="E68" s="6">
-        <v>-4.06</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="5">
-        <v>40.86</v>
+        <v>44.19</v>
       </c>
       <c r="D69" s="5">
-        <v>44.23</v>
+        <v>40.76</v>
       </c>
       <c r="E69" s="7">
-        <v>3.37</v>
+        <v>-3.43</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C70" s="5">
-        <v>60.57</v>
+        <v>-34.82</v>
       </c>
       <c r="D70" s="5">
-        <v>53.71</v>
+        <v>-33.52</v>
       </c>
       <c r="E70" s="6">
-        <v>-6.86</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C71" s="5">
-        <v>39.65</v>
+        <v>29.85</v>
       </c>
       <c r="D71" s="5">
-        <v>44.19</v>
+        <v>6.7</v>
       </c>
       <c r="E71" s="7">
-        <v>4.54</v>
+        <v>-23.15</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C72" s="5">
-        <v>-22.06</v>
+        <v>23.53</v>
       </c>
       <c r="D72" s="5">
-        <v>-34.82</v>
-      </c>
-      <c r="E72" s="6">
-        <v>-12.76</v>
+        <v>-18.24</v>
+      </c>
+      <c r="E72" s="7">
+        <v>-41.77</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C73" s="5">
-        <v>-30.02</v>
+        <v>6.49</v>
       </c>
       <c r="D73" s="5">
-        <v>29.85</v>
+        <v>-31.38</v>
       </c>
       <c r="E73" s="7">
-        <v>59.87</v>
+        <v>-37.87</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C74" s="5">
-        <v>-74.78</v>
+        <v>-26.61</v>
       </c>
       <c r="D74" s="5">
-        <v>23.53</v>
+        <v>-40.56</v>
       </c>
       <c r="E74" s="7">
-        <v>98.31</v>
+        <v>-13.95</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="5">
-        <v>4.08</v>
+        <v>-42.07</v>
       </c>
       <c r="D75" s="5">
-        <v>6.49</v>
-      </c>
-      <c r="E75" s="7">
-        <v>2.41</v>
+        <v>114.39</v>
+      </c>
+      <c r="E75" s="6">
+        <v>156.46</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="5">
-        <v>-46.11</v>
+        <v>-7.77</v>
       </c>
       <c r="D76" s="5">
-        <v>-26.61</v>
+        <v>-15.28</v>
       </c>
       <c r="E76" s="7">
-        <v>19.5</v>
+        <v>-7.51</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="5">
-        <v>-29.72</v>
+        <v>-62.63</v>
       </c>
       <c r="D77" s="5">
-        <v>-42.07</v>
+        <v>-48.2</v>
       </c>
       <c r="E77" s="6">
-        <v>-12.35</v>
+        <v>14.43</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="5">
-        <v>-64.14</v>
+        <v>-25.61</v>
       </c>
       <c r="D78" s="5">
-        <v>-7.77</v>
-      </c>
-      <c r="E78" s="7">
-        <v>56.37</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="5">
-        <v>-68.81999999999999</v>
-      </c>
-      <c r="D79" s="5">
-        <v>-62.63</v>
-      </c>
-      <c r="E79" s="7">
-        <v>6.19</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="5">
-        <v>-54.73</v>
-      </c>
-      <c r="D80" s="5">
-        <v>-25.61</v>
-      </c>
-      <c r="E80" s="7">
-        <v>29.12</v>
+        <v>-23.76</v>
+      </c>
+      <c r="E78" s="6">
+        <v>1.85</v>
       </c>
     </row>
   </sheetData>
@@ -3418,16 +3384,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="10">
-        <v>42.7</v>
+        <v>41</v>
       </c>
       <c r="E2" s="10">
         <v>60</v>
       </c>
       <c r="F2" s="10">
-        <v>-5</v>
+        <v>-6.4</v>
       </c>
       <c r="G2" s="10">
-        <v>2.4</v>
+        <v>-1.5</v>
       </c>
       <c r="H2" s="10">
         <v>55.4</v>
@@ -3564,31 +3530,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="13">
-        <v>0.6581</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="B2" s="13">
-        <v>0.1964</v>
+        <v>0.1943</v>
       </c>
       <c r="C2" s="13">
-        <v>0.1588</v>
+        <v>0.1571</v>
       </c>
       <c r="D2" s="13">
-        <v>0.0867</v>
+        <v>0.0784</v>
       </c>
       <c r="E2" s="13">
-        <v>0.0204</v>
+        <v>0.0182</v>
       </c>
       <c r="F2" s="13">
-        <v>-0.0077</v>
+        <v>-0.0115</v>
       </c>
       <c r="G2" s="13">
-        <v>-0.0582</v>
+        <v>-0.0614</v>
       </c>
       <c r="H2" s="13">
-        <v>-0.0706</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="I2" s="13">
-        <v>-0.0924</v>
+        <v>-0.0946</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,7 +178,28 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -264,14 +285,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -304,13 +325,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,14 +401,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -902,10 +924,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1332.8</v>
+        <v>1324.7</v>
       </c>
       <c r="D2">
-        <v>-0.52</v>
+        <v>-0.61</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -914,46 +936,46 @@
         <v>1247.38</v>
       </c>
       <c r="G2">
-        <v>-29.95</v>
+        <v>-30.38</v>
       </c>
       <c r="H2">
-        <v>6.85</v>
+        <v>6.2</v>
       </c>
       <c r="I2">
-        <v>-4.39</v>
+        <v>-3.9</v>
       </c>
       <c r="J2">
-        <v>-2.14</v>
+        <v>-4.23</v>
       </c>
       <c r="K2">
-        <v>-2.73</v>
+        <v>-2.23</v>
       </c>
       <c r="L2">
-        <v>-26.76</v>
+        <v>-26.7</v>
       </c>
       <c r="M2">
-        <v>-9.460000000000001</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="P2">
-        <v>1354.28</v>
+        <v>1343.54</v>
       </c>
       <c r="Q2">
-        <v>1364.34</v>
+        <v>1361.91</v>
       </c>
       <c r="R2">
-        <v>1354.24</v>
+        <v>1353.87</v>
       </c>
       <c r="S2">
-        <v>1538.07</v>
+        <v>1535.49</v>
       </c>
       <c r="T2">
-        <v>-13.35</v>
+        <v>-13.73</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -968,34 +990,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>42.43</v>
+        <v>40.73</v>
       </c>
       <c r="Z2">
-        <v>-2.21</v>
+        <v>-4.86</v>
       </c>
       <c r="AA2">
-        <v>1.72</v>
+        <v>0.4</v>
       </c>
       <c r="AB2">
-        <v>-3.93</v>
+        <v>-5.26</v>
       </c>
       <c r="AC2">
-        <v>12.77</v>
+        <v>2.02</v>
       </c>
       <c r="AD2">
-        <v>28.18</v>
+        <v>13.65</v>
       </c>
       <c r="AE2">
-        <v>28.3</v>
+        <v>27.59</v>
       </c>
       <c r="AF2">
-        <v>-33.52</v>
+        <v>-52.15</v>
       </c>
       <c r="AG2">
-        <v>1404.26</v>
+        <v>1405.3</v>
       </c>
       <c r="AH2">
-        <v>1324.41</v>
+        <v>1318.51</v>
       </c>
       <c r="AI2">
         <v>1318.07</v>
@@ -1004,7 +1026,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>19.89</v>
+        <v>22.02</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1015,10 +1037,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2985.7</v>
+        <v>2964.9</v>
       </c>
       <c r="D3">
-        <v>-0.33</v>
+        <v>-0.7</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1027,25 +1049,25 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-7.05</v>
+        <v>-7.7</v>
       </c>
       <c r="H3">
-        <v>69.83</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="I3">
-        <v>-2.11</v>
+        <v>-2.02</v>
       </c>
       <c r="J3">
-        <v>-6.37</v>
+        <v>-5.89</v>
       </c>
       <c r="K3">
-        <v>10.1</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="L3">
-        <v>29.85</v>
+        <v>31.84</v>
       </c>
       <c r="M3">
-        <v>15.71</v>
+        <v>15.64</v>
       </c>
       <c r="N3">
         <v>88</v>
@@ -1054,61 +1076,61 @@
         <v>74</v>
       </c>
       <c r="P3">
-        <v>3007.44</v>
+        <v>2995.22</v>
       </c>
       <c r="Q3">
-        <v>3059.47</v>
+        <v>3050.14</v>
       </c>
       <c r="R3">
-        <v>3050.17</v>
+        <v>3050.98</v>
       </c>
       <c r="S3">
-        <v>2463.5</v>
+        <v>2465.81</v>
       </c>
       <c r="T3">
-        <v>21.2</v>
+        <v>20.24</v>
       </c>
       <c r="U3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V3" t="s">
         <v>47</v>
       </c>
       <c r="W3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y3">
-        <v>42.25</v>
+        <v>39.95</v>
       </c>
       <c r="Z3">
-        <v>-14.46</v>
+        <v>-18.42</v>
       </c>
       <c r="AA3">
-        <v>-2.12</v>
+        <v>-5.38</v>
       </c>
       <c r="AB3">
-        <v>-12.33</v>
+        <v>-13.03</v>
       </c>
       <c r="AC3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>7.76</v>
+        <v>3.46</v>
       </c>
       <c r="AE3">
-        <v>67.62</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="AF3">
-        <v>6.7</v>
+        <v>24.05</v>
       </c>
       <c r="AG3">
-        <v>3191.72</v>
+        <v>3181.4</v>
       </c>
       <c r="AH3">
-        <v>2927.22</v>
+        <v>2918.89</v>
       </c>
       <c r="AI3">
         <v>2959.69</v>
@@ -1117,7 +1139,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>27.8</v>
+        <v>28.76</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1128,10 +1150,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1332.3</v>
+        <v>1319</v>
       </c>
       <c r="D4">
-        <v>-2.47</v>
+        <v>-1</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1140,46 +1162,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-16.96</v>
+        <v>-17.79</v>
       </c>
       <c r="H4">
-        <v>72.40000000000001</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="I4">
-        <v>-3.46</v>
+        <v>-3.83</v>
       </c>
       <c r="J4">
-        <v>-16.96</v>
+        <v>-15.2</v>
       </c>
       <c r="K4">
-        <v>-5.84</v>
+        <v>-4.35</v>
       </c>
       <c r="L4">
-        <v>39.14</v>
+        <v>40.81</v>
       </c>
       <c r="M4">
-        <v>7.84</v>
+        <v>7.49</v>
       </c>
       <c r="N4">
         <v>77</v>
       </c>
       <c r="O4">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P4">
-        <v>1362.24</v>
+        <v>1351.74</v>
       </c>
       <c r="Q4">
-        <v>1411.97</v>
+        <v>1400.73</v>
       </c>
       <c r="R4">
-        <v>1471.2</v>
+        <v>1469.03</v>
       </c>
       <c r="S4">
-        <v>1157.08</v>
+        <v>1158.52</v>
       </c>
       <c r="T4">
-        <v>15.14</v>
+        <v>13.85</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1194,43 +1216,43 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>32.53</v>
+        <v>30.86</v>
       </c>
       <c r="Z4">
-        <v>-35.65</v>
+        <v>-37.95</v>
       </c>
       <c r="AA4">
-        <v>-30.73</v>
+        <v>-32.17</v>
       </c>
       <c r="AB4">
-        <v>-4.92</v>
+        <v>-5.77</v>
       </c>
       <c r="AC4">
-        <v>24.94</v>
+        <v>14.3</v>
       </c>
       <c r="AD4">
-        <v>26.3</v>
+        <v>23.47</v>
       </c>
       <c r="AE4">
-        <v>44.77</v>
+        <v>44.34</v>
       </c>
       <c r="AF4">
-        <v>-18.24</v>
+        <v>-33.62</v>
       </c>
       <c r="AG4">
-        <v>1546.22</v>
+        <v>1525.87</v>
       </c>
       <c r="AH4">
-        <v>1277.71</v>
+        <v>1275.59</v>
       </c>
       <c r="AI4">
-        <v>1477.32</v>
+        <v>1466.37</v>
       </c>
       <c r="AJ4" t="s">
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>25.53</v>
+        <v>24.81</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1241,10 +1263,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1665</v>
+        <v>1658</v>
       </c>
       <c r="D5">
-        <v>-0.19</v>
+        <v>-0.42</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1253,25 +1275,25 @@
         <v>1294.84</v>
       </c>
       <c r="G5">
-        <v>-11.59</v>
+        <v>-11.96</v>
       </c>
       <c r="H5">
-        <v>28.59</v>
+        <v>28.05</v>
       </c>
       <c r="I5">
-        <v>-2.06</v>
+        <v>-2.18</v>
       </c>
       <c r="J5">
-        <v>-8.609999999999999</v>
+        <v>-9.35</v>
       </c>
       <c r="K5">
-        <v>-5.72</v>
+        <v>-7.25</v>
       </c>
       <c r="L5">
-        <v>22.3</v>
+        <v>23.75</v>
       </c>
       <c r="M5">
-        <v>19.43</v>
+        <v>19.33</v>
       </c>
       <c r="N5">
         <v>55</v>
@@ -1280,19 +1302,19 @@
         <v>60</v>
       </c>
       <c r="P5">
-        <v>1680.54</v>
+        <v>1673.14</v>
       </c>
       <c r="Q5">
-        <v>1742.81</v>
+        <v>1734.39</v>
       </c>
       <c r="R5">
-        <v>1787.99</v>
+        <v>1785.22</v>
       </c>
       <c r="S5">
-        <v>1582.49</v>
+        <v>1583.66</v>
       </c>
       <c r="T5">
-        <v>5.21</v>
+        <v>4.69</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1307,43 +1329,43 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>31.1</v>
+        <v>30.05</v>
       </c>
       <c r="Z5">
-        <v>-35.94</v>
+        <v>-36.88</v>
       </c>
       <c r="AA5">
-        <v>-29.1</v>
+        <v>-30.65</v>
       </c>
       <c r="AB5">
-        <v>-6.84</v>
+        <v>-6.23</v>
       </c>
       <c r="AC5">
-        <v>26.26</v>
+        <v>23.25</v>
       </c>
       <c r="AD5">
-        <v>26.93</v>
+        <v>25.56</v>
       </c>
       <c r="AE5">
-        <v>35.68</v>
+        <v>35.19</v>
       </c>
       <c r="AF5">
-        <v>-31.38</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="AG5">
-        <v>1872.92</v>
+        <v>1863.52</v>
       </c>
       <c r="AH5">
-        <v>1612.71</v>
+        <v>1605.27</v>
       </c>
       <c r="AI5">
-        <v>1763.6</v>
+        <v>1761.08</v>
       </c>
       <c r="AJ5" t="s">
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>55.4</v>
+        <v>55.59</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1354,10 +1376,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>206.99</v>
+        <v>206.1</v>
       </c>
       <c r="D6">
-        <v>-0.96</v>
+        <v>-0.43</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1366,46 +1388,46 @@
         <v>115.38</v>
       </c>
       <c r="G6">
-        <v>-16.84</v>
+        <v>-17.2</v>
       </c>
       <c r="H6">
-        <v>79.40000000000001</v>
+        <v>78.63</v>
       </c>
       <c r="I6">
-        <v>-0.96</v>
+        <v>-0.97</v>
       </c>
       <c r="J6">
-        <v>-8.48</v>
+        <v>-5.88</v>
       </c>
       <c r="K6">
-        <v>-7.8</v>
+        <v>-6.88</v>
       </c>
       <c r="L6">
-        <v>82.39</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="M6">
-        <v>64.87</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P6">
-        <v>208.75</v>
+        <v>208.35</v>
       </c>
       <c r="Q6">
-        <v>212.13</v>
+        <v>211.6</v>
       </c>
       <c r="R6">
-        <v>219.45</v>
+        <v>218.93</v>
       </c>
       <c r="S6">
-        <v>178.57</v>
+        <v>178.76</v>
       </c>
       <c r="T6">
-        <v>15.92</v>
+        <v>15.29</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1420,43 +1442,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>39.34</v>
+        <v>38.23</v>
       </c>
       <c r="Z6">
-        <v>-3.17</v>
+        <v>-3.27</v>
       </c>
       <c r="AA6">
-        <v>-3.15</v>
+        <v>-3.18</v>
       </c>
       <c r="AB6">
-        <v>-0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="AC6">
-        <v>49.84</v>
+        <v>26.1</v>
       </c>
       <c r="AD6">
-        <v>48.72</v>
+        <v>43.2</v>
       </c>
       <c r="AE6">
-        <v>5.29</v>
+        <v>5.31</v>
       </c>
       <c r="AF6">
-        <v>-40.56</v>
+        <v>-36.78</v>
       </c>
       <c r="AG6">
-        <v>220.04</v>
+        <v>219.66</v>
       </c>
       <c r="AH6">
-        <v>204.22</v>
+        <v>203.55</v>
       </c>
       <c r="AI6">
-        <v>223.23</v>
+        <v>222.84</v>
       </c>
       <c r="AJ6" t="s">
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>21.12</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1467,10 +1489,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>421</v>
+        <v>419.4</v>
       </c>
       <c r="D7">
-        <v>-0.71</v>
+        <v>-0.38</v>
       </c>
       <c r="E7">
         <v>589.48</v>
@@ -1479,25 +1501,25 @@
         <v>393.4</v>
       </c>
       <c r="G7">
-        <v>-28.58</v>
+        <v>-28.85</v>
       </c>
       <c r="H7">
-        <v>7.02</v>
+        <v>6.61</v>
       </c>
       <c r="I7">
-        <v>-5.39</v>
+        <v>-3.92</v>
       </c>
       <c r="J7">
-        <v>-2.05</v>
+        <v>-3.64</v>
       </c>
       <c r="K7">
-        <v>-4.69</v>
+        <v>-2.83</v>
       </c>
       <c r="L7">
-        <v>-28.28</v>
+        <v>-28.85</v>
       </c>
       <c r="M7">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="N7">
         <v>23</v>
@@ -1506,19 +1528,19 @@
         <v>20</v>
       </c>
       <c r="P7">
-        <v>429.27</v>
+        <v>425.85</v>
       </c>
       <c r="Q7">
-        <v>433.01</v>
+        <v>432.3</v>
       </c>
       <c r="R7">
-        <v>428.27</v>
+        <v>428.16</v>
       </c>
       <c r="S7">
-        <v>481.14</v>
+        <v>480.47</v>
       </c>
       <c r="T7">
-        <v>-12.5</v>
+        <v>-12.71</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1533,34 +1555,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>42.61</v>
+        <v>41.7</v>
       </c>
       <c r="Z7">
-        <v>-0.55</v>
+        <v>-1.45</v>
       </c>
       <c r="AA7">
-        <v>0.9399999999999999</v>
+        <v>0.46</v>
       </c>
       <c r="AB7">
-        <v>-1.49</v>
+        <v>-1.91</v>
       </c>
       <c r="AC7">
-        <v>8.630000000000001</v>
+        <v>0</v>
       </c>
       <c r="AD7">
-        <v>23.55</v>
+        <v>10.29</v>
       </c>
       <c r="AE7">
-        <v>10.32</v>
+        <v>10.05</v>
       </c>
       <c r="AF7">
-        <v>114.39</v>
+        <v>-20.35</v>
       </c>
       <c r="AG7">
-        <v>446.38</v>
+        <v>446.99</v>
       </c>
       <c r="AH7">
-        <v>419.65</v>
+        <v>417.62</v>
       </c>
       <c r="AI7">
         <v>411.2</v>
@@ -1569,7 +1591,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>18.67</v>
+        <v>20.94</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1580,10 +1602,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>660.35</v>
+        <v>655.05</v>
       </c>
       <c r="D8">
-        <v>-0.87</v>
+        <v>-0.8</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1592,46 +1614,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-18.3</v>
+        <v>-18.96</v>
       </c>
       <c r="H8">
-        <v>41.18</v>
+        <v>40.05</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>-0.79</v>
       </c>
       <c r="J8">
-        <v>-8.49</v>
+        <v>-8.44</v>
       </c>
       <c r="K8">
-        <v>7.83</v>
+        <v>6.33</v>
       </c>
       <c r="L8">
-        <v>12.15</v>
+        <v>10.72</v>
       </c>
       <c r="M8">
-        <v>-6.14</v>
+        <v>-6.48</v>
       </c>
       <c r="N8">
         <v>66</v>
       </c>
       <c r="O8">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="P8">
-        <v>660.88</v>
+        <v>659.84</v>
       </c>
       <c r="Q8">
-        <v>669.37</v>
+        <v>666.74</v>
       </c>
       <c r="R8">
-        <v>702.29</v>
+        <v>701.05</v>
       </c>
       <c r="S8">
-        <v>612.47</v>
+        <v>612.63</v>
       </c>
       <c r="T8">
-        <v>7.82</v>
+        <v>6.92</v>
       </c>
       <c r="U8" t="s">
         <v>48</v>
@@ -1646,34 +1668,34 @@
         <v>2</v>
       </c>
       <c r="Y8">
-        <v>41.78</v>
+        <v>39.61</v>
       </c>
       <c r="Z8">
-        <v>-11.57</v>
+        <v>-11.44</v>
       </c>
       <c r="AA8">
-        <v>-12.82</v>
+        <v>-12.54</v>
       </c>
       <c r="AB8">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="AC8">
-        <v>88</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="AD8">
-        <v>78.01000000000001</v>
+        <v>83.66</v>
       </c>
       <c r="AE8">
-        <v>17.55</v>
+        <v>17.68</v>
       </c>
       <c r="AF8">
-        <v>-15.28</v>
+        <v>-44.5</v>
       </c>
       <c r="AG8">
-        <v>710.9</v>
+        <v>704.55</v>
       </c>
       <c r="AH8">
-        <v>627.85</v>
+        <v>628.9400000000001</v>
       </c>
       <c r="AI8">
         <v>713.42</v>
@@ -1682,7 +1704,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>24.97</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1693,10 +1715,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>194.24</v>
+        <v>192.11</v>
       </c>
       <c r="D9">
-        <v>0.72</v>
+        <v>-1.1</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1705,46 +1727,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-30.03</v>
+        <v>-30.8</v>
       </c>
       <c r="H9">
-        <v>12.73</v>
+        <v>11.5</v>
       </c>
       <c r="I9">
-        <v>0.36</v>
+        <v>-2.67</v>
       </c>
       <c r="J9">
-        <v>2.63</v>
+        <v>1.68</v>
       </c>
       <c r="K9">
-        <v>-3.27</v>
+        <v>-3.82</v>
       </c>
       <c r="L9">
-        <v>-23.19</v>
+        <v>-23.37</v>
       </c>
       <c r="M9">
-        <v>-6.91</v>
+        <v>-7.14</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P9">
-        <v>195.62</v>
+        <v>194.57</v>
       </c>
       <c r="Q9">
-        <v>191.03</v>
+        <v>191.14</v>
       </c>
       <c r="R9">
-        <v>188.96</v>
+        <v>189</v>
       </c>
       <c r="S9">
-        <v>210.1</v>
+        <v>209.75</v>
       </c>
       <c r="T9">
-        <v>-7.55</v>
+        <v>-8.41</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1759,34 +1781,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>55.97</v>
+        <v>51.76</v>
       </c>
       <c r="Z9">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="AA9">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AB9">
-        <v>0.55</v>
+        <v>0.29</v>
       </c>
       <c r="AC9">
-        <v>61.14</v>
+        <v>44.81</v>
       </c>
       <c r="AD9">
-        <v>76.93000000000001</v>
+        <v>60.49</v>
       </c>
       <c r="AE9">
-        <v>4.95</v>
+        <v>4.82</v>
       </c>
       <c r="AF9">
-        <v>-48.2</v>
+        <v>-56.02</v>
       </c>
       <c r="AG9">
-        <v>197.84</v>
+        <v>197.95</v>
       </c>
       <c r="AH9">
-        <v>184.22</v>
+        <v>184.34</v>
       </c>
       <c r="AI9">
         <v>197.85</v>
@@ -1795,7 +1817,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>47.12</v>
+        <v>44.91</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1806,10 +1828,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>76.11</v>
+        <v>76.37</v>
       </c>
       <c r="D10">
-        <v>-1.09</v>
+        <v>0.34</v>
       </c>
       <c r="E10">
         <v>150.86</v>
@@ -1818,25 +1840,25 @@
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-49.55</v>
+        <v>-49.38</v>
       </c>
       <c r="H10">
-        <v>28.39</v>
+        <v>28.83</v>
       </c>
       <c r="I10">
-        <v>-1.37</v>
+        <v>-1.31</v>
       </c>
       <c r="J10">
-        <v>-7.23</v>
+        <v>-6.18</v>
       </c>
       <c r="K10">
-        <v>-1.76</v>
+        <v>-1.02</v>
       </c>
       <c r="L10">
-        <v>-42.99</v>
+        <v>-41.96</v>
       </c>
       <c r="M10">
-        <v>-1.15</v>
+        <v>-0.86</v>
       </c>
       <c r="N10">
         <v>12</v>
@@ -1845,19 +1867,19 @@
         <v>11</v>
       </c>
       <c r="P10">
-        <v>76.69</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="Q10">
-        <v>77.36</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="R10">
-        <v>79.77</v>
+        <v>79.66</v>
       </c>
       <c r="S10">
-        <v>82.28</v>
+        <v>82.2</v>
       </c>
       <c r="T10">
-        <v>-7.5</v>
+        <v>-7.09</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1872,34 +1894,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>40.76</v>
+        <v>42.26</v>
       </c>
       <c r="Z10">
-        <v>-0.95</v>
+        <v>-0.93</v>
       </c>
       <c r="AA10">
-        <v>-0.98</v>
+        <v>-0.97</v>
       </c>
       <c r="AB10">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="AC10">
-        <v>63.8</v>
+        <v>67.34</v>
       </c>
       <c r="AD10">
-        <v>69.97</v>
+        <v>68.58</v>
       </c>
       <c r="AE10">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="AF10">
-        <v>-23.76</v>
+        <v>-66.44</v>
       </c>
       <c r="AG10">
-        <v>80.41</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="AH10">
-        <v>74.3</v>
+        <v>74.47</v>
       </c>
       <c r="AI10">
         <v>74.97</v>
@@ -1908,7 +1930,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>14.99</v>
+        <v>14.17</v>
       </c>
     </row>
   </sheetData>
@@ -2049,7 +2071,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2069,1263 +2091,1318 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C8" s="6">
+        <v>-2.14</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-4.23</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-2.09</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-6.37</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-5.89</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-16.96</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-15.2</v>
+      </c>
+      <c r="E10" s="8">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-8.609999999999999</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-9.35</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-8.48</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-5.88</v>
+      </c>
+      <c r="E12" s="8">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-2.05</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-3.64</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-1.59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-8.49</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-8.44</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>2.63</v>
+      </c>
+      <c r="D15" s="6">
+        <v>1.68</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-7.23</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-6.18</v>
+      </c>
+      <c r="E16" s="8">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-4.39</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-3.9</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-2.11</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-2.02</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3.46</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-3.83</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-2.06</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-2.18</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-0.96</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-0.97</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-5.39</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-3.92</v>
+      </c>
+      <c r="E22" s="8">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>0</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-0.79</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.79</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>0.36</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-2.67</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-3.03</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-1.37</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-1.31</v>
+      </c>
+      <c r="E25" s="8">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-26.76</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-26.7</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>29.85</v>
+      </c>
+      <c r="D27" s="6">
+        <v>31.84</v>
+      </c>
+      <c r="E27" s="8">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>39.14</v>
+      </c>
+      <c r="D28" s="6">
+        <v>40.81</v>
+      </c>
+      <c r="E28" s="8">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>22.3</v>
+      </c>
+      <c r="D29" s="6">
+        <v>23.75</v>
+      </c>
+      <c r="E29" s="8">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>82.39</v>
+      </c>
+      <c r="D30" s="6">
+        <v>77.98999999999999</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-4.4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-28.28</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-28.85</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>12.15</v>
+      </c>
+      <c r="D32" s="6">
+        <v>10.72</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-1.43</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-23.19</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-23.37</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-42.99</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-41.96</v>
+      </c>
+      <c r="E34" s="8">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-2.73</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-2.23</v>
+      </c>
+      <c r="E35" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>10.1</v>
+      </c>
+      <c r="D36" s="6">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-5.84</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-4.35</v>
+      </c>
+      <c r="E37" s="8">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-5.72</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-7.25</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-1.53</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-7.8</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-6.88</v>
+      </c>
+      <c r="E39" s="8">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-4.69</v>
+      </c>
+      <c r="D40" s="6">
         <v>-2.83</v>
       </c>
-      <c r="D7" s="5">
-        <v>-2.14</v>
-      </c>
-      <c r="E7" s="6">
-        <v>0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="E40" s="8">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>7.83</v>
+      </c>
+      <c r="D41" s="6">
+        <v>6.33</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-3.27</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-3.82</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-1.76</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-1.02</v>
+      </c>
+      <c r="E43" s="8">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-29.95</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-30.38</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5">
-        <v>-5.73</v>
-      </c>
-      <c r="D8" s="5">
-        <v>-6.37</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-0.64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-7.05</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-7.7</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="5">
-        <v>-11.67</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
         <v>-16.96</v>
       </c>
-      <c r="E9" s="7">
-        <v>-5.29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D46" s="6">
+        <v>-17.79</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-0.83</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="5">
-        <v>-7.85</v>
-      </c>
-      <c r="D10" s="5">
-        <v>-8.609999999999999</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-0.76</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-11.59</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-11.96</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5">
-        <v>-3</v>
-      </c>
-      <c r="D11" s="5">
-        <v>-8.48</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-5.48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-16.84</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-17.2</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>-1.89</v>
-      </c>
-      <c r="D12" s="5">
-        <v>-2.05</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-28.58</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-28.85</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-7.6</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-8.49</v>
-      </c>
-      <c r="E13" s="7">
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-18.3</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-18.96</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-0.66</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-30.03</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-30.8</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-0.77</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="6">
+        <v>-49.55</v>
+      </c>
+      <c r="D52" s="6">
+        <v>-49.38</v>
+      </c>
+      <c r="E52" s="8">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>1332.8</v>
+      </c>
+      <c r="D53" s="6">
+        <v>1324.7</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-8.1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>2985.7</v>
+      </c>
+      <c r="D54" s="6">
+        <v>2964.9</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-20.8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>1332.3</v>
+      </c>
+      <c r="D55" s="6">
+        <v>1319</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-13.3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>1665</v>
+      </c>
+      <c r="D56" s="6">
+        <v>1658</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>206.99</v>
+      </c>
+      <c r="D57" s="6">
+        <v>206.1</v>
+      </c>
+      <c r="E57" s="7">
         <v>-0.89</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>421</v>
+      </c>
+      <c r="D58" s="6">
+        <v>419.4</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>660.35</v>
+      </c>
+      <c r="D59" s="6">
+        <v>655.05</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-5.3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="5">
-        <v>1.84</v>
-      </c>
-      <c r="D14" s="5">
-        <v>2.63</v>
-      </c>
-      <c r="E14" s="6">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="6">
+        <v>194.24</v>
+      </c>
+      <c r="D60" s="6">
+        <v>192.11</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-2.13</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-6.49</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-7.23</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-0.74</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B61" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="6">
+        <v>76.11</v>
+      </c>
+      <c r="D61" s="6">
+        <v>76.37</v>
+      </c>
+      <c r="E61" s="8">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-3.24</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-4.39</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-1.15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B62" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="6">
+        <v>42.43</v>
+      </c>
+      <c r="D62" s="6">
+        <v>40.73</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-1.79</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-2.11</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-0.32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B63" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="6">
+        <v>42.25</v>
+      </c>
+      <c r="D63" s="6">
+        <v>39.95</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-2.3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-1.3</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-3.46</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-2.16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="6">
+        <v>32.53</v>
+      </c>
+      <c r="D64" s="6">
+        <v>30.86</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-1.67</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-2.26</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-2.06</v>
-      </c>
-      <c r="E19" s="6">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>31.1</v>
+      </c>
+      <c r="D65" s="6">
+        <v>30.05</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-1.05</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-0.45</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-0.96</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.51</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>39.34</v>
+      </c>
+      <c r="D66" s="6">
+        <v>38.23</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-1.11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-2.76</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-5.39</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-2.63</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>42.61</v>
+      </c>
+      <c r="D67" s="6">
+        <v>41.7</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="5">
-        <v>-0.12</v>
-      </c>
-      <c r="D22" s="5">
-        <v>0</v>
-      </c>
-      <c r="E22" s="6">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>41.78</v>
+      </c>
+      <c r="D68" s="6">
+        <v>39.61</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-2.17</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="5">
-        <v>1.19</v>
-      </c>
-      <c r="D23" s="5">
-        <v>0.36</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-0.83</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>55.97</v>
+      </c>
+      <c r="D69" s="6">
+        <v>51.76</v>
+      </c>
+      <c r="E69" s="7">
+        <v>-4.21</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="5">
-        <v>0.38</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-1.37</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-1.75</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="6">
+        <v>40.76</v>
+      </c>
+      <c r="D70" s="6">
+        <v>42.26</v>
+      </c>
+      <c r="E70" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-25.21</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-26.76</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-1.55</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B71" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="6">
+        <v>-33.52</v>
+      </c>
+      <c r="D71" s="6">
+        <v>-52.15</v>
+      </c>
+      <c r="E71" s="7">
+        <v>-18.63</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>28.72</v>
-      </c>
-      <c r="D26" s="5">
-        <v>29.85</v>
-      </c>
-      <c r="E26" s="6">
-        <v>1.13</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B72" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="6">
+        <v>6.7</v>
+      </c>
+      <c r="D72" s="6">
+        <v>24.05</v>
+      </c>
+      <c r="E72" s="8">
+        <v>17.35</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>40.57</v>
-      </c>
-      <c r="D27" s="5">
-        <v>39.14</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-1.43</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B73" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="6">
+        <v>-18.24</v>
+      </c>
+      <c r="D73" s="6">
+        <v>-33.62</v>
+      </c>
+      <c r="E73" s="7">
+        <v>-15.38</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="5">
-        <v>23.35</v>
-      </c>
-      <c r="D28" s="5">
-        <v>22.3</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-1.05</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="6">
+        <v>-31.38</v>
+      </c>
+      <c r="D74" s="6">
+        <v>-8.210000000000001</v>
+      </c>
+      <c r="E74" s="8">
+        <v>23.17</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="5">
-        <v>80.33</v>
-      </c>
-      <c r="D29" s="5">
-        <v>82.39</v>
-      </c>
-      <c r="E29" s="6">
-        <v>2.06</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
+        <v>-40.56</v>
+      </c>
+      <c r="D75" s="6">
+        <v>-36.78</v>
+      </c>
+      <c r="E75" s="8">
+        <v>3.78</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-29.3</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-28.28</v>
-      </c>
-      <c r="E30" s="6">
-        <v>1.02</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>114.39</v>
+      </c>
+      <c r="D76" s="6">
+        <v>-20.35</v>
+      </c>
+      <c r="E76" s="7">
+        <v>-134.74</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="5">
-        <v>11.84</v>
-      </c>
-      <c r="D31" s="5">
-        <v>12.15</v>
-      </c>
-      <c r="E31" s="6">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>-15.28</v>
+      </c>
+      <c r="D77" s="6">
+        <v>-44.5</v>
+      </c>
+      <c r="E77" s="7">
+        <v>-29.22</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-23.92</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-23.19</v>
-      </c>
-      <c r="E32" s="6">
-        <v>0.73</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="6">
+        <v>-48.2</v>
+      </c>
+      <c r="D78" s="6">
+        <v>-56.02</v>
+      </c>
+      <c r="E78" s="7">
+        <v>-7.82</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-43.52</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-42.99</v>
-      </c>
-      <c r="E33" s="6">
-        <v>0.53</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-1.38</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-2.73</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-1.35</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="5">
-        <v>19.97</v>
-      </c>
-      <c r="D35" s="5">
-        <v>10.1</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-9.869999999999999</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-0.05</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-5.84</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-5.79</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-3.6</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-5.72</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-2.12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-2.28</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-7.8</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-5.52</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-2.81</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-4.69</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-1.88</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="5">
-        <v>9.869999999999999</v>
-      </c>
-      <c r="D40" s="5">
-        <v>7.83</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-2.04</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-1.67</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-3.27</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-1.6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="5">
-        <v>3.5</v>
-      </c>
-      <c r="D42" s="5">
-        <v>-1.76</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-5.26</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-29.58</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-29.95</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-6.74</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-7.05</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-0.31</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-14.86</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-16.96</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-2.1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-11.42</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-11.59</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="5">
-        <v>-16.03</v>
-      </c>
-      <c r="D47" s="5">
-        <v>-16.84</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="5">
-        <v>-28.07</v>
-      </c>
-      <c r="D48" s="5">
-        <v>-28.58</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-0.51</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="5">
-        <v>-17.58</v>
-      </c>
-      <c r="D49" s="5">
-        <v>-18.3</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-0.72</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="5">
-        <v>-30.53</v>
-      </c>
-      <c r="D50" s="5">
-        <v>-30.03</v>
-      </c>
-      <c r="E50" s="6">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="5">
-        <v>-48.99</v>
-      </c>
-      <c r="D51" s="5">
-        <v>-49.55</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="5">
-        <v>1339.8</v>
-      </c>
-      <c r="D52" s="5">
-        <v>1332.8</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-7</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="5">
-        <v>2995.5</v>
-      </c>
-      <c r="D53" s="5">
-        <v>2985.7</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-9.800000000000001</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="5">
-        <v>1366</v>
-      </c>
-      <c r="D54" s="5">
-        <v>1332.3</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-33.7</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="5">
-        <v>1668.2</v>
-      </c>
-      <c r="D55" s="5">
-        <v>1665</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-3.2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="5">
-        <v>209</v>
-      </c>
-      <c r="D56" s="5">
-        <v>206.99</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-2.01</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="5">
-        <v>424</v>
-      </c>
-      <c r="D57" s="5">
-        <v>421</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="5">
-        <v>666.15</v>
-      </c>
-      <c r="D58" s="5">
-        <v>660.35</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-5.8</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="5">
-        <v>192.86</v>
-      </c>
-      <c r="D59" s="5">
-        <v>194.24</v>
-      </c>
-      <c r="E59" s="6">
-        <v>1.38</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="5">
-        <v>76.95</v>
-      </c>
-      <c r="D60" s="5">
-        <v>76.11</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-0.84</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="5">
-        <v>43.91</v>
-      </c>
-      <c r="D61" s="5">
-        <v>42.43</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-1.48</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="5">
-        <v>43.34</v>
-      </c>
-      <c r="D62" s="5">
-        <v>42.25</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-1.09</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="5">
-        <v>37.29</v>
-      </c>
-      <c r="D63" s="5">
-        <v>32.53</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-4.76</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="5">
-        <v>31.56</v>
-      </c>
-      <c r="D64" s="5">
-        <v>31.1</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-0.46</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="5">
-        <v>41.86</v>
-      </c>
-      <c r="D65" s="5">
-        <v>39.34</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-2.52</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="5">
-        <v>44.3</v>
-      </c>
-      <c r="D66" s="5">
-        <v>42.61</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-1.69</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="5">
-        <v>44.23</v>
-      </c>
-      <c r="D67" s="5">
-        <v>41.78</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-2.45</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="5">
-        <v>53.71</v>
-      </c>
-      <c r="D68" s="5">
-        <v>55.97</v>
-      </c>
-      <c r="E68" s="6">
-        <v>2.26</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="5">
-        <v>44.19</v>
-      </c>
-      <c r="D69" s="5">
-        <v>40.76</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-3.43</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B70" s="3" t="s">
+      <c r="B79" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C70" s="5">
-        <v>-34.82</v>
-      </c>
-      <c r="D70" s="5">
-        <v>-33.52</v>
-      </c>
-      <c r="E70" s="6">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="5">
-        <v>29.85</v>
-      </c>
-      <c r="D71" s="5">
-        <v>6.7</v>
-      </c>
-      <c r="E71" s="7">
-        <v>-23.15</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="5">
-        <v>23.53</v>
-      </c>
-      <c r="D72" s="5">
-        <v>-18.24</v>
-      </c>
-      <c r="E72" s="7">
-        <v>-41.77</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="5">
-        <v>6.49</v>
-      </c>
-      <c r="D73" s="5">
-        <v>-31.38</v>
-      </c>
-      <c r="E73" s="7">
-        <v>-37.87</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="5">
-        <v>-26.61</v>
-      </c>
-      <c r="D74" s="5">
-        <v>-40.56</v>
-      </c>
-      <c r="E74" s="7">
-        <v>-13.95</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="5">
-        <v>-42.07</v>
-      </c>
-      <c r="D75" s="5">
-        <v>114.39</v>
-      </c>
-      <c r="E75" s="6">
-        <v>156.46</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="5">
-        <v>-7.77</v>
-      </c>
-      <c r="D76" s="5">
-        <v>-15.28</v>
-      </c>
-      <c r="E76" s="7">
-        <v>-7.51</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="5">
-        <v>-62.63</v>
-      </c>
-      <c r="D77" s="5">
-        <v>-48.2</v>
-      </c>
-      <c r="E77" s="6">
-        <v>14.43</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="5">
-        <v>-25.61</v>
-      </c>
-      <c r="D78" s="5">
+      <c r="C79" s="6">
         <v>-23.76</v>
       </c>
-      <c r="E78" s="6">
-        <v>1.85</v>
+      <c r="D79" s="6">
+        <v>-66.44</v>
+      </c>
+      <c r="E79" s="7">
+        <v>-42.68</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3345,61 +3422,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="8" t="s">
+      <c r="B1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="11">
+        <v>56.16</v>
+      </c>
+      <c r="C2" s="12">
+        <v>9</v>
+      </c>
+      <c r="D2" s="11">
+        <v>39.5</v>
+      </c>
+      <c r="E2" s="11">
         <v>60</v>
       </c>
-      <c r="E1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="10">
-        <v>56.16</v>
-      </c>
-      <c r="C2" s="11">
-        <v>9</v>
-      </c>
-      <c r="D2" s="10">
-        <v>41</v>
-      </c>
-      <c r="E2" s="10">
-        <v>60</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-6.4</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-1.5</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-6.3</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-1.4</v>
+      </c>
+      <c r="H2" s="11">
         <v>55.4</v>
       </c>
-      <c r="I2" s="10">
-        <v>10</v>
+      <c r="I2" s="11">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3500,61 +3577,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="13">
-        <v>0.6487000000000001</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.1943</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.1571</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.0784</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.0182</v>
-      </c>
-      <c r="F2" s="13">
-        <v>-0.0115</v>
-      </c>
-      <c r="G2" s="13">
-        <v>-0.0614</v>
-      </c>
-      <c r="H2" s="13">
-        <v>-0.06909999999999999</v>
-      </c>
-      <c r="I2" s="13">
-        <v>-0.0946</v>
+      <c r="A2" s="14">
+        <v>0.6474</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1933</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1564</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.07490000000000001</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.0161</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.0086</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.06480000000000001</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.07139999999999999</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.09710000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="66">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,28 +178,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -285,14 +264,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -325,13 +304,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -401,15 +380,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -924,10 +902,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1324.7</v>
+        <v>1321.4</v>
       </c>
       <c r="D2">
-        <v>-0.61</v>
+        <v>-0.25</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -936,46 +914,46 @@
         <v>1247.38</v>
       </c>
       <c r="G2">
-        <v>-30.38</v>
+        <v>-30.55</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>5.93</v>
       </c>
       <c r="I2">
-        <v>-3.9</v>
+        <v>-3.04</v>
       </c>
       <c r="J2">
-        <v>-4.23</v>
+        <v>-3.78</v>
       </c>
       <c r="K2">
-        <v>-2.23</v>
+        <v>-2.25</v>
       </c>
       <c r="L2">
-        <v>-26.7</v>
+        <v>-25.68</v>
       </c>
       <c r="M2">
-        <v>-9.710000000000001</v>
+        <v>-9.66</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P2">
-        <v>1343.54</v>
+        <v>1335.26</v>
       </c>
       <c r="Q2">
-        <v>1361.91</v>
+        <v>1359.09</v>
       </c>
       <c r="R2">
-        <v>1353.87</v>
+        <v>1353.44</v>
       </c>
       <c r="S2">
-        <v>1535.49</v>
+        <v>1532.84</v>
       </c>
       <c r="T2">
-        <v>-13.73</v>
+        <v>-13.79</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -990,34 +968,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>40.73</v>
+        <v>40.03</v>
       </c>
       <c r="Z2">
-        <v>-4.86</v>
+        <v>-7.14</v>
       </c>
       <c r="AA2">
-        <v>0.4</v>
+        <v>-1.11</v>
       </c>
       <c r="AB2">
-        <v>-5.26</v>
+        <v>-6.03</v>
       </c>
       <c r="AC2">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>13.65</v>
+        <v>4.93</v>
       </c>
       <c r="AE2">
-        <v>27.59</v>
+        <v>26.55</v>
       </c>
       <c r="AF2">
-        <v>-52.15</v>
+        <v>-51.91</v>
       </c>
       <c r="AG2">
-        <v>1405.3</v>
+        <v>1405.38</v>
       </c>
       <c r="AH2">
-        <v>1318.51</v>
+        <v>1312.8</v>
       </c>
       <c r="AI2">
         <v>1318.07</v>
@@ -1026,7 +1004,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>22.02</v>
+        <v>24.35</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1037,10 +1015,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2964.9</v>
+        <v>3035.1</v>
       </c>
       <c r="D3">
-        <v>-0.7</v>
+        <v>2.37</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1049,46 +1027,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-7.7</v>
+        <v>-5.51</v>
       </c>
       <c r="H3">
-        <v>68.65000000000001</v>
+        <v>72.64</v>
       </c>
       <c r="I3">
-        <v>-2.02</v>
+        <v>0.5</v>
       </c>
       <c r="J3">
-        <v>-5.89</v>
+        <v>-3.69</v>
       </c>
       <c r="K3">
-        <v>9.210000000000001</v>
+        <v>12.89</v>
       </c>
       <c r="L3">
-        <v>31.84</v>
+        <v>39.41</v>
       </c>
       <c r="M3">
-        <v>15.64</v>
+        <v>16.32</v>
       </c>
       <c r="N3">
         <v>88</v>
       </c>
       <c r="O3">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="P3">
-        <v>2995.22</v>
+        <v>2998.24</v>
       </c>
       <c r="Q3">
-        <v>3050.14</v>
+        <v>3043.87</v>
       </c>
       <c r="R3">
-        <v>3050.98</v>
+        <v>3052.25</v>
       </c>
       <c r="S3">
-        <v>2465.81</v>
+        <v>2468.52</v>
       </c>
       <c r="T3">
-        <v>20.24</v>
+        <v>22.95</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1103,34 +1081,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>39.95</v>
+        <v>49.88</v>
       </c>
       <c r="Z3">
-        <v>-18.42</v>
+        <v>-15.71</v>
       </c>
       <c r="AA3">
-        <v>-5.38</v>
+        <v>-7.45</v>
       </c>
       <c r="AB3">
-        <v>-13.03</v>
+        <v>-8.26</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>30.2</v>
       </c>
       <c r="AD3">
-        <v>3.46</v>
+        <v>11.07</v>
       </c>
       <c r="AE3">
-        <v>68.98999999999999</v>
+        <v>71.06</v>
       </c>
       <c r="AF3">
-        <v>24.05</v>
+        <v>56.76</v>
       </c>
       <c r="AG3">
-        <v>3181.4</v>
+        <v>3164.43</v>
       </c>
       <c r="AH3">
-        <v>2918.89</v>
+        <v>2923.3</v>
       </c>
       <c r="AI3">
         <v>2959.69</v>
@@ -1139,7 +1117,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>28.76</v>
+        <v>26.71</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1150,10 +1128,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1319</v>
+        <v>1348</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>2.2</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1162,46 +1140,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-17.79</v>
+        <v>-15.99</v>
       </c>
       <c r="H4">
-        <v>70.68000000000001</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="I4">
-        <v>-3.83</v>
+        <v>-1.78</v>
       </c>
       <c r="J4">
-        <v>-15.2</v>
+        <v>-12.68</v>
       </c>
       <c r="K4">
-        <v>-4.35</v>
+        <v>-1.53</v>
       </c>
       <c r="L4">
-        <v>40.81</v>
+        <v>47.48</v>
       </c>
       <c r="M4">
-        <v>7.49</v>
+        <v>7.83</v>
       </c>
       <c r="N4">
         <v>77</v>
       </c>
       <c r="O4">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="P4">
-        <v>1351.74</v>
+        <v>1346.86</v>
       </c>
       <c r="Q4">
-        <v>1400.73</v>
+        <v>1392.44</v>
       </c>
       <c r="R4">
-        <v>1469.03</v>
+        <v>1467.53</v>
       </c>
       <c r="S4">
-        <v>1158.52</v>
+        <v>1160.18</v>
       </c>
       <c r="T4">
-        <v>13.85</v>
+        <v>16.19</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1216,43 +1194,43 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>30.86</v>
+        <v>38.31</v>
       </c>
       <c r="Z4">
-        <v>-37.95</v>
+        <v>-37</v>
       </c>
       <c r="AA4">
-        <v>-32.17</v>
+        <v>-33.14</v>
       </c>
       <c r="AB4">
-        <v>-5.77</v>
+        <v>-3.86</v>
       </c>
       <c r="AC4">
-        <v>14.3</v>
+        <v>24.51</v>
       </c>
       <c r="AD4">
-        <v>23.47</v>
+        <v>21.25</v>
       </c>
       <c r="AE4">
-        <v>44.34</v>
+        <v>43.52</v>
       </c>
       <c r="AF4">
-        <v>-33.62</v>
+        <v>-55.84</v>
       </c>
       <c r="AG4">
-        <v>1525.87</v>
+        <v>1507.58</v>
       </c>
       <c r="AH4">
-        <v>1275.59</v>
+        <v>1277.29</v>
       </c>
       <c r="AI4">
-        <v>1466.37</v>
+        <v>1462.12</v>
       </c>
       <c r="AJ4" t="s">
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>24.81</v>
+        <v>24.19</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1263,10 +1241,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1658</v>
+        <v>1700</v>
       </c>
       <c r="D5">
-        <v>-0.42</v>
+        <v>2.53</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1275,46 +1253,46 @@
         <v>1294.84</v>
       </c>
       <c r="G5">
-        <v>-11.96</v>
+        <v>-9.73</v>
       </c>
       <c r="H5">
-        <v>28.05</v>
+        <v>31.29</v>
       </c>
       <c r="I5">
-        <v>-2.18</v>
+        <v>0.38</v>
       </c>
       <c r="J5">
-        <v>-9.35</v>
+        <v>-6.92</v>
       </c>
       <c r="K5">
-        <v>-7.25</v>
+        <v>-4.51</v>
       </c>
       <c r="L5">
-        <v>23.75</v>
+        <v>28.84</v>
       </c>
       <c r="M5">
-        <v>19.33</v>
+        <v>19.85</v>
       </c>
       <c r="N5">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="O5">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="P5">
-        <v>1673.14</v>
+        <v>1674.44</v>
       </c>
       <c r="Q5">
-        <v>1734.39</v>
+        <v>1727.52</v>
       </c>
       <c r="R5">
-        <v>1785.22</v>
+        <v>1783.56</v>
       </c>
       <c r="S5">
-        <v>1583.66</v>
+        <v>1585.09</v>
       </c>
       <c r="T5">
-        <v>4.69</v>
+        <v>7.25</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1329,34 +1307,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>30.05</v>
+        <v>42.58</v>
       </c>
       <c r="Z5">
-        <v>-36.88</v>
+        <v>-33.86</v>
       </c>
       <c r="AA5">
-        <v>-30.65</v>
+        <v>-31.29</v>
       </c>
       <c r="AB5">
-        <v>-6.23</v>
+        <v>-2.56</v>
       </c>
       <c r="AC5">
-        <v>23.25</v>
+        <v>47.37</v>
       </c>
       <c r="AD5">
-        <v>25.56</v>
+        <v>32.29</v>
       </c>
       <c r="AE5">
-        <v>35.19</v>
+        <v>35.74</v>
       </c>
       <c r="AF5">
-        <v>-8.210000000000001</v>
+        <v>-10.95</v>
       </c>
       <c r="AG5">
-        <v>1863.52</v>
+        <v>1847.9</v>
       </c>
       <c r="AH5">
-        <v>1605.27</v>
+        <v>1607.15</v>
       </c>
       <c r="AI5">
         <v>1761.08</v>
@@ -1365,7 +1343,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>55.59</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1376,37 +1354,37 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>206.1</v>
+        <v>205.25</v>
       </c>
       <c r="D6">
-        <v>-0.43</v>
+        <v>-0.41</v>
       </c>
       <c r="E6">
         <v>248.91</v>
       </c>
       <c r="F6">
-        <v>115.38</v>
+        <v>116.81</v>
       </c>
       <c r="G6">
-        <v>-17.2</v>
+        <v>-17.54</v>
       </c>
       <c r="H6">
-        <v>78.63</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="I6">
-        <v>-0.97</v>
+        <v>-1.79</v>
       </c>
       <c r="J6">
-        <v>-5.88</v>
+        <v>-5.23</v>
       </c>
       <c r="K6">
-        <v>-6.88</v>
+        <v>-6.41</v>
       </c>
       <c r="L6">
-        <v>77.98999999999999</v>
+        <v>77.89</v>
       </c>
       <c r="M6">
-        <v>64.73999999999999</v>
+        <v>65.44</v>
       </c>
       <c r="N6">
         <v>99</v>
@@ -1415,19 +1393,19 @@
         <v>85</v>
       </c>
       <c r="P6">
-        <v>208.35</v>
+        <v>207.6</v>
       </c>
       <c r="Q6">
-        <v>211.6</v>
+        <v>211.14</v>
       </c>
       <c r="R6">
-        <v>218.93</v>
+        <v>218.43</v>
       </c>
       <c r="S6">
-        <v>178.76</v>
+        <v>178.97</v>
       </c>
       <c r="T6">
-        <v>15.29</v>
+        <v>14.68</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1442,43 +1420,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>38.23</v>
+        <v>37.17</v>
       </c>
       <c r="Z6">
-        <v>-3.27</v>
+        <v>-3.37</v>
       </c>
       <c r="AA6">
-        <v>-3.18</v>
+        <v>-3.22</v>
       </c>
       <c r="AB6">
-        <v>-0.09</v>
+        <v>-0.16</v>
       </c>
       <c r="AC6">
-        <v>26.1</v>
+        <v>8.98</v>
       </c>
       <c r="AD6">
-        <v>43.2</v>
+        <v>28.3</v>
       </c>
       <c r="AE6">
-        <v>5.31</v>
+        <v>5.16</v>
       </c>
       <c r="AF6">
-        <v>-36.78</v>
+        <v>-31.9</v>
       </c>
       <c r="AG6">
-        <v>219.66</v>
+        <v>219.56</v>
       </c>
       <c r="AH6">
-        <v>203.55</v>
+        <v>202.73</v>
       </c>
       <c r="AI6">
-        <v>222.84</v>
+        <v>222.04</v>
       </c>
       <c r="AJ6" t="s">
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>21.99</v>
+        <v>22.74</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1489,10 +1467,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>419.4</v>
+        <v>417.5</v>
       </c>
       <c r="D7">
-        <v>-0.38</v>
+        <v>-0.45</v>
       </c>
       <c r="E7">
         <v>589.48</v>
@@ -1501,25 +1479,25 @@
         <v>393.4</v>
       </c>
       <c r="G7">
-        <v>-28.85</v>
+        <v>-29.17</v>
       </c>
       <c r="H7">
-        <v>6.61</v>
+        <v>6.13</v>
       </c>
       <c r="I7">
-        <v>-3.92</v>
+        <v>-3.8</v>
       </c>
       <c r="J7">
-        <v>-3.64</v>
+        <v>-3.71</v>
       </c>
       <c r="K7">
-        <v>-2.83</v>
+        <v>-2.46</v>
       </c>
       <c r="L7">
-        <v>-28.85</v>
+        <v>-27.66</v>
       </c>
       <c r="M7">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="N7">
         <v>23</v>
@@ -1528,19 +1506,19 @@
         <v>20</v>
       </c>
       <c r="P7">
-        <v>425.85</v>
+        <v>422.55</v>
       </c>
       <c r="Q7">
-        <v>432.3</v>
+        <v>431.25</v>
       </c>
       <c r="R7">
-        <v>428.16</v>
+        <v>428.02</v>
       </c>
       <c r="S7">
-        <v>480.47</v>
+        <v>479.77</v>
       </c>
       <c r="T7">
-        <v>-12.71</v>
+        <v>-12.98</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1555,34 +1533,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>41.7</v>
+        <v>40.59</v>
       </c>
       <c r="Z7">
-        <v>-1.45</v>
+        <v>-2.3</v>
       </c>
       <c r="AA7">
-        <v>0.46</v>
+        <v>-0.09</v>
       </c>
       <c r="AB7">
-        <v>-1.91</v>
+        <v>-2.21</v>
       </c>
       <c r="AC7">
         <v>0</v>
       </c>
       <c r="AD7">
-        <v>10.29</v>
+        <v>2.88</v>
       </c>
       <c r="AE7">
-        <v>10.05</v>
+        <v>9.6</v>
       </c>
       <c r="AF7">
-        <v>-20.35</v>
+        <v>-39.79</v>
       </c>
       <c r="AG7">
-        <v>446.99</v>
+        <v>447.03</v>
       </c>
       <c r="AH7">
-        <v>417.62</v>
+        <v>415.48</v>
       </c>
       <c r="AI7">
         <v>411.2</v>
@@ -1591,7 +1569,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>20.94</v>
+        <v>23.56</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1602,10 +1580,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>655.05</v>
+        <v>654.05</v>
       </c>
       <c r="D8">
-        <v>-0.8</v>
+        <v>-0.15</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1614,46 +1592,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-18.96</v>
+        <v>-19.08</v>
       </c>
       <c r="H8">
-        <v>40.05</v>
+        <v>39.83</v>
       </c>
       <c r="I8">
-        <v>-0.79</v>
+        <v>-0.53</v>
       </c>
       <c r="J8">
-        <v>-8.44</v>
+        <v>-7.58</v>
       </c>
       <c r="K8">
-        <v>6.33</v>
+        <v>7.24</v>
       </c>
       <c r="L8">
-        <v>10.72</v>
+        <v>11.92</v>
       </c>
       <c r="M8">
-        <v>-6.48</v>
+        <v>-6.74</v>
       </c>
       <c r="N8">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="O8">
         <v>61</v>
       </c>
       <c r="P8">
-        <v>659.84</v>
+        <v>659.14</v>
       </c>
       <c r="Q8">
-        <v>666.74</v>
+        <v>664.11</v>
       </c>
       <c r="R8">
-        <v>701.05</v>
+        <v>699.25</v>
       </c>
       <c r="S8">
-        <v>612.63</v>
+        <v>612.8099999999999</v>
       </c>
       <c r="T8">
-        <v>6.92</v>
+        <v>6.73</v>
       </c>
       <c r="U8" t="s">
         <v>48</v>
@@ -1668,43 +1646,43 @@
         <v>2</v>
       </c>
       <c r="Y8">
-        <v>39.61</v>
+        <v>39.2</v>
       </c>
       <c r="Z8">
-        <v>-11.44</v>
+        <v>-11.28</v>
       </c>
       <c r="AA8">
-        <v>-12.54</v>
+        <v>-12.29</v>
       </c>
       <c r="AB8">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AC8">
-        <v>81.65000000000001</v>
+        <v>68.56</v>
       </c>
       <c r="AD8">
-        <v>83.66</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="AE8">
-        <v>17.68</v>
+        <v>17.07</v>
       </c>
       <c r="AF8">
-        <v>-44.5</v>
+        <v>-47.76</v>
       </c>
       <c r="AG8">
-        <v>704.55</v>
+        <v>697.27</v>
       </c>
       <c r="AH8">
-        <v>628.9400000000001</v>
+        <v>630.96</v>
       </c>
       <c r="AI8">
-        <v>713.42</v>
+        <v>707.83</v>
       </c>
       <c r="AJ8" t="s">
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>25.1</v>
+        <v>25.22</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1715,10 +1693,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>192.11</v>
+        <v>192.16</v>
       </c>
       <c r="D9">
-        <v>-1.1</v>
+        <v>0.03</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1727,46 +1705,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-30.8</v>
+        <v>-30.78</v>
       </c>
       <c r="H9">
-        <v>11.5</v>
+        <v>11.53</v>
       </c>
       <c r="I9">
-        <v>-2.67</v>
+        <v>-2.7</v>
       </c>
       <c r="J9">
-        <v>1.68</v>
+        <v>1.22</v>
       </c>
       <c r="K9">
-        <v>-3.82</v>
+        <v>-3.62</v>
       </c>
       <c r="L9">
-        <v>-23.37</v>
+        <v>-24.39</v>
       </c>
       <c r="M9">
-        <v>-7.14</v>
+        <v>-7.13</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P9">
-        <v>194.57</v>
+        <v>193.5</v>
       </c>
       <c r="Q9">
-        <v>191.14</v>
+        <v>191.32</v>
       </c>
       <c r="R9">
-        <v>189</v>
+        <v>189.05</v>
       </c>
       <c r="S9">
-        <v>209.75</v>
+        <v>209.38</v>
       </c>
       <c r="T9">
-        <v>-8.41</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1781,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>51.76</v>
+        <v>51.85</v>
       </c>
       <c r="Z9">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AA9">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AB9">
-        <v>0.29</v>
+        <v>0.11</v>
       </c>
       <c r="AC9">
-        <v>44.81</v>
+        <v>41.37</v>
       </c>
       <c r="AD9">
-        <v>60.49</v>
+        <v>49.11</v>
       </c>
       <c r="AE9">
-        <v>4.82</v>
+        <v>4.67</v>
       </c>
       <c r="AF9">
-        <v>-56.02</v>
+        <v>13.44</v>
       </c>
       <c r="AG9">
-        <v>197.95</v>
+        <v>198.03</v>
       </c>
       <c r="AH9">
-        <v>184.34</v>
+        <v>184.6</v>
       </c>
       <c r="AI9">
         <v>197.85</v>
@@ -1817,7 +1795,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>44.91</v>
+        <v>41.98</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1828,10 +1806,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>76.37</v>
+        <v>76.53</v>
       </c>
       <c r="D10">
-        <v>0.34</v>
+        <v>0.21</v>
       </c>
       <c r="E10">
         <v>150.86</v>
@@ -1840,46 +1818,46 @@
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-49.38</v>
+        <v>-49.27</v>
       </c>
       <c r="H10">
-        <v>28.83</v>
+        <v>29.1</v>
       </c>
       <c r="I10">
-        <v>-1.31</v>
+        <v>-0.44</v>
       </c>
       <c r="J10">
-        <v>-6.18</v>
+        <v>-5.01</v>
       </c>
       <c r="K10">
-        <v>-1.02</v>
+        <v>2.77</v>
       </c>
       <c r="L10">
-        <v>-41.96</v>
+        <v>-40.96</v>
       </c>
       <c r="M10">
-        <v>-0.86</v>
+        <v>-0.47</v>
       </c>
       <c r="N10">
         <v>12</v>
       </c>
       <c r="O10">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="P10">
-        <v>76.48999999999999</v>
+        <v>76.42</v>
       </c>
       <c r="Q10">
-        <v>77.15000000000001</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="R10">
-        <v>79.66</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="S10">
-        <v>82.2</v>
+        <v>82.11</v>
       </c>
       <c r="T10">
-        <v>-7.09</v>
+        <v>-6.8</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1894,34 +1872,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>42.26</v>
+        <v>43.2</v>
       </c>
       <c r="Z10">
-        <v>-0.93</v>
+        <v>-0.89</v>
       </c>
       <c r="AA10">
-        <v>-0.97</v>
+        <v>-0.95</v>
       </c>
       <c r="AB10">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AC10">
-        <v>67.34</v>
+        <v>61.58</v>
       </c>
       <c r="AD10">
-        <v>68.58</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="AE10">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AF10">
-        <v>-66.44</v>
+        <v>-2.39</v>
       </c>
       <c r="AG10">
-        <v>79.81999999999999</v>
+        <v>79.22</v>
       </c>
       <c r="AH10">
-        <v>74.47</v>
+        <v>74.7</v>
       </c>
       <c r="AI10">
         <v>74.97</v>
@@ -1930,7 +1908,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>14.17</v>
+        <v>14.15</v>
       </c>
     </row>
   </sheetData>
@@ -2071,7 +2049,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2091,1318 +2069,1297 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>64</v>
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-4.23</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-3.78</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.45</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-5.89</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-3.69</v>
+      </c>
+      <c r="E8" s="6">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-15.2</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-12.68</v>
+      </c>
+      <c r="E9" s="6">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-9.35</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-6.92</v>
+      </c>
+      <c r="E10" s="6">
+        <v>2.43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-5.88</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-5.23</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-3.64</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-3.71</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-8.44</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-7.58</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="5">
+        <v>1.68</v>
+      </c>
+      <c r="D14" s="5">
+        <v>1.22</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-6.18</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-5.01</v>
+      </c>
+      <c r="E15" s="6">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-2.14</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-4.23</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-2.09</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-3.9</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-3.04</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-6.37</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-5.89</v>
-      </c>
-      <c r="E9" s="8">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-2.02</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="E17" s="6">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-16.96</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-15.2</v>
-      </c>
-      <c r="E10" s="8">
-        <v>1.76</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-3.83</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-1.78</v>
+      </c>
+      <c r="E18" s="6">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-8.609999999999999</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-9.35</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.74</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-2.18</v>
+      </c>
+      <c r="D19" s="5">
+        <v>0.38</v>
+      </c>
+      <c r="E19" s="6">
+        <v>2.56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-8.48</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-5.88</v>
-      </c>
-      <c r="E12" s="8">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-0.97</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-1.79</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-2.05</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-3.64</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-1.59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-3.92</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-3.8</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-8.49</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-8.44</v>
-      </c>
-      <c r="E14" s="8">
+      <c r="B22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-0.79</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-0.53</v>
+      </c>
+      <c r="E22" s="6">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-2.67</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-2.7</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-1.31</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-0.44</v>
+      </c>
+      <c r="E24" s="6">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-26.7</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-25.68</v>
+      </c>
+      <c r="E25" s="6">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>31.84</v>
+      </c>
+      <c r="D26" s="5">
+        <v>39.41</v>
+      </c>
+      <c r="E26" s="6">
+        <v>7.57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>40.81</v>
+      </c>
+      <c r="D27" s="5">
+        <v>47.48</v>
+      </c>
+      <c r="E27" s="6">
+        <v>6.67</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="5">
+        <v>23.75</v>
+      </c>
+      <c r="D28" s="5">
+        <v>28.84</v>
+      </c>
+      <c r="E28" s="6">
+        <v>5.09</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="5">
+        <v>77.98999999999999</v>
+      </c>
+      <c r="D29" s="5">
+        <v>77.89</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-28.85</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-27.66</v>
+      </c>
+      <c r="E30" s="6">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="5">
+        <v>10.72</v>
+      </c>
+      <c r="D31" s="5">
+        <v>11.92</v>
+      </c>
+      <c r="E31" s="6">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-23.37</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-24.39</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="5">
+        <v>-41.96</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-40.96</v>
+      </c>
+      <c r="E33" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-2.23</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-2.25</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="5">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="D35" s="5">
+        <v>12.89</v>
+      </c>
+      <c r="E35" s="6">
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-4.35</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-1.53</v>
+      </c>
+      <c r="E36" s="6">
+        <v>2.82</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-7.25</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-4.51</v>
+      </c>
+      <c r="E37" s="6">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-6.88</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-6.41</v>
+      </c>
+      <c r="E38" s="6">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-2.83</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-2.46</v>
+      </c>
+      <c r="E39" s="6">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="5">
+        <v>6.33</v>
+      </c>
+      <c r="D40" s="5">
+        <v>7.24</v>
+      </c>
+      <c r="E40" s="6">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-3.82</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-3.62</v>
+      </c>
+      <c r="E41" s="6">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="5">
+        <v>-1.02</v>
+      </c>
+      <c r="D42" s="5">
+        <v>2.77</v>
+      </c>
+      <c r="E42" s="6">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-30.38</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-30.55</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-7.7</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-5.51</v>
+      </c>
+      <c r="E44" s="6">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-17.79</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-15.99</v>
+      </c>
+      <c r="E45" s="6">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="5">
+        <v>-11.96</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-9.73</v>
+      </c>
+      <c r="E46" s="6">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="5">
+        <v>-17.2</v>
+      </c>
+      <c r="D47" s="5">
+        <v>-17.54</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="5">
+        <v>-28.85</v>
+      </c>
+      <c r="D48" s="5">
+        <v>-29.17</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="5">
+        <v>-18.96</v>
+      </c>
+      <c r="D49" s="5">
+        <v>-19.08</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="5">
+        <v>-30.8</v>
+      </c>
+      <c r="D50" s="5">
+        <v>-30.78</v>
+      </c>
+      <c r="E50" s="6">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="5">
+        <v>-49.38</v>
+      </c>
+      <c r="D51" s="5">
+        <v>-49.27</v>
+      </c>
+      <c r="E51" s="6">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="5">
+        <v>1324.7</v>
+      </c>
+      <c r="D52" s="5">
+        <v>1321.4</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-3.3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="5">
+        <v>2964.9</v>
+      </c>
+      <c r="D53" s="5">
+        <v>3035.1</v>
+      </c>
+      <c r="E53" s="6">
+        <v>70.2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="5">
+        <v>1319</v>
+      </c>
+      <c r="D54" s="5">
+        <v>1348</v>
+      </c>
+      <c r="E54" s="6">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="5">
+        <v>1658</v>
+      </c>
+      <c r="D55" s="5">
+        <v>1700</v>
+      </c>
+      <c r="E55" s="6">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="5">
+        <v>206.1</v>
+      </c>
+      <c r="D56" s="5">
+        <v>205.25</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="5">
+        <v>419.4</v>
+      </c>
+      <c r="D57" s="5">
+        <v>417.5</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-1.9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="5">
+        <v>655.05</v>
+      </c>
+      <c r="D58" s="5">
+        <v>654.05</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="5">
+        <v>192.11</v>
+      </c>
+      <c r="D59" s="5">
+        <v>192.16</v>
+      </c>
+      <c r="E59" s="6">
         <v>0.05</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="5">
+        <v>76.37</v>
+      </c>
+      <c r="D60" s="5">
+        <v>76.53</v>
+      </c>
+      <c r="E60" s="6">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="5">
+        <v>55</v>
+      </c>
+      <c r="D61" s="5">
+        <v>66</v>
+      </c>
+      <c r="E61" s="6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="5">
+        <v>66</v>
+      </c>
+      <c r="D62" s="5">
+        <v>55</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="5">
+        <v>40.73</v>
+      </c>
+      <c r="D63" s="5">
+        <v>40.03</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="5">
+        <v>39.95</v>
+      </c>
+      <c r="D64" s="5">
+        <v>49.88</v>
+      </c>
+      <c r="E64" s="6">
+        <v>9.93</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="5">
+        <v>30.86</v>
+      </c>
+      <c r="D65" s="5">
+        <v>38.31</v>
+      </c>
+      <c r="E65" s="6">
+        <v>7.45</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="5">
+        <v>30.05</v>
+      </c>
+      <c r="D66" s="5">
+        <v>42.58</v>
+      </c>
+      <c r="E66" s="6">
+        <v>12.53</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="5">
+        <v>38.23</v>
+      </c>
+      <c r="D67" s="5">
+        <v>37.17</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="5">
+        <v>41.7</v>
+      </c>
+      <c r="D68" s="5">
+        <v>40.59</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-1.11</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="5">
+        <v>39.61</v>
+      </c>
+      <c r="D69" s="5">
+        <v>39.2</v>
+      </c>
+      <c r="E69" s="7">
+        <v>-0.41</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>2.63</v>
-      </c>
-      <c r="D15" s="6">
-        <v>1.68</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-0.95</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B70" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="5">
+        <v>51.76</v>
+      </c>
+      <c r="D70" s="5">
+        <v>51.85</v>
+      </c>
+      <c r="E70" s="6">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-7.23</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-6.18</v>
-      </c>
-      <c r="E16" s="8">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B71" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="5">
+        <v>42.26</v>
+      </c>
+      <c r="D71" s="5">
+        <v>43.2</v>
+      </c>
+      <c r="E71" s="6">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-4.39</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-3.9</v>
-      </c>
-      <c r="E17" s="8">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B72" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="5">
+        <v>-52.15</v>
+      </c>
+      <c r="D72" s="5">
+        <v>-51.91</v>
+      </c>
+      <c r="E72" s="6">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-2.11</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-2.02</v>
-      </c>
-      <c r="E18" s="8">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B73" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="5">
+        <v>24.05</v>
+      </c>
+      <c r="D73" s="5">
+        <v>56.76</v>
+      </c>
+      <c r="E73" s="6">
+        <v>32.71</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3.46</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-3.83</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B74" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="5">
+        <v>-33.62</v>
+      </c>
+      <c r="D74" s="5">
+        <v>-55.84</v>
+      </c>
+      <c r="E74" s="7">
+        <v>-22.22</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-2.06</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-2.18</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B75" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="5">
+        <v>-8.210000000000001</v>
+      </c>
+      <c r="D75" s="5">
+        <v>-10.95</v>
+      </c>
+      <c r="E75" s="7">
+        <v>-2.74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-0.96</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-0.97</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B76" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="5">
+        <v>-36.78</v>
+      </c>
+      <c r="D76" s="5">
+        <v>-31.9</v>
+      </c>
+      <c r="E76" s="6">
+        <v>4.88</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-5.39</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-3.92</v>
-      </c>
-      <c r="E22" s="8">
-        <v>1.47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B77" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="5">
+        <v>-20.35</v>
+      </c>
+      <c r="D77" s="5">
+        <v>-39.79</v>
+      </c>
+      <c r="E77" s="7">
+        <v>-19.44</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>0</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-0.79</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B78" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="5">
+        <v>-44.5</v>
+      </c>
+      <c r="D78" s="5">
+        <v>-47.76</v>
+      </c>
+      <c r="E78" s="7">
+        <v>-3.26</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>0.36</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-2.67</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-3.03</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B79" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="5">
+        <v>-56.02</v>
+      </c>
+      <c r="D79" s="5">
+        <v>13.44</v>
+      </c>
+      <c r="E79" s="6">
+        <v>69.45999999999999</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-1.37</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-1.31</v>
-      </c>
-      <c r="E25" s="8">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-26.76</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-26.7</v>
-      </c>
-      <c r="E26" s="8">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>29.85</v>
-      </c>
-      <c r="D27" s="6">
-        <v>31.84</v>
-      </c>
-      <c r="E27" s="8">
-        <v>1.99</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>39.14</v>
-      </c>
-      <c r="D28" s="6">
-        <v>40.81</v>
-      </c>
-      <c r="E28" s="8">
-        <v>1.67</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>22.3</v>
-      </c>
-      <c r="D29" s="6">
-        <v>23.75</v>
-      </c>
-      <c r="E29" s="8">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>82.39</v>
-      </c>
-      <c r="D30" s="6">
-        <v>77.98999999999999</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-4.4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-28.28</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-28.85</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-0.57</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>12.15</v>
-      </c>
-      <c r="D32" s="6">
-        <v>10.72</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-1.43</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-23.19</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-23.37</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-0.18</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-42.99</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-41.96</v>
-      </c>
-      <c r="E34" s="8">
-        <v>1.03</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-2.73</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-2.23</v>
-      </c>
-      <c r="E35" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>10.1</v>
-      </c>
-      <c r="D36" s="6">
-        <v>9.210000000000001</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-0.89</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-5.84</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-4.35</v>
-      </c>
-      <c r="E37" s="8">
-        <v>1.49</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-5.72</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-7.25</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-1.53</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-7.8</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-6.88</v>
-      </c>
-      <c r="E39" s="8">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-4.69</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-2.83</v>
-      </c>
-      <c r="E40" s="8">
-        <v>1.86</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>7.83</v>
-      </c>
-      <c r="D41" s="6">
-        <v>6.33</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-3.27</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-3.82</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-0.55</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-1.76</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-1.02</v>
-      </c>
-      <c r="E43" s="8">
-        <v>0.74</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-29.95</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-30.38</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-7.05</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-7.7</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-0.65</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-16.96</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-17.79</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-0.83</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-11.59</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-11.96</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-16.84</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-17.2</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-0.36</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-28.58</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-28.85</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-18.3</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-18.96</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-0.66</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-30.03</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-30.8</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-0.77</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="6">
-        <v>-49.55</v>
-      </c>
-      <c r="D52" s="6">
-        <v>-49.38</v>
-      </c>
-      <c r="E52" s="8">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>1332.8</v>
-      </c>
-      <c r="D53" s="6">
-        <v>1324.7</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-8.1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>2985.7</v>
-      </c>
-      <c r="D54" s="6">
-        <v>2964.9</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-20.8</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>1332.3</v>
-      </c>
-      <c r="D55" s="6">
-        <v>1319</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-13.3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>1665</v>
-      </c>
-      <c r="D56" s="6">
-        <v>1658</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-7</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>206.99</v>
-      </c>
-      <c r="D57" s="6">
-        <v>206.1</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-0.89</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>421</v>
-      </c>
-      <c r="D58" s="6">
-        <v>419.4</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-1.6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>660.35</v>
-      </c>
-      <c r="D59" s="6">
-        <v>655.05</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-5.3</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="6">
-        <v>194.24</v>
-      </c>
-      <c r="D60" s="6">
-        <v>192.11</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-2.13</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="6">
-        <v>76.11</v>
-      </c>
-      <c r="D61" s="6">
-        <v>76.37</v>
-      </c>
-      <c r="E61" s="8">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="6">
-        <v>42.43</v>
-      </c>
-      <c r="D62" s="6">
-        <v>40.73</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="6">
-        <v>42.25</v>
-      </c>
-      <c r="D63" s="6">
-        <v>39.95</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-2.3</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="6">
-        <v>32.53</v>
-      </c>
-      <c r="D64" s="6">
-        <v>30.86</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-1.67</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>31.1</v>
-      </c>
-      <c r="D65" s="6">
-        <v>30.05</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-1.05</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>39.34</v>
-      </c>
-      <c r="D66" s="6">
-        <v>38.23</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-1.11</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>42.61</v>
-      </c>
-      <c r="D67" s="6">
-        <v>41.7</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-0.91</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>41.78</v>
-      </c>
-      <c r="D68" s="6">
-        <v>39.61</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-2.17</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="6">
-        <v>55.97</v>
-      </c>
-      <c r="D69" s="6">
-        <v>51.76</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-4.21</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="6">
-        <v>40.76</v>
-      </c>
-      <c r="D70" s="6">
-        <v>42.26</v>
-      </c>
-      <c r="E70" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B71" s="5" t="s">
+      <c r="B80" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C71" s="6">
-        <v>-33.52</v>
-      </c>
-      <c r="D71" s="6">
-        <v>-52.15</v>
-      </c>
-      <c r="E71" s="7">
-        <v>-18.63</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="6">
-        <v>6.7</v>
-      </c>
-      <c r="D72" s="6">
-        <v>24.05</v>
-      </c>
-      <c r="E72" s="8">
-        <v>17.35</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="6">
-        <v>-18.24</v>
-      </c>
-      <c r="D73" s="6">
-        <v>-33.62</v>
-      </c>
-      <c r="E73" s="7">
-        <v>-15.38</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="6">
-        <v>-31.38</v>
-      </c>
-      <c r="D74" s="6">
-        <v>-8.210000000000001</v>
-      </c>
-      <c r="E74" s="8">
-        <v>23.17</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="6">
-        <v>-40.56</v>
-      </c>
-      <c r="D75" s="6">
-        <v>-36.78</v>
-      </c>
-      <c r="E75" s="8">
-        <v>3.78</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>114.39</v>
-      </c>
-      <c r="D76" s="6">
-        <v>-20.35</v>
-      </c>
-      <c r="E76" s="7">
-        <v>-134.74</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>-15.28</v>
-      </c>
-      <c r="D77" s="6">
-        <v>-44.5</v>
-      </c>
-      <c r="E77" s="7">
-        <v>-29.22</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>-48.2</v>
-      </c>
-      <c r="D78" s="6">
-        <v>-56.02</v>
-      </c>
-      <c r="E78" s="7">
-        <v>-7.82</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>-23.76</v>
-      </c>
-      <c r="D79" s="6">
+      <c r="C80" s="5">
         <v>-66.44</v>
       </c>
-      <c r="E79" s="7">
-        <v>-42.68</v>
+      <c r="D80" s="5">
+        <v>-2.39</v>
+      </c>
+      <c r="E80" s="6">
+        <v>64.05</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3422,60 +3379,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>72</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>56.16</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
-        <v>39.5</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>42.5</v>
+      </c>
+      <c r="E2" s="10">
         <v>60</v>
       </c>
-      <c r="F2" s="11">
-        <v>-6.3</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-1.4</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-5.3</v>
+      </c>
+      <c r="G2" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="H2" s="10">
         <v>55.4</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -3577,61 +3534,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>0.6474</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.1933</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1564</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.07490000000000001</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.0161</v>
-      </c>
-      <c r="F2" s="14">
-        <v>-0.0086</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.06480000000000001</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.07139999999999999</v>
-      </c>
-      <c r="I2" s="14">
-        <v>-0.09710000000000001</v>
+      <c r="A2" s="13">
+        <v>0.6544</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.1985</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.1632</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.07829999999999999</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.0183</v>
+      </c>
+      <c r="F2" s="13">
+        <v>-0.004699999999999999</v>
+      </c>
+      <c r="G2" s="13">
+        <v>-0.0674</v>
+      </c>
+      <c r="H2" s="13">
+        <v>-0.0713</v>
+      </c>
+      <c r="I2" s="13">
+        <v>-0.09660000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="66">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,10 +169,10 @@
     <t>No</t>
   </si>
   <si>
+    <t>DOWN</t>
+  </si>
+  <si>
     <t>UP</t>
-  </si>
-  <si>
-    <t>DOWN</t>
   </si>
   <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
@@ -264,14 +264,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -304,13 +304,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -902,10 +902,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1321.4</v>
+        <v>1316.6</v>
       </c>
       <c r="D2">
-        <v>-0.25</v>
+        <v>-0.36</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -914,46 +914,46 @@
         <v>1247.38</v>
       </c>
       <c r="G2">
-        <v>-30.55</v>
+        <v>-30.8</v>
       </c>
       <c r="H2">
-        <v>5.93</v>
+        <v>5.55</v>
       </c>
       <c r="I2">
-        <v>-3.04</v>
+        <v>-3.02</v>
       </c>
       <c r="J2">
-        <v>-3.78</v>
+        <v>-4.43</v>
       </c>
       <c r="K2">
-        <v>-2.25</v>
+        <v>-2.58</v>
       </c>
       <c r="L2">
-        <v>-25.68</v>
+        <v>-25.86</v>
       </c>
       <c r="M2">
-        <v>-9.66</v>
+        <v>-9.82</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P2">
-        <v>1335.26</v>
+        <v>1327.06</v>
       </c>
       <c r="Q2">
-        <v>1359.09</v>
+        <v>1355.85</v>
       </c>
       <c r="R2">
-        <v>1353.44</v>
+        <v>1353.32</v>
       </c>
       <c r="S2">
-        <v>1532.84</v>
+        <v>1530.17</v>
       </c>
       <c r="T2">
-        <v>-13.79</v>
+        <v>-13.96</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -968,43 +968,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>40.03</v>
+        <v>38.98</v>
       </c>
       <c r="Z2">
-        <v>-7.14</v>
+        <v>-9.23</v>
       </c>
       <c r="AA2">
-        <v>-1.11</v>
+        <v>-2.73</v>
       </c>
       <c r="AB2">
-        <v>-6.03</v>
+        <v>-6.5</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>4.93</v>
+        <v>0.67</v>
       </c>
       <c r="AE2">
-        <v>26.55</v>
+        <v>26.14</v>
       </c>
       <c r="AF2">
-        <v>-51.91</v>
+        <v>-36.86</v>
       </c>
       <c r="AG2">
-        <v>1405.38</v>
+        <v>1404.57</v>
       </c>
       <c r="AH2">
-        <v>1312.8</v>
+        <v>1307.13</v>
       </c>
       <c r="AI2">
-        <v>1318.07</v>
+        <v>1389.52</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>24.35</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1015,10 +1015,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3035.1</v>
+        <v>3007.3</v>
       </c>
       <c r="D3">
-        <v>2.37</v>
+        <v>-0.92</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1027,46 +1027,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-5.51</v>
+        <v>-6.38</v>
       </c>
       <c r="H3">
-        <v>72.64</v>
+        <v>71.06</v>
       </c>
       <c r="I3">
-        <v>0.5</v>
+        <v>-0.09</v>
       </c>
       <c r="J3">
-        <v>-3.69</v>
+        <v>-4.85</v>
       </c>
       <c r="K3">
-        <v>12.89</v>
+        <v>10.41</v>
       </c>
       <c r="L3">
-        <v>39.41</v>
+        <v>31.76</v>
       </c>
       <c r="M3">
-        <v>16.32</v>
+        <v>15.9</v>
       </c>
       <c r="N3">
         <v>88</v>
       </c>
       <c r="O3">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="P3">
-        <v>2998.24</v>
+        <v>2997.7</v>
       </c>
       <c r="Q3">
-        <v>3043.87</v>
+        <v>3035.07</v>
       </c>
       <c r="R3">
-        <v>3052.25</v>
+        <v>3051.46</v>
       </c>
       <c r="S3">
-        <v>2468.52</v>
+        <v>2471.09</v>
       </c>
       <c r="T3">
-        <v>22.95</v>
+        <v>21.7</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1081,43 +1081,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>49.88</v>
+        <v>46.59</v>
       </c>
       <c r="Z3">
-        <v>-15.71</v>
+        <v>-15.62</v>
       </c>
       <c r="AA3">
-        <v>-7.45</v>
+        <v>-9.08</v>
       </c>
       <c r="AB3">
-        <v>-8.26</v>
+        <v>-6.54</v>
       </c>
       <c r="AC3">
-        <v>30.2</v>
+        <v>50.41</v>
       </c>
       <c r="AD3">
-        <v>11.07</v>
+        <v>26.87</v>
       </c>
       <c r="AE3">
-        <v>71.06</v>
+        <v>69.77</v>
       </c>
       <c r="AF3">
-        <v>56.76</v>
+        <v>-13.43</v>
       </c>
       <c r="AG3">
-        <v>3164.43</v>
+        <v>3137.03</v>
       </c>
       <c r="AH3">
-        <v>2923.3</v>
+        <v>2933.1</v>
       </c>
       <c r="AI3">
         <v>2959.69</v>
       </c>
       <c r="AJ3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AK3">
-        <v>26.71</v>
+        <v>23.96</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1128,10 +1128,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1348</v>
+        <v>1327.6</v>
       </c>
       <c r="D4">
-        <v>2.2</v>
+        <v>-1.51</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1140,46 +1140,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-15.99</v>
+        <v>-17.26</v>
       </c>
       <c r="H4">
-        <v>74.43000000000001</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="I4">
-        <v>-1.78</v>
+        <v>-3.02</v>
       </c>
       <c r="J4">
-        <v>-12.68</v>
+        <v>-12.31</v>
       </c>
       <c r="K4">
-        <v>-1.53</v>
+        <v>-3.64</v>
       </c>
       <c r="L4">
-        <v>47.48</v>
+        <v>42.89</v>
       </c>
       <c r="M4">
-        <v>7.83</v>
+        <v>7.22</v>
       </c>
       <c r="N4">
         <v>77</v>
       </c>
       <c r="O4">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="P4">
-        <v>1346.86</v>
+        <v>1338.58</v>
       </c>
       <c r="Q4">
-        <v>1392.44</v>
+        <v>1382.32</v>
       </c>
       <c r="R4">
-        <v>1467.53</v>
+        <v>1463.57</v>
       </c>
       <c r="S4">
-        <v>1160.18</v>
+        <v>1161.79</v>
       </c>
       <c r="T4">
-        <v>16.19</v>
+        <v>14.27</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1194,43 +1194,43 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>38.31</v>
+        <v>35.42</v>
       </c>
       <c r="Z4">
-        <v>-37</v>
+        <v>-37.47</v>
       </c>
       <c r="AA4">
-        <v>-33.14</v>
+        <v>-34.01</v>
       </c>
       <c r="AB4">
-        <v>-3.86</v>
+        <v>-3.46</v>
       </c>
       <c r="AC4">
-        <v>24.51</v>
+        <v>39.51</v>
       </c>
       <c r="AD4">
-        <v>21.25</v>
+        <v>26.11</v>
       </c>
       <c r="AE4">
-        <v>43.52</v>
+        <v>42.24</v>
       </c>
       <c r="AF4">
-        <v>-55.84</v>
+        <v>-69.22</v>
       </c>
       <c r="AG4">
-        <v>1507.58</v>
+        <v>1480.95</v>
       </c>
       <c r="AH4">
-        <v>1277.29</v>
+        <v>1283.68</v>
       </c>
       <c r="AI4">
-        <v>1462.12</v>
+        <v>1461.41</v>
       </c>
       <c r="AJ4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AK4">
-        <v>24.19</v>
+        <v>23.64</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1244,7 +1244,7 @@
         <v>1700</v>
       </c>
       <c r="D5">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1259,19 +1259,19 @@
         <v>31.29</v>
       </c>
       <c r="I5">
-        <v>0.38</v>
+        <v>1.13</v>
       </c>
       <c r="J5">
-        <v>-6.92</v>
+        <v>-7.48</v>
       </c>
       <c r="K5">
-        <v>-4.51</v>
+        <v>-3.16</v>
       </c>
       <c r="L5">
-        <v>28.84</v>
+        <v>27.46</v>
       </c>
       <c r="M5">
-        <v>19.85</v>
+        <v>20.32</v>
       </c>
       <c r="N5">
         <v>66</v>
@@ -1280,19 +1280,19 @@
         <v>65</v>
       </c>
       <c r="P5">
-        <v>1674.44</v>
+        <v>1678.24</v>
       </c>
       <c r="Q5">
-        <v>1727.52</v>
+        <v>1720.32</v>
       </c>
       <c r="R5">
-        <v>1783.56</v>
+        <v>1781.22</v>
       </c>
       <c r="S5">
-        <v>1585.09</v>
+        <v>1586.53</v>
       </c>
       <c r="T5">
-        <v>7.25</v>
+        <v>7.15</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1310,40 +1310,40 @@
         <v>42.58</v>
       </c>
       <c r="Z5">
-        <v>-33.86</v>
+        <v>-31.1</v>
       </c>
       <c r="AA5">
-        <v>-31.29</v>
+        <v>-31.25</v>
       </c>
       <c r="AB5">
-        <v>-2.56</v>
+        <v>0.16</v>
       </c>
       <c r="AC5">
-        <v>47.37</v>
+        <v>72.5</v>
       </c>
       <c r="AD5">
-        <v>32.29</v>
+        <v>47.71</v>
       </c>
       <c r="AE5">
-        <v>35.74</v>
+        <v>36.24</v>
       </c>
       <c r="AF5">
-        <v>-10.95</v>
+        <v>-28.29</v>
       </c>
       <c r="AG5">
-        <v>1847.9</v>
+        <v>1827.91</v>
       </c>
       <c r="AH5">
-        <v>1607.15</v>
+        <v>1612.74</v>
       </c>
       <c r="AI5">
         <v>1761.08</v>
       </c>
       <c r="AJ5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AK5">
-        <v>49.63</v>
+        <v>44.45</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1354,10 +1354,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>205.25</v>
+        <v>203.56</v>
       </c>
       <c r="D6">
-        <v>-0.41</v>
+        <v>-0.82</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1366,46 +1366,46 @@
         <v>116.81</v>
       </c>
       <c r="G6">
-        <v>-17.54</v>
+        <v>-18.22</v>
       </c>
       <c r="H6">
-        <v>75.70999999999999</v>
+        <v>74.27</v>
       </c>
       <c r="I6">
-        <v>-1.79</v>
+        <v>-3.37</v>
       </c>
       <c r="J6">
-        <v>-5.23</v>
+        <v>-5.08</v>
       </c>
       <c r="K6">
-        <v>-6.41</v>
+        <v>-7.09</v>
       </c>
       <c r="L6">
-        <v>77.89</v>
+        <v>71.38</v>
       </c>
       <c r="M6">
-        <v>65.44</v>
+        <v>66.34</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="P6">
-        <v>207.6</v>
+        <v>206.18</v>
       </c>
       <c r="Q6">
-        <v>211.14</v>
+        <v>210.32</v>
       </c>
       <c r="R6">
-        <v>218.43</v>
+        <v>217.85</v>
       </c>
       <c r="S6">
-        <v>178.97</v>
+        <v>179.18</v>
       </c>
       <c r="T6">
-        <v>14.68</v>
+        <v>13.61</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1420,43 +1420,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>37.17</v>
+        <v>35.06</v>
       </c>
       <c r="Z6">
-        <v>-3.37</v>
+        <v>-3.55</v>
       </c>
       <c r="AA6">
-        <v>-3.22</v>
+        <v>-3.28</v>
       </c>
       <c r="AB6">
-        <v>-0.16</v>
+        <v>-0.27</v>
       </c>
       <c r="AC6">
-        <v>8.98</v>
+        <v>2.23</v>
       </c>
       <c r="AD6">
-        <v>28.3</v>
+        <v>12.43</v>
       </c>
       <c r="AE6">
-        <v>5.16</v>
+        <v>5.07</v>
       </c>
       <c r="AF6">
-        <v>-31.9</v>
+        <v>-10.18</v>
       </c>
       <c r="AG6">
-        <v>219.56</v>
+        <v>218.3</v>
       </c>
       <c r="AH6">
-        <v>202.73</v>
+        <v>202.34</v>
       </c>
       <c r="AI6">
-        <v>222.04</v>
+        <v>218.98</v>
       </c>
       <c r="AJ6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AK6">
-        <v>22.74</v>
+        <v>25.75</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1467,10 +1467,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>417.5</v>
+        <v>415.25</v>
       </c>
       <c r="D7">
-        <v>-0.45</v>
+        <v>-0.54</v>
       </c>
       <c r="E7">
         <v>589.48</v>
@@ -1479,46 +1479,46 @@
         <v>393.4</v>
       </c>
       <c r="G7">
-        <v>-29.17</v>
+        <v>-29.56</v>
       </c>
       <c r="H7">
-        <v>6.13</v>
+        <v>5.55</v>
       </c>
       <c r="I7">
-        <v>-3.8</v>
+        <v>-3.62</v>
       </c>
       <c r="J7">
-        <v>-3.71</v>
+        <v>-5.3</v>
       </c>
       <c r="K7">
-        <v>-2.46</v>
+        <v>-3.33</v>
       </c>
       <c r="L7">
-        <v>-27.66</v>
+        <v>-29.13</v>
       </c>
       <c r="M7">
-        <v>1.83</v>
+        <v>1.45</v>
       </c>
       <c r="N7">
         <v>23</v>
       </c>
       <c r="O7">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P7">
-        <v>422.55</v>
+        <v>419.43</v>
       </c>
       <c r="Q7">
-        <v>431.25</v>
+        <v>430.13</v>
       </c>
       <c r="R7">
         <v>428.02</v>
       </c>
       <c r="S7">
-        <v>479.77</v>
+        <v>479.09</v>
       </c>
       <c r="T7">
-        <v>-12.98</v>
+        <v>-13.32</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1533,43 +1533,43 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>40.59</v>
+        <v>39.25</v>
       </c>
       <c r="Z7">
-        <v>-2.3</v>
+        <v>-3.11</v>
       </c>
       <c r="AA7">
-        <v>-0.09</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AB7">
-        <v>-2.21</v>
+        <v>-2.42</v>
       </c>
       <c r="AC7">
         <v>0</v>
       </c>
       <c r="AD7">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AE7">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="AF7">
-        <v>-39.79</v>
+        <v>50.26</v>
       </c>
       <c r="AG7">
-        <v>447.03</v>
+        <v>447.11</v>
       </c>
       <c r="AH7">
-        <v>415.48</v>
+        <v>413.14</v>
       </c>
       <c r="AI7">
         <v>411.2</v>
       </c>
       <c r="AJ7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AK7">
-        <v>23.56</v>
+        <v>27.59</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1580,10 +1580,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>654.05</v>
+        <v>646.9</v>
       </c>
       <c r="D8">
-        <v>-0.15</v>
+        <v>-1.09</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1592,46 +1592,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-19.08</v>
+        <v>-19.96</v>
       </c>
       <c r="H8">
-        <v>39.83</v>
+        <v>38.3</v>
       </c>
       <c r="I8">
-        <v>-0.53</v>
+        <v>-2</v>
       </c>
       <c r="J8">
-        <v>-7.58</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="K8">
-        <v>7.24</v>
+        <v>3.82</v>
       </c>
       <c r="L8">
-        <v>11.92</v>
+        <v>8.52</v>
       </c>
       <c r="M8">
-        <v>-6.74</v>
+        <v>-7.82</v>
       </c>
       <c r="N8">
         <v>55</v>
       </c>
       <c r="O8">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="P8">
-        <v>659.14</v>
+        <v>656.5</v>
       </c>
       <c r="Q8">
-        <v>664.11</v>
+        <v>660.8099999999999</v>
       </c>
       <c r="R8">
-        <v>699.25</v>
+        <v>696.95</v>
       </c>
       <c r="S8">
-        <v>612.8099999999999</v>
+        <v>612.9400000000001</v>
       </c>
       <c r="T8">
-        <v>6.73</v>
+        <v>5.54</v>
       </c>
       <c r="U8" t="s">
         <v>48</v>
@@ -1646,43 +1646,43 @@
         <v>2</v>
       </c>
       <c r="Y8">
-        <v>39.2</v>
+        <v>36.29</v>
       </c>
       <c r="Z8">
-        <v>-11.28</v>
+        <v>-11.6</v>
       </c>
       <c r="AA8">
-        <v>-12.29</v>
+        <v>-12.15</v>
       </c>
       <c r="AB8">
-        <v>1.01</v>
+        <v>0.55</v>
       </c>
       <c r="AC8">
-        <v>68.56</v>
+        <v>46.88</v>
       </c>
       <c r="AD8">
-        <v>79.40000000000001</v>
+        <v>65.7</v>
       </c>
       <c r="AE8">
-        <v>17.07</v>
+        <v>16.49</v>
       </c>
       <c r="AF8">
-        <v>-47.76</v>
+        <v>-57.86</v>
       </c>
       <c r="AG8">
-        <v>697.27</v>
+        <v>685.61</v>
       </c>
       <c r="AH8">
-        <v>630.96</v>
+        <v>636.02</v>
       </c>
       <c r="AI8">
-        <v>707.83</v>
+        <v>700.01</v>
       </c>
       <c r="AJ8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AK8">
-        <v>25.22</v>
+        <v>26.91</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1696,7 +1696,7 @@
         <v>192.16</v>
       </c>
       <c r="D9">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1711,40 +1711,40 @@
         <v>11.53</v>
       </c>
       <c r="I9">
-        <v>-2.7</v>
+        <v>-2.02</v>
       </c>
       <c r="J9">
-        <v>1.22</v>
+        <v>1.86</v>
       </c>
       <c r="K9">
-        <v>-3.62</v>
+        <v>-4.95</v>
       </c>
       <c r="L9">
-        <v>-24.39</v>
+        <v>-24.72</v>
       </c>
       <c r="M9">
-        <v>-7.13</v>
+        <v>-7.11</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P9">
-        <v>193.5</v>
+        <v>192.71</v>
       </c>
       <c r="Q9">
-        <v>191.32</v>
+        <v>191.46</v>
       </c>
       <c r="R9">
-        <v>189.05</v>
+        <v>189.12</v>
       </c>
       <c r="S9">
-        <v>209.38</v>
+        <v>209</v>
       </c>
       <c r="T9">
-        <v>-8.220000000000001</v>
+        <v>-8.06</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1762,40 +1762,40 @@
         <v>51.85</v>
       </c>
       <c r="Z9">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AA9">
         <v>1.25</v>
       </c>
       <c r="AB9">
-        <v>0.11</v>
+        <v>-0.03</v>
       </c>
       <c r="AC9">
-        <v>41.37</v>
+        <v>29.93</v>
       </c>
       <c r="AD9">
-        <v>49.11</v>
+        <v>38.7</v>
       </c>
       <c r="AE9">
-        <v>4.67</v>
+        <v>4.53</v>
       </c>
       <c r="AF9">
-        <v>13.44</v>
+        <v>-64.31</v>
       </c>
       <c r="AG9">
-        <v>198.03</v>
+        <v>198.12</v>
       </c>
       <c r="AH9">
-        <v>184.6</v>
+        <v>184.8</v>
       </c>
       <c r="AI9">
         <v>197.85</v>
       </c>
       <c r="AJ9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AK9">
-        <v>41.98</v>
+        <v>39.43</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1809,7 +1809,7 @@
         <v>76.53</v>
       </c>
       <c r="D10">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>150.86</v>
@@ -1824,40 +1824,40 @@
         <v>29.1</v>
       </c>
       <c r="I10">
-        <v>-0.44</v>
+        <v>0.51</v>
       </c>
       <c r="J10">
-        <v>-5.01</v>
+        <v>-4.61</v>
       </c>
       <c r="K10">
-        <v>2.77</v>
+        <v>-2.05</v>
       </c>
       <c r="L10">
-        <v>-40.96</v>
+        <v>-40.61</v>
       </c>
       <c r="M10">
-        <v>-0.47</v>
+        <v>0.26</v>
       </c>
       <c r="N10">
         <v>12</v>
       </c>
       <c r="O10">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="P10">
-        <v>76.42</v>
+        <v>76.5</v>
       </c>
       <c r="Q10">
-        <v>76.95999999999999</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="R10">
-        <v>79.54000000000001</v>
+        <v>79.37</v>
       </c>
       <c r="S10">
-        <v>82.11</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="T10">
-        <v>-6.8</v>
+        <v>-6.71</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1875,40 +1875,40 @@
         <v>43.2</v>
       </c>
       <c r="Z10">
-        <v>-0.89</v>
+        <v>-0.84</v>
       </c>
       <c r="AA10">
-        <v>-0.95</v>
+        <v>-0.93</v>
       </c>
       <c r="AB10">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="AC10">
-        <v>61.58</v>
+        <v>73.66</v>
       </c>
       <c r="AD10">
-        <v>64.23999999999999</v>
+        <v>67.53</v>
       </c>
       <c r="AE10">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AF10">
-        <v>-2.39</v>
+        <v>-35.87</v>
       </c>
       <c r="AG10">
-        <v>79.22</v>
+        <v>78.52</v>
       </c>
       <c r="AH10">
-        <v>74.7</v>
+        <v>75.05</v>
       </c>
       <c r="AI10">
         <v>74.97</v>
       </c>
       <c r="AJ10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AK10">
-        <v>14.15</v>
+        <v>14.13</v>
       </c>
     </row>
   </sheetData>
@@ -2049,7 +2049,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2106,13 +2106,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-4.23</v>
+        <v>-3.78</v>
       </c>
       <c r="D7" s="5">
-        <v>-3.78</v>
+        <v>-4.43</v>
       </c>
       <c r="E7" s="6">
-        <v>0.45</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2123,13 +2123,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-5.89</v>
+        <v>-3.69</v>
       </c>
       <c r="D8" s="5">
-        <v>-3.69</v>
+        <v>-4.85</v>
       </c>
       <c r="E8" s="6">
-        <v>2.2</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2140,13 +2140,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-15.2</v>
+        <v>-12.68</v>
       </c>
       <c r="D9" s="5">
-        <v>-12.68</v>
-      </c>
-      <c r="E9" s="6">
-        <v>2.52</v>
+        <v>-12.31</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.37</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2157,13 +2157,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-9.35</v>
+        <v>-6.92</v>
       </c>
       <c r="D10" s="5">
-        <v>-6.92</v>
+        <v>-7.48</v>
       </c>
       <c r="E10" s="6">
-        <v>2.43</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2174,13 +2174,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-5.88</v>
+        <v>-5.23</v>
       </c>
       <c r="D11" s="5">
-        <v>-5.23</v>
-      </c>
-      <c r="E11" s="6">
-        <v>0.65</v>
+        <v>-5.08</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.15</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2191,13 +2191,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="5">
-        <v>-3.64</v>
+        <v>-3.71</v>
       </c>
       <c r="D12" s="5">
-        <v>-3.71</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.07000000000000001</v>
+        <v>-5.3</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-1.59</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2208,13 +2208,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="5">
-        <v>-8.44</v>
+        <v>-7.58</v>
       </c>
       <c r="D13" s="5">
-        <v>-7.58</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="E13" s="6">
-        <v>0.86</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2225,13 +2225,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="5">
-        <v>1.68</v>
+        <v>1.22</v>
       </c>
       <c r="D14" s="5">
-        <v>1.22</v>
+        <v>1.86</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.46</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2242,13 +2242,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="5">
-        <v>-6.18</v>
+        <v>-5.01</v>
       </c>
       <c r="D15" s="5">
-        <v>-5.01</v>
-      </c>
-      <c r="E15" s="6">
-        <v>1.17</v>
+        <v>-4.61</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.4</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2259,13 +2259,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>-3.9</v>
+        <v>-3.04</v>
       </c>
       <c r="D16" s="5">
-        <v>-3.04</v>
-      </c>
-      <c r="E16" s="6">
-        <v>0.86</v>
+        <v>-3.02</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2276,13 +2276,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="5">
-        <v>-2.02</v>
+        <v>0.5</v>
       </c>
       <c r="D17" s="5">
-        <v>0.5</v>
+        <v>-0.09</v>
       </c>
       <c r="E17" s="6">
-        <v>2.52</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2293,13 +2293,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="5">
-        <v>-3.83</v>
+        <v>-1.78</v>
       </c>
       <c r="D18" s="5">
-        <v>-1.78</v>
+        <v>-3.02</v>
       </c>
       <c r="E18" s="6">
-        <v>2.05</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2310,13 +2310,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="5">
-        <v>-2.18</v>
+        <v>0.38</v>
       </c>
       <c r="D19" s="5">
-        <v>0.38</v>
-      </c>
-      <c r="E19" s="6">
-        <v>2.56</v>
+        <v>1.13</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.75</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2327,13 +2327,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="5">
-        <v>-0.97</v>
+        <v>-1.79</v>
       </c>
       <c r="D20" s="5">
-        <v>-1.79</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.82</v>
+        <v>-3.37</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-1.58</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2344,13 +2344,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="5">
-        <v>-3.92</v>
+        <v>-3.8</v>
       </c>
       <c r="D21" s="5">
-        <v>-3.8</v>
-      </c>
-      <c r="E21" s="6">
-        <v>0.12</v>
+        <v>-3.62</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.18</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2361,13 +2361,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="5">
-        <v>-0.79</v>
+        <v>-0.53</v>
       </c>
       <c r="D22" s="5">
-        <v>-0.53</v>
+        <v>-2</v>
       </c>
       <c r="E22" s="6">
-        <v>0.26</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2378,13 +2378,13 @@
         <v>8</v>
       </c>
       <c r="C23" s="5">
-        <v>-2.67</v>
+        <v>-2.7</v>
       </c>
       <c r="D23" s="5">
-        <v>-2.7</v>
+        <v>-2.02</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.03</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2395,13 +2395,13 @@
         <v>8</v>
       </c>
       <c r="C24" s="5">
-        <v>-1.31</v>
+        <v>-0.44</v>
       </c>
       <c r="D24" s="5">
-        <v>-0.44</v>
-      </c>
-      <c r="E24" s="6">
-        <v>0.87</v>
+        <v>0.51</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.95</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2412,13 +2412,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="5">
-        <v>-26.7</v>
+        <v>-25.68</v>
       </c>
       <c r="D25" s="5">
-        <v>-25.68</v>
+        <v>-25.86</v>
       </c>
       <c r="E25" s="6">
-        <v>1.02</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2429,13 +2429,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="5">
-        <v>31.84</v>
+        <v>39.41</v>
       </c>
       <c r="D26" s="5">
-        <v>39.41</v>
+        <v>31.76</v>
       </c>
       <c r="E26" s="6">
-        <v>7.57</v>
+        <v>-7.65</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2446,13 +2446,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="5">
-        <v>40.81</v>
+        <v>47.48</v>
       </c>
       <c r="D27" s="5">
-        <v>47.48</v>
+        <v>42.89</v>
       </c>
       <c r="E27" s="6">
-        <v>6.67</v>
+        <v>-4.59</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2463,13 +2463,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="5">
-        <v>23.75</v>
+        <v>28.84</v>
       </c>
       <c r="D28" s="5">
-        <v>28.84</v>
+        <v>27.46</v>
       </c>
       <c r="E28" s="6">
-        <v>5.09</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2480,13 +2480,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="5">
-        <v>77.98999999999999</v>
+        <v>77.89</v>
       </c>
       <c r="D29" s="5">
-        <v>77.89</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-0.1</v>
+        <v>71.38</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-6.51</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2497,13 +2497,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="5">
-        <v>-28.85</v>
+        <v>-27.66</v>
       </c>
       <c r="D30" s="5">
-        <v>-27.66</v>
+        <v>-29.13</v>
       </c>
       <c r="E30" s="6">
-        <v>1.19</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2514,13 +2514,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="5">
-        <v>10.72</v>
+        <v>11.92</v>
       </c>
       <c r="D31" s="5">
-        <v>11.92</v>
+        <v>8.52</v>
       </c>
       <c r="E31" s="6">
-        <v>1.2</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2531,13 +2531,13 @@
         <v>11</v>
       </c>
       <c r="C32" s="5">
-        <v>-23.37</v>
+        <v>-24.39</v>
       </c>
       <c r="D32" s="5">
-        <v>-24.39</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-1.02</v>
+        <v>-24.72</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-0.33</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2548,13 +2548,13 @@
         <v>11</v>
       </c>
       <c r="C33" s="5">
-        <v>-41.96</v>
+        <v>-40.96</v>
       </c>
       <c r="D33" s="5">
-        <v>-40.96</v>
-      </c>
-      <c r="E33" s="6">
-        <v>1</v>
+        <v>-40.61</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0.35</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2565,13 +2565,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="5">
-        <v>-2.23</v>
+        <v>-2.25</v>
       </c>
       <c r="D34" s="5">
-        <v>-2.25</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-0.02</v>
+        <v>-2.58</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-0.33</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2582,13 +2582,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="5">
-        <v>9.210000000000001</v>
+        <v>12.89</v>
       </c>
       <c r="D35" s="5">
-        <v>12.89</v>
+        <v>10.41</v>
       </c>
       <c r="E35" s="6">
-        <v>3.68</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2599,13 +2599,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="5">
-        <v>-4.35</v>
+        <v>-1.53</v>
       </c>
       <c r="D36" s="5">
-        <v>-1.53</v>
+        <v>-3.64</v>
       </c>
       <c r="E36" s="6">
-        <v>2.82</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2616,13 +2616,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="5">
-        <v>-7.25</v>
+        <v>-4.51</v>
       </c>
       <c r="D37" s="5">
-        <v>-4.51</v>
-      </c>
-      <c r="E37" s="6">
-        <v>2.74</v>
+        <v>-3.16</v>
+      </c>
+      <c r="E37" s="7">
+        <v>1.35</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2633,13 +2633,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="5">
-        <v>-6.88</v>
+        <v>-6.41</v>
       </c>
       <c r="D38" s="5">
-        <v>-6.41</v>
+        <v>-7.09</v>
       </c>
       <c r="E38" s="6">
-        <v>0.47</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2650,13 +2650,13 @@
         <v>10</v>
       </c>
       <c r="C39" s="5">
-        <v>-2.83</v>
+        <v>-2.46</v>
       </c>
       <c r="D39" s="5">
-        <v>-2.46</v>
+        <v>-3.33</v>
       </c>
       <c r="E39" s="6">
-        <v>0.37</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2667,13 +2667,13 @@
         <v>10</v>
       </c>
       <c r="C40" s="5">
-        <v>6.33</v>
+        <v>7.24</v>
       </c>
       <c r="D40" s="5">
-        <v>7.24</v>
+        <v>3.82</v>
       </c>
       <c r="E40" s="6">
-        <v>0.91</v>
+        <v>-3.42</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2684,13 +2684,13 @@
         <v>10</v>
       </c>
       <c r="C41" s="5">
-        <v>-3.82</v>
+        <v>-3.62</v>
       </c>
       <c r="D41" s="5">
-        <v>-3.62</v>
+        <v>-4.95</v>
       </c>
       <c r="E41" s="6">
-        <v>0.2</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2701,13 +2701,13 @@
         <v>10</v>
       </c>
       <c r="C42" s="5">
-        <v>-1.02</v>
+        <v>2.77</v>
       </c>
       <c r="D42" s="5">
-        <v>2.77</v>
+        <v>-2.05</v>
       </c>
       <c r="E42" s="6">
-        <v>3.79</v>
+        <v>-4.82</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2718,13 +2718,13 @@
         <v>6</v>
       </c>
       <c r="C43" s="5">
-        <v>-30.38</v>
+        <v>-30.55</v>
       </c>
       <c r="D43" s="5">
-        <v>-30.55</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-0.17</v>
+        <v>-30.8</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2735,13 +2735,13 @@
         <v>6</v>
       </c>
       <c r="C44" s="5">
-        <v>-7.7</v>
+        <v>-5.51</v>
       </c>
       <c r="D44" s="5">
-        <v>-5.51</v>
+        <v>-6.38</v>
       </c>
       <c r="E44" s="6">
-        <v>2.19</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2752,608 +2752,421 @@
         <v>6</v>
       </c>
       <c r="C45" s="5">
-        <v>-17.79</v>
+        <v>-15.99</v>
       </c>
       <c r="D45" s="5">
-        <v>-15.99</v>
+        <v>-17.26</v>
       </c>
       <c r="E45" s="6">
-        <v>1.8</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="5">
-        <v>-11.96</v>
+        <v>-17.54</v>
       </c>
       <c r="D46" s="5">
-        <v>-9.73</v>
+        <v>-18.22</v>
       </c>
       <c r="E46" s="6">
-        <v>2.23</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="5">
-        <v>-17.2</v>
+        <v>-29.17</v>
       </c>
       <c r="D47" s="5">
-        <v>-17.54</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-0.34</v>
+        <v>-29.56</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="5">
-        <v>-28.85</v>
+        <v>-19.08</v>
       </c>
       <c r="D48" s="5">
-        <v>-29.17</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-0.32</v>
+        <v>-19.96</v>
+      </c>
+      <c r="E48" s="6">
+        <v>-0.88</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C49" s="5">
-        <v>-18.96</v>
+        <v>1321.4</v>
       </c>
       <c r="D49" s="5">
-        <v>-19.08</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-0.12</v>
+        <v>1316.6</v>
+      </c>
+      <c r="E49" s="6">
+        <v>-4.8</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C50" s="5">
-        <v>-30.8</v>
+        <v>3035.1</v>
       </c>
       <c r="D50" s="5">
-        <v>-30.78</v>
+        <v>3007.3</v>
       </c>
       <c r="E50" s="6">
-        <v>0.02</v>
+        <v>-27.8</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C51" s="5">
-        <v>-49.38</v>
+        <v>1348</v>
       </c>
       <c r="D51" s="5">
-        <v>-49.27</v>
+        <v>1327.6</v>
       </c>
       <c r="E51" s="6">
-        <v>0.11</v>
+        <v>-20.4</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C52" s="5">
-        <v>1324.7</v>
+        <v>205.25</v>
       </c>
       <c r="D52" s="5">
-        <v>1321.4</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-3.3</v>
+        <v>203.56</v>
+      </c>
+      <c r="E52" s="6">
+        <v>-1.69</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C53" s="5">
-        <v>2964.9</v>
+        <v>417.5</v>
       </c>
       <c r="D53" s="5">
-        <v>3035.1</v>
+        <v>415.25</v>
       </c>
       <c r="E53" s="6">
-        <v>70.2</v>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="5">
-        <v>1319</v>
+        <v>654.05</v>
       </c>
       <c r="D54" s="5">
-        <v>1348</v>
+        <v>646.9</v>
       </c>
       <c r="E54" s="6">
-        <v>29</v>
+        <v>-7.15</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C55" s="5">
-        <v>1658</v>
+        <v>40.03</v>
       </c>
       <c r="D55" s="5">
-        <v>1700</v>
+        <v>38.98</v>
       </c>
       <c r="E55" s="6">
-        <v>42</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C56" s="5">
-        <v>206.1</v>
+        <v>49.88</v>
       </c>
       <c r="D56" s="5">
-        <v>205.25</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-0.85</v>
+        <v>46.59</v>
+      </c>
+      <c r="E56" s="6">
+        <v>-3.29</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C57" s="5">
-        <v>419.4</v>
+        <v>38.31</v>
       </c>
       <c r="D57" s="5">
-        <v>417.5</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-1.9</v>
+        <v>35.42</v>
+      </c>
+      <c r="E57" s="6">
+        <v>-2.89</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C58" s="5">
-        <v>655.05</v>
+        <v>37.17</v>
       </c>
       <c r="D58" s="5">
-        <v>654.05</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-1</v>
+        <v>35.06</v>
+      </c>
+      <c r="E58" s="6">
+        <v>-2.11</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C59" s="5">
-        <v>192.11</v>
+        <v>40.59</v>
       </c>
       <c r="D59" s="5">
-        <v>192.16</v>
+        <v>39.25</v>
       </c>
       <c r="E59" s="6">
-        <v>0.05</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C60" s="5">
-        <v>76.37</v>
+        <v>39.2</v>
       </c>
       <c r="D60" s="5">
-        <v>76.53</v>
+        <v>36.29</v>
       </c>
       <c r="E60" s="6">
-        <v>0.16</v>
+        <v>-2.91</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C61" s="5">
-        <v>55</v>
+        <v>-51.91</v>
       </c>
       <c r="D61" s="5">
-        <v>66</v>
-      </c>
-      <c r="E61" s="6">
-        <v>11</v>
+        <v>-36.86</v>
+      </c>
+      <c r="E61" s="7">
+        <v>15.05</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C62" s="5">
-        <v>66</v>
+        <v>56.76</v>
       </c>
       <c r="D62" s="5">
-        <v>55</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-11</v>
+        <v>-13.43</v>
+      </c>
+      <c r="E62" s="6">
+        <v>-70.19</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C63" s="5">
-        <v>40.73</v>
+        <v>-55.84</v>
       </c>
       <c r="D63" s="5">
-        <v>40.03</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-0.7</v>
+        <v>-69.22</v>
+      </c>
+      <c r="E63" s="6">
+        <v>-13.38</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C64" s="5">
-        <v>39.95</v>
+        <v>-10.95</v>
       </c>
       <c r="D64" s="5">
-        <v>49.88</v>
+        <v>-28.29</v>
       </c>
       <c r="E64" s="6">
-        <v>9.93</v>
+        <v>-17.34</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C65" s="5">
-        <v>30.86</v>
+        <v>-31.9</v>
       </c>
       <c r="D65" s="5">
-        <v>38.31</v>
-      </c>
-      <c r="E65" s="6">
-        <v>7.45</v>
+        <v>-10.18</v>
+      </c>
+      <c r="E65" s="7">
+        <v>21.72</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C66" s="5">
-        <v>30.05</v>
+        <v>-39.79</v>
       </c>
       <c r="D66" s="5">
-        <v>42.58</v>
-      </c>
-      <c r="E66" s="6">
-        <v>12.53</v>
+        <v>50.26</v>
+      </c>
+      <c r="E66" s="7">
+        <v>90.05</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C67" s="5">
-        <v>38.23</v>
+        <v>-47.76</v>
       </c>
       <c r="D67" s="5">
-        <v>37.17</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-1.06</v>
+        <v>-57.86</v>
+      </c>
+      <c r="E67" s="6">
+        <v>-10.1</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C68" s="5">
-        <v>41.7</v>
+        <v>13.44</v>
       </c>
       <c r="D68" s="5">
-        <v>40.59</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-1.11</v>
+        <v>-64.31</v>
+      </c>
+      <c r="E68" s="6">
+        <v>-77.75</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C69" s="5">
-        <v>39.61</v>
+        <v>-2.39</v>
       </c>
       <c r="D69" s="5">
-        <v>39.2</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-0.41</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="5">
-        <v>51.76</v>
-      </c>
-      <c r="D70" s="5">
-        <v>51.85</v>
-      </c>
-      <c r="E70" s="6">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="5">
-        <v>42.26</v>
-      </c>
-      <c r="D71" s="5">
-        <v>43.2</v>
-      </c>
-      <c r="E71" s="6">
-        <v>0.9399999999999999</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="5">
-        <v>-52.15</v>
-      </c>
-      <c r="D72" s="5">
-        <v>-51.91</v>
-      </c>
-      <c r="E72" s="6">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="5">
-        <v>24.05</v>
-      </c>
-      <c r="D73" s="5">
-        <v>56.76</v>
-      </c>
-      <c r="E73" s="6">
-        <v>32.71</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="5">
-        <v>-33.62</v>
-      </c>
-      <c r="D74" s="5">
-        <v>-55.84</v>
-      </c>
-      <c r="E74" s="7">
-        <v>-22.22</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="5">
-        <v>-8.210000000000001</v>
-      </c>
-      <c r="D75" s="5">
-        <v>-10.95</v>
-      </c>
-      <c r="E75" s="7">
-        <v>-2.74</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="5">
-        <v>-36.78</v>
-      </c>
-      <c r="D76" s="5">
-        <v>-31.9</v>
-      </c>
-      <c r="E76" s="6">
-        <v>4.88</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="5">
-        <v>-20.35</v>
-      </c>
-      <c r="D77" s="5">
-        <v>-39.79</v>
-      </c>
-      <c r="E77" s="7">
-        <v>-19.44</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="5">
-        <v>-44.5</v>
-      </c>
-      <c r="D78" s="5">
-        <v>-47.76</v>
-      </c>
-      <c r="E78" s="7">
-        <v>-3.26</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="5">
-        <v>-56.02</v>
-      </c>
-      <c r="D79" s="5">
-        <v>13.44</v>
-      </c>
-      <c r="E79" s="6">
-        <v>69.45999999999999</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="5">
-        <v>-66.44</v>
-      </c>
-      <c r="D80" s="5">
-        <v>-2.39</v>
-      </c>
-      <c r="E80" s="6">
-        <v>64.05</v>
+        <v>-35.87</v>
+      </c>
+      <c r="E69" s="6">
+        <v>-33.48</v>
       </c>
     </row>
   </sheetData>
@@ -3418,16 +3231,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="10">
-        <v>42.5</v>
+        <v>41</v>
       </c>
       <c r="E2" s="10">
         <v>60</v>
       </c>
       <c r="F2" s="10">
-        <v>-5.3</v>
+        <v>-5.6</v>
       </c>
       <c r="G2" s="10">
-        <v>0.2</v>
+        <v>-1.4</v>
       </c>
       <c r="H2" s="10">
         <v>55.4</v>
@@ -3553,10 +3366,10 @@
         <v>45</v>
       </c>
       <c r="G1" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1" s="12" t="s">
         <v>43</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>44</v>
       </c>
       <c r="I1" s="12" t="s">
         <v>37</v>
@@ -3564,31 +3377,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="13">
-        <v>0.6544</v>
+        <v>0.6634</v>
       </c>
       <c r="B2" s="13">
-        <v>0.1985</v>
+        <v>0.2032</v>
       </c>
       <c r="C2" s="13">
-        <v>0.1632</v>
+        <v>0.159</v>
       </c>
       <c r="D2" s="13">
-        <v>0.07829999999999999</v>
+        <v>0.0722</v>
       </c>
       <c r="E2" s="13">
-        <v>0.0183</v>
+        <v>0.0145</v>
       </c>
       <c r="F2" s="13">
-        <v>-0.004699999999999999</v>
+        <v>0.0026</v>
       </c>
       <c r="G2" s="13">
-        <v>-0.0674</v>
+        <v>-0.0711</v>
       </c>
       <c r="H2" s="13">
-        <v>-0.0713</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="I2" s="13">
-        <v>-0.09660000000000001</v>
+        <v>-0.09820000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="77">
   <si>
     <t>Symbol</t>
   </si>
@@ -163,12 +163,12 @@
     <t>Unknown</t>
   </si>
   <si>
+    <t>No</t>
+  </si>
+  <si>
     <t>Yes</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>DOWN</t>
   </si>
   <si>
@@ -178,7 +178,40 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>51.9 → 47.4</t>
+  </si>
+  <si>
+    <t>51.9</t>
+  </si>
+  <si>
+    <t>47.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -380,14 +413,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -902,10 +936,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1316.6</v>
+        <v>1303.8</v>
       </c>
       <c r="D2">
-        <v>-0.36</v>
+        <v>-0.97</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -914,97 +948,97 @@
         <v>1247.38</v>
       </c>
       <c r="G2">
-        <v>-30.8</v>
+        <v>-31.48</v>
       </c>
       <c r="H2">
-        <v>5.55</v>
+        <v>4.52</v>
       </c>
       <c r="I2">
-        <v>-3.02</v>
+        <v>-2.69</v>
       </c>
       <c r="J2">
-        <v>-4.43</v>
+        <v>-5.62</v>
       </c>
       <c r="K2">
-        <v>-2.58</v>
+        <v>-2.98</v>
       </c>
       <c r="L2">
-        <v>-25.86</v>
+        <v>-26.65</v>
       </c>
       <c r="M2">
-        <v>-9.82</v>
+        <v>-10.36</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P2">
-        <v>1327.06</v>
+        <v>1319.86</v>
       </c>
       <c r="Q2">
-        <v>1355.85</v>
+        <v>1351.65</v>
       </c>
       <c r="R2">
-        <v>1353.32</v>
+        <v>1353.16</v>
       </c>
       <c r="S2">
-        <v>1530.17</v>
+        <v>1527.35</v>
       </c>
       <c r="T2">
-        <v>-13.96</v>
+        <v>-14.64</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
       </c>
       <c r="V2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="W2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2">
-        <v>38.98</v>
+        <v>36.24</v>
       </c>
       <c r="Z2">
-        <v>-9.23</v>
+        <v>-11.78</v>
       </c>
       <c r="AA2">
-        <v>-2.73</v>
+        <v>-4.54</v>
       </c>
       <c r="AB2">
-        <v>-6.5</v>
+        <v>-7.24</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AE2">
-        <v>26.14</v>
+        <v>25.57</v>
       </c>
       <c r="AF2">
-        <v>-36.86</v>
+        <v>-43.12</v>
       </c>
       <c r="AG2">
-        <v>1404.57</v>
+        <v>1403.18</v>
       </c>
       <c r="AH2">
-        <v>1307.13</v>
+        <v>1300.12</v>
       </c>
       <c r="AI2">
-        <v>1389.52</v>
+        <v>1386.85</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>28.2</v>
+        <v>31.53</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1015,10 +1049,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3007.3</v>
+        <v>3002.5</v>
       </c>
       <c r="D3">
-        <v>-0.92</v>
+        <v>-0.16</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1027,25 +1061,25 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-6.38</v>
+        <v>-6.53</v>
       </c>
       <c r="H3">
-        <v>71.06</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="I3">
-        <v>-0.09</v>
+        <v>0.23</v>
       </c>
       <c r="J3">
-        <v>-4.85</v>
+        <v>-5.68</v>
       </c>
       <c r="K3">
-        <v>10.41</v>
+        <v>11.06</v>
       </c>
       <c r="L3">
-        <v>31.76</v>
+        <v>31.28</v>
       </c>
       <c r="M3">
-        <v>15.9</v>
+        <v>15.57</v>
       </c>
       <c r="N3">
         <v>88</v>
@@ -1054,61 +1088,61 @@
         <v>75</v>
       </c>
       <c r="P3">
-        <v>2997.7</v>
+        <v>2999.1</v>
       </c>
       <c r="Q3">
-        <v>3035.07</v>
+        <v>3026.06</v>
       </c>
       <c r="R3">
-        <v>3051.46</v>
+        <v>3052.14</v>
       </c>
       <c r="S3">
-        <v>2471.09</v>
+        <v>2473.42</v>
       </c>
       <c r="T3">
-        <v>21.7</v>
+        <v>21.39</v>
       </c>
       <c r="U3" t="s">
+        <v>47</v>
+      </c>
+      <c r="V3" t="s">
         <v>48</v>
       </c>
-      <c r="V3" t="s">
+      <c r="W3" t="s">
         <v>47</v>
-      </c>
-      <c r="W3" t="s">
-        <v>48</v>
       </c>
       <c r="X3">
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>46.59</v>
+        <v>46.03</v>
       </c>
       <c r="Z3">
-        <v>-15.62</v>
+        <v>-15.76</v>
       </c>
       <c r="AA3">
-        <v>-9.08</v>
+        <v>-10.42</v>
       </c>
       <c r="AB3">
-        <v>-6.54</v>
+        <v>-5.34</v>
       </c>
       <c r="AC3">
-        <v>50.41</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="AD3">
-        <v>26.87</v>
+        <v>49.84</v>
       </c>
       <c r="AE3">
-        <v>69.77</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="AF3">
-        <v>-13.43</v>
+        <v>-33.44</v>
       </c>
       <c r="AG3">
-        <v>3137.03</v>
+        <v>3101.49</v>
       </c>
       <c r="AH3">
-        <v>2933.1</v>
+        <v>2950.62</v>
       </c>
       <c r="AI3">
         <v>2959.69</v>
@@ -1117,7 +1151,7 @@
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>23.96</v>
+        <v>21.83</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1128,10 +1162,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1327.6</v>
+        <v>1308</v>
       </c>
       <c r="D4">
-        <v>-1.51</v>
+        <v>-1.48</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1140,97 +1174,97 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-17.26</v>
+        <v>-18.48</v>
       </c>
       <c r="H4">
-        <v>71.79000000000001</v>
+        <v>69.25</v>
       </c>
       <c r="I4">
-        <v>-3.02</v>
+        <v>-4.25</v>
       </c>
       <c r="J4">
-        <v>-12.31</v>
+        <v>-14.51</v>
       </c>
       <c r="K4">
-        <v>-3.64</v>
+        <v>-4.05</v>
       </c>
       <c r="L4">
-        <v>42.89</v>
+        <v>40.51</v>
       </c>
       <c r="M4">
-        <v>7.22</v>
+        <v>6.77</v>
       </c>
       <c r="N4">
         <v>77</v>
       </c>
       <c r="O4">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="P4">
-        <v>1338.58</v>
+        <v>1326.98</v>
       </c>
       <c r="Q4">
-        <v>1382.32</v>
+        <v>1370.62</v>
       </c>
       <c r="R4">
-        <v>1463.57</v>
+        <v>1459.92</v>
       </c>
       <c r="S4">
-        <v>1161.79</v>
+        <v>1162.77</v>
       </c>
       <c r="T4">
-        <v>14.27</v>
+        <v>12.49</v>
       </c>
       <c r="U4" t="s">
+        <v>47</v>
+      </c>
+      <c r="V4" t="s">
         <v>48</v>
       </c>
-      <c r="V4" t="s">
+      <c r="W4" t="s">
         <v>47</v>
-      </c>
-      <c r="W4" t="s">
-        <v>48</v>
       </c>
       <c r="X4">
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>35.42</v>
+        <v>32.85</v>
       </c>
       <c r="Z4">
-        <v>-37.47</v>
+        <v>-38.97</v>
       </c>
       <c r="AA4">
-        <v>-34.01</v>
+        <v>-35</v>
       </c>
       <c r="AB4">
-        <v>-3.46</v>
+        <v>-3.97</v>
       </c>
       <c r="AC4">
-        <v>39.51</v>
+        <v>46.07</v>
       </c>
       <c r="AD4">
-        <v>26.11</v>
+        <v>36.7</v>
       </c>
       <c r="AE4">
-        <v>42.24</v>
+        <v>41.25</v>
       </c>
       <c r="AF4">
-        <v>-69.22</v>
+        <v>-58.39</v>
       </c>
       <c r="AG4">
-        <v>1480.95</v>
+        <v>1441</v>
       </c>
       <c r="AH4">
-        <v>1283.68</v>
+        <v>1300.24</v>
       </c>
       <c r="AI4">
-        <v>1461.41</v>
+        <v>1445.94</v>
       </c>
       <c r="AJ4" t="s">
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>23.64</v>
+        <v>24.65</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1241,10 +1275,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1700</v>
+        <v>1682.4</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>-1.04</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1253,88 +1287,88 @@
         <v>1294.84</v>
       </c>
       <c r="G5">
-        <v>-9.73</v>
+        <v>-10.66</v>
       </c>
       <c r="H5">
-        <v>31.29</v>
+        <v>29.93</v>
       </c>
       <c r="I5">
-        <v>1.13</v>
+        <v>0.85</v>
       </c>
       <c r="J5">
-        <v>-7.48</v>
+        <v>-8.76</v>
       </c>
       <c r="K5">
-        <v>-3.16</v>
+        <v>-4.69</v>
       </c>
       <c r="L5">
-        <v>27.46</v>
+        <v>26.98</v>
       </c>
       <c r="M5">
-        <v>20.32</v>
+        <v>19.63</v>
       </c>
       <c r="N5">
         <v>66</v>
       </c>
       <c r="O5">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P5">
-        <v>1678.24</v>
+        <v>1681.08</v>
       </c>
       <c r="Q5">
-        <v>1720.32</v>
+        <v>1712.12</v>
       </c>
       <c r="R5">
-        <v>1781.22</v>
+        <v>1778.92</v>
       </c>
       <c r="S5">
-        <v>1586.53</v>
+        <v>1587.7</v>
       </c>
       <c r="T5">
-        <v>7.15</v>
+        <v>5.96</v>
       </c>
       <c r="U5" t="s">
+        <v>47</v>
+      </c>
+      <c r="V5" t="s">
         <v>48</v>
       </c>
-      <c r="V5" t="s">
+      <c r="W5" t="s">
         <v>47</v>
-      </c>
-      <c r="W5" t="s">
-        <v>48</v>
       </c>
       <c r="X5">
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>42.58</v>
+        <v>39.17</v>
       </c>
       <c r="Z5">
-        <v>-31.1</v>
+        <v>-29.99</v>
       </c>
       <c r="AA5">
-        <v>-31.25</v>
+        <v>-31</v>
       </c>
       <c r="AB5">
-        <v>0.16</v>
+        <v>1.02</v>
       </c>
       <c r="AC5">
-        <v>72.5</v>
+        <v>92.48999999999999</v>
       </c>
       <c r="AD5">
-        <v>47.71</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="AE5">
-        <v>36.24</v>
+        <v>36.01</v>
       </c>
       <c r="AF5">
-        <v>-28.29</v>
+        <v>-42.38</v>
       </c>
       <c r="AG5">
-        <v>1827.91</v>
+        <v>1802.91</v>
       </c>
       <c r="AH5">
-        <v>1612.74</v>
+        <v>1621.33</v>
       </c>
       <c r="AI5">
         <v>1761.08</v>
@@ -1343,7 +1377,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>44.45</v>
+        <v>39.97</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1354,10 +1388,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>203.56</v>
+        <v>205.58</v>
       </c>
       <c r="D6">
-        <v>-0.82</v>
+        <v>0.99</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1366,88 +1400,88 @@
         <v>116.81</v>
       </c>
       <c r="G6">
-        <v>-18.22</v>
+        <v>-17.41</v>
       </c>
       <c r="H6">
-        <v>74.27</v>
+        <v>76</v>
       </c>
       <c r="I6">
-        <v>-3.37</v>
+        <v>-1.64</v>
       </c>
       <c r="J6">
-        <v>-5.08</v>
+        <v>-6.54</v>
       </c>
       <c r="K6">
-        <v>-7.09</v>
+        <v>-6.66</v>
       </c>
       <c r="L6">
-        <v>71.38</v>
+        <v>73.78</v>
       </c>
       <c r="M6">
-        <v>66.34</v>
+        <v>67.8</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P6">
-        <v>206.18</v>
+        <v>205.5</v>
       </c>
       <c r="Q6">
-        <v>210.32</v>
+        <v>209.58</v>
       </c>
       <c r="R6">
-        <v>217.85</v>
+        <v>217.44</v>
       </c>
       <c r="S6">
-        <v>179.18</v>
+        <v>179.39</v>
       </c>
       <c r="T6">
-        <v>13.61</v>
+        <v>14.6</v>
       </c>
       <c r="U6" t="s">
+        <v>47</v>
+      </c>
+      <c r="V6" t="s">
         <v>48</v>
       </c>
-      <c r="V6" t="s">
+      <c r="W6" t="s">
         <v>47</v>
-      </c>
-      <c r="W6" t="s">
-        <v>48</v>
       </c>
       <c r="X6">
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>35.06</v>
+        <v>39.47</v>
       </c>
       <c r="Z6">
-        <v>-3.55</v>
+        <v>-3.49</v>
       </c>
       <c r="AA6">
-        <v>-3.28</v>
+        <v>-3.32</v>
       </c>
       <c r="AB6">
-        <v>-0.27</v>
+        <v>-0.16</v>
       </c>
       <c r="AC6">
-        <v>2.23</v>
+        <v>13.66</v>
       </c>
       <c r="AD6">
-        <v>12.43</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AE6">
-        <v>5.07</v>
+        <v>5.08</v>
       </c>
       <c r="AF6">
-        <v>-10.18</v>
+        <v>2.85</v>
       </c>
       <c r="AG6">
-        <v>218.3</v>
+        <v>216.28</v>
       </c>
       <c r="AH6">
-        <v>202.34</v>
+        <v>202.89</v>
       </c>
       <c r="AI6">
         <v>218.98</v>
@@ -1456,7 +1490,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>25.75</v>
+        <v>24.42</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1467,10 +1501,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>415.25</v>
+        <v>412.4</v>
       </c>
       <c r="D7">
-        <v>-0.54</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="E7">
         <v>589.48</v>
@@ -1479,70 +1513,70 @@
         <v>393.4</v>
       </c>
       <c r="G7">
-        <v>-29.56</v>
+        <v>-30.04</v>
       </c>
       <c r="H7">
-        <v>5.55</v>
+        <v>4.83</v>
       </c>
       <c r="I7">
-        <v>-3.62</v>
+        <v>-2.74</v>
       </c>
       <c r="J7">
-        <v>-5.3</v>
+        <v>-5.8</v>
       </c>
       <c r="K7">
-        <v>-3.33</v>
+        <v>-3.67</v>
       </c>
       <c r="L7">
-        <v>-29.13</v>
+        <v>-29.41</v>
       </c>
       <c r="M7">
-        <v>1.45</v>
+        <v>0.92</v>
       </c>
       <c r="N7">
         <v>23</v>
       </c>
       <c r="O7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P7">
-        <v>419.43</v>
+        <v>417.11</v>
       </c>
       <c r="Q7">
-        <v>430.13</v>
+        <v>428.7</v>
       </c>
       <c r="R7">
-        <v>428.02</v>
+        <v>428</v>
       </c>
       <c r="S7">
-        <v>479.09</v>
+        <v>478.31</v>
       </c>
       <c r="T7">
-        <v>-13.32</v>
+        <v>-13.78</v>
       </c>
       <c r="U7" t="s">
+        <v>48</v>
+      </c>
+      <c r="V7" t="s">
         <v>47</v>
       </c>
-      <c r="V7" t="s">
-        <v>48</v>
-      </c>
       <c r="W7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="X7">
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>39.25</v>
+        <v>37.57</v>
       </c>
       <c r="Z7">
-        <v>-3.11</v>
+        <v>-3.94</v>
       </c>
       <c r="AA7">
-        <v>-0.6899999999999999</v>
+        <v>-1.34</v>
       </c>
       <c r="AB7">
-        <v>-2.42</v>
+        <v>-2.6</v>
       </c>
       <c r="AC7">
         <v>0</v>
@@ -1551,16 +1585,16 @@
         <v>0</v>
       </c>
       <c r="AE7">
-        <v>9.5</v>
+        <v>9.32</v>
       </c>
       <c r="AF7">
-        <v>50.26</v>
+        <v>-13.23</v>
       </c>
       <c r="AG7">
-        <v>447.11</v>
+        <v>446.65</v>
       </c>
       <c r="AH7">
-        <v>413.14</v>
+        <v>410.76</v>
       </c>
       <c r="AI7">
         <v>411.2</v>
@@ -1569,7 +1603,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>27.59</v>
+        <v>31.09</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1580,10 +1614,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>646.9</v>
+        <v>647.3</v>
       </c>
       <c r="D8">
-        <v>-1.09</v>
+        <v>0.06</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1592,97 +1626,97 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-19.96</v>
+        <v>-19.92</v>
       </c>
       <c r="H8">
-        <v>38.3</v>
+        <v>38.39</v>
       </c>
       <c r="I8">
-        <v>-2</v>
+        <v>-2.83</v>
       </c>
       <c r="J8">
-        <v>-8.449999999999999</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="K8">
-        <v>3.82</v>
+        <v>6.05</v>
       </c>
       <c r="L8">
-        <v>8.52</v>
+        <v>5.83</v>
       </c>
       <c r="M8">
-        <v>-7.82</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="N8">
         <v>55</v>
       </c>
       <c r="O8">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P8">
-        <v>656.5</v>
+        <v>652.73</v>
       </c>
       <c r="Q8">
-        <v>660.8099999999999</v>
+        <v>658.16</v>
       </c>
       <c r="R8">
-        <v>696.95</v>
+        <v>695.22</v>
       </c>
       <c r="S8">
-        <v>612.9400000000001</v>
+        <v>613</v>
       </c>
       <c r="T8">
-        <v>5.54</v>
+        <v>5.59</v>
       </c>
       <c r="U8" t="s">
+        <v>47</v>
+      </c>
+      <c r="V8" t="s">
         <v>48</v>
       </c>
-      <c r="V8" t="s">
+      <c r="W8" t="s">
         <v>47</v>
-      </c>
-      <c r="W8" t="s">
-        <v>48</v>
       </c>
       <c r="X8">
         <v>2</v>
       </c>
       <c r="Y8">
-        <v>36.29</v>
+        <v>36.57</v>
       </c>
       <c r="Z8">
-        <v>-11.6</v>
+        <v>-11.69</v>
       </c>
       <c r="AA8">
-        <v>-12.15</v>
+        <v>-12.06</v>
       </c>
       <c r="AB8">
-        <v>0.55</v>
+        <v>0.37</v>
       </c>
       <c r="AC8">
-        <v>46.88</v>
+        <v>31.91</v>
       </c>
       <c r="AD8">
-        <v>65.7</v>
+        <v>49.12</v>
       </c>
       <c r="AE8">
-        <v>16.49</v>
+        <v>15.97</v>
       </c>
       <c r="AF8">
-        <v>-57.86</v>
+        <v>-58.32</v>
       </c>
       <c r="AG8">
-        <v>685.61</v>
+        <v>675.3</v>
       </c>
       <c r="AH8">
-        <v>636.02</v>
+        <v>641.02</v>
       </c>
       <c r="AI8">
-        <v>700.01</v>
+        <v>698.3200000000001</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>26.91</v>
+        <v>28.42</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1693,10 +1727,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>192.16</v>
+        <v>190.04</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>-1.1</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1705,88 +1739,88 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-30.78</v>
+        <v>-31.54</v>
       </c>
       <c r="H9">
-        <v>11.53</v>
+        <v>10.3</v>
       </c>
       <c r="I9">
-        <v>-2.02</v>
+        <v>-1.46</v>
       </c>
       <c r="J9">
-        <v>1.86</v>
+        <v>0.35</v>
       </c>
       <c r="K9">
-        <v>-4.95</v>
+        <v>-3.4</v>
       </c>
       <c r="L9">
-        <v>-24.72</v>
+        <v>-24.77</v>
       </c>
       <c r="M9">
-        <v>-7.11</v>
+        <v>-7.34</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P9">
-        <v>192.71</v>
+        <v>192.14</v>
       </c>
       <c r="Q9">
-        <v>191.46</v>
+        <v>191.26</v>
       </c>
       <c r="R9">
-        <v>189.12</v>
+        <v>189.21</v>
       </c>
       <c r="S9">
-        <v>209</v>
+        <v>208.57</v>
       </c>
       <c r="T9">
-        <v>-8.06</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="U9" t="s">
+        <v>48</v>
+      </c>
+      <c r="V9" t="s">
         <v>47</v>
       </c>
-      <c r="V9" t="s">
-        <v>48</v>
-      </c>
       <c r="W9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="X9">
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>51.85</v>
+        <v>47.43</v>
       </c>
       <c r="Z9">
-        <v>1.22</v>
+        <v>0.92</v>
       </c>
       <c r="AA9">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AB9">
-        <v>-0.03</v>
+        <v>-0.26</v>
       </c>
       <c r="AC9">
-        <v>29.93</v>
+        <v>18.8</v>
       </c>
       <c r="AD9">
-        <v>38.7</v>
+        <v>30.03</v>
       </c>
       <c r="AE9">
-        <v>4.53</v>
+        <v>4.54</v>
       </c>
       <c r="AF9">
-        <v>-64.31</v>
+        <v>-61.85</v>
       </c>
       <c r="AG9">
-        <v>198.12</v>
+        <v>197.84</v>
       </c>
       <c r="AH9">
-        <v>184.8</v>
+        <v>184.68</v>
       </c>
       <c r="AI9">
         <v>197.85</v>
@@ -1795,7 +1829,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>39.43</v>
+        <v>35.63</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1806,10 +1840,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>76.53</v>
+        <v>75.7</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>-1.08</v>
       </c>
       <c r="E10">
         <v>150.86</v>
@@ -1818,88 +1852,88 @@
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-49.27</v>
+        <v>-49.82</v>
       </c>
       <c r="H10">
-        <v>29.1</v>
+        <v>27.7</v>
       </c>
       <c r="I10">
-        <v>0.51</v>
+        <v>-1.62</v>
       </c>
       <c r="J10">
-        <v>-4.61</v>
+        <v>-5.42</v>
       </c>
       <c r="K10">
-        <v>-2.05</v>
+        <v>-1.15</v>
       </c>
       <c r="L10">
-        <v>-40.61</v>
+        <v>-41.22</v>
       </c>
       <c r="M10">
-        <v>0.26</v>
+        <v>-0.4</v>
       </c>
       <c r="N10">
         <v>12</v>
       </c>
       <c r="O10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P10">
-        <v>76.5</v>
+        <v>76.25</v>
       </c>
       <c r="Q10">
-        <v>76.79000000000001</v>
+        <v>76.58</v>
       </c>
       <c r="R10">
-        <v>79.37</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="S10">
-        <v>82.04000000000001</v>
+        <v>81.94</v>
       </c>
       <c r="T10">
-        <v>-6.71</v>
+        <v>-7.62</v>
       </c>
       <c r="U10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="W10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="X10">
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>43.2</v>
+        <v>39.32</v>
       </c>
       <c r="Z10">
-        <v>-0.84</v>
+        <v>-0.87</v>
       </c>
       <c r="AA10">
-        <v>-0.93</v>
+        <v>-0.92</v>
       </c>
       <c r="AB10">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="AC10">
-        <v>73.66</v>
+        <v>58.14</v>
       </c>
       <c r="AD10">
-        <v>67.53</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="AE10">
         <v>1.77</v>
       </c>
       <c r="AF10">
-        <v>-35.87</v>
+        <v>-60.93</v>
       </c>
       <c r="AG10">
-        <v>78.52</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="AH10">
-        <v>75.05</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="AI10">
         <v>74.97</v>
@@ -1908,7 +1942,7 @@
         <v>50</v>
       </c>
       <c r="AK10">
-        <v>14.13</v>
+        <v>15.26</v>
       </c>
     </row>
   </sheetData>
@@ -2049,7 +2083,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2069,1110 +2103,1318 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C8" s="6">
         <v>-3.78</v>
       </c>
-      <c r="D7" s="5">
-        <v>-4.43</v>
-      </c>
-      <c r="E7" s="6">
-        <v>-0.65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="D8" s="6">
+        <v>-5.62</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-1.84</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C9" s="6">
         <v>-3.69</v>
       </c>
-      <c r="D8" s="5">
-        <v>-4.85</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-1.16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D9" s="6">
+        <v>-5.68</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-1.99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C10" s="6">
         <v>-12.68</v>
       </c>
-      <c r="D9" s="5">
-        <v>-12.31</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D10" s="6">
+        <v>-14.51</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-1.83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C11" s="6">
         <v>-6.92</v>
       </c>
-      <c r="D10" s="5">
-        <v>-7.48</v>
-      </c>
-      <c r="E10" s="6">
-        <v>-0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D11" s="6">
+        <v>-8.76</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C12" s="6">
         <v>-5.23</v>
       </c>
-      <c r="D11" s="5">
-        <v>-5.08</v>
-      </c>
-      <c r="E11" s="7">
+      <c r="D12" s="6">
+        <v>-6.54</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-1.31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-3.71</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-5.8</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-2.09</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-7.58</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-1.62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>1.22</v>
+      </c>
+      <c r="D15" s="6">
+        <v>0.35</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-5.01</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-5.42</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-0.41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-3.04</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-2.69</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="D18" s="6">
+        <v>0.23</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-1.78</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-4.25</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-2.47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.38</v>
+      </c>
+      <c r="D20" s="6">
+        <v>0.85</v>
+      </c>
+      <c r="E20" s="8">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-1.79</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-1.64</v>
+      </c>
+      <c r="E21" s="8">
         <v>0.15</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>-3.71</v>
-      </c>
-      <c r="D12" s="5">
-        <v>-5.3</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-1.59</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-3.8</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-2.74</v>
+      </c>
+      <c r="E22" s="8">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-7.58</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-8.449999999999999</v>
-      </c>
-      <c r="E13" s="6">
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-0.53</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-2.83</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-2.3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-2.7</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-1.46</v>
+      </c>
+      <c r="E24" s="8">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-0.44</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-1.62</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1.18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-25.68</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-26.65</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>39.41</v>
+      </c>
+      <c r="D27" s="6">
+        <v>31.28</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-8.130000000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>47.48</v>
+      </c>
+      <c r="D28" s="6">
+        <v>40.51</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-6.97</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>28.84</v>
+      </c>
+      <c r="D29" s="6">
+        <v>26.98</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-1.86</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>77.89</v>
+      </c>
+      <c r="D30" s="6">
+        <v>73.78</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-4.11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-27.66</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-29.41</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-1.75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>11.92</v>
+      </c>
+      <c r="D32" s="6">
+        <v>5.83</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-6.09</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-24.39</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-24.77</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-40.96</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-41.22</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-2.25</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-2.98</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>12.89</v>
+      </c>
+      <c r="D36" s="6">
+        <v>11.06</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-1.83</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-1.53</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-4.05</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-2.52</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-4.51</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-4.69</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-6.41</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-6.66</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-2.46</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-3.67</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-1.21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>7.24</v>
+      </c>
+      <c r="D41" s="6">
+        <v>6.05</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-1.19</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-3.62</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-3.4</v>
+      </c>
+      <c r="E42" s="8">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="6">
+        <v>2.77</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-1.15</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-3.92</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-30.55</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-31.48</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-5.51</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-6.53</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-15.99</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-18.48</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-2.49</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-9.73</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-10.66</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-17.54</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-17.41</v>
+      </c>
+      <c r="E48" s="8">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-29.17</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-30.04</v>
+      </c>
+      <c r="E49" s="7">
         <v>-0.87</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-19.08</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-19.92</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="5">
-        <v>1.22</v>
-      </c>
-      <c r="D14" s="5">
-        <v>1.86</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-30.78</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-31.54</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-5.01</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-4.61</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B52" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="6">
+        <v>-49.27</v>
+      </c>
+      <c r="D52" s="6">
+        <v>-49.82</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-3.04</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>1321.4</v>
+      </c>
+      <c r="D53" s="6">
+        <v>1303.8</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-17.6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>3035.1</v>
+      </c>
+      <c r="D54" s="6">
+        <v>3002.5</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-32.6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>1348</v>
+      </c>
+      <c r="D55" s="6">
+        <v>1308</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>1700</v>
+      </c>
+      <c r="D56" s="6">
+        <v>1682.4</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-17.6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>205.25</v>
+      </c>
+      <c r="D57" s="6">
+        <v>205.58</v>
+      </c>
+      <c r="E57" s="8">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>417.5</v>
+      </c>
+      <c r="D58" s="6">
+        <v>412.4</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-5.1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>654.05</v>
+      </c>
+      <c r="D59" s="6">
+        <v>647.3</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-6.75</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="6">
+        <v>192.16</v>
+      </c>
+      <c r="D60" s="6">
+        <v>190.04</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-2.12</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="6">
+        <v>76.53</v>
+      </c>
+      <c r="D61" s="6">
+        <v>75.7</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-0.83</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="6">
+        <v>40.03</v>
+      </c>
+      <c r="D62" s="6">
+        <v>36.24</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-3.79</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="6">
+        <v>49.88</v>
+      </c>
+      <c r="D63" s="6">
+        <v>46.03</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-3.85</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="6">
+        <v>38.31</v>
+      </c>
+      <c r="D64" s="6">
+        <v>32.85</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-5.46</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>42.58</v>
+      </c>
+      <c r="D65" s="6">
+        <v>39.17</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-3.41</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>37.17</v>
+      </c>
+      <c r="D66" s="6">
+        <v>39.47</v>
+      </c>
+      <c r="E66" s="8">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>40.59</v>
+      </c>
+      <c r="D67" s="6">
+        <v>37.57</v>
+      </c>
+      <c r="E67" s="7">
         <v>-3.02</v>
       </c>
-      <c r="E16" s="7">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>39.2</v>
+      </c>
+      <c r="D68" s="6">
+        <v>36.57</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-2.63</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>51.85</v>
+      </c>
+      <c r="D69" s="6">
+        <v>47.43</v>
+      </c>
+      <c r="E69" s="7">
+        <v>-4.42</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="6">
+        <v>43.2</v>
+      </c>
+      <c r="D70" s="6">
+        <v>39.32</v>
+      </c>
+      <c r="E70" s="7">
+        <v>-3.88</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="6">
+        <v>-51.91</v>
+      </c>
+      <c r="D71" s="6">
+        <v>-43.12</v>
+      </c>
+      <c r="E71" s="8">
+        <v>8.789999999999999</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.09</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-0.59</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B72" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="6">
+        <v>56.76</v>
+      </c>
+      <c r="D72" s="6">
+        <v>-33.44</v>
+      </c>
+      <c r="E72" s="7">
+        <v>-90.2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-1.78</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-3.02</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-1.24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B73" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="6">
+        <v>-55.84</v>
+      </c>
+      <c r="D73" s="6">
+        <v>-58.39</v>
+      </c>
+      <c r="E73" s="7">
+        <v>-2.55</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>0.38</v>
-      </c>
-      <c r="D19" s="5">
-        <v>1.13</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="6">
+        <v>-10.95</v>
+      </c>
+      <c r="D74" s="6">
+        <v>-42.38</v>
+      </c>
+      <c r="E74" s="7">
+        <v>-31.43</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-1.79</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-3.37</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-1.58</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
+        <v>-31.9</v>
+      </c>
+      <c r="D75" s="6">
+        <v>2.85</v>
+      </c>
+      <c r="E75" s="8">
+        <v>34.75</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-3.8</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-3.62</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>-39.79</v>
+      </c>
+      <c r="D76" s="6">
+        <v>-13.23</v>
+      </c>
+      <c r="E76" s="8">
+        <v>26.56</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="5">
-        <v>-0.53</v>
-      </c>
-      <c r="D22" s="5">
-        <v>-2</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-1.47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>-47.76</v>
+      </c>
+      <c r="D77" s="6">
+        <v>-58.32</v>
+      </c>
+      <c r="E77" s="7">
+        <v>-10.56</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="5">
-        <v>-2.7</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-2.02</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="6">
+        <v>13.44</v>
+      </c>
+      <c r="D78" s="6">
+        <v>-61.85</v>
+      </c>
+      <c r="E78" s="7">
+        <v>-75.29000000000001</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-0.44</v>
-      </c>
-      <c r="D24" s="5">
-        <v>0.51</v>
-      </c>
-      <c r="E24" s="7">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-25.68</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-25.86</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-0.18</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>39.41</v>
-      </c>
-      <c r="D26" s="5">
-        <v>31.76</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-7.65</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>47.48</v>
-      </c>
-      <c r="D27" s="5">
-        <v>42.89</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-4.59</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="5">
-        <v>28.84</v>
-      </c>
-      <c r="D28" s="5">
-        <v>27.46</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-1.38</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="5">
-        <v>77.89</v>
-      </c>
-      <c r="D29" s="5">
-        <v>71.38</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-6.51</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-27.66</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-29.13</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-1.47</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="5">
-        <v>11.92</v>
-      </c>
-      <c r="D31" s="5">
-        <v>8.52</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-3.4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-24.39</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-24.72</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-0.33</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-40.96</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-40.61</v>
-      </c>
-      <c r="E33" s="7">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-2.25</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-2.58</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-0.33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="5">
-        <v>12.89</v>
-      </c>
-      <c r="D35" s="5">
-        <v>10.41</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-2.48</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-1.53</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-3.64</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-2.11</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-4.51</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-3.16</v>
-      </c>
-      <c r="E37" s="7">
-        <v>1.35</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-6.41</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-7.09</v>
-      </c>
-      <c r="E38" s="6">
-        <v>-0.68</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-2.46</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-3.33</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-0.87</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="5">
-        <v>7.24</v>
-      </c>
-      <c r="D40" s="5">
-        <v>3.82</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-3.42</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-3.62</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-4.95</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-1.33</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="5">
-        <v>2.77</v>
-      </c>
-      <c r="D42" s="5">
-        <v>-2.05</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-4.82</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-30.55</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-30.8</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-5.51</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-6.38</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-0.87</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-15.99</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-17.26</v>
-      </c>
-      <c r="E45" s="6">
-        <v>-1.27</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-17.54</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-18.22</v>
-      </c>
-      <c r="E46" s="6">
-        <v>-0.68</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="5">
-        <v>-29.17</v>
-      </c>
-      <c r="D47" s="5">
-        <v>-29.56</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-0.39</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="5">
-        <v>-19.08</v>
-      </c>
-      <c r="D48" s="5">
-        <v>-19.96</v>
-      </c>
-      <c r="E48" s="6">
-        <v>-0.88</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="5">
-        <v>1321.4</v>
-      </c>
-      <c r="D49" s="5">
-        <v>1316.6</v>
-      </c>
-      <c r="E49" s="6">
-        <v>-4.8</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="5">
-        <v>3035.1</v>
-      </c>
-      <c r="D50" s="5">
-        <v>3007.3</v>
-      </c>
-      <c r="E50" s="6">
-        <v>-27.8</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="5">
-        <v>1348</v>
-      </c>
-      <c r="D51" s="5">
-        <v>1327.6</v>
-      </c>
-      <c r="E51" s="6">
-        <v>-20.4</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="5">
-        <v>205.25</v>
-      </c>
-      <c r="D52" s="5">
-        <v>203.56</v>
-      </c>
-      <c r="E52" s="6">
-        <v>-1.69</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="5">
-        <v>417.5</v>
-      </c>
-      <c r="D53" s="5">
-        <v>415.25</v>
-      </c>
-      <c r="E53" s="6">
-        <v>-2.25</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="5">
-        <v>654.05</v>
-      </c>
-      <c r="D54" s="5">
-        <v>646.9</v>
-      </c>
-      <c r="E54" s="6">
-        <v>-7.15</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="5">
-        <v>40.03</v>
-      </c>
-      <c r="D55" s="5">
-        <v>38.98</v>
-      </c>
-      <c r="E55" s="6">
-        <v>-1.05</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="5">
-        <v>49.88</v>
-      </c>
-      <c r="D56" s="5">
-        <v>46.59</v>
-      </c>
-      <c r="E56" s="6">
-        <v>-3.29</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="5">
-        <v>38.31</v>
-      </c>
-      <c r="D57" s="5">
-        <v>35.42</v>
-      </c>
-      <c r="E57" s="6">
-        <v>-2.89</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="5">
-        <v>37.17</v>
-      </c>
-      <c r="D58" s="5">
-        <v>35.06</v>
-      </c>
-      <c r="E58" s="6">
-        <v>-2.11</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="5">
-        <v>40.59</v>
-      </c>
-      <c r="D59" s="5">
-        <v>39.25</v>
-      </c>
-      <c r="E59" s="6">
-        <v>-1.34</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="5">
-        <v>39.2</v>
-      </c>
-      <c r="D60" s="5">
-        <v>36.29</v>
-      </c>
-      <c r="E60" s="6">
-        <v>-2.91</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B61" s="3" t="s">
+      <c r="B79" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C61" s="5">
-        <v>-51.91</v>
-      </c>
-      <c r="D61" s="5">
-        <v>-36.86</v>
-      </c>
-      <c r="E61" s="7">
-        <v>15.05</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="5">
-        <v>56.76</v>
-      </c>
-      <c r="D62" s="5">
-        <v>-13.43</v>
-      </c>
-      <c r="E62" s="6">
-        <v>-70.19</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="5">
-        <v>-55.84</v>
-      </c>
-      <c r="D63" s="5">
-        <v>-69.22</v>
-      </c>
-      <c r="E63" s="6">
-        <v>-13.38</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="5">
-        <v>-10.95</v>
-      </c>
-      <c r="D64" s="5">
-        <v>-28.29</v>
-      </c>
-      <c r="E64" s="6">
-        <v>-17.34</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="5">
-        <v>-31.9</v>
-      </c>
-      <c r="D65" s="5">
-        <v>-10.18</v>
-      </c>
-      <c r="E65" s="7">
-        <v>21.72</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="5">
-        <v>-39.79</v>
-      </c>
-      <c r="D66" s="5">
-        <v>50.26</v>
-      </c>
-      <c r="E66" s="7">
-        <v>90.05</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="5">
-        <v>-47.76</v>
-      </c>
-      <c r="D67" s="5">
-        <v>-57.86</v>
-      </c>
-      <c r="E67" s="6">
-        <v>-10.1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="5">
-        <v>13.44</v>
-      </c>
-      <c r="D68" s="5">
-        <v>-64.31</v>
-      </c>
-      <c r="E68" s="6">
-        <v>-77.75</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="5">
+      <c r="C79" s="6">
         <v>-2.39</v>
       </c>
-      <c r="D69" s="5">
-        <v>-35.87</v>
-      </c>
-      <c r="E69" s="6">
-        <v>-33.48</v>
+      <c r="D79" s="6">
+        <v>-60.93</v>
+      </c>
+      <c r="E79" s="7">
+        <v>-58.54</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3192,60 +3434,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="8" t="s">
+      <c r="B1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="11">
+        <v>56.16</v>
+      </c>
+      <c r="C2" s="12">
+        <v>9</v>
+      </c>
+      <c r="D2" s="11">
+        <v>39.4</v>
+      </c>
+      <c r="E2" s="11">
         <v>60</v>
       </c>
-      <c r="E1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="10">
-        <v>56.16</v>
-      </c>
-      <c r="C2" s="11">
-        <v>9</v>
-      </c>
-      <c r="D2" s="10">
-        <v>41</v>
-      </c>
-      <c r="E2" s="10">
-        <v>60</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-5.6</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-1.4</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-6.8</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-1.1</v>
+      </c>
+      <c r="H2" s="11">
         <v>55.4</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -3347,61 +3589,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="13">
-        <v>0.6634</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.2032</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.159</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.0722</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.0145</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.0026</v>
-      </c>
-      <c r="G2" s="13">
-        <v>-0.0711</v>
-      </c>
-      <c r="H2" s="13">
-        <v>-0.07820000000000001</v>
-      </c>
-      <c r="I2" s="13">
-        <v>-0.09820000000000001</v>
+      <c r="A2" s="14">
+        <v>0.6779999999999999</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1963</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1557</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.0677</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.0092</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.004</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.07339999999999999</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.08699999999999999</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.1036</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -200,18 +200,6 @@
   </si>
   <si>
     <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>51.9 → 47.4</t>
-  </si>
-  <si>
-    <t>51.9</t>
-  </si>
-  <si>
-    <t>47.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -936,10 +924,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1303.8</v>
+        <v>1288.7</v>
       </c>
       <c r="D2">
-        <v>-0.97</v>
+        <v>-1.16</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -948,46 +936,46 @@
         <v>1247.38</v>
       </c>
       <c r="G2">
-        <v>-31.48</v>
+        <v>-32.27</v>
       </c>
       <c r="H2">
-        <v>4.52</v>
+        <v>3.31</v>
       </c>
       <c r="I2">
-        <v>-2.69</v>
+        <v>-3.31</v>
       </c>
       <c r="J2">
-        <v>-5.62</v>
+        <v>-7.14</v>
       </c>
       <c r="K2">
-        <v>-2.98</v>
+        <v>-4.75</v>
       </c>
       <c r="L2">
-        <v>-26.65</v>
+        <v>-27.44</v>
       </c>
       <c r="M2">
-        <v>-10.36</v>
+        <v>-10.07</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P2">
-        <v>1319.86</v>
+        <v>1311.04</v>
       </c>
       <c r="Q2">
-        <v>1351.65</v>
+        <v>1348.14</v>
       </c>
       <c r="R2">
-        <v>1353.16</v>
+        <v>1352.59</v>
       </c>
       <c r="S2">
-        <v>1527.35</v>
+        <v>1524.55</v>
       </c>
       <c r="T2">
-        <v>-14.64</v>
+        <v>-15.47</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1002,16 +990,16 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>36.24</v>
+        <v>33.26</v>
       </c>
       <c r="Z2">
-        <v>-11.78</v>
+        <v>-14.85</v>
       </c>
       <c r="AA2">
-        <v>-4.54</v>
+        <v>-6.6</v>
       </c>
       <c r="AB2">
-        <v>-7.24</v>
+        <v>-8.25</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -1020,25 +1008,25 @@
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>25.57</v>
+        <v>25.48</v>
       </c>
       <c r="AF2">
-        <v>-43.12</v>
+        <v>-35.63</v>
       </c>
       <c r="AG2">
-        <v>1403.18</v>
+        <v>1406.67</v>
       </c>
       <c r="AH2">
-        <v>1300.12</v>
+        <v>1289.6</v>
       </c>
       <c r="AI2">
-        <v>1386.85</v>
+        <v>1374.58</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>31.53</v>
+        <v>35.67</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1049,10 +1037,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3002.5</v>
+        <v>2990.3</v>
       </c>
       <c r="D3">
-        <v>-0.16</v>
+        <v>-0.41</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1061,46 +1049,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-6.53</v>
+        <v>-6.91</v>
       </c>
       <c r="H3">
-        <v>70.79000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="I3">
-        <v>0.23</v>
+        <v>0.15</v>
       </c>
       <c r="J3">
-        <v>-5.68</v>
+        <v>-6.05</v>
       </c>
       <c r="K3">
-        <v>11.06</v>
+        <v>10.9</v>
       </c>
       <c r="L3">
-        <v>31.28</v>
+        <v>31.21</v>
       </c>
       <c r="M3">
-        <v>15.57</v>
+        <v>15.96</v>
       </c>
       <c r="N3">
         <v>88</v>
       </c>
       <c r="O3">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P3">
-        <v>2999.1</v>
+        <v>3000.02</v>
       </c>
       <c r="Q3">
-        <v>3026.06</v>
+        <v>3018.19</v>
       </c>
       <c r="R3">
-        <v>3052.14</v>
+        <v>3052.37</v>
       </c>
       <c r="S3">
-        <v>2473.42</v>
+        <v>2475.75</v>
       </c>
       <c r="T3">
-        <v>21.39</v>
+        <v>20.78</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1115,34 +1103,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>46.03</v>
+        <v>44.55</v>
       </c>
       <c r="Z3">
-        <v>-15.76</v>
+        <v>-16.66</v>
       </c>
       <c r="AA3">
-        <v>-10.42</v>
+        <v>-11.67</v>
       </c>
       <c r="AB3">
-        <v>-5.34</v>
+        <v>-5</v>
       </c>
       <c r="AC3">
-        <v>68.90000000000001</v>
+        <v>52.7</v>
       </c>
       <c r="AD3">
-        <v>49.84</v>
+        <v>57.34</v>
       </c>
       <c r="AE3">
-        <v>67.18000000000001</v>
+        <v>66.08</v>
       </c>
       <c r="AF3">
-        <v>-33.44</v>
+        <v>-12.33</v>
       </c>
       <c r="AG3">
-        <v>3101.49</v>
+        <v>3069.01</v>
       </c>
       <c r="AH3">
-        <v>2950.62</v>
+        <v>2967.36</v>
       </c>
       <c r="AI3">
         <v>2959.69</v>
@@ -1151,7 +1139,7 @@
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>21.83</v>
+        <v>22.66</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1162,10 +1150,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1308</v>
+        <v>1293</v>
       </c>
       <c r="D4">
-        <v>-1.48</v>
+        <v>-1.15</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1174,25 +1162,25 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-18.48</v>
+        <v>-19.41</v>
       </c>
       <c r="H4">
-        <v>69.25</v>
+        <v>67.31</v>
       </c>
       <c r="I4">
-        <v>-4.25</v>
+        <v>-2.95</v>
       </c>
       <c r="J4">
-        <v>-14.51</v>
+        <v>-16.14</v>
       </c>
       <c r="K4">
-        <v>-4.05</v>
+        <v>-4.8</v>
       </c>
       <c r="L4">
-        <v>40.51</v>
+        <v>39.91</v>
       </c>
       <c r="M4">
-        <v>6.77</v>
+        <v>6.68</v>
       </c>
       <c r="N4">
         <v>77</v>
@@ -1201,19 +1189,19 @@
         <v>70</v>
       </c>
       <c r="P4">
-        <v>1326.98</v>
+        <v>1319.12</v>
       </c>
       <c r="Q4">
-        <v>1370.62</v>
+        <v>1361.65</v>
       </c>
       <c r="R4">
-        <v>1459.92</v>
+        <v>1455.09</v>
       </c>
       <c r="S4">
-        <v>1162.77</v>
+        <v>1163.54</v>
       </c>
       <c r="T4">
-        <v>12.49</v>
+        <v>11.13</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1228,43 +1216,43 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>32.85</v>
+        <v>31</v>
       </c>
       <c r="Z4">
-        <v>-38.97</v>
+        <v>-40.9</v>
       </c>
       <c r="AA4">
-        <v>-35</v>
+        <v>-36.18</v>
       </c>
       <c r="AB4">
-        <v>-3.97</v>
+        <v>-4.72</v>
       </c>
       <c r="AC4">
-        <v>46.07</v>
+        <v>22.03</v>
       </c>
       <c r="AD4">
-        <v>36.7</v>
+        <v>35.87</v>
       </c>
       <c r="AE4">
-        <v>41.25</v>
+        <v>40.57</v>
       </c>
       <c r="AF4">
-        <v>-58.39</v>
+        <v>-38.47</v>
       </c>
       <c r="AG4">
-        <v>1441</v>
+        <v>1422.54</v>
       </c>
       <c r="AH4">
-        <v>1300.24</v>
+        <v>1300.77</v>
       </c>
       <c r="AI4">
-        <v>1445.94</v>
+        <v>1418.72</v>
       </c>
       <c r="AJ4" t="s">
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>24.65</v>
+        <v>27.63</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1275,10 +1263,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1682.4</v>
+        <v>1681.9</v>
       </c>
       <c r="D5">
-        <v>-1.04</v>
+        <v>-0.03</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1287,46 +1275,46 @@
         <v>1294.84</v>
       </c>
       <c r="G5">
-        <v>-10.66</v>
+        <v>-10.69</v>
       </c>
       <c r="H5">
-        <v>29.93</v>
+        <v>29.89</v>
       </c>
       <c r="I5">
-        <v>0.85</v>
+        <v>1.02</v>
       </c>
       <c r="J5">
-        <v>-8.76</v>
+        <v>-8.91</v>
       </c>
       <c r="K5">
-        <v>-4.69</v>
+        <v>-5.82</v>
       </c>
       <c r="L5">
-        <v>26.98</v>
+        <v>27.99</v>
       </c>
       <c r="M5">
-        <v>19.63</v>
+        <v>20.26</v>
       </c>
       <c r="N5">
         <v>66</v>
       </c>
       <c r="O5">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P5">
-        <v>1681.08</v>
+        <v>1684.46</v>
       </c>
       <c r="Q5">
-        <v>1712.12</v>
+        <v>1705.24</v>
       </c>
       <c r="R5">
-        <v>1778.92</v>
+        <v>1776.19</v>
       </c>
       <c r="S5">
-        <v>1587.7</v>
+        <v>1588.85</v>
       </c>
       <c r="T5">
-        <v>5.96</v>
+        <v>5.86</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1341,34 +1329,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>39.17</v>
+        <v>39.07</v>
       </c>
       <c r="Z5">
-        <v>-29.99</v>
+        <v>-28.81</v>
       </c>
       <c r="AA5">
-        <v>-31</v>
+        <v>-30.56</v>
       </c>
       <c r="AB5">
-        <v>1.02</v>
+        <v>1.75</v>
       </c>
       <c r="AC5">
-        <v>92.48999999999999</v>
+        <v>83.16</v>
       </c>
       <c r="AD5">
-        <v>70.79000000000001</v>
+        <v>82.72</v>
       </c>
       <c r="AE5">
-        <v>36.01</v>
+        <v>34.65</v>
       </c>
       <c r="AF5">
-        <v>-42.38</v>
+        <v>-46.6</v>
       </c>
       <c r="AG5">
-        <v>1802.91</v>
+        <v>1781.49</v>
       </c>
       <c r="AH5">
-        <v>1621.33</v>
+        <v>1629</v>
       </c>
       <c r="AI5">
         <v>1761.08</v>
@@ -1377,7 +1365,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>39.97</v>
+        <v>36.09</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1388,10 +1376,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>205.58</v>
+        <v>204.02</v>
       </c>
       <c r="D6">
-        <v>0.99</v>
+        <v>-0.76</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1400,25 +1388,25 @@
         <v>116.81</v>
       </c>
       <c r="G6">
-        <v>-17.41</v>
+        <v>-18.03</v>
       </c>
       <c r="H6">
-        <v>76</v>
+        <v>74.66</v>
       </c>
       <c r="I6">
-        <v>-1.64</v>
+        <v>-1.43</v>
       </c>
       <c r="J6">
-        <v>-6.54</v>
+        <v>-7.42</v>
       </c>
       <c r="K6">
-        <v>-6.66</v>
+        <v>-6.98</v>
       </c>
       <c r="L6">
-        <v>73.78</v>
+        <v>74.2</v>
       </c>
       <c r="M6">
-        <v>67.8</v>
+        <v>67.52</v>
       </c>
       <c r="N6">
         <v>99</v>
@@ -1427,19 +1415,19 @@
         <v>84</v>
       </c>
       <c r="P6">
-        <v>205.5</v>
+        <v>204.9</v>
       </c>
       <c r="Q6">
-        <v>209.58</v>
+        <v>208.94</v>
       </c>
       <c r="R6">
-        <v>217.44</v>
+        <v>217</v>
       </c>
       <c r="S6">
-        <v>179.39</v>
+        <v>179.6</v>
       </c>
       <c r="T6">
-        <v>14.6</v>
+        <v>13.6</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1454,34 +1442,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>39.47</v>
+        <v>37.36</v>
       </c>
       <c r="Z6">
-        <v>-3.49</v>
+        <v>-3.52</v>
       </c>
       <c r="AA6">
-        <v>-3.32</v>
+        <v>-3.36</v>
       </c>
       <c r="AB6">
         <v>-0.16</v>
       </c>
       <c r="AC6">
-        <v>13.66</v>
+        <v>20.78</v>
       </c>
       <c r="AD6">
-        <v>8.289999999999999</v>
+        <v>12.22</v>
       </c>
       <c r="AE6">
-        <v>5.08</v>
+        <v>4.94</v>
       </c>
       <c r="AF6">
-        <v>2.85</v>
+        <v>-42.39</v>
       </c>
       <c r="AG6">
-        <v>216.28</v>
+        <v>215.12</v>
       </c>
       <c r="AH6">
-        <v>202.89</v>
+        <v>202.76</v>
       </c>
       <c r="AI6">
         <v>218.98</v>
@@ -1490,7 +1478,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>24.42</v>
+        <v>24.01</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1501,10 +1489,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>412.4</v>
+        <v>407.5</v>
       </c>
       <c r="D7">
-        <v>-0.6899999999999999</v>
+        <v>-1.19</v>
       </c>
       <c r="E7">
         <v>589.48</v>
@@ -1513,49 +1501,49 @@
         <v>393.4</v>
       </c>
       <c r="G7">
-        <v>-30.04</v>
+        <v>-30.87</v>
       </c>
       <c r="H7">
-        <v>4.83</v>
+        <v>3.58</v>
       </c>
       <c r="I7">
-        <v>-2.74</v>
+        <v>-3.21</v>
       </c>
       <c r="J7">
-        <v>-5.8</v>
+        <v>-7.56</v>
       </c>
       <c r="K7">
-        <v>-3.67</v>
+        <v>-6.17</v>
       </c>
       <c r="L7">
-        <v>-29.41</v>
+        <v>-29.5</v>
       </c>
       <c r="M7">
-        <v>0.92</v>
+        <v>1.57</v>
       </c>
       <c r="N7">
         <v>23</v>
       </c>
       <c r="O7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P7">
-        <v>417.11</v>
+        <v>414.41</v>
       </c>
       <c r="Q7">
-        <v>428.7</v>
+        <v>427.54</v>
       </c>
       <c r="R7">
-        <v>428</v>
+        <v>427.87</v>
       </c>
       <c r="S7">
-        <v>478.31</v>
+        <v>477.52</v>
       </c>
       <c r="T7">
-        <v>-13.78</v>
+        <v>-14.66</v>
       </c>
       <c r="U7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V7" t="s">
         <v>47</v>
@@ -1564,19 +1552,19 @@
         <v>47</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7">
-        <v>37.57</v>
+        <v>34.8</v>
       </c>
       <c r="Z7">
-        <v>-3.94</v>
+        <v>-4.94</v>
       </c>
       <c r="AA7">
-        <v>-1.34</v>
+        <v>-2.06</v>
       </c>
       <c r="AB7">
-        <v>-2.6</v>
+        <v>-2.88</v>
       </c>
       <c r="AC7">
         <v>0</v>
@@ -1585,25 +1573,25 @@
         <v>0</v>
       </c>
       <c r="AE7">
-        <v>9.32</v>
+        <v>9.15</v>
       </c>
       <c r="AF7">
-        <v>-13.23</v>
+        <v>-24.39</v>
       </c>
       <c r="AG7">
-        <v>446.65</v>
+        <v>447.79</v>
       </c>
       <c r="AH7">
-        <v>410.76</v>
+        <v>407.29</v>
       </c>
       <c r="AI7">
-        <v>411.2</v>
+        <v>436.39</v>
       </c>
       <c r="AJ7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AK7">
-        <v>31.09</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1614,10 +1602,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>647.3</v>
+        <v>664.25</v>
       </c>
       <c r="D8">
-        <v>0.06</v>
+        <v>2.62</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1626,46 +1614,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-19.92</v>
+        <v>-17.82</v>
       </c>
       <c r="H8">
-        <v>38.39</v>
+        <v>42.01</v>
       </c>
       <c r="I8">
-        <v>-2.83</v>
+        <v>0.59</v>
       </c>
       <c r="J8">
-        <v>-9.199999999999999</v>
+        <v>-5.16</v>
       </c>
       <c r="K8">
-        <v>6.05</v>
+        <v>4.13</v>
       </c>
       <c r="L8">
-        <v>5.83</v>
+        <v>9.07</v>
       </c>
       <c r="M8">
-        <v>-8.699999999999999</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="N8">
         <v>55</v>
       </c>
       <c r="O8">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="P8">
-        <v>652.73</v>
+        <v>653.51</v>
       </c>
       <c r="Q8">
-        <v>658.16</v>
+        <v>657.29</v>
       </c>
       <c r="R8">
-        <v>695.22</v>
+        <v>693.47</v>
       </c>
       <c r="S8">
-        <v>613</v>
+        <v>613.13</v>
       </c>
       <c r="T8">
-        <v>5.59</v>
+        <v>8.34</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1680,34 +1668,34 @@
         <v>2</v>
       </c>
       <c r="Y8">
-        <v>36.57</v>
+        <v>47.29</v>
       </c>
       <c r="Z8">
-        <v>-11.69</v>
+        <v>-10.27</v>
       </c>
       <c r="AA8">
-        <v>-12.06</v>
+        <v>-11.7</v>
       </c>
       <c r="AB8">
-        <v>0.37</v>
+        <v>1.43</v>
       </c>
       <c r="AC8">
-        <v>31.91</v>
+        <v>45.01</v>
       </c>
       <c r="AD8">
-        <v>49.12</v>
+        <v>41.27</v>
       </c>
       <c r="AE8">
-        <v>15.97</v>
+        <v>17.73</v>
       </c>
       <c r="AF8">
-        <v>-58.32</v>
+        <v>959.14</v>
       </c>
       <c r="AG8">
-        <v>675.3</v>
+        <v>670.8099999999999</v>
       </c>
       <c r="AH8">
-        <v>641.02</v>
+        <v>643.77</v>
       </c>
       <c r="AI8">
         <v>698.3200000000001</v>
@@ -1716,7 +1704,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>28.42</v>
+        <v>29.39</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1727,10 +1715,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>190.04</v>
+        <v>188.72</v>
       </c>
       <c r="D9">
-        <v>-1.1</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1739,46 +1727,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-31.54</v>
+        <v>-32.02</v>
       </c>
       <c r="H9">
-        <v>10.3</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="I9">
-        <v>-1.46</v>
+        <v>-2.84</v>
       </c>
       <c r="J9">
-        <v>0.35</v>
+        <v>-2.69</v>
       </c>
       <c r="K9">
-        <v>-3.4</v>
+        <v>-4.8</v>
       </c>
       <c r="L9">
-        <v>-24.77</v>
+        <v>-25.26</v>
       </c>
       <c r="M9">
-        <v>-7.34</v>
+        <v>-7.48</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="P9">
-        <v>192.14</v>
+        <v>191.04</v>
       </c>
       <c r="Q9">
-        <v>191.26</v>
+        <v>191.2</v>
       </c>
       <c r="R9">
         <v>189.21</v>
       </c>
       <c r="S9">
-        <v>208.57</v>
+        <v>208.14</v>
       </c>
       <c r="T9">
-        <v>-8.890000000000001</v>
+        <v>-9.33</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1793,34 +1781,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>47.43</v>
+        <v>44.86</v>
       </c>
       <c r="Z9">
-        <v>0.92</v>
+        <v>0.58</v>
       </c>
       <c r="AA9">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AB9">
-        <v>-0.26</v>
+        <v>-0.48</v>
       </c>
       <c r="AC9">
-        <v>18.8</v>
+        <v>7.5</v>
       </c>
       <c r="AD9">
-        <v>30.03</v>
+        <v>18.75</v>
       </c>
       <c r="AE9">
-        <v>4.54</v>
+        <v>4.52</v>
       </c>
       <c r="AF9">
-        <v>-61.85</v>
+        <v>-53.86</v>
       </c>
       <c r="AG9">
-        <v>197.84</v>
+        <v>197.86</v>
       </c>
       <c r="AH9">
-        <v>184.68</v>
+        <v>184.55</v>
       </c>
       <c r="AI9">
         <v>197.85</v>
@@ -1829,7 +1817,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>35.63</v>
+        <v>32.38</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1840,10 +1828,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>75.7</v>
+        <v>73.34</v>
       </c>
       <c r="D10">
-        <v>-1.08</v>
+        <v>-3.12</v>
       </c>
       <c r="E10">
         <v>150.86</v>
@@ -1852,46 +1840,46 @@
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-49.82</v>
+        <v>-51.39</v>
       </c>
       <c r="H10">
-        <v>27.7</v>
+        <v>23.72</v>
       </c>
       <c r="I10">
-        <v>-1.62</v>
+        <v>-3.64</v>
       </c>
       <c r="J10">
-        <v>-5.42</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="K10">
-        <v>-1.15</v>
+        <v>-5.14</v>
       </c>
       <c r="L10">
-        <v>-41.22</v>
+        <v>-43</v>
       </c>
       <c r="M10">
-        <v>-0.4</v>
+        <v>0.02</v>
       </c>
       <c r="N10">
         <v>12</v>
       </c>
       <c r="O10">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>76.25</v>
+        <v>75.69</v>
       </c>
       <c r="Q10">
-        <v>76.58</v>
+        <v>76.45</v>
       </c>
       <c r="R10">
-        <v>79.26000000000001</v>
+        <v>79.09</v>
       </c>
       <c r="S10">
-        <v>81.94</v>
+        <v>81.84</v>
       </c>
       <c r="T10">
-        <v>-7.62</v>
+        <v>-10.39</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1906,43 +1894,43 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>39.32</v>
+        <v>30.83</v>
       </c>
       <c r="Z10">
-        <v>-0.87</v>
+        <v>-1.06</v>
       </c>
       <c r="AA10">
-        <v>-0.92</v>
+        <v>-0.95</v>
       </c>
       <c r="AB10">
-        <v>0.05</v>
+        <v>-0.12</v>
       </c>
       <c r="AC10">
-        <v>58.14</v>
+        <v>32.03</v>
       </c>
       <c r="AD10">
-        <v>64.45999999999999</v>
+        <v>54.61</v>
       </c>
       <c r="AE10">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="AF10">
-        <v>-60.93</v>
+        <v>25.92</v>
       </c>
       <c r="AG10">
-        <v>77.65000000000001</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="AH10">
-        <v>75.51000000000001</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="AI10">
-        <v>74.97</v>
+        <v>80.34</v>
       </c>
       <c r="AJ10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AK10">
-        <v>15.26</v>
+        <v>20.13</v>
       </c>
     </row>
   </sheetData>
@@ -2083,7 +2071,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2123,7 +2111,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2141,1280 +2129,1260 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>68</v>
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-5.62</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-7.14</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-1.52</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-3.78</v>
+        <v>-5.68</v>
       </c>
       <c r="D8" s="6">
-        <v>-5.62</v>
+        <v>-6.05</v>
       </c>
       <c r="E8" s="7">
-        <v>-1.84</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-3.69</v>
+        <v>-14.51</v>
       </c>
       <c r="D9" s="6">
-        <v>-5.68</v>
+        <v>-16.14</v>
       </c>
       <c r="E9" s="7">
-        <v>-1.99</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-12.68</v>
+        <v>-8.76</v>
       </c>
       <c r="D10" s="6">
-        <v>-14.51</v>
+        <v>-8.91</v>
       </c>
       <c r="E10" s="7">
-        <v>-1.83</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-6.92</v>
+        <v>-6.54</v>
       </c>
       <c r="D11" s="6">
-        <v>-8.76</v>
+        <v>-7.42</v>
       </c>
       <c r="E11" s="7">
-        <v>-1.84</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-5.23</v>
+        <v>-5.8</v>
       </c>
       <c r="D12" s="6">
-        <v>-6.54</v>
+        <v>-7.56</v>
       </c>
       <c r="E12" s="7">
-        <v>-1.31</v>
+        <v>-1.76</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-3.71</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="D13" s="6">
-        <v>-5.8</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-2.09</v>
+        <v>-5.16</v>
+      </c>
+      <c r="E13" s="8">
+        <v>4.04</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-7.58</v>
+        <v>0.35</v>
       </c>
       <c r="D14" s="6">
-        <v>-9.199999999999999</v>
+        <v>-2.69</v>
       </c>
       <c r="E14" s="7">
-        <v>-1.62</v>
+        <v>-3.04</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>1.22</v>
+        <v>-5.42</v>
       </c>
       <c r="D15" s="6">
-        <v>0.35</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="E15" s="7">
-        <v>-0.87</v>
+        <v>-2.69</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-5.01</v>
+        <v>-2.69</v>
       </c>
       <c r="D16" s="6">
-        <v>-5.42</v>
+        <v>-3.31</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.41</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-3.04</v>
+        <v>0.23</v>
       </c>
       <c r="D17" s="6">
-        <v>-2.69</v>
-      </c>
-      <c r="E17" s="8">
-        <v>0.35</v>
+        <v>0.15</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>0.5</v>
+        <v>-4.25</v>
       </c>
       <c r="D18" s="6">
-        <v>0.23</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-0.27</v>
+        <v>-2.95</v>
+      </c>
+      <c r="E18" s="8">
+        <v>1.3</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-1.78</v>
+        <v>0.85</v>
       </c>
       <c r="D19" s="6">
-        <v>-4.25</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-2.47</v>
+        <v>1.02</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0.17</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>0.38</v>
+        <v>-1.64</v>
       </c>
       <c r="D20" s="6">
-        <v>0.85</v>
+        <v>-1.43</v>
       </c>
       <c r="E20" s="8">
-        <v>0.47</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-1.79</v>
+        <v>-2.74</v>
       </c>
       <c r="D21" s="6">
-        <v>-1.64</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0.15</v>
+        <v>-3.21</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-3.8</v>
+        <v>-2.83</v>
       </c>
       <c r="D22" s="6">
-        <v>-2.74</v>
+        <v>0.59</v>
       </c>
       <c r="E22" s="8">
-        <v>1.06</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>-0.53</v>
+        <v>-1.46</v>
       </c>
       <c r="D23" s="6">
-        <v>-2.83</v>
+        <v>-2.84</v>
       </c>
       <c r="E23" s="7">
-        <v>-2.3</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>-2.7</v>
+        <v>-1.62</v>
       </c>
       <c r="D24" s="6">
-        <v>-1.46</v>
-      </c>
-      <c r="E24" s="8">
-        <v>1.24</v>
+        <v>-3.64</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-2.02</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>-0.44</v>
+        <v>-26.65</v>
       </c>
       <c r="D25" s="6">
-        <v>-1.62</v>
+        <v>-27.44</v>
       </c>
       <c r="E25" s="7">
-        <v>-1.18</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>-25.68</v>
+        <v>31.28</v>
       </c>
       <c r="D26" s="6">
-        <v>-26.65</v>
+        <v>31.21</v>
       </c>
       <c r="E26" s="7">
-        <v>-0.97</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>39.41</v>
+        <v>40.51</v>
       </c>
       <c r="D27" s="6">
-        <v>31.28</v>
+        <v>39.91</v>
       </c>
       <c r="E27" s="7">
-        <v>-8.130000000000001</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>47.48</v>
+        <v>26.98</v>
       </c>
       <c r="D28" s="6">
-        <v>40.51</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-6.97</v>
+        <v>27.99</v>
+      </c>
+      <c r="E28" s="8">
+        <v>1.01</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>28.84</v>
+        <v>73.78</v>
       </c>
       <c r="D29" s="6">
-        <v>26.98</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-1.86</v>
+        <v>74.2</v>
+      </c>
+      <c r="E29" s="8">
+        <v>0.42</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>77.89</v>
+        <v>-29.41</v>
       </c>
       <c r="D30" s="6">
-        <v>73.78</v>
+        <v>-29.5</v>
       </c>
       <c r="E30" s="7">
-        <v>-4.11</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>-27.66</v>
+        <v>5.83</v>
       </c>
       <c r="D31" s="6">
-        <v>-29.41</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-1.75</v>
+        <v>9.07</v>
+      </c>
+      <c r="E31" s="8">
+        <v>3.24</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>11.92</v>
+        <v>-24.77</v>
       </c>
       <c r="D32" s="6">
-        <v>5.83</v>
+        <v>-25.26</v>
       </c>
       <c r="E32" s="7">
-        <v>-6.09</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>-24.39</v>
+        <v>-41.22</v>
       </c>
       <c r="D33" s="6">
-        <v>-24.77</v>
+        <v>-43</v>
       </c>
       <c r="E33" s="7">
-        <v>-0.38</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>-40.96</v>
+        <v>-2.98</v>
       </c>
       <c r="D34" s="6">
-        <v>-41.22</v>
+        <v>-4.75</v>
       </c>
       <c r="E34" s="7">
-        <v>-0.26</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-2.25</v>
+        <v>11.06</v>
       </c>
       <c r="D35" s="6">
-        <v>-2.98</v>
+        <v>10.9</v>
       </c>
       <c r="E35" s="7">
-        <v>-0.73</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>12.89</v>
+        <v>-4.05</v>
       </c>
       <c r="D36" s="6">
-        <v>11.06</v>
+        <v>-4.8</v>
       </c>
       <c r="E36" s="7">
-        <v>-1.83</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>-1.53</v>
+        <v>-4.69</v>
       </c>
       <c r="D37" s="6">
-        <v>-4.05</v>
+        <v>-5.82</v>
       </c>
       <c r="E37" s="7">
-        <v>-2.52</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>-4.51</v>
+        <v>-6.66</v>
       </c>
       <c r="D38" s="6">
-        <v>-4.69</v>
+        <v>-6.98</v>
       </c>
       <c r="E38" s="7">
-        <v>-0.18</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>-6.41</v>
+        <v>-3.67</v>
       </c>
       <c r="D39" s="6">
-        <v>-6.66</v>
+        <v>-6.17</v>
       </c>
       <c r="E39" s="7">
-        <v>-0.25</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>-2.46</v>
+        <v>6.05</v>
       </c>
       <c r="D40" s="6">
-        <v>-3.67</v>
+        <v>4.13</v>
       </c>
       <c r="E40" s="7">
-        <v>-1.21</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>7.24</v>
+        <v>-3.4</v>
       </c>
       <c r="D41" s="6">
-        <v>6.05</v>
+        <v>-4.8</v>
       </c>
       <c r="E41" s="7">
-        <v>-1.19</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="6">
-        <v>-3.62</v>
+        <v>-1.15</v>
       </c>
       <c r="D42" s="6">
-        <v>-3.4</v>
-      </c>
-      <c r="E42" s="8">
-        <v>0.22</v>
+        <v>-5.14</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-3.99</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C43" s="6">
-        <v>2.77</v>
+        <v>-31.48</v>
       </c>
       <c r="D43" s="6">
-        <v>-1.15</v>
+        <v>-32.27</v>
       </c>
       <c r="E43" s="7">
-        <v>-3.92</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-30.55</v>
+        <v>-6.53</v>
       </c>
       <c r="D44" s="6">
-        <v>-31.48</v>
+        <v>-6.91</v>
       </c>
       <c r="E44" s="7">
-        <v>-0.93</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-5.51</v>
+        <v>-18.48</v>
       </c>
       <c r="D45" s="6">
-        <v>-6.53</v>
+        <v>-19.41</v>
       </c>
       <c r="E45" s="7">
-        <v>-1.02</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-15.99</v>
+        <v>-10.66</v>
       </c>
       <c r="D46" s="6">
-        <v>-18.48</v>
+        <v>-10.69</v>
       </c>
       <c r="E46" s="7">
-        <v>-2.49</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-9.73</v>
+        <v>-17.41</v>
       </c>
       <c r="D47" s="6">
-        <v>-10.66</v>
+        <v>-18.03</v>
       </c>
       <c r="E47" s="7">
-        <v>-0.93</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-17.54</v>
+        <v>-30.04</v>
       </c>
       <c r="D48" s="6">
-        <v>-17.41</v>
-      </c>
-      <c r="E48" s="8">
-        <v>0.13</v>
+        <v>-30.87</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-0.83</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-29.17</v>
+        <v>-19.92</v>
       </c>
       <c r="D49" s="6">
-        <v>-30.04</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-0.87</v>
+        <v>-17.82</v>
+      </c>
+      <c r="E49" s="8">
+        <v>2.1</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-19.08</v>
+        <v>-31.54</v>
       </c>
       <c r="D50" s="6">
-        <v>-19.92</v>
+        <v>-32.02</v>
       </c>
       <c r="E50" s="7">
-        <v>-0.84</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="6">
-        <v>-30.78</v>
+        <v>-49.82</v>
       </c>
       <c r="D51" s="6">
-        <v>-31.54</v>
+        <v>-51.39</v>
       </c>
       <c r="E51" s="7">
-        <v>-0.76</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C52" s="6">
-        <v>-49.27</v>
+        <v>1303.8</v>
       </c>
       <c r="D52" s="6">
-        <v>-49.82</v>
+        <v>1288.7</v>
       </c>
       <c r="E52" s="7">
-        <v>-0.55</v>
+        <v>-15.1</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>1321.4</v>
+        <v>3002.5</v>
       </c>
       <c r="D53" s="6">
-        <v>1303.8</v>
+        <v>2990.3</v>
       </c>
       <c r="E53" s="7">
-        <v>-17.6</v>
+        <v>-12.2</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>3035.1</v>
+        <v>1308</v>
       </c>
       <c r="D54" s="6">
-        <v>3002.5</v>
+        <v>1293</v>
       </c>
       <c r="E54" s="7">
-        <v>-32.6</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>1348</v>
+        <v>1682.4</v>
       </c>
       <c r="D55" s="6">
-        <v>1308</v>
+        <v>1681.9</v>
       </c>
       <c r="E55" s="7">
-        <v>-40</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>1700</v>
+        <v>205.58</v>
       </c>
       <c r="D56" s="6">
-        <v>1682.4</v>
+        <v>204.02</v>
       </c>
       <c r="E56" s="7">
-        <v>-17.6</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>205.25</v>
+        <v>412.4</v>
       </c>
       <c r="D57" s="6">
-        <v>205.58</v>
-      </c>
-      <c r="E57" s="8">
-        <v>0.33</v>
+        <v>407.5</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-4.9</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>417.5</v>
+        <v>647.3</v>
       </c>
       <c r="D58" s="6">
-        <v>412.4</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-5.1</v>
+        <v>664.25</v>
+      </c>
+      <c r="E58" s="8">
+        <v>16.95</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="6">
-        <v>654.05</v>
+        <v>190.04</v>
       </c>
       <c r="D59" s="6">
-        <v>647.3</v>
+        <v>188.72</v>
       </c>
       <c r="E59" s="7">
-        <v>-6.75</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C60" s="6">
-        <v>192.16</v>
+        <v>75.7</v>
       </c>
       <c r="D60" s="6">
-        <v>190.04</v>
+        <v>73.34</v>
       </c>
       <c r="E60" s="7">
-        <v>-2.12</v>
+        <v>-2.36</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C61" s="6">
-        <v>76.53</v>
+        <v>36.24</v>
       </c>
       <c r="D61" s="6">
-        <v>75.7</v>
+        <v>33.26</v>
       </c>
       <c r="E61" s="7">
-        <v>-0.83</v>
+        <v>-2.98</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C62" s="6">
-        <v>40.03</v>
+        <v>46.03</v>
       </c>
       <c r="D62" s="6">
-        <v>36.24</v>
+        <v>44.55</v>
       </c>
       <c r="E62" s="7">
-        <v>-3.79</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C63" s="6">
-        <v>49.88</v>
+        <v>32.85</v>
       </c>
       <c r="D63" s="6">
-        <v>46.03</v>
+        <v>31</v>
       </c>
       <c r="E63" s="7">
-        <v>-3.85</v>
+        <v>-1.85</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C64" s="6">
-        <v>38.31</v>
+        <v>39.17</v>
       </c>
       <c r="D64" s="6">
-        <v>32.85</v>
+        <v>39.07</v>
       </c>
       <c r="E64" s="7">
-        <v>-5.46</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C65" s="6">
-        <v>42.58</v>
+        <v>39.47</v>
       </c>
       <c r="D65" s="6">
-        <v>39.17</v>
+        <v>37.36</v>
       </c>
       <c r="E65" s="7">
-        <v>-3.41</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="6">
-        <v>37.17</v>
+        <v>37.57</v>
       </c>
       <c r="D66" s="6">
-        <v>39.47</v>
-      </c>
-      <c r="E66" s="8">
-        <v>2.3</v>
+        <v>34.8</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-2.77</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="6">
-        <v>40.59</v>
+        <v>36.57</v>
       </c>
       <c r="D67" s="6">
-        <v>37.57</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-3.02</v>
+        <v>47.29</v>
+      </c>
+      <c r="E67" s="8">
+        <v>10.72</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="6">
-        <v>39.2</v>
+        <v>47.43</v>
       </c>
       <c r="D68" s="6">
-        <v>36.57</v>
+        <v>44.86</v>
       </c>
       <c r="E68" s="7">
-        <v>-2.63</v>
+        <v>-2.57</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="6">
-        <v>51.85</v>
+        <v>39.32</v>
       </c>
       <c r="D69" s="6">
-        <v>47.43</v>
+        <v>30.83</v>
       </c>
       <c r="E69" s="7">
-        <v>-4.42</v>
+        <v>-8.49</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C70" s="6">
-        <v>43.2</v>
+        <v>-43.12</v>
       </c>
       <c r="D70" s="6">
-        <v>39.32</v>
-      </c>
-      <c r="E70" s="7">
-        <v>-3.88</v>
+        <v>-35.63</v>
+      </c>
+      <c r="E70" s="8">
+        <v>7.49</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C71" s="6">
-        <v>-51.91</v>
+        <v>-33.44</v>
       </c>
       <c r="D71" s="6">
-        <v>-43.12</v>
+        <v>-12.33</v>
       </c>
       <c r="E71" s="8">
-        <v>8.789999999999999</v>
+        <v>21.11</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C72" s="6">
-        <v>56.76</v>
+        <v>-58.39</v>
       </c>
       <c r="D72" s="6">
-        <v>-33.44</v>
-      </c>
-      <c r="E72" s="7">
-        <v>-90.2</v>
+        <v>-38.47</v>
+      </c>
+      <c r="E72" s="8">
+        <v>19.92</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C73" s="6">
-        <v>-55.84</v>
+        <v>-42.38</v>
       </c>
       <c r="D73" s="6">
-        <v>-58.39</v>
+        <v>-46.6</v>
       </c>
       <c r="E73" s="7">
-        <v>-2.55</v>
+        <v>-4.22</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C74" s="6">
-        <v>-10.95</v>
+        <v>2.85</v>
       </c>
       <c r="D74" s="6">
-        <v>-42.38</v>
+        <v>-42.39</v>
       </c>
       <c r="E74" s="7">
-        <v>-31.43</v>
+        <v>-45.24</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="6">
-        <v>-31.9</v>
+        <v>-13.23</v>
       </c>
       <c r="D75" s="6">
-        <v>2.85</v>
-      </c>
-      <c r="E75" s="8">
-        <v>34.75</v>
+        <v>-24.39</v>
+      </c>
+      <c r="E75" s="7">
+        <v>-11.16</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="6">
-        <v>-39.79</v>
+        <v>-58.32</v>
       </c>
       <c r="D76" s="6">
-        <v>-13.23</v>
+        <v>959.14</v>
       </c>
       <c r="E76" s="8">
-        <v>26.56</v>
+        <v>1017.46</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="6">
-        <v>-47.76</v>
+        <v>-61.85</v>
       </c>
       <c r="D77" s="6">
-        <v>-58.32</v>
-      </c>
-      <c r="E77" s="7">
-        <v>-10.56</v>
+        <v>-53.86</v>
+      </c>
+      <c r="E77" s="8">
+        <v>7.99</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="6">
-        <v>13.44</v>
+        <v>-60.93</v>
       </c>
       <c r="D78" s="6">
-        <v>-61.85</v>
-      </c>
-      <c r="E78" s="7">
-        <v>-75.29000000000001</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>-2.39</v>
-      </c>
-      <c r="D79" s="6">
-        <v>-60.93</v>
-      </c>
-      <c r="E79" s="7">
-        <v>-58.54</v>
+        <v>25.92</v>
+      </c>
+      <c r="E78" s="8">
+        <v>86.84999999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3438,28 +3406,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>72</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3473,16 +3441,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>39.4</v>
+        <v>38.1</v>
       </c>
       <c r="E2" s="11">
         <v>60</v>
       </c>
       <c r="F2" s="11">
-        <v>-6.8</v>
+        <v>-7.7</v>
       </c>
       <c r="G2" s="11">
-        <v>-1.1</v>
+        <v>-2.6</v>
       </c>
       <c r="H2" s="11">
         <v>55.4</v>
@@ -3619,31 +3587,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.6779999999999999</v>
+        <v>0.6751999999999999</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1963</v>
+        <v>0.2026</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1557</v>
+        <v>0.1596</v>
       </c>
       <c r="D2" s="14">
-        <v>0.0677</v>
+        <v>0.0668</v>
       </c>
       <c r="E2" s="14">
-        <v>0.0092</v>
+        <v>0.0157</v>
       </c>
       <c r="F2" s="14">
-        <v>-0.004</v>
+        <v>0.0002</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.07339999999999999</v>
+        <v>-0.07480000000000001</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.08699999999999999</v>
+        <v>-0.09119999999999999</v>
       </c>
       <c r="I2" s="14">
-        <v>-0.1036</v>
+        <v>-0.1007</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="66">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,28 +178,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -285,14 +264,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -325,13 +304,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -401,15 +380,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -924,10 +902,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1288.7</v>
+        <v>1301.1</v>
       </c>
       <c r="D2">
-        <v>-1.16</v>
+        <v>0.96</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -936,46 +914,46 @@
         <v>1247.38</v>
       </c>
       <c r="G2">
-        <v>-32.27</v>
+        <v>-31.62</v>
       </c>
       <c r="H2">
-        <v>3.31</v>
+        <v>4.31</v>
       </c>
       <c r="I2">
-        <v>-3.31</v>
+        <v>-1.78</v>
       </c>
       <c r="J2">
-        <v>-7.14</v>
+        <v>-4.26</v>
       </c>
       <c r="K2">
-        <v>-4.75</v>
+        <v>-3.78</v>
       </c>
       <c r="L2">
-        <v>-27.44</v>
+        <v>-26.59</v>
       </c>
       <c r="M2">
-        <v>-10.07</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P2">
-        <v>1311.04</v>
+        <v>1306.32</v>
       </c>
       <c r="Q2">
-        <v>1348.14</v>
+        <v>1346.5</v>
       </c>
       <c r="R2">
-        <v>1352.59</v>
+        <v>1352.44</v>
       </c>
       <c r="S2">
-        <v>1524.55</v>
+        <v>1521.7</v>
       </c>
       <c r="T2">
-        <v>-15.47</v>
+        <v>-14.5</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -990,34 +968,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>33.26</v>
+        <v>37.78</v>
       </c>
       <c r="Z2">
-        <v>-14.85</v>
+        <v>-16.1</v>
       </c>
       <c r="AA2">
-        <v>-6.6</v>
+        <v>-8.5</v>
       </c>
       <c r="AB2">
-        <v>-8.25</v>
+        <v>-7.6</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AE2">
-        <v>25.48</v>
+        <v>25.33</v>
       </c>
       <c r="AF2">
-        <v>-35.63</v>
+        <v>-50.21</v>
       </c>
       <c r="AG2">
-        <v>1406.67</v>
+        <v>1408.44</v>
       </c>
       <c r="AH2">
-        <v>1289.6</v>
+        <v>1284.55</v>
       </c>
       <c r="AI2">
         <v>1374.58</v>
@@ -1026,7 +1004,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>35.67</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1037,10 +1015,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2990.3</v>
+        <v>2994.9</v>
       </c>
       <c r="D3">
-        <v>-0.41</v>
+        <v>0.15</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1049,46 +1027,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-6.91</v>
+        <v>-6.76</v>
       </c>
       <c r="H3">
-        <v>70.09999999999999</v>
+        <v>70.36</v>
       </c>
       <c r="I3">
-        <v>0.15</v>
+        <v>1.01</v>
       </c>
       <c r="J3">
-        <v>-6.05</v>
+        <v>-4.85</v>
       </c>
       <c r="K3">
-        <v>10.9</v>
+        <v>10.27</v>
       </c>
       <c r="L3">
-        <v>31.21</v>
+        <v>31.32</v>
       </c>
       <c r="M3">
-        <v>15.96</v>
+        <v>15.99</v>
       </c>
       <c r="N3">
         <v>88</v>
       </c>
       <c r="O3">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="P3">
-        <v>3000.02</v>
+        <v>3006.02</v>
       </c>
       <c r="Q3">
-        <v>3018.19</v>
+        <v>3017.43</v>
       </c>
       <c r="R3">
-        <v>3052.37</v>
+        <v>3053.68</v>
       </c>
       <c r="S3">
-        <v>2475.75</v>
+        <v>2478.32</v>
       </c>
       <c r="T3">
-        <v>20.78</v>
+        <v>20.84</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1103,34 +1081,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>44.55</v>
+        <v>45.27</v>
       </c>
       <c r="Z3">
-        <v>-16.66</v>
+        <v>-16.81</v>
       </c>
       <c r="AA3">
-        <v>-11.67</v>
+        <v>-12.7</v>
       </c>
       <c r="AB3">
-        <v>-5</v>
+        <v>-4.12</v>
       </c>
       <c r="AC3">
-        <v>52.7</v>
+        <v>48.67</v>
       </c>
       <c r="AD3">
-        <v>57.34</v>
+        <v>56.76</v>
       </c>
       <c r="AE3">
-        <v>66.08</v>
+        <v>62.86</v>
       </c>
       <c r="AF3">
-        <v>-12.33</v>
+        <v>-33.31</v>
       </c>
       <c r="AG3">
-        <v>3069.01</v>
+        <v>3069.21</v>
       </c>
       <c r="AH3">
-        <v>2967.36</v>
+        <v>2965.65</v>
       </c>
       <c r="AI3">
         <v>2959.69</v>
@@ -1139,7 +1117,7 @@
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>22.66</v>
+        <v>23.39</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1150,10 +1128,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1293</v>
+        <v>1301.8</v>
       </c>
       <c r="D4">
-        <v>-1.15</v>
+        <v>0.68</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1162,46 +1140,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-19.41</v>
+        <v>-18.87</v>
       </c>
       <c r="H4">
-        <v>67.31</v>
+        <v>68.45</v>
       </c>
       <c r="I4">
-        <v>-2.95</v>
+        <v>-1.3</v>
       </c>
       <c r="J4">
-        <v>-16.14</v>
+        <v>-11.58</v>
       </c>
       <c r="K4">
-        <v>-4.8</v>
+        <v>-4.44</v>
       </c>
       <c r="L4">
-        <v>39.91</v>
+        <v>41.89</v>
       </c>
       <c r="M4">
-        <v>6.68</v>
+        <v>6.82</v>
       </c>
       <c r="N4">
         <v>77</v>
       </c>
       <c r="O4">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P4">
-        <v>1319.12</v>
+        <v>1315.68</v>
       </c>
       <c r="Q4">
-        <v>1361.65</v>
+        <v>1357.75</v>
       </c>
       <c r="R4">
-        <v>1455.09</v>
+        <v>1451.46</v>
       </c>
       <c r="S4">
-        <v>1163.54</v>
+        <v>1164.35</v>
       </c>
       <c r="T4">
-        <v>11.13</v>
+        <v>11.81</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1216,34 +1194,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>31</v>
+        <v>33.37</v>
       </c>
       <c r="Z4">
-        <v>-40.9</v>
+        <v>-41.24</v>
       </c>
       <c r="AA4">
-        <v>-36.18</v>
+        <v>-37.19</v>
       </c>
       <c r="AB4">
-        <v>-4.72</v>
+        <v>-4.05</v>
       </c>
       <c r="AC4">
-        <v>22.03</v>
+        <v>15.3</v>
       </c>
       <c r="AD4">
-        <v>35.87</v>
+        <v>27.8</v>
       </c>
       <c r="AE4">
-        <v>40.57</v>
+        <v>38.91</v>
       </c>
       <c r="AF4">
-        <v>-38.47</v>
+        <v>-49.84</v>
       </c>
       <c r="AG4">
-        <v>1422.54</v>
+        <v>1423.53</v>
       </c>
       <c r="AH4">
-        <v>1300.77</v>
+        <v>1291.97</v>
       </c>
       <c r="AI4">
         <v>1418.72</v>
@@ -1252,7 +1230,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>27.63</v>
+        <v>30.21</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1263,58 +1241,58 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1681.9</v>
+        <v>1696</v>
       </c>
       <c r="D5">
-        <v>-0.03</v>
+        <v>0.84</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
       </c>
       <c r="F5">
-        <v>1294.84</v>
+        <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-10.69</v>
+        <v>-9.94</v>
       </c>
       <c r="H5">
-        <v>29.89</v>
+        <v>30.65</v>
       </c>
       <c r="I5">
-        <v>1.02</v>
+        <v>2.29</v>
       </c>
       <c r="J5">
-        <v>-8.91</v>
+        <v>-6.78</v>
       </c>
       <c r="K5">
-        <v>-5.82</v>
+        <v>-4.69</v>
       </c>
       <c r="L5">
-        <v>27.99</v>
+        <v>30.98</v>
       </c>
       <c r="M5">
-        <v>20.26</v>
+        <v>20.45</v>
       </c>
       <c r="N5">
         <v>66</v>
       </c>
       <c r="O5">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="P5">
-        <v>1684.46</v>
+        <v>1692.06</v>
       </c>
       <c r="Q5">
-        <v>1705.24</v>
+        <v>1701.12</v>
       </c>
       <c r="R5">
-        <v>1776.19</v>
+        <v>1773.84</v>
       </c>
       <c r="S5">
-        <v>1588.85</v>
+        <v>1590.1</v>
       </c>
       <c r="T5">
-        <v>5.86</v>
+        <v>6.66</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1329,34 +1307,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>39.07</v>
+        <v>43.28</v>
       </c>
       <c r="Z5">
-        <v>-28.81</v>
+        <v>-26.44</v>
       </c>
       <c r="AA5">
-        <v>-30.56</v>
+        <v>-29.74</v>
       </c>
       <c r="AB5">
-        <v>1.75</v>
+        <v>3.3</v>
       </c>
       <c r="AC5">
         <v>83.16</v>
       </c>
       <c r="AD5">
-        <v>82.72</v>
+        <v>86.27</v>
       </c>
       <c r="AE5">
-        <v>34.65</v>
+        <v>33.47</v>
       </c>
       <c r="AF5">
-        <v>-46.6</v>
+        <v>-26.84</v>
       </c>
       <c r="AG5">
-        <v>1781.49</v>
+        <v>1769.16</v>
       </c>
       <c r="AH5">
-        <v>1629</v>
+        <v>1633.08</v>
       </c>
       <c r="AI5">
         <v>1761.08</v>
@@ -1365,7 +1343,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>36.09</v>
+        <v>32.79</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1376,37 +1354,37 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>204.02</v>
+        <v>204</v>
       </c>
       <c r="D6">
-        <v>-0.76</v>
+        <v>-0.01</v>
       </c>
       <c r="E6">
         <v>248.91</v>
       </c>
       <c r="F6">
-        <v>116.81</v>
+        <v>118.42</v>
       </c>
       <c r="G6">
-        <v>-18.03</v>
+        <v>-18.04</v>
       </c>
       <c r="H6">
-        <v>74.66</v>
+        <v>72.27</v>
       </c>
       <c r="I6">
-        <v>-1.43</v>
+        <v>-1.02</v>
       </c>
       <c r="J6">
-        <v>-7.42</v>
+        <v>-5.97</v>
       </c>
       <c r="K6">
-        <v>-6.98</v>
+        <v>-6.99</v>
       </c>
       <c r="L6">
-        <v>74.2</v>
+        <v>74.64</v>
       </c>
       <c r="M6">
-        <v>67.52</v>
+        <v>67.47</v>
       </c>
       <c r="N6">
         <v>99</v>
@@ -1415,19 +1393,19 @@
         <v>84</v>
       </c>
       <c r="P6">
-        <v>204.9</v>
+        <v>204.48</v>
       </c>
       <c r="Q6">
-        <v>208.94</v>
+        <v>208.53</v>
       </c>
       <c r="R6">
-        <v>217</v>
+        <v>216.67</v>
       </c>
       <c r="S6">
-        <v>179.6</v>
+        <v>179.83</v>
       </c>
       <c r="T6">
-        <v>13.6</v>
+        <v>13.44</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1442,43 +1420,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>37.36</v>
+        <v>37.33</v>
       </c>
       <c r="Z6">
-        <v>-3.52</v>
+        <v>-3.51</v>
       </c>
       <c r="AA6">
-        <v>-3.36</v>
+        <v>-3.39</v>
       </c>
       <c r="AB6">
-        <v>-0.16</v>
+        <v>-0.12</v>
       </c>
       <c r="AC6">
-        <v>20.78</v>
+        <v>27.81</v>
       </c>
       <c r="AD6">
-        <v>12.22</v>
+        <v>20.75</v>
       </c>
       <c r="AE6">
-        <v>4.94</v>
+        <v>4.78</v>
       </c>
       <c r="AF6">
-        <v>-42.39</v>
+        <v>-39.52</v>
       </c>
       <c r="AG6">
-        <v>215.12</v>
+        <v>214.88</v>
       </c>
       <c r="AH6">
-        <v>202.76</v>
+        <v>202.17</v>
       </c>
       <c r="AI6">
-        <v>218.98</v>
+        <v>218.48</v>
       </c>
       <c r="AJ6" t="s">
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>24.01</v>
+        <v>23.65</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1489,10 +1467,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>407.5</v>
+        <v>411</v>
       </c>
       <c r="D7">
-        <v>-1.19</v>
+        <v>0.86</v>
       </c>
       <c r="E7">
         <v>589.48</v>
@@ -1501,46 +1479,46 @@
         <v>393.4</v>
       </c>
       <c r="G7">
-        <v>-30.87</v>
+        <v>-30.28</v>
       </c>
       <c r="H7">
-        <v>3.58</v>
+        <v>4.47</v>
       </c>
       <c r="I7">
-        <v>-3.21</v>
+        <v>-2</v>
       </c>
       <c r="J7">
-        <v>-7.56</v>
+        <v>-4.6</v>
       </c>
       <c r="K7">
-        <v>-6.17</v>
+        <v>-5.34</v>
       </c>
       <c r="L7">
-        <v>-29.5</v>
+        <v>-28.55</v>
       </c>
       <c r="M7">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="N7">
         <v>23</v>
       </c>
       <c r="O7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P7">
-        <v>414.41</v>
+        <v>412.73</v>
       </c>
       <c r="Q7">
-        <v>427.54</v>
+        <v>426.91</v>
       </c>
       <c r="R7">
-        <v>427.87</v>
+        <v>427.94</v>
       </c>
       <c r="S7">
-        <v>477.52</v>
+        <v>476.76</v>
       </c>
       <c r="T7">
-        <v>-14.66</v>
+        <v>-13.79</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1555,34 +1533,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>34.8</v>
+        <v>38.3</v>
       </c>
       <c r="Z7">
-        <v>-4.94</v>
+        <v>-5.39</v>
       </c>
       <c r="AA7">
-        <v>-2.06</v>
+        <v>-2.73</v>
       </c>
       <c r="AB7">
-        <v>-2.88</v>
+        <v>-2.66</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE7">
-        <v>9.15</v>
+        <v>9.02</v>
       </c>
       <c r="AF7">
-        <v>-24.39</v>
+        <v>27.86</v>
       </c>
       <c r="AG7">
-        <v>447.79</v>
+        <v>448.42</v>
       </c>
       <c r="AH7">
-        <v>407.29</v>
+        <v>405.41</v>
       </c>
       <c r="AI7">
         <v>436.39</v>
@@ -1591,7 +1569,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>35.15</v>
+        <v>36.58</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1602,10 +1580,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>664.25</v>
+        <v>657.65</v>
       </c>
       <c r="D8">
-        <v>2.62</v>
+        <v>-0.99</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1614,46 +1592,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-17.82</v>
+        <v>-18.63</v>
       </c>
       <c r="H8">
-        <v>42.01</v>
+        <v>40.6</v>
       </c>
       <c r="I8">
-        <v>0.59</v>
+        <v>0.4</v>
       </c>
       <c r="J8">
-        <v>-5.16</v>
+        <v>-3.51</v>
       </c>
       <c r="K8">
-        <v>4.13</v>
+        <v>0.78</v>
       </c>
       <c r="L8">
-        <v>9.07</v>
+        <v>8.32</v>
       </c>
       <c r="M8">
-        <v>-9.119999999999999</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="N8">
         <v>55</v>
       </c>
       <c r="O8">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="P8">
-        <v>653.51</v>
+        <v>654.03</v>
       </c>
       <c r="Q8">
-        <v>657.29</v>
+        <v>657.04</v>
       </c>
       <c r="R8">
-        <v>693.47</v>
+        <v>692.0599999999999</v>
       </c>
       <c r="S8">
-        <v>613.13</v>
+        <v>613.26</v>
       </c>
       <c r="T8">
-        <v>8.34</v>
+        <v>7.24</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1668,34 +1646,34 @@
         <v>2</v>
       </c>
       <c r="Y8">
-        <v>47.29</v>
+        <v>44.16</v>
       </c>
       <c r="Z8">
-        <v>-10.27</v>
+        <v>-9.57</v>
       </c>
       <c r="AA8">
-        <v>-11.7</v>
+        <v>-11.27</v>
       </c>
       <c r="AB8">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="AC8">
-        <v>45.01</v>
+        <v>63.52</v>
       </c>
       <c r="AD8">
-        <v>41.27</v>
+        <v>46.82</v>
       </c>
       <c r="AE8">
-        <v>17.73</v>
+        <v>17.37</v>
       </c>
       <c r="AF8">
-        <v>959.14</v>
+        <v>-40.76</v>
       </c>
       <c r="AG8">
-        <v>670.8099999999999</v>
+        <v>670.34</v>
       </c>
       <c r="AH8">
-        <v>643.77</v>
+        <v>643.75</v>
       </c>
       <c r="AI8">
         <v>698.3200000000001</v>
@@ -1704,7 +1682,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>29.39</v>
+        <v>30.23</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1715,10 +1693,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>188.72</v>
+        <v>188.64</v>
       </c>
       <c r="D9">
-        <v>-0.6899999999999999</v>
+        <v>-0.04</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1727,22 +1705,22 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-32.02</v>
+        <v>-32.05</v>
       </c>
       <c r="H9">
-        <v>9.529999999999999</v>
+        <v>9.48</v>
       </c>
       <c r="I9">
-        <v>-2.84</v>
+        <v>-1.81</v>
       </c>
       <c r="J9">
-        <v>-2.69</v>
+        <v>-0.66</v>
       </c>
       <c r="K9">
-        <v>-4.8</v>
+        <v>-3.33</v>
       </c>
       <c r="L9">
-        <v>-25.26</v>
+        <v>-24.51</v>
       </c>
       <c r="M9">
         <v>-7.48</v>
@@ -1751,22 +1729,22 @@
         <v>45</v>
       </c>
       <c r="O9">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="P9">
-        <v>191.04</v>
+        <v>190.34</v>
       </c>
       <c r="Q9">
-        <v>191.2</v>
+        <v>191.26</v>
       </c>
       <c r="R9">
-        <v>189.21</v>
+        <v>189.24</v>
       </c>
       <c r="S9">
-        <v>208.14</v>
+        <v>207.71</v>
       </c>
       <c r="T9">
-        <v>-9.33</v>
+        <v>-9.18</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1781,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>44.86</v>
+        <v>44.7</v>
       </c>
       <c r="Z9">
-        <v>0.58</v>
+        <v>0.29</v>
       </c>
       <c r="AA9">
-        <v>1.06</v>
+        <v>0.91</v>
       </c>
       <c r="AB9">
-        <v>-0.48</v>
+        <v>-0.61</v>
       </c>
       <c r="AC9">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>18.75</v>
+        <v>8.77</v>
       </c>
       <c r="AE9">
-        <v>4.52</v>
+        <v>4.48</v>
       </c>
       <c r="AF9">
-        <v>-53.86</v>
+        <v>28.21</v>
       </c>
       <c r="AG9">
-        <v>197.86</v>
+        <v>197.79</v>
       </c>
       <c r="AH9">
-        <v>184.55</v>
+        <v>184.73</v>
       </c>
       <c r="AI9">
         <v>197.85</v>
@@ -1817,7 +1795,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>32.38</v>
+        <v>28.91</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1828,10 +1806,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>73.34</v>
+        <v>75.5</v>
       </c>
       <c r="D10">
-        <v>-3.12</v>
+        <v>2.95</v>
       </c>
       <c r="E10">
         <v>150.86</v>
@@ -1840,46 +1818,46 @@
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-51.39</v>
+        <v>-49.95</v>
       </c>
       <c r="H10">
-        <v>23.72</v>
+        <v>27.36</v>
       </c>
       <c r="I10">
-        <v>-3.64</v>
+        <v>-1.14</v>
       </c>
       <c r="J10">
-        <v>-8.109999999999999</v>
+        <v>-0.68</v>
       </c>
       <c r="K10">
-        <v>-5.14</v>
+        <v>-1.59</v>
       </c>
       <c r="L10">
-        <v>-43</v>
+        <v>-39.83</v>
       </c>
       <c r="M10">
-        <v>0.02</v>
+        <v>0.61</v>
       </c>
       <c r="N10">
         <v>12</v>
       </c>
       <c r="O10">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="P10">
-        <v>75.69</v>
+        <v>75.52</v>
       </c>
       <c r="Q10">
-        <v>76.45</v>
+        <v>76.44</v>
       </c>
       <c r="R10">
-        <v>79.09</v>
+        <v>79.03</v>
       </c>
       <c r="S10">
-        <v>81.84</v>
+        <v>81.76000000000001</v>
       </c>
       <c r="T10">
-        <v>-10.39</v>
+        <v>-7.65</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1894,34 +1872,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>30.83</v>
+        <v>42.97</v>
       </c>
       <c r="Z10">
-        <v>-1.06</v>
+        <v>-1.03</v>
       </c>
       <c r="AA10">
-        <v>-0.95</v>
+        <v>-0.96</v>
       </c>
       <c r="AB10">
-        <v>-0.12</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AC10">
-        <v>32.03</v>
+        <v>35.16</v>
       </c>
       <c r="AD10">
-        <v>54.61</v>
+        <v>41.77</v>
       </c>
       <c r="AE10">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="AF10">
-        <v>25.92</v>
+        <v>-3.68</v>
       </c>
       <c r="AG10">
-        <v>78.23999999999999</v>
+        <v>78.25</v>
       </c>
       <c r="AH10">
-        <v>74.65000000000001</v>
+        <v>74.62</v>
       </c>
       <c r="AI10">
         <v>80.34</v>
@@ -1930,7 +1908,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>20.13</v>
+        <v>24.12</v>
       </c>
     </row>
   </sheetData>
@@ -2091,47 +2069,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -2139,1244 +2082,1244 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>64</v>
+      <c r="B6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-5.62</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-7.14</v>
       </c>
-      <c r="E7" s="7">
-        <v>-1.52</v>
+      <c r="D7" s="5">
+        <v>-4.26</v>
+      </c>
+      <c r="E7" s="6">
+        <v>2.88</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-5.68</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-6.05</v>
       </c>
-      <c r="E8" s="7">
-        <v>-0.37</v>
+      <c r="D8" s="5">
+        <v>-4.85</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1.2</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-14.51</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-16.14</v>
       </c>
-      <c r="E9" s="7">
-        <v>-1.63</v>
+      <c r="D9" s="5">
+        <v>-11.58</v>
+      </c>
+      <c r="E9" s="6">
+        <v>4.56</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-8.76</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-8.91</v>
       </c>
-      <c r="E10" s="7">
-        <v>-0.15</v>
+      <c r="D10" s="5">
+        <v>-6.78</v>
+      </c>
+      <c r="E10" s="6">
+        <v>2.13</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-6.54</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-7.42</v>
       </c>
-      <c r="E11" s="7">
-        <v>-0.88</v>
+      <c r="D11" s="5">
+        <v>-5.97</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1.45</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
-        <v>-5.8</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>-7.56</v>
       </c>
-      <c r="E12" s="7">
-        <v>-1.76</v>
+      <c r="D12" s="5">
+        <v>-4.6</v>
+      </c>
+      <c r="E12" s="6">
+        <v>2.96</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="6">
-        <v>-9.199999999999999</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>-5.16</v>
       </c>
-      <c r="E13" s="8">
-        <v>4.04</v>
+      <c r="D13" s="5">
+        <v>-3.51</v>
+      </c>
+      <c r="E13" s="6">
+        <v>1.65</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="6">
-        <v>0.35</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>-2.69</v>
       </c>
-      <c r="E14" s="7">
-        <v>-3.04</v>
+      <c r="D14" s="5">
+        <v>-0.66</v>
+      </c>
+      <c r="E14" s="6">
+        <v>2.03</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="6">
-        <v>-5.42</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>-8.109999999999999</v>
       </c>
-      <c r="E15" s="7">
-        <v>-2.69</v>
+      <c r="D15" s="5">
+        <v>-0.68</v>
+      </c>
+      <c r="E15" s="6">
+        <v>7.43</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="6">
-        <v>-2.69</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="5">
         <v>-3.31</v>
       </c>
-      <c r="E16" s="7">
-        <v>-0.62</v>
+      <c r="D16" s="5">
+        <v>-1.78</v>
+      </c>
+      <c r="E16" s="6">
+        <v>1.53</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="6">
-        <v>0.23</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C17" s="5">
         <v>0.15</v>
       </c>
-      <c r="E17" s="7">
+      <c r="D17" s="5">
+        <v>1.01</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-2.95</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-1.3</v>
+      </c>
+      <c r="E18" s="6">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>1.02</v>
+      </c>
+      <c r="D19" s="5">
+        <v>2.29</v>
+      </c>
+      <c r="E19" s="6">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-1.43</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-1.02</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-3.21</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-2</v>
+      </c>
+      <c r="E21" s="6">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5">
+        <v>0.59</v>
+      </c>
+      <c r="D22" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-2.84</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-1.81</v>
+      </c>
+      <c r="E23" s="6">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-3.64</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-1.14</v>
+      </c>
+      <c r="E24" s="6">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-27.44</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-26.59</v>
+      </c>
+      <c r="E25" s="6">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>31.21</v>
+      </c>
+      <c r="D26" s="5">
+        <v>31.32</v>
+      </c>
+      <c r="E26" s="6">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>39.91</v>
+      </c>
+      <c r="D27" s="5">
+        <v>41.89</v>
+      </c>
+      <c r="E27" s="6">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="5">
+        <v>27.99</v>
+      </c>
+      <c r="D28" s="5">
+        <v>30.98</v>
+      </c>
+      <c r="E28" s="6">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="5">
+        <v>74.2</v>
+      </c>
+      <c r="D29" s="5">
+        <v>74.64</v>
+      </c>
+      <c r="E29" s="6">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-29.5</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-28.55</v>
+      </c>
+      <c r="E30" s="6">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="5">
+        <v>9.07</v>
+      </c>
+      <c r="D31" s="5">
+        <v>8.32</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-25.26</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-24.51</v>
+      </c>
+      <c r="E32" s="6">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="5">
+        <v>-43</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-39.83</v>
+      </c>
+      <c r="E33" s="6">
+        <v>3.17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-4.75</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-3.78</v>
+      </c>
+      <c r="E34" s="6">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="5">
+        <v>10.9</v>
+      </c>
+      <c r="D35" s="5">
+        <v>10.27</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-4.8</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-4.44</v>
+      </c>
+      <c r="E36" s="6">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-5.82</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-4.69</v>
+      </c>
+      <c r="E37" s="6">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-6.98</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-6.99</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-6.17</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-5.34</v>
+      </c>
+      <c r="E39" s="6">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="5">
+        <v>4.13</v>
+      </c>
+      <c r="D40" s="5">
+        <v>0.78</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-3.35</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-4.8</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-3.33</v>
+      </c>
+      <c r="E41" s="6">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="5">
+        <v>-5.14</v>
+      </c>
+      <c r="D42" s="5">
+        <v>-1.59</v>
+      </c>
+      <c r="E42" s="6">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-32.27</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-31.62</v>
+      </c>
+      <c r="E43" s="6">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-6.91</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-6.76</v>
+      </c>
+      <c r="E44" s="6">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-19.41</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-18.87</v>
+      </c>
+      <c r="E45" s="6">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="5">
+        <v>-10.69</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-9.94</v>
+      </c>
+      <c r="E46" s="6">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="5">
+        <v>-18.03</v>
+      </c>
+      <c r="D47" s="5">
+        <v>-18.04</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="5">
+        <v>-30.87</v>
+      </c>
+      <c r="D48" s="5">
+        <v>-30.28</v>
+      </c>
+      <c r="E48" s="6">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="5">
+        <v>-17.82</v>
+      </c>
+      <c r="D49" s="5">
+        <v>-18.63</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="5">
+        <v>-32.02</v>
+      </c>
+      <c r="D50" s="5">
+        <v>-32.05</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="5">
+        <v>-51.39</v>
+      </c>
+      <c r="D51" s="5">
+        <v>-49.95</v>
+      </c>
+      <c r="E51" s="6">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="5">
+        <v>1288.7</v>
+      </c>
+      <c r="D52" s="5">
+        <v>1301.1</v>
+      </c>
+      <c r="E52" s="6">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="5">
+        <v>2990.3</v>
+      </c>
+      <c r="D53" s="5">
+        <v>2994.9</v>
+      </c>
+      <c r="E53" s="6">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="5">
+        <v>1293</v>
+      </c>
+      <c r="D54" s="5">
+        <v>1301.8</v>
+      </c>
+      <c r="E54" s="6">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="5">
+        <v>1681.9</v>
+      </c>
+      <c r="D55" s="5">
+        <v>1696</v>
+      </c>
+      <c r="E55" s="6">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="5">
+        <v>204.02</v>
+      </c>
+      <c r="D56" s="5">
+        <v>204</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="5">
+        <v>407.5</v>
+      </c>
+      <c r="D57" s="5">
+        <v>411</v>
+      </c>
+      <c r="E57" s="6">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="5">
+        <v>664.25</v>
+      </c>
+      <c r="D58" s="5">
+        <v>657.65</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-6.6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="5">
+        <v>188.72</v>
+      </c>
+      <c r="D59" s="5">
+        <v>188.64</v>
+      </c>
+      <c r="E59" s="7">
         <v>-0.08</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="5">
+        <v>73.34</v>
+      </c>
+      <c r="D60" s="5">
+        <v>75.5</v>
+      </c>
+      <c r="E60" s="6">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="5">
+        <v>33.26</v>
+      </c>
+      <c r="D61" s="5">
+        <v>37.78</v>
+      </c>
+      <c r="E61" s="6">
+        <v>4.52</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="5">
+        <v>44.55</v>
+      </c>
+      <c r="D62" s="5">
+        <v>45.27</v>
+      </c>
+      <c r="E62" s="6">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-4.25</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-2.95</v>
-      </c>
-      <c r="E18" s="8">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B63" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="5">
+        <v>31</v>
+      </c>
+      <c r="D63" s="5">
+        <v>33.37</v>
+      </c>
+      <c r="E63" s="6">
+        <v>2.37</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>0.85</v>
-      </c>
-      <c r="D19" s="6">
-        <v>1.02</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B64" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="5">
+        <v>39.07</v>
+      </c>
+      <c r="D64" s="5">
+        <v>43.28</v>
+      </c>
+      <c r="E64" s="6">
+        <v>4.21</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-1.64</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-1.43</v>
-      </c>
-      <c r="E20" s="8">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B65" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="5">
+        <v>37.36</v>
+      </c>
+      <c r="D65" s="5">
+        <v>37.33</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-2.74</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-3.21</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.47</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B66" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="5">
+        <v>34.8</v>
+      </c>
+      <c r="D66" s="5">
+        <v>38.3</v>
+      </c>
+      <c r="E66" s="6">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-2.83</v>
-      </c>
-      <c r="D22" s="6">
-        <v>0.59</v>
-      </c>
-      <c r="E22" s="8">
-        <v>3.42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B67" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="5">
+        <v>47.29</v>
+      </c>
+      <c r="D67" s="5">
+        <v>44.16</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-3.13</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-1.46</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-2.84</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-1.38</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B68" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="5">
+        <v>44.86</v>
+      </c>
+      <c r="D68" s="5">
+        <v>44.7</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-1.62</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-3.64</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-2.02</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B69" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="5">
+        <v>30.83</v>
+      </c>
+      <c r="D69" s="5">
+        <v>42.97</v>
+      </c>
+      <c r="E69" s="6">
+        <v>12.14</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-26.65</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-27.44</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B70" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="5">
+        <v>-35.63</v>
+      </c>
+      <c r="D70" s="5">
+        <v>-50.21</v>
+      </c>
+      <c r="E70" s="7">
+        <v>-14.58</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>31.28</v>
-      </c>
-      <c r="D26" s="6">
-        <v>31.21</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B71" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="5">
+        <v>-12.33</v>
+      </c>
+      <c r="D71" s="5">
+        <v>-33.31</v>
+      </c>
+      <c r="E71" s="7">
+        <v>-20.98</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>40.51</v>
-      </c>
-      <c r="D27" s="6">
-        <v>39.91</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B72" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="5">
+        <v>-38.47</v>
+      </c>
+      <c r="D72" s="5">
+        <v>-49.84</v>
+      </c>
+      <c r="E72" s="7">
+        <v>-11.37</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>26.98</v>
-      </c>
-      <c r="D28" s="6">
-        <v>27.99</v>
-      </c>
-      <c r="E28" s="8">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B73" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="5">
+        <v>-46.6</v>
+      </c>
+      <c r="D73" s="5">
+        <v>-26.84</v>
+      </c>
+      <c r="E73" s="6">
+        <v>19.76</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>73.78</v>
-      </c>
-      <c r="D29" s="6">
-        <v>74.2</v>
-      </c>
-      <c r="E29" s="8">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B74" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="5">
+        <v>-42.39</v>
+      </c>
+      <c r="D74" s="5">
+        <v>-39.52</v>
+      </c>
+      <c r="E74" s="6">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-29.41</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-29.5</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-0.09</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B75" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="5">
+        <v>-24.39</v>
+      </c>
+      <c r="D75" s="5">
+        <v>27.86</v>
+      </c>
+      <c r="E75" s="6">
+        <v>52.25</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>5.83</v>
-      </c>
-      <c r="D31" s="6">
-        <v>9.07</v>
-      </c>
-      <c r="E31" s="8">
-        <v>3.24</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B76" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="5">
+        <v>959.14</v>
+      </c>
+      <c r="D76" s="5">
+        <v>-40.76</v>
+      </c>
+      <c r="E76" s="7">
+        <v>-999.9</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-24.77</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-25.26</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-0.49</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B77" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="5">
+        <v>-53.86</v>
+      </c>
+      <c r="D77" s="5">
+        <v>28.21</v>
+      </c>
+      <c r="E77" s="6">
+        <v>82.06999999999999</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-41.22</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-43</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-1.78</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-2.98</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-4.75</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-1.77</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>11.06</v>
-      </c>
-      <c r="D35" s="6">
-        <v>10.9</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-0.16</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-4.05</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-4.8</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-0.75</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-4.69</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-5.82</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-1.13</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-6.66</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-6.98</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.32</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-3.67</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-6.17</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-2.5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>6.05</v>
-      </c>
-      <c r="D40" s="6">
-        <v>4.13</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-1.92</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-3.4</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-4.8</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-1.15</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-5.14</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-3.99</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-31.48</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-32.27</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-6.53</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-6.91</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-0.38</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-18.48</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-19.41</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-0.93</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-10.66</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-10.69</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-0.03</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-17.41</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-18.03</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-0.62</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-30.04</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-30.87</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-0.83</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-19.92</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-17.82</v>
-      </c>
-      <c r="E49" s="8">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-31.54</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-32.02</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-0.48</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-49.82</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-51.39</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-1.57</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="6">
-        <v>1303.8</v>
-      </c>
-      <c r="D52" s="6">
-        <v>1288.7</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-15.1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>3002.5</v>
-      </c>
-      <c r="D53" s="6">
-        <v>2990.3</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-12.2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>1308</v>
-      </c>
-      <c r="D54" s="6">
-        <v>1293</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-15</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>1682.4</v>
-      </c>
-      <c r="D55" s="6">
-        <v>1681.9</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>205.58</v>
-      </c>
-      <c r="D56" s="6">
-        <v>204.02</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-1.56</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>412.4</v>
-      </c>
-      <c r="D57" s="6">
-        <v>407.5</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-4.9</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>647.3</v>
-      </c>
-      <c r="D58" s="6">
-        <v>664.25</v>
-      </c>
-      <c r="E58" s="8">
-        <v>16.95</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>190.04</v>
-      </c>
-      <c r="D59" s="6">
-        <v>188.72</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-1.32</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="6">
-        <v>75.7</v>
-      </c>
-      <c r="D60" s="6">
-        <v>73.34</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-2.36</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="6">
-        <v>36.24</v>
-      </c>
-      <c r="D61" s="6">
-        <v>33.26</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-2.98</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="6">
-        <v>46.03</v>
-      </c>
-      <c r="D62" s="6">
-        <v>44.55</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-1.48</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="6">
-        <v>32.85</v>
-      </c>
-      <c r="D63" s="6">
+      <c r="B78" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E63" s="7">
-        <v>-1.85</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="6">
-        <v>39.17</v>
-      </c>
-      <c r="D64" s="6">
-        <v>39.07</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>39.47</v>
-      </c>
-      <c r="D65" s="6">
-        <v>37.36</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-2.11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>37.57</v>
-      </c>
-      <c r="D66" s="6">
-        <v>34.8</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-2.77</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>36.57</v>
-      </c>
-      <c r="D67" s="6">
-        <v>47.29</v>
-      </c>
-      <c r="E67" s="8">
-        <v>10.72</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>47.43</v>
-      </c>
-      <c r="D68" s="6">
-        <v>44.86</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-2.57</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="6">
-        <v>39.32</v>
-      </c>
-      <c r="D69" s="6">
-        <v>30.83</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-8.49</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="6">
-        <v>-43.12</v>
-      </c>
-      <c r="D70" s="6">
-        <v>-35.63</v>
-      </c>
-      <c r="E70" s="8">
-        <v>7.49</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="6">
-        <v>-33.44</v>
-      </c>
-      <c r="D71" s="6">
-        <v>-12.33</v>
-      </c>
-      <c r="E71" s="8">
-        <v>21.11</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="6">
-        <v>-58.39</v>
-      </c>
-      <c r="D72" s="6">
-        <v>-38.47</v>
-      </c>
-      <c r="E72" s="8">
-        <v>19.92</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="6">
-        <v>-42.38</v>
-      </c>
-      <c r="D73" s="6">
-        <v>-46.6</v>
-      </c>
-      <c r="E73" s="7">
-        <v>-4.22</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="6">
-        <v>2.85</v>
-      </c>
-      <c r="D74" s="6">
-        <v>-42.39</v>
-      </c>
-      <c r="E74" s="7">
-        <v>-45.24</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="6">
-        <v>-13.23</v>
-      </c>
-      <c r="D75" s="6">
-        <v>-24.39</v>
-      </c>
-      <c r="E75" s="7">
-        <v>-11.16</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>-58.32</v>
-      </c>
-      <c r="D76" s="6">
-        <v>959.14</v>
-      </c>
-      <c r="E76" s="8">
-        <v>1017.46</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>-61.85</v>
-      </c>
-      <c r="D77" s="6">
-        <v>-53.86</v>
-      </c>
-      <c r="E77" s="8">
-        <v>7.99</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>-60.93</v>
-      </c>
-      <c r="D78" s="6">
+      <c r="C78" s="5">
         <v>25.92</v>
       </c>
-      <c r="E78" s="8">
-        <v>86.84999999999999</v>
+      <c r="D78" s="5">
+        <v>-3.68</v>
+      </c>
+      <c r="E78" s="7">
+        <v>-29.6</v>
       </c>
     </row>
   </sheetData>
@@ -3402,60 +3345,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>72</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>56.16</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
-        <v>38.1</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>40.8</v>
+      </c>
+      <c r="E2" s="10">
         <v>60</v>
       </c>
-      <c r="F2" s="11">
-        <v>-7.7</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-2.6</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-4.8</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-2.1</v>
+      </c>
+      <c r="H2" s="10">
         <v>55.4</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -3557,61 +3500,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>0.6751999999999999</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.2026</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1596</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.0668</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.0157</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.0002</v>
-      </c>
-      <c r="G2" s="14">
+      <c r="A2" s="13">
+        <v>0.6747</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.2045</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.1599</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.0682</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.0174</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0.0061</v>
+      </c>
+      <c r="G2" s="13">
         <v>-0.07480000000000001</v>
       </c>
-      <c r="H2" s="14">
-        <v>-0.09119999999999999</v>
-      </c>
-      <c r="I2" s="14">
-        <v>-0.1007</v>
+      <c r="H2" s="13">
+        <v>-0.09300000000000001</v>
+      </c>
+      <c r="I2" s="13">
+        <v>-0.0989</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,7 +178,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>43.6 → 56.2</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>43.6</t>
+  </si>
+  <si>
+    <t>56.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -380,17 +407,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -902,10 +930,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1301.1</v>
+        <v>1300.9</v>
       </c>
       <c r="D2">
-        <v>0.96</v>
+        <v>-0.5</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -914,46 +942,46 @@
         <v>1247.38</v>
       </c>
       <c r="G2">
-        <v>-31.62</v>
+        <v>-31.63</v>
       </c>
       <c r="H2">
-        <v>4.31</v>
+        <v>4.29</v>
       </c>
       <c r="I2">
-        <v>-1.78</v>
+        <v>-1.19</v>
       </c>
       <c r="J2">
-        <v>-4.26</v>
+        <v>-2.98</v>
       </c>
       <c r="K2">
-        <v>-3.78</v>
+        <v>-7.37</v>
       </c>
       <c r="L2">
-        <v>-26.59</v>
+        <v>-29.64</v>
       </c>
       <c r="M2">
-        <v>-9.890000000000001</v>
+        <v>-9.81</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="P2">
-        <v>1306.32</v>
+        <v>1300.38</v>
       </c>
       <c r="Q2">
-        <v>1346.5</v>
+        <v>1341.96</v>
       </c>
       <c r="R2">
-        <v>1352.44</v>
+        <v>1351.95</v>
       </c>
       <c r="S2">
-        <v>1521.7</v>
+        <v>1516.33</v>
       </c>
       <c r="T2">
-        <v>-14.5</v>
+        <v>-14.21</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -968,34 +996,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>37.78</v>
+        <v>38.47</v>
       </c>
       <c r="Z2">
-        <v>-16.1</v>
+        <v>-16.95</v>
       </c>
       <c r="AA2">
-        <v>-8.5</v>
+        <v>-11.45</v>
       </c>
       <c r="AB2">
-        <v>-7.6</v>
+        <v>-5.49</v>
       </c>
       <c r="AC2">
-        <v>6.09</v>
+        <v>23.21</v>
       </c>
       <c r="AD2">
-        <v>2.03</v>
+        <v>15.02</v>
       </c>
       <c r="AE2">
-        <v>25.33</v>
+        <v>24.59</v>
       </c>
       <c r="AF2">
-        <v>-50.21</v>
+        <v>-54.73</v>
       </c>
       <c r="AG2">
-        <v>1408.44</v>
+        <v>1408.86</v>
       </c>
       <c r="AH2">
-        <v>1284.55</v>
+        <v>1275.06</v>
       </c>
       <c r="AI2">
         <v>1374.58</v>
@@ -1004,7 +1032,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>38.67</v>
+        <v>37.77</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1015,10 +1043,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2994.9</v>
+        <v>2998.6</v>
       </c>
       <c r="D3">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1027,46 +1055,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-6.76</v>
+        <v>-6.65</v>
       </c>
       <c r="H3">
-        <v>70.36</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="I3">
-        <v>1.01</v>
+        <v>-0.29</v>
       </c>
       <c r="J3">
-        <v>-4.85</v>
+        <v>-0.92</v>
       </c>
       <c r="K3">
-        <v>10.27</v>
+        <v>1.03</v>
       </c>
       <c r="L3">
-        <v>31.32</v>
+        <v>25.6</v>
       </c>
       <c r="M3">
-        <v>15.99</v>
+        <v>15.89</v>
       </c>
       <c r="N3">
         <v>88</v>
       </c>
       <c r="O3">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="P3">
-        <v>3006.02</v>
+        <v>2996.66</v>
       </c>
       <c r="Q3">
-        <v>3017.43</v>
+        <v>3014.06</v>
       </c>
       <c r="R3">
-        <v>3053.68</v>
+        <v>3057.01</v>
       </c>
       <c r="S3">
-        <v>2478.32</v>
+        <v>2483.88</v>
       </c>
       <c r="T3">
-        <v>20.84</v>
+        <v>20.72</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1081,34 +1109,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>45.27</v>
+        <v>45.89</v>
       </c>
       <c r="Z3">
-        <v>-16.81</v>
+        <v>-16.07</v>
       </c>
       <c r="AA3">
-        <v>-12.7</v>
+        <v>-13.99</v>
       </c>
       <c r="AB3">
-        <v>-4.12</v>
+        <v>-2.08</v>
       </c>
       <c r="AC3">
-        <v>48.67</v>
+        <v>55.11</v>
       </c>
       <c r="AD3">
-        <v>56.76</v>
+        <v>50.99</v>
       </c>
       <c r="AE3">
-        <v>62.86</v>
+        <v>59.41</v>
       </c>
       <c r="AF3">
-        <v>-33.31</v>
+        <v>-18.42</v>
       </c>
       <c r="AG3">
-        <v>3069.21</v>
+        <v>3066.04</v>
       </c>
       <c r="AH3">
-        <v>2965.65</v>
+        <v>2962.08</v>
       </c>
       <c r="AI3">
         <v>2959.69</v>
@@ -1117,7 +1145,7 @@
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>23.39</v>
+        <v>24.05</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1128,10 +1156,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1301.8</v>
+        <v>1308</v>
       </c>
       <c r="D4">
-        <v>0.68</v>
+        <v>-0.91</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1140,46 +1168,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-18.87</v>
+        <v>-18.48</v>
       </c>
       <c r="H4">
-        <v>68.45</v>
+        <v>69.25</v>
       </c>
       <c r="I4">
-        <v>-1.3</v>
+        <v>-1.48</v>
       </c>
       <c r="J4">
-        <v>-11.58</v>
+        <v>-6.24</v>
       </c>
       <c r="K4">
-        <v>-4.44</v>
+        <v>-10.25</v>
       </c>
       <c r="L4">
-        <v>41.89</v>
+        <v>34.37</v>
       </c>
       <c r="M4">
-        <v>6.82</v>
+        <v>6.61</v>
       </c>
       <c r="N4">
         <v>77</v>
       </c>
       <c r="O4">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="P4">
-        <v>1315.68</v>
+        <v>1306.16</v>
       </c>
       <c r="Q4">
-        <v>1357.75</v>
+        <v>1349.41</v>
       </c>
       <c r="R4">
-        <v>1451.46</v>
+        <v>1445.22</v>
       </c>
       <c r="S4">
-        <v>1164.35</v>
+        <v>1166.53</v>
       </c>
       <c r="T4">
-        <v>11.81</v>
+        <v>12.13</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1194,34 +1222,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>33.37</v>
+        <v>36.28</v>
       </c>
       <c r="Z4">
-        <v>-41.24</v>
+        <v>-38.8</v>
       </c>
       <c r="AA4">
-        <v>-37.19</v>
+        <v>-37.9</v>
       </c>
       <c r="AB4">
-        <v>-4.05</v>
+        <v>-0.9</v>
       </c>
       <c r="AC4">
-        <v>15.3</v>
+        <v>57.59</v>
       </c>
       <c r="AD4">
-        <v>27.8</v>
+        <v>36.38</v>
       </c>
       <c r="AE4">
-        <v>38.91</v>
+        <v>36.65</v>
       </c>
       <c r="AF4">
-        <v>-49.84</v>
+        <v>-59.02</v>
       </c>
       <c r="AG4">
-        <v>1423.53</v>
+        <v>1414.15</v>
       </c>
       <c r="AH4">
-        <v>1291.97</v>
+        <v>1284.67</v>
       </c>
       <c r="AI4">
         <v>1418.72</v>
@@ -1230,7 +1258,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>30.21</v>
+        <v>30.35</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1241,10 +1269,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1696</v>
+        <v>1672.1</v>
       </c>
       <c r="D5">
-        <v>0.84</v>
+        <v>-1.64</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1253,46 +1281,46 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-9.94</v>
+        <v>-11.21</v>
       </c>
       <c r="H5">
-        <v>30.65</v>
+        <v>28.81</v>
       </c>
       <c r="I5">
-        <v>2.29</v>
+        <v>-1.64</v>
       </c>
       <c r="J5">
-        <v>-6.78</v>
+        <v>-5.44</v>
       </c>
       <c r="K5">
-        <v>-4.69</v>
+        <v>-7.29</v>
       </c>
       <c r="L5">
-        <v>30.98</v>
+        <v>22.62</v>
       </c>
       <c r="M5">
-        <v>20.45</v>
+        <v>19.83</v>
       </c>
       <c r="N5">
         <v>66</v>
       </c>
       <c r="O5">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="P5">
-        <v>1692.06</v>
+        <v>1686.48</v>
       </c>
       <c r="Q5">
-        <v>1701.12</v>
+        <v>1692.79</v>
       </c>
       <c r="R5">
-        <v>1773.84</v>
+        <v>1769.43</v>
       </c>
       <c r="S5">
-        <v>1590.1</v>
+        <v>1592.58</v>
       </c>
       <c r="T5">
-        <v>6.66</v>
+        <v>4.99</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1307,34 +1335,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>43.28</v>
+        <v>38.48</v>
       </c>
       <c r="Z5">
-        <v>-26.44</v>
+        <v>-23.97</v>
       </c>
       <c r="AA5">
-        <v>-29.74</v>
+        <v>-27.66</v>
       </c>
       <c r="AB5">
-        <v>3.3</v>
+        <v>3.69</v>
       </c>
       <c r="AC5">
-        <v>83.16</v>
+        <v>86.18000000000001</v>
       </c>
       <c r="AD5">
-        <v>86.27</v>
+        <v>86.67</v>
       </c>
       <c r="AE5">
-        <v>33.47</v>
+        <v>31.99</v>
       </c>
       <c r="AF5">
-        <v>-26.84</v>
+        <v>-52.05</v>
       </c>
       <c r="AG5">
-        <v>1769.16</v>
+        <v>1743.34</v>
       </c>
       <c r="AH5">
-        <v>1633.08</v>
+        <v>1642.24</v>
       </c>
       <c r="AI5">
         <v>1761.08</v>
@@ -1343,7 +1371,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>32.79</v>
+        <v>27.17</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1354,10 +1382,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>204</v>
+        <v>203.7</v>
       </c>
       <c r="D6">
-        <v>-0.01</v>
+        <v>-0.88</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1366,46 +1394,46 @@
         <v>118.42</v>
       </c>
       <c r="G6">
-        <v>-18.04</v>
+        <v>-18.16</v>
       </c>
       <c r="H6">
-        <v>72.27</v>
+        <v>72.01000000000001</v>
       </c>
       <c r="I6">
-        <v>-1.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J6">
-        <v>-5.97</v>
+        <v>-4.66</v>
       </c>
       <c r="K6">
-        <v>-6.99</v>
+        <v>-16.7</v>
       </c>
       <c r="L6">
-        <v>74.64</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="M6">
-        <v>67.47</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="P6">
-        <v>204.48</v>
+        <v>204.56</v>
       </c>
       <c r="Q6">
-        <v>208.53</v>
+        <v>207.61</v>
       </c>
       <c r="R6">
-        <v>216.67</v>
+        <v>216.08</v>
       </c>
       <c r="S6">
-        <v>179.83</v>
+        <v>180.3</v>
       </c>
       <c r="T6">
-        <v>13.44</v>
+        <v>12.98</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1420,43 +1448,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>37.33</v>
+        <v>38.09</v>
       </c>
       <c r="Z6">
-        <v>-3.51</v>
+        <v>-3.32</v>
       </c>
       <c r="AA6">
-        <v>-3.39</v>
+        <v>-3.37</v>
       </c>
       <c r="AB6">
-        <v>-0.12</v>
+        <v>0.05</v>
       </c>
       <c r="AC6">
-        <v>27.81</v>
+        <v>39.84</v>
       </c>
       <c r="AD6">
-        <v>20.75</v>
+        <v>34.45</v>
       </c>
       <c r="AE6">
-        <v>4.78</v>
+        <v>4.52</v>
       </c>
       <c r="AF6">
-        <v>-39.52</v>
+        <v>-37.03</v>
       </c>
       <c r="AG6">
-        <v>214.88</v>
+        <v>213.25</v>
       </c>
       <c r="AH6">
-        <v>202.17</v>
+        <v>201.96</v>
       </c>
       <c r="AI6">
-        <v>218.48</v>
+        <v>217.63</v>
       </c>
       <c r="AJ6" t="s">
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>23.65</v>
+        <v>23.32</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1467,58 +1495,58 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>411</v>
+        <v>408.75</v>
       </c>
       <c r="D7">
-        <v>0.86</v>
+        <v>-1.39</v>
       </c>
       <c r="E7">
-        <v>589.48</v>
+        <v>588.98</v>
       </c>
       <c r="F7">
         <v>393.4</v>
       </c>
       <c r="G7">
-        <v>-30.28</v>
+        <v>-30.6</v>
       </c>
       <c r="H7">
-        <v>4.47</v>
+        <v>3.9</v>
       </c>
       <c r="I7">
-        <v>-2</v>
+        <v>-1.57</v>
       </c>
       <c r="J7">
-        <v>-4.6</v>
+        <v>-3.86</v>
       </c>
       <c r="K7">
-        <v>-5.34</v>
+        <v>-8.66</v>
       </c>
       <c r="L7">
-        <v>-28.55</v>
+        <v>-30.66</v>
       </c>
       <c r="M7">
-        <v>1.74</v>
+        <v>1.45</v>
       </c>
       <c r="N7">
         <v>23</v>
       </c>
       <c r="O7">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="P7">
-        <v>412.73</v>
+        <v>410.83</v>
       </c>
       <c r="Q7">
-        <v>426.91</v>
+        <v>425.27</v>
       </c>
       <c r="R7">
-        <v>427.94</v>
+        <v>427.86</v>
       </c>
       <c r="S7">
-        <v>476.76</v>
+        <v>475.18</v>
       </c>
       <c r="T7">
-        <v>-13.79</v>
+        <v>-13.98</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1533,34 +1561,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>38.3</v>
+        <v>38</v>
       </c>
       <c r="Z7">
-        <v>-5.39</v>
+        <v>-5.8</v>
       </c>
       <c r="AA7">
-        <v>-2.73</v>
+        <v>-3.77</v>
       </c>
       <c r="AB7">
-        <v>-2.66</v>
+        <v>-2.03</v>
       </c>
       <c r="AC7">
-        <v>4.99</v>
+        <v>19.75</v>
       </c>
       <c r="AD7">
-        <v>1.66</v>
+        <v>13.27</v>
       </c>
       <c r="AE7">
-        <v>9.02</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="AF7">
-        <v>27.86</v>
+        <v>-28.99</v>
       </c>
       <c r="AG7">
-        <v>448.42</v>
+        <v>448.7</v>
       </c>
       <c r="AH7">
-        <v>405.41</v>
+        <v>401.84</v>
       </c>
       <c r="AI7">
         <v>436.39</v>
@@ -1569,7 +1597,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>36.58</v>
+        <v>32.24</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1580,10 +1608,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>657.65</v>
+        <v>639.6</v>
       </c>
       <c r="D8">
-        <v>-0.99</v>
+        <v>-1.01</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1592,46 +1620,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-18.63</v>
+        <v>-20.87</v>
       </c>
       <c r="H8">
-        <v>40.6</v>
+        <v>36.74</v>
       </c>
       <c r="I8">
-        <v>0.4</v>
+        <v>-1.13</v>
       </c>
       <c r="J8">
-        <v>-3.51</v>
+        <v>-2.03</v>
       </c>
       <c r="K8">
-        <v>0.78</v>
+        <v>-10.28</v>
       </c>
       <c r="L8">
-        <v>8.32</v>
+        <v>1.76</v>
       </c>
       <c r="M8">
-        <v>-9.300000000000001</v>
+        <v>-11.54</v>
       </c>
       <c r="N8">
         <v>55</v>
       </c>
       <c r="O8">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="P8">
-        <v>654.03</v>
+        <v>650.98</v>
       </c>
       <c r="Q8">
-        <v>657.04</v>
+        <v>655.66</v>
       </c>
       <c r="R8">
-        <v>692.0599999999999</v>
+        <v>688.88</v>
       </c>
       <c r="S8">
-        <v>613.26</v>
+        <v>613.42</v>
       </c>
       <c r="T8">
-        <v>7.24</v>
+        <v>4.27</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1646,43 +1674,43 @@
         <v>2</v>
       </c>
       <c r="Y8">
-        <v>44.16</v>
+        <v>36.79</v>
       </c>
       <c r="Z8">
-        <v>-9.57</v>
+        <v>-10.44</v>
       </c>
       <c r="AA8">
-        <v>-11.27</v>
+        <v>-10.88</v>
       </c>
       <c r="AB8">
-        <v>1.71</v>
+        <v>0.43</v>
       </c>
       <c r="AC8">
-        <v>63.52</v>
+        <v>34.4</v>
       </c>
       <c r="AD8">
-        <v>46.82</v>
+        <v>54.71</v>
       </c>
       <c r="AE8">
-        <v>17.37</v>
+        <v>17.23</v>
       </c>
       <c r="AF8">
-        <v>-40.76</v>
+        <v>-55.49</v>
       </c>
       <c r="AG8">
-        <v>670.34</v>
+        <v>671.53</v>
       </c>
       <c r="AH8">
-        <v>643.75</v>
+        <v>639.8</v>
       </c>
       <c r="AI8">
-        <v>698.3200000000001</v>
+        <v>698.1</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>30.23</v>
+        <v>24.11</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1693,10 +1721,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>188.64</v>
+        <v>193.88</v>
       </c>
       <c r="D9">
-        <v>-0.04</v>
+        <v>3.06</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1705,46 +1733,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-32.05</v>
+        <v>-30.16</v>
       </c>
       <c r="H9">
-        <v>9.48</v>
+        <v>12.52</v>
       </c>
       <c r="I9">
-        <v>-1.81</v>
+        <v>0.9</v>
       </c>
       <c r="J9">
-        <v>-0.66</v>
+        <v>3.04</v>
       </c>
       <c r="K9">
-        <v>-3.33</v>
+        <v>0.42</v>
       </c>
       <c r="L9">
-        <v>-24.51</v>
+        <v>-25.3</v>
       </c>
       <c r="M9">
-        <v>-7.48</v>
+        <v>-6.9</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="P9">
-        <v>190.34</v>
+        <v>189.88</v>
       </c>
       <c r="Q9">
-        <v>191.26</v>
+        <v>191.57</v>
       </c>
       <c r="R9">
-        <v>189.24</v>
+        <v>189.35</v>
       </c>
       <c r="S9">
-        <v>207.71</v>
+        <v>206.86</v>
       </c>
       <c r="T9">
-        <v>-9.18</v>
+        <v>-6.27</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1759,34 +1787,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>44.7</v>
+        <v>56.2</v>
       </c>
       <c r="Z9">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="AA9">
-        <v>0.91</v>
+        <v>0.64</v>
       </c>
       <c r="AB9">
-        <v>-0.61</v>
+        <v>-0.36</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>20.84</v>
       </c>
       <c r="AD9">
-        <v>8.77</v>
+        <v>6.95</v>
       </c>
       <c r="AE9">
-        <v>4.48</v>
+        <v>4.84</v>
       </c>
       <c r="AF9">
-        <v>28.21</v>
+        <v>216.03</v>
       </c>
       <c r="AG9">
-        <v>197.79</v>
+        <v>197.97</v>
       </c>
       <c r="AH9">
-        <v>184.73</v>
+        <v>185.17</v>
       </c>
       <c r="AI9">
         <v>197.85</v>
@@ -1795,7 +1823,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>28.91</v>
+        <v>26.48</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1806,10 +1834,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>75.5</v>
+        <v>75.14</v>
       </c>
       <c r="D10">
-        <v>2.95</v>
+        <v>-0.46</v>
       </c>
       <c r="E10">
         <v>150.86</v>
@@ -1818,46 +1846,46 @@
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-49.95</v>
+        <v>-50.19</v>
       </c>
       <c r="H10">
-        <v>27.36</v>
+        <v>26.75</v>
       </c>
       <c r="I10">
-        <v>-1.14</v>
+        <v>-1.82</v>
       </c>
       <c r="J10">
-        <v>-0.68</v>
+        <v>-1.98</v>
       </c>
       <c r="K10">
-        <v>-1.59</v>
+        <v>-4.69</v>
       </c>
       <c r="L10">
-        <v>-39.83</v>
+        <v>-45.68</v>
       </c>
       <c r="M10">
-        <v>0.61</v>
+        <v>-0.93</v>
       </c>
       <c r="N10">
         <v>12</v>
       </c>
       <c r="O10">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>75.52</v>
+        <v>75.03</v>
       </c>
       <c r="Q10">
-        <v>76.44</v>
+        <v>76.26000000000001</v>
       </c>
       <c r="R10">
-        <v>79.03</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="S10">
-        <v>81.76000000000001</v>
+        <v>81.59</v>
       </c>
       <c r="T10">
-        <v>-7.65</v>
+        <v>-7.9</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1872,34 +1900,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>42.97</v>
+        <v>41.56</v>
       </c>
       <c r="Z10">
-        <v>-1.03</v>
+        <v>-0.99</v>
       </c>
       <c r="AA10">
-        <v>-0.96</v>
+        <v>-0.97</v>
       </c>
       <c r="AB10">
-        <v>-0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="AC10">
-        <v>35.16</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="AD10">
-        <v>41.77</v>
+        <v>59.28</v>
       </c>
       <c r="AE10">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="AF10">
-        <v>-3.68</v>
+        <v>-16.19</v>
       </c>
       <c r="AG10">
-        <v>78.25</v>
+        <v>78.13</v>
       </c>
       <c r="AH10">
-        <v>74.62</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="AI10">
         <v>80.34</v>
@@ -1908,7 +1936,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>24.12</v>
+        <v>29.46</v>
       </c>
     </row>
   </sheetData>
@@ -2069,12 +2097,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>52</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -2082,1244 +2145,1244 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>57</v>
+      <c r="B6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-7.14</v>
-      </c>
-      <c r="D7" s="5">
-        <v>-4.26</v>
-      </c>
-      <c r="E7" s="6">
-        <v>2.88</v>
+      <c r="C7" s="6">
+        <v>-1.99</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-2.98</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-0.99</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-6.05</v>
-      </c>
-      <c r="D8" s="5">
-        <v>-4.85</v>
-      </c>
-      <c r="E8" s="6">
-        <v>1.2</v>
+      <c r="C8" s="6">
+        <v>-0.43</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-0.92</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-0.49</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-16.14</v>
-      </c>
-      <c r="D9" s="5">
-        <v>-11.58</v>
-      </c>
-      <c r="E9" s="6">
-        <v>4.56</v>
+      <c r="C9" s="6">
+        <v>-4.34</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-6.24</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-1.9</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-8.91</v>
-      </c>
-      <c r="D10" s="5">
-        <v>-6.78</v>
-      </c>
-      <c r="E10" s="6">
-        <v>2.13</v>
+      <c r="C10" s="6">
+        <v>-4.41</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-5.44</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-1.03</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-7.42</v>
-      </c>
-      <c r="D11" s="5">
-        <v>-5.97</v>
-      </c>
-      <c r="E11" s="6">
-        <v>1.45</v>
+      <c r="C11" s="6">
+        <v>-3.17</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-4.66</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.49</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
-        <v>-7.56</v>
-      </c>
-      <c r="D12" s="5">
-        <v>-4.6</v>
-      </c>
-      <c r="E12" s="6">
-        <v>2.96</v>
+      <c r="C12" s="6">
+        <v>-2.14</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-3.86</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-1.72</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="5">
-        <v>-5.16</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-3.51</v>
-      </c>
-      <c r="E13" s="6">
-        <v>1.65</v>
+      <c r="C13" s="6">
+        <v>-2.49</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-2.03</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.46</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="5">
-        <v>-2.69</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-0.66</v>
-      </c>
-      <c r="E14" s="6">
-        <v>2.03</v>
+      <c r="C14" s="6">
+        <v>0.37</v>
+      </c>
+      <c r="D14" s="6">
+        <v>3.04</v>
+      </c>
+      <c r="E14" s="8">
+        <v>2.67</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="5">
-        <v>-8.109999999999999</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-0.68</v>
-      </c>
-      <c r="E15" s="6">
-        <v>7.43</v>
+      <c r="C15" s="6">
+        <v>-0.25</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-1.98</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-1.73</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>-3.31</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-1.78</v>
-      </c>
-      <c r="E16" s="6">
-        <v>1.53</v>
+      <c r="C16" s="6">
+        <v>-1.06</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-1.19</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="5">
-        <v>0.15</v>
-      </c>
-      <c r="D17" s="5">
-        <v>1.01</v>
-      </c>
-      <c r="E17" s="6">
-        <v>0.86</v>
+      <c r="C17" s="6">
+        <v>-1.26</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-0.29</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.97</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="5">
-        <v>-2.95</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-1.3</v>
-      </c>
-      <c r="E18" s="6">
-        <v>1.65</v>
+      <c r="C18" s="6">
+        <v>-2.08</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-1.48</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0.6</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="5">
-        <v>1.02</v>
-      </c>
-      <c r="D19" s="5">
-        <v>2.29</v>
-      </c>
-      <c r="E19" s="6">
-        <v>1.27</v>
+      <c r="C19" s="6">
+        <v>0</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-1.64</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-1.64</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="5">
-        <v>-1.43</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-1.02</v>
-      </c>
-      <c r="E20" s="6">
-        <v>0.41</v>
+      <c r="C20" s="6">
+        <v>0.12</v>
+      </c>
+      <c r="D20" s="6">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="5">
-        <v>-3.21</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-2</v>
-      </c>
-      <c r="E21" s="6">
-        <v>1.21</v>
+      <c r="C21" s="6">
+        <v>-0.72</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-1.57</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.85</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="5">
-        <v>0.59</v>
-      </c>
-      <c r="D22" s="5">
-        <v>0.4</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-0.19</v>
+      <c r="C22" s="6">
+        <v>-1.22</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-1.13</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.09</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="5">
-        <v>-2.84</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-1.81</v>
-      </c>
-      <c r="E23" s="6">
+      <c r="C23" s="6">
+        <v>-2.1</v>
+      </c>
+      <c r="D23" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="E23" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-1.36</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-1.82</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-28.67</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-29.64</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>28.49</v>
+      </c>
+      <c r="D26" s="6">
+        <v>25.6</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-2.89</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>40.18</v>
+      </c>
+      <c r="D27" s="6">
+        <v>34.37</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-5.81</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>28.63</v>
+      </c>
+      <c r="D28" s="6">
+        <v>22.62</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-6.01</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>71.61</v>
+      </c>
+      <c r="D29" s="6">
+        <v>68.06999999999999</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-3.54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-29.4</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-30.66</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-1.26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>3.65</v>
+      </c>
+      <c r="D31" s="6">
+        <v>1.76</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-1.89</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-25.13</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-25.3</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-42.7</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-45.68</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-2.98</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-4.87</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-7.37</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>5.22</v>
+      </c>
+      <c r="D35" s="6">
         <v>1.03</v>
       </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="E35" s="7">
+        <v>-4.19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-6.46</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-10.25</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-3.79</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-5.31</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-7.29</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-1.98</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-11.95</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-16.7</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-4.75</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-5.75</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-8.66</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-2.91</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-1.95</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-10.28</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-8.33</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-2.56</v>
+      </c>
+      <c r="D41" s="6">
+        <v>0.42</v>
+      </c>
+      <c r="E41" s="8">
+        <v>2.98</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-3.64</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-1.14</v>
-      </c>
-      <c r="E24" s="6">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-3.58</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-4.69</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-1.11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-27.44</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-26.59</v>
-      </c>
-      <c r="E25" s="6">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-31.29</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-31.63</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>31.21</v>
-      </c>
-      <c r="D26" s="5">
-        <v>31.32</v>
-      </c>
-      <c r="E26" s="6">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-6.7</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-6.65</v>
+      </c>
+      <c r="E44" s="8">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>39.91</v>
-      </c>
-      <c r="D27" s="5">
-        <v>41.89</v>
-      </c>
-      <c r="E27" s="6">
-        <v>1.98</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-17.73</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-18.48</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="5">
-        <v>27.99</v>
-      </c>
-      <c r="D28" s="5">
-        <v>30.98</v>
-      </c>
-      <c r="E28" s="6">
-        <v>2.99</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-9.73</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-11.21</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-1.48</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="5">
-        <v>74.2</v>
-      </c>
-      <c r="D29" s="5">
-        <v>74.64</v>
-      </c>
-      <c r="E29" s="6">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-17.44</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-18.16</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-29.5</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-28.55</v>
-      </c>
-      <c r="E30" s="6">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-29.68</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-30.6</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="5">
-        <v>9.07</v>
-      </c>
-      <c r="D31" s="5">
-        <v>8.32</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-0.75</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-25.26</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-24.51</v>
-      </c>
-      <c r="E32" s="6">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-43</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-39.83</v>
-      </c>
-      <c r="E33" s="6">
-        <v>3.17</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-4.75</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-3.78</v>
-      </c>
-      <c r="E34" s="6">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="5">
-        <v>10.9</v>
-      </c>
-      <c r="D35" s="5">
-        <v>10.27</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-4.8</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-4.44</v>
-      </c>
-      <c r="E36" s="6">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-5.82</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-4.69</v>
-      </c>
-      <c r="E37" s="6">
-        <v>1.13</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-6.98</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-6.99</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-6.17</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-5.34</v>
-      </c>
-      <c r="E39" s="6">
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="5">
-        <v>4.13</v>
-      </c>
-      <c r="D40" s="5">
-        <v>0.78</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-3.35</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-4.8</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-3.33</v>
-      </c>
-      <c r="E41" s="6">
-        <v>1.47</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="5">
-        <v>-5.14</v>
-      </c>
-      <c r="D42" s="5">
-        <v>-1.59</v>
-      </c>
-      <c r="E42" s="6">
-        <v>3.55</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="3" t="s">
+      <c r="B49" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="5">
-        <v>-32.27</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-31.62</v>
-      </c>
-      <c r="E43" s="6">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-6.91</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-6.76</v>
-      </c>
-      <c r="E44" s="6">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-19.41</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-18.87</v>
-      </c>
-      <c r="E45" s="6">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-10.69</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-9.94</v>
-      </c>
-      <c r="E46" s="6">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="5">
-        <v>-18.03</v>
-      </c>
-      <c r="D47" s="5">
-        <v>-18.04</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="5">
-        <v>-30.87</v>
-      </c>
-      <c r="D48" s="5">
-        <v>-30.28</v>
-      </c>
-      <c r="E48" s="6">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="5">
-        <v>-17.82</v>
-      </c>
-      <c r="D49" s="5">
-        <v>-18.63</v>
+      <c r="C49" s="6">
+        <v>-20.06</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-20.87</v>
       </c>
       <c r="E49" s="7">
         <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
+      <c r="A50" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C50" s="5">
-        <v>-32.02</v>
-      </c>
-      <c r="D50" s="5">
-        <v>-32.05</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-0.03</v>
+      <c r="C50" s="6">
+        <v>-32.23</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-30.16</v>
+      </c>
+      <c r="E50" s="8">
+        <v>2.07</v>
       </c>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
+      <c r="A51" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="5">
-        <v>-51.39</v>
-      </c>
-      <c r="D51" s="5">
-        <v>-49.95</v>
-      </c>
-      <c r="E51" s="6">
-        <v>1.44</v>
+      <c r="C51" s="6">
+        <v>-49.96</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-50.19</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
+      <c r="A52" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C52" s="5">
-        <v>1288.7</v>
-      </c>
-      <c r="D52" s="5">
-        <v>1301.1</v>
-      </c>
-      <c r="E52" s="6">
-        <v>12.4</v>
+      <c r="C52" s="6">
+        <v>1307.4</v>
+      </c>
+      <c r="D52" s="6">
+        <v>1300.9</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-6.5</v>
       </c>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
+      <c r="A53" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B53" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C53" s="5">
-        <v>2990.3</v>
-      </c>
-      <c r="D53" s="5">
-        <v>2994.9</v>
-      </c>
-      <c r="E53" s="6">
-        <v>4.6</v>
+      <c r="C53" s="6">
+        <v>2997</v>
+      </c>
+      <c r="D53" s="6">
+        <v>2998.6</v>
+      </c>
+      <c r="E53" s="8">
+        <v>1.6</v>
       </c>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
+      <c r="A54" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B54" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C54" s="5">
-        <v>1293</v>
-      </c>
-      <c r="D54" s="5">
-        <v>1301.8</v>
-      </c>
-      <c r="E54" s="6">
-        <v>8.800000000000001</v>
+      <c r="C54" s="6">
+        <v>1320</v>
+      </c>
+      <c r="D54" s="6">
+        <v>1308</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-12</v>
       </c>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
+      <c r="A55" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C55" s="5">
-        <v>1681.9</v>
-      </c>
-      <c r="D55" s="5">
-        <v>1696</v>
-      </c>
-      <c r="E55" s="6">
-        <v>14.1</v>
+      <c r="C55" s="6">
+        <v>1700</v>
+      </c>
+      <c r="D55" s="6">
+        <v>1672.1</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-27.9</v>
       </c>
     </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
+      <c r="A56" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B56" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C56" s="5">
-        <v>204.02</v>
-      </c>
-      <c r="D56" s="5">
-        <v>204</v>
+      <c r="C56" s="6">
+        <v>205.5</v>
+      </c>
+      <c r="D56" s="6">
+        <v>203.7</v>
       </c>
       <c r="E56" s="7">
-        <v>-0.02</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
+      <c r="A57" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B57" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C57" s="5">
-        <v>407.5</v>
-      </c>
-      <c r="D57" s="5">
-        <v>411</v>
-      </c>
-      <c r="E57" s="6">
-        <v>3.5</v>
+      <c r="C57" s="6">
+        <v>414.5</v>
+      </c>
+      <c r="D57" s="6">
+        <v>408.75</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-5.75</v>
       </c>
     </row>
     <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
+      <c r="A58" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B58" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C58" s="5">
-        <v>664.25</v>
-      </c>
-      <c r="D58" s="5">
-        <v>657.65</v>
+      <c r="C58" s="6">
+        <v>646.1</v>
+      </c>
+      <c r="D58" s="6">
+        <v>639.6</v>
       </c>
       <c r="E58" s="7">
-        <v>-6.6</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
+      <c r="A59" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B59" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C59" s="5">
-        <v>188.72</v>
-      </c>
-      <c r="D59" s="5">
-        <v>188.64</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-0.08</v>
+      <c r="C59" s="6">
+        <v>188.12</v>
+      </c>
+      <c r="D59" s="6">
+        <v>193.88</v>
+      </c>
+      <c r="E59" s="8">
+        <v>5.76</v>
       </c>
     </row>
     <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
+      <c r="A60" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B60" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C60" s="5">
-        <v>73.34</v>
-      </c>
-      <c r="D60" s="5">
-        <v>75.5</v>
-      </c>
-      <c r="E60" s="6">
-        <v>2.16</v>
+      <c r="C60" s="6">
+        <v>75.48999999999999</v>
+      </c>
+      <c r="D60" s="6">
+        <v>75.14</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
+      <c r="A61" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B61" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C61" s="5">
-        <v>33.26</v>
-      </c>
-      <c r="D61" s="5">
-        <v>37.78</v>
-      </c>
-      <c r="E61" s="6">
-        <v>4.52</v>
+      <c r="C61" s="6">
+        <v>40</v>
+      </c>
+      <c r="D61" s="6">
+        <v>38.47</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-1.53</v>
       </c>
     </row>
     <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
+      <c r="A62" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B62" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C62" s="5">
-        <v>44.55</v>
-      </c>
-      <c r="D62" s="5">
-        <v>45.27</v>
-      </c>
-      <c r="E62" s="6">
-        <v>0.72</v>
+      <c r="C62" s="6">
+        <v>45.61</v>
+      </c>
+      <c r="D62" s="6">
+        <v>45.89</v>
+      </c>
+      <c r="E62" s="8">
+        <v>0.28</v>
       </c>
     </row>
     <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
+      <c r="A63" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="B63" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C63" s="5">
+      <c r="C63" s="6">
+        <v>38.11</v>
+      </c>
+      <c r="D63" s="6">
+        <v>36.28</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-1.83</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="6">
+        <v>44.46</v>
+      </c>
+      <c r="D64" s="6">
+        <v>38.48</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-5.98</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>40.85</v>
+      </c>
+      <c r="D65" s="6">
+        <v>38.09</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-2.76</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>41.66</v>
+      </c>
+      <c r="D66" s="6">
+        <v>38</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-3.66</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>39.26</v>
+      </c>
+      <c r="D67" s="6">
+        <v>36.79</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-2.47</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>43.63</v>
+      </c>
+      <c r="D68" s="6">
+        <v>56.2</v>
+      </c>
+      <c r="E68" s="8">
+        <v>12.57</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>42.93</v>
+      </c>
+      <c r="D69" s="6">
+        <v>41.56</v>
+      </c>
+      <c r="E69" s="7">
+        <v>-1.37</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B70" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D63" s="5">
-        <v>33.37</v>
-      </c>
-      <c r="E63" s="6">
-        <v>2.37</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
+      <c r="C70" s="6">
+        <v>-39.31</v>
+      </c>
+      <c r="D70" s="6">
+        <v>-54.73</v>
+      </c>
+      <c r="E70" s="7">
+        <v>-15.42</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="6">
+        <v>-24.05</v>
+      </c>
+      <c r="D71" s="6">
+        <v>-18.42</v>
+      </c>
+      <c r="E71" s="8">
+        <v>5.63</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="6">
+        <v>-42.73</v>
+      </c>
+      <c r="D72" s="6">
+        <v>-59.02</v>
+      </c>
+      <c r="E72" s="7">
+        <v>-16.29</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B64" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="5">
-        <v>39.07</v>
-      </c>
-      <c r="D64" s="5">
-        <v>43.28</v>
-      </c>
-      <c r="E64" s="6">
-        <v>4.21</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
+      <c r="B73" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="6">
+        <v>-51.21</v>
+      </c>
+      <c r="D73" s="6">
+        <v>-52.05</v>
+      </c>
+      <c r="E73" s="7">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B65" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="5">
-        <v>37.36</v>
-      </c>
-      <c r="D65" s="5">
-        <v>37.33</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-0.03</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
+      <c r="B74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="6">
+        <v>-35.46</v>
+      </c>
+      <c r="D74" s="6">
+        <v>-37.03</v>
+      </c>
+      <c r="E74" s="7">
+        <v>-1.57</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B66" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="5">
-        <v>34.8</v>
-      </c>
-      <c r="D66" s="5">
-        <v>38.3</v>
-      </c>
-      <c r="E66" s="6">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="3" t="s">
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
+        <v>91.95</v>
+      </c>
+      <c r="D75" s="6">
+        <v>-28.99</v>
+      </c>
+      <c r="E75" s="7">
+        <v>-120.94</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B67" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="5">
-        <v>47.29</v>
-      </c>
-      <c r="D67" s="5">
-        <v>44.16</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-3.13</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="3" t="s">
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>-26.53</v>
+      </c>
+      <c r="D76" s="6">
+        <v>-55.49</v>
+      </c>
+      <c r="E76" s="7">
+        <v>-28.96</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B68" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="5">
-        <v>44.86</v>
-      </c>
-      <c r="D68" s="5">
-        <v>44.7</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-0.16</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="3" t="s">
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>156.98</v>
+      </c>
+      <c r="D77" s="6">
+        <v>216.03</v>
+      </c>
+      <c r="E77" s="8">
+        <v>59.05</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B69" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="5">
-        <v>30.83</v>
-      </c>
-      <c r="D69" s="5">
-        <v>42.97</v>
-      </c>
-      <c r="E69" s="6">
-        <v>12.14</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B70" s="3" t="s">
+      <c r="B78" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C70" s="5">
-        <v>-35.63</v>
-      </c>
-      <c r="D70" s="5">
-        <v>-50.21</v>
-      </c>
-      <c r="E70" s="7">
-        <v>-14.58</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="5">
-        <v>-12.33</v>
-      </c>
-      <c r="D71" s="5">
-        <v>-33.31</v>
-      </c>
-      <c r="E71" s="7">
-        <v>-20.98</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="5">
-        <v>-38.47</v>
-      </c>
-      <c r="D72" s="5">
-        <v>-49.84</v>
-      </c>
-      <c r="E72" s="7">
-        <v>-11.37</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="5">
-        <v>-46.6</v>
-      </c>
-      <c r="D73" s="5">
-        <v>-26.84</v>
-      </c>
-      <c r="E73" s="6">
-        <v>19.76</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="5">
-        <v>-42.39</v>
-      </c>
-      <c r="D74" s="5">
-        <v>-39.52</v>
-      </c>
-      <c r="E74" s="6">
-        <v>2.87</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="5">
-        <v>-24.39</v>
-      </c>
-      <c r="D75" s="5">
-        <v>27.86</v>
-      </c>
-      <c r="E75" s="6">
-        <v>52.25</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="5">
-        <v>959.14</v>
-      </c>
-      <c r="D76" s="5">
-        <v>-40.76</v>
-      </c>
-      <c r="E76" s="7">
-        <v>-999.9</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="5">
-        <v>-53.86</v>
-      </c>
-      <c r="D77" s="5">
-        <v>28.21</v>
-      </c>
-      <c r="E77" s="6">
-        <v>82.06999999999999</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="5">
-        <v>25.92</v>
-      </c>
-      <c r="D78" s="5">
-        <v>-3.68</v>
-      </c>
-      <c r="E78" s="7">
-        <v>-29.6</v>
+      <c r="C78" s="6">
+        <v>-18.13</v>
+      </c>
+      <c r="D78" s="6">
+        <v>-16.19</v>
+      </c>
+      <c r="E78" s="8">
+        <v>1.94</v>
       </c>
     </row>
   </sheetData>
@@ -3345,60 +3408,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="8" t="s">
+      <c r="B1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="11">
+        <v>56.16</v>
+      </c>
+      <c r="C2" s="12">
+        <v>9</v>
+      </c>
+      <c r="D2" s="11">
+        <v>41.1</v>
+      </c>
+      <c r="E2" s="11">
         <v>60</v>
       </c>
-      <c r="E1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="10">
-        <v>56.16</v>
-      </c>
-      <c r="C2" s="11">
-        <v>9</v>
-      </c>
-      <c r="D2" s="10">
-        <v>40.8</v>
-      </c>
-      <c r="E2" s="10">
-        <v>60</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-4.8</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-2.1</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-2.8</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-7.1</v>
+      </c>
+      <c r="H2" s="11">
         <v>55.4</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -3500,61 +3563,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="12" t="s">
-        <v>37</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="13">
-        <v>0.6747</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.2045</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.1599</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.0682</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.0174</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.0061</v>
-      </c>
-      <c r="G2" s="13">
-        <v>-0.07480000000000001</v>
-      </c>
-      <c r="H2" s="13">
-        <v>-0.09300000000000001</v>
-      </c>
-      <c r="I2" s="13">
-        <v>-0.0989</v>
+      <c r="A2" s="14">
+        <v>0.6751</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1983</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1589</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.06610000000000001</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.0145</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.009300000000000001</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.06900000000000001</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.09810000000000001</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.1154</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,16 +196,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>43.6 → 56.2</t>
+    <t>45.9 → 60.9</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>43.6</t>
-  </si>
-  <si>
-    <t>56.2</t>
+    <t>45.9</t>
+  </si>
+  <si>
+    <t>60.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -930,10 +930,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1300.9</v>
+        <v>1305.9</v>
       </c>
       <c r="D2">
-        <v>-0.5</v>
+        <v>0.38</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -942,25 +942,25 @@
         <v>1247.38</v>
       </c>
       <c r="G2">
-        <v>-31.63</v>
+        <v>-31.37</v>
       </c>
       <c r="H2">
-        <v>4.29</v>
+        <v>4.69</v>
       </c>
       <c r="I2">
-        <v>-1.19</v>
+        <v>0.16</v>
       </c>
       <c r="J2">
-        <v>-2.98</v>
+        <v>-3.84</v>
       </c>
       <c r="K2">
-        <v>-7.37</v>
+        <v>-7.93</v>
       </c>
       <c r="L2">
-        <v>-29.64</v>
+        <v>-29.5</v>
       </c>
       <c r="M2">
-        <v>-9.81</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="N2">
         <v>34</v>
@@ -969,19 +969,19 @@
         <v>20</v>
       </c>
       <c r="P2">
-        <v>1300.38</v>
+        <v>1300.8</v>
       </c>
       <c r="Q2">
-        <v>1341.96</v>
+        <v>1340.17</v>
       </c>
       <c r="R2">
-        <v>1351.95</v>
+        <v>1350.94</v>
       </c>
       <c r="S2">
-        <v>1516.33</v>
+        <v>1513.75</v>
       </c>
       <c r="T2">
-        <v>-14.21</v>
+        <v>-13.73</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -996,43 +996,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>38.47</v>
+        <v>40.36</v>
       </c>
       <c r="Z2">
-        <v>-16.95</v>
+        <v>-16.8</v>
       </c>
       <c r="AA2">
-        <v>-11.45</v>
+        <v>-12.52</v>
       </c>
       <c r="AB2">
-        <v>-5.49</v>
+        <v>-4.27</v>
       </c>
       <c r="AC2">
-        <v>23.21</v>
+        <v>29.32</v>
       </c>
       <c r="AD2">
-        <v>15.02</v>
+        <v>22.76</v>
       </c>
       <c r="AE2">
-        <v>24.59</v>
+        <v>24.19</v>
       </c>
       <c r="AF2">
-        <v>-54.73</v>
+        <v>-58.24</v>
       </c>
       <c r="AG2">
-        <v>1408.86</v>
+        <v>1408.98</v>
       </c>
       <c r="AH2">
-        <v>1275.06</v>
+        <v>1271.35</v>
       </c>
       <c r="AI2">
-        <v>1374.58</v>
+        <v>1373.07</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>37.77</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,10 +1043,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2998.6</v>
+        <v>3110</v>
       </c>
       <c r="D3">
-        <v>0.05</v>
+        <v>3.72</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1055,46 +1055,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-6.65</v>
+        <v>-3.18</v>
       </c>
       <c r="H3">
-        <v>70.56999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I3">
-        <v>-0.29</v>
+        <v>3.58</v>
       </c>
       <c r="J3">
-        <v>-0.92</v>
+        <v>2.42</v>
       </c>
       <c r="K3">
-        <v>1.03</v>
+        <v>4.65</v>
       </c>
       <c r="L3">
-        <v>25.6</v>
+        <v>30.34</v>
       </c>
       <c r="M3">
-        <v>15.89</v>
+        <v>16.14</v>
       </c>
       <c r="N3">
         <v>88</v>
       </c>
       <c r="O3">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="P3">
-        <v>2996.66</v>
+        <v>3018.16</v>
       </c>
       <c r="Q3">
-        <v>3014.06</v>
+        <v>3019.45</v>
       </c>
       <c r="R3">
-        <v>3057.01</v>
+        <v>3060.36</v>
       </c>
       <c r="S3">
-        <v>2483.88</v>
+        <v>2487.86</v>
       </c>
       <c r="T3">
-        <v>20.72</v>
+        <v>25.01</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1109,34 +1109,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>45.89</v>
+        <v>60.91</v>
       </c>
       <c r="Z3">
-        <v>-16.07</v>
+        <v>-6.6</v>
       </c>
       <c r="AA3">
-        <v>-13.99</v>
+        <v>-12.51</v>
       </c>
       <c r="AB3">
-        <v>-2.08</v>
+        <v>5.91</v>
       </c>
       <c r="AC3">
-        <v>55.11</v>
+        <v>72.28</v>
       </c>
       <c r="AD3">
-        <v>50.99</v>
+        <v>58.86</v>
       </c>
       <c r="AE3">
-        <v>59.41</v>
+        <v>65.7</v>
       </c>
       <c r="AF3">
-        <v>-18.42</v>
+        <v>102.42</v>
       </c>
       <c r="AG3">
-        <v>3066.04</v>
+        <v>3086.44</v>
       </c>
       <c r="AH3">
-        <v>2962.08</v>
+        <v>2952.45</v>
       </c>
       <c r="AI3">
         <v>2959.69</v>
@@ -1145,7 +1145,7 @@
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>24.05</v>
+        <v>25.44</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1156,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1308</v>
+        <v>1330</v>
       </c>
       <c r="D4">
-        <v>-0.91</v>
+        <v>1.68</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1168,46 +1168,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-18.48</v>
+        <v>-17.11</v>
       </c>
       <c r="H4">
-        <v>69.25</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I4">
-        <v>-1.48</v>
+        <v>1.68</v>
       </c>
       <c r="J4">
-        <v>-6.24</v>
+        <v>-4.98</v>
       </c>
       <c r="K4">
-        <v>-10.25</v>
+        <v>-10.73</v>
       </c>
       <c r="L4">
-        <v>34.37</v>
+        <v>36.28</v>
       </c>
       <c r="M4">
-        <v>6.61</v>
+        <v>5.93</v>
       </c>
       <c r="N4">
         <v>77</v>
       </c>
       <c r="O4">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="P4">
-        <v>1306.16</v>
+        <v>1310.56</v>
       </c>
       <c r="Q4">
-        <v>1349.41</v>
+        <v>1347.02</v>
       </c>
       <c r="R4">
-        <v>1445.22</v>
+        <v>1442.17</v>
       </c>
       <c r="S4">
-        <v>1166.53</v>
+        <v>1167.87</v>
       </c>
       <c r="T4">
-        <v>12.13</v>
+        <v>13.88</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1222,34 +1222,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>36.28</v>
+        <v>41.8</v>
       </c>
       <c r="Z4">
-        <v>-38.8</v>
+        <v>-35.98</v>
       </c>
       <c r="AA4">
-        <v>-37.9</v>
+        <v>-37.51</v>
       </c>
       <c r="AB4">
-        <v>-0.9</v>
+        <v>1.53</v>
       </c>
       <c r="AC4">
-        <v>57.59</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="AD4">
-        <v>36.38</v>
+        <v>58.83</v>
       </c>
       <c r="AE4">
-        <v>36.65</v>
+        <v>36.54</v>
       </c>
       <c r="AF4">
-        <v>-59.02</v>
+        <v>65.38</v>
       </c>
       <c r="AG4">
-        <v>1414.15</v>
+        <v>1410.87</v>
       </c>
       <c r="AH4">
-        <v>1284.67</v>
+        <v>1283.17</v>
       </c>
       <c r="AI4">
         <v>1418.72</v>
@@ -1258,7 +1258,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>30.35</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1269,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1672.1</v>
+        <v>1702.7</v>
       </c>
       <c r="D5">
-        <v>-1.64</v>
+        <v>1.83</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1281,46 +1281,46 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-11.21</v>
+        <v>-9.58</v>
       </c>
       <c r="H5">
-        <v>28.81</v>
+        <v>31.17</v>
       </c>
       <c r="I5">
-        <v>-1.64</v>
+        <v>1.21</v>
       </c>
       <c r="J5">
-        <v>-5.44</v>
+        <v>-3.82</v>
       </c>
       <c r="K5">
-        <v>-7.29</v>
+        <v>-6.28</v>
       </c>
       <c r="L5">
-        <v>22.62</v>
+        <v>24.75</v>
       </c>
       <c r="M5">
-        <v>19.83</v>
+        <v>19.4</v>
       </c>
       <c r="N5">
         <v>66</v>
       </c>
       <c r="O5">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="P5">
-        <v>1686.48</v>
+        <v>1690.54</v>
       </c>
       <c r="Q5">
-        <v>1692.79</v>
+        <v>1689.19</v>
       </c>
       <c r="R5">
-        <v>1769.43</v>
+        <v>1767.39</v>
       </c>
       <c r="S5">
-        <v>1592.58</v>
+        <v>1593.94</v>
       </c>
       <c r="T5">
-        <v>4.99</v>
+        <v>6.82</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1335,34 +1335,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>38.48</v>
+        <v>46.91</v>
       </c>
       <c r="Z5">
-        <v>-23.97</v>
+        <v>-21.27</v>
       </c>
       <c r="AA5">
-        <v>-27.66</v>
+        <v>-26.38</v>
       </c>
       <c r="AB5">
-        <v>3.69</v>
+        <v>5.12</v>
       </c>
       <c r="AC5">
         <v>86.18000000000001</v>
       </c>
       <c r="AD5">
-        <v>86.67</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="AE5">
-        <v>31.99</v>
+        <v>31.96</v>
       </c>
       <c r="AF5">
-        <v>-52.05</v>
+        <v>-40.56</v>
       </c>
       <c r="AG5">
-        <v>1743.34</v>
+        <v>1722.48</v>
       </c>
       <c r="AH5">
-        <v>1642.24</v>
+        <v>1655.9</v>
       </c>
       <c r="AI5">
         <v>1761.08</v>
@@ -1371,7 +1371,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>27.17</v>
+        <v>23.63</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,10 +1382,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>203.7</v>
+        <v>206.33</v>
       </c>
       <c r="D6">
-        <v>-0.88</v>
+        <v>1.29</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1394,46 +1394,46 @@
         <v>118.42</v>
       </c>
       <c r="G6">
-        <v>-18.16</v>
+        <v>-17.11</v>
       </c>
       <c r="H6">
-        <v>72.01000000000001</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="I6">
-        <v>0.07000000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="J6">
-        <v>-4.66</v>
+        <v>-3.57</v>
       </c>
       <c r="K6">
-        <v>-16.7</v>
+        <v>-17.11</v>
       </c>
       <c r="L6">
-        <v>68.06999999999999</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="M6">
-        <v>67.51000000000001</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="P6">
-        <v>204.56</v>
+        <v>204.71</v>
       </c>
       <c r="Q6">
-        <v>207.61</v>
+        <v>207.51</v>
       </c>
       <c r="R6">
-        <v>216.08</v>
+        <v>215.8</v>
       </c>
       <c r="S6">
-        <v>180.3</v>
+        <v>180.57</v>
       </c>
       <c r="T6">
-        <v>12.98</v>
+        <v>14.27</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1448,34 +1448,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>38.09</v>
+        <v>44.05</v>
       </c>
       <c r="Z6">
-        <v>-3.32</v>
+        <v>-3.05</v>
       </c>
       <c r="AA6">
-        <v>-3.37</v>
+        <v>-3.31</v>
       </c>
       <c r="AB6">
-        <v>0.05</v>
+        <v>0.26</v>
       </c>
       <c r="AC6">
-        <v>39.84</v>
+        <v>66.14</v>
       </c>
       <c r="AD6">
-        <v>34.45</v>
+        <v>47.23</v>
       </c>
       <c r="AE6">
-        <v>4.52</v>
+        <v>4.58</v>
       </c>
       <c r="AF6">
-        <v>-37.03</v>
+        <v>0.72</v>
       </c>
       <c r="AG6">
-        <v>213.25</v>
+        <v>213.17</v>
       </c>
       <c r="AH6">
-        <v>201.96</v>
+        <v>201.85</v>
       </c>
       <c r="AI6">
         <v>217.63</v>
@@ -1484,7 +1484,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>23.32</v>
+        <v>21.13</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1495,58 +1495,58 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>408.75</v>
+        <v>413.1</v>
       </c>
       <c r="D7">
-        <v>-1.39</v>
+        <v>1.06</v>
       </c>
       <c r="E7">
-        <v>588.98</v>
+        <v>588.6900000000001</v>
       </c>
       <c r="F7">
         <v>393.4</v>
       </c>
       <c r="G7">
-        <v>-30.6</v>
+        <v>-29.83</v>
       </c>
       <c r="H7">
-        <v>3.9</v>
+        <v>5.01</v>
       </c>
       <c r="I7">
-        <v>-1.57</v>
+        <v>0.17</v>
       </c>
       <c r="J7">
-        <v>-3.86</v>
+        <v>-4.14</v>
       </c>
       <c r="K7">
-        <v>-8.66</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="L7">
-        <v>-30.66</v>
+        <v>-29.86</v>
       </c>
       <c r="M7">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="N7">
         <v>23</v>
       </c>
       <c r="O7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P7">
-        <v>410.83</v>
+        <v>410.97</v>
       </c>
       <c r="Q7">
-        <v>425.27</v>
+        <v>424.62</v>
       </c>
       <c r="R7">
-        <v>427.86</v>
+        <v>427.54</v>
       </c>
       <c r="S7">
-        <v>475.18</v>
+        <v>474.47</v>
       </c>
       <c r="T7">
-        <v>-13.98</v>
+        <v>-12.93</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1561,34 +1561,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>38</v>
+        <v>42.14</v>
       </c>
       <c r="Z7">
-        <v>-5.8</v>
+        <v>-5.7</v>
       </c>
       <c r="AA7">
-        <v>-3.77</v>
+        <v>-4.16</v>
       </c>
       <c r="AB7">
-        <v>-2.03</v>
+        <v>-1.55</v>
       </c>
       <c r="AC7">
-        <v>19.75</v>
+        <v>29.09</v>
       </c>
       <c r="AD7">
-        <v>13.27</v>
+        <v>21.3</v>
       </c>
       <c r="AE7">
-        <v>9.210000000000001</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="AF7">
-        <v>-28.99</v>
+        <v>-52.6</v>
       </c>
       <c r="AG7">
-        <v>448.7</v>
+        <v>448.67</v>
       </c>
       <c r="AH7">
-        <v>401.84</v>
+        <v>400.58</v>
       </c>
       <c r="AI7">
         <v>436.39</v>
@@ -1597,7 +1597,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>32.24</v>
+        <v>31.51</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1608,10 +1608,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>639.6</v>
+        <v>640.25</v>
       </c>
       <c r="D8">
-        <v>-1.01</v>
+        <v>0.1</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1620,46 +1620,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-20.87</v>
+        <v>-20.79</v>
       </c>
       <c r="H8">
-        <v>36.74</v>
+        <v>36.88</v>
       </c>
       <c r="I8">
-        <v>-1.13</v>
+        <v>-1.09</v>
       </c>
       <c r="J8">
-        <v>-2.03</v>
+        <v>-3.07</v>
       </c>
       <c r="K8">
-        <v>-10.28</v>
+        <v>-20.79</v>
       </c>
       <c r="L8">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="M8">
-        <v>-11.54</v>
+        <v>-12.39</v>
       </c>
       <c r="N8">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O8">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="P8">
-        <v>650.98</v>
+        <v>649.5700000000001</v>
       </c>
       <c r="Q8">
-        <v>655.66</v>
+        <v>655.4</v>
       </c>
       <c r="R8">
-        <v>688.88</v>
+        <v>687.29</v>
       </c>
       <c r="S8">
-        <v>613.42</v>
+        <v>613.53</v>
       </c>
       <c r="T8">
-        <v>4.27</v>
+        <v>4.35</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1674,43 +1674,43 @@
         <v>2</v>
       </c>
       <c r="Y8">
-        <v>36.79</v>
+        <v>37.22</v>
       </c>
       <c r="Z8">
-        <v>-10.44</v>
+        <v>-10.75</v>
       </c>
       <c r="AA8">
-        <v>-10.88</v>
+        <v>-10.85</v>
       </c>
       <c r="AB8">
-        <v>0.43</v>
+        <v>0.1</v>
       </c>
       <c r="AC8">
-        <v>34.4</v>
+        <v>13.37</v>
       </c>
       <c r="AD8">
-        <v>54.71</v>
+        <v>37.99</v>
       </c>
       <c r="AE8">
-        <v>17.23</v>
+        <v>16.67</v>
       </c>
       <c r="AF8">
-        <v>-55.49</v>
+        <v>-51.09</v>
       </c>
       <c r="AG8">
-        <v>671.53</v>
+        <v>672.13</v>
       </c>
       <c r="AH8">
-        <v>639.8</v>
+        <v>638.67</v>
       </c>
       <c r="AI8">
-        <v>698.1</v>
+        <v>690.22</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>24.11</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1721,10 +1721,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>193.88</v>
+        <v>200.64</v>
       </c>
       <c r="D9">
-        <v>3.06</v>
+        <v>3.49</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1733,46 +1733,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-30.16</v>
+        <v>-27.72</v>
       </c>
       <c r="H9">
-        <v>12.52</v>
+        <v>16.45</v>
       </c>
       <c r="I9">
-        <v>0.9</v>
+        <v>5.58</v>
       </c>
       <c r="J9">
-        <v>3.04</v>
+        <v>6.93</v>
       </c>
       <c r="K9">
-        <v>0.42</v>
+        <v>3.71</v>
       </c>
       <c r="L9">
-        <v>-25.3</v>
+        <v>-23.11</v>
       </c>
       <c r="M9">
-        <v>-6.9</v>
+        <v>-6.19</v>
       </c>
       <c r="N9">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="O9">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="P9">
-        <v>189.88</v>
+        <v>192</v>
       </c>
       <c r="Q9">
-        <v>191.57</v>
+        <v>192.3</v>
       </c>
       <c r="R9">
-        <v>189.35</v>
+        <v>189.54</v>
       </c>
       <c r="S9">
-        <v>206.86</v>
+        <v>206.5</v>
       </c>
       <c r="T9">
-        <v>-6.27</v>
+        <v>-2.84</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1787,43 +1787,43 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>56.2</v>
+        <v>65.83</v>
       </c>
       <c r="Z9">
-        <v>0.28</v>
+        <v>1.01</v>
       </c>
       <c r="AA9">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="AB9">
-        <v>-0.36</v>
+        <v>0.29</v>
       </c>
       <c r="AC9">
-        <v>20.84</v>
+        <v>54.17</v>
       </c>
       <c r="AD9">
-        <v>6.95</v>
+        <v>25</v>
       </c>
       <c r="AE9">
-        <v>4.84</v>
+        <v>5.34</v>
       </c>
       <c r="AF9">
-        <v>216.03</v>
+        <v>445.09</v>
       </c>
       <c r="AG9">
-        <v>197.97</v>
+        <v>199.36</v>
       </c>
       <c r="AH9">
-        <v>185.17</v>
+        <v>185.23</v>
       </c>
       <c r="AI9">
-        <v>197.85</v>
+        <v>182.89</v>
       </c>
       <c r="AJ9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AK9">
-        <v>26.48</v>
+        <v>31.25</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1834,10 +1834,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>75.14</v>
+        <v>74.77</v>
       </c>
       <c r="D10">
-        <v>-0.46</v>
+        <v>-0.49</v>
       </c>
       <c r="E10">
         <v>150.86</v>
@@ -1846,46 +1846,46 @@
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-50.19</v>
+        <v>-50.44</v>
       </c>
       <c r="H10">
-        <v>26.75</v>
+        <v>26.13</v>
       </c>
       <c r="I10">
-        <v>-1.82</v>
+        <v>-1.23</v>
       </c>
       <c r="J10">
-        <v>-1.98</v>
+        <v>-3.42</v>
       </c>
       <c r="K10">
-        <v>-4.69</v>
+        <v>-13.83</v>
       </c>
       <c r="L10">
-        <v>-45.68</v>
+        <v>-48.52</v>
       </c>
       <c r="M10">
-        <v>-0.93</v>
+        <v>-0.11</v>
       </c>
       <c r="N10">
         <v>12</v>
       </c>
       <c r="O10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="P10">
-        <v>75.03</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="Q10">
-        <v>76.26000000000001</v>
+        <v>76.18000000000001</v>
       </c>
       <c r="R10">
-        <v>78.84999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="S10">
-        <v>81.59</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="T10">
-        <v>-7.9</v>
+        <v>-8.27</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1900,34 +1900,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>41.56</v>
+        <v>40.1</v>
       </c>
       <c r="Z10">
-        <v>-0.99</v>
+        <v>-1</v>
       </c>
       <c r="AA10">
-        <v>-0.97</v>
+        <v>-0.98</v>
       </c>
       <c r="AB10">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="AC10">
-        <v>84.26000000000001</v>
+        <v>77.37</v>
       </c>
       <c r="AD10">
-        <v>59.28</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="AE10">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AF10">
-        <v>-16.19</v>
+        <v>14.04</v>
       </c>
       <c r="AG10">
-        <v>78.13</v>
+        <v>78.16</v>
       </c>
       <c r="AH10">
-        <v>74.40000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="AI10">
         <v>80.34</v>
@@ -1936,7 +1936,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>29.46</v>
+        <v>32.95</v>
       </c>
     </row>
   </sheetData>
@@ -2077,7 +2077,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2117,7 +2117,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2169,13 +2169,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>-1.99</v>
+        <v>-2.98</v>
       </c>
       <c r="D7" s="6">
-        <v>-2.98</v>
+        <v>-3.84</v>
       </c>
       <c r="E7" s="7">
-        <v>-0.99</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2186,13 +2186,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-0.43</v>
+        <v>-0.92</v>
       </c>
       <c r="D8" s="6">
-        <v>-0.92</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-0.49</v>
+        <v>2.42</v>
+      </c>
+      <c r="E8" s="8">
+        <v>3.34</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2203,13 +2203,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-4.34</v>
+        <v>-6.24</v>
       </c>
       <c r="D9" s="6">
-        <v>-6.24</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-1.9</v>
+        <v>-4.98</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1.26</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2220,13 +2220,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-4.41</v>
+        <v>-5.44</v>
       </c>
       <c r="D10" s="6">
-        <v>-5.44</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-1.03</v>
+        <v>-3.82</v>
+      </c>
+      <c r="E10" s="8">
+        <v>1.62</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2237,13 +2237,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-3.17</v>
+        <v>-4.66</v>
       </c>
       <c r="D11" s="6">
-        <v>-4.66</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-1.49</v>
+        <v>-3.57</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1.09</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2254,13 +2254,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-2.14</v>
+        <v>-3.86</v>
       </c>
       <c r="D12" s="6">
-        <v>-3.86</v>
+        <v>-4.14</v>
       </c>
       <c r="E12" s="7">
-        <v>-1.72</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2271,13 +2271,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-2.49</v>
+        <v>-2.03</v>
       </c>
       <c r="D13" s="6">
-        <v>-2.03</v>
-      </c>
-      <c r="E13" s="8">
-        <v>0.46</v>
+        <v>-3.07</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-1.04</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2288,13 +2288,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>0.37</v>
+        <v>3.04</v>
       </c>
       <c r="D14" s="6">
-        <v>3.04</v>
+        <v>6.93</v>
       </c>
       <c r="E14" s="8">
-        <v>2.67</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2305,13 +2305,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-0.25</v>
+        <v>-1.98</v>
       </c>
       <c r="D15" s="6">
-        <v>-1.98</v>
+        <v>-3.42</v>
       </c>
       <c r="E15" s="7">
-        <v>-1.73</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2322,13 +2322,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-1.06</v>
+        <v>-1.19</v>
       </c>
       <c r="D16" s="6">
-        <v>-1.19</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-0.13</v>
+        <v>0.16</v>
+      </c>
+      <c r="E16" s="8">
+        <v>1.35</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2339,13 +2339,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-1.26</v>
+        <v>-0.29</v>
       </c>
       <c r="D17" s="6">
-        <v>-0.29</v>
+        <v>3.58</v>
       </c>
       <c r="E17" s="8">
-        <v>0.97</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2356,13 +2356,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-2.08</v>
+        <v>-1.48</v>
       </c>
       <c r="D18" s="6">
-        <v>-1.48</v>
+        <v>1.68</v>
       </c>
       <c r="E18" s="8">
-        <v>0.6</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2373,13 +2373,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>0</v>
+        <v>-1.64</v>
       </c>
       <c r="D19" s="6">
-        <v>-1.64</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-1.64</v>
+        <v>1.21</v>
+      </c>
+      <c r="E19" s="8">
+        <v>2.85</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2390,13 +2390,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D20" s="6">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.05</v>
+        <v>0.36</v>
+      </c>
+      <c r="E20" s="8">
+        <v>0.29</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2407,13 +2407,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-0.72</v>
+        <v>-1.57</v>
       </c>
       <c r="D21" s="6">
-        <v>-1.57</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.85</v>
+        <v>0.17</v>
+      </c>
+      <c r="E21" s="8">
+        <v>1.74</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2424,13 +2424,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-1.22</v>
+        <v>-1.13</v>
       </c>
       <c r="D22" s="6">
-        <v>-1.13</v>
+        <v>-1.09</v>
       </c>
       <c r="E22" s="8">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2441,13 +2441,13 @@
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>-2.1</v>
+        <v>0.9</v>
       </c>
       <c r="D23" s="6">
-        <v>0.9</v>
+        <v>5.58</v>
       </c>
       <c r="E23" s="8">
-        <v>3</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2458,13 +2458,13 @@
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>-1.36</v>
+        <v>-1.82</v>
       </c>
       <c r="D24" s="6">
-        <v>-1.82</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.46</v>
+        <v>-1.23</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0.59</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2475,13 +2475,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>-28.67</v>
+        <v>-29.64</v>
       </c>
       <c r="D25" s="6">
-        <v>-29.64</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.97</v>
+        <v>-29.5</v>
+      </c>
+      <c r="E25" s="8">
+        <v>0.14</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2492,13 +2492,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>28.49</v>
+        <v>25.6</v>
       </c>
       <c r="D26" s="6">
-        <v>25.6</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-2.89</v>
+        <v>30.34</v>
+      </c>
+      <c r="E26" s="8">
+        <v>4.74</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2509,13 +2509,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>40.18</v>
+        <v>34.37</v>
       </c>
       <c r="D27" s="6">
-        <v>34.37</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-5.81</v>
+        <v>36.28</v>
+      </c>
+      <c r="E27" s="8">
+        <v>1.91</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2526,13 +2526,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>28.63</v>
+        <v>22.62</v>
       </c>
       <c r="D28" s="6">
-        <v>22.62</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-6.01</v>
+        <v>24.75</v>
+      </c>
+      <c r="E28" s="8">
+        <v>2.13</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2543,13 +2543,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>71.61</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="D29" s="6">
-        <v>68.06999999999999</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-3.54</v>
+        <v>71.95999999999999</v>
+      </c>
+      <c r="E29" s="8">
+        <v>3.89</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2560,13 +2560,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>-29.4</v>
+        <v>-30.66</v>
       </c>
       <c r="D30" s="6">
-        <v>-30.66</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-1.26</v>
+        <v>-29.86</v>
+      </c>
+      <c r="E30" s="8">
+        <v>0.8</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2577,13 +2577,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>3.65</v>
+        <v>1.76</v>
       </c>
       <c r="D31" s="6">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="E31" s="7">
-        <v>-1.89</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2594,13 +2594,13 @@
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>-25.13</v>
+        <v>-25.3</v>
       </c>
       <c r="D32" s="6">
-        <v>-25.3</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-0.17</v>
+        <v>-23.11</v>
+      </c>
+      <c r="E32" s="8">
+        <v>2.19</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2611,13 +2611,13 @@
         <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>-42.7</v>
+        <v>-45.68</v>
       </c>
       <c r="D33" s="6">
-        <v>-45.68</v>
+        <v>-48.52</v>
       </c>
       <c r="E33" s="7">
-        <v>-2.98</v>
+        <v>-2.84</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2628,13 +2628,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>-4.87</v>
+        <v>-7.37</v>
       </c>
       <c r="D34" s="6">
-        <v>-7.37</v>
+        <v>-7.93</v>
       </c>
       <c r="E34" s="7">
-        <v>-2.5</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2645,13 +2645,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>5.22</v>
+        <v>1.03</v>
       </c>
       <c r="D35" s="6">
-        <v>1.03</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-4.19</v>
+        <v>4.65</v>
+      </c>
+      <c r="E35" s="8">
+        <v>3.62</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2662,13 +2662,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>-6.46</v>
+        <v>-10.25</v>
       </c>
       <c r="D36" s="6">
-        <v>-10.25</v>
+        <v>-10.73</v>
       </c>
       <c r="E36" s="7">
-        <v>-3.79</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2679,13 +2679,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>-5.31</v>
+        <v>-7.29</v>
       </c>
       <c r="D37" s="6">
-        <v>-7.29</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-1.98</v>
+        <v>-6.28</v>
+      </c>
+      <c r="E37" s="8">
+        <v>1.01</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2696,13 +2696,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>-11.95</v>
+        <v>-16.7</v>
       </c>
       <c r="D38" s="6">
-        <v>-16.7</v>
+        <v>-17.11</v>
       </c>
       <c r="E38" s="7">
-        <v>-4.75</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2713,13 +2713,13 @@
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>-5.75</v>
+        <v>-8.66</v>
       </c>
       <c r="D39" s="6">
-        <v>-8.66</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="E39" s="7">
-        <v>-2.91</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2730,13 +2730,13 @@
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>-1.95</v>
+        <v>-10.28</v>
       </c>
       <c r="D40" s="6">
-        <v>-10.28</v>
+        <v>-20.79</v>
       </c>
       <c r="E40" s="7">
-        <v>-8.33</v>
+        <v>-10.51</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2747,13 +2747,13 @@
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>-2.56</v>
+        <v>0.42</v>
       </c>
       <c r="D41" s="6">
-        <v>0.42</v>
+        <v>3.71</v>
       </c>
       <c r="E41" s="8">
-        <v>2.98</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2764,13 +2764,13 @@
         <v>10</v>
       </c>
       <c r="C42" s="6">
-        <v>-3.58</v>
+        <v>-4.69</v>
       </c>
       <c r="D42" s="6">
-        <v>-4.69</v>
+        <v>-13.83</v>
       </c>
       <c r="E42" s="7">
-        <v>-1.11</v>
+        <v>-9.140000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2781,13 +2781,13 @@
         <v>6</v>
       </c>
       <c r="C43" s="6">
-        <v>-31.29</v>
+        <v>-31.63</v>
       </c>
       <c r="D43" s="6">
-        <v>-31.63</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-0.34</v>
+        <v>-31.37</v>
+      </c>
+      <c r="E43" s="8">
+        <v>0.26</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2798,13 +2798,13 @@
         <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-6.7</v>
+        <v>-6.65</v>
       </c>
       <c r="D44" s="6">
-        <v>-6.65</v>
+        <v>-3.18</v>
       </c>
       <c r="E44" s="8">
-        <v>0.05</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2815,13 +2815,13 @@
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-17.73</v>
+        <v>-18.48</v>
       </c>
       <c r="D45" s="6">
-        <v>-18.48</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-0.75</v>
+        <v>-17.11</v>
+      </c>
+      <c r="E45" s="8">
+        <v>1.37</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2832,13 +2832,13 @@
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-9.73</v>
+        <v>-11.21</v>
       </c>
       <c r="D46" s="6">
-        <v>-11.21</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-1.48</v>
+        <v>-9.58</v>
+      </c>
+      <c r="E46" s="8">
+        <v>1.63</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2849,13 +2849,13 @@
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-17.44</v>
+        <v>-18.16</v>
       </c>
       <c r="D47" s="6">
-        <v>-18.16</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-0.72</v>
+        <v>-17.11</v>
+      </c>
+      <c r="E47" s="8">
+        <v>1.05</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2866,13 +2866,13 @@
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-29.68</v>
+        <v>-30.6</v>
       </c>
       <c r="D48" s="6">
-        <v>-30.6</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-0.92</v>
+        <v>-29.83</v>
+      </c>
+      <c r="E48" s="8">
+        <v>0.77</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2883,13 +2883,13 @@
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-20.06</v>
+        <v>-20.87</v>
       </c>
       <c r="D49" s="6">
-        <v>-20.87</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-0.8100000000000001</v>
+        <v>-20.79</v>
+      </c>
+      <c r="E49" s="8">
+        <v>0.08</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2900,13 +2900,13 @@
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-32.23</v>
+        <v>-30.16</v>
       </c>
       <c r="D50" s="6">
-        <v>-30.16</v>
+        <v>-27.72</v>
       </c>
       <c r="E50" s="8">
-        <v>2.07</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2917,13 +2917,13 @@
         <v>6</v>
       </c>
       <c r="C51" s="6">
-        <v>-49.96</v>
+        <v>-50.19</v>
       </c>
       <c r="D51" s="6">
-        <v>-50.19</v>
+        <v>-50.44</v>
       </c>
       <c r="E51" s="7">
-        <v>-0.23</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2934,13 +2934,13 @@
         <v>2</v>
       </c>
       <c r="C52" s="6">
-        <v>1307.4</v>
+        <v>1300.9</v>
       </c>
       <c r="D52" s="6">
-        <v>1300.9</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-6.5</v>
+        <v>1305.9</v>
+      </c>
+      <c r="E52" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2951,13 +2951,13 @@
         <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>2997</v>
+        <v>2998.6</v>
       </c>
       <c r="D53" s="6">
-        <v>2998.6</v>
+        <v>3110</v>
       </c>
       <c r="E53" s="8">
-        <v>1.6</v>
+        <v>111.4</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2968,13 +2968,13 @@
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>1320</v>
+        <v>1308</v>
       </c>
       <c r="D54" s="6">
-        <v>1308</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-12</v>
+        <v>1330</v>
+      </c>
+      <c r="E54" s="8">
+        <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>1700</v>
+        <v>1672.1</v>
       </c>
       <c r="D55" s="6">
-        <v>1672.1</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-27.9</v>
+        <v>1702.7</v>
+      </c>
+      <c r="E55" s="8">
+        <v>30.6</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -3002,13 +3002,13 @@
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>205.5</v>
+        <v>203.7</v>
       </c>
       <c r="D56" s="6">
-        <v>203.7</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-1.8</v>
+        <v>206.33</v>
+      </c>
+      <c r="E56" s="8">
+        <v>2.63</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -3019,13 +3019,13 @@
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>414.5</v>
+        <v>408.75</v>
       </c>
       <c r="D57" s="6">
-        <v>408.75</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-5.75</v>
+        <v>413.1</v>
+      </c>
+      <c r="E57" s="8">
+        <v>4.35</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -3036,13 +3036,13 @@
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>646.1</v>
+        <v>639.6</v>
       </c>
       <c r="D58" s="6">
-        <v>639.6</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-6.5</v>
+        <v>640.25</v>
+      </c>
+      <c r="E58" s="8">
+        <v>0.65</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -3053,13 +3053,13 @@
         <v>2</v>
       </c>
       <c r="C59" s="6">
-        <v>188.12</v>
+        <v>193.88</v>
       </c>
       <c r="D59" s="6">
-        <v>193.88</v>
+        <v>200.64</v>
       </c>
       <c r="E59" s="8">
-        <v>5.76</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -3070,319 +3070,353 @@
         <v>2</v>
       </c>
       <c r="C60" s="6">
-        <v>75.48999999999999</v>
+        <v>75.14</v>
       </c>
       <c r="D60" s="6">
-        <v>75.14</v>
+        <v>74.77</v>
       </c>
       <c r="E60" s="7">
-        <v>-0.35</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C61" s="6">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="D61" s="6">
-        <v>38.47</v>
+        <v>45</v>
       </c>
       <c r="E61" s="7">
-        <v>-1.53</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C62" s="6">
-        <v>45.61</v>
+        <v>45</v>
       </c>
       <c r="D62" s="6">
-        <v>45.89</v>
+        <v>55</v>
       </c>
       <c r="E62" s="8">
-        <v>0.28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C63" s="6">
-        <v>38.11</v>
+        <v>38.47</v>
       </c>
       <c r="D63" s="6">
-        <v>36.28</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-1.83</v>
+        <v>40.36</v>
+      </c>
+      <c r="E63" s="8">
+        <v>1.89</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C64" s="6">
-        <v>44.46</v>
+        <v>45.89</v>
       </c>
       <c r="D64" s="6">
-        <v>38.48</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-5.98</v>
+        <v>60.91</v>
+      </c>
+      <c r="E64" s="8">
+        <v>15.02</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C65" s="6">
-        <v>40.85</v>
+        <v>36.28</v>
       </c>
       <c r="D65" s="6">
-        <v>38.09</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-2.76</v>
+        <v>41.8</v>
+      </c>
+      <c r="E65" s="8">
+        <v>5.52</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="6">
-        <v>41.66</v>
+        <v>38.48</v>
       </c>
       <c r="D66" s="6">
-        <v>38</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-3.66</v>
+        <v>46.91</v>
+      </c>
+      <c r="E66" s="8">
+        <v>8.43</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="6">
-        <v>39.26</v>
+        <v>38.09</v>
       </c>
       <c r="D67" s="6">
-        <v>36.79</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-2.47</v>
+        <v>44.05</v>
+      </c>
+      <c r="E67" s="8">
+        <v>5.96</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="6">
-        <v>43.63</v>
+        <v>38</v>
       </c>
       <c r="D68" s="6">
-        <v>56.2</v>
+        <v>42.14</v>
       </c>
       <c r="E68" s="8">
-        <v>12.57</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="6">
-        <v>42.93</v>
+        <v>36.79</v>
       </c>
       <c r="D69" s="6">
-        <v>41.56</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-1.37</v>
+        <v>37.22</v>
+      </c>
+      <c r="E69" s="8">
+        <v>0.43</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C70" s="6">
-        <v>-39.31</v>
+        <v>56.2</v>
       </c>
       <c r="D70" s="6">
-        <v>-54.73</v>
-      </c>
-      <c r="E70" s="7">
-        <v>-15.42</v>
+        <v>65.83</v>
+      </c>
+      <c r="E70" s="8">
+        <v>9.630000000000001</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C71" s="6">
-        <v>-24.05</v>
+        <v>41.56</v>
       </c>
       <c r="D71" s="6">
-        <v>-18.42</v>
-      </c>
-      <c r="E71" s="8">
-        <v>5.63</v>
+        <v>40.1</v>
+      </c>
+      <c r="E71" s="7">
+        <v>-1.46</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C72" s="6">
-        <v>-42.73</v>
+        <v>-54.73</v>
       </c>
       <c r="D72" s="6">
-        <v>-59.02</v>
+        <v>-58.24</v>
       </c>
       <c r="E72" s="7">
-        <v>-16.29</v>
+        <v>-3.51</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C73" s="6">
-        <v>-51.21</v>
+        <v>-18.42</v>
       </c>
       <c r="D73" s="6">
-        <v>-52.05</v>
-      </c>
-      <c r="E73" s="7">
-        <v>-0.84</v>
+        <v>102.42</v>
+      </c>
+      <c r="E73" s="8">
+        <v>120.84</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C74" s="6">
-        <v>-35.46</v>
+        <v>-59.02</v>
       </c>
       <c r="D74" s="6">
-        <v>-37.03</v>
-      </c>
-      <c r="E74" s="7">
-        <v>-1.57</v>
+        <v>65.38</v>
+      </c>
+      <c r="E74" s="8">
+        <v>124.4</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="6">
-        <v>91.95</v>
+        <v>-52.05</v>
       </c>
       <c r="D75" s="6">
-        <v>-28.99</v>
-      </c>
-      <c r="E75" s="7">
-        <v>-120.94</v>
+        <v>-40.56</v>
+      </c>
+      <c r="E75" s="8">
+        <v>11.49</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="6">
-        <v>-26.53</v>
+        <v>-37.03</v>
       </c>
       <c r="D76" s="6">
-        <v>-55.49</v>
-      </c>
-      <c r="E76" s="7">
-        <v>-28.96</v>
+        <v>0.72</v>
+      </c>
+      <c r="E76" s="8">
+        <v>37.75</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="6">
-        <v>156.98</v>
+        <v>-28.99</v>
       </c>
       <c r="D77" s="6">
-        <v>216.03</v>
-      </c>
-      <c r="E77" s="8">
-        <v>59.05</v>
+        <v>-52.6</v>
+      </c>
+      <c r="E77" s="7">
+        <v>-23.61</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="6">
-        <v>-18.13</v>
+        <v>-55.49</v>
       </c>
       <c r="D78" s="6">
+        <v>-51.09</v>
+      </c>
+      <c r="E78" s="8">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
+        <v>216.03</v>
+      </c>
+      <c r="D79" s="6">
+        <v>445.09</v>
+      </c>
+      <c r="E79" s="8">
+        <v>229.06</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="6">
         <v>-16.19</v>
       </c>
-      <c r="E78" s="8">
-        <v>1.94</v>
+      <c r="D80" s="6">
+        <v>14.04</v>
+      </c>
+      <c r="E80" s="8">
+        <v>30.23</v>
       </c>
     </row>
   </sheetData>
@@ -3447,16 +3481,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>41.1</v>
+        <v>46.6</v>
       </c>
       <c r="E2" s="11">
         <v>60</v>
       </c>
       <c r="F2" s="11">
-        <v>-2.8</v>
+        <v>-1.9</v>
       </c>
       <c r="G2" s="11">
-        <v>-7.1</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="H2" s="11">
         <v>55.4</v>
@@ -3593,31 +3627,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.6751</v>
+        <v>0.6631999999999999</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1983</v>
+        <v>0.194</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1589</v>
+        <v>0.1614</v>
       </c>
       <c r="D2" s="14">
-        <v>0.06610000000000001</v>
+        <v>0.0593</v>
       </c>
       <c r="E2" s="14">
-        <v>0.0145</v>
+        <v>0.0157</v>
       </c>
       <c r="F2" s="14">
-        <v>-0.009300000000000001</v>
+        <v>-0.0011</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.06900000000000001</v>
+        <v>-0.0619</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.09810000000000001</v>
+        <v>-0.0964</v>
       </c>
       <c r="I2" s="14">
-        <v>-0.1154</v>
+        <v>-0.1239</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="66">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,34 +178,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>45.9 → 60.9</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>45.9</t>
-  </si>
-  <si>
-    <t>60.9</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -407,18 +380,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -930,10 +902,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1305.9</v>
+        <v>1331.7</v>
       </c>
       <c r="D2">
-        <v>0.38</v>
+        <v>1.98</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -942,46 +914,46 @@
         <v>1247.38</v>
       </c>
       <c r="G2">
-        <v>-31.37</v>
+        <v>-30.01</v>
       </c>
       <c r="H2">
-        <v>4.69</v>
+        <v>6.76</v>
       </c>
       <c r="I2">
-        <v>0.16</v>
+        <v>3.34</v>
       </c>
       <c r="J2">
-        <v>-3.84</v>
+        <v>-0.75</v>
       </c>
       <c r="K2">
-        <v>-7.93</v>
+        <v>-6.11</v>
       </c>
       <c r="L2">
-        <v>-29.5</v>
+        <v>-27.6</v>
       </c>
       <c r="M2">
-        <v>-9.640000000000001</v>
+        <v>-9.35</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="P2">
-        <v>1300.8</v>
+        <v>1309.4</v>
       </c>
       <c r="Q2">
-        <v>1340.17</v>
+        <v>1338.21</v>
       </c>
       <c r="R2">
-        <v>1350.94</v>
+        <v>1350.59</v>
       </c>
       <c r="S2">
-        <v>1513.75</v>
+        <v>1511.26</v>
       </c>
       <c r="T2">
-        <v>-13.73</v>
+        <v>-11.88</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -996,34 +968,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>40.36</v>
+        <v>49.03</v>
       </c>
       <c r="Z2">
-        <v>-16.8</v>
+        <v>-14.43</v>
       </c>
       <c r="AA2">
-        <v>-12.52</v>
+        <v>-12.9</v>
       </c>
       <c r="AB2">
-        <v>-4.27</v>
+        <v>-1.52</v>
       </c>
       <c r="AC2">
-        <v>29.32</v>
+        <v>53</v>
       </c>
       <c r="AD2">
-        <v>22.76</v>
+        <v>35.18</v>
       </c>
       <c r="AE2">
-        <v>24.19</v>
+        <v>24.76</v>
       </c>
       <c r="AF2">
-        <v>-58.24</v>
+        <v>5.13</v>
       </c>
       <c r="AG2">
-        <v>1408.98</v>
+        <v>1405.57</v>
       </c>
       <c r="AH2">
-        <v>1271.35</v>
+        <v>1270.85</v>
       </c>
       <c r="AI2">
         <v>1373.07</v>
@@ -1032,7 +1004,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>38.4</v>
+        <v>34.31</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,10 +1015,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3110</v>
+        <v>3112</v>
       </c>
       <c r="D3">
-        <v>3.72</v>
+        <v>0.06</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1055,25 +1027,25 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-3.18</v>
+        <v>-3.12</v>
       </c>
       <c r="H3">
-        <v>76.90000000000001</v>
+        <v>77.02</v>
       </c>
       <c r="I3">
-        <v>3.58</v>
+        <v>4.07</v>
       </c>
       <c r="J3">
-        <v>2.42</v>
+        <v>3.65</v>
       </c>
       <c r="K3">
-        <v>4.65</v>
+        <v>4.72</v>
       </c>
       <c r="L3">
-        <v>30.34</v>
+        <v>30.97</v>
       </c>
       <c r="M3">
-        <v>16.14</v>
+        <v>16.15</v>
       </c>
       <c r="N3">
         <v>88</v>
@@ -1082,19 +1054,19 @@
         <v>75</v>
       </c>
       <c r="P3">
-        <v>3018.16</v>
+        <v>3042.5</v>
       </c>
       <c r="Q3">
-        <v>3019.45</v>
+        <v>3023.82</v>
       </c>
       <c r="R3">
-        <v>3060.36</v>
+        <v>3063.72</v>
       </c>
       <c r="S3">
-        <v>2487.86</v>
+        <v>2491.58</v>
       </c>
       <c r="T3">
-        <v>25.01</v>
+        <v>24.9</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1109,34 +1081,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>60.91</v>
+        <v>61.12</v>
       </c>
       <c r="Z3">
-        <v>-6.6</v>
+        <v>1.05</v>
       </c>
       <c r="AA3">
-        <v>-12.51</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="AB3">
-        <v>5.91</v>
+        <v>10.85</v>
       </c>
       <c r="AC3">
-        <v>72.28</v>
+        <v>86.61</v>
       </c>
       <c r="AD3">
-        <v>58.86</v>
+        <v>71.33</v>
       </c>
       <c r="AE3">
-        <v>65.7</v>
+        <v>66.16</v>
       </c>
       <c r="AF3">
-        <v>102.42</v>
+        <v>91.84</v>
       </c>
       <c r="AG3">
-        <v>3086.44</v>
+        <v>3102.6</v>
       </c>
       <c r="AH3">
-        <v>2952.45</v>
+        <v>2945.04</v>
       </c>
       <c r="AI3">
         <v>2959.69</v>
@@ -1145,7 +1117,7 @@
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>25.44</v>
+        <v>28.77</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1128,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1330</v>
+        <v>1303.2</v>
       </c>
       <c r="D4">
-        <v>1.68</v>
+        <v>-2.02</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1168,46 +1140,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-17.11</v>
+        <v>-18.78</v>
       </c>
       <c r="H4">
-        <v>72.09999999999999</v>
+        <v>68.63</v>
       </c>
       <c r="I4">
-        <v>1.68</v>
+        <v>0.79</v>
       </c>
       <c r="J4">
-        <v>-4.98</v>
+        <v>-5.41</v>
       </c>
       <c r="K4">
-        <v>-10.73</v>
+        <v>-12.53</v>
       </c>
       <c r="L4">
-        <v>36.28</v>
+        <v>34.82</v>
       </c>
       <c r="M4">
-        <v>5.93</v>
+        <v>4.49</v>
       </c>
       <c r="N4">
         <v>77</v>
       </c>
       <c r="O4">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="P4">
-        <v>1310.56</v>
+        <v>1312.6</v>
       </c>
       <c r="Q4">
-        <v>1347.02</v>
+        <v>1343.52</v>
       </c>
       <c r="R4">
-        <v>1442.17</v>
+        <v>1438.58</v>
       </c>
       <c r="S4">
-        <v>1167.87</v>
+        <v>1169.09</v>
       </c>
       <c r="T4">
-        <v>13.88</v>
+        <v>11.47</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1222,34 +1194,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>41.8</v>
+        <v>37.53</v>
       </c>
       <c r="Z4">
-        <v>-35.98</v>
+        <v>-35.51</v>
       </c>
       <c r="AA4">
-        <v>-37.51</v>
+        <v>-37.11</v>
       </c>
       <c r="AB4">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AC4">
-        <v>82.65000000000001</v>
+        <v>75.48</v>
       </c>
       <c r="AD4">
-        <v>58.83</v>
+        <v>71.91</v>
       </c>
       <c r="AE4">
-        <v>36.54</v>
+        <v>37.05</v>
       </c>
       <c r="AF4">
-        <v>65.38</v>
+        <v>62.32</v>
       </c>
       <c r="AG4">
-        <v>1410.87</v>
+        <v>1408.99</v>
       </c>
       <c r="AH4">
-        <v>1283.17</v>
+        <v>1278.06</v>
       </c>
       <c r="AI4">
         <v>1418.72</v>
@@ -1258,7 +1230,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>29.1</v>
+        <v>25.34</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1241,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1702.7</v>
+        <v>1691.5</v>
       </c>
       <c r="D5">
-        <v>1.83</v>
+        <v>-0.66</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1281,46 +1253,46 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-9.58</v>
+        <v>-10.18</v>
       </c>
       <c r="H5">
-        <v>31.17</v>
+        <v>30.3</v>
       </c>
       <c r="I5">
-        <v>1.21</v>
+        <v>0.57</v>
       </c>
       <c r="J5">
-        <v>-3.82</v>
+        <v>-4.69</v>
       </c>
       <c r="K5">
-        <v>-6.28</v>
+        <v>-6.9</v>
       </c>
       <c r="L5">
-        <v>24.75</v>
+        <v>24.73</v>
       </c>
       <c r="M5">
-        <v>19.4</v>
+        <v>19.22</v>
       </c>
       <c r="N5">
         <v>66</v>
       </c>
       <c r="O5">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="P5">
-        <v>1690.54</v>
+        <v>1692.46</v>
       </c>
       <c r="Q5">
-        <v>1689.19</v>
+        <v>1687.78</v>
       </c>
       <c r="R5">
-        <v>1767.39</v>
+        <v>1764.78</v>
       </c>
       <c r="S5">
-        <v>1593.94</v>
+        <v>1595.18</v>
       </c>
       <c r="T5">
-        <v>6.82</v>
+        <v>6.04</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1335,34 +1307,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>46.91</v>
+        <v>44.51</v>
       </c>
       <c r="Z5">
-        <v>-21.27</v>
+        <v>-19.8</v>
       </c>
       <c r="AA5">
-        <v>-26.38</v>
+        <v>-25.07</v>
       </c>
       <c r="AB5">
-        <v>5.12</v>
+        <v>5.27</v>
       </c>
       <c r="AC5">
-        <v>86.18000000000001</v>
+        <v>81.42</v>
       </c>
       <c r="AD5">
-        <v>87.68000000000001</v>
+        <v>84.59</v>
       </c>
       <c r="AE5">
-        <v>31.96</v>
+        <v>31.77</v>
       </c>
       <c r="AF5">
-        <v>-40.56</v>
+        <v>-9.35</v>
       </c>
       <c r="AG5">
-        <v>1722.48</v>
+        <v>1717.87</v>
       </c>
       <c r="AH5">
-        <v>1655.9</v>
+        <v>1657.69</v>
       </c>
       <c r="AI5">
         <v>1761.08</v>
@@ -1371,7 +1343,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>23.63</v>
+        <v>23.56</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,10 +1354,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>206.33</v>
+        <v>207.2</v>
       </c>
       <c r="D6">
-        <v>1.29</v>
+        <v>0.42</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1394,25 +1366,25 @@
         <v>118.42</v>
       </c>
       <c r="G6">
-        <v>-17.11</v>
+        <v>-16.76</v>
       </c>
       <c r="H6">
-        <v>74.23999999999999</v>
+        <v>74.97</v>
       </c>
       <c r="I6">
-        <v>0.36</v>
+        <v>1.56</v>
       </c>
       <c r="J6">
-        <v>-3.57</v>
+        <v>-0.5</v>
       </c>
       <c r="K6">
-        <v>-17.11</v>
+        <v>-16.76</v>
       </c>
       <c r="L6">
-        <v>71.95999999999999</v>
+        <v>73.77</v>
       </c>
       <c r="M6">
-        <v>66.31999999999999</v>
+        <v>64.84</v>
       </c>
       <c r="N6">
         <v>99</v>
@@ -1421,19 +1393,19 @@
         <v>82</v>
       </c>
       <c r="P6">
-        <v>204.71</v>
+        <v>205.35</v>
       </c>
       <c r="Q6">
-        <v>207.51</v>
+        <v>207.39</v>
       </c>
       <c r="R6">
-        <v>215.8</v>
+        <v>215.49</v>
       </c>
       <c r="S6">
-        <v>180.57</v>
+        <v>180.85</v>
       </c>
       <c r="T6">
-        <v>14.27</v>
+        <v>14.57</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1448,34 +1420,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>44.05</v>
+        <v>45.9</v>
       </c>
       <c r="Z6">
-        <v>-3.05</v>
+        <v>-2.74</v>
       </c>
       <c r="AA6">
-        <v>-3.31</v>
+        <v>-3.19</v>
       </c>
       <c r="AB6">
-        <v>0.26</v>
+        <v>0.46</v>
       </c>
       <c r="AC6">
-        <v>66.14</v>
+        <v>77.92</v>
       </c>
       <c r="AD6">
-        <v>47.23</v>
+        <v>61.3</v>
       </c>
       <c r="AE6">
-        <v>4.58</v>
+        <v>4.76</v>
       </c>
       <c r="AF6">
-        <v>0.72</v>
+        <v>62.88</v>
       </c>
       <c r="AG6">
-        <v>213.17</v>
+        <v>212.98</v>
       </c>
       <c r="AH6">
-        <v>201.85</v>
+        <v>201.81</v>
       </c>
       <c r="AI6">
         <v>217.63</v>
@@ -1484,7 +1456,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>21.13</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1495,10 +1467,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>413.1</v>
+        <v>419.2</v>
       </c>
       <c r="D7">
-        <v>1.06</v>
+        <v>1.48</v>
       </c>
       <c r="E7">
         <v>588.6900000000001</v>
@@ -1507,46 +1479,46 @@
         <v>393.4</v>
       </c>
       <c r="G7">
-        <v>-29.83</v>
+        <v>-28.79</v>
       </c>
       <c r="H7">
-        <v>5.01</v>
+        <v>6.56</v>
       </c>
       <c r="I7">
-        <v>0.17</v>
+        <v>2.87</v>
       </c>
       <c r="J7">
-        <v>-4.14</v>
+        <v>-1.6</v>
       </c>
       <c r="K7">
-        <v>-9.699999999999999</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="L7">
-        <v>-29.86</v>
+        <v>-28.45</v>
       </c>
       <c r="M7">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="N7">
         <v>23</v>
       </c>
       <c r="O7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P7">
-        <v>410.97</v>
+        <v>413.31</v>
       </c>
       <c r="Q7">
-        <v>424.62</v>
+        <v>423.82</v>
       </c>
       <c r="R7">
-        <v>427.54</v>
+        <v>427.41</v>
       </c>
       <c r="S7">
-        <v>474.47</v>
+        <v>473.78</v>
       </c>
       <c r="T7">
-        <v>-12.93</v>
+        <v>-11.52</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1561,34 +1533,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>42.14</v>
+        <v>47.45</v>
       </c>
       <c r="Z7">
-        <v>-5.7</v>
+        <v>-5.07</v>
       </c>
       <c r="AA7">
-        <v>-4.16</v>
+        <v>-4.34</v>
       </c>
       <c r="AB7">
-        <v>-1.55</v>
+        <v>-0.74</v>
       </c>
       <c r="AC7">
-        <v>29.09</v>
+        <v>46.18</v>
       </c>
       <c r="AD7">
-        <v>21.3</v>
+        <v>31.67</v>
       </c>
       <c r="AE7">
-        <v>9.130000000000001</v>
+        <v>9.24</v>
       </c>
       <c r="AF7">
-        <v>-52.6</v>
+        <v>-12.28</v>
       </c>
       <c r="AG7">
-        <v>448.67</v>
+        <v>447.44</v>
       </c>
       <c r="AH7">
-        <v>400.58</v>
+        <v>400.2</v>
       </c>
       <c r="AI7">
         <v>436.39</v>
@@ -1597,7 +1569,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>31.51</v>
+        <v>29.23</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1608,10 +1580,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>640.25</v>
+        <v>643.7</v>
       </c>
       <c r="D8">
-        <v>0.1</v>
+        <v>0.54</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1620,46 +1592,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-20.79</v>
+        <v>-20.36</v>
       </c>
       <c r="H8">
-        <v>36.88</v>
+        <v>37.62</v>
       </c>
       <c r="I8">
-        <v>-1.09</v>
+        <v>-3.09</v>
       </c>
       <c r="J8">
-        <v>-3.07</v>
+        <v>-0.29</v>
       </c>
       <c r="K8">
-        <v>-20.79</v>
+        <v>-20.36</v>
       </c>
       <c r="L8">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="M8">
-        <v>-12.39</v>
+        <v>-13.14</v>
       </c>
       <c r="N8">
         <v>45</v>
       </c>
       <c r="O8">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="P8">
-        <v>649.5700000000001</v>
+        <v>645.46</v>
       </c>
       <c r="Q8">
-        <v>655.4</v>
+        <v>654.79</v>
       </c>
       <c r="R8">
-        <v>687.29</v>
+        <v>685.89</v>
       </c>
       <c r="S8">
-        <v>613.53</v>
+        <v>613.6900000000001</v>
       </c>
       <c r="T8">
-        <v>4.35</v>
+        <v>4.89</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1674,34 +1646,34 @@
         <v>2</v>
       </c>
       <c r="Y8">
-        <v>37.22</v>
+        <v>39.54</v>
       </c>
       <c r="Z8">
-        <v>-10.75</v>
+        <v>-10.6</v>
       </c>
       <c r="AA8">
-        <v>-10.85</v>
+        <v>-10.8</v>
       </c>
       <c r="AB8">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="AC8">
-        <v>13.37</v>
+        <v>14.22</v>
       </c>
       <c r="AD8">
-        <v>37.99</v>
+        <v>20.66</v>
       </c>
       <c r="AE8">
-        <v>16.67</v>
+        <v>16.58</v>
       </c>
       <c r="AF8">
-        <v>-51.09</v>
+        <v>-24.58</v>
       </c>
       <c r="AG8">
-        <v>672.13</v>
+        <v>672.3099999999999</v>
       </c>
       <c r="AH8">
-        <v>638.67</v>
+        <v>637.26</v>
       </c>
       <c r="AI8">
         <v>690.22</v>
@@ -1710,7 +1682,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>21.9</v>
+        <v>20.57</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1721,10 +1693,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>200.64</v>
+        <v>201.9</v>
       </c>
       <c r="D9">
-        <v>3.49</v>
+        <v>0.63</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1733,46 +1705,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-27.72</v>
+        <v>-27.27</v>
       </c>
       <c r="H9">
-        <v>16.45</v>
+        <v>17.18</v>
       </c>
       <c r="I9">
-        <v>5.58</v>
+        <v>6.98</v>
       </c>
       <c r="J9">
-        <v>6.93</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="K9">
-        <v>3.71</v>
+        <v>4.36</v>
       </c>
       <c r="L9">
-        <v>-23.11</v>
+        <v>-22.35</v>
       </c>
       <c r="M9">
-        <v>-6.19</v>
+        <v>-6.06</v>
       </c>
       <c r="N9">
         <v>55</v>
       </c>
       <c r="O9">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P9">
-        <v>192</v>
+        <v>194.64</v>
       </c>
       <c r="Q9">
-        <v>192.3</v>
+        <v>192.9</v>
       </c>
       <c r="R9">
-        <v>189.54</v>
+        <v>189.63</v>
       </c>
       <c r="S9">
-        <v>206.5</v>
+        <v>206.16</v>
       </c>
       <c r="T9">
-        <v>-2.84</v>
+        <v>-2.07</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1787,43 +1759,43 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>65.83</v>
+        <v>67.27</v>
       </c>
       <c r="Z9">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="AA9">
-        <v>0.71</v>
+        <v>0.91</v>
       </c>
       <c r="AB9">
-        <v>0.29</v>
+        <v>0.77</v>
       </c>
       <c r="AC9">
+        <v>87.51000000000001</v>
+      </c>
+      <c r="AD9">
         <v>54.17</v>
       </c>
-      <c r="AD9">
-        <v>25</v>
-      </c>
       <c r="AE9">
-        <v>5.34</v>
+        <v>5.33</v>
       </c>
       <c r="AF9">
-        <v>445.09</v>
+        <v>22.36</v>
       </c>
       <c r="AG9">
-        <v>199.36</v>
+        <v>201.06</v>
       </c>
       <c r="AH9">
-        <v>185.23</v>
+        <v>184.73</v>
       </c>
       <c r="AI9">
-        <v>182.89</v>
+        <v>185.88</v>
       </c>
       <c r="AJ9" t="s">
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>31.25</v>
+        <v>35.39</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1834,37 +1806,37 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>74.77</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="D10">
-        <v>-0.49</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E10">
-        <v>150.86</v>
+        <v>148.9</v>
       </c>
       <c r="F10">
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-50.44</v>
+        <v>-50.07</v>
       </c>
       <c r="H10">
-        <v>26.13</v>
+        <v>25.42</v>
       </c>
       <c r="I10">
-        <v>-1.23</v>
+        <v>1.38</v>
       </c>
       <c r="J10">
-        <v>-3.42</v>
+        <v>-2.79</v>
       </c>
       <c r="K10">
-        <v>-13.83</v>
+        <v>-14.31</v>
       </c>
       <c r="L10">
-        <v>-48.52</v>
+        <v>-50.72</v>
       </c>
       <c r="M10">
-        <v>-0.11</v>
+        <v>-1.06</v>
       </c>
       <c r="N10">
         <v>12</v>
@@ -1873,19 +1845,19 @@
         <v>5</v>
       </c>
       <c r="P10">
-        <v>74.84999999999999</v>
+        <v>75.05</v>
       </c>
       <c r="Q10">
-        <v>76.18000000000001</v>
+        <v>76.09</v>
       </c>
       <c r="R10">
-        <v>78.7</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="S10">
-        <v>81.51000000000001</v>
+        <v>81.45</v>
       </c>
       <c r="T10">
-        <v>-8.27</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1900,34 +1872,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>40.1</v>
+        <v>38.46</v>
       </c>
       <c r="Z10">
-        <v>-1</v>
+        <v>-1.03</v>
       </c>
       <c r="AA10">
-        <v>-0.98</v>
+        <v>-0.99</v>
       </c>
       <c r="AB10">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="AC10">
-        <v>77.37</v>
+        <v>67.23999999999999</v>
       </c>
       <c r="AD10">
-        <v>73.34999999999999</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="AE10">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="AF10">
-        <v>14.04</v>
+        <v>85.36</v>
       </c>
       <c r="AG10">
-        <v>78.16</v>
+        <v>78.23</v>
       </c>
       <c r="AH10">
-        <v>74.2</v>
+        <v>73.94</v>
       </c>
       <c r="AI10">
         <v>80.34</v>
@@ -1936,7 +1908,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>32.95</v>
+        <v>36.63</v>
       </c>
     </row>
   </sheetData>
@@ -2077,7 +2049,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2097,47 +2069,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -2145,1278 +2082,1244 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>66</v>
+      <c r="B6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-2.98</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-3.84</v>
       </c>
-      <c r="E7" s="7">
-        <v>-0.86</v>
+      <c r="D7" s="5">
+        <v>-0.75</v>
+      </c>
+      <c r="E7" s="6">
+        <v>3.09</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-0.92</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>2.42</v>
       </c>
-      <c r="E8" s="8">
+      <c r="D8" s="5">
+        <v>3.65</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-4.98</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-5.41</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-3.82</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-4.69</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-3.57</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-0.5</v>
+      </c>
+      <c r="E11" s="6">
+        <v>3.07</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-4.14</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-1.6</v>
+      </c>
+      <c r="E12" s="6">
+        <v>2.54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-3.07</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-0.29</v>
+      </c>
+      <c r="E13" s="6">
+        <v>2.78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="5">
+        <v>6.93</v>
+      </c>
+      <c r="D14" s="5">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="E14" s="6">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-3.42</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-2.79</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0.16</v>
+      </c>
+      <c r="D16" s="5">
         <v>3.34</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="E16" s="6">
+        <v>3.18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>3.58</v>
+      </c>
+      <c r="D17" s="5">
+        <v>4.07</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-6.24</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-4.98</v>
-      </c>
-      <c r="E9" s="8">
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>1.68</v>
+      </c>
+      <c r="D18" s="5">
+        <v>0.79</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>1.21</v>
+      </c>
+      <c r="D19" s="5">
+        <v>0.57</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>0.36</v>
+      </c>
+      <c r="D20" s="5">
+        <v>1.56</v>
+      </c>
+      <c r="E20" s="6">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5">
+        <v>0.17</v>
+      </c>
+      <c r="D21" s="5">
+        <v>2.87</v>
+      </c>
+      <c r="E21" s="6">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-1.09</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-3.09</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="5">
+        <v>5.58</v>
+      </c>
+      <c r="D23" s="5">
+        <v>6.98</v>
+      </c>
+      <c r="E23" s="6">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-1.23</v>
+      </c>
+      <c r="D24" s="5">
+        <v>1.38</v>
+      </c>
+      <c r="E24" s="6">
+        <v>2.61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-29.5</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-27.6</v>
+      </c>
+      <c r="E25" s="6">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>30.34</v>
+      </c>
+      <c r="D26" s="5">
+        <v>30.97</v>
+      </c>
+      <c r="E26" s="6">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>36.28</v>
+      </c>
+      <c r="D27" s="5">
+        <v>34.82</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-1.46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="5">
+        <v>24.75</v>
+      </c>
+      <c r="D28" s="5">
+        <v>24.73</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="5">
+        <v>71.95999999999999</v>
+      </c>
+      <c r="D29" s="5">
+        <v>73.77</v>
+      </c>
+      <c r="E29" s="6">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-29.86</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-28.45</v>
+      </c>
+      <c r="E30" s="6">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="5">
+        <v>1.6</v>
+      </c>
+      <c r="D31" s="5">
+        <v>4.2</v>
+      </c>
+      <c r="E31" s="6">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-23.11</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-22.35</v>
+      </c>
+      <c r="E32" s="6">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="5">
+        <v>-48.52</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-50.72</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-2.2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-7.93</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-6.11</v>
+      </c>
+      <c r="E34" s="6">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="5">
+        <v>4.65</v>
+      </c>
+      <c r="D35" s="5">
+        <v>4.72</v>
+      </c>
+      <c r="E35" s="6">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-10.73</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-12.53</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-6.28</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-6.9</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-0.62</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-17.11</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-16.76</v>
+      </c>
+      <c r="E38" s="6">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-8.369999999999999</v>
+      </c>
+      <c r="E39" s="6">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-20.79</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-20.36</v>
+      </c>
+      <c r="E40" s="6">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="5">
+        <v>3.71</v>
+      </c>
+      <c r="D41" s="5">
+        <v>4.36</v>
+      </c>
+      <c r="E41" s="6">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="5">
+        <v>-13.83</v>
+      </c>
+      <c r="D42" s="5">
+        <v>-14.31</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-31.37</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-30.01</v>
+      </c>
+      <c r="E43" s="6">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-3.18</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-3.12</v>
+      </c>
+      <c r="E44" s="6">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-17.11</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-18.78</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-1.67</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="5">
+        <v>-9.58</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-10.18</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="5">
+        <v>-17.11</v>
+      </c>
+      <c r="D47" s="5">
+        <v>-16.76</v>
+      </c>
+      <c r="E47" s="6">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="5">
+        <v>-29.83</v>
+      </c>
+      <c r="D48" s="5">
+        <v>-28.79</v>
+      </c>
+      <c r="E48" s="6">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="5">
+        <v>-20.79</v>
+      </c>
+      <c r="D49" s="5">
+        <v>-20.36</v>
+      </c>
+      <c r="E49" s="6">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="5">
+        <v>-27.72</v>
+      </c>
+      <c r="D50" s="5">
+        <v>-27.27</v>
+      </c>
+      <c r="E50" s="6">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="5">
+        <v>-50.44</v>
+      </c>
+      <c r="D51" s="5">
+        <v>-50.07</v>
+      </c>
+      <c r="E51" s="6">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="5">
+        <v>1305.9</v>
+      </c>
+      <c r="D52" s="5">
+        <v>1331.7</v>
+      </c>
+      <c r="E52" s="6">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="5">
+        <v>3110</v>
+      </c>
+      <c r="D53" s="5">
+        <v>3112</v>
+      </c>
+      <c r="E53" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="5">
+        <v>1330</v>
+      </c>
+      <c r="D54" s="5">
+        <v>1303.2</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-26.8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="5">
+        <v>1702.7</v>
+      </c>
+      <c r="D55" s="5">
+        <v>1691.5</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-11.2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="5">
+        <v>206.33</v>
+      </c>
+      <c r="D56" s="5">
+        <v>207.2</v>
+      </c>
+      <c r="E56" s="6">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="5">
+        <v>413.1</v>
+      </c>
+      <c r="D57" s="5">
+        <v>419.2</v>
+      </c>
+      <c r="E57" s="6">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="5">
+        <v>640.25</v>
+      </c>
+      <c r="D58" s="5">
+        <v>643.7</v>
+      </c>
+      <c r="E58" s="6">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="5">
+        <v>200.64</v>
+      </c>
+      <c r="D59" s="5">
+        <v>201.9</v>
+      </c>
+      <c r="E59" s="6">
         <v>1.26</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="5">
+        <v>74.77</v>
+      </c>
+      <c r="D60" s="5">
+        <v>74.34999999999999</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="5">
+        <v>40.36</v>
+      </c>
+      <c r="D61" s="5">
+        <v>49.03</v>
+      </c>
+      <c r="E61" s="6">
+        <v>8.67</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="5">
+        <v>60.91</v>
+      </c>
+      <c r="D62" s="5">
+        <v>61.12</v>
+      </c>
+      <c r="E62" s="6">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="5">
+        <v>41.8</v>
+      </c>
+      <c r="D63" s="5">
+        <v>37.53</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-4.27</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-5.44</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-3.82</v>
-      </c>
-      <c r="E10" s="8">
-        <v>1.62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B64" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="5">
+        <v>46.91</v>
+      </c>
+      <c r="D64" s="5">
+        <v>44.51</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-2.4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-4.66</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-3.57</v>
-      </c>
-      <c r="E11" s="8">
-        <v>1.09</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B65" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="5">
+        <v>44.05</v>
+      </c>
+      <c r="D65" s="5">
+        <v>45.9</v>
+      </c>
+      <c r="E65" s="6">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-3.86</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-4.14</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B66" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="5">
+        <v>42.14</v>
+      </c>
+      <c r="D66" s="5">
+        <v>47.45</v>
+      </c>
+      <c r="E66" s="6">
+        <v>5.31</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-2.03</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-3.07</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-1.04</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B67" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="5">
+        <v>37.22</v>
+      </c>
+      <c r="D67" s="5">
+        <v>39.54</v>
+      </c>
+      <c r="E67" s="6">
+        <v>2.32</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>3.04</v>
-      </c>
-      <c r="D14" s="6">
-        <v>6.93</v>
-      </c>
-      <c r="E14" s="8">
-        <v>3.89</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B68" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="5">
+        <v>65.83</v>
+      </c>
+      <c r="D68" s="5">
+        <v>67.27</v>
+      </c>
+      <c r="E68" s="6">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-1.98</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-3.42</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-1.44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B69" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="5">
+        <v>40.1</v>
+      </c>
+      <c r="D69" s="5">
+        <v>38.46</v>
+      </c>
+      <c r="E69" s="7">
+        <v>-1.64</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-1.19</v>
-      </c>
-      <c r="D16" s="6">
-        <v>0.16</v>
-      </c>
-      <c r="E16" s="8">
-        <v>1.35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B70" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="5">
+        <v>-58.24</v>
+      </c>
+      <c r="D70" s="5">
+        <v>5.13</v>
+      </c>
+      <c r="E70" s="6">
+        <v>63.37</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-0.29</v>
-      </c>
-      <c r="D17" s="6">
-        <v>3.58</v>
-      </c>
-      <c r="E17" s="8">
-        <v>3.87</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B71" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="5">
+        <v>102.42</v>
+      </c>
+      <c r="D71" s="5">
+        <v>91.84</v>
+      </c>
+      <c r="E71" s="7">
+        <v>-10.58</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-1.48</v>
-      </c>
-      <c r="D18" s="6">
-        <v>1.68</v>
-      </c>
-      <c r="E18" s="8">
-        <v>3.16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B72" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="5">
+        <v>65.38</v>
+      </c>
+      <c r="D72" s="5">
+        <v>62.32</v>
+      </c>
+      <c r="E72" s="7">
+        <v>-3.06</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-1.64</v>
-      </c>
-      <c r="D19" s="6">
-        <v>1.21</v>
-      </c>
-      <c r="E19" s="8">
-        <v>2.85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B73" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="5">
+        <v>-40.56</v>
+      </c>
+      <c r="D73" s="5">
+        <v>-9.35</v>
+      </c>
+      <c r="E73" s="6">
+        <v>31.21</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="D20" s="6">
-        <v>0.36</v>
-      </c>
-      <c r="E20" s="8">
-        <v>0.29</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B74" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="5">
+        <v>0.72</v>
+      </c>
+      <c r="D74" s="5">
+        <v>62.88</v>
+      </c>
+      <c r="E74" s="6">
+        <v>62.16</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-1.57</v>
-      </c>
-      <c r="D21" s="6">
-        <v>0.17</v>
-      </c>
-      <c r="E21" s="8">
-        <v>1.74</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B75" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="5">
+        <v>-52.6</v>
+      </c>
+      <c r="D75" s="5">
+        <v>-12.28</v>
+      </c>
+      <c r="E75" s="6">
+        <v>40.32</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-1.13</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-1.09</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B76" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="5">
+        <v>-51.09</v>
+      </c>
+      <c r="D76" s="5">
+        <v>-24.58</v>
+      </c>
+      <c r="E76" s="6">
+        <v>26.51</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>0.9</v>
-      </c>
-      <c r="D23" s="6">
-        <v>5.58</v>
-      </c>
-      <c r="E23" s="8">
-        <v>4.68</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B77" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="5">
+        <v>445.09</v>
+      </c>
+      <c r="D77" s="5">
+        <v>22.36</v>
+      </c>
+      <c r="E77" s="7">
+        <v>-422.73</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-1.82</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-1.23</v>
-      </c>
-      <c r="E24" s="8">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-29.64</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-29.5</v>
-      </c>
-      <c r="E25" s="8">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>25.6</v>
-      </c>
-      <c r="D26" s="6">
-        <v>30.34</v>
-      </c>
-      <c r="E26" s="8">
-        <v>4.74</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>34.37</v>
-      </c>
-      <c r="D27" s="6">
-        <v>36.28</v>
-      </c>
-      <c r="E27" s="8">
-        <v>1.91</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>22.62</v>
-      </c>
-      <c r="D28" s="6">
-        <v>24.75</v>
-      </c>
-      <c r="E28" s="8">
-        <v>2.13</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>68.06999999999999</v>
-      </c>
-      <c r="D29" s="6">
-        <v>71.95999999999999</v>
-      </c>
-      <c r="E29" s="8">
-        <v>3.89</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-30.66</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-29.86</v>
-      </c>
-      <c r="E30" s="8">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>1.76</v>
-      </c>
-      <c r="D31" s="6">
-        <v>1.6</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-0.16</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-25.3</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-23.11</v>
-      </c>
-      <c r="E32" s="8">
-        <v>2.19</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-45.68</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-48.52</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-2.84</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-7.37</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-7.93</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>1.03</v>
-      </c>
-      <c r="D35" s="6">
-        <v>4.65</v>
-      </c>
-      <c r="E35" s="8">
-        <v>3.62</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-10.25</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-10.73</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-0.48</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-7.29</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-6.28</v>
-      </c>
-      <c r="E37" s="8">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-16.7</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-17.11</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.41</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-8.66</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-9.699999999999999</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-1.04</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-10.28</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-20.79</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-10.51</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>0.42</v>
-      </c>
-      <c r="D41" s="6">
-        <v>3.71</v>
-      </c>
-      <c r="E41" s="8">
-        <v>3.29</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-4.69</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-13.83</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-9.140000000000001</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-31.63</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-31.37</v>
-      </c>
-      <c r="E43" s="8">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-6.65</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-3.18</v>
-      </c>
-      <c r="E44" s="8">
-        <v>3.47</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-18.48</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-17.11</v>
-      </c>
-      <c r="E45" s="8">
-        <v>1.37</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-11.21</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-9.58</v>
-      </c>
-      <c r="E46" s="8">
-        <v>1.63</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-18.16</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-17.11</v>
-      </c>
-      <c r="E47" s="8">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-30.6</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-29.83</v>
-      </c>
-      <c r="E48" s="8">
-        <v>0.77</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-20.87</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-20.79</v>
-      </c>
-      <c r="E49" s="8">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-30.16</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-27.72</v>
-      </c>
-      <c r="E50" s="8">
-        <v>2.44</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-50.19</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-50.44</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="6">
-        <v>1300.9</v>
-      </c>
-      <c r="D52" s="6">
-        <v>1305.9</v>
-      </c>
-      <c r="E52" s="8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>2998.6</v>
-      </c>
-      <c r="D53" s="6">
-        <v>3110</v>
-      </c>
-      <c r="E53" s="8">
-        <v>111.4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>1308</v>
-      </c>
-      <c r="D54" s="6">
-        <v>1330</v>
-      </c>
-      <c r="E54" s="8">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>1672.1</v>
-      </c>
-      <c r="D55" s="6">
-        <v>1702.7</v>
-      </c>
-      <c r="E55" s="8">
-        <v>30.6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>203.7</v>
-      </c>
-      <c r="D56" s="6">
-        <v>206.33</v>
-      </c>
-      <c r="E56" s="8">
-        <v>2.63</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>408.75</v>
-      </c>
-      <c r="D57" s="6">
-        <v>413.1</v>
-      </c>
-      <c r="E57" s="8">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>639.6</v>
-      </c>
-      <c r="D58" s="6">
-        <v>640.25</v>
-      </c>
-      <c r="E58" s="8">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>193.88</v>
-      </c>
-      <c r="D59" s="6">
-        <v>200.64</v>
-      </c>
-      <c r="E59" s="8">
-        <v>6.76</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="6">
-        <v>75.14</v>
-      </c>
-      <c r="D60" s="6">
-        <v>74.77</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" s="6">
-        <v>55</v>
-      </c>
-      <c r="D61" s="6">
-        <v>45</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="6">
-        <v>45</v>
-      </c>
-      <c r="D62" s="6">
-        <v>55</v>
-      </c>
-      <c r="E62" s="8">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="6">
-        <v>38.47</v>
-      </c>
-      <c r="D63" s="6">
-        <v>40.36</v>
-      </c>
-      <c r="E63" s="8">
-        <v>1.89</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="6">
-        <v>45.89</v>
-      </c>
-      <c r="D64" s="6">
-        <v>60.91</v>
-      </c>
-      <c r="E64" s="8">
-        <v>15.02</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>36.28</v>
-      </c>
-      <c r="D65" s="6">
-        <v>41.8</v>
-      </c>
-      <c r="E65" s="8">
-        <v>5.52</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>38.48</v>
-      </c>
-      <c r="D66" s="6">
-        <v>46.91</v>
-      </c>
-      <c r="E66" s="8">
-        <v>8.43</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>38.09</v>
-      </c>
-      <c r="D67" s="6">
-        <v>44.05</v>
-      </c>
-      <c r="E67" s="8">
-        <v>5.96</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>38</v>
-      </c>
-      <c r="D68" s="6">
-        <v>42.14</v>
-      </c>
-      <c r="E68" s="8">
-        <v>4.14</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="6">
-        <v>36.79</v>
-      </c>
-      <c r="D69" s="6">
-        <v>37.22</v>
-      </c>
-      <c r="E69" s="8">
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="6">
-        <v>56.2</v>
-      </c>
-      <c r="D70" s="6">
-        <v>65.83</v>
-      </c>
-      <c r="E70" s="8">
-        <v>9.630000000000001</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="6">
-        <v>41.56</v>
-      </c>
-      <c r="D71" s="6">
-        <v>40.1</v>
-      </c>
-      <c r="E71" s="7">
-        <v>-1.46</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B72" s="5" t="s">
+      <c r="B78" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C72" s="6">
-        <v>-54.73</v>
-      </c>
-      <c r="D72" s="6">
-        <v>-58.24</v>
-      </c>
-      <c r="E72" s="7">
-        <v>-3.51</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="6">
-        <v>-18.42</v>
-      </c>
-      <c r="D73" s="6">
-        <v>102.42</v>
-      </c>
-      <c r="E73" s="8">
-        <v>120.84</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="6">
-        <v>-59.02</v>
-      </c>
-      <c r="D74" s="6">
-        <v>65.38</v>
-      </c>
-      <c r="E74" s="8">
-        <v>124.4</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="6">
-        <v>-52.05</v>
-      </c>
-      <c r="D75" s="6">
-        <v>-40.56</v>
-      </c>
-      <c r="E75" s="8">
-        <v>11.49</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>-37.03</v>
-      </c>
-      <c r="D76" s="6">
-        <v>0.72</v>
-      </c>
-      <c r="E76" s="8">
-        <v>37.75</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>-28.99</v>
-      </c>
-      <c r="D77" s="6">
-        <v>-52.6</v>
-      </c>
-      <c r="E77" s="7">
-        <v>-23.61</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>-55.49</v>
-      </c>
-      <c r="D78" s="6">
-        <v>-51.09</v>
-      </c>
-      <c r="E78" s="8">
-        <v>4.4</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>216.03</v>
-      </c>
-      <c r="D79" s="6">
-        <v>445.09</v>
-      </c>
-      <c r="E79" s="8">
-        <v>229.06</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>-16.19</v>
-      </c>
-      <c r="D80" s="6">
+      <c r="C78" s="5">
         <v>14.04</v>
       </c>
-      <c r="E80" s="8">
-        <v>30.23</v>
+      <c r="D78" s="5">
+        <v>85.36</v>
+      </c>
+      <c r="E78" s="6">
+        <v>71.31999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -3442,60 +3345,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>74</v>
+      <c r="B1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>56.16</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
-        <v>46.6</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>47.9</v>
+      </c>
+      <c r="E2" s="10">
         <v>60</v>
       </c>
-      <c r="F2" s="11">
-        <v>-1.9</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-8.699999999999999</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-0.4</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-8.5</v>
+      </c>
+      <c r="H2" s="10">
         <v>55.4</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -3597,61 +3500,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="12" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>0.6631999999999999</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.194</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1614</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.0593</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.0157</v>
-      </c>
-      <c r="F2" s="14">
-        <v>-0.0011</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.0619</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.0964</v>
-      </c>
-      <c r="I2" s="14">
-        <v>-0.1239</v>
+      <c r="A2" s="13">
+        <v>0.6484000000000001</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.1922</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.1615</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.0449</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.0181</v>
+      </c>
+      <c r="F2" s="13">
+        <v>-0.0106</v>
+      </c>
+      <c r="G2" s="13">
+        <v>-0.06059999999999999</v>
+      </c>
+      <c r="H2" s="13">
+        <v>-0.0935</v>
+      </c>
+      <c r="I2" s="13">
+        <v>-0.1314</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="83">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,7 +178,58 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>Near 52W High</t>
+  </si>
+  <si>
+    <t>-3.1% → -1.3%</t>
+  </si>
+  <si>
+    <t>🟢 BREAKOUT WATCH</t>
+  </si>
+  <si>
+    <t>-3.1%</t>
+  </si>
+  <si>
+    <t>-1.3%</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>44.5 → 50.0</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>44.5</t>
+  </si>
+  <si>
+    <t>50.0</t>
+  </si>
+  <si>
+    <t>45.9 → 59.0</t>
+  </si>
+  <si>
+    <t>45.9</t>
+  </si>
+  <si>
+    <t>59.0</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -380,17 +431,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -902,10 +954,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1331.7</v>
+        <v>1310.6</v>
       </c>
       <c r="D2">
-        <v>1.98</v>
+        <v>-1.58</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -914,46 +966,46 @@
         <v>1247.38</v>
       </c>
       <c r="G2">
-        <v>-30.01</v>
+        <v>-31.12</v>
       </c>
       <c r="H2">
-        <v>6.76</v>
+        <v>5.07</v>
       </c>
       <c r="I2">
-        <v>3.34</v>
+        <v>0.73</v>
       </c>
       <c r="J2">
-        <v>-0.75</v>
+        <v>-4.39</v>
       </c>
       <c r="K2">
-        <v>-6.11</v>
+        <v>-5.8</v>
       </c>
       <c r="L2">
-        <v>-27.6</v>
+        <v>-27.62</v>
       </c>
       <c r="M2">
-        <v>-9.35</v>
+        <v>-10.2</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P2">
-        <v>1309.4</v>
+        <v>1311.3</v>
       </c>
       <c r="Q2">
-        <v>1338.21</v>
+        <v>1335.92</v>
       </c>
       <c r="R2">
-        <v>1350.59</v>
+        <v>1349.81</v>
       </c>
       <c r="S2">
-        <v>1511.26</v>
+        <v>1508.64</v>
       </c>
       <c r="T2">
-        <v>-11.88</v>
+        <v>-13.13</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -968,34 +1020,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>49.03</v>
+        <v>43.46</v>
       </c>
       <c r="Z2">
-        <v>-14.43</v>
+        <v>-14.09</v>
       </c>
       <c r="AA2">
-        <v>-12.9</v>
+        <v>-13.14</v>
       </c>
       <c r="AB2">
-        <v>-1.52</v>
+        <v>-0.95</v>
       </c>
       <c r="AC2">
-        <v>53</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="AD2">
-        <v>35.18</v>
+        <v>49.81</v>
       </c>
       <c r="AE2">
-        <v>24.76</v>
+        <v>24.78</v>
       </c>
       <c r="AF2">
-        <v>5.13</v>
+        <v>-59.15</v>
       </c>
       <c r="AG2">
-        <v>1405.57</v>
+        <v>1403.78</v>
       </c>
       <c r="AH2">
-        <v>1270.85</v>
+        <v>1268.05</v>
       </c>
       <c r="AI2">
         <v>1373.07</v>
@@ -1004,7 +1056,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>34.31</v>
+        <v>30.77</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1015,10 +1067,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3112</v>
+        <v>3169</v>
       </c>
       <c r="D3">
-        <v>0.06</v>
+        <v>1.83</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1027,46 +1079,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-3.12</v>
+        <v>-1.34</v>
       </c>
       <c r="H3">
-        <v>77.02</v>
+        <v>80.26000000000001</v>
       </c>
       <c r="I3">
-        <v>4.07</v>
+        <v>5.81</v>
       </c>
       <c r="J3">
-        <v>3.65</v>
+        <v>4.78</v>
       </c>
       <c r="K3">
-        <v>4.72</v>
+        <v>7.93</v>
       </c>
       <c r="L3">
-        <v>30.97</v>
+        <v>36.37</v>
       </c>
       <c r="M3">
-        <v>16.15</v>
+        <v>16.1</v>
       </c>
       <c r="N3">
         <v>88</v>
       </c>
       <c r="O3">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="P3">
-        <v>3042.5</v>
+        <v>3077.32</v>
       </c>
       <c r="Q3">
-        <v>3023.82</v>
+        <v>3029.82</v>
       </c>
       <c r="R3">
-        <v>3063.72</v>
+        <v>3068.07</v>
       </c>
       <c r="S3">
-        <v>2491.58</v>
+        <v>2495.94</v>
       </c>
       <c r="T3">
-        <v>24.9</v>
+        <v>26.97</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1081,34 +1133,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>61.12</v>
+        <v>66.59</v>
       </c>
       <c r="Z3">
-        <v>1.05</v>
+        <v>11.58</v>
       </c>
       <c r="AA3">
-        <v>-9.800000000000001</v>
+        <v>-5.52</v>
       </c>
       <c r="AB3">
-        <v>10.85</v>
+        <v>17.1</v>
       </c>
       <c r="AC3">
-        <v>86.61</v>
+        <v>100</v>
       </c>
       <c r="AD3">
-        <v>71.33</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="AE3">
-        <v>66.16</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="AF3">
-        <v>91.84</v>
+        <v>61.53</v>
       </c>
       <c r="AG3">
-        <v>3102.6</v>
+        <v>3131.58</v>
       </c>
       <c r="AH3">
-        <v>2945.04</v>
+        <v>2928.05</v>
       </c>
       <c r="AI3">
         <v>2959.69</v>
@@ -1117,7 +1169,7 @@
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>28.77</v>
+        <v>31.78</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1128,10 +1180,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1303.2</v>
+        <v>1328.5</v>
       </c>
       <c r="D4">
-        <v>-2.02</v>
+        <v>1.94</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1140,46 +1192,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-18.78</v>
+        <v>-17.2</v>
       </c>
       <c r="H4">
-        <v>68.63</v>
+        <v>71.91</v>
       </c>
       <c r="I4">
-        <v>0.79</v>
+        <v>2.05</v>
       </c>
       <c r="J4">
-        <v>-5.41</v>
+        <v>-3.25</v>
       </c>
       <c r="K4">
-        <v>-12.53</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="L4">
-        <v>34.82</v>
+        <v>38.79</v>
       </c>
       <c r="M4">
-        <v>4.49</v>
+        <v>4.84</v>
       </c>
       <c r="N4">
         <v>77</v>
       </c>
       <c r="O4">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="P4">
-        <v>1312.6</v>
+        <v>1317.94</v>
       </c>
       <c r="Q4">
-        <v>1343.52</v>
+        <v>1342.02</v>
       </c>
       <c r="R4">
-        <v>1438.58</v>
+        <v>1435.83</v>
       </c>
       <c r="S4">
-        <v>1169.09</v>
+        <v>1170.53</v>
       </c>
       <c r="T4">
-        <v>11.47</v>
+        <v>13.5</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1194,34 +1246,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>37.53</v>
+        <v>43.41</v>
       </c>
       <c r="Z4">
-        <v>-35.51</v>
+        <v>-32.71</v>
       </c>
       <c r="AA4">
-        <v>-37.11</v>
+        <v>-36.23</v>
       </c>
       <c r="AB4">
-        <v>1.61</v>
+        <v>3.52</v>
       </c>
       <c r="AC4">
-        <v>75.48</v>
+        <v>87</v>
       </c>
       <c r="AD4">
-        <v>71.91</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="AE4">
-        <v>37.05</v>
+        <v>36.29</v>
       </c>
       <c r="AF4">
-        <v>62.32</v>
+        <v>-47.18</v>
       </c>
       <c r="AG4">
-        <v>1408.99</v>
+        <v>1407.4</v>
       </c>
       <c r="AH4">
-        <v>1278.06</v>
+        <v>1276.63</v>
       </c>
       <c r="AI4">
         <v>1418.72</v>
@@ -1230,7 +1282,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>25.34</v>
+        <v>22.25</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1241,10 +1293,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1691.5</v>
+        <v>1714</v>
       </c>
       <c r="D5">
-        <v>-0.66</v>
+        <v>1.33</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1253,46 +1305,46 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-10.18</v>
+        <v>-8.98</v>
       </c>
       <c r="H5">
-        <v>30.3</v>
+        <v>32.04</v>
       </c>
       <c r="I5">
-        <v>0.57</v>
+        <v>1.06</v>
       </c>
       <c r="J5">
-        <v>-4.69</v>
+        <v>-0.33</v>
       </c>
       <c r="K5">
-        <v>-6.9</v>
+        <v>-4.62</v>
       </c>
       <c r="L5">
-        <v>24.73</v>
+        <v>28.33</v>
       </c>
       <c r="M5">
-        <v>19.22</v>
+        <v>19.36</v>
       </c>
       <c r="N5">
         <v>66</v>
       </c>
       <c r="O5">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="P5">
-        <v>1692.46</v>
+        <v>1696.06</v>
       </c>
       <c r="Q5">
-        <v>1687.78</v>
+        <v>1690.27</v>
       </c>
       <c r="R5">
-        <v>1764.78</v>
+        <v>1762.48</v>
       </c>
       <c r="S5">
-        <v>1595.18</v>
+        <v>1596.56</v>
       </c>
       <c r="T5">
-        <v>6.04</v>
+        <v>7.36</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1307,34 +1359,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>44.51</v>
+        <v>50.04</v>
       </c>
       <c r="Z5">
-        <v>-19.8</v>
+        <v>-16.63</v>
       </c>
       <c r="AA5">
-        <v>-25.07</v>
+        <v>-23.38</v>
       </c>
       <c r="AB5">
-        <v>5.27</v>
+        <v>6.75</v>
       </c>
       <c r="AC5">
-        <v>81.42</v>
+        <v>95.25</v>
       </c>
       <c r="AD5">
-        <v>84.59</v>
+        <v>87.62</v>
       </c>
       <c r="AE5">
-        <v>31.77</v>
+        <v>31.48</v>
       </c>
       <c r="AF5">
-        <v>-9.35</v>
+        <v>-4.62</v>
       </c>
       <c r="AG5">
-        <v>1717.87</v>
+        <v>1720.37</v>
       </c>
       <c r="AH5">
-        <v>1657.69</v>
+        <v>1660.18</v>
       </c>
       <c r="AI5">
         <v>1761.08</v>
@@ -1343,7 +1395,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>23.56</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1354,10 +1406,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>207.2</v>
+        <v>215</v>
       </c>
       <c r="D6">
-        <v>0.42</v>
+        <v>3.76</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1366,46 +1418,46 @@
         <v>118.42</v>
       </c>
       <c r="G6">
-        <v>-16.76</v>
+        <v>-13.62</v>
       </c>
       <c r="H6">
-        <v>74.97</v>
+        <v>81.56</v>
       </c>
       <c r="I6">
-        <v>1.56</v>
+        <v>5.39</v>
       </c>
       <c r="J6">
-        <v>-0.5</v>
+        <v>2.62</v>
       </c>
       <c r="K6">
-        <v>-16.76</v>
+        <v>-11.66</v>
       </c>
       <c r="L6">
-        <v>73.77</v>
+        <v>80.89</v>
       </c>
       <c r="M6">
-        <v>64.84</v>
+        <v>64.45</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="P6">
-        <v>205.35</v>
+        <v>207.55</v>
       </c>
       <c r="Q6">
-        <v>207.39</v>
+        <v>207.69</v>
       </c>
       <c r="R6">
-        <v>215.49</v>
+        <v>215.38</v>
       </c>
       <c r="S6">
-        <v>180.85</v>
+        <v>181.17</v>
       </c>
       <c r="T6">
-        <v>14.57</v>
+        <v>18.67</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1420,34 +1472,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>45.9</v>
+        <v>59.01</v>
       </c>
       <c r="Z6">
-        <v>-2.74</v>
+        <v>-1.84</v>
       </c>
       <c r="AA6">
-        <v>-3.19</v>
+        <v>-2.92</v>
       </c>
       <c r="AB6">
-        <v>0.46</v>
+        <v>1.08</v>
       </c>
       <c r="AC6">
-        <v>77.92</v>
+        <v>100</v>
       </c>
       <c r="AD6">
-        <v>61.3</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="AE6">
-        <v>4.76</v>
+        <v>5.15</v>
       </c>
       <c r="AF6">
-        <v>62.88</v>
+        <v>386.06</v>
       </c>
       <c r="AG6">
-        <v>212.98</v>
+        <v>214.21</v>
       </c>
       <c r="AH6">
-        <v>201.81</v>
+        <v>201.18</v>
       </c>
       <c r="AI6">
         <v>217.63</v>
@@ -1456,7 +1508,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>23.99</v>
+        <v>28.29</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1467,10 +1519,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>419.2</v>
+        <v>411.05</v>
       </c>
       <c r="D7">
-        <v>1.48</v>
+        <v>-1.94</v>
       </c>
       <c r="E7">
         <v>588.6900000000001</v>
@@ -1479,46 +1531,46 @@
         <v>393.4</v>
       </c>
       <c r="G7">
-        <v>-28.79</v>
+        <v>-30.18</v>
       </c>
       <c r="H7">
-        <v>6.56</v>
+        <v>4.49</v>
       </c>
       <c r="I7">
-        <v>2.87</v>
+        <v>0.01</v>
       </c>
       <c r="J7">
-        <v>-1.6</v>
+        <v>-5.57</v>
       </c>
       <c r="K7">
-        <v>-8.369999999999999</v>
+        <v>-7.76</v>
       </c>
       <c r="L7">
-        <v>-28.45</v>
+        <v>-28.43</v>
       </c>
       <c r="M7">
-        <v>1.81</v>
+        <v>0.82</v>
       </c>
       <c r="N7">
         <v>23</v>
       </c>
       <c r="O7">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P7">
-        <v>413.31</v>
+        <v>413.32</v>
       </c>
       <c r="Q7">
-        <v>423.82</v>
+        <v>422.66</v>
       </c>
       <c r="R7">
-        <v>427.41</v>
+        <v>427.1</v>
       </c>
       <c r="S7">
-        <v>473.78</v>
+        <v>473.07</v>
       </c>
       <c r="T7">
-        <v>-11.52</v>
+        <v>-13.11</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1533,34 +1585,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>47.45</v>
+        <v>41.92</v>
       </c>
       <c r="Z7">
-        <v>-5.07</v>
+        <v>-5.17</v>
       </c>
       <c r="AA7">
-        <v>-4.34</v>
+        <v>-4.51</v>
       </c>
       <c r="AB7">
-        <v>-0.74</v>
+        <v>-0.67</v>
       </c>
       <c r="AC7">
-        <v>46.18</v>
+        <v>59</v>
       </c>
       <c r="AD7">
-        <v>31.67</v>
+        <v>44.76</v>
       </c>
       <c r="AE7">
-        <v>9.24</v>
+        <v>9.4</v>
       </c>
       <c r="AF7">
-        <v>-12.28</v>
+        <v>-63.78</v>
       </c>
       <c r="AG7">
-        <v>447.44</v>
+        <v>446.41</v>
       </c>
       <c r="AH7">
-        <v>400.2</v>
+        <v>398.92</v>
       </c>
       <c r="AI7">
         <v>436.39</v>
@@ -1569,7 +1621,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>29.23</v>
+        <v>26.67</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1580,10 +1632,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>643.7</v>
+        <v>645.35</v>
       </c>
       <c r="D8">
-        <v>0.54</v>
+        <v>0.26</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1592,46 +1644,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-20.36</v>
+        <v>-20.16</v>
       </c>
       <c r="H8">
-        <v>37.62</v>
+        <v>37.97</v>
       </c>
       <c r="I8">
-        <v>-3.09</v>
+        <v>-1.87</v>
       </c>
       <c r="J8">
-        <v>-0.29</v>
+        <v>-1.61</v>
       </c>
       <c r="K8">
-        <v>-20.36</v>
+        <v>-16.52</v>
       </c>
       <c r="L8">
-        <v>4.2</v>
+        <v>4.51</v>
       </c>
       <c r="M8">
-        <v>-13.14</v>
+        <v>-13.32</v>
       </c>
       <c r="N8">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="O8">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="P8">
-        <v>645.46</v>
+        <v>643</v>
       </c>
       <c r="Q8">
-        <v>654.79</v>
+        <v>654.55</v>
       </c>
       <c r="R8">
-        <v>685.89</v>
+        <v>684.74</v>
       </c>
       <c r="S8">
-        <v>613.6900000000001</v>
+        <v>613.87</v>
       </c>
       <c r="T8">
-        <v>4.89</v>
+        <v>5.13</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1646,34 +1698,34 @@
         <v>2</v>
       </c>
       <c r="Y8">
-        <v>39.54</v>
+        <v>40.68</v>
       </c>
       <c r="Z8">
-        <v>-10.6</v>
+        <v>-10.22</v>
       </c>
       <c r="AA8">
-        <v>-10.8</v>
+        <v>-10.69</v>
       </c>
       <c r="AB8">
-        <v>0.2</v>
+        <v>0.46</v>
       </c>
       <c r="AC8">
-        <v>14.22</v>
+        <v>25.99</v>
       </c>
       <c r="AD8">
-        <v>20.66</v>
+        <v>17.86</v>
       </c>
       <c r="AE8">
-        <v>16.58</v>
+        <v>15.98</v>
       </c>
       <c r="AF8">
-        <v>-24.58</v>
+        <v>-25.01</v>
       </c>
       <c r="AG8">
-        <v>672.3099999999999</v>
+        <v>672.46</v>
       </c>
       <c r="AH8">
-        <v>637.26</v>
+        <v>636.63</v>
       </c>
       <c r="AI8">
         <v>690.22</v>
@@ -1682,7 +1734,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>20.57</v>
+        <v>19.32</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1693,10 +1745,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>201.9</v>
+        <v>199.74</v>
       </c>
       <c r="D9">
-        <v>0.63</v>
+        <v>-1.07</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1705,46 +1757,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-27.27</v>
+        <v>-28.05</v>
       </c>
       <c r="H9">
-        <v>17.18</v>
+        <v>15.93</v>
       </c>
       <c r="I9">
-        <v>6.98</v>
+        <v>5.88</v>
       </c>
       <c r="J9">
-        <v>8.449999999999999</v>
+        <v>5.18</v>
       </c>
       <c r="K9">
-        <v>4.36</v>
+        <v>3.87</v>
       </c>
       <c r="L9">
-        <v>-22.35</v>
+        <v>-22.7</v>
       </c>
       <c r="M9">
-        <v>-6.06</v>
+        <v>-6.28</v>
       </c>
       <c r="N9">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O9">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="P9">
-        <v>194.64</v>
+        <v>196.86</v>
       </c>
       <c r="Q9">
-        <v>192.9</v>
+        <v>193.5</v>
       </c>
       <c r="R9">
-        <v>189.63</v>
+        <v>189.76</v>
       </c>
       <c r="S9">
-        <v>206.16</v>
+        <v>205.8</v>
       </c>
       <c r="T9">
-        <v>-2.07</v>
+        <v>-2.95</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1759,34 +1811,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>67.27</v>
+        <v>62.4</v>
       </c>
       <c r="Z9">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AA9">
-        <v>0.91</v>
+        <v>1.12</v>
       </c>
       <c r="AB9">
-        <v>0.77</v>
+        <v>0.87</v>
       </c>
       <c r="AC9">
-        <v>87.51000000000001</v>
+        <v>93.14</v>
       </c>
       <c r="AD9">
-        <v>54.17</v>
+        <v>78.27</v>
       </c>
       <c r="AE9">
-        <v>5.33</v>
+        <v>5.36</v>
       </c>
       <c r="AF9">
-        <v>22.36</v>
+        <v>-12.2</v>
       </c>
       <c r="AG9">
-        <v>201.06</v>
+        <v>201.81</v>
       </c>
       <c r="AH9">
-        <v>184.73</v>
+        <v>185.2</v>
       </c>
       <c r="AI9">
         <v>185.88</v>
@@ -1795,7 +1847,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>35.39</v>
+        <v>37.4</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1806,58 +1858,58 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>74.34999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="D10">
-        <v>-0.5600000000000001</v>
+        <v>-0.2</v>
       </c>
       <c r="E10">
-        <v>148.9</v>
+        <v>142.47</v>
       </c>
       <c r="F10">
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-50.07</v>
+        <v>-47.92</v>
       </c>
       <c r="H10">
-        <v>25.42</v>
+        <v>25.17</v>
       </c>
       <c r="I10">
-        <v>1.38</v>
+        <v>-1.72</v>
       </c>
       <c r="J10">
-        <v>-2.79</v>
+        <v>-2.62</v>
       </c>
       <c r="K10">
-        <v>-14.31</v>
+        <v>-10.76</v>
       </c>
       <c r="L10">
-        <v>-50.72</v>
+        <v>-50.17</v>
       </c>
       <c r="M10">
-        <v>-1.06</v>
+        <v>-0.93</v>
       </c>
       <c r="N10">
         <v>12</v>
       </c>
       <c r="O10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P10">
-        <v>75.05</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="Q10">
-        <v>76.09</v>
+        <v>75.98</v>
       </c>
       <c r="R10">
-        <v>78.54000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="S10">
-        <v>81.45</v>
+        <v>81.39</v>
       </c>
       <c r="T10">
-        <v>-8.710000000000001</v>
+        <v>-8.83</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1872,34 +1924,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>38.46</v>
+        <v>37.86</v>
       </c>
       <c r="Z10">
-        <v>-1.03</v>
+        <v>-1.05</v>
       </c>
       <c r="AA10">
-        <v>-0.99</v>
+        <v>-1</v>
       </c>
       <c r="AB10">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="AC10">
-        <v>67.23999999999999</v>
+        <v>58.91</v>
       </c>
       <c r="AD10">
-        <v>76.29000000000001</v>
+        <v>67.84</v>
       </c>
       <c r="AE10">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AF10">
-        <v>85.36</v>
+        <v>-45.15</v>
       </c>
       <c r="AG10">
-        <v>78.23</v>
+        <v>78.28</v>
       </c>
       <c r="AH10">
-        <v>73.94</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="AI10">
         <v>80.34</v>
@@ -1908,7 +1960,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>36.63</v>
+        <v>39.81</v>
       </c>
     </row>
   </sheetData>
@@ -2049,7 +2101,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2069,1263 +2121,1372 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>52</v>
       </c>
+      <c r="C2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>57</v>
+      <c r="A5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>-3.84</v>
-      </c>
-      <c r="D7" s="5">
-        <v>-0.75</v>
-      </c>
-      <c r="E7" s="6">
-        <v>3.09</v>
-      </c>
+      <c r="A7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-0.75</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-4.39</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-3.64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>2.42</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C10" s="6">
         <v>3.65</v>
       </c>
-      <c r="E8" s="6">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D10" s="6">
+        <v>4.78</v>
+      </c>
+      <c r="E10" s="8">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-4.98</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C11" s="6">
         <v>-5.41</v>
       </c>
-      <c r="E9" s="7">
+      <c r="D11" s="6">
+        <v>-3.25</v>
+      </c>
+      <c r="E11" s="8">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-4.69</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-0.33</v>
+      </c>
+      <c r="E12" s="8">
+        <v>4.36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-0.5</v>
+      </c>
+      <c r="D13" s="6">
+        <v>2.62</v>
+      </c>
+      <c r="E13" s="8">
+        <v>3.12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-1.6</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-5.57</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-3.97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-0.29</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-1.61</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-1.32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="6">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="D16" s="6">
+        <v>5.18</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-3.27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-2.79</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-2.62</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>3.34</v>
+      </c>
+      <c r="D18" s="6">
+        <v>0.73</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-2.61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>4.07</v>
+      </c>
+      <c r="D19" s="6">
+        <v>5.81</v>
+      </c>
+      <c r="E19" s="8">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.79</v>
+      </c>
+      <c r="D20" s="6">
+        <v>2.05</v>
+      </c>
+      <c r="E20" s="8">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>0.57</v>
+      </c>
+      <c r="D21" s="6">
+        <v>1.06</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>1.56</v>
+      </c>
+      <c r="D22" s="6">
+        <v>5.39</v>
+      </c>
+      <c r="E22" s="8">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>2.87</v>
+      </c>
+      <c r="D23" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-2.86</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-3.09</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-1.87</v>
+      </c>
+      <c r="E24" s="8">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="6">
+        <v>6.98</v>
+      </c>
+      <c r="D25" s="6">
+        <v>5.88</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1.1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="6">
+        <v>1.38</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-1.72</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-3.1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-27.6</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-27.62</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>30.97</v>
+      </c>
+      <c r="D28" s="6">
+        <v>36.37</v>
+      </c>
+      <c r="E28" s="8">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>34.82</v>
+      </c>
+      <c r="D29" s="6">
+        <v>38.79</v>
+      </c>
+      <c r="E29" s="8">
+        <v>3.97</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>24.73</v>
+      </c>
+      <c r="D30" s="6">
+        <v>28.33</v>
+      </c>
+      <c r="E30" s="8">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>73.77</v>
+      </c>
+      <c r="D31" s="6">
+        <v>80.89</v>
+      </c>
+      <c r="E31" s="8">
+        <v>7.12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-28.45</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-28.43</v>
+      </c>
+      <c r="E32" s="8">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>4.2</v>
+      </c>
+      <c r="D33" s="6">
+        <v>4.51</v>
+      </c>
+      <c r="E33" s="8">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-22.35</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-22.7</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-50.72</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-50.17</v>
+      </c>
+      <c r="E35" s="8">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-6.11</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-5.8</v>
+      </c>
+      <c r="E36" s="8">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>4.72</v>
+      </c>
+      <c r="D37" s="6">
+        <v>7.93</v>
+      </c>
+      <c r="E37" s="8">
+        <v>3.21</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-12.53</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-9.960000000000001</v>
+      </c>
+      <c r="E38" s="8">
+        <v>2.57</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-6.9</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-4.62</v>
+      </c>
+      <c r="E39" s="8">
+        <v>2.28</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-16.76</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-11.66</v>
+      </c>
+      <c r="E40" s="8">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-8.369999999999999</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-7.76</v>
+      </c>
+      <c r="E41" s="8">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-20.36</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-16.52</v>
+      </c>
+      <c r="E42" s="8">
+        <v>3.84</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="6">
+        <v>4.36</v>
+      </c>
+      <c r="D43" s="6">
+        <v>3.87</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-0.49</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-14.31</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-10.76</v>
+      </c>
+      <c r="E44" s="8">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-30.01</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-31.12</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-1.11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-3.12</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-1.34</v>
+      </c>
+      <c r="E46" s="8">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-18.78</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-17.2</v>
+      </c>
+      <c r="E47" s="8">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-10.18</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-8.98</v>
+      </c>
+      <c r="E48" s="8">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-16.76</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-13.62</v>
+      </c>
+      <c r="E49" s="8">
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-28.79</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-30.18</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-1.39</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-20.36</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-20.16</v>
+      </c>
+      <c r="E51" s="8">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="6">
+        <v>-27.27</v>
+      </c>
+      <c r="D52" s="6">
+        <v>-28.05</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-0.78</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="6">
+        <v>-50.07</v>
+      </c>
+      <c r="D53" s="6">
+        <v>-47.92</v>
+      </c>
+      <c r="E53" s="8">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>1331.7</v>
+      </c>
+      <c r="D54" s="6">
+        <v>1310.6</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-21.1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>3112</v>
+      </c>
+      <c r="D55" s="6">
+        <v>3169</v>
+      </c>
+      <c r="E55" s="8">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>1303.2</v>
+      </c>
+      <c r="D56" s="6">
+        <v>1328.5</v>
+      </c>
+      <c r="E56" s="8">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>1691.5</v>
+      </c>
+      <c r="D57" s="6">
+        <v>1714</v>
+      </c>
+      <c r="E57" s="8">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>207.2</v>
+      </c>
+      <c r="D58" s="6">
+        <v>215</v>
+      </c>
+      <c r="E58" s="8">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>419.2</v>
+      </c>
+      <c r="D59" s="6">
+        <v>411.05</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-8.15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="6">
+        <v>643.7</v>
+      </c>
+      <c r="D60" s="6">
+        <v>645.35</v>
+      </c>
+      <c r="E60" s="8">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="6">
+        <v>201.9</v>
+      </c>
+      <c r="D61" s="6">
+        <v>199.74</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-2.16</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="6">
+        <v>74.34999999999999</v>
+      </c>
+      <c r="D62" s="6">
+        <v>74.2</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="6">
+        <v>45</v>
+      </c>
+      <c r="D63" s="6">
+        <v>55</v>
+      </c>
+      <c r="E63" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="6">
+        <v>55</v>
+      </c>
+      <c r="D64" s="6">
+        <v>45</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>49.03</v>
+      </c>
+      <c r="D65" s="6">
+        <v>43.46</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-5.57</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>61.12</v>
+      </c>
+      <c r="D66" s="6">
+        <v>66.59</v>
+      </c>
+      <c r="E66" s="8">
+        <v>5.47</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>37.53</v>
+      </c>
+      <c r="D67" s="6">
+        <v>43.41</v>
+      </c>
+      <c r="E67" s="8">
+        <v>5.88</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>44.51</v>
+      </c>
+      <c r="D68" s="6">
+        <v>50.04</v>
+      </c>
+      <c r="E68" s="8">
+        <v>5.53</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>45.9</v>
+      </c>
+      <c r="D69" s="6">
+        <v>59.01</v>
+      </c>
+      <c r="E69" s="8">
+        <v>13.11</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="6">
+        <v>47.45</v>
+      </c>
+      <c r="D70" s="6">
+        <v>41.92</v>
+      </c>
+      <c r="E70" s="7">
+        <v>-5.53</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="6">
+        <v>39.54</v>
+      </c>
+      <c r="D71" s="6">
+        <v>40.68</v>
+      </c>
+      <c r="E71" s="8">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="6">
+        <v>67.27</v>
+      </c>
+      <c r="D72" s="6">
+        <v>62.4</v>
+      </c>
+      <c r="E72" s="7">
+        <v>-4.87</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="6">
+        <v>38.46</v>
+      </c>
+      <c r="D73" s="6">
+        <v>37.86</v>
+      </c>
+      <c r="E73" s="7">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="6">
+        <v>5.13</v>
+      </c>
+      <c r="D74" s="6">
+        <v>-59.15</v>
+      </c>
+      <c r="E74" s="7">
+        <v>-64.28</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
+        <v>91.84</v>
+      </c>
+      <c r="D75" s="6">
+        <v>61.53</v>
+      </c>
+      <c r="E75" s="7">
+        <v>-30.31</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>62.32</v>
+      </c>
+      <c r="D76" s="6">
+        <v>-47.18</v>
+      </c>
+      <c r="E76" s="7">
+        <v>-109.5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>-9.35</v>
+      </c>
+      <c r="D77" s="6">
+        <v>-4.62</v>
+      </c>
+      <c r="E77" s="8">
+        <v>4.73</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="6">
+        <v>62.88</v>
+      </c>
+      <c r="D78" s="6">
+        <v>386.06</v>
+      </c>
+      <c r="E78" s="8">
+        <v>323.18</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
+        <v>-12.28</v>
+      </c>
+      <c r="D79" s="6">
+        <v>-63.78</v>
+      </c>
+      <c r="E79" s="7">
+        <v>-51.5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="6">
+        <v>-24.58</v>
+      </c>
+      <c r="D80" s="6">
+        <v>-25.01</v>
+      </c>
+      <c r="E80" s="7">
         <v>-0.43</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="5">
-        <v>-3.82</v>
-      </c>
-      <c r="D10" s="5">
-        <v>-4.69</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-0.87</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5">
-        <v>-3.57</v>
-      </c>
-      <c r="D11" s="5">
-        <v>-0.5</v>
-      </c>
-      <c r="E11" s="6">
-        <v>3.07</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>-4.14</v>
-      </c>
-      <c r="D12" s="5">
-        <v>-1.6</v>
-      </c>
-      <c r="E12" s="6">
-        <v>2.54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-3.07</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-0.29</v>
-      </c>
-      <c r="E13" s="6">
-        <v>2.78</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+    <row r="81" spans="1:5">
+      <c r="A81" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="5">
-        <v>6.93</v>
-      </c>
-      <c r="D14" s="5">
-        <v>8.449999999999999</v>
-      </c>
-      <c r="E14" s="6">
-        <v>1.52</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B81" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="6">
+        <v>22.36</v>
+      </c>
+      <c r="D81" s="6">
+        <v>-12.2</v>
+      </c>
+      <c r="E81" s="7">
+        <v>-34.56</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-3.42</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-2.79</v>
-      </c>
-      <c r="E15" s="6">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>0.16</v>
-      </c>
-      <c r="D16" s="5">
-        <v>3.34</v>
-      </c>
-      <c r="E16" s="6">
-        <v>3.18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>3.58</v>
-      </c>
-      <c r="D17" s="5">
-        <v>4.07</v>
-      </c>
-      <c r="E17" s="6">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>1.68</v>
-      </c>
-      <c r="D18" s="5">
-        <v>0.79</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-0.89</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>1.21</v>
-      </c>
-      <c r="D19" s="5">
-        <v>0.57</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.64</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>0.36</v>
-      </c>
-      <c r="D20" s="5">
-        <v>1.56</v>
-      </c>
-      <c r="E20" s="6">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="5">
-        <v>0.17</v>
-      </c>
-      <c r="D21" s="5">
-        <v>2.87</v>
-      </c>
-      <c r="E21" s="6">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="5">
-        <v>-1.09</v>
-      </c>
-      <c r="D22" s="5">
-        <v>-3.09</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="5">
-        <v>5.58</v>
-      </c>
-      <c r="D23" s="5">
-        <v>6.98</v>
-      </c>
-      <c r="E23" s="6">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-1.23</v>
-      </c>
-      <c r="D24" s="5">
-        <v>1.38</v>
-      </c>
-      <c r="E24" s="6">
-        <v>2.61</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-29.5</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-27.6</v>
-      </c>
-      <c r="E25" s="6">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>30.34</v>
-      </c>
-      <c r="D26" s="5">
-        <v>30.97</v>
-      </c>
-      <c r="E26" s="6">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>36.28</v>
-      </c>
-      <c r="D27" s="5">
-        <v>34.82</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-1.46</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="5">
-        <v>24.75</v>
-      </c>
-      <c r="D28" s="5">
-        <v>24.73</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-0.02</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="5">
-        <v>71.95999999999999</v>
-      </c>
-      <c r="D29" s="5">
-        <v>73.77</v>
-      </c>
-      <c r="E29" s="6">
-        <v>1.81</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-29.86</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-28.45</v>
-      </c>
-      <c r="E30" s="6">
-        <v>1.41</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="5">
-        <v>1.6</v>
-      </c>
-      <c r="D31" s="5">
-        <v>4.2</v>
-      </c>
-      <c r="E31" s="6">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-23.11</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-22.35</v>
-      </c>
-      <c r="E32" s="6">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-48.52</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-50.72</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-2.2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-7.93</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-6.11</v>
-      </c>
-      <c r="E34" s="6">
-        <v>1.82</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="5">
-        <v>4.65</v>
-      </c>
-      <c r="D35" s="5">
-        <v>4.72</v>
-      </c>
-      <c r="E35" s="6">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-10.73</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-12.53</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-1.8</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-6.28</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-6.9</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.62</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-17.11</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-16.76</v>
-      </c>
-      <c r="E38" s="6">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-9.699999999999999</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-8.369999999999999</v>
-      </c>
-      <c r="E39" s="6">
-        <v>1.33</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-20.79</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-20.36</v>
-      </c>
-      <c r="E40" s="6">
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="5">
-        <v>3.71</v>
-      </c>
-      <c r="D41" s="5">
-        <v>4.36</v>
-      </c>
-      <c r="E41" s="6">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="5">
-        <v>-13.83</v>
-      </c>
-      <c r="D42" s="5">
-        <v>-14.31</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-0.48</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-31.37</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-30.01</v>
-      </c>
-      <c r="E43" s="6">
-        <v>1.36</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-3.18</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-3.12</v>
-      </c>
-      <c r="E44" s="6">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-17.11</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-18.78</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-1.67</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-9.58</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-10.18</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="5">
-        <v>-17.11</v>
-      </c>
-      <c r="D47" s="5">
-        <v>-16.76</v>
-      </c>
-      <c r="E47" s="6">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="5">
-        <v>-29.83</v>
-      </c>
-      <c r="D48" s="5">
-        <v>-28.79</v>
-      </c>
-      <c r="E48" s="6">
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="5">
-        <v>-20.79</v>
-      </c>
-      <c r="D49" s="5">
-        <v>-20.36</v>
-      </c>
-      <c r="E49" s="6">
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="5">
-        <v>-27.72</v>
-      </c>
-      <c r="D50" s="5">
-        <v>-27.27</v>
-      </c>
-      <c r="E50" s="6">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="5">
-        <v>-50.44</v>
-      </c>
-      <c r="D51" s="5">
-        <v>-50.07</v>
-      </c>
-      <c r="E51" s="6">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="5">
-        <v>1305.9</v>
-      </c>
-      <c r="D52" s="5">
-        <v>1331.7</v>
-      </c>
-      <c r="E52" s="6">
-        <v>25.8</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="5">
-        <v>3110</v>
-      </c>
-      <c r="D53" s="5">
-        <v>3112</v>
-      </c>
-      <c r="E53" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="5">
-        <v>1330</v>
-      </c>
-      <c r="D54" s="5">
-        <v>1303.2</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-26.8</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="5">
-        <v>1702.7</v>
-      </c>
-      <c r="D55" s="5">
-        <v>1691.5</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-11.2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="5">
-        <v>206.33</v>
-      </c>
-      <c r="D56" s="5">
-        <v>207.2</v>
-      </c>
-      <c r="E56" s="6">
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="5">
-        <v>413.1</v>
-      </c>
-      <c r="D57" s="5">
-        <v>419.2</v>
-      </c>
-      <c r="E57" s="6">
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="5">
-        <v>640.25</v>
-      </c>
-      <c r="D58" s="5">
-        <v>643.7</v>
-      </c>
-      <c r="E58" s="6">
-        <v>3.45</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="5">
-        <v>200.64</v>
-      </c>
-      <c r="D59" s="5">
-        <v>201.9</v>
-      </c>
-      <c r="E59" s="6">
-        <v>1.26</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="5">
-        <v>74.77</v>
-      </c>
-      <c r="D60" s="5">
-        <v>74.34999999999999</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-0.42</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="5">
-        <v>40.36</v>
-      </c>
-      <c r="D61" s="5">
-        <v>49.03</v>
-      </c>
-      <c r="E61" s="6">
-        <v>8.67</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="5">
-        <v>60.91</v>
-      </c>
-      <c r="D62" s="5">
-        <v>61.12</v>
-      </c>
-      <c r="E62" s="6">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="5">
-        <v>41.8</v>
-      </c>
-      <c r="D63" s="5">
-        <v>37.53</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-4.27</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="5">
-        <v>46.91</v>
-      </c>
-      <c r="D64" s="5">
-        <v>44.51</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-2.4</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="5">
-        <v>44.05</v>
-      </c>
-      <c r="D65" s="5">
-        <v>45.9</v>
-      </c>
-      <c r="E65" s="6">
-        <v>1.85</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="5">
-        <v>42.14</v>
-      </c>
-      <c r="D66" s="5">
-        <v>47.45</v>
-      </c>
-      <c r="E66" s="6">
-        <v>5.31</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="5">
-        <v>37.22</v>
-      </c>
-      <c r="D67" s="5">
-        <v>39.54</v>
-      </c>
-      <c r="E67" s="6">
-        <v>2.32</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="5">
-        <v>65.83</v>
-      </c>
-      <c r="D68" s="5">
-        <v>67.27</v>
-      </c>
-      <c r="E68" s="6">
-        <v>1.44</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="5">
-        <v>40.1</v>
-      </c>
-      <c r="D69" s="5">
-        <v>38.46</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-1.64</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B70" s="3" t="s">
+      <c r="B82" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C70" s="5">
-        <v>-58.24</v>
-      </c>
-      <c r="D70" s="5">
-        <v>5.13</v>
-      </c>
-      <c r="E70" s="6">
-        <v>63.37</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="5">
-        <v>102.42</v>
-      </c>
-      <c r="D71" s="5">
-        <v>91.84</v>
-      </c>
-      <c r="E71" s="7">
-        <v>-10.58</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="5">
-        <v>65.38</v>
-      </c>
-      <c r="D72" s="5">
-        <v>62.32</v>
-      </c>
-      <c r="E72" s="7">
-        <v>-3.06</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="5">
-        <v>-40.56</v>
-      </c>
-      <c r="D73" s="5">
-        <v>-9.35</v>
-      </c>
-      <c r="E73" s="6">
-        <v>31.21</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="5">
-        <v>0.72</v>
-      </c>
-      <c r="D74" s="5">
-        <v>62.88</v>
-      </c>
-      <c r="E74" s="6">
-        <v>62.16</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="5">
-        <v>-52.6</v>
-      </c>
-      <c r="D75" s="5">
-        <v>-12.28</v>
-      </c>
-      <c r="E75" s="6">
-        <v>40.32</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="5">
-        <v>-51.09</v>
-      </c>
-      <c r="D76" s="5">
-        <v>-24.58</v>
-      </c>
-      <c r="E76" s="6">
-        <v>26.51</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="5">
-        <v>445.09</v>
-      </c>
-      <c r="D77" s="5">
-        <v>22.36</v>
-      </c>
-      <c r="E77" s="7">
-        <v>-422.73</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="5">
-        <v>14.04</v>
-      </c>
-      <c r="D78" s="5">
+      <c r="C82" s="6">
         <v>85.36</v>
       </c>
-      <c r="E78" s="6">
-        <v>71.31999999999999</v>
+      <c r="D82" s="6">
+        <v>-45.15</v>
+      </c>
+      <c r="E82" s="7">
+        <v>-130.51</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3345,60 +3506,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="8" t="s">
+      <c r="B1" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="11">
+        <v>56.16</v>
+      </c>
+      <c r="C2" s="12">
+        <v>9</v>
+      </c>
+      <c r="D2" s="11">
+        <v>49.5</v>
+      </c>
+      <c r="E2" s="11">
         <v>60</v>
       </c>
-      <c r="E1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="10">
-        <v>56.16</v>
-      </c>
-      <c r="C2" s="11">
-        <v>9</v>
-      </c>
-      <c r="D2" s="10">
-        <v>47.9</v>
-      </c>
-      <c r="E2" s="10">
-        <v>60</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-0.4</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-8.5</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-0.6</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-6.1</v>
+      </c>
+      <c r="H2" s="11">
         <v>55.4</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -3500,61 +3661,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="13" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="13">
-        <v>0.6484000000000001</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.1922</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.1615</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.0449</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.0181</v>
-      </c>
-      <c r="F2" s="13">
-        <v>-0.0106</v>
-      </c>
-      <c r="G2" s="13">
-        <v>-0.06059999999999999</v>
-      </c>
-      <c r="H2" s="13">
-        <v>-0.0935</v>
-      </c>
-      <c r="I2" s="13">
-        <v>-0.1314</v>
+      <c r="A2" s="14">
+        <v>0.6445000000000001</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1936</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.161</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.0484</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.008199999999999999</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.009300000000000001</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.06280000000000001</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.102</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.1332</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,43 +193,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Near 52W High</t>
-  </si>
-  <si>
-    <t>-3.1% → -1.3%</t>
-  </si>
-  <si>
-    <t>🟢 BREAKOUT WATCH</t>
-  </si>
-  <si>
-    <t>-3.1%</t>
-  </si>
-  <si>
-    <t>-1.3%</t>
-  </si>
-  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>44.5 → 50.0</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>44.5</t>
+    <t>50.0 → 48.5</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>50.0</t>
   </si>
   <si>
-    <t>45.9 → 59.0</t>
-  </si>
-  <si>
-    <t>45.9</t>
-  </si>
-  <si>
-    <t>59.0</t>
+    <t>48.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -315,14 +291,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -355,13 +331,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -954,10 +930,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1310.6</v>
+        <v>1306.4</v>
       </c>
       <c r="D2">
-        <v>-1.58</v>
+        <v>-0.32</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -966,46 +942,46 @@
         <v>1247.38</v>
       </c>
       <c r="G2">
-        <v>-31.12</v>
+        <v>-31.34</v>
       </c>
       <c r="H2">
-        <v>5.07</v>
+        <v>4.73</v>
       </c>
       <c r="I2">
-        <v>0.73</v>
+        <v>-0.08</v>
       </c>
       <c r="J2">
-        <v>-4.39</v>
+        <v>-3.69</v>
       </c>
       <c r="K2">
-        <v>-5.8</v>
+        <v>-3.39</v>
       </c>
       <c r="L2">
-        <v>-27.62</v>
+        <v>-27.31</v>
       </c>
       <c r="M2">
-        <v>-10.2</v>
+        <v>-10.56</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P2">
-        <v>1311.3</v>
+        <v>1311.1</v>
       </c>
       <c r="Q2">
-        <v>1335.92</v>
+        <v>1333.37</v>
       </c>
       <c r="R2">
-        <v>1349.81</v>
+        <v>1348.76</v>
       </c>
       <c r="S2">
-        <v>1508.64</v>
+        <v>1506</v>
       </c>
       <c r="T2">
-        <v>-13.13</v>
+        <v>-13.25</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1020,34 +996,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>43.46</v>
+        <v>42.43</v>
       </c>
       <c r="Z2">
-        <v>-14.09</v>
+        <v>-14</v>
       </c>
       <c r="AA2">
-        <v>-13.14</v>
+        <v>-13.31</v>
       </c>
       <c r="AB2">
-        <v>-0.95</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AC2">
-        <v>67.09999999999999</v>
+        <v>74.28</v>
       </c>
       <c r="AD2">
-        <v>49.81</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="AE2">
-        <v>24.78</v>
+        <v>23.8</v>
       </c>
       <c r="AF2">
-        <v>-59.15</v>
+        <v>-57.59</v>
       </c>
       <c r="AG2">
-        <v>1403.78</v>
+        <v>1401.66</v>
       </c>
       <c r="AH2">
-        <v>1268.05</v>
+        <v>1265.07</v>
       </c>
       <c r="AI2">
         <v>1373.07</v>
@@ -1056,7 +1032,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>30.77</v>
+        <v>27.14</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1067,10 +1043,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3169</v>
+        <v>3168.5</v>
       </c>
       <c r="D3">
-        <v>1.83</v>
+        <v>-0.02</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1079,46 +1055,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-1.34</v>
+        <v>-1.36</v>
       </c>
       <c r="H3">
-        <v>80.26000000000001</v>
+        <v>80.23</v>
       </c>
       <c r="I3">
-        <v>5.81</v>
+        <v>5.72</v>
       </c>
       <c r="J3">
-        <v>4.78</v>
+        <v>3.92</v>
       </c>
       <c r="K3">
-        <v>7.93</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="L3">
-        <v>36.37</v>
+        <v>37.65</v>
       </c>
       <c r="M3">
-        <v>16.1</v>
+        <v>15.95</v>
       </c>
       <c r="N3">
         <v>88</v>
       </c>
       <c r="O3">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P3">
-        <v>3077.32</v>
+        <v>3111.62</v>
       </c>
       <c r="Q3">
-        <v>3029.82</v>
+        <v>3037.77</v>
       </c>
       <c r="R3">
-        <v>3068.07</v>
+        <v>3071.17</v>
       </c>
       <c r="S3">
-        <v>2495.94</v>
+        <v>2500.31</v>
       </c>
       <c r="T3">
-        <v>26.97</v>
+        <v>26.72</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1133,43 +1109,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>66.59</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="Z3">
-        <v>11.58</v>
+        <v>19.66</v>
       </c>
       <c r="AA3">
-        <v>-5.52</v>
+        <v>-0.49</v>
       </c>
       <c r="AB3">
-        <v>17.1</v>
+        <v>20.15</v>
       </c>
       <c r="AC3">
-        <v>100</v>
+        <v>99.89</v>
       </c>
       <c r="AD3">
-        <v>86.29000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="AE3">
-        <v>65.51000000000001</v>
+        <v>63.72</v>
       </c>
       <c r="AF3">
-        <v>61.53</v>
+        <v>-52.7</v>
       </c>
       <c r="AG3">
-        <v>3131.58</v>
+        <v>3156.31</v>
       </c>
       <c r="AH3">
-        <v>2928.05</v>
+        <v>2919.22</v>
       </c>
       <c r="AI3">
-        <v>2959.69</v>
+        <v>2962.35</v>
       </c>
       <c r="AJ3" t="s">
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>31.78</v>
+        <v>34.56</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1180,10 +1156,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1328.5</v>
+        <v>1311</v>
       </c>
       <c r="D4">
-        <v>1.94</v>
+        <v>-1.32</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1192,46 +1168,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-17.2</v>
+        <v>-18.29</v>
       </c>
       <c r="H4">
-        <v>71.91</v>
+        <v>69.64</v>
       </c>
       <c r="I4">
-        <v>2.05</v>
+        <v>-0.68</v>
       </c>
       <c r="J4">
-        <v>-3.25</v>
+        <v>-3.51</v>
       </c>
       <c r="K4">
-        <v>-9.960000000000001</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="L4">
-        <v>38.79</v>
+        <v>35.98</v>
       </c>
       <c r="M4">
-        <v>4.84</v>
+        <v>4.34</v>
       </c>
       <c r="N4">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="O4">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="P4">
-        <v>1317.94</v>
+        <v>1316.14</v>
       </c>
       <c r="Q4">
-        <v>1342.02</v>
+        <v>1338.42</v>
       </c>
       <c r="R4">
-        <v>1435.83</v>
+        <v>1431.92</v>
       </c>
       <c r="S4">
-        <v>1170.53</v>
+        <v>1171.86</v>
       </c>
       <c r="T4">
-        <v>13.5</v>
+        <v>11.87</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1246,43 +1222,43 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>43.41</v>
+        <v>40.57</v>
       </c>
       <c r="Z4">
-        <v>-32.71</v>
+        <v>-31.54</v>
       </c>
       <c r="AA4">
-        <v>-36.23</v>
+        <v>-35.29</v>
       </c>
       <c r="AB4">
-        <v>3.52</v>
+        <v>3.75</v>
       </c>
       <c r="AC4">
-        <v>87</v>
+        <v>79.45</v>
       </c>
       <c r="AD4">
-        <v>81.70999999999999</v>
+        <v>80.64</v>
       </c>
       <c r="AE4">
-        <v>36.29</v>
+        <v>35.5</v>
       </c>
       <c r="AF4">
-        <v>-47.18</v>
+        <v>-48.12</v>
       </c>
       <c r="AG4">
-        <v>1407.4</v>
+        <v>1402.21</v>
       </c>
       <c r="AH4">
-        <v>1276.63</v>
+        <v>1274.62</v>
       </c>
       <c r="AI4">
-        <v>1418.72</v>
+        <v>1418.61</v>
       </c>
       <c r="AJ4" t="s">
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>22.25</v>
+        <v>19.57</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1293,10 +1269,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1714</v>
+        <v>1707.5</v>
       </c>
       <c r="D5">
-        <v>1.33</v>
+        <v>-0.38</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1305,46 +1281,46 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-8.98</v>
+        <v>-9.33</v>
       </c>
       <c r="H5">
-        <v>32.04</v>
+        <v>31.54</v>
       </c>
       <c r="I5">
-        <v>1.06</v>
+        <v>0.44</v>
       </c>
       <c r="J5">
-        <v>-0.33</v>
+        <v>2.61</v>
       </c>
       <c r="K5">
-        <v>-4.62</v>
+        <v>-3.86</v>
       </c>
       <c r="L5">
-        <v>28.33</v>
+        <v>27.92</v>
       </c>
       <c r="M5">
-        <v>19.36</v>
+        <v>19.19</v>
       </c>
       <c r="N5">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="O5">
         <v>68</v>
       </c>
       <c r="P5">
-        <v>1696.06</v>
+        <v>1697.56</v>
       </c>
       <c r="Q5">
-        <v>1690.27</v>
+        <v>1690.82</v>
       </c>
       <c r="R5">
-        <v>1762.48</v>
+        <v>1759.79</v>
       </c>
       <c r="S5">
-        <v>1596.56</v>
+        <v>1597.75</v>
       </c>
       <c r="T5">
-        <v>7.36</v>
+        <v>6.87</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1359,34 +1335,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>50.04</v>
+        <v>48.54</v>
       </c>
       <c r="Z5">
-        <v>-16.63</v>
+        <v>-14.47</v>
       </c>
       <c r="AA5">
-        <v>-23.38</v>
+        <v>-21.6</v>
       </c>
       <c r="AB5">
-        <v>6.75</v>
+        <v>7.13</v>
       </c>
       <c r="AC5">
-        <v>95.25</v>
+        <v>92.73999999999999</v>
       </c>
       <c r="AD5">
-        <v>87.62</v>
+        <v>89.8</v>
       </c>
       <c r="AE5">
-        <v>31.48</v>
+        <v>31</v>
       </c>
       <c r="AF5">
-        <v>-4.62</v>
+        <v>63.55</v>
       </c>
       <c r="AG5">
-        <v>1720.37</v>
+        <v>1721.79</v>
       </c>
       <c r="AH5">
-        <v>1660.18</v>
+        <v>1659.86</v>
       </c>
       <c r="AI5">
         <v>1761.08</v>
@@ -1395,7 +1371,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>23.5</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1406,10 +1382,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>215</v>
+        <v>212.63</v>
       </c>
       <c r="D6">
-        <v>3.76</v>
+        <v>-1.1</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1418,46 +1394,46 @@
         <v>118.42</v>
       </c>
       <c r="G6">
-        <v>-13.62</v>
+        <v>-14.58</v>
       </c>
       <c r="H6">
-        <v>81.56</v>
+        <v>79.56</v>
       </c>
       <c r="I6">
-        <v>5.39</v>
+        <v>3.47</v>
       </c>
       <c r="J6">
-        <v>2.62</v>
+        <v>1.75</v>
       </c>
       <c r="K6">
-        <v>-11.66</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="L6">
-        <v>80.89</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="M6">
-        <v>64.45</v>
+        <v>62.59</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P6">
-        <v>207.55</v>
+        <v>208.97</v>
       </c>
       <c r="Q6">
-        <v>207.69</v>
+        <v>207.76</v>
       </c>
       <c r="R6">
-        <v>215.38</v>
+        <v>215.02</v>
       </c>
       <c r="S6">
-        <v>181.17</v>
+        <v>181.48</v>
       </c>
       <c r="T6">
-        <v>18.67</v>
+        <v>17.16</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1472,34 +1448,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>59.01</v>
+        <v>54.68</v>
       </c>
       <c r="Z6">
-        <v>-1.84</v>
+        <v>-1.3</v>
       </c>
       <c r="AA6">
-        <v>-2.92</v>
+        <v>-2.6</v>
       </c>
       <c r="AB6">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="AC6">
-        <v>100</v>
+        <v>93.95999999999999</v>
       </c>
       <c r="AD6">
-        <v>81.34999999999999</v>
+        <v>90.63</v>
       </c>
       <c r="AE6">
-        <v>5.15</v>
+        <v>5.18</v>
       </c>
       <c r="AF6">
-        <v>386.06</v>
+        <v>-16.9</v>
       </c>
       <c r="AG6">
-        <v>214.21</v>
+        <v>214.45</v>
       </c>
       <c r="AH6">
-        <v>201.18</v>
+        <v>201.07</v>
       </c>
       <c r="AI6">
         <v>217.63</v>
@@ -1508,7 +1484,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>28.29</v>
+        <v>32.02</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1519,10 +1495,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>411.05</v>
+        <v>412.05</v>
       </c>
       <c r="D7">
-        <v>-1.94</v>
+        <v>0.24</v>
       </c>
       <c r="E7">
         <v>588.6900000000001</v>
@@ -1531,46 +1507,46 @@
         <v>393.4</v>
       </c>
       <c r="G7">
-        <v>-30.18</v>
+        <v>-30.01</v>
       </c>
       <c r="H7">
-        <v>4.49</v>
+        <v>4.74</v>
       </c>
       <c r="I7">
-        <v>0.01</v>
+        <v>-0.59</v>
       </c>
       <c r="J7">
-        <v>-5.57</v>
+        <v>-5.1</v>
       </c>
       <c r="K7">
-        <v>-7.76</v>
+        <v>-4.79</v>
       </c>
       <c r="L7">
-        <v>-28.43</v>
+        <v>-28.73</v>
       </c>
       <c r="M7">
-        <v>0.82</v>
+        <v>0.5</v>
       </c>
       <c r="N7">
         <v>23</v>
       </c>
       <c r="O7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P7">
-        <v>413.32</v>
+        <v>412.83</v>
       </c>
       <c r="Q7">
-        <v>422.66</v>
+        <v>421.65</v>
       </c>
       <c r="R7">
-        <v>427.1</v>
+        <v>426.74</v>
       </c>
       <c r="S7">
-        <v>473.07</v>
+        <v>472.36</v>
       </c>
       <c r="T7">
-        <v>-13.11</v>
+        <v>-12.77</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1585,34 +1561,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>41.92</v>
+        <v>42.8</v>
       </c>
       <c r="Z7">
-        <v>-5.17</v>
+        <v>-5.12</v>
       </c>
       <c r="AA7">
-        <v>-4.51</v>
+        <v>-4.63</v>
       </c>
       <c r="AB7">
-        <v>-0.67</v>
+        <v>-0.49</v>
       </c>
       <c r="AC7">
-        <v>59</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="AD7">
-        <v>44.76</v>
+        <v>56.97</v>
       </c>
       <c r="AE7">
-        <v>9.4</v>
+        <v>8.98</v>
       </c>
       <c r="AF7">
-        <v>-63.78</v>
+        <v>-22.2</v>
       </c>
       <c r="AG7">
-        <v>446.41</v>
+        <v>445.41</v>
       </c>
       <c r="AH7">
-        <v>398.92</v>
+        <v>397.9</v>
       </c>
       <c r="AI7">
         <v>436.39</v>
@@ -1621,7 +1597,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>26.67</v>
+        <v>23.81</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1632,10 +1608,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>645.35</v>
+        <v>636.5</v>
       </c>
       <c r="D8">
-        <v>0.26</v>
+        <v>-1.37</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1644,46 +1620,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-20.16</v>
+        <v>-21.25</v>
       </c>
       <c r="H8">
-        <v>37.97</v>
+        <v>36.08</v>
       </c>
       <c r="I8">
-        <v>-1.87</v>
+        <v>-1.49</v>
       </c>
       <c r="J8">
-        <v>-1.61</v>
+        <v>-2.1</v>
       </c>
       <c r="K8">
-        <v>-16.52</v>
+        <v>-13.23</v>
       </c>
       <c r="L8">
-        <v>4.51</v>
+        <v>0.87</v>
       </c>
       <c r="M8">
-        <v>-13.32</v>
+        <v>-14.37</v>
       </c>
       <c r="N8">
         <v>55</v>
       </c>
       <c r="O8">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="P8">
-        <v>643</v>
+        <v>641.08</v>
       </c>
       <c r="Q8">
-        <v>654.55</v>
+        <v>653.8</v>
       </c>
       <c r="R8">
-        <v>684.74</v>
+        <v>682.98</v>
       </c>
       <c r="S8">
-        <v>613.87</v>
+        <v>613.99</v>
       </c>
       <c r="T8">
-        <v>5.13</v>
+        <v>3.67</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1698,43 +1674,43 @@
         <v>2</v>
       </c>
       <c r="Y8">
-        <v>40.68</v>
+        <v>36.7</v>
       </c>
       <c r="Z8">
-        <v>-10.22</v>
+        <v>-10.52</v>
       </c>
       <c r="AA8">
-        <v>-10.69</v>
+        <v>-10.65</v>
       </c>
       <c r="AB8">
-        <v>0.46</v>
+        <v>0.13</v>
       </c>
       <c r="AC8">
-        <v>25.99</v>
+        <v>24.44</v>
       </c>
       <c r="AD8">
-        <v>17.86</v>
+        <v>21.55</v>
       </c>
       <c r="AE8">
-        <v>15.98</v>
+        <v>15.58</v>
       </c>
       <c r="AF8">
-        <v>-25.01</v>
+        <v>-69.02</v>
       </c>
       <c r="AG8">
-        <v>672.46</v>
+        <v>673.4299999999999</v>
       </c>
       <c r="AH8">
-        <v>636.63</v>
+        <v>634.17</v>
       </c>
       <c r="AI8">
-        <v>690.22</v>
+        <v>686.8099999999999</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>19.32</v>
+        <v>16.89</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1745,10 +1721,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>199.74</v>
+        <v>196.27</v>
       </c>
       <c r="D9">
-        <v>-1.07</v>
+        <v>-1.74</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1757,46 +1733,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-28.05</v>
+        <v>-29.3</v>
       </c>
       <c r="H9">
-        <v>15.93</v>
+        <v>13.91</v>
       </c>
       <c r="I9">
-        <v>5.88</v>
+        <v>4.33</v>
       </c>
       <c r="J9">
-        <v>5.18</v>
+        <v>4.63</v>
       </c>
       <c r="K9">
-        <v>3.87</v>
+        <v>2.95</v>
       </c>
       <c r="L9">
-        <v>-22.7</v>
+        <v>-24.41</v>
       </c>
       <c r="M9">
-        <v>-6.28</v>
+        <v>-6.64</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="P9">
-        <v>196.86</v>
+        <v>198.49</v>
       </c>
       <c r="Q9">
-        <v>193.5</v>
+        <v>193.85</v>
       </c>
       <c r="R9">
-        <v>189.76</v>
+        <v>189.83</v>
       </c>
       <c r="S9">
-        <v>205.8</v>
+        <v>205.41</v>
       </c>
       <c r="T9">
-        <v>-2.95</v>
+        <v>-4.45</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1811,34 +1787,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>62.4</v>
+        <v>55.46</v>
       </c>
       <c r="Z9">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AA9">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AB9">
-        <v>0.87</v>
+        <v>0.67</v>
       </c>
       <c r="AC9">
-        <v>93.14</v>
+        <v>76.48</v>
       </c>
       <c r="AD9">
-        <v>78.27</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="AE9">
-        <v>5.36</v>
+        <v>5.3</v>
       </c>
       <c r="AF9">
-        <v>-12.2</v>
+        <v>-71.51000000000001</v>
       </c>
       <c r="AG9">
-        <v>201.81</v>
+        <v>202.01</v>
       </c>
       <c r="AH9">
-        <v>185.2</v>
+        <v>185.68</v>
       </c>
       <c r="AI9">
         <v>185.88</v>
@@ -1847,7 +1823,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>37.4</v>
+        <v>35.66</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1858,37 +1834,37 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>74.2</v>
+        <v>73.77</v>
       </c>
       <c r="D10">
-        <v>-0.2</v>
+        <v>-0.58</v>
       </c>
       <c r="E10">
-        <v>142.47</v>
+        <v>141.99</v>
       </c>
       <c r="F10">
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-47.92</v>
+        <v>-48.05</v>
       </c>
       <c r="H10">
-        <v>25.17</v>
+        <v>24.44</v>
       </c>
       <c r="I10">
-        <v>-1.72</v>
+        <v>-2.28</v>
       </c>
       <c r="J10">
-        <v>-2.62</v>
+        <v>-3.25</v>
       </c>
       <c r="K10">
-        <v>-10.76</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="L10">
-        <v>-50.17</v>
+        <v>-48.22</v>
       </c>
       <c r="M10">
-        <v>-0.93</v>
+        <v>-1.37</v>
       </c>
       <c r="N10">
         <v>12</v>
@@ -1897,19 +1873,19 @@
         <v>6</v>
       </c>
       <c r="P10">
-        <v>74.79000000000001</v>
+        <v>74.45</v>
       </c>
       <c r="Q10">
-        <v>75.98</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="R10">
-        <v>78.40000000000001</v>
+        <v>78.20999999999999</v>
       </c>
       <c r="S10">
-        <v>81.39</v>
+        <v>81.31999999999999</v>
       </c>
       <c r="T10">
-        <v>-8.83</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1924,43 +1900,43 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>37.86</v>
+        <v>36.13</v>
       </c>
       <c r="Z10">
-        <v>-1.05</v>
+        <v>-1.09</v>
       </c>
       <c r="AA10">
-        <v>-1</v>
+        <v>-1.02</v>
       </c>
       <c r="AB10">
-        <v>-0.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AC10">
-        <v>58.91</v>
+        <v>49.77</v>
       </c>
       <c r="AD10">
-        <v>67.84</v>
+        <v>58.64</v>
       </c>
       <c r="AE10">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AF10">
-        <v>-45.15</v>
+        <v>-38.18</v>
       </c>
       <c r="AG10">
-        <v>78.28</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="AH10">
-        <v>73.68000000000001</v>
+        <v>73.38</v>
       </c>
       <c r="AI10">
-        <v>80.34</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="AJ10" t="s">
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>39.81</v>
+        <v>43.43</v>
       </c>
     </row>
   </sheetData>
@@ -2101,7 +2077,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2141,7 +2117,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2159,1334 +2135,1294 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-4.39</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-3.69</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>74</v>
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>4.78</v>
+      </c>
+      <c r="D8" s="6">
+        <v>3.92</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-0.86</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-0.75</v>
+        <v>-3.25</v>
       </c>
       <c r="D9" s="6">
-        <v>-4.39</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-3.64</v>
+        <v>-3.51</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-0.26</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>3.65</v>
+        <v>-0.33</v>
       </c>
       <c r="D10" s="6">
-        <v>4.78</v>
-      </c>
-      <c r="E10" s="8">
-        <v>1.13</v>
+        <v>2.61</v>
+      </c>
+      <c r="E10" s="7">
+        <v>2.94</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-5.41</v>
+        <v>2.62</v>
       </c>
       <c r="D11" s="6">
-        <v>-3.25</v>
+        <v>1.75</v>
       </c>
       <c r="E11" s="8">
-        <v>2.16</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-4.69</v>
+        <v>-5.57</v>
       </c>
       <c r="D12" s="6">
-        <v>-0.33</v>
-      </c>
-      <c r="E12" s="8">
-        <v>4.36</v>
+        <v>-5.1</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.47</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-0.5</v>
+        <v>-1.61</v>
       </c>
       <c r="D13" s="6">
-        <v>2.62</v>
+        <v>-2.1</v>
       </c>
       <c r="E13" s="8">
-        <v>3.12</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-1.6</v>
+        <v>5.18</v>
       </c>
       <c r="D14" s="6">
-        <v>-5.57</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-3.97</v>
+        <v>4.63</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-0.29</v>
+        <v>-2.62</v>
       </c>
       <c r="D15" s="6">
-        <v>-1.61</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-1.32</v>
+        <v>-3.25</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-0.63</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>8.449999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="D16" s="6">
-        <v>5.18</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-3.27</v>
+        <v>-0.08</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-2.79</v>
+        <v>5.81</v>
       </c>
       <c r="D17" s="6">
-        <v>-2.62</v>
+        <v>5.72</v>
       </c>
       <c r="E17" s="8">
-        <v>0.17</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>3.34</v>
+        <v>2.05</v>
       </c>
       <c r="D18" s="6">
-        <v>0.73</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-2.61</v>
+        <v>-0.68</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-2.73</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>4.07</v>
+        <v>1.06</v>
       </c>
       <c r="D19" s="6">
-        <v>5.81</v>
+        <v>0.44</v>
       </c>
       <c r="E19" s="8">
-        <v>1.74</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>0.79</v>
+        <v>5.39</v>
       </c>
       <c r="D20" s="6">
-        <v>2.05</v>
+        <v>3.47</v>
       </c>
       <c r="E20" s="8">
-        <v>1.26</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>0.57</v>
+        <v>0.01</v>
       </c>
       <c r="D21" s="6">
-        <v>1.06</v>
+        <v>-0.59</v>
       </c>
       <c r="E21" s="8">
-        <v>0.49</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>1.56</v>
+        <v>-1.87</v>
       </c>
       <c r="D22" s="6">
-        <v>5.39</v>
-      </c>
-      <c r="E22" s="8">
-        <v>3.83</v>
+        <v>-1.49</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.38</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>2.87</v>
+        <v>5.88</v>
       </c>
       <c r="D23" s="6">
-        <v>0.01</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-2.86</v>
+        <v>4.33</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-1.55</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>-3.09</v>
+        <v>-1.72</v>
       </c>
       <c r="D24" s="6">
-        <v>-1.87</v>
+        <v>-2.28</v>
       </c>
       <c r="E24" s="8">
-        <v>1.22</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>6.98</v>
+        <v>-27.62</v>
       </c>
       <c r="D25" s="6">
-        <v>5.88</v>
+        <v>-27.31</v>
       </c>
       <c r="E25" s="7">
-        <v>-1.1</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>1.38</v>
+        <v>36.37</v>
       </c>
       <c r="D26" s="6">
-        <v>-1.72</v>
+        <v>37.65</v>
       </c>
       <c r="E26" s="7">
-        <v>-3.1</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>-27.6</v>
+        <v>38.79</v>
       </c>
       <c r="D27" s="6">
-        <v>-27.62</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-0.02</v>
+        <v>35.98</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-2.81</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>30.97</v>
+        <v>28.33</v>
       </c>
       <c r="D28" s="6">
-        <v>36.37</v>
+        <v>27.92</v>
       </c>
       <c r="E28" s="8">
-        <v>5.4</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>34.82</v>
+        <v>80.89</v>
       </c>
       <c r="D29" s="6">
-        <v>38.79</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="E29" s="8">
-        <v>3.97</v>
+        <v>-5.35</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>24.73</v>
+        <v>-28.43</v>
       </c>
       <c r="D30" s="6">
-        <v>28.33</v>
+        <v>-28.73</v>
       </c>
       <c r="E30" s="8">
-        <v>3.6</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>73.77</v>
+        <v>4.51</v>
       </c>
       <c r="D31" s="6">
-        <v>80.89</v>
+        <v>0.87</v>
       </c>
       <c r="E31" s="8">
-        <v>7.12</v>
+        <v>-3.64</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>-28.45</v>
+        <v>-22.7</v>
       </c>
       <c r="D32" s="6">
-        <v>-28.43</v>
+        <v>-24.41</v>
       </c>
       <c r="E32" s="8">
-        <v>0.02</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>4.2</v>
+        <v>-50.17</v>
       </c>
       <c r="D33" s="6">
-        <v>4.51</v>
-      </c>
-      <c r="E33" s="8">
-        <v>0.31</v>
+        <v>-48.22</v>
+      </c>
+      <c r="E33" s="7">
+        <v>1.95</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>-22.35</v>
+        <v>-5.8</v>
       </c>
       <c r="D34" s="6">
-        <v>-22.7</v>
+        <v>-3.39</v>
       </c>
       <c r="E34" s="7">
-        <v>-0.35</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-50.72</v>
+        <v>7.93</v>
       </c>
       <c r="D35" s="6">
-        <v>-50.17</v>
-      </c>
-      <c r="E35" s="8">
-        <v>0.55</v>
+        <v>8.949999999999999</v>
+      </c>
+      <c r="E35" s="7">
+        <v>1.02</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>-6.11</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="D36" s="6">
-        <v>-5.8</v>
-      </c>
-      <c r="E36" s="8">
-        <v>0.31</v>
+        <v>-9.390000000000001</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0.57</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>4.72</v>
+        <v>-4.62</v>
       </c>
       <c r="D37" s="6">
-        <v>7.93</v>
-      </c>
-      <c r="E37" s="8">
-        <v>3.21</v>
+        <v>-3.86</v>
+      </c>
+      <c r="E37" s="7">
+        <v>0.76</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>-12.53</v>
+        <v>-11.66</v>
       </c>
       <c r="D38" s="6">
-        <v>-9.960000000000001</v>
-      </c>
-      <c r="E38" s="8">
-        <v>2.57</v>
+        <v>-8.470000000000001</v>
+      </c>
+      <c r="E38" s="7">
+        <v>3.19</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>-6.9</v>
+        <v>-7.76</v>
       </c>
       <c r="D39" s="6">
-        <v>-4.62</v>
-      </c>
-      <c r="E39" s="8">
-        <v>2.28</v>
+        <v>-4.79</v>
+      </c>
+      <c r="E39" s="7">
+        <v>2.97</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>-16.76</v>
+        <v>-16.52</v>
       </c>
       <c r="D40" s="6">
-        <v>-11.66</v>
-      </c>
-      <c r="E40" s="8">
-        <v>5.1</v>
+        <v>-13.23</v>
+      </c>
+      <c r="E40" s="7">
+        <v>3.29</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>-8.369999999999999</v>
+        <v>3.87</v>
       </c>
       <c r="D41" s="6">
-        <v>-7.76</v>
+        <v>2.95</v>
       </c>
       <c r="E41" s="8">
-        <v>0.61</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="6">
-        <v>-20.36</v>
+        <v>-10.76</v>
       </c>
       <c r="D42" s="6">
-        <v>-16.52</v>
-      </c>
-      <c r="E42" s="8">
-        <v>3.84</v>
+        <v>-9.890000000000001</v>
+      </c>
+      <c r="E42" s="7">
+        <v>0.87</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C43" s="6">
-        <v>4.36</v>
+        <v>-31.12</v>
       </c>
       <c r="D43" s="6">
-        <v>3.87</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-0.49</v>
+        <v>-31.34</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-14.31</v>
+        <v>-1.34</v>
       </c>
       <c r="D44" s="6">
-        <v>-10.76</v>
+        <v>-1.36</v>
       </c>
       <c r="E44" s="8">
-        <v>3.55</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-30.01</v>
+        <v>-17.2</v>
       </c>
       <c r="D45" s="6">
-        <v>-31.12</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-1.11</v>
+        <v>-18.29</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-1.09</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-3.12</v>
+        <v>-8.98</v>
       </c>
       <c r="D46" s="6">
-        <v>-1.34</v>
+        <v>-9.33</v>
       </c>
       <c r="E46" s="8">
-        <v>1.78</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-18.78</v>
+        <v>-13.62</v>
       </c>
       <c r="D47" s="6">
-        <v>-17.2</v>
+        <v>-14.58</v>
       </c>
       <c r="E47" s="8">
-        <v>1.58</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-10.18</v>
+        <v>-30.18</v>
       </c>
       <c r="D48" s="6">
-        <v>-8.98</v>
-      </c>
-      <c r="E48" s="8">
-        <v>1.2</v>
+        <v>-30.01</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0.17</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-16.76</v>
+        <v>-20.16</v>
       </c>
       <c r="D49" s="6">
-        <v>-13.62</v>
+        <v>-21.25</v>
       </c>
       <c r="E49" s="8">
-        <v>3.14</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-28.79</v>
+        <v>-28.05</v>
       </c>
       <c r="D50" s="6">
-        <v>-30.18</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-1.39</v>
+        <v>-29.3</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-1.25</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="6">
-        <v>-20.36</v>
+        <v>-47.92</v>
       </c>
       <c r="D51" s="6">
-        <v>-20.16</v>
+        <v>-48.05</v>
       </c>
       <c r="E51" s="8">
-        <v>0.2</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C52" s="6">
-        <v>-27.27</v>
+        <v>1310.6</v>
       </c>
       <c r="D52" s="6">
-        <v>-28.05</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-0.78</v>
+        <v>1306.4</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-4.2</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>-50.07</v>
+        <v>3169</v>
       </c>
       <c r="D53" s="6">
-        <v>-47.92</v>
+        <v>3168.5</v>
       </c>
       <c r="E53" s="8">
-        <v>2.15</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>1331.7</v>
+        <v>1328.5</v>
       </c>
       <c r="D54" s="6">
-        <v>1310.6</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-21.1</v>
+        <v>1311</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-17.5</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>3112</v>
+        <v>1714</v>
       </c>
       <c r="D55" s="6">
-        <v>3169</v>
+        <v>1707.5</v>
       </c>
       <c r="E55" s="8">
-        <v>57</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>1303.2</v>
+        <v>215</v>
       </c>
       <c r="D56" s="6">
-        <v>1328.5</v>
+        <v>212.63</v>
       </c>
       <c r="E56" s="8">
-        <v>25.3</v>
+        <v>-2.37</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>1691.5</v>
+        <v>411.05</v>
       </c>
       <c r="D57" s="6">
-        <v>1714</v>
-      </c>
-      <c r="E57" s="8">
-        <v>22.5</v>
+        <v>412.05</v>
+      </c>
+      <c r="E57" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>207.2</v>
+        <v>645.35</v>
       </c>
       <c r="D58" s="6">
-        <v>215</v>
+        <v>636.5</v>
       </c>
       <c r="E58" s="8">
-        <v>7.8</v>
+        <v>-8.85</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="6">
-        <v>419.2</v>
+        <v>199.74</v>
       </c>
       <c r="D59" s="6">
-        <v>411.05</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-8.15</v>
+        <v>196.27</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-3.47</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C60" s="6">
-        <v>643.7</v>
+        <v>74.2</v>
       </c>
       <c r="D60" s="6">
-        <v>645.35</v>
+        <v>73.77</v>
       </c>
       <c r="E60" s="8">
-        <v>1.65</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C61" s="6">
-        <v>201.9</v>
+        <v>77</v>
       </c>
       <c r="D61" s="6">
-        <v>199.74</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-2.16</v>
+        <v>66</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-11</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C62" s="6">
-        <v>74.34999999999999</v>
+        <v>66</v>
       </c>
       <c r="D62" s="6">
-        <v>74.2</v>
+        <v>77</v>
       </c>
       <c r="E62" s="7">
-        <v>-0.15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C63" s="6">
-        <v>45</v>
+        <v>43.46</v>
       </c>
       <c r="D63" s="6">
-        <v>55</v>
+        <v>42.43</v>
       </c>
       <c r="E63" s="8">
-        <v>10</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C64" s="6">
-        <v>55</v>
+        <v>66.59</v>
       </c>
       <c r="D64" s="6">
-        <v>45</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-10</v>
+        <v>66.51000000000001</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C65" s="6">
-        <v>49.03</v>
+        <v>43.41</v>
       </c>
       <c r="D65" s="6">
-        <v>43.46</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-5.57</v>
+        <v>40.57</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-2.84</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="6">
-        <v>61.12</v>
+        <v>50.04</v>
       </c>
       <c r="D66" s="6">
-        <v>66.59</v>
+        <v>48.54</v>
       </c>
       <c r="E66" s="8">
-        <v>5.47</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="6">
-        <v>37.53</v>
+        <v>59.01</v>
       </c>
       <c r="D67" s="6">
-        <v>43.41</v>
+        <v>54.68</v>
       </c>
       <c r="E67" s="8">
-        <v>5.88</v>
+        <v>-4.33</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="6">
-        <v>44.51</v>
+        <v>41.92</v>
       </c>
       <c r="D68" s="6">
-        <v>50.04</v>
-      </c>
-      <c r="E68" s="8">
-        <v>5.53</v>
+        <v>42.8</v>
+      </c>
+      <c r="E68" s="7">
+        <v>0.88</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="6">
-        <v>45.9</v>
+        <v>40.68</v>
       </c>
       <c r="D69" s="6">
-        <v>59.01</v>
+        <v>36.7</v>
       </c>
       <c r="E69" s="8">
-        <v>13.11</v>
+        <v>-3.98</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C70" s="6">
-        <v>47.45</v>
+        <v>62.4</v>
       </c>
       <c r="D70" s="6">
-        <v>41.92</v>
-      </c>
-      <c r="E70" s="7">
-        <v>-5.53</v>
+        <v>55.46</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-6.94</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C71" s="6">
-        <v>39.54</v>
+        <v>37.86</v>
       </c>
       <c r="D71" s="6">
-        <v>40.68</v>
+        <v>36.13</v>
       </c>
       <c r="E71" s="8">
-        <v>1.14</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C72" s="6">
-        <v>67.27</v>
+        <v>-59.15</v>
       </c>
       <c r="D72" s="6">
-        <v>62.4</v>
+        <v>-57.59</v>
       </c>
       <c r="E72" s="7">
-        <v>-4.87</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C73" s="6">
-        <v>38.46</v>
+        <v>61.53</v>
       </c>
       <c r="D73" s="6">
-        <v>37.86</v>
-      </c>
-      <c r="E73" s="7">
-        <v>-0.6</v>
+        <v>-52.7</v>
+      </c>
+      <c r="E73" s="8">
+        <v>-114.23</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C74" s="6">
-        <v>5.13</v>
+        <v>-47.18</v>
       </c>
       <c r="D74" s="6">
-        <v>-59.15</v>
-      </c>
-      <c r="E74" s="7">
-        <v>-64.28</v>
+        <v>-48.12</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="6">
-        <v>91.84</v>
+        <v>-4.62</v>
       </c>
       <c r="D75" s="6">
-        <v>61.53</v>
+        <v>63.55</v>
       </c>
       <c r="E75" s="7">
-        <v>-30.31</v>
+        <v>68.17</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="6">
-        <v>62.32</v>
+        <v>386.06</v>
       </c>
       <c r="D76" s="6">
-        <v>-47.18</v>
-      </c>
-      <c r="E76" s="7">
-        <v>-109.5</v>
+        <v>-16.9</v>
+      </c>
+      <c r="E76" s="8">
+        <v>-402.96</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="6">
-        <v>-9.35</v>
+        <v>-63.78</v>
       </c>
       <c r="D77" s="6">
-        <v>-4.62</v>
-      </c>
-      <c r="E77" s="8">
-        <v>4.73</v>
+        <v>-22.2</v>
+      </c>
+      <c r="E77" s="7">
+        <v>41.58</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="6">
-        <v>62.88</v>
+        <v>-25.01</v>
       </c>
       <c r="D78" s="6">
-        <v>386.06</v>
+        <v>-69.02</v>
       </c>
       <c r="E78" s="8">
-        <v>323.18</v>
+        <v>-44.01</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C79" s="6">
-        <v>-12.28</v>
+        <v>-12.2</v>
       </c>
       <c r="D79" s="6">
-        <v>-63.78</v>
-      </c>
-      <c r="E79" s="7">
-        <v>-51.5</v>
+        <v>-71.51000000000001</v>
+      </c>
+      <c r="E79" s="8">
+        <v>-59.31</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C80" s="6">
-        <v>-24.58</v>
+        <v>-45.15</v>
       </c>
       <c r="D80" s="6">
-        <v>-25.01</v>
+        <v>-38.18</v>
       </c>
       <c r="E80" s="7">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="6">
-        <v>22.36</v>
-      </c>
-      <c r="D81" s="6">
-        <v>-12.2</v>
-      </c>
-      <c r="E81" s="7">
-        <v>-34.56</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="6">
-        <v>85.36</v>
-      </c>
-      <c r="D82" s="6">
-        <v>-45.15</v>
-      </c>
-      <c r="E82" s="7">
-        <v>-130.51</v>
+        <v>6.97</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3510,28 +3446,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3545,16 +3481,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>49.5</v>
+        <v>47.1</v>
       </c>
       <c r="E2" s="11">
         <v>60</v>
       </c>
       <c r="F2" s="11">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
       <c r="G2" s="11">
-        <v>-6.1</v>
+        <v>-4.6</v>
       </c>
       <c r="H2" s="11">
         <v>55.4</v>
@@ -3691,31 +3627,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.6445000000000001</v>
+        <v>0.6259</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1936</v>
+        <v>0.1919</v>
       </c>
       <c r="C2" s="14">
-        <v>0.161</v>
+        <v>0.1595</v>
       </c>
       <c r="D2" s="14">
-        <v>0.0484</v>
+        <v>0.0434</v>
       </c>
       <c r="E2" s="14">
-        <v>0.008199999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="F2" s="14">
-        <v>-0.009300000000000001</v>
+        <v>-0.0137</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.06280000000000001</v>
+        <v>-0.0664</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.102</v>
+        <v>-0.1056</v>
       </c>
       <c r="I2" s="14">
-        <v>-0.1332</v>
+        <v>-0.1437</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="86">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,19 +193,52 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-1.4% → -11.0%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
+  </si>
+  <si>
+    <t>-1.4%</t>
+  </si>
+  <si>
+    <t>-11.0%</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>50.0 → 48.5</t>
+    <t>66.5 → 35.3</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>50.0</t>
-  </si>
-  <si>
-    <t>48.5</t>
+    <t>66.5</t>
+  </si>
+  <si>
+    <t>35.3</t>
+  </si>
+  <si>
+    <t>54.7 → 36.7</t>
+  </si>
+  <si>
+    <t>54.7</t>
+  </si>
+  <si>
+    <t>36.7</t>
+  </si>
+  <si>
+    <t>55.5 → 49.1</t>
+  </si>
+  <si>
+    <t>55.5</t>
+  </si>
+  <si>
+    <t>49.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -257,7 +290,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -291,6 +324,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -304,7 +344,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -326,6 +366,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -407,7 +453,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -415,14 +461,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -431,7 +478,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -930,10 +977,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1306.4</v>
+        <v>1276.5</v>
       </c>
       <c r="D2">
-        <v>-0.32</v>
+        <v>-2.29</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -942,46 +989,46 @@
         <v>1247.38</v>
       </c>
       <c r="G2">
-        <v>-31.34</v>
+        <v>-32.91</v>
       </c>
       <c r="H2">
-        <v>4.73</v>
+        <v>2.33</v>
       </c>
       <c r="I2">
-        <v>-0.08</v>
+        <v>-1.88</v>
       </c>
       <c r="J2">
-        <v>-3.69</v>
+        <v>-5.96</v>
       </c>
       <c r="K2">
-        <v>-3.39</v>
+        <v>-6.28</v>
       </c>
       <c r="L2">
-        <v>-27.31</v>
+        <v>-28.61</v>
       </c>
       <c r="M2">
-        <v>-10.56</v>
+        <v>-11.16</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="P2">
-        <v>1311.1</v>
+        <v>1306.22</v>
       </c>
       <c r="Q2">
-        <v>1333.37</v>
+        <v>1327.29</v>
       </c>
       <c r="R2">
-        <v>1348.76</v>
+        <v>1347.42</v>
       </c>
       <c r="S2">
-        <v>1506</v>
+        <v>1503.17</v>
       </c>
       <c r="T2">
-        <v>-13.25</v>
+        <v>-15.08</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -996,43 +1043,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>42.43</v>
+        <v>35.89</v>
       </c>
       <c r="Z2">
-        <v>-14</v>
+        <v>-16.15</v>
       </c>
       <c r="AA2">
-        <v>-13.31</v>
+        <v>-13.88</v>
       </c>
       <c r="AB2">
-        <v>-0.6899999999999999</v>
+        <v>-2.27</v>
       </c>
       <c r="AC2">
-        <v>74.28</v>
+        <v>46.5</v>
       </c>
       <c r="AD2">
-        <v>64.79000000000001</v>
+        <v>62.63</v>
       </c>
       <c r="AE2">
-        <v>23.8</v>
+        <v>24.7</v>
       </c>
       <c r="AF2">
-        <v>-57.59</v>
+        <v>83.33</v>
       </c>
       <c r="AG2">
-        <v>1401.66</v>
+        <v>1392.94</v>
       </c>
       <c r="AH2">
-        <v>1265.07</v>
+        <v>1261.64</v>
       </c>
       <c r="AI2">
-        <v>1373.07</v>
+        <v>1361.09</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>27.14</v>
+        <v>28.66</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,10 +1090,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3168.5</v>
+        <v>2859.1</v>
       </c>
       <c r="D3">
-        <v>-0.02</v>
+        <v>-9.76</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1055,46 +1102,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-1.36</v>
+        <v>-10.99</v>
       </c>
       <c r="H3">
-        <v>80.23</v>
+        <v>62.63</v>
       </c>
       <c r="I3">
-        <v>5.72</v>
+        <v>-4.65</v>
       </c>
       <c r="J3">
-        <v>3.92</v>
+        <v>-5</v>
       </c>
       <c r="K3">
-        <v>8.949999999999999</v>
+        <v>-3.63</v>
       </c>
       <c r="L3">
-        <v>37.65</v>
+        <v>25.9</v>
       </c>
       <c r="M3">
-        <v>15.95</v>
+        <v>12.54</v>
       </c>
       <c r="N3">
         <v>88</v>
       </c>
       <c r="O3">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="P3">
-        <v>3111.62</v>
+        <v>3083.72</v>
       </c>
       <c r="Q3">
-        <v>3037.77</v>
+        <v>3027.32</v>
       </c>
       <c r="R3">
-        <v>3071.17</v>
+        <v>3067.58</v>
       </c>
       <c r="S3">
-        <v>2500.31</v>
+        <v>2502.57</v>
       </c>
       <c r="T3">
-        <v>26.72</v>
+        <v>14.25</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1109,43 +1156,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>66.51000000000001</v>
+        <v>35.28</v>
       </c>
       <c r="Z3">
-        <v>19.66</v>
+        <v>1.08</v>
       </c>
       <c r="AA3">
-        <v>-0.49</v>
+        <v>-0.17</v>
       </c>
       <c r="AB3">
-        <v>20.15</v>
+        <v>1.25</v>
       </c>
       <c r="AC3">
-        <v>99.89</v>
+        <v>66.56</v>
       </c>
       <c r="AD3">
-        <v>95.5</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="AE3">
-        <v>63.72</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="AF3">
-        <v>-52.7</v>
+        <v>1067.96</v>
       </c>
       <c r="AG3">
-        <v>3156.31</v>
+        <v>3169.17</v>
       </c>
       <c r="AH3">
-        <v>2919.22</v>
+        <v>2885.47</v>
       </c>
       <c r="AI3">
-        <v>2962.35</v>
+        <v>3173.87</v>
       </c>
       <c r="AJ3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AK3">
-        <v>34.56</v>
+        <v>35.94</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1203,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1311</v>
+        <v>1214.9</v>
       </c>
       <c r="D4">
-        <v>-1.32</v>
+        <v>-7.33</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1168,46 +1215,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-18.29</v>
+        <v>-24.28</v>
       </c>
       <c r="H4">
-        <v>69.64</v>
+        <v>57.21</v>
       </c>
       <c r="I4">
-        <v>-0.68</v>
+        <v>-7.12</v>
       </c>
       <c r="J4">
-        <v>-3.51</v>
+        <v>-12.15</v>
       </c>
       <c r="K4">
-        <v>-9.390000000000001</v>
+        <v>-16.18</v>
       </c>
       <c r="L4">
-        <v>35.98</v>
+        <v>30.46</v>
       </c>
       <c r="M4">
-        <v>4.34</v>
+        <v>2.6</v>
       </c>
       <c r="N4">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="O4">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="P4">
-        <v>1316.14</v>
+        <v>1297.52</v>
       </c>
       <c r="Q4">
-        <v>1338.42</v>
+        <v>1329.41</v>
       </c>
       <c r="R4">
-        <v>1431.92</v>
+        <v>1426.17</v>
       </c>
       <c r="S4">
-        <v>1171.86</v>
+        <v>1172.58</v>
       </c>
       <c r="T4">
-        <v>11.87</v>
+        <v>3.61</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1222,43 +1269,43 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>40.57</v>
+        <v>29.25</v>
       </c>
       <c r="Z4">
-        <v>-31.54</v>
+        <v>-37.93</v>
       </c>
       <c r="AA4">
-        <v>-35.29</v>
+        <v>-35.82</v>
       </c>
       <c r="AB4">
-        <v>3.75</v>
+        <v>-2.11</v>
       </c>
       <c r="AC4">
-        <v>79.45</v>
+        <v>59.12</v>
       </c>
       <c r="AD4">
-        <v>80.64</v>
+        <v>75.19</v>
       </c>
       <c r="AE4">
-        <v>35.5</v>
+        <v>39.83</v>
       </c>
       <c r="AF4">
-        <v>-48.12</v>
+        <v>63.95</v>
       </c>
       <c r="AG4">
-        <v>1402.21</v>
+        <v>1408.57</v>
       </c>
       <c r="AH4">
-        <v>1274.62</v>
+        <v>1250.25</v>
       </c>
       <c r="AI4">
-        <v>1418.61</v>
+        <v>1382.39</v>
       </c>
       <c r="AJ4" t="s">
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>19.57</v>
+        <v>24.67</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1316,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1707.5</v>
+        <v>1593.1</v>
       </c>
       <c r="D5">
-        <v>-0.38</v>
+        <v>-6.7</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1281,46 +1328,46 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-9.33</v>
+        <v>-15.4</v>
       </c>
       <c r="H5">
-        <v>31.54</v>
+        <v>22.72</v>
       </c>
       <c r="I5">
-        <v>0.44</v>
+        <v>-4.72</v>
       </c>
       <c r="J5">
-        <v>2.61</v>
+        <v>-6.09</v>
       </c>
       <c r="K5">
-        <v>-3.86</v>
+        <v>-11.83</v>
       </c>
       <c r="L5">
-        <v>27.92</v>
+        <v>21.62</v>
       </c>
       <c r="M5">
-        <v>19.19</v>
+        <v>16.95</v>
       </c>
       <c r="N5">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="O5">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="P5">
-        <v>1697.56</v>
+        <v>1681.76</v>
       </c>
       <c r="Q5">
-        <v>1690.82</v>
+        <v>1685.43</v>
       </c>
       <c r="R5">
-        <v>1759.79</v>
+        <v>1754.95</v>
       </c>
       <c r="S5">
-        <v>1597.75</v>
+        <v>1598.22</v>
       </c>
       <c r="T5">
-        <v>6.87</v>
+        <v>-0.32</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1332,37 +1379,37 @@
         <v>47</v>
       </c>
       <c r="X5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>48.54</v>
+        <v>30.9</v>
       </c>
       <c r="Z5">
-        <v>-14.47</v>
+        <v>-21.74</v>
       </c>
       <c r="AA5">
-        <v>-21.6</v>
+        <v>-21.63</v>
       </c>
       <c r="AB5">
-        <v>7.13</v>
+        <v>-0.12</v>
       </c>
       <c r="AC5">
-        <v>92.73999999999999</v>
+        <v>65.58</v>
       </c>
       <c r="AD5">
-        <v>89.8</v>
+        <v>84.52</v>
       </c>
       <c r="AE5">
-        <v>31</v>
+        <v>37.24</v>
       </c>
       <c r="AF5">
-        <v>63.55</v>
+        <v>383.28</v>
       </c>
       <c r="AG5">
-        <v>1721.79</v>
+        <v>1738.58</v>
       </c>
       <c r="AH5">
-        <v>1659.86</v>
+        <v>1632.28</v>
       </c>
       <c r="AI5">
         <v>1761.08</v>
@@ -1371,7 +1418,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>24.3</v>
+        <v>28.77</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,58 +1429,58 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>212.63</v>
+        <v>198</v>
       </c>
       <c r="D6">
-        <v>-1.1</v>
+        <v>-6.88</v>
       </c>
       <c r="E6">
         <v>248.91</v>
       </c>
       <c r="F6">
-        <v>118.42</v>
+        <v>118.99</v>
       </c>
       <c r="G6">
-        <v>-14.58</v>
+        <v>-20.45</v>
       </c>
       <c r="H6">
-        <v>79.56</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I6">
-        <v>3.47</v>
+        <v>-2.8</v>
       </c>
       <c r="J6">
-        <v>1.75</v>
+        <v>-6.3</v>
       </c>
       <c r="K6">
-        <v>-8.470000000000001</v>
+        <v>-16.08</v>
       </c>
       <c r="L6">
-        <v>75.54000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="M6">
-        <v>62.59</v>
+        <v>58.66</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="P6">
-        <v>208.97</v>
+        <v>207.83</v>
       </c>
       <c r="Q6">
-        <v>207.76</v>
+        <v>206.98</v>
       </c>
       <c r="R6">
-        <v>215.02</v>
+        <v>214.35</v>
       </c>
       <c r="S6">
-        <v>181.48</v>
+        <v>181.71</v>
       </c>
       <c r="T6">
-        <v>17.16</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1448,34 +1495,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>54.68</v>
+        <v>36.73</v>
       </c>
       <c r="Z6">
-        <v>-1.3</v>
+        <v>-2.03</v>
       </c>
       <c r="AA6">
-        <v>-2.6</v>
+        <v>-2.49</v>
       </c>
       <c r="AB6">
-        <v>1.3</v>
+        <v>0.45</v>
       </c>
       <c r="AC6">
-        <v>93.95999999999999</v>
+        <v>62.95</v>
       </c>
       <c r="AD6">
-        <v>90.63</v>
+        <v>85.64</v>
       </c>
       <c r="AE6">
-        <v>5.18</v>
+        <v>5.89</v>
       </c>
       <c r="AF6">
-        <v>-16.9</v>
+        <v>216.53</v>
       </c>
       <c r="AG6">
-        <v>214.45</v>
+        <v>214.39</v>
       </c>
       <c r="AH6">
-        <v>201.07</v>
+        <v>199.56</v>
       </c>
       <c r="AI6">
         <v>217.63</v>
@@ -1484,7 +1531,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>32.02</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1495,10 +1542,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>412.05</v>
+        <v>401.15</v>
       </c>
       <c r="D7">
-        <v>0.24</v>
+        <v>-2.65</v>
       </c>
       <c r="E7">
         <v>588.6900000000001</v>
@@ -1507,46 +1554,46 @@
         <v>393.4</v>
       </c>
       <c r="G7">
-        <v>-30.01</v>
+        <v>-31.86</v>
       </c>
       <c r="H7">
-        <v>4.74</v>
+        <v>1.97</v>
       </c>
       <c r="I7">
-        <v>-0.59</v>
+        <v>-1.86</v>
       </c>
       <c r="J7">
-        <v>-5.1</v>
+        <v>-7.18</v>
       </c>
       <c r="K7">
-        <v>-4.79</v>
+        <v>-8.24</v>
       </c>
       <c r="L7">
-        <v>-28.73</v>
+        <v>-29.62</v>
       </c>
       <c r="M7">
-        <v>0.5</v>
+        <v>-0.2</v>
       </c>
       <c r="N7">
         <v>23</v>
       </c>
       <c r="O7">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P7">
-        <v>412.83</v>
+        <v>411.31</v>
       </c>
       <c r="Q7">
-        <v>421.65</v>
+        <v>419.51</v>
       </c>
       <c r="R7">
-        <v>426.74</v>
+        <v>426.28</v>
       </c>
       <c r="S7">
-        <v>472.36</v>
+        <v>471.57</v>
       </c>
       <c r="T7">
-        <v>-12.77</v>
+        <v>-14.93</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1561,43 +1608,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>42.8</v>
+        <v>36.33</v>
       </c>
       <c r="Z7">
-        <v>-5.12</v>
+        <v>-5.88</v>
       </c>
       <c r="AA7">
-        <v>-4.63</v>
+        <v>-4.88</v>
       </c>
       <c r="AB7">
-        <v>-0.49</v>
+        <v>-1</v>
       </c>
       <c r="AC7">
-        <v>65.73999999999999</v>
+        <v>42.59</v>
       </c>
       <c r="AD7">
-        <v>56.97</v>
+        <v>55.77</v>
       </c>
       <c r="AE7">
-        <v>8.98</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="AF7">
-        <v>-22.2</v>
+        <v>-19.54</v>
       </c>
       <c r="AG7">
-        <v>445.41</v>
+        <v>442.49</v>
       </c>
       <c r="AH7">
-        <v>397.9</v>
+        <v>396.53</v>
       </c>
       <c r="AI7">
-        <v>436.39</v>
+        <v>433.63</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>23.81</v>
+        <v>24.08</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1608,10 +1655,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>636.5</v>
+        <v>621.2</v>
       </c>
       <c r="D8">
-        <v>-1.37</v>
+        <v>-2.4</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1620,46 +1667,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-21.25</v>
+        <v>-23.14</v>
       </c>
       <c r="H8">
-        <v>36.08</v>
+        <v>32.81</v>
       </c>
       <c r="I8">
-        <v>-1.49</v>
+        <v>-2.88</v>
       </c>
       <c r="J8">
-        <v>-2.1</v>
+        <v>-4.64</v>
       </c>
       <c r="K8">
-        <v>-13.23</v>
+        <v>-15.81</v>
       </c>
       <c r="L8">
-        <v>0.87</v>
+        <v>-2.25</v>
       </c>
       <c r="M8">
-        <v>-14.37</v>
+        <v>-15.6</v>
       </c>
       <c r="N8">
         <v>55</v>
       </c>
       <c r="O8">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="P8">
-        <v>641.08</v>
+        <v>637.4</v>
       </c>
       <c r="Q8">
-        <v>653.8</v>
+        <v>651.48</v>
       </c>
       <c r="R8">
-        <v>682.98</v>
+        <v>680.86</v>
       </c>
       <c r="S8">
-        <v>613.99</v>
+        <v>614</v>
       </c>
       <c r="T8">
-        <v>3.67</v>
+        <v>1.17</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1674,43 +1721,43 @@
         <v>2</v>
       </c>
       <c r="Y8">
-        <v>36.7</v>
+        <v>31.06</v>
       </c>
       <c r="Z8">
-        <v>-10.52</v>
+        <v>-11.85</v>
       </c>
       <c r="AA8">
-        <v>-10.65</v>
+        <v>-10.89</v>
       </c>
       <c r="AB8">
-        <v>0.13</v>
+        <v>-0.96</v>
       </c>
       <c r="AC8">
-        <v>24.44</v>
+        <v>14.57</v>
       </c>
       <c r="AD8">
-        <v>21.55</v>
+        <v>21.67</v>
       </c>
       <c r="AE8">
-        <v>15.58</v>
+        <v>16.13</v>
       </c>
       <c r="AF8">
-        <v>-69.02</v>
+        <v>-18.52</v>
       </c>
       <c r="AG8">
-        <v>673.4299999999999</v>
+        <v>674.85</v>
       </c>
       <c r="AH8">
-        <v>634.17</v>
+        <v>628.11</v>
       </c>
       <c r="AI8">
-        <v>686.8099999999999</v>
+        <v>675.1</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>16.89</v>
+        <v>19.06</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1721,10 +1768,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>196.27</v>
+        <v>192.55</v>
       </c>
       <c r="D9">
-        <v>-1.74</v>
+        <v>-1.9</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1733,46 +1780,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-29.3</v>
+        <v>-30.64</v>
       </c>
       <c r="H9">
-        <v>13.91</v>
+        <v>11.75</v>
       </c>
       <c r="I9">
-        <v>4.33</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="J9">
-        <v>4.63</v>
+        <v>1.64</v>
       </c>
       <c r="K9">
-        <v>2.95</v>
+        <v>1</v>
       </c>
       <c r="L9">
-        <v>-24.41</v>
+        <v>-23.58</v>
       </c>
       <c r="M9">
-        <v>-6.64</v>
+        <v>-7.02</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P9">
-        <v>198.49</v>
+        <v>198.22</v>
       </c>
       <c r="Q9">
-        <v>193.85</v>
+        <v>193.96</v>
       </c>
       <c r="R9">
-        <v>189.83</v>
+        <v>190</v>
       </c>
       <c r="S9">
-        <v>205.41</v>
+        <v>205.01</v>
       </c>
       <c r="T9">
-        <v>-4.45</v>
+        <v>-6.08</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1787,34 +1834,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>55.46</v>
+        <v>49.14</v>
       </c>
       <c r="Z9">
-        <v>1.96</v>
+        <v>1.6</v>
       </c>
       <c r="AA9">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AB9">
-        <v>0.67</v>
+        <v>0.25</v>
       </c>
       <c r="AC9">
-        <v>76.48</v>
+        <v>50.93</v>
       </c>
       <c r="AD9">
-        <v>85.70999999999999</v>
+        <v>73.51000000000001</v>
       </c>
       <c r="AE9">
         <v>5.3</v>
       </c>
       <c r="AF9">
-        <v>-71.51000000000001</v>
+        <v>-13.64</v>
       </c>
       <c r="AG9">
-        <v>202.01</v>
+        <v>201.98</v>
       </c>
       <c r="AH9">
-        <v>185.68</v>
+        <v>185.94</v>
       </c>
       <c r="AI9">
         <v>185.88</v>
@@ -1823,7 +1870,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>35.66</v>
+        <v>31.17</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1834,34 +1881,34 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>73.77</v>
+        <v>72.2</v>
       </c>
       <c r="D10">
-        <v>-0.58</v>
+        <v>-2.13</v>
       </c>
       <c r="E10">
-        <v>141.99</v>
+        <v>141.26</v>
       </c>
       <c r="F10">
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-48.05</v>
+        <v>-48.89</v>
       </c>
       <c r="H10">
-        <v>24.44</v>
+        <v>21.79</v>
       </c>
       <c r="I10">
-        <v>-2.28</v>
+        <v>-3.91</v>
       </c>
       <c r="J10">
-        <v>-3.25</v>
+        <v>-6.36</v>
       </c>
       <c r="K10">
-        <v>-9.890000000000001</v>
+        <v>-12.21</v>
       </c>
       <c r="L10">
-        <v>-48.22</v>
+        <v>-49.15</v>
       </c>
       <c r="M10">
         <v>-1.37</v>
@@ -1873,19 +1920,19 @@
         <v>6</v>
       </c>
       <c r="P10">
-        <v>74.45</v>
+        <v>73.86</v>
       </c>
       <c r="Q10">
-        <v>75.81999999999999</v>
+        <v>75.56</v>
       </c>
       <c r="R10">
-        <v>78.20999999999999</v>
+        <v>78.03</v>
       </c>
       <c r="S10">
-        <v>81.31999999999999</v>
+        <v>81.23</v>
       </c>
       <c r="T10">
-        <v>-9.279999999999999</v>
+        <v>-11.12</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1900,43 +1947,43 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>36.13</v>
+        <v>30.61</v>
       </c>
       <c r="Z10">
-        <v>-1.09</v>
+        <v>-1.24</v>
       </c>
       <c r="AA10">
-        <v>-1.02</v>
+        <v>-1.06</v>
       </c>
       <c r="AB10">
-        <v>-0.07000000000000001</v>
+        <v>-0.17</v>
       </c>
       <c r="AC10">
-        <v>49.77</v>
+        <v>30.75</v>
       </c>
       <c r="AD10">
-        <v>58.64</v>
+        <v>46.48</v>
       </c>
       <c r="AE10">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AF10">
-        <v>-38.18</v>
+        <v>10.97</v>
       </c>
       <c r="AG10">
-        <v>78.26000000000001</v>
+        <v>78.37</v>
       </c>
       <c r="AH10">
-        <v>73.38</v>
+        <v>72.75</v>
       </c>
       <c r="AI10">
-        <v>79.76000000000001</v>
+        <v>78.88</v>
       </c>
       <c r="AJ10" t="s">
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>43.43</v>
+        <v>47.76</v>
       </c>
     </row>
   </sheetData>
@@ -2077,7 +2124,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2117,7 +2164,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2135,1294 +2182,1354 @@
         <v>61</v>
       </c>
     </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="C5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="B9" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7">
+        <v>-3.69</v>
+      </c>
+      <c r="D10" s="7">
+        <v>-5.96</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-2.27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>3.92</v>
+      </c>
+      <c r="D11" s="7">
+        <v>-5</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-8.92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>-3.51</v>
+      </c>
+      <c r="D12" s="7">
+        <v>-12.15</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-8.640000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>2.61</v>
+      </c>
+      <c r="D13" s="7">
+        <v>-6.09</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-8.699999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>1.75</v>
+      </c>
+      <c r="D14" s="7">
+        <v>-6.3</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-8.050000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7">
+        <v>-5.1</v>
+      </c>
+      <c r="D15" s="7">
+        <v>-7.18</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-2.08</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-2.1</v>
+      </c>
+      <c r="D16" s="7">
+        <v>-4.64</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-2.54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="7">
+        <v>4.63</v>
+      </c>
+      <c r="D17" s="7">
+        <v>1.64</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-2.99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-3.25</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-6.36</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-3.11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-0.08</v>
+      </c>
+      <c r="D19" s="7">
+        <v>-1.88</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>5.72</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-4.65</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-10.37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-0.68</v>
+      </c>
+      <c r="D21" s="7">
+        <v>-7.12</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-6.44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>0.44</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-4.72</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-5.16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>3.47</v>
+      </c>
+      <c r="D23" s="7">
+        <v>-2.8</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-6.27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7">
+        <v>-0.59</v>
+      </c>
+      <c r="D24" s="7">
+        <v>-1.86</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-1.27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="7">
+        <v>-1.49</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-2.88</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-1.39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="7">
+        <v>4.33</v>
+      </c>
+      <c r="D26" s="7">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-5.02</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="7">
+        <v>-2.28</v>
+      </c>
+      <c r="D27" s="7">
+        <v>-3.91</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-1.63</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>-27.31</v>
+      </c>
+      <c r="D28" s="7">
+        <v>-28.61</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>37.65</v>
+      </c>
+      <c r="D29" s="7">
+        <v>25.9</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-11.75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>35.98</v>
+      </c>
+      <c r="D30" s="7">
+        <v>30.46</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-5.52</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7">
+        <v>27.92</v>
+      </c>
+      <c r="D31" s="7">
+        <v>21.62</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-6.3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7">
+        <v>75.54000000000001</v>
+      </c>
+      <c r="D32" s="7">
+        <v>67.2</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-8.34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-28.73</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-29.62</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0.87</v>
+      </c>
+      <c r="D34" s="7">
+        <v>-2.25</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-3.12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="7">
+        <v>-24.41</v>
+      </c>
+      <c r="D35" s="7">
+        <v>-23.58</v>
+      </c>
+      <c r="E35" s="9">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="7">
+        <v>-48.22</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-49.15</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-3.39</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-6.28</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-2.89</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-3.63</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-12.58</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-9.390000000000001</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-16.18</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-6.79</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7">
+        <v>-3.86</v>
+      </c>
+      <c r="D40" s="7">
+        <v>-11.83</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-7.97</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="7">
+        <v>-8.470000000000001</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-16.08</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-7.61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-4.79</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-8.24</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-3.45</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="7">
+        <v>-13.23</v>
+      </c>
+      <c r="D43" s="7">
+        <v>-15.81</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-2.58</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="7">
+        <v>2.95</v>
+      </c>
+      <c r="D44" s="7">
+        <v>1</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-1.95</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="7">
+        <v>-9.890000000000001</v>
+      </c>
+      <c r="D45" s="7">
+        <v>-12.21</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-2.32</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="7">
+        <v>-31.34</v>
+      </c>
+      <c r="D46" s="7">
+        <v>-32.91</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-1.57</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="7">
+        <v>-1.36</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-10.99</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-9.630000000000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7">
+        <v>-18.29</v>
+      </c>
+      <c r="D48" s="7">
+        <v>-24.28</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-5.99</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="7">
+        <v>-9.33</v>
+      </c>
+      <c r="D49" s="7">
+        <v>-15.4</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-6.07</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="7">
+        <v>-14.58</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-20.45</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-5.87</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="7">
+        <v>-30.01</v>
+      </c>
+      <c r="D51" s="7">
+        <v>-31.86</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-1.85</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="7">
+        <v>-21.25</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-23.14</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-1.89</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="7">
+        <v>-29.3</v>
+      </c>
+      <c r="D53" s="7">
+        <v>-30.64</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-1.34</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="7">
+        <v>-48.05</v>
+      </c>
+      <c r="D54" s="7">
+        <v>-48.89</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="7">
+        <v>1306.4</v>
+      </c>
+      <c r="D55" s="7">
+        <v>1276.5</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-29.9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="7">
+        <v>3168.5</v>
+      </c>
+      <c r="D56" s="7">
+        <v>2859.1</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-309.4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="7">
+        <v>1311</v>
+      </c>
+      <c r="D57" s="7">
+        <v>1214.9</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-96.09999999999999</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="7">
+        <v>1707.5</v>
+      </c>
+      <c r="D58" s="7">
+        <v>1593.1</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-114.4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="7">
+        <v>212.63</v>
+      </c>
+      <c r="D59" s="7">
+        <v>198</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-14.63</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="7">
+        <v>412.05</v>
+      </c>
+      <c r="D60" s="7">
+        <v>401.15</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-10.9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="7">
+        <v>636.5</v>
+      </c>
+      <c r="D61" s="7">
+        <v>621.2</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-15.3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="7">
+        <v>196.27</v>
+      </c>
+      <c r="D62" s="7">
+        <v>192.55</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-3.72</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C63" s="7">
+        <v>73.77</v>
+      </c>
+      <c r="D63" s="7">
+        <v>72.2</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-1.57</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="7">
         <v>66</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="D64" s="7">
+        <v>77</v>
+      </c>
+      <c r="E64" s="9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" s="7">
+        <v>77</v>
+      </c>
+      <c r="D65" s="7">
+        <v>66</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-4.39</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-3.69</v>
-      </c>
-      <c r="E7" s="7">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="B66" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="7">
+        <v>42.43</v>
+      </c>
+      <c r="D66" s="7">
+        <v>35.89</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-6.54</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>4.78</v>
-      </c>
-      <c r="D8" s="6">
-        <v>3.92</v>
-      </c>
-      <c r="E8" s="8">
-        <v>-0.86</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B67" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="7">
+        <v>66.51000000000001</v>
+      </c>
+      <c r="D67" s="7">
+        <v>35.28</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-31.23</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-3.25</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-3.51</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-0.26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B68" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="7">
+        <v>40.57</v>
+      </c>
+      <c r="D68" s="7">
+        <v>29.25</v>
+      </c>
+      <c r="E68" s="8">
+        <v>-11.32</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-0.33</v>
-      </c>
-      <c r="D10" s="6">
-        <v>2.61</v>
-      </c>
-      <c r="E10" s="7">
-        <v>2.94</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B69" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="7">
+        <v>48.54</v>
+      </c>
+      <c r="D69" s="7">
+        <v>30.9</v>
+      </c>
+      <c r="E69" s="8">
+        <v>-17.64</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>2.62</v>
-      </c>
-      <c r="D11" s="6">
-        <v>1.75</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-0.87</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B70" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="7">
+        <v>54.68</v>
+      </c>
+      <c r="D70" s="7">
+        <v>36.73</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-17.95</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-5.57</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-5.1</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B71" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="7">
+        <v>42.8</v>
+      </c>
+      <c r="D71" s="7">
+        <v>36.33</v>
+      </c>
+      <c r="E71" s="8">
+        <v>-6.47</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-1.61</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-2.1</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-0.49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B72" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="7">
+        <v>36.7</v>
+      </c>
+      <c r="D72" s="7">
+        <v>31.06</v>
+      </c>
+      <c r="E72" s="8">
+        <v>-5.64</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>5.18</v>
-      </c>
-      <c r="D14" s="6">
-        <v>4.63</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-0.55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B73" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="7">
+        <v>55.46</v>
+      </c>
+      <c r="D73" s="7">
+        <v>49.14</v>
+      </c>
+      <c r="E73" s="8">
+        <v>-6.32</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-2.62</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-3.25</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B74" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C74" s="7">
+        <v>36.13</v>
+      </c>
+      <c r="D74" s="7">
+        <v>30.61</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-5.52</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0.73</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-0.08</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B75" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="7">
+        <v>-57.59</v>
+      </c>
+      <c r="D75" s="7">
+        <v>83.33</v>
+      </c>
+      <c r="E75" s="9">
+        <v>140.92</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>5.81</v>
-      </c>
-      <c r="D17" s="6">
-        <v>5.72</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-0.09</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B76" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="7">
+        <v>-52.7</v>
+      </c>
+      <c r="D76" s="7">
+        <v>1067.96</v>
+      </c>
+      <c r="E76" s="9">
+        <v>1120.66</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>2.05</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-0.68</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-2.73</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B77" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="7">
+        <v>-48.12</v>
+      </c>
+      <c r="D77" s="7">
+        <v>63.95</v>
+      </c>
+      <c r="E77" s="9">
+        <v>112.07</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>1.06</v>
-      </c>
-      <c r="D19" s="6">
-        <v>0.44</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-0.62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B78" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="7">
+        <v>63.55</v>
+      </c>
+      <c r="D78" s="7">
+        <v>383.28</v>
+      </c>
+      <c r="E78" s="9">
+        <v>319.73</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>5.39</v>
-      </c>
-      <c r="D20" s="6">
-        <v>3.47</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-1.92</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B79" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="7">
+        <v>-16.9</v>
+      </c>
+      <c r="D79" s="7">
+        <v>216.53</v>
+      </c>
+      <c r="E79" s="9">
+        <v>233.43</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>0.01</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-0.59</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B80" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="7">
+        <v>-22.2</v>
+      </c>
+      <c r="D80" s="7">
+        <v>-19.54</v>
+      </c>
+      <c r="E80" s="9">
+        <v>2.66</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-1.87</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-1.49</v>
-      </c>
-      <c r="E22" s="7">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B81" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="7">
+        <v>-69.02</v>
+      </c>
+      <c r="D81" s="7">
+        <v>-18.52</v>
+      </c>
+      <c r="E81" s="9">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>5.88</v>
-      </c>
-      <c r="D23" s="6">
-        <v>4.33</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-1.55</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B82" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="7">
+        <v>-71.51000000000001</v>
+      </c>
+      <c r="D82" s="7">
+        <v>-13.64</v>
+      </c>
+      <c r="E82" s="9">
+        <v>57.87</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-1.72</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-2.28</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-27.62</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-27.31</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>36.37</v>
-      </c>
-      <c r="D26" s="6">
-        <v>37.65</v>
-      </c>
-      <c r="E26" s="7">
-        <v>1.28</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>38.79</v>
-      </c>
-      <c r="D27" s="6">
-        <v>35.98</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-2.81</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>28.33</v>
-      </c>
-      <c r="D28" s="6">
-        <v>27.92</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-0.41</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>80.89</v>
-      </c>
-      <c r="D29" s="6">
-        <v>75.54000000000001</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-5.35</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-28.43</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-28.73</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>4.51</v>
-      </c>
-      <c r="D31" s="6">
-        <v>0.87</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-3.64</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-22.7</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-24.41</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-1.71</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-50.17</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-48.22</v>
-      </c>
-      <c r="E33" s="7">
-        <v>1.95</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-5.8</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-3.39</v>
-      </c>
-      <c r="E34" s="7">
-        <v>2.41</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>7.93</v>
-      </c>
-      <c r="D35" s="6">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="E35" s="7">
-        <v>1.02</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-9.960000000000001</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-9.390000000000001</v>
-      </c>
-      <c r="E36" s="7">
-        <v>0.57</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-4.62</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-3.86</v>
-      </c>
-      <c r="E37" s="7">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-11.66</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-8.470000000000001</v>
-      </c>
-      <c r="E38" s="7">
-        <v>3.19</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-7.76</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-4.79</v>
-      </c>
-      <c r="E39" s="7">
-        <v>2.97</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-16.52</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-13.23</v>
-      </c>
-      <c r="E40" s="7">
-        <v>3.29</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>3.87</v>
-      </c>
-      <c r="D41" s="6">
-        <v>2.95</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-0.92</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-10.76</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-9.890000000000001</v>
-      </c>
-      <c r="E42" s="7">
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-31.12</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-31.34</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-0.22</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-1.34</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-1.36</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-0.02</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-17.2</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-18.29</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-1.09</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-8.98</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-9.33</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-0.35</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-13.62</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-14.58</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-0.96</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-30.18</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-30.01</v>
-      </c>
-      <c r="E48" s="7">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-20.16</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-21.25</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-1.09</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-28.05</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-29.3</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-47.92</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-48.05</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-0.13</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="6">
-        <v>1310.6</v>
-      </c>
-      <c r="D52" s="6">
-        <v>1306.4</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-4.2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>3169</v>
-      </c>
-      <c r="D53" s="6">
-        <v>3168.5</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>1328.5</v>
-      </c>
-      <c r="D54" s="6">
-        <v>1311</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-17.5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>1714</v>
-      </c>
-      <c r="D55" s="6">
-        <v>1707.5</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-6.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>215</v>
-      </c>
-      <c r="D56" s="6">
-        <v>212.63</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-2.37</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>411.05</v>
-      </c>
-      <c r="D57" s="6">
-        <v>412.05</v>
-      </c>
-      <c r="E57" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>645.35</v>
-      </c>
-      <c r="D58" s="6">
-        <v>636.5</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-8.85</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>199.74</v>
-      </c>
-      <c r="D59" s="6">
-        <v>196.27</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-3.47</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="6">
-        <v>74.2</v>
-      </c>
-      <c r="D60" s="6">
-        <v>73.77</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" s="6">
-        <v>77</v>
-      </c>
-      <c r="D61" s="6">
-        <v>66</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="6">
-        <v>66</v>
-      </c>
-      <c r="D62" s="6">
-        <v>77</v>
-      </c>
-      <c r="E62" s="7">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="6">
-        <v>43.46</v>
-      </c>
-      <c r="D63" s="6">
-        <v>42.43</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-1.03</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="6">
-        <v>66.59</v>
-      </c>
-      <c r="D64" s="6">
-        <v>66.51000000000001</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-0.08</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>43.41</v>
-      </c>
-      <c r="D65" s="6">
-        <v>40.57</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-2.84</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>50.04</v>
-      </c>
-      <c r="D66" s="6">
-        <v>48.54</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>59.01</v>
-      </c>
-      <c r="D67" s="6">
-        <v>54.68</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-4.33</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>41.92</v>
-      </c>
-      <c r="D68" s="6">
-        <v>42.8</v>
-      </c>
-      <c r="E68" s="7">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="6">
-        <v>40.68</v>
-      </c>
-      <c r="D69" s="6">
-        <v>36.7</v>
-      </c>
-      <c r="E69" s="8">
-        <v>-3.98</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="6">
-        <v>62.4</v>
-      </c>
-      <c r="D70" s="6">
-        <v>55.46</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-6.94</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="6">
-        <v>37.86</v>
-      </c>
-      <c r="D71" s="6">
-        <v>36.13</v>
-      </c>
-      <c r="E71" s="8">
-        <v>-1.73</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B72" s="5" t="s">
+      <c r="B83" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C72" s="6">
-        <v>-59.15</v>
-      </c>
-      <c r="D72" s="6">
-        <v>-57.59</v>
-      </c>
-      <c r="E72" s="7">
-        <v>1.56</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="6">
-        <v>61.53</v>
-      </c>
-      <c r="D73" s="6">
-        <v>-52.7</v>
-      </c>
-      <c r="E73" s="8">
-        <v>-114.23</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="6">
-        <v>-47.18</v>
-      </c>
-      <c r="D74" s="6">
-        <v>-48.12</v>
-      </c>
-      <c r="E74" s="8">
-        <v>-0.9399999999999999</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="6">
-        <v>-4.62</v>
-      </c>
-      <c r="D75" s="6">
-        <v>63.55</v>
-      </c>
-      <c r="E75" s="7">
-        <v>68.17</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>386.06</v>
-      </c>
-      <c r="D76" s="6">
-        <v>-16.9</v>
-      </c>
-      <c r="E76" s="8">
-        <v>-402.96</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>-63.78</v>
-      </c>
-      <c r="D77" s="6">
-        <v>-22.2</v>
-      </c>
-      <c r="E77" s="7">
-        <v>41.58</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>-25.01</v>
-      </c>
-      <c r="D78" s="6">
-        <v>-69.02</v>
-      </c>
-      <c r="E78" s="8">
-        <v>-44.01</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>-12.2</v>
-      </c>
-      <c r="D79" s="6">
-        <v>-71.51000000000001</v>
-      </c>
-      <c r="E79" s="8">
-        <v>-59.31</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>-45.15</v>
-      </c>
-      <c r="D80" s="6">
+      <c r="C83" s="7">
         <v>-38.18</v>
       </c>
-      <c r="E80" s="7">
-        <v>6.97</v>
+      <c r="D83" s="7">
+        <v>10.97</v>
+      </c>
+      <c r="E83" s="9">
+        <v>49.15</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3442,60 +3549,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>74</v>
+      <c r="B1" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11">
-        <v>56.16</v>
-      </c>
-      <c r="C2" s="12">
+      <c r="B2" s="12">
+        <v>48.16</v>
+      </c>
+      <c r="C2" s="13">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
-        <v>47.1</v>
-      </c>
-      <c r="E2" s="11">
-        <v>60</v>
-      </c>
-      <c r="F2" s="11">
-        <v>-0.5</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-4.6</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="D2" s="12">
+        <v>35</v>
+      </c>
+      <c r="E2" s="12">
+        <v>40</v>
+      </c>
+      <c r="F2" s="12">
+        <v>-5.8</v>
+      </c>
+      <c r="G2" s="12">
+        <v>-9.9</v>
+      </c>
+      <c r="H2" s="12">
         <v>55.4</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="12">
         <v>0</v>
       </c>
     </row>
@@ -3597,61 +3704,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="14" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>0.6259</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.1919</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1595</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.0434</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.005</v>
-      </c>
-      <c r="F2" s="14">
+      <c r="A2" s="15">
+        <v>0.5866</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.1695</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.1254</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.026</v>
+      </c>
+      <c r="E2" s="15">
+        <v>-0.002</v>
+      </c>
+      <c r="F2" s="15">
         <v>-0.0137</v>
       </c>
-      <c r="G2" s="14">
-        <v>-0.0664</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.1056</v>
-      </c>
-      <c r="I2" s="14">
-        <v>-0.1437</v>
+      <c r="G2" s="15">
+        <v>-0.0702</v>
+      </c>
+      <c r="H2" s="15">
+        <v>-0.1116</v>
+      </c>
+      <c r="I2" s="15">
+        <v>-0.156</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="79">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,52 +193,31 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>-1.4% → -11.0%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>-1.4%</t>
-  </si>
-  <si>
-    <t>-11.0%</t>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>29.2 → 38.8</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>29.2</t>
+  </si>
+  <si>
+    <t>38.8</t>
   </si>
   <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>66.5 → 35.3</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>66.5</t>
-  </si>
-  <si>
-    <t>35.3</t>
-  </si>
-  <si>
-    <t>54.7 → 36.7</t>
-  </si>
-  <si>
-    <t>54.7</t>
-  </si>
-  <si>
-    <t>36.7</t>
-  </si>
-  <si>
-    <t>55.5 → 49.1</t>
-  </si>
-  <si>
-    <t>55.5</t>
+    <t>49.1 → 52.0</t>
   </si>
   <si>
     <t>49.1</t>
+  </si>
+  <si>
+    <t>52.0</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -290,7 +269,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -324,7 +303,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -336,15 +315,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -371,19 +343,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -453,7 +419,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -461,15 +427,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -478,7 +443,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -977,10 +942,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1276.5</v>
+        <v>1272.3</v>
       </c>
       <c r="D2">
-        <v>-2.29</v>
+        <v>-0.33</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -989,46 +954,46 @@
         <v>1247.38</v>
       </c>
       <c r="G2">
-        <v>-32.91</v>
+        <v>-33.13</v>
       </c>
       <c r="H2">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>-1.88</v>
+        <v>-2.57</v>
       </c>
       <c r="J2">
-        <v>-5.96</v>
+        <v>-8.99</v>
       </c>
       <c r="K2">
-        <v>-6.28</v>
+        <v>-5.27</v>
       </c>
       <c r="L2">
-        <v>-28.61</v>
+        <v>-28.95</v>
       </c>
       <c r="M2">
-        <v>-11.16</v>
+        <v>-11.3</v>
       </c>
       <c r="N2">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="O2">
         <v>19</v>
       </c>
       <c r="P2">
-        <v>1306.22</v>
+        <v>1299.5</v>
       </c>
       <c r="Q2">
-        <v>1327.29</v>
+        <v>1321.67</v>
       </c>
       <c r="R2">
-        <v>1347.42</v>
+        <v>1345.87</v>
       </c>
       <c r="S2">
-        <v>1503.17</v>
+        <v>1500.37</v>
       </c>
       <c r="T2">
-        <v>-15.08</v>
+        <v>-15.2</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1043,43 +1008,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>35.89</v>
+        <v>35.07</v>
       </c>
       <c r="Z2">
-        <v>-16.15</v>
+        <v>-17.99</v>
       </c>
       <c r="AA2">
-        <v>-13.88</v>
+        <v>-14.7</v>
       </c>
       <c r="AB2">
-        <v>-2.27</v>
+        <v>-3.29</v>
       </c>
       <c r="AC2">
-        <v>46.5</v>
+        <v>28.77</v>
       </c>
       <c r="AD2">
-        <v>62.63</v>
+        <v>49.85</v>
       </c>
       <c r="AE2">
-        <v>24.7</v>
+        <v>24.18</v>
       </c>
       <c r="AF2">
-        <v>83.33</v>
+        <v>-36.99</v>
       </c>
       <c r="AG2">
-        <v>1392.94</v>
+        <v>1385.85</v>
       </c>
       <c r="AH2">
-        <v>1261.64</v>
+        <v>1257.49</v>
       </c>
       <c r="AI2">
-        <v>1361.09</v>
+        <v>1352.19</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>28.66</v>
+        <v>29.97</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1090,10 +1055,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2859.1</v>
+        <v>2863.9</v>
       </c>
       <c r="D3">
-        <v>-9.76</v>
+        <v>0.17</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1102,46 +1067,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-10.99</v>
+        <v>-10.84</v>
       </c>
       <c r="H3">
-        <v>62.63</v>
+        <v>62.91</v>
       </c>
       <c r="I3">
-        <v>-4.65</v>
+        <v>-7.91</v>
       </c>
       <c r="J3">
-        <v>-5</v>
+        <v>-6.65</v>
       </c>
       <c r="K3">
-        <v>-3.63</v>
+        <v>-2.07</v>
       </c>
       <c r="L3">
-        <v>25.9</v>
+        <v>25.93</v>
       </c>
       <c r="M3">
-        <v>12.54</v>
+        <v>12.9</v>
       </c>
       <c r="N3">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="O3">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P3">
-        <v>3083.72</v>
+        <v>3034.5</v>
       </c>
       <c r="Q3">
-        <v>3027.32</v>
+        <v>3018.02</v>
       </c>
       <c r="R3">
-        <v>3067.58</v>
+        <v>3063.67</v>
       </c>
       <c r="S3">
-        <v>2502.57</v>
+        <v>2504.83</v>
       </c>
       <c r="T3">
-        <v>14.25</v>
+        <v>14.33</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1156,43 +1121,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>35.28</v>
+        <v>35.78</v>
       </c>
       <c r="Z3">
-        <v>1.08</v>
+        <v>-13.1</v>
       </c>
       <c r="AA3">
-        <v>-0.17</v>
+        <v>-2.76</v>
       </c>
       <c r="AB3">
-        <v>1.25</v>
+        <v>-10.34</v>
       </c>
       <c r="AC3">
-        <v>66.56</v>
+        <v>33.76</v>
       </c>
       <c r="AD3">
-        <v>88.81999999999999</v>
+        <v>66.73</v>
       </c>
       <c r="AE3">
-        <v>81.26000000000001</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="AF3">
-        <v>1067.96</v>
+        <v>134.1</v>
       </c>
       <c r="AG3">
-        <v>3169.17</v>
+        <v>3176.98</v>
       </c>
       <c r="AH3">
-        <v>2885.47</v>
+        <v>2859.05</v>
       </c>
       <c r="AI3">
-        <v>3173.87</v>
+        <v>3141.31</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>35.94</v>
+        <v>37.38</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1203,10 +1168,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1214.9</v>
+        <v>1265</v>
       </c>
       <c r="D4">
-        <v>-7.33</v>
+        <v>4.12</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1215,46 +1180,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-24.28</v>
+        <v>-21.16</v>
       </c>
       <c r="H4">
-        <v>57.21</v>
+        <v>63.69</v>
       </c>
       <c r="I4">
-        <v>-7.12</v>
+        <v>-4.89</v>
       </c>
       <c r="J4">
-        <v>-12.15</v>
+        <v>-9.32</v>
       </c>
       <c r="K4">
-        <v>-16.18</v>
+        <v>-11.38</v>
       </c>
       <c r="L4">
-        <v>30.46</v>
+        <v>37.33</v>
       </c>
       <c r="M4">
-        <v>2.6</v>
+        <v>3.22</v>
       </c>
       <c r="N4">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="O4">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="P4">
-        <v>1297.52</v>
+        <v>1284.52</v>
       </c>
       <c r="Q4">
-        <v>1329.41</v>
+        <v>1323.46</v>
       </c>
       <c r="R4">
-        <v>1426.17</v>
+        <v>1420.47</v>
       </c>
       <c r="S4">
-        <v>1172.58</v>
+        <v>1173.52</v>
       </c>
       <c r="T4">
-        <v>3.61</v>
+        <v>7.8</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1269,43 +1234,43 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>29.25</v>
+        <v>38.83</v>
       </c>
       <c r="Z4">
-        <v>-37.93</v>
+        <v>-38.51</v>
       </c>
       <c r="AA4">
-        <v>-35.82</v>
+        <v>-36.36</v>
       </c>
       <c r="AB4">
-        <v>-2.11</v>
+        <v>-2.15</v>
       </c>
       <c r="AC4">
-        <v>59.12</v>
+        <v>48.34</v>
       </c>
       <c r="AD4">
-        <v>75.19</v>
+        <v>62.3</v>
       </c>
       <c r="AE4">
-        <v>39.83</v>
+        <v>41.01</v>
       </c>
       <c r="AF4">
-        <v>63.95</v>
+        <v>184.74</v>
       </c>
       <c r="AG4">
-        <v>1408.57</v>
+        <v>1403.23</v>
       </c>
       <c r="AH4">
-        <v>1250.25</v>
+        <v>1243.69</v>
       </c>
       <c r="AI4">
-        <v>1382.39</v>
+        <v>1367.12</v>
       </c>
       <c r="AJ4" t="s">
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>24.67</v>
+        <v>29.09</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1316,10 +1281,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1593.1</v>
+        <v>1647.5</v>
       </c>
       <c r="D5">
-        <v>-6.7</v>
+        <v>3.41</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1328,46 +1293,46 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-15.4</v>
+        <v>-12.52</v>
       </c>
       <c r="H5">
-        <v>22.72</v>
+        <v>26.91</v>
       </c>
       <c r="I5">
-        <v>-4.72</v>
+        <v>-3.24</v>
       </c>
       <c r="J5">
-        <v>-6.09</v>
+        <v>-3.15</v>
       </c>
       <c r="K5">
-        <v>-11.83</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="L5">
-        <v>21.62</v>
+        <v>25.77</v>
       </c>
       <c r="M5">
-        <v>16.95</v>
+        <v>17.85</v>
       </c>
       <c r="N5">
         <v>66</v>
       </c>
       <c r="O5">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="P5">
-        <v>1681.76</v>
+        <v>1670.72</v>
       </c>
       <c r="Q5">
-        <v>1685.43</v>
+        <v>1682.47</v>
       </c>
       <c r="R5">
-        <v>1754.95</v>
+        <v>1751.35</v>
       </c>
       <c r="S5">
-        <v>1598.22</v>
+        <v>1598.99</v>
       </c>
       <c r="T5">
-        <v>-0.32</v>
+        <v>3.03</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1379,46 +1344,46 @@
         <v>47</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5">
-        <v>30.9</v>
+        <v>41.74</v>
       </c>
       <c r="Z5">
-        <v>-21.74</v>
+        <v>-22.85</v>
       </c>
       <c r="AA5">
-        <v>-21.63</v>
+        <v>-21.87</v>
       </c>
       <c r="AB5">
-        <v>-0.12</v>
+        <v>-0.98</v>
       </c>
       <c r="AC5">
-        <v>65.58</v>
+        <v>51.74</v>
       </c>
       <c r="AD5">
-        <v>84.52</v>
+        <v>70.02</v>
       </c>
       <c r="AE5">
-        <v>37.24</v>
+        <v>39.04</v>
       </c>
       <c r="AF5">
-        <v>383.28</v>
+        <v>78.73</v>
       </c>
       <c r="AG5">
-        <v>1738.58</v>
+        <v>1737.2</v>
       </c>
       <c r="AH5">
-        <v>1632.28</v>
+        <v>1627.74</v>
       </c>
       <c r="AI5">
-        <v>1761.08</v>
+        <v>1757.42</v>
       </c>
       <c r="AJ5" t="s">
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>28.77</v>
+        <v>32.65</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1429,58 +1394,58 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>198</v>
+        <v>204.36</v>
       </c>
       <c r="D6">
-        <v>-6.88</v>
+        <v>3.21</v>
       </c>
       <c r="E6">
         <v>248.91</v>
       </c>
       <c r="F6">
-        <v>118.99</v>
+        <v>120.13</v>
       </c>
       <c r="G6">
-        <v>-20.45</v>
+        <v>-17.9</v>
       </c>
       <c r="H6">
-        <v>66.40000000000001</v>
+        <v>70.12</v>
       </c>
       <c r="I6">
-        <v>-2.8</v>
+        <v>-0.95</v>
       </c>
       <c r="J6">
-        <v>-6.3</v>
+        <v>-4.35</v>
       </c>
       <c r="K6">
-        <v>-16.08</v>
+        <v>-12.11</v>
       </c>
       <c r="L6">
-        <v>67.2</v>
+        <v>71.75</v>
       </c>
       <c r="M6">
-        <v>58.66</v>
+        <v>58.12</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="P6">
-        <v>207.83</v>
+        <v>207.44</v>
       </c>
       <c r="Q6">
-        <v>206.98</v>
+        <v>206.7</v>
       </c>
       <c r="R6">
-        <v>214.35</v>
+        <v>213.76</v>
       </c>
       <c r="S6">
-        <v>181.71</v>
+        <v>181.97</v>
       </c>
       <c r="T6">
-        <v>8.960000000000001</v>
+        <v>12.3</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1495,34 +1460,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>36.73</v>
+        <v>45.16</v>
       </c>
       <c r="Z6">
-        <v>-2.03</v>
+        <v>-2.08</v>
       </c>
       <c r="AA6">
-        <v>-2.49</v>
+        <v>-2.4</v>
       </c>
       <c r="AB6">
-        <v>0.45</v>
+        <v>0.33</v>
       </c>
       <c r="AC6">
-        <v>62.95</v>
+        <v>43.67</v>
       </c>
       <c r="AD6">
-        <v>85.64</v>
+        <v>66.86</v>
       </c>
       <c r="AE6">
-        <v>5.89</v>
+        <v>6.03</v>
       </c>
       <c r="AF6">
-        <v>216.53</v>
+        <v>102.19</v>
       </c>
       <c r="AG6">
-        <v>214.39</v>
+        <v>214.06</v>
       </c>
       <c r="AH6">
-        <v>199.56</v>
+        <v>199.33</v>
       </c>
       <c r="AI6">
         <v>217.63</v>
@@ -1531,7 +1496,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>30.9</v>
+        <v>29.93</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1542,10 +1507,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>401.15</v>
+        <v>402.2</v>
       </c>
       <c r="D7">
-        <v>-2.65</v>
+        <v>0.26</v>
       </c>
       <c r="E7">
         <v>588.6900000000001</v>
@@ -1554,46 +1519,46 @@
         <v>393.4</v>
       </c>
       <c r="G7">
-        <v>-31.86</v>
+        <v>-31.68</v>
       </c>
       <c r="H7">
-        <v>1.97</v>
+        <v>2.24</v>
       </c>
       <c r="I7">
-        <v>-1.86</v>
+        <v>-2.64</v>
       </c>
       <c r="J7">
-        <v>-7.18</v>
+        <v>-9.41</v>
       </c>
       <c r="K7">
-        <v>-8.24</v>
+        <v>-5.33</v>
       </c>
       <c r="L7">
-        <v>-29.62</v>
+        <v>-28.05</v>
       </c>
       <c r="M7">
-        <v>-0.2</v>
+        <v>-0.17</v>
       </c>
       <c r="N7">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="O7">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P7">
-        <v>411.31</v>
+        <v>409.13</v>
       </c>
       <c r="Q7">
-        <v>419.51</v>
+        <v>417.82</v>
       </c>
       <c r="R7">
-        <v>426.28</v>
+        <v>425.77</v>
       </c>
       <c r="S7">
-        <v>471.57</v>
+        <v>470.79</v>
       </c>
       <c r="T7">
-        <v>-14.93</v>
+        <v>-14.57</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1608,43 +1573,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>36.33</v>
+        <v>37.31</v>
       </c>
       <c r="Z7">
-        <v>-5.88</v>
+        <v>-6.33</v>
       </c>
       <c r="AA7">
-        <v>-4.88</v>
+        <v>-5.17</v>
       </c>
       <c r="AB7">
-        <v>-1</v>
+        <v>-1.16</v>
       </c>
       <c r="AC7">
-        <v>42.59</v>
+        <v>31.7</v>
       </c>
       <c r="AD7">
-        <v>55.77</v>
+        <v>46.67</v>
       </c>
       <c r="AE7">
-        <v>9.119999999999999</v>
+        <v>8.91</v>
       </c>
       <c r="AF7">
-        <v>-19.54</v>
+        <v>-50.77</v>
       </c>
       <c r="AG7">
-        <v>442.49</v>
+        <v>440.66</v>
       </c>
       <c r="AH7">
-        <v>396.53</v>
+        <v>394.98</v>
       </c>
       <c r="AI7">
-        <v>433.63</v>
+        <v>430.79</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>24.08</v>
+        <v>24.37</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1655,10 +1620,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>621.2</v>
+        <v>613.65</v>
       </c>
       <c r="D8">
-        <v>-2.4</v>
+        <v>-1.22</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1667,46 +1632,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-23.14</v>
+        <v>-24.08</v>
       </c>
       <c r="H8">
-        <v>32.81</v>
+        <v>31.19</v>
       </c>
       <c r="I8">
-        <v>-2.88</v>
+        <v>-4.15</v>
       </c>
       <c r="J8">
-        <v>-4.64</v>
+        <v>-8.08</v>
       </c>
       <c r="K8">
-        <v>-15.81</v>
+        <v>-14.46</v>
       </c>
       <c r="L8">
-        <v>-2.25</v>
+        <v>3.6</v>
       </c>
       <c r="M8">
-        <v>-15.6</v>
+        <v>-16.47</v>
       </c>
       <c r="N8">
         <v>55</v>
       </c>
       <c r="O8">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="P8">
-        <v>637.4</v>
+        <v>632.08</v>
       </c>
       <c r="Q8">
-        <v>651.48</v>
+        <v>648.8099999999999</v>
       </c>
       <c r="R8">
-        <v>680.86</v>
+        <v>678.47</v>
       </c>
       <c r="S8">
-        <v>614</v>
+        <v>613.97</v>
       </c>
       <c r="T8">
-        <v>1.17</v>
+        <v>-0.05</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1718,46 +1683,46 @@
         <v>47</v>
       </c>
       <c r="X8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y8">
-        <v>31.06</v>
+        <v>28.71</v>
       </c>
       <c r="Z8">
-        <v>-11.85</v>
+        <v>-13.36</v>
       </c>
       <c r="AA8">
-        <v>-10.89</v>
+        <v>-11.39</v>
       </c>
       <c r="AB8">
-        <v>-0.96</v>
+        <v>-1.98</v>
       </c>
       <c r="AC8">
-        <v>14.57</v>
+        <v>1.27</v>
       </c>
       <c r="AD8">
-        <v>21.67</v>
+        <v>13.42</v>
       </c>
       <c r="AE8">
-        <v>16.13</v>
+        <v>16.38</v>
       </c>
       <c r="AF8">
-        <v>-18.52</v>
+        <v>-25.49</v>
       </c>
       <c r="AG8">
-        <v>674.85</v>
+        <v>676.51</v>
       </c>
       <c r="AH8">
-        <v>628.11</v>
+        <v>621.12</v>
       </c>
       <c r="AI8">
-        <v>675.1</v>
+        <v>668.99</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>19.06</v>
+        <v>21.75</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1768,10 +1733,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>192.55</v>
+        <v>194.38</v>
       </c>
       <c r="D9">
-        <v>-1.9</v>
+        <v>0.95</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1780,46 +1745,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-30.64</v>
+        <v>-29.98</v>
       </c>
       <c r="H9">
-        <v>11.75</v>
+        <v>12.81</v>
       </c>
       <c r="I9">
-        <v>-0.6899999999999999</v>
+        <v>-3.12</v>
       </c>
       <c r="J9">
-        <v>1.64</v>
+        <v>2.14</v>
       </c>
       <c r="K9">
-        <v>1</v>
+        <v>2.21</v>
       </c>
       <c r="L9">
-        <v>-23.58</v>
+        <v>-22.12</v>
       </c>
       <c r="M9">
-        <v>-7.02</v>
+        <v>-6.82</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="P9">
-        <v>198.22</v>
+        <v>196.97</v>
       </c>
       <c r="Q9">
-        <v>193.96</v>
+        <v>194.15</v>
       </c>
       <c r="R9">
-        <v>190</v>
+        <v>190.14</v>
       </c>
       <c r="S9">
-        <v>205.01</v>
+        <v>204.62</v>
       </c>
       <c r="T9">
-        <v>-6.08</v>
+        <v>-5</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1834,34 +1799,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>49.14</v>
+        <v>52.04</v>
       </c>
       <c r="Z9">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AA9">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AB9">
-        <v>0.25</v>
+        <v>0.08</v>
       </c>
       <c r="AC9">
-        <v>50.93</v>
+        <v>36.31</v>
       </c>
       <c r="AD9">
-        <v>73.51000000000001</v>
+        <v>54.57</v>
       </c>
       <c r="AE9">
-        <v>5.3</v>
+        <v>5.17</v>
       </c>
       <c r="AF9">
-        <v>-13.64</v>
+        <v>-9.06</v>
       </c>
       <c r="AG9">
-        <v>201.98</v>
+        <v>202.01</v>
       </c>
       <c r="AH9">
-        <v>185.94</v>
+        <v>186.29</v>
       </c>
       <c r="AI9">
         <v>185.88</v>
@@ -1870,7 +1835,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>31.17</v>
+        <v>27.28</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1881,10 +1846,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>72.2</v>
+        <v>71.42</v>
       </c>
       <c r="D10">
-        <v>-2.13</v>
+        <v>-1.08</v>
       </c>
       <c r="E10">
         <v>141.26</v>
@@ -1893,46 +1858,46 @@
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-48.89</v>
+        <v>-49.44</v>
       </c>
       <c r="H10">
-        <v>21.79</v>
+        <v>20.48</v>
       </c>
       <c r="I10">
-        <v>-3.91</v>
+        <v>-4.48</v>
       </c>
       <c r="J10">
-        <v>-6.36</v>
+        <v>-7.71</v>
       </c>
       <c r="K10">
-        <v>-12.21</v>
+        <v>-12.85</v>
       </c>
       <c r="L10">
-        <v>-49.15</v>
+        <v>-49.25</v>
       </c>
       <c r="M10">
-        <v>-1.37</v>
+        <v>-1.34</v>
       </c>
       <c r="N10">
         <v>12</v>
       </c>
       <c r="O10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P10">
-        <v>73.86</v>
+        <v>73.19</v>
       </c>
       <c r="Q10">
-        <v>75.56</v>
+        <v>75.3</v>
       </c>
       <c r="R10">
-        <v>78.03</v>
+        <v>77.8</v>
       </c>
       <c r="S10">
-        <v>81.23</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="T10">
-        <v>-11.12</v>
+        <v>-11.99</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1947,43 +1912,43 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>30.61</v>
+        <v>28.3</v>
       </c>
       <c r="Z10">
-        <v>-1.24</v>
+        <v>-1.4</v>
       </c>
       <c r="AA10">
-        <v>-1.06</v>
+        <v>-1.13</v>
       </c>
       <c r="AB10">
-        <v>-0.17</v>
+        <v>-0.27</v>
       </c>
       <c r="AC10">
-        <v>30.75</v>
+        <v>13.21</v>
       </c>
       <c r="AD10">
-        <v>46.48</v>
+        <v>31.24</v>
       </c>
       <c r="AE10">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AF10">
-        <v>10.97</v>
+        <v>-26.85</v>
       </c>
       <c r="AG10">
-        <v>78.37</v>
+        <v>78.61</v>
       </c>
       <c r="AH10">
-        <v>72.75</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="AI10">
-        <v>78.88</v>
+        <v>78.19</v>
       </c>
       <c r="AJ10" t="s">
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>47.76</v>
+        <v>51.83</v>
       </c>
     </row>
   </sheetData>
@@ -2164,7 +2129,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2183,1353 +2148,1347 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-5.96</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-8.99</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-3.03</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-5</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-6.65</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-1.65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-12.15</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-9.32</v>
+      </c>
+      <c r="E10" s="8">
+        <v>2.83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-6.09</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-3.15</v>
+      </c>
+      <c r="E11" s="8">
+        <v>2.94</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-6.3</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-4.35</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-7.18</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-9.41</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-2.23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-4.64</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-8.08</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-3.44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E9" s="3" t="s">
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>1.64</v>
+      </c>
+      <c r="D15" s="6">
+        <v>2.14</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-6.36</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-7.71</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-1.35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-1.88</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-2.57</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-4.65</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-7.91</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-3.26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-7.12</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-4.89</v>
+      </c>
+      <c r="E19" s="8">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-4.72</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-3.24</v>
+      </c>
+      <c r="E20" s="8">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-2.8</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-0.95</v>
+      </c>
+      <c r="E21" s="8">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-1.86</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-2.64</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-0.78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-2.88</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-4.15</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-1.27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-3.12</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-2.43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-3.91</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-4.48</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-28.61</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-28.95</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>25.9</v>
+      </c>
+      <c r="D27" s="6">
+        <v>25.93</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>30.46</v>
+      </c>
+      <c r="D28" s="6">
+        <v>37.33</v>
+      </c>
+      <c r="E28" s="8">
+        <v>6.87</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>21.62</v>
+      </c>
+      <c r="D29" s="6">
+        <v>25.77</v>
+      </c>
+      <c r="E29" s="8">
+        <v>4.15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>67.2</v>
+      </c>
+      <c r="D30" s="6">
+        <v>71.75</v>
+      </c>
+      <c r="E30" s="8">
+        <v>4.55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-29.62</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-28.05</v>
+      </c>
+      <c r="E31" s="8">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-2.25</v>
+      </c>
+      <c r="D32" s="6">
+        <v>3.6</v>
+      </c>
+      <c r="E32" s="8">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-23.58</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-22.12</v>
+      </c>
+      <c r="E33" s="8">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-49.15</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-49.25</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-6.28</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-5.27</v>
+      </c>
+      <c r="E35" s="8">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-3.63</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-2.07</v>
+      </c>
+      <c r="E36" s="8">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-16.18</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-11.38</v>
+      </c>
+      <c r="E37" s="8">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-11.83</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-8.279999999999999</v>
+      </c>
+      <c r="E38" s="8">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-16.08</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-12.11</v>
+      </c>
+      <c r="E39" s="8">
+        <v>3.97</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-8.24</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-5.33</v>
+      </c>
+      <c r="E40" s="8">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-15.81</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-14.46</v>
+      </c>
+      <c r="E41" s="8">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6">
+        <v>1</v>
+      </c>
+      <c r="D42" s="6">
+        <v>2.21</v>
+      </c>
+      <c r="E42" s="8">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-12.21</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-12.85</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-32.91</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-33.13</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-10.99</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-10.84</v>
+      </c>
+      <c r="E45" s="8">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-24.28</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-21.16</v>
+      </c>
+      <c r="E46" s="8">
+        <v>3.12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-15.4</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-12.52</v>
+      </c>
+      <c r="E47" s="8">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-20.45</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-17.9</v>
+      </c>
+      <c r="E48" s="8">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-31.86</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-31.68</v>
+      </c>
+      <c r="E49" s="8">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-23.14</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-24.08</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-30.64</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-29.98</v>
+      </c>
+      <c r="E51" s="8">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="6">
+        <v>-48.89</v>
+      </c>
+      <c r="D52" s="6">
+        <v>-49.44</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>1276.5</v>
+      </c>
+      <c r="D53" s="6">
+        <v>1272.3</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-4.2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>2859.1</v>
+      </c>
+      <c r="D54" s="6">
+        <v>2863.9</v>
+      </c>
+      <c r="E54" s="8">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>1214.9</v>
+      </c>
+      <c r="D55" s="6">
+        <v>1265</v>
+      </c>
+      <c r="E55" s="8">
+        <v>50.1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>1593.1</v>
+      </c>
+      <c r="D56" s="6">
+        <v>1647.5</v>
+      </c>
+      <c r="E56" s="8">
+        <v>54.4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>198</v>
+      </c>
+      <c r="D57" s="6">
+        <v>204.36</v>
+      </c>
+      <c r="E57" s="8">
+        <v>6.36</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>401.15</v>
+      </c>
+      <c r="D58" s="6">
+        <v>402.2</v>
+      </c>
+      <c r="E58" s="8">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>621.2</v>
+      </c>
+      <c r="D59" s="6">
+        <v>613.65</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-7.55</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="6">
+        <v>192.55</v>
+      </c>
+      <c r="D60" s="6">
+        <v>194.38</v>
+      </c>
+      <c r="E60" s="8">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="6">
+        <v>72.2</v>
+      </c>
+      <c r="D61" s="6">
+        <v>71.42</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-0.78</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="6">
+        <v>34</v>
+      </c>
+      <c r="D62" s="6">
+        <v>23</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="6">
+        <v>88</v>
+      </c>
+      <c r="D63" s="6">
         <v>77</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="E63" s="7">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="6">
+        <v>77</v>
+      </c>
+      <c r="D64" s="6">
+        <v>88</v>
+      </c>
+      <c r="E64" s="8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" s="6">
+        <v>23</v>
+      </c>
+      <c r="D65" s="6">
+        <v>34</v>
+      </c>
+      <c r="E65" s="8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-3.69</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-5.96</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-2.27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>35.89</v>
+      </c>
+      <c r="D66" s="6">
+        <v>35.07</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-0.82</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>3.92</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-5</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-8.92</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>35.28</v>
+      </c>
+      <c r="D67" s="6">
+        <v>35.78</v>
+      </c>
+      <c r="E67" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-3.51</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-12.15</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-8.640000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>29.25</v>
+      </c>
+      <c r="D68" s="6">
+        <v>38.83</v>
+      </c>
+      <c r="E68" s="8">
+        <v>9.58</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>2.61</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-6.09</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-8.699999999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>30.9</v>
+      </c>
+      <c r="D69" s="6">
+        <v>41.74</v>
+      </c>
+      <c r="E69" s="8">
+        <v>10.84</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>1.75</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-6.3</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-8.050000000000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="6">
+        <v>36.73</v>
+      </c>
+      <c r="D70" s="6">
+        <v>45.16</v>
+      </c>
+      <c r="E70" s="8">
+        <v>8.43</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-5.1</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-7.18</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-2.08</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="6">
+        <v>36.33</v>
+      </c>
+      <c r="D71" s="6">
+        <v>37.31</v>
+      </c>
+      <c r="E71" s="8">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-2.1</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-4.64</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-2.54</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B72" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="6">
+        <v>31.06</v>
+      </c>
+      <c r="D72" s="6">
+        <v>28.71</v>
+      </c>
+      <c r="E72" s="7">
+        <v>-2.35</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="7">
-        <v>4.63</v>
-      </c>
-      <c r="D17" s="7">
-        <v>1.64</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-2.99</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B73" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="6">
+        <v>49.14</v>
+      </c>
+      <c r="D73" s="6">
+        <v>52.04</v>
+      </c>
+      <c r="E73" s="8">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-3.25</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-6.36</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-3.11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B74" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C74" s="6">
+        <v>30.61</v>
+      </c>
+      <c r="D74" s="6">
+        <v>28.3</v>
+      </c>
+      <c r="E74" s="7">
+        <v>-2.31</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-0.08</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-1.88</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-1.8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
+        <v>83.33</v>
+      </c>
+      <c r="D75" s="6">
+        <v>-36.99</v>
+      </c>
+      <c r="E75" s="7">
+        <v>-120.32</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>5.72</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-4.65</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-10.37</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>1067.96</v>
+      </c>
+      <c r="D76" s="6">
+        <v>134.1</v>
+      </c>
+      <c r="E76" s="7">
+        <v>-933.86</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-0.68</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-7.12</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-6.44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>63.95</v>
+      </c>
+      <c r="D77" s="6">
+        <v>184.74</v>
+      </c>
+      <c r="E77" s="8">
+        <v>120.79</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>0.44</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-4.72</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-5.16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="6">
+        <v>383.28</v>
+      </c>
+      <c r="D78" s="6">
+        <v>78.73</v>
+      </c>
+      <c r="E78" s="7">
+        <v>-304.55</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>3.47</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-2.8</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-6.27</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
+        <v>216.53</v>
+      </c>
+      <c r="D79" s="6">
+        <v>102.19</v>
+      </c>
+      <c r="E79" s="7">
+        <v>-114.34</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7">
-        <v>-0.59</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-1.86</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-1.27</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B80" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="6">
+        <v>-19.54</v>
+      </c>
+      <c r="D80" s="6">
+        <v>-50.77</v>
+      </c>
+      <c r="E80" s="7">
+        <v>-31.23</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-1.49</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-2.88</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-1.39</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B81" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="6">
+        <v>-18.52</v>
+      </c>
+      <c r="D81" s="6">
+        <v>-25.49</v>
+      </c>
+      <c r="E81" s="7">
+        <v>-6.97</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="7">
-        <v>4.33</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-0.6899999999999999</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-5.02</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B82" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="6">
+        <v>-13.64</v>
+      </c>
+      <c r="D82" s="6">
+        <v>-9.06</v>
+      </c>
+      <c r="E82" s="8">
+        <v>4.58</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="7">
-        <v>-2.28</v>
-      </c>
-      <c r="D27" s="7">
-        <v>-3.91</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-1.63</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>-27.31</v>
-      </c>
-      <c r="D28" s="7">
-        <v>-28.61</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>37.65</v>
-      </c>
-      <c r="D29" s="7">
-        <v>25.9</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-11.75</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>35.98</v>
-      </c>
-      <c r="D30" s="7">
-        <v>30.46</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-5.52</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="7">
-        <v>27.92</v>
-      </c>
-      <c r="D31" s="7">
-        <v>21.62</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-6.3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="7">
-        <v>75.54000000000001</v>
-      </c>
-      <c r="D32" s="7">
-        <v>67.2</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-8.34</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-28.73</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-29.62</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-0.89</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="7">
-        <v>0.87</v>
-      </c>
-      <c r="D34" s="7">
-        <v>-2.25</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-3.12</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="7">
-        <v>-24.41</v>
-      </c>
-      <c r="D35" s="7">
-        <v>-23.58</v>
-      </c>
-      <c r="E35" s="9">
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-48.22</v>
-      </c>
-      <c r="D36" s="7">
-        <v>-49.15</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-0.93</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-3.39</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-6.28</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-2.89</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="7">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="D38" s="7">
-        <v>-3.63</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-12.58</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-9.390000000000001</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-16.18</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-6.79</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-3.86</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-11.83</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-7.97</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-8.470000000000001</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-16.08</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-7.61</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-4.79</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-8.24</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-3.45</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="7">
-        <v>-13.23</v>
-      </c>
-      <c r="D43" s="7">
-        <v>-15.81</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-2.58</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="7">
-        <v>2.95</v>
-      </c>
-      <c r="D44" s="7">
-        <v>1</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-1.95</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="7">
-        <v>-9.890000000000001</v>
-      </c>
-      <c r="D45" s="7">
-        <v>-12.21</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-2.32</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-31.34</v>
-      </c>
-      <c r="D46" s="7">
-        <v>-32.91</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-1.57</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-1.36</v>
-      </c>
-      <c r="D47" s="7">
-        <v>-10.99</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-9.630000000000001</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="7">
-        <v>-18.29</v>
-      </c>
-      <c r="D48" s="7">
-        <v>-24.28</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-5.99</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="7">
-        <v>-9.33</v>
-      </c>
-      <c r="D49" s="7">
-        <v>-15.4</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-6.07</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="7">
-        <v>-14.58</v>
-      </c>
-      <c r="D50" s="7">
-        <v>-20.45</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-5.87</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="7">
-        <v>-30.01</v>
-      </c>
-      <c r="D51" s="7">
-        <v>-31.86</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-1.85</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="7">
-        <v>-21.25</v>
-      </c>
-      <c r="D52" s="7">
-        <v>-23.14</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-1.89</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53" s="7">
-        <v>-29.3</v>
-      </c>
-      <c r="D53" s="7">
-        <v>-30.64</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-1.34</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C54" s="7">
-        <v>-48.05</v>
-      </c>
-      <c r="D54" s="7">
-        <v>-48.89</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-0.84</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="7">
-        <v>1306.4</v>
-      </c>
-      <c r="D55" s="7">
-        <v>1276.5</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-29.9</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="7">
-        <v>3168.5</v>
-      </c>
-      <c r="D56" s="7">
-        <v>2859.1</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-309.4</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="7">
-        <v>1311</v>
-      </c>
-      <c r="D57" s="7">
-        <v>1214.9</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-96.09999999999999</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="7">
-        <v>1707.5</v>
-      </c>
-      <c r="D58" s="7">
-        <v>1593.1</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-114.4</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="7">
-        <v>212.63</v>
-      </c>
-      <c r="D59" s="7">
-        <v>198</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-14.63</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="7">
-        <v>412.05</v>
-      </c>
-      <c r="D60" s="7">
-        <v>401.15</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-10.9</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="7">
-        <v>636.5</v>
-      </c>
-      <c r="D61" s="7">
-        <v>621.2</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-15.3</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C62" s="7">
-        <v>196.27</v>
-      </c>
-      <c r="D62" s="7">
-        <v>192.55</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-3.72</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C63" s="7">
-        <v>73.77</v>
-      </c>
-      <c r="D63" s="7">
-        <v>72.2</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-1.57</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C64" s="7">
-        <v>66</v>
-      </c>
-      <c r="D64" s="7">
-        <v>77</v>
-      </c>
-      <c r="E64" s="9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C65" s="7">
-        <v>77</v>
-      </c>
-      <c r="D65" s="7">
-        <v>66</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="7">
-        <v>42.43</v>
-      </c>
-      <c r="D66" s="7">
-        <v>35.89</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-6.54</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="7">
-        <v>66.51000000000001</v>
-      </c>
-      <c r="D67" s="7">
-        <v>35.28</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-31.23</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="7">
-        <v>40.57</v>
-      </c>
-      <c r="D68" s="7">
-        <v>29.25</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-11.32</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="7">
-        <v>48.54</v>
-      </c>
-      <c r="D69" s="7">
-        <v>30.9</v>
-      </c>
-      <c r="E69" s="8">
-        <v>-17.64</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="7">
-        <v>54.68</v>
-      </c>
-      <c r="D70" s="7">
-        <v>36.73</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-17.95</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="7">
-        <v>42.8</v>
-      </c>
-      <c r="D71" s="7">
-        <v>36.33</v>
-      </c>
-      <c r="E71" s="8">
-        <v>-6.47</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="7">
-        <v>36.7</v>
-      </c>
-      <c r="D72" s="7">
-        <v>31.06</v>
-      </c>
-      <c r="E72" s="8">
-        <v>-5.64</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="7">
-        <v>55.46</v>
-      </c>
-      <c r="D73" s="7">
-        <v>49.14</v>
-      </c>
-      <c r="E73" s="8">
-        <v>-6.32</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C74" s="7">
-        <v>36.13</v>
-      </c>
-      <c r="D74" s="7">
-        <v>30.61</v>
-      </c>
-      <c r="E74" s="8">
-        <v>-5.52</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B75" s="6" t="s">
+      <c r="B83" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C75" s="7">
-        <v>-57.59</v>
-      </c>
-      <c r="D75" s="7">
-        <v>83.33</v>
-      </c>
-      <c r="E75" s="9">
-        <v>140.92</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="7">
-        <v>-52.7</v>
-      </c>
-      <c r="D76" s="7">
-        <v>1067.96</v>
-      </c>
-      <c r="E76" s="9">
-        <v>1120.66</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="7">
-        <v>-48.12</v>
-      </c>
-      <c r="D77" s="7">
-        <v>63.95</v>
-      </c>
-      <c r="E77" s="9">
-        <v>112.07</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="7">
-        <v>63.55</v>
-      </c>
-      <c r="D78" s="7">
-        <v>383.28</v>
-      </c>
-      <c r="E78" s="9">
-        <v>319.73</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="7">
-        <v>-16.9</v>
-      </c>
-      <c r="D79" s="7">
-        <v>216.53</v>
-      </c>
-      <c r="E79" s="9">
-        <v>233.43</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="7">
-        <v>-22.2</v>
-      </c>
-      <c r="D80" s="7">
-        <v>-19.54</v>
-      </c>
-      <c r="E80" s="9">
-        <v>2.66</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="7">
-        <v>-69.02</v>
-      </c>
-      <c r="D81" s="7">
-        <v>-18.52</v>
-      </c>
-      <c r="E81" s="9">
-        <v>50.5</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="7">
-        <v>-71.51000000000001</v>
-      </c>
-      <c r="D82" s="7">
-        <v>-13.64</v>
-      </c>
-      <c r="E82" s="9">
-        <v>57.87</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" s="7">
-        <v>-38.18</v>
-      </c>
-      <c r="D83" s="7">
+      <c r="C83" s="6">
         <v>10.97</v>
       </c>
-      <c r="E83" s="9">
-        <v>49.15</v>
+      <c r="D83" s="6">
+        <v>-26.85</v>
+      </c>
+      <c r="E83" s="7">
+        <v>-37.82</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3549,60 +3508,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="I1" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="C1" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>85</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>48.16</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="12">
         <v>9</v>
       </c>
-      <c r="D2" s="12">
-        <v>35</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="11">
+        <v>38.1</v>
+      </c>
+      <c r="E2" s="11">
         <v>40</v>
       </c>
-      <c r="F2" s="12">
-        <v>-5.8</v>
-      </c>
-      <c r="G2" s="12">
-        <v>-9.9</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="11">
+        <v>-6.2</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-7.7</v>
+      </c>
+      <c r="H2" s="11">
         <v>55.4</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -3704,61 +3663,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="13" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="15">
-        <v>0.5866</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.1695</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.1254</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.026</v>
-      </c>
-      <c r="E2" s="15">
-        <v>-0.002</v>
-      </c>
-      <c r="F2" s="15">
-        <v>-0.0137</v>
-      </c>
-      <c r="G2" s="15">
-        <v>-0.0702</v>
-      </c>
-      <c r="H2" s="15">
-        <v>-0.1116</v>
-      </c>
-      <c r="I2" s="15">
-        <v>-0.156</v>
+      <c r="A2" s="14">
+        <v>0.5811999999999999</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1785</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.129</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.0322</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.0017</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.0134</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.0682</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.113</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.1647</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,31 +193,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>29.2 → 38.8</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>29.2</t>
-  </si>
-  <si>
-    <t>38.8</t>
-  </si>
-  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>49.1 → 52.0</t>
-  </si>
-  <si>
-    <t>49.1</t>
+    <t>52.0 → 47.1</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>52.0</t>
+  </si>
+  <si>
+    <t>47.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -303,14 +291,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -343,13 +331,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -942,10 +930,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1272.3</v>
+        <v>1266.6</v>
       </c>
       <c r="D2">
-        <v>-0.33</v>
+        <v>-0.45</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -954,46 +942,46 @@
         <v>1247.38</v>
       </c>
       <c r="G2">
-        <v>-33.13</v>
+        <v>-33.43</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>1.54</v>
       </c>
       <c r="I2">
-        <v>-2.57</v>
+        <v>-4.89</v>
       </c>
       <c r="J2">
-        <v>-8.99</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="K2">
-        <v>-5.27</v>
+        <v>-5.69</v>
       </c>
       <c r="L2">
-        <v>-28.95</v>
+        <v>-29.3</v>
       </c>
       <c r="M2">
-        <v>-11.3</v>
+        <v>-11.74</v>
       </c>
       <c r="N2">
         <v>23</v>
       </c>
       <c r="O2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P2">
-        <v>1299.5</v>
+        <v>1286.48</v>
       </c>
       <c r="Q2">
-        <v>1321.67</v>
+        <v>1315.3</v>
       </c>
       <c r="R2">
-        <v>1345.87</v>
+        <v>1344.61</v>
       </c>
       <c r="S2">
-        <v>1500.37</v>
+        <v>1497.55</v>
       </c>
       <c r="T2">
-        <v>-15.2</v>
+        <v>-15.42</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1008,43 +996,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>35.07</v>
+        <v>33.94</v>
       </c>
       <c r="Z2">
-        <v>-17.99</v>
+        <v>-19.68</v>
       </c>
       <c r="AA2">
-        <v>-14.7</v>
+        <v>-15.7</v>
       </c>
       <c r="AB2">
-        <v>-3.29</v>
+        <v>-3.98</v>
       </c>
       <c r="AC2">
-        <v>28.77</v>
+        <v>10.83</v>
       </c>
       <c r="AD2">
-        <v>49.85</v>
+        <v>28.7</v>
       </c>
       <c r="AE2">
-        <v>24.18</v>
+        <v>23.84</v>
       </c>
       <c r="AF2">
-        <v>-36.99</v>
+        <v>4.04</v>
       </c>
       <c r="AG2">
-        <v>1385.85</v>
+        <v>1374.34</v>
       </c>
       <c r="AH2">
-        <v>1257.49</v>
+        <v>1256.26</v>
       </c>
       <c r="AI2">
-        <v>1352.19</v>
+        <v>1334.07</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>29.97</v>
+        <v>32.82</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1055,10 +1043,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2863.9</v>
+        <v>2891.8</v>
       </c>
       <c r="D3">
-        <v>0.17</v>
+        <v>0.97</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1067,46 +1055,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-10.84</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="H3">
-        <v>62.91</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="I3">
-        <v>-7.91</v>
+        <v>-7.08</v>
       </c>
       <c r="J3">
-        <v>-6.65</v>
+        <v>-5.19</v>
       </c>
       <c r="K3">
-        <v>-2.07</v>
+        <v>-2.68</v>
       </c>
       <c r="L3">
-        <v>25.93</v>
+        <v>28.89</v>
       </c>
       <c r="M3">
-        <v>12.9</v>
+        <v>13.04</v>
       </c>
       <c r="N3">
         <v>77</v>
       </c>
       <c r="O3">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="P3">
-        <v>3034.5</v>
+        <v>2990.46</v>
       </c>
       <c r="Q3">
-        <v>3018.02</v>
+        <v>3010.11</v>
       </c>
       <c r="R3">
-        <v>3063.67</v>
+        <v>3062.25</v>
       </c>
       <c r="S3">
-        <v>2504.83</v>
+        <v>2507.1</v>
       </c>
       <c r="T3">
-        <v>14.33</v>
+        <v>15.34</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1121,43 +1109,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>35.78</v>
+        <v>38.77</v>
       </c>
       <c r="Z3">
-        <v>-13.1</v>
+        <v>-21.84</v>
       </c>
       <c r="AA3">
-        <v>-2.76</v>
+        <v>-6.58</v>
       </c>
       <c r="AB3">
-        <v>-10.34</v>
+        <v>-15.26</v>
       </c>
       <c r="AC3">
-        <v>33.76</v>
+        <v>4.25</v>
       </c>
       <c r="AD3">
-        <v>66.73</v>
+        <v>34.85</v>
       </c>
       <c r="AE3">
-        <v>82.34999999999999</v>
+        <v>81.79000000000001</v>
       </c>
       <c r="AF3">
-        <v>134.1</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="AG3">
-        <v>3176.98</v>
+        <v>3177.87</v>
       </c>
       <c r="AH3">
-        <v>2859.05</v>
+        <v>2842.34</v>
       </c>
       <c r="AI3">
-        <v>3141.31</v>
+        <v>3113.12</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>37.38</v>
+        <v>38.95</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1168,10 +1156,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1265</v>
+        <v>1296</v>
       </c>
       <c r="D4">
-        <v>4.12</v>
+        <v>2.45</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1180,46 +1168,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-21.16</v>
+        <v>-19.23</v>
       </c>
       <c r="H4">
-        <v>63.69</v>
+        <v>67.7</v>
       </c>
       <c r="I4">
-        <v>-4.89</v>
+        <v>-0.55</v>
       </c>
       <c r="J4">
-        <v>-9.32</v>
+        <v>-6.36</v>
       </c>
       <c r="K4">
-        <v>-11.38</v>
+        <v>-8.94</v>
       </c>
       <c r="L4">
-        <v>37.33</v>
+        <v>41.87</v>
       </c>
       <c r="M4">
-        <v>3.22</v>
+        <v>3.61</v>
       </c>
       <c r="N4">
         <v>88</v>
       </c>
       <c r="O4">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="P4">
-        <v>1284.52</v>
+        <v>1283.08</v>
       </c>
       <c r="Q4">
-        <v>1323.46</v>
+        <v>1319.26</v>
       </c>
       <c r="R4">
-        <v>1420.47</v>
+        <v>1416.17</v>
       </c>
       <c r="S4">
-        <v>1173.52</v>
+        <v>1174.66</v>
       </c>
       <c r="T4">
-        <v>7.8</v>
+        <v>10.33</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1234,34 +1222,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>38.83</v>
+        <v>43.89</v>
       </c>
       <c r="Z4">
-        <v>-38.51</v>
+        <v>-36.05</v>
       </c>
       <c r="AA4">
-        <v>-36.36</v>
+        <v>-36.3</v>
       </c>
       <c r="AB4">
-        <v>-2.15</v>
+        <v>0.25</v>
       </c>
       <c r="AC4">
-        <v>48.34</v>
+        <v>55.89</v>
       </c>
       <c r="AD4">
-        <v>62.3</v>
+        <v>54.45</v>
       </c>
       <c r="AE4">
-        <v>41.01</v>
+        <v>42.83</v>
       </c>
       <c r="AF4">
-        <v>184.74</v>
+        <v>67.36</v>
       </c>
       <c r="AG4">
-        <v>1403.23</v>
+        <v>1395.25</v>
       </c>
       <c r="AH4">
-        <v>1243.69</v>
+        <v>1243.27</v>
       </c>
       <c r="AI4">
         <v>1367.12</v>
@@ -1270,7 +1258,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>29.09</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1281,10 +1269,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1647.5</v>
+        <v>1672.7</v>
       </c>
       <c r="D5">
-        <v>3.41</v>
+        <v>1.53</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1293,46 +1281,46 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-12.52</v>
+        <v>-11.18</v>
       </c>
       <c r="H5">
-        <v>26.91</v>
+        <v>28.85</v>
       </c>
       <c r="I5">
-        <v>-3.24</v>
+        <v>-1.11</v>
       </c>
       <c r="J5">
-        <v>-3.15</v>
+        <v>-1.99</v>
       </c>
       <c r="K5">
-        <v>-8.279999999999999</v>
+        <v>-6.21</v>
       </c>
       <c r="L5">
-        <v>25.77</v>
+        <v>27.95</v>
       </c>
       <c r="M5">
-        <v>17.85</v>
+        <v>17.92</v>
       </c>
       <c r="N5">
         <v>66</v>
       </c>
       <c r="O5">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="P5">
-        <v>1670.72</v>
+        <v>1666.96</v>
       </c>
       <c r="Q5">
-        <v>1682.47</v>
+        <v>1681.1</v>
       </c>
       <c r="R5">
-        <v>1751.35</v>
+        <v>1749.13</v>
       </c>
       <c r="S5">
-        <v>1598.99</v>
+        <v>1599.82</v>
       </c>
       <c r="T5">
-        <v>3.03</v>
+        <v>4.56</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1347,34 +1335,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>41.74</v>
+        <v>45.97</v>
       </c>
       <c r="Z5">
-        <v>-22.85</v>
+        <v>-21.45</v>
       </c>
       <c r="AA5">
-        <v>-21.87</v>
+        <v>-21.79</v>
       </c>
       <c r="AB5">
-        <v>-0.98</v>
+        <v>0.34</v>
       </c>
       <c r="AC5">
-        <v>51.74</v>
+        <v>47.16</v>
       </c>
       <c r="AD5">
-        <v>70.02</v>
+        <v>54.83</v>
       </c>
       <c r="AE5">
-        <v>39.04</v>
+        <v>39.44</v>
       </c>
       <c r="AF5">
-        <v>78.73</v>
+        <v>5.85</v>
       </c>
       <c r="AG5">
-        <v>1737.2</v>
+        <v>1735.36</v>
       </c>
       <c r="AH5">
-        <v>1627.74</v>
+        <v>1626.85</v>
       </c>
       <c r="AI5">
         <v>1757.42</v>
@@ -1383,7 +1371,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>32.65</v>
+        <v>32.83</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1394,58 +1382,58 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>204.36</v>
+        <v>207.7</v>
       </c>
       <c r="D6">
-        <v>3.21</v>
+        <v>1.63</v>
       </c>
       <c r="E6">
         <v>248.91</v>
       </c>
       <c r="F6">
-        <v>120.13</v>
+        <v>121.37</v>
       </c>
       <c r="G6">
-        <v>-17.9</v>
+        <v>-16.56</v>
       </c>
       <c r="H6">
-        <v>70.12</v>
+        <v>71.13</v>
       </c>
       <c r="I6">
-        <v>-0.95</v>
+        <v>0.24</v>
       </c>
       <c r="J6">
-        <v>-4.35</v>
+        <v>-1.07</v>
       </c>
       <c r="K6">
-        <v>-12.11</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="L6">
-        <v>71.75</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="M6">
-        <v>58.12</v>
+        <v>57.1</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P6">
-        <v>207.44</v>
+        <v>207.54</v>
       </c>
       <c r="Q6">
-        <v>206.7</v>
+        <v>206.63</v>
       </c>
       <c r="R6">
-        <v>213.76</v>
+        <v>213.29</v>
       </c>
       <c r="S6">
-        <v>181.97</v>
+        <v>182.24</v>
       </c>
       <c r="T6">
-        <v>12.3</v>
+        <v>13.97</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1460,31 +1448,31 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>45.16</v>
+        <v>49</v>
       </c>
       <c r="Z6">
-        <v>-2.08</v>
+        <v>-1.82</v>
       </c>
       <c r="AA6">
-        <v>-2.4</v>
+        <v>-2.29</v>
       </c>
       <c r="AB6">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="AC6">
-        <v>43.67</v>
+        <v>35.76</v>
       </c>
       <c r="AD6">
-        <v>66.86</v>
+        <v>47.46</v>
       </c>
       <c r="AE6">
-        <v>6.03</v>
+        <v>6.14</v>
       </c>
       <c r="AF6">
-        <v>102.19</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="AG6">
-        <v>214.06</v>
+        <v>213.94</v>
       </c>
       <c r="AH6">
         <v>199.33</v>
@@ -1496,7 +1484,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>29.93</v>
+        <v>27.58</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1507,10 +1495,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>402.2</v>
+        <v>402.7</v>
       </c>
       <c r="D7">
-        <v>0.26</v>
+        <v>0.12</v>
       </c>
       <c r="E7">
         <v>588.6900000000001</v>
@@ -1519,46 +1507,46 @@
         <v>393.4</v>
       </c>
       <c r="G7">
-        <v>-31.68</v>
+        <v>-31.59</v>
       </c>
       <c r="H7">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="I7">
-        <v>-2.64</v>
+        <v>-3.94</v>
       </c>
       <c r="J7">
-        <v>-9.41</v>
+        <v>-7.65</v>
       </c>
       <c r="K7">
-        <v>-5.33</v>
+        <v>-5.08</v>
       </c>
       <c r="L7">
-        <v>-28.05</v>
+        <v>-28.14</v>
       </c>
       <c r="M7">
-        <v>-0.17</v>
+        <v>-0.48</v>
       </c>
       <c r="N7">
         <v>34</v>
       </c>
       <c r="O7">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P7">
-        <v>409.13</v>
+        <v>405.83</v>
       </c>
       <c r="Q7">
-        <v>417.82</v>
+        <v>415.71</v>
       </c>
       <c r="R7">
-        <v>425.77</v>
+        <v>425.52</v>
       </c>
       <c r="S7">
-        <v>470.79</v>
+        <v>470</v>
       </c>
       <c r="T7">
-        <v>-14.57</v>
+        <v>-14.32</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1573,43 +1561,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>37.31</v>
+        <v>37.8</v>
       </c>
       <c r="Z7">
-        <v>-6.33</v>
+        <v>-6.57</v>
       </c>
       <c r="AA7">
-        <v>-5.17</v>
+        <v>-5.45</v>
       </c>
       <c r="AB7">
-        <v>-1.16</v>
+        <v>-1.12</v>
       </c>
       <c r="AC7">
-        <v>31.7</v>
+        <v>18.53</v>
       </c>
       <c r="AD7">
-        <v>46.67</v>
+        <v>30.94</v>
       </c>
       <c r="AE7">
-        <v>8.91</v>
+        <v>8.82</v>
       </c>
       <c r="AF7">
-        <v>-50.77</v>
+        <v>-50.48</v>
       </c>
       <c r="AG7">
-        <v>440.66</v>
+        <v>435.59</v>
       </c>
       <c r="AH7">
-        <v>394.98</v>
+        <v>395.82</v>
       </c>
       <c r="AI7">
-        <v>430.79</v>
+        <v>425.32</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>24.37</v>
+        <v>26.67</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1620,10 +1608,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>613.65</v>
+        <v>614.95</v>
       </c>
       <c r="D8">
-        <v>-1.22</v>
+        <v>0.21</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1632,46 +1620,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-24.08</v>
+        <v>-23.92</v>
       </c>
       <c r="H8">
-        <v>31.19</v>
+        <v>31.47</v>
       </c>
       <c r="I8">
-        <v>-4.15</v>
+        <v>-4.47</v>
       </c>
       <c r="J8">
-        <v>-8.08</v>
+        <v>-7.8</v>
       </c>
       <c r="K8">
-        <v>-14.46</v>
+        <v>-17.32</v>
       </c>
       <c r="L8">
-        <v>3.6</v>
+        <v>4.07</v>
       </c>
       <c r="M8">
-        <v>-16.47</v>
+        <v>-16.08</v>
       </c>
       <c r="N8">
         <v>55</v>
       </c>
       <c r="O8">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P8">
-        <v>632.08</v>
+        <v>626.33</v>
       </c>
       <c r="Q8">
-        <v>648.8099999999999</v>
+        <v>646.54</v>
       </c>
       <c r="R8">
-        <v>678.47</v>
+        <v>676.4400000000001</v>
       </c>
       <c r="S8">
-        <v>613.97</v>
+        <v>613.92</v>
       </c>
       <c r="T8">
-        <v>-0.05</v>
+        <v>0.17</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1683,46 +1671,46 @@
         <v>47</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y8">
-        <v>28.71</v>
+        <v>29.7</v>
       </c>
       <c r="Z8">
-        <v>-13.36</v>
+        <v>-14.29</v>
       </c>
       <c r="AA8">
-        <v>-11.39</v>
+        <v>-11.97</v>
       </c>
       <c r="AB8">
-        <v>-1.98</v>
+        <v>-2.32</v>
       </c>
       <c r="AC8">
-        <v>1.27</v>
+        <v>1.77</v>
       </c>
       <c r="AD8">
-        <v>13.42</v>
+        <v>5.87</v>
       </c>
       <c r="AE8">
-        <v>16.38</v>
+        <v>16.69</v>
       </c>
       <c r="AF8">
-        <v>-25.49</v>
+        <v>-18.71</v>
       </c>
       <c r="AG8">
-        <v>676.51</v>
+        <v>677.51</v>
       </c>
       <c r="AH8">
-        <v>621.12</v>
+        <v>615.58</v>
       </c>
       <c r="AI8">
-        <v>668.99</v>
+        <v>664.6799999999999</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>21.75</v>
+        <v>24.93</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1733,10 +1721,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>194.38</v>
+        <v>191.25</v>
       </c>
       <c r="D9">
-        <v>0.95</v>
+        <v>-1.61</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1745,46 +1733,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-29.98</v>
+        <v>-31.11</v>
       </c>
       <c r="H9">
-        <v>12.81</v>
+        <v>11</v>
       </c>
       <c r="I9">
-        <v>-3.12</v>
+        <v>-5.27</v>
       </c>
       <c r="J9">
-        <v>2.14</v>
+        <v>0.35</v>
       </c>
       <c r="K9">
-        <v>2.21</v>
+        <v>1.05</v>
       </c>
       <c r="L9">
-        <v>-22.12</v>
+        <v>-23.96</v>
       </c>
       <c r="M9">
-        <v>-6.82</v>
+        <v>-7.15</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="P9">
-        <v>196.97</v>
+        <v>194.84</v>
       </c>
       <c r="Q9">
-        <v>194.15</v>
+        <v>194.03</v>
       </c>
       <c r="R9">
-        <v>190.14</v>
+        <v>190.29</v>
       </c>
       <c r="S9">
-        <v>204.62</v>
+        <v>204.21</v>
       </c>
       <c r="T9">
-        <v>-5</v>
+        <v>-6.34</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1799,34 +1787,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>52.04</v>
+        <v>47.1</v>
       </c>
       <c r="Z9">
-        <v>1.45</v>
+        <v>1.07</v>
       </c>
       <c r="AA9">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AB9">
-        <v>0.08</v>
+        <v>-0.24</v>
       </c>
       <c r="AC9">
-        <v>36.31</v>
+        <v>24.53</v>
       </c>
       <c r="AD9">
-        <v>54.57</v>
+        <v>37.26</v>
       </c>
       <c r="AE9">
-        <v>5.17</v>
+        <v>5.14</v>
       </c>
       <c r="AF9">
-        <v>-9.06</v>
+        <v>-15.7</v>
       </c>
       <c r="AG9">
-        <v>202.01</v>
+        <v>202</v>
       </c>
       <c r="AH9">
-        <v>186.29</v>
+        <v>186.07</v>
       </c>
       <c r="AI9">
         <v>185.88</v>
@@ -1835,7 +1823,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>27.28</v>
+        <v>25.81</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1846,37 +1834,37 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>71.42</v>
+        <v>70.84</v>
       </c>
       <c r="D10">
-        <v>-1.08</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E10">
-        <v>141.26</v>
+        <v>140.51</v>
       </c>
       <c r="F10">
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-49.44</v>
+        <v>-49.58</v>
       </c>
       <c r="H10">
-        <v>20.48</v>
+        <v>19.5</v>
       </c>
       <c r="I10">
-        <v>-4.48</v>
+        <v>-4.72</v>
       </c>
       <c r="J10">
-        <v>-7.71</v>
+        <v>-7.59</v>
       </c>
       <c r="K10">
-        <v>-12.85</v>
+        <v>-14.23</v>
       </c>
       <c r="L10">
-        <v>-49.25</v>
+        <v>-49.85</v>
       </c>
       <c r="M10">
-        <v>-1.34</v>
+        <v>-1.65</v>
       </c>
       <c r="N10">
         <v>12</v>
@@ -1885,19 +1873,19 @@
         <v>5</v>
       </c>
       <c r="P10">
-        <v>73.19</v>
+        <v>72.48999999999999</v>
       </c>
       <c r="Q10">
-        <v>75.3</v>
+        <v>74.98</v>
       </c>
       <c r="R10">
-        <v>77.8</v>
+        <v>77.59</v>
       </c>
       <c r="S10">
-        <v>81.15000000000001</v>
+        <v>81.06999999999999</v>
       </c>
       <c r="T10">
-        <v>-11.99</v>
+        <v>-12.62</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1912,43 +1900,43 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>28.3</v>
+        <v>26.69</v>
       </c>
       <c r="Z10">
-        <v>-1.4</v>
+        <v>-1.56</v>
       </c>
       <c r="AA10">
-        <v>-1.13</v>
+        <v>-1.21</v>
       </c>
       <c r="AB10">
-        <v>-0.27</v>
+        <v>-0.34</v>
       </c>
       <c r="AC10">
-        <v>13.21</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>31.24</v>
+        <v>14.65</v>
       </c>
       <c r="AE10">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AF10">
-        <v>-26.85</v>
+        <v>-7.2</v>
       </c>
       <c r="AG10">
-        <v>78.61</v>
+        <v>78.72</v>
       </c>
       <c r="AH10">
-        <v>71.98999999999999</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="AI10">
-        <v>78.19</v>
+        <v>76.63</v>
       </c>
       <c r="AJ10" t="s">
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>51.83</v>
+        <v>55.97</v>
       </c>
     </row>
   </sheetData>
@@ -2089,7 +2077,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2129,7 +2117,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2147,1348 +2135,1260 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>70</v>
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-8.99</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-8.529999999999999</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.46</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-5.96</v>
+        <v>-6.65</v>
       </c>
       <c r="D8" s="6">
-        <v>-8.99</v>
+        <v>-5.19</v>
       </c>
       <c r="E8" s="7">
-        <v>-3.03</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-5</v>
+        <v>-9.32</v>
       </c>
       <c r="D9" s="6">
-        <v>-6.65</v>
+        <v>-6.36</v>
       </c>
       <c r="E9" s="7">
-        <v>-1.65</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-12.15</v>
+        <v>-3.15</v>
       </c>
       <c r="D10" s="6">
-        <v>-9.32</v>
-      </c>
-      <c r="E10" s="8">
-        <v>2.83</v>
+        <v>-1.99</v>
+      </c>
+      <c r="E10" s="7">
+        <v>1.16</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-6.09</v>
+        <v>-4.35</v>
       </c>
       <c r="D11" s="6">
-        <v>-3.15</v>
-      </c>
-      <c r="E11" s="8">
-        <v>2.94</v>
+        <v>-1.07</v>
+      </c>
+      <c r="E11" s="7">
+        <v>3.28</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-6.3</v>
+        <v>-9.41</v>
       </c>
       <c r="D12" s="6">
-        <v>-4.35</v>
-      </c>
-      <c r="E12" s="8">
-        <v>1.95</v>
+        <v>-7.65</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1.76</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-7.18</v>
+        <v>-8.08</v>
       </c>
       <c r="D13" s="6">
-        <v>-9.41</v>
+        <v>-7.8</v>
       </c>
       <c r="E13" s="7">
-        <v>-2.23</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-4.64</v>
+        <v>2.14</v>
       </c>
       <c r="D14" s="6">
-        <v>-8.08</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-3.44</v>
+        <v>0.35</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-1.79</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>1.64</v>
+        <v>-7.71</v>
       </c>
       <c r="D15" s="6">
-        <v>2.14</v>
-      </c>
-      <c r="E15" s="8">
-        <v>0.5</v>
+        <v>-7.59</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.12</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-6.36</v>
+        <v>-2.57</v>
       </c>
       <c r="D16" s="6">
-        <v>-7.71</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-1.35</v>
+        <v>-4.89</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-2.32</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-1.88</v>
+        <v>-7.91</v>
       </c>
       <c r="D17" s="6">
-        <v>-2.57</v>
+        <v>-7.08</v>
       </c>
       <c r="E17" s="7">
-        <v>-0.6899999999999999</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-4.65</v>
+        <v>-4.89</v>
       </c>
       <c r="D18" s="6">
-        <v>-7.91</v>
+        <v>-0.55</v>
       </c>
       <c r="E18" s="7">
-        <v>-3.26</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-7.12</v>
+        <v>-3.24</v>
       </c>
       <c r="D19" s="6">
-        <v>-4.89</v>
-      </c>
-      <c r="E19" s="8">
-        <v>2.23</v>
+        <v>-1.11</v>
+      </c>
+      <c r="E19" s="7">
+        <v>2.13</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-4.72</v>
+        <v>-0.95</v>
       </c>
       <c r="D20" s="6">
-        <v>-3.24</v>
-      </c>
-      <c r="E20" s="8">
-        <v>1.48</v>
+        <v>0.24</v>
+      </c>
+      <c r="E20" s="7">
+        <v>1.19</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-2.8</v>
+        <v>-2.64</v>
       </c>
       <c r="D21" s="6">
-        <v>-0.95</v>
+        <v>-3.94</v>
       </c>
       <c r="E21" s="8">
-        <v>1.85</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-1.86</v>
+        <v>-4.15</v>
       </c>
       <c r="D22" s="6">
-        <v>-2.64</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-0.78</v>
+        <v>-4.47</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-0.32</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>-2.88</v>
+        <v>-3.12</v>
       </c>
       <c r="D23" s="6">
-        <v>-4.15</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-1.27</v>
+        <v>-5.27</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-2.15</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>-0.6899999999999999</v>
+        <v>-4.48</v>
       </c>
       <c r="D24" s="6">
-        <v>-3.12</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-2.43</v>
+        <v>-4.72</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-0.24</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>-3.91</v>
+        <v>-28.95</v>
       </c>
       <c r="D25" s="6">
-        <v>-4.48</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.57</v>
+        <v>-29.3</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>-28.61</v>
+        <v>25.93</v>
       </c>
       <c r="D26" s="6">
-        <v>-28.95</v>
+        <v>28.89</v>
       </c>
       <c r="E26" s="7">
-        <v>-0.34</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>25.9</v>
+        <v>37.33</v>
       </c>
       <c r="D27" s="6">
-        <v>25.93</v>
-      </c>
-      <c r="E27" s="8">
-        <v>0.03</v>
+        <v>41.87</v>
+      </c>
+      <c r="E27" s="7">
+        <v>4.54</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>30.46</v>
+        <v>25.77</v>
       </c>
       <c r="D28" s="6">
-        <v>37.33</v>
-      </c>
-      <c r="E28" s="8">
-        <v>6.87</v>
+        <v>27.95</v>
+      </c>
+      <c r="E28" s="7">
+        <v>2.18</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>21.62</v>
+        <v>71.75</v>
       </c>
       <c r="D29" s="6">
-        <v>25.77</v>
-      </c>
-      <c r="E29" s="8">
-        <v>4.15</v>
+        <v>72.90000000000001</v>
+      </c>
+      <c r="E29" s="7">
+        <v>1.15</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>67.2</v>
+        <v>-28.05</v>
       </c>
       <c r="D30" s="6">
-        <v>71.75</v>
+        <v>-28.14</v>
       </c>
       <c r="E30" s="8">
-        <v>4.55</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>-29.62</v>
+        <v>3.6</v>
       </c>
       <c r="D31" s="6">
-        <v>-28.05</v>
-      </c>
-      <c r="E31" s="8">
-        <v>1.57</v>
+        <v>4.07</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.47</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>-2.25</v>
+        <v>-22.12</v>
       </c>
       <c r="D32" s="6">
-        <v>3.6</v>
+        <v>-23.96</v>
       </c>
       <c r="E32" s="8">
-        <v>5.85</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>-23.58</v>
+        <v>-49.25</v>
       </c>
       <c r="D33" s="6">
-        <v>-22.12</v>
+        <v>-49.85</v>
       </c>
       <c r="E33" s="8">
-        <v>1.46</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>-49.15</v>
+        <v>-5.27</v>
       </c>
       <c r="D34" s="6">
-        <v>-49.25</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-0.1</v>
+        <v>-5.69</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-0.42</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-6.28</v>
+        <v>-2.07</v>
       </c>
       <c r="D35" s="6">
-        <v>-5.27</v>
+        <v>-2.68</v>
       </c>
       <c r="E35" s="8">
-        <v>1.01</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>-3.63</v>
+        <v>-11.38</v>
       </c>
       <c r="D36" s="6">
-        <v>-2.07</v>
-      </c>
-      <c r="E36" s="8">
-        <v>1.56</v>
+        <v>-8.94</v>
+      </c>
+      <c r="E36" s="7">
+        <v>2.44</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>-16.18</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="D37" s="6">
-        <v>-11.38</v>
-      </c>
-      <c r="E37" s="8">
-        <v>4.8</v>
+        <v>-6.21</v>
+      </c>
+      <c r="E37" s="7">
+        <v>2.07</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>-11.83</v>
+        <v>-12.11</v>
       </c>
       <c r="D38" s="6">
-        <v>-8.279999999999999</v>
-      </c>
-      <c r="E38" s="8">
-        <v>3.55</v>
+        <v>-9.710000000000001</v>
+      </c>
+      <c r="E38" s="7">
+        <v>2.4</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>-16.08</v>
+        <v>-5.33</v>
       </c>
       <c r="D39" s="6">
-        <v>-12.11</v>
-      </c>
-      <c r="E39" s="8">
-        <v>3.97</v>
+        <v>-5.08</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.25</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>-8.24</v>
+        <v>-14.46</v>
       </c>
       <c r="D40" s="6">
-        <v>-5.33</v>
+        <v>-17.32</v>
       </c>
       <c r="E40" s="8">
-        <v>2.91</v>
+        <v>-2.86</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>-15.81</v>
+        <v>2.21</v>
       </c>
       <c r="D41" s="6">
-        <v>-14.46</v>
+        <v>1.05</v>
       </c>
       <c r="E41" s="8">
-        <v>1.35</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="6">
-        <v>1</v>
+        <v>-12.85</v>
       </c>
       <c r="D42" s="6">
-        <v>2.21</v>
+        <v>-14.23</v>
       </c>
       <c r="E42" s="8">
-        <v>1.21</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C43" s="6">
-        <v>-12.21</v>
+        <v>-33.13</v>
       </c>
       <c r="D43" s="6">
-        <v>-12.85</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-0.64</v>
+        <v>-33.43</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-32.91</v>
+        <v>-10.84</v>
       </c>
       <c r="D44" s="6">
-        <v>-33.13</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="E44" s="7">
-        <v>-0.22</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-10.99</v>
+        <v>-21.16</v>
       </c>
       <c r="D45" s="6">
-        <v>-10.84</v>
-      </c>
-      <c r="E45" s="8">
-        <v>0.15</v>
+        <v>-19.23</v>
+      </c>
+      <c r="E45" s="7">
+        <v>1.93</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-24.28</v>
+        <v>-12.52</v>
       </c>
       <c r="D46" s="6">
-        <v>-21.16</v>
-      </c>
-      <c r="E46" s="8">
-        <v>3.12</v>
+        <v>-11.18</v>
+      </c>
+      <c r="E46" s="7">
+        <v>1.34</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-15.4</v>
+        <v>-17.9</v>
       </c>
       <c r="D47" s="6">
-        <v>-12.52</v>
-      </c>
-      <c r="E47" s="8">
-        <v>2.88</v>
+        <v>-16.56</v>
+      </c>
+      <c r="E47" s="7">
+        <v>1.34</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-20.45</v>
+        <v>-31.68</v>
       </c>
       <c r="D48" s="6">
-        <v>-17.9</v>
-      </c>
-      <c r="E48" s="8">
-        <v>2.55</v>
+        <v>-31.59</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0.09</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-31.86</v>
+        <v>-24.08</v>
       </c>
       <c r="D49" s="6">
-        <v>-31.68</v>
-      </c>
-      <c r="E49" s="8">
-        <v>0.18</v>
+        <v>-23.92</v>
+      </c>
+      <c r="E49" s="7">
+        <v>0.16</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-23.14</v>
+        <v>-29.98</v>
       </c>
       <c r="D50" s="6">
-        <v>-24.08</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-0.9399999999999999</v>
+        <v>-31.11</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-1.13</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="6">
-        <v>-30.64</v>
+        <v>-49.44</v>
       </c>
       <c r="D51" s="6">
-        <v>-29.98</v>
+        <v>-49.58</v>
       </c>
       <c r="E51" s="8">
-        <v>0.66</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C52" s="6">
-        <v>-48.89</v>
+        <v>1272.3</v>
       </c>
       <c r="D52" s="6">
-        <v>-49.44</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-0.55</v>
+        <v>1266.6</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-5.7</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>1276.5</v>
+        <v>2863.9</v>
       </c>
       <c r="D53" s="6">
-        <v>1272.3</v>
+        <v>2891.8</v>
       </c>
       <c r="E53" s="7">
-        <v>-4.2</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>2859.1</v>
+        <v>1265</v>
       </c>
       <c r="D54" s="6">
-        <v>2863.9</v>
-      </c>
-      <c r="E54" s="8">
-        <v>4.8</v>
+        <v>1296</v>
+      </c>
+      <c r="E54" s="7">
+        <v>31</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>1214.9</v>
+        <v>1647.5</v>
       </c>
       <c r="D55" s="6">
-        <v>1265</v>
-      </c>
-      <c r="E55" s="8">
-        <v>50.1</v>
+        <v>1672.7</v>
+      </c>
+      <c r="E55" s="7">
+        <v>25.2</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>1593.1</v>
+        <v>204.36</v>
       </c>
       <c r="D56" s="6">
-        <v>1647.5</v>
-      </c>
-      <c r="E56" s="8">
-        <v>54.4</v>
+        <v>207.7</v>
+      </c>
+      <c r="E56" s="7">
+        <v>3.34</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>198</v>
+        <v>402.2</v>
       </c>
       <c r="D57" s="6">
-        <v>204.36</v>
-      </c>
-      <c r="E57" s="8">
-        <v>6.36</v>
+        <v>402.7</v>
+      </c>
+      <c r="E57" s="7">
+        <v>0.5</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>401.15</v>
+        <v>613.65</v>
       </c>
       <c r="D58" s="6">
-        <v>402.2</v>
-      </c>
-      <c r="E58" s="8">
-        <v>1.05</v>
+        <v>614.95</v>
+      </c>
+      <c r="E58" s="7">
+        <v>1.3</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="6">
-        <v>621.2</v>
+        <v>194.38</v>
       </c>
       <c r="D59" s="6">
-        <v>613.65</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-7.55</v>
+        <v>191.25</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-3.13</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C60" s="6">
-        <v>192.55</v>
+        <v>71.42</v>
       </c>
       <c r="D60" s="6">
-        <v>194.38</v>
+        <v>70.84</v>
       </c>
       <c r="E60" s="8">
-        <v>1.83</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C61" s="6">
-        <v>72.2</v>
+        <v>35.07</v>
       </c>
       <c r="D61" s="6">
-        <v>71.42</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-0.78</v>
+        <v>33.94</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-1.13</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C62" s="6">
-        <v>34</v>
+        <v>35.78</v>
       </c>
       <c r="D62" s="6">
-        <v>23</v>
+        <v>38.77</v>
       </c>
       <c r="E62" s="7">
-        <v>-11</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C63" s="6">
-        <v>88</v>
+        <v>38.83</v>
       </c>
       <c r="D63" s="6">
-        <v>77</v>
+        <v>43.89</v>
       </c>
       <c r="E63" s="7">
-        <v>-11</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C64" s="6">
-        <v>77</v>
+        <v>41.74</v>
       </c>
       <c r="D64" s="6">
-        <v>88</v>
-      </c>
-      <c r="E64" s="8">
-        <v>11</v>
+        <v>45.97</v>
+      </c>
+      <c r="E64" s="7">
+        <v>4.23</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C65" s="6">
-        <v>23</v>
+        <v>45.16</v>
       </c>
       <c r="D65" s="6">
-        <v>34</v>
-      </c>
-      <c r="E65" s="8">
-        <v>11</v>
+        <v>49</v>
+      </c>
+      <c r="E65" s="7">
+        <v>3.84</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="6">
-        <v>35.89</v>
+        <v>37.31</v>
       </c>
       <c r="D66" s="6">
-        <v>35.07</v>
+        <v>37.8</v>
       </c>
       <c r="E66" s="7">
-        <v>-0.82</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="6">
-        <v>35.28</v>
+        <v>28.71</v>
       </c>
       <c r="D67" s="6">
-        <v>35.78</v>
-      </c>
-      <c r="E67" s="8">
-        <v>0.5</v>
+        <v>29.7</v>
+      </c>
+      <c r="E67" s="7">
+        <v>0.99</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="6">
-        <v>29.25</v>
+        <v>52.04</v>
       </c>
       <c r="D68" s="6">
-        <v>38.83</v>
+        <v>47.1</v>
       </c>
       <c r="E68" s="8">
-        <v>9.58</v>
+        <v>-4.94</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="6">
-        <v>30.9</v>
+        <v>28.3</v>
       </c>
       <c r="D69" s="6">
-        <v>41.74</v>
+        <v>26.69</v>
       </c>
       <c r="E69" s="8">
-        <v>10.84</v>
+        <v>-1.61</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C70" s="6">
-        <v>36.73</v>
+        <v>-36.99</v>
       </c>
       <c r="D70" s="6">
-        <v>45.16</v>
-      </c>
-      <c r="E70" s="8">
-        <v>8.43</v>
+        <v>4.04</v>
+      </c>
+      <c r="E70" s="7">
+        <v>41.03</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C71" s="6">
-        <v>36.33</v>
+        <v>134.1</v>
       </c>
       <c r="D71" s="6">
-        <v>37.31</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="E71" s="8">
-        <v>0.98</v>
+        <v>-142.47</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C72" s="6">
-        <v>31.06</v>
+        <v>184.74</v>
       </c>
       <c r="D72" s="6">
-        <v>28.71</v>
-      </c>
-      <c r="E72" s="7">
-        <v>-2.35</v>
+        <v>67.36</v>
+      </c>
+      <c r="E72" s="8">
+        <v>-117.38</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C73" s="6">
-        <v>49.14</v>
+        <v>78.73</v>
       </c>
       <c r="D73" s="6">
-        <v>52.04</v>
+        <v>5.85</v>
       </c>
       <c r="E73" s="8">
-        <v>2.9</v>
+        <v>-72.88</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C74" s="6">
-        <v>30.61</v>
+        <v>102.19</v>
       </c>
       <c r="D74" s="6">
-        <v>28.3</v>
-      </c>
-      <c r="E74" s="7">
-        <v>-2.31</v>
+        <v>-8.949999999999999</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-111.14</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="6">
-        <v>83.33</v>
+        <v>-50.77</v>
       </c>
       <c r="D75" s="6">
-        <v>-36.99</v>
+        <v>-50.48</v>
       </c>
       <c r="E75" s="7">
-        <v>-120.32</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="6">
-        <v>1067.96</v>
+        <v>-25.49</v>
       </c>
       <c r="D76" s="6">
-        <v>134.1</v>
+        <v>-18.71</v>
       </c>
       <c r="E76" s="7">
-        <v>-933.86</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="6">
-        <v>63.95</v>
+        <v>-9.06</v>
       </c>
       <c r="D77" s="6">
-        <v>184.74</v>
+        <v>-15.7</v>
       </c>
       <c r="E77" s="8">
-        <v>120.79</v>
+        <v>-6.64</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="6">
-        <v>383.28</v>
+        <v>-26.85</v>
       </c>
       <c r="D78" s="6">
-        <v>78.73</v>
+        <v>-7.2</v>
       </c>
       <c r="E78" s="7">
-        <v>-304.55</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>216.53</v>
-      </c>
-      <c r="D79" s="6">
-        <v>102.19</v>
-      </c>
-      <c r="E79" s="7">
-        <v>-114.34</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>-19.54</v>
-      </c>
-      <c r="D80" s="6">
-        <v>-50.77</v>
-      </c>
-      <c r="E80" s="7">
-        <v>-31.23</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="6">
-        <v>-18.52</v>
-      </c>
-      <c r="D81" s="6">
-        <v>-25.49</v>
-      </c>
-      <c r="E81" s="7">
-        <v>-6.97</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="6">
-        <v>-13.64</v>
-      </c>
-      <c r="D82" s="6">
-        <v>-9.06</v>
-      </c>
-      <c r="E82" s="8">
-        <v>4.58</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" s="6">
-        <v>10.97</v>
-      </c>
-      <c r="D83" s="6">
-        <v>-26.85</v>
-      </c>
-      <c r="E83" s="7">
-        <v>-37.82</v>
+        <v>19.65</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3512,28 +3412,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3541,22 +3441,22 @@
         <v>46</v>
       </c>
       <c r="B2" s="11">
-        <v>48.16</v>
+        <v>56.16</v>
       </c>
       <c r="C2" s="12">
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>38.1</v>
+        <v>39.2</v>
       </c>
       <c r="E2" s="11">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F2" s="11">
-        <v>-6.2</v>
+        <v>-5.1</v>
       </c>
       <c r="G2" s="11">
-        <v>-7.7</v>
+        <v>-7.6</v>
       </c>
       <c r="H2" s="11">
         <v>55.4</v>
@@ -3693,31 +3593,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.5811999999999999</v>
+        <v>0.5710000000000001</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1785</v>
+        <v>0.1792</v>
       </c>
       <c r="C2" s="14">
-        <v>0.129</v>
+        <v>0.1304</v>
       </c>
       <c r="D2" s="14">
-        <v>0.0322</v>
+        <v>0.0361</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.0017</v>
+        <v>-0.0048</v>
       </c>
       <c r="F2" s="14">
-        <v>-0.0134</v>
+        <v>-0.0165</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.0682</v>
+        <v>-0.07150000000000001</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.113</v>
+        <v>-0.1174</v>
       </c>
       <c r="I2" s="14">
-        <v>-0.1647</v>
+        <v>-0.1608</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,16 +196,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>52.0 → 47.1</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>52.0</t>
-  </si>
-  <si>
-    <t>47.1</t>
+    <t>46.0 → 51.1</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>46.0</t>
+  </si>
+  <si>
+    <t>51.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -291,14 +291,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -331,13 +331,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -930,10 +930,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1266.6</v>
+        <v>1272</v>
       </c>
       <c r="D2">
-        <v>-0.45</v>
+        <v>0.43</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -942,25 +942,25 @@
         <v>1247.38</v>
       </c>
       <c r="G2">
-        <v>-33.43</v>
+        <v>-33.15</v>
       </c>
       <c r="H2">
-        <v>1.54</v>
+        <v>1.97</v>
       </c>
       <c r="I2">
-        <v>-4.89</v>
+        <v>-2.95</v>
       </c>
       <c r="J2">
-        <v>-8.529999999999999</v>
+        <v>-8.75</v>
       </c>
       <c r="K2">
-        <v>-5.69</v>
+        <v>-3.79</v>
       </c>
       <c r="L2">
-        <v>-29.3</v>
+        <v>-29.64</v>
       </c>
       <c r="M2">
-        <v>-11.74</v>
+        <v>-11.63</v>
       </c>
       <c r="N2">
         <v>23</v>
@@ -969,19 +969,19 @@
         <v>20</v>
       </c>
       <c r="P2">
-        <v>1286.48</v>
+        <v>1278.76</v>
       </c>
       <c r="Q2">
-        <v>1315.3</v>
+        <v>1309.98</v>
       </c>
       <c r="R2">
-        <v>1344.61</v>
+        <v>1343.11</v>
       </c>
       <c r="S2">
-        <v>1497.55</v>
+        <v>1494.73</v>
       </c>
       <c r="T2">
-        <v>-15.42</v>
+        <v>-14.9</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -996,34 +996,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>33.94</v>
+        <v>36.05</v>
       </c>
       <c r="Z2">
-        <v>-19.68</v>
+        <v>-20.35</v>
       </c>
       <c r="AA2">
-        <v>-15.7</v>
+        <v>-16.63</v>
       </c>
       <c r="AB2">
-        <v>-3.98</v>
+        <v>-3.72</v>
       </c>
       <c r="AC2">
-        <v>10.83</v>
+        <v>11.15</v>
       </c>
       <c r="AD2">
-        <v>28.7</v>
+        <v>16.92</v>
       </c>
       <c r="AE2">
-        <v>23.84</v>
+        <v>23.09</v>
       </c>
       <c r="AF2">
-        <v>4.04</v>
+        <v>-30.87</v>
       </c>
       <c r="AG2">
-        <v>1374.34</v>
+        <v>1364.04</v>
       </c>
       <c r="AH2">
-        <v>1256.26</v>
+        <v>1255.92</v>
       </c>
       <c r="AI2">
         <v>1334.07</v>
@@ -1032,7 +1032,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>32.82</v>
+        <v>33.39</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,10 +1043,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2891.8</v>
+        <v>2901</v>
       </c>
       <c r="D3">
-        <v>0.97</v>
+        <v>0.32</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1055,46 +1055,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-9.970000000000001</v>
+        <v>-9.69</v>
       </c>
       <c r="H3">
-        <v>64.48999999999999</v>
+        <v>65.02</v>
       </c>
       <c r="I3">
-        <v>-7.08</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="J3">
-        <v>-5.19</v>
+        <v>-4.89</v>
       </c>
       <c r="K3">
-        <v>-2.68</v>
+        <v>-4.79</v>
       </c>
       <c r="L3">
-        <v>28.89</v>
+        <v>27.06</v>
       </c>
       <c r="M3">
-        <v>13.04</v>
+        <v>13.18</v>
       </c>
       <c r="N3">
         <v>77</v>
       </c>
       <c r="O3">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="P3">
-        <v>2990.46</v>
+        <v>2936.86</v>
       </c>
       <c r="Q3">
-        <v>3010.11</v>
+        <v>3003.86</v>
       </c>
       <c r="R3">
-        <v>3062.25</v>
+        <v>3058.87</v>
       </c>
       <c r="S3">
-        <v>2507.1</v>
+        <v>2509.3</v>
       </c>
       <c r="T3">
-        <v>15.34</v>
+        <v>15.61</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1109,34 +1109,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>38.77</v>
+        <v>39.76</v>
       </c>
       <c r="Z3">
-        <v>-21.84</v>
+        <v>-27.7</v>
       </c>
       <c r="AA3">
-        <v>-6.58</v>
+        <v>-10.8</v>
       </c>
       <c r="AB3">
-        <v>-15.26</v>
+        <v>-16.9</v>
       </c>
       <c r="AC3">
-        <v>4.25</v>
+        <v>9.02</v>
       </c>
       <c r="AD3">
-        <v>34.85</v>
+        <v>15.68</v>
       </c>
       <c r="AE3">
-        <v>81.79000000000001</v>
+        <v>78.47</v>
       </c>
       <c r="AF3">
-        <v>-8.369999999999999</v>
+        <v>-55.37</v>
       </c>
       <c r="AG3">
-        <v>3177.87</v>
+        <v>3178.31</v>
       </c>
       <c r="AH3">
-        <v>2842.34</v>
+        <v>2829.4</v>
       </c>
       <c r="AI3">
         <v>3113.12</v>
@@ -1145,7 +1145,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>38.95</v>
+        <v>39.34</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1156,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1296</v>
+        <v>1283.4</v>
       </c>
       <c r="D4">
-        <v>2.45</v>
+        <v>-0.97</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1168,46 +1168,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-19.23</v>
+        <v>-20.01</v>
       </c>
       <c r="H4">
-        <v>67.7</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="I4">
-        <v>-0.55</v>
+        <v>-3.39</v>
       </c>
       <c r="J4">
-        <v>-6.36</v>
+        <v>-7</v>
       </c>
       <c r="K4">
-        <v>-8.94</v>
+        <v>-15.88</v>
       </c>
       <c r="L4">
-        <v>41.87</v>
+        <v>37.77</v>
       </c>
       <c r="M4">
-        <v>3.61</v>
+        <v>3.49</v>
       </c>
       <c r="N4">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="O4">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="P4">
-        <v>1283.08</v>
+        <v>1274.06</v>
       </c>
       <c r="Q4">
-        <v>1319.26</v>
+        <v>1314.86</v>
       </c>
       <c r="R4">
-        <v>1416.17</v>
+        <v>1411.33</v>
       </c>
       <c r="S4">
-        <v>1174.66</v>
+        <v>1175.63</v>
       </c>
       <c r="T4">
-        <v>10.33</v>
+        <v>9.17</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1222,34 +1222,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>43.89</v>
+        <v>42.36</v>
       </c>
       <c r="Z4">
-        <v>-36.05</v>
+        <v>-34.72</v>
       </c>
       <c r="AA4">
-        <v>-36.3</v>
+        <v>-35.98</v>
       </c>
       <c r="AB4">
-        <v>0.25</v>
+        <v>1.26</v>
       </c>
       <c r="AC4">
-        <v>55.89</v>
+        <v>85.73</v>
       </c>
       <c r="AD4">
-        <v>54.45</v>
+        <v>63.32</v>
       </c>
       <c r="AE4">
-        <v>42.83</v>
+        <v>42.04</v>
       </c>
       <c r="AF4">
-        <v>67.36</v>
+        <v>-29.74</v>
       </c>
       <c r="AG4">
-        <v>1395.25</v>
+        <v>1388.26</v>
       </c>
       <c r="AH4">
-        <v>1243.27</v>
+        <v>1241.45</v>
       </c>
       <c r="AI4">
         <v>1367.12</v>
@@ -1258,7 +1258,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>28.41</v>
+        <v>26.93</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1269,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1672.7</v>
+        <v>1706.5</v>
       </c>
       <c r="D5">
-        <v>1.53</v>
+        <v>2.02</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1281,46 +1281,46 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-11.18</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="H5">
-        <v>28.85</v>
+        <v>31.46</v>
       </c>
       <c r="I5">
-        <v>-1.11</v>
+        <v>-0.44</v>
       </c>
       <c r="J5">
-        <v>-1.99</v>
+        <v>0.38</v>
       </c>
       <c r="K5">
-        <v>-6.21</v>
+        <v>-6.06</v>
       </c>
       <c r="L5">
-        <v>27.95</v>
+        <v>28.34</v>
       </c>
       <c r="M5">
-        <v>17.92</v>
+        <v>18.36</v>
       </c>
       <c r="N5">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="O5">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P5">
-        <v>1666.96</v>
+        <v>1665.46</v>
       </c>
       <c r="Q5">
-        <v>1681.1</v>
+        <v>1681.68</v>
       </c>
       <c r="R5">
-        <v>1749.13</v>
+        <v>1746.99</v>
       </c>
       <c r="S5">
-        <v>1599.82</v>
+        <v>1600.85</v>
       </c>
       <c r="T5">
-        <v>4.56</v>
+        <v>6.6</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1335,34 +1335,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>45.97</v>
+        <v>51.1</v>
       </c>
       <c r="Z5">
-        <v>-21.45</v>
+        <v>-17.41</v>
       </c>
       <c r="AA5">
-        <v>-21.79</v>
+        <v>-20.91</v>
       </c>
       <c r="AB5">
-        <v>0.34</v>
+        <v>3.5</v>
       </c>
       <c r="AC5">
-        <v>47.16</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="AD5">
-        <v>54.83</v>
+        <v>59.32</v>
       </c>
       <c r="AE5">
-        <v>39.44</v>
+        <v>39.34</v>
       </c>
       <c r="AF5">
-        <v>5.85</v>
+        <v>48.56</v>
       </c>
       <c r="AG5">
-        <v>1735.36</v>
+        <v>1736.79</v>
       </c>
       <c r="AH5">
-        <v>1626.85</v>
+        <v>1626.57</v>
       </c>
       <c r="AI5">
         <v>1757.42</v>
@@ -1371,7 +1371,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>32.83</v>
+        <v>29.04</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,58 +1382,58 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>207.7</v>
+        <v>208.29</v>
       </c>
       <c r="D6">
-        <v>1.63</v>
+        <v>0.28</v>
       </c>
       <c r="E6">
         <v>248.91</v>
       </c>
       <c r="F6">
-        <v>121.37</v>
+        <v>121.67</v>
       </c>
       <c r="G6">
-        <v>-16.56</v>
+        <v>-16.32</v>
       </c>
       <c r="H6">
-        <v>71.13</v>
+        <v>71.19</v>
       </c>
       <c r="I6">
-        <v>0.24</v>
+        <v>-3.12</v>
       </c>
       <c r="J6">
-        <v>-1.07</v>
+        <v>-0.33</v>
       </c>
       <c r="K6">
-        <v>-9.710000000000001</v>
+        <v>-10.45</v>
       </c>
       <c r="L6">
-        <v>72.90000000000001</v>
+        <v>71.62</v>
       </c>
       <c r="M6">
-        <v>57.1</v>
+        <v>58.8</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P6">
-        <v>207.54</v>
+        <v>206.2</v>
       </c>
       <c r="Q6">
-        <v>206.63</v>
+        <v>206.64</v>
       </c>
       <c r="R6">
-        <v>213.29</v>
+        <v>212.86</v>
       </c>
       <c r="S6">
-        <v>182.24</v>
+        <v>182.52</v>
       </c>
       <c r="T6">
-        <v>13.97</v>
+        <v>14.12</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1448,31 +1448,31 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>49</v>
+        <v>49.67</v>
       </c>
       <c r="Z6">
-        <v>-1.82</v>
+        <v>-1.55</v>
       </c>
       <c r="AA6">
-        <v>-2.29</v>
+        <v>-2.14</v>
       </c>
       <c r="AB6">
-        <v>0.47</v>
+        <v>0.59</v>
       </c>
       <c r="AC6">
-        <v>35.76</v>
+        <v>53.77</v>
       </c>
       <c r="AD6">
-        <v>47.46</v>
+        <v>44.4</v>
       </c>
       <c r="AE6">
-        <v>6.14</v>
+        <v>6.04</v>
       </c>
       <c r="AF6">
-        <v>-8.949999999999999</v>
+        <v>-13.56</v>
       </c>
       <c r="AG6">
-        <v>213.94</v>
+        <v>213.95</v>
       </c>
       <c r="AH6">
         <v>199.33</v>
@@ -1484,7 +1484,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>27.58</v>
+        <v>24.76</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1495,10 +1495,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>402.7</v>
+        <v>405</v>
       </c>
       <c r="D7">
-        <v>0.12</v>
+        <v>0.57</v>
       </c>
       <c r="E7">
         <v>588.6900000000001</v>
@@ -1507,46 +1507,46 @@
         <v>393.4</v>
       </c>
       <c r="G7">
-        <v>-31.59</v>
+        <v>-31.2</v>
       </c>
       <c r="H7">
-        <v>2.36</v>
+        <v>2.95</v>
       </c>
       <c r="I7">
-        <v>-3.94</v>
+        <v>-1.47</v>
       </c>
       <c r="J7">
-        <v>-7.65</v>
+        <v>-8.99</v>
       </c>
       <c r="K7">
-        <v>-5.08</v>
+        <v>-2.52</v>
       </c>
       <c r="L7">
-        <v>-28.14</v>
+        <v>-28.23</v>
       </c>
       <c r="M7">
-        <v>-0.48</v>
+        <v>-0.75</v>
       </c>
       <c r="N7">
         <v>34</v>
       </c>
       <c r="O7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P7">
-        <v>405.83</v>
+        <v>404.62</v>
       </c>
       <c r="Q7">
-        <v>415.71</v>
+        <v>414.13</v>
       </c>
       <c r="R7">
-        <v>425.52</v>
+        <v>425.09</v>
       </c>
       <c r="S7">
-        <v>470</v>
+        <v>469.24</v>
       </c>
       <c r="T7">
-        <v>-14.32</v>
+        <v>-13.69</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1561,34 +1561,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>37.8</v>
+        <v>40.13</v>
       </c>
       <c r="Z7">
-        <v>-6.57</v>
+        <v>-6.5</v>
       </c>
       <c r="AA7">
-        <v>-5.45</v>
+        <v>-5.66</v>
       </c>
       <c r="AB7">
-        <v>-1.12</v>
+        <v>-0.84</v>
       </c>
       <c r="AC7">
-        <v>18.53</v>
+        <v>28.56</v>
       </c>
       <c r="AD7">
-        <v>30.94</v>
+        <v>26.26</v>
       </c>
       <c r="AE7">
-        <v>8.82</v>
+        <v>8.42</v>
       </c>
       <c r="AF7">
-        <v>-50.48</v>
+        <v>-65.51000000000001</v>
       </c>
       <c r="AG7">
-        <v>435.59</v>
+        <v>431.96</v>
       </c>
       <c r="AH7">
-        <v>395.82</v>
+        <v>396.3</v>
       </c>
       <c r="AI7">
         <v>425.32</v>
@@ -1597,7 +1597,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>26.67</v>
+        <v>27.03</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1608,10 +1608,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>614.95</v>
+        <v>614.05</v>
       </c>
       <c r="D8">
-        <v>0.21</v>
+        <v>-0.15</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1620,22 +1620,22 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-23.92</v>
+        <v>-24.03</v>
       </c>
       <c r="H8">
-        <v>31.47</v>
+        <v>31.28</v>
       </c>
       <c r="I8">
-        <v>-4.47</v>
+        <v>-4.85</v>
       </c>
       <c r="J8">
-        <v>-7.8</v>
+        <v>-7.01</v>
       </c>
       <c r="K8">
-        <v>-17.32</v>
+        <v>-19.41</v>
       </c>
       <c r="L8">
-        <v>4.07</v>
+        <v>3.39</v>
       </c>
       <c r="M8">
         <v>-16.08</v>
@@ -1644,22 +1644,22 @@
         <v>55</v>
       </c>
       <c r="O8">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P8">
-        <v>626.33</v>
+        <v>620.0700000000001</v>
       </c>
       <c r="Q8">
-        <v>646.54</v>
+        <v>644.23</v>
       </c>
       <c r="R8">
-        <v>676.4400000000001</v>
+        <v>674.34</v>
       </c>
       <c r="S8">
-        <v>613.92</v>
+        <v>613.88</v>
       </c>
       <c r="T8">
-        <v>0.17</v>
+        <v>0.03</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1674,34 +1674,34 @@
         <v>2</v>
       </c>
       <c r="Y8">
-        <v>29.7</v>
+        <v>29.39</v>
       </c>
       <c r="Z8">
-        <v>-14.29</v>
+        <v>-14.93</v>
       </c>
       <c r="AA8">
-        <v>-11.97</v>
+        <v>-12.56</v>
       </c>
       <c r="AB8">
-        <v>-2.32</v>
+        <v>-2.37</v>
       </c>
       <c r="AC8">
-        <v>1.77</v>
+        <v>2.99</v>
       </c>
       <c r="AD8">
-        <v>5.87</v>
+        <v>2.01</v>
       </c>
       <c r="AE8">
-        <v>16.69</v>
+        <v>16.14</v>
       </c>
       <c r="AF8">
-        <v>-18.71</v>
+        <v>-49.55</v>
       </c>
       <c r="AG8">
-        <v>677.51</v>
+        <v>677.6900000000001</v>
       </c>
       <c r="AH8">
-        <v>615.58</v>
+        <v>610.78</v>
       </c>
       <c r="AI8">
         <v>664.6799999999999</v>
@@ -1710,7 +1710,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>24.93</v>
+        <v>27.69</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1721,10 +1721,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>191.25</v>
+        <v>190.79</v>
       </c>
       <c r="D9">
-        <v>-1.61</v>
+        <v>-0.24</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1733,46 +1733,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-31.11</v>
+        <v>-31.27</v>
       </c>
       <c r="H9">
-        <v>11</v>
+        <v>10.73</v>
       </c>
       <c r="I9">
-        <v>-5.27</v>
+        <v>-4.48</v>
       </c>
       <c r="J9">
-        <v>0.35</v>
+        <v>-1.42</v>
       </c>
       <c r="K9">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="L9">
-        <v>-23.96</v>
+        <v>-23.67</v>
       </c>
       <c r="M9">
-        <v>-7.15</v>
+        <v>-7.19</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P9">
-        <v>194.84</v>
+        <v>193.05</v>
       </c>
       <c r="Q9">
-        <v>194.03</v>
+        <v>193.7</v>
       </c>
       <c r="R9">
-        <v>190.29</v>
+        <v>190.45</v>
       </c>
       <c r="S9">
-        <v>204.21</v>
+        <v>203.78</v>
       </c>
       <c r="T9">
-        <v>-6.34</v>
+        <v>-6.38</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1787,34 +1787,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>47.1</v>
+        <v>46.4</v>
       </c>
       <c r="Z9">
-        <v>1.07</v>
+        <v>0.72</v>
       </c>
       <c r="AA9">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AB9">
-        <v>-0.24</v>
+        <v>-0.47</v>
       </c>
       <c r="AC9">
-        <v>24.53</v>
+        <v>20.67</v>
       </c>
       <c r="AD9">
-        <v>37.26</v>
+        <v>27.17</v>
       </c>
       <c r="AE9">
-        <v>5.14</v>
+        <v>4.99</v>
       </c>
       <c r="AF9">
-        <v>-15.7</v>
+        <v>-70.05</v>
       </c>
       <c r="AG9">
-        <v>202</v>
+        <v>201.63</v>
       </c>
       <c r="AH9">
-        <v>186.07</v>
+        <v>185.78</v>
       </c>
       <c r="AI9">
         <v>185.88</v>
@@ -1823,7 +1823,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>25.81</v>
+        <v>24.54</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1834,58 +1834,58 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>70.84</v>
+        <v>70.66</v>
       </c>
       <c r="D10">
-        <v>-0.8100000000000001</v>
+        <v>-0.25</v>
       </c>
       <c r="E10">
-        <v>140.51</v>
+        <v>139.7</v>
       </c>
       <c r="F10">
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-49.58</v>
+        <v>-49.42</v>
       </c>
       <c r="H10">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="I10">
-        <v>-4.72</v>
+        <v>-4.77</v>
       </c>
       <c r="J10">
-        <v>-7.59</v>
+        <v>-8.44</v>
       </c>
       <c r="K10">
-        <v>-14.23</v>
+        <v>-16.62</v>
       </c>
       <c r="L10">
-        <v>-49.85</v>
+        <v>-49.71</v>
       </c>
       <c r="M10">
-        <v>-1.65</v>
+        <v>-1.47</v>
       </c>
       <c r="N10">
         <v>12</v>
       </c>
       <c r="O10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P10">
-        <v>72.48999999999999</v>
+        <v>71.78</v>
       </c>
       <c r="Q10">
-        <v>74.98</v>
+        <v>74.64</v>
       </c>
       <c r="R10">
-        <v>77.59</v>
+        <v>77.38</v>
       </c>
       <c r="S10">
-        <v>81.06999999999999</v>
+        <v>80.98999999999999</v>
       </c>
       <c r="T10">
-        <v>-12.62</v>
+        <v>-12.75</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1900,34 +1900,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>26.69</v>
+        <v>26.19</v>
       </c>
       <c r="Z10">
-        <v>-1.56</v>
+        <v>-1.67</v>
       </c>
       <c r="AA10">
-        <v>-1.21</v>
+        <v>-1.31</v>
       </c>
       <c r="AB10">
-        <v>-0.34</v>
+        <v>-0.37</v>
       </c>
       <c r="AC10">
         <v>0</v>
       </c>
       <c r="AD10">
-        <v>14.65</v>
+        <v>4.4</v>
       </c>
       <c r="AE10">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AF10">
-        <v>-7.2</v>
+        <v>-43.43</v>
       </c>
       <c r="AG10">
-        <v>78.72</v>
+        <v>78.67</v>
       </c>
       <c r="AH10">
-        <v>71.23999999999999</v>
+        <v>70.62</v>
       </c>
       <c r="AI10">
         <v>76.63</v>
@@ -1936,7 +1936,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>55.97</v>
+        <v>54.52</v>
       </c>
     </row>
   </sheetData>
@@ -2077,7 +2077,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2117,7 +2117,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2169,13 +2169,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>-8.99</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="D7" s="6">
-        <v>-8.529999999999999</v>
+        <v>-8.75</v>
       </c>
       <c r="E7" s="7">
-        <v>0.46</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2186,13 +2186,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-6.65</v>
+        <v>-5.19</v>
       </c>
       <c r="D8" s="6">
-        <v>-5.19</v>
-      </c>
-      <c r="E8" s="7">
-        <v>1.46</v>
+        <v>-4.89</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0.3</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2203,13 +2203,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-9.32</v>
+        <v>-6.36</v>
       </c>
       <c r="D9" s="6">
-        <v>-6.36</v>
+        <v>-7</v>
       </c>
       <c r="E9" s="7">
-        <v>2.96</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2220,13 +2220,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-3.15</v>
+        <v>-1.99</v>
       </c>
       <c r="D10" s="6">
-        <v>-1.99</v>
-      </c>
-      <c r="E10" s="7">
-        <v>1.16</v>
+        <v>0.38</v>
+      </c>
+      <c r="E10" s="8">
+        <v>2.37</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2237,13 +2237,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-4.35</v>
+        <v>-1.07</v>
       </c>
       <c r="D11" s="6">
-        <v>-1.07</v>
-      </c>
-      <c r="E11" s="7">
-        <v>3.28</v>
+        <v>-0.33</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0.74</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2254,13 +2254,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-9.41</v>
+        <v>-7.65</v>
       </c>
       <c r="D12" s="6">
-        <v>-7.65</v>
+        <v>-8.99</v>
       </c>
       <c r="E12" s="7">
-        <v>1.76</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2271,13 +2271,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-8.08</v>
+        <v>-7.8</v>
       </c>
       <c r="D13" s="6">
-        <v>-7.8</v>
-      </c>
-      <c r="E13" s="7">
-        <v>0.28</v>
+        <v>-7.01</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.79</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2288,13 +2288,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>2.14</v>
+        <v>0.35</v>
       </c>
       <c r="D14" s="6">
-        <v>0.35</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-1.79</v>
+        <v>-1.42</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-1.77</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2305,13 +2305,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-7.71</v>
+        <v>-7.59</v>
       </c>
       <c r="D15" s="6">
-        <v>-7.59</v>
+        <v>-8.44</v>
       </c>
       <c r="E15" s="7">
-        <v>0.12</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2322,13 +2322,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-2.57</v>
+        <v>-4.89</v>
       </c>
       <c r="D16" s="6">
-        <v>-4.89</v>
+        <v>-2.95</v>
       </c>
       <c r="E16" s="8">
-        <v>-2.32</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2339,13 +2339,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-7.91</v>
+        <v>-7.08</v>
       </c>
       <c r="D17" s="6">
-        <v>-7.08</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="E17" s="7">
-        <v>0.83</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2356,13 +2356,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-4.89</v>
+        <v>-0.55</v>
       </c>
       <c r="D18" s="6">
-        <v>-0.55</v>
+        <v>-3.39</v>
       </c>
       <c r="E18" s="7">
-        <v>4.34</v>
+        <v>-2.84</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2373,13 +2373,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-3.24</v>
+        <v>-1.11</v>
       </c>
       <c r="D19" s="6">
-        <v>-1.11</v>
-      </c>
-      <c r="E19" s="7">
-        <v>2.13</v>
+        <v>-0.44</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0.67</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2390,13 +2390,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-0.95</v>
+        <v>0.24</v>
       </c>
       <c r="D20" s="6">
-        <v>0.24</v>
+        <v>-3.12</v>
       </c>
       <c r="E20" s="7">
-        <v>1.19</v>
+        <v>-3.36</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2407,13 +2407,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-2.64</v>
+        <v>-3.94</v>
       </c>
       <c r="D21" s="6">
-        <v>-3.94</v>
+        <v>-1.47</v>
       </c>
       <c r="E21" s="8">
-        <v>-1.3</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2424,13 +2424,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-4.15</v>
+        <v>-4.47</v>
       </c>
       <c r="D22" s="6">
-        <v>-4.47</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-0.32</v>
+        <v>-4.85</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-0.38</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2441,13 +2441,13 @@
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>-3.12</v>
+        <v>-5.27</v>
       </c>
       <c r="D23" s="6">
-        <v>-5.27</v>
+        <v>-4.48</v>
       </c>
       <c r="E23" s="8">
-        <v>-2.15</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2458,13 +2458,13 @@
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>-4.48</v>
+        <v>-4.72</v>
       </c>
       <c r="D24" s="6">
-        <v>-4.72</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-0.24</v>
+        <v>-4.77</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2475,13 +2475,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>-28.95</v>
+        <v>-29.3</v>
       </c>
       <c r="D25" s="6">
-        <v>-29.3</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-0.35</v>
+        <v>-29.64</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.34</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2492,13 +2492,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>25.93</v>
+        <v>28.89</v>
       </c>
       <c r="D26" s="6">
-        <v>28.89</v>
+        <v>27.06</v>
       </c>
       <c r="E26" s="7">
-        <v>2.96</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2509,13 +2509,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>37.33</v>
+        <v>41.87</v>
       </c>
       <c r="D27" s="6">
-        <v>41.87</v>
+        <v>37.77</v>
       </c>
       <c r="E27" s="7">
-        <v>4.54</v>
+        <v>-4.1</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2526,13 +2526,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>25.77</v>
+        <v>27.95</v>
       </c>
       <c r="D28" s="6">
-        <v>27.95</v>
-      </c>
-      <c r="E28" s="7">
-        <v>2.18</v>
+        <v>28.34</v>
+      </c>
+      <c r="E28" s="8">
+        <v>0.39</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2543,13 +2543,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>71.75</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D29" s="6">
-        <v>72.90000000000001</v>
+        <v>71.62</v>
       </c>
       <c r="E29" s="7">
-        <v>1.15</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2560,12 +2560,12 @@
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>-28.05</v>
+        <v>-28.14</v>
       </c>
       <c r="D30" s="6">
-        <v>-28.14</v>
-      </c>
-      <c r="E30" s="8">
+        <v>-28.23</v>
+      </c>
+      <c r="E30" s="7">
         <v>-0.09</v>
       </c>
     </row>
@@ -2577,13 +2577,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>3.6</v>
+        <v>4.07</v>
       </c>
       <c r="D31" s="6">
-        <v>4.07</v>
+        <v>3.39</v>
       </c>
       <c r="E31" s="7">
-        <v>0.47</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2594,13 +2594,13 @@
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>-22.12</v>
+        <v>-23.96</v>
       </c>
       <c r="D32" s="6">
-        <v>-23.96</v>
+        <v>-23.67</v>
       </c>
       <c r="E32" s="8">
-        <v>-1.84</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2611,13 +2611,13 @@
         <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>-49.25</v>
+        <v>-49.85</v>
       </c>
       <c r="D33" s="6">
-        <v>-49.85</v>
+        <v>-49.71</v>
       </c>
       <c r="E33" s="8">
-        <v>-0.6</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2628,13 +2628,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>-5.27</v>
+        <v>-5.69</v>
       </c>
       <c r="D34" s="6">
-        <v>-5.69</v>
+        <v>-3.79</v>
       </c>
       <c r="E34" s="8">
-        <v>-0.42</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2645,13 +2645,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-2.07</v>
+        <v>-2.68</v>
       </c>
       <c r="D35" s="6">
-        <v>-2.68</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-0.61</v>
+        <v>-4.79</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-2.11</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2662,13 +2662,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>-11.38</v>
+        <v>-8.94</v>
       </c>
       <c r="D36" s="6">
-        <v>-8.94</v>
+        <v>-15.88</v>
       </c>
       <c r="E36" s="7">
-        <v>2.44</v>
+        <v>-6.94</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2679,13 +2679,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>-8.279999999999999</v>
+        <v>-6.21</v>
       </c>
       <c r="D37" s="6">
-        <v>-6.21</v>
-      </c>
-      <c r="E37" s="7">
-        <v>2.07</v>
+        <v>-6.06</v>
+      </c>
+      <c r="E37" s="8">
+        <v>0.15</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2696,13 +2696,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>-12.11</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="D38" s="6">
-        <v>-9.710000000000001</v>
+        <v>-10.45</v>
       </c>
       <c r="E38" s="7">
-        <v>2.4</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2713,13 +2713,13 @@
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>-5.33</v>
+        <v>-5.08</v>
       </c>
       <c r="D39" s="6">
-        <v>-5.08</v>
-      </c>
-      <c r="E39" s="7">
-        <v>0.25</v>
+        <v>-2.52</v>
+      </c>
+      <c r="E39" s="8">
+        <v>2.56</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2730,13 +2730,13 @@
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>-14.46</v>
+        <v>-17.32</v>
       </c>
       <c r="D40" s="6">
-        <v>-17.32</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-2.86</v>
+        <v>-19.41</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-2.09</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2747,13 +2747,13 @@
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>2.21</v>
+        <v>1.05</v>
       </c>
       <c r="D41" s="6">
-        <v>1.05</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-1.16</v>
+        <v>1.01</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-0.04</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2764,13 +2764,13 @@
         <v>10</v>
       </c>
       <c r="C42" s="6">
-        <v>-12.85</v>
+        <v>-14.23</v>
       </c>
       <c r="D42" s="6">
-        <v>-14.23</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-1.38</v>
+        <v>-16.62</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-2.39</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2781,13 +2781,13 @@
         <v>6</v>
       </c>
       <c r="C43" s="6">
-        <v>-33.13</v>
+        <v>-33.43</v>
       </c>
       <c r="D43" s="6">
-        <v>-33.43</v>
+        <v>-33.15</v>
       </c>
       <c r="E43" s="8">
-        <v>-0.3</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2798,13 +2798,13 @@
         <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-10.84</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="D44" s="6">
-        <v>-9.970000000000001</v>
-      </c>
-      <c r="E44" s="7">
-        <v>0.87</v>
+        <v>-9.69</v>
+      </c>
+      <c r="E44" s="8">
+        <v>0.28</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2815,13 +2815,13 @@
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-21.16</v>
+        <v>-19.23</v>
       </c>
       <c r="D45" s="6">
-        <v>-19.23</v>
+        <v>-20.01</v>
       </c>
       <c r="E45" s="7">
-        <v>1.93</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2832,13 +2832,13 @@
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-12.52</v>
+        <v>-11.18</v>
       </c>
       <c r="D46" s="6">
-        <v>-11.18</v>
-      </c>
-      <c r="E46" s="7">
-        <v>1.34</v>
+        <v>-9.380000000000001</v>
+      </c>
+      <c r="E46" s="8">
+        <v>1.8</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2849,13 +2849,13 @@
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-17.9</v>
+        <v>-16.56</v>
       </c>
       <c r="D47" s="6">
-        <v>-16.56</v>
-      </c>
-      <c r="E47" s="7">
-        <v>1.34</v>
+        <v>-16.32</v>
+      </c>
+      <c r="E47" s="8">
+        <v>0.24</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2866,13 +2866,13 @@
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-31.68</v>
+        <v>-31.59</v>
       </c>
       <c r="D48" s="6">
-        <v>-31.59</v>
-      </c>
-      <c r="E48" s="7">
-        <v>0.09</v>
+        <v>-31.2</v>
+      </c>
+      <c r="E48" s="8">
+        <v>0.39</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2883,13 +2883,13 @@
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-24.08</v>
+        <v>-23.92</v>
       </c>
       <c r="D49" s="6">
-        <v>-23.92</v>
+        <v>-24.03</v>
       </c>
       <c r="E49" s="7">
-        <v>0.16</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2900,13 +2900,13 @@
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-29.98</v>
+        <v>-31.11</v>
       </c>
       <c r="D50" s="6">
-        <v>-31.11</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-1.13</v>
+        <v>-31.27</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2917,13 +2917,13 @@
         <v>6</v>
       </c>
       <c r="C51" s="6">
-        <v>-49.44</v>
+        <v>-49.58</v>
       </c>
       <c r="D51" s="6">
-        <v>-49.58</v>
+        <v>-49.42</v>
       </c>
       <c r="E51" s="8">
-        <v>-0.14</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2934,13 +2934,13 @@
         <v>2</v>
       </c>
       <c r="C52" s="6">
-        <v>1272.3</v>
+        <v>1266.6</v>
       </c>
       <c r="D52" s="6">
-        <v>1266.6</v>
+        <v>1272</v>
       </c>
       <c r="E52" s="8">
-        <v>-5.7</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2951,13 +2951,13 @@
         <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>2863.9</v>
+        <v>2891.8</v>
       </c>
       <c r="D53" s="6">
-        <v>2891.8</v>
-      </c>
-      <c r="E53" s="7">
-        <v>27.9</v>
+        <v>2901</v>
+      </c>
+      <c r="E53" s="8">
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2968,13 +2968,13 @@
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>1265</v>
+        <v>1296</v>
       </c>
       <c r="D54" s="6">
-        <v>1296</v>
+        <v>1283.4</v>
       </c>
       <c r="E54" s="7">
-        <v>31</v>
+        <v>-12.6</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>1647.5</v>
+        <v>1672.7</v>
       </c>
       <c r="D55" s="6">
-        <v>1672.7</v>
-      </c>
-      <c r="E55" s="7">
-        <v>25.2</v>
+        <v>1706.5</v>
+      </c>
+      <c r="E55" s="8">
+        <v>33.8</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -3002,13 +3002,13 @@
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>204.36</v>
+        <v>207.7</v>
       </c>
       <c r="D56" s="6">
-        <v>207.7</v>
-      </c>
-      <c r="E56" s="7">
-        <v>3.34</v>
+        <v>208.29</v>
+      </c>
+      <c r="E56" s="8">
+        <v>0.59</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -3019,13 +3019,13 @@
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>402.2</v>
+        <v>402.7</v>
       </c>
       <c r="D57" s="6">
-        <v>402.7</v>
-      </c>
-      <c r="E57" s="7">
-        <v>0.5</v>
+        <v>405</v>
+      </c>
+      <c r="E57" s="8">
+        <v>2.3</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -3036,13 +3036,13 @@
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>613.65</v>
+        <v>614.95</v>
       </c>
       <c r="D58" s="6">
-        <v>614.95</v>
+        <v>614.05</v>
       </c>
       <c r="E58" s="7">
-        <v>1.3</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -3053,13 +3053,13 @@
         <v>2</v>
       </c>
       <c r="C59" s="6">
-        <v>194.38</v>
+        <v>191.25</v>
       </c>
       <c r="D59" s="6">
-        <v>191.25</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-3.13</v>
+        <v>190.79</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-0.46</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -3070,319 +3070,353 @@
         <v>2</v>
       </c>
       <c r="C60" s="6">
-        <v>71.42</v>
+        <v>70.84</v>
       </c>
       <c r="D60" s="6">
-        <v>70.84</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-0.58</v>
+        <v>70.66</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C61" s="6">
-        <v>35.07</v>
+        <v>88</v>
       </c>
       <c r="D61" s="6">
-        <v>33.94</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-1.13</v>
+        <v>66</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-22</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C62" s="6">
-        <v>35.78</v>
+        <v>66</v>
       </c>
       <c r="D62" s="6">
-        <v>38.77</v>
-      </c>
-      <c r="E62" s="7">
-        <v>2.99</v>
+        <v>88</v>
+      </c>
+      <c r="E62" s="8">
+        <v>22</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C63" s="6">
-        <v>38.83</v>
+        <v>33.94</v>
       </c>
       <c r="D63" s="6">
-        <v>43.89</v>
-      </c>
-      <c r="E63" s="7">
-        <v>5.06</v>
+        <v>36.05</v>
+      </c>
+      <c r="E63" s="8">
+        <v>2.11</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C64" s="6">
-        <v>41.74</v>
+        <v>38.77</v>
       </c>
       <c r="D64" s="6">
-        <v>45.97</v>
-      </c>
-      <c r="E64" s="7">
-        <v>4.23</v>
+        <v>39.76</v>
+      </c>
+      <c r="E64" s="8">
+        <v>0.99</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C65" s="6">
-        <v>45.16</v>
+        <v>43.89</v>
       </c>
       <c r="D65" s="6">
-        <v>49</v>
+        <v>42.36</v>
       </c>
       <c r="E65" s="7">
-        <v>3.84</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="6">
-        <v>37.31</v>
+        <v>45.97</v>
       </c>
       <c r="D66" s="6">
-        <v>37.8</v>
-      </c>
-      <c r="E66" s="7">
-        <v>0.49</v>
+        <v>51.1</v>
+      </c>
+      <c r="E66" s="8">
+        <v>5.13</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="6">
-        <v>28.71</v>
+        <v>49</v>
       </c>
       <c r="D67" s="6">
-        <v>29.7</v>
-      </c>
-      <c r="E67" s="7">
-        <v>0.99</v>
+        <v>49.67</v>
+      </c>
+      <c r="E67" s="8">
+        <v>0.67</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="6">
-        <v>52.04</v>
+        <v>37.8</v>
       </c>
       <c r="D68" s="6">
-        <v>47.1</v>
+        <v>40.13</v>
       </c>
       <c r="E68" s="8">
-        <v>-4.94</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="6">
-        <v>28.3</v>
+        <v>29.7</v>
       </c>
       <c r="D69" s="6">
-        <v>26.69</v>
-      </c>
-      <c r="E69" s="8">
-        <v>-1.61</v>
+        <v>29.39</v>
+      </c>
+      <c r="E69" s="7">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C70" s="6">
-        <v>-36.99</v>
+        <v>47.1</v>
       </c>
       <c r="D70" s="6">
-        <v>4.04</v>
+        <v>46.4</v>
       </c>
       <c r="E70" s="7">
-        <v>41.03</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C71" s="6">
-        <v>134.1</v>
+        <v>26.69</v>
       </c>
       <c r="D71" s="6">
-        <v>-8.369999999999999</v>
-      </c>
-      <c r="E71" s="8">
-        <v>-142.47</v>
+        <v>26.19</v>
+      </c>
+      <c r="E71" s="7">
+        <v>-0.5</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C72" s="6">
-        <v>184.74</v>
+        <v>4.04</v>
       </c>
       <c r="D72" s="6">
-        <v>67.36</v>
-      </c>
-      <c r="E72" s="8">
-        <v>-117.38</v>
+        <v>-30.87</v>
+      </c>
+      <c r="E72" s="7">
+        <v>-34.91</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C73" s="6">
-        <v>78.73</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="D73" s="6">
-        <v>5.85</v>
-      </c>
-      <c r="E73" s="8">
-        <v>-72.88</v>
+        <v>-55.37</v>
+      </c>
+      <c r="E73" s="7">
+        <v>-47</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C74" s="6">
-        <v>102.19</v>
+        <v>67.36</v>
       </c>
       <c r="D74" s="6">
-        <v>-8.949999999999999</v>
-      </c>
-      <c r="E74" s="8">
-        <v>-111.14</v>
+        <v>-29.74</v>
+      </c>
+      <c r="E74" s="7">
+        <v>-97.09999999999999</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="6">
-        <v>-50.77</v>
+        <v>5.85</v>
       </c>
       <c r="D75" s="6">
-        <v>-50.48</v>
-      </c>
-      <c r="E75" s="7">
-        <v>0.29</v>
+        <v>48.56</v>
+      </c>
+      <c r="E75" s="8">
+        <v>42.71</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="6">
-        <v>-25.49</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="D76" s="6">
-        <v>-18.71</v>
+        <v>-13.56</v>
       </c>
       <c r="E76" s="7">
-        <v>6.78</v>
+        <v>-4.61</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="6">
-        <v>-9.06</v>
+        <v>-50.48</v>
       </c>
       <c r="D77" s="6">
-        <v>-15.7</v>
-      </c>
-      <c r="E77" s="8">
-        <v>-6.64</v>
+        <v>-65.51000000000001</v>
+      </c>
+      <c r="E77" s="7">
+        <v>-15.03</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="6">
-        <v>-26.85</v>
+        <v>-18.71</v>
       </c>
       <c r="D78" s="6">
+        <v>-49.55</v>
+      </c>
+      <c r="E78" s="7">
+        <v>-30.84</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
+        <v>-15.7</v>
+      </c>
+      <c r="D79" s="6">
+        <v>-70.05</v>
+      </c>
+      <c r="E79" s="7">
+        <v>-54.35</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="6">
         <v>-7.2</v>
       </c>
-      <c r="E78" s="7">
-        <v>19.65</v>
+      <c r="D80" s="6">
+        <v>-43.43</v>
+      </c>
+      <c r="E80" s="7">
+        <v>-36.23</v>
       </c>
     </row>
   </sheetData>
@@ -3447,16 +3481,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>39.2</v>
+        <v>40.1</v>
       </c>
       <c r="E2" s="11">
         <v>60</v>
       </c>
       <c r="F2" s="11">
-        <v>-5.1</v>
+        <v>-5.2</v>
       </c>
       <c r="G2" s="11">
-        <v>-7.6</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="H2" s="11">
         <v>55.4</v>
@@ -3593,28 +3627,28 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.5710000000000001</v>
+        <v>0.588</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1792</v>
+        <v>0.1836</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1304</v>
+        <v>0.1318</v>
       </c>
       <c r="D2" s="14">
-        <v>0.0361</v>
+        <v>0.0349</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.0048</v>
+        <v>-0.0075</v>
       </c>
       <c r="F2" s="14">
-        <v>-0.0165</v>
+        <v>-0.0147</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.07150000000000001</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.1174</v>
+        <v>-0.1163</v>
       </c>
       <c r="I2" s="14">
         <v>-0.1608</v>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,19 +193,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>46.0 → 51.1</t>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>26.2 → 47.4</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>46.0</t>
-  </si>
-  <si>
-    <t>51.1</t>
+    <t>26.2</t>
+  </si>
+  <si>
+    <t>47.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -417,8 +417,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -930,10 +930,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1272</v>
+        <v>1283.8</v>
       </c>
       <c r="D2">
-        <v>0.43</v>
+        <v>0.93</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -942,46 +942,46 @@
         <v>1247.38</v>
       </c>
       <c r="G2">
-        <v>-33.15</v>
+        <v>-32.53</v>
       </c>
       <c r="H2">
-        <v>1.97</v>
+        <v>2.92</v>
       </c>
       <c r="I2">
-        <v>-2.95</v>
+        <v>-1.73</v>
       </c>
       <c r="J2">
-        <v>-8.75</v>
+        <v>-6.86</v>
       </c>
       <c r="K2">
-        <v>-3.79</v>
+        <v>-2.16</v>
       </c>
       <c r="L2">
-        <v>-29.64</v>
+        <v>-29.13</v>
       </c>
       <c r="M2">
-        <v>-11.63</v>
+        <v>-11.51</v>
       </c>
       <c r="N2">
         <v>23</v>
       </c>
       <c r="O2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="P2">
-        <v>1278.76</v>
+        <v>1274.24</v>
       </c>
       <c r="Q2">
-        <v>1309.98</v>
+        <v>1306.03</v>
       </c>
       <c r="R2">
-        <v>1343.11</v>
+        <v>1342.03</v>
       </c>
       <c r="S2">
-        <v>1494.73</v>
+        <v>1492.01</v>
       </c>
       <c r="T2">
-        <v>-14.9</v>
+        <v>-13.95</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -996,34 +996,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>36.05</v>
+        <v>40.5</v>
       </c>
       <c r="Z2">
-        <v>-20.35</v>
+        <v>-19.7</v>
       </c>
       <c r="AA2">
-        <v>-16.63</v>
+        <v>-17.24</v>
       </c>
       <c r="AB2">
-        <v>-3.72</v>
+        <v>-2.46</v>
       </c>
       <c r="AC2">
-        <v>11.15</v>
+        <v>22.63</v>
       </c>
       <c r="AD2">
-        <v>16.92</v>
+        <v>14.87</v>
       </c>
       <c r="AE2">
-        <v>23.09</v>
+        <v>22.68</v>
       </c>
       <c r="AF2">
-        <v>-30.87</v>
+        <v>-18.96</v>
       </c>
       <c r="AG2">
-        <v>1364.04</v>
+        <v>1355.16</v>
       </c>
       <c r="AH2">
-        <v>1255.92</v>
+        <v>1256.9</v>
       </c>
       <c r="AI2">
         <v>1334.07</v>
@@ -1032,7 +1032,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>33.39</v>
+        <v>31.78</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,10 +1043,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2901</v>
+        <v>2938</v>
       </c>
       <c r="D3">
-        <v>0.32</v>
+        <v>1.28</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1055,46 +1055,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-9.69</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="H3">
-        <v>65.02</v>
+        <v>67.12</v>
       </c>
       <c r="I3">
-        <v>-8.460000000000001</v>
+        <v>-7.27</v>
       </c>
       <c r="J3">
-        <v>-4.89</v>
+        <v>-2.91</v>
       </c>
       <c r="K3">
-        <v>-4.79</v>
+        <v>-1.03</v>
       </c>
       <c r="L3">
-        <v>27.06</v>
+        <v>29.25</v>
       </c>
       <c r="M3">
-        <v>13.18</v>
+        <v>13.25</v>
       </c>
       <c r="N3">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="O3">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="P3">
-        <v>2936.86</v>
+        <v>2890.76</v>
       </c>
       <c r="Q3">
-        <v>3003.86</v>
+        <v>2999.76</v>
       </c>
       <c r="R3">
-        <v>3058.87</v>
+        <v>3056.87</v>
       </c>
       <c r="S3">
-        <v>2509.3</v>
+        <v>2511.81</v>
       </c>
       <c r="T3">
-        <v>15.61</v>
+        <v>16.97</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1109,34 +1109,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>39.76</v>
+        <v>43.72</v>
       </c>
       <c r="Z3">
-        <v>-27.7</v>
+        <v>-29.03</v>
       </c>
       <c r="AA3">
-        <v>-10.8</v>
+        <v>-14.45</v>
       </c>
       <c r="AB3">
-        <v>-16.9</v>
+        <v>-14.58</v>
       </c>
       <c r="AC3">
-        <v>9.02</v>
+        <v>17.46</v>
       </c>
       <c r="AD3">
-        <v>15.68</v>
+        <v>10.24</v>
       </c>
       <c r="AE3">
-        <v>78.47</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="AF3">
-        <v>-55.37</v>
+        <v>-41.93</v>
       </c>
       <c r="AG3">
-        <v>3178.31</v>
+        <v>3176.45</v>
       </c>
       <c r="AH3">
-        <v>2829.4</v>
+        <v>2823.06</v>
       </c>
       <c r="AI3">
         <v>3113.12</v>
@@ -1145,7 +1145,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>39.34</v>
+        <v>37.05</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1156,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1283.4</v>
+        <v>1301.3</v>
       </c>
       <c r="D4">
-        <v>-0.97</v>
+        <v>1.39</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1168,46 +1168,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-20.01</v>
+        <v>-18.9</v>
       </c>
       <c r="H4">
-        <v>66.06999999999999</v>
+        <v>68.39</v>
       </c>
       <c r="I4">
-        <v>-3.39</v>
+        <v>-0.74</v>
       </c>
       <c r="J4">
-        <v>-7</v>
+        <v>-5.12</v>
       </c>
       <c r="K4">
-        <v>-15.88</v>
+        <v>-12.69</v>
       </c>
       <c r="L4">
-        <v>37.77</v>
+        <v>39.35</v>
       </c>
       <c r="M4">
-        <v>3.49</v>
+        <v>3.18</v>
       </c>
       <c r="N4">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="O4">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="P4">
-        <v>1274.06</v>
+        <v>1272.12</v>
       </c>
       <c r="Q4">
-        <v>1314.86</v>
+        <v>1311.3</v>
       </c>
       <c r="R4">
-        <v>1411.33</v>
+        <v>1406.83</v>
       </c>
       <c r="S4">
-        <v>1175.63</v>
+        <v>1176.75</v>
       </c>
       <c r="T4">
-        <v>9.17</v>
+        <v>10.58</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1222,34 +1222,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>42.36</v>
+        <v>45.29</v>
       </c>
       <c r="Z4">
-        <v>-34.72</v>
+        <v>-31.85</v>
       </c>
       <c r="AA4">
-        <v>-35.98</v>
+        <v>-35.16</v>
       </c>
       <c r="AB4">
-        <v>1.26</v>
+        <v>3.3</v>
       </c>
       <c r="AC4">
-        <v>85.73</v>
+        <v>96.51000000000001</v>
       </c>
       <c r="AD4">
-        <v>63.32</v>
+        <v>79.38</v>
       </c>
       <c r="AE4">
-        <v>42.04</v>
+        <v>40.92</v>
       </c>
       <c r="AF4">
-        <v>-29.74</v>
+        <v>-52.26</v>
       </c>
       <c r="AG4">
-        <v>1388.26</v>
+        <v>1379.69</v>
       </c>
       <c r="AH4">
-        <v>1241.45</v>
+        <v>1242.91</v>
       </c>
       <c r="AI4">
         <v>1367.12</v>
@@ -1258,7 +1258,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>26.93</v>
+        <v>25.69</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1269,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1706.5</v>
+        <v>1707.3</v>
       </c>
       <c r="D5">
-        <v>2.02</v>
+        <v>0.05</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1281,46 +1281,46 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-9.380000000000001</v>
+        <v>-9.34</v>
       </c>
       <c r="H5">
-        <v>31.46</v>
+        <v>31.52</v>
       </c>
       <c r="I5">
-        <v>-0.44</v>
+        <v>-0.01</v>
       </c>
       <c r="J5">
-        <v>0.38</v>
+        <v>0.73</v>
       </c>
       <c r="K5">
-        <v>-6.06</v>
+        <v>-5.01</v>
       </c>
       <c r="L5">
-        <v>28.34</v>
+        <v>28.31</v>
       </c>
       <c r="M5">
-        <v>18.36</v>
+        <v>18.51</v>
       </c>
       <c r="N5">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="O5">
         <v>67</v>
       </c>
       <c r="P5">
-        <v>1665.46</v>
+        <v>1665.42</v>
       </c>
       <c r="Q5">
-        <v>1681.68</v>
+        <v>1682.37</v>
       </c>
       <c r="R5">
-        <v>1746.99</v>
+        <v>1745.22</v>
       </c>
       <c r="S5">
-        <v>1600.85</v>
+        <v>1601.94</v>
       </c>
       <c r="T5">
-        <v>6.6</v>
+        <v>6.58</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1335,34 +1335,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>51.1</v>
+        <v>51.22</v>
       </c>
       <c r="Z5">
-        <v>-17.41</v>
+        <v>-13.99</v>
       </c>
       <c r="AA5">
-        <v>-20.91</v>
+        <v>-19.53</v>
       </c>
       <c r="AB5">
-        <v>3.5</v>
+        <v>5.54</v>
       </c>
       <c r="AC5">
-        <v>79.06999999999999</v>
+        <v>92.91</v>
       </c>
       <c r="AD5">
-        <v>59.32</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="AE5">
-        <v>39.34</v>
+        <v>38.28</v>
       </c>
       <c r="AF5">
-        <v>48.56</v>
+        <v>-44.71</v>
       </c>
       <c r="AG5">
-        <v>1736.79</v>
+        <v>1738.44</v>
       </c>
       <c r="AH5">
-        <v>1626.57</v>
+        <v>1626.3</v>
       </c>
       <c r="AI5">
         <v>1757.42</v>
@@ -1371,7 +1371,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>29.04</v>
+        <v>25.18</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,58 +1382,58 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>208.29</v>
+        <v>207.2</v>
       </c>
       <c r="D6">
-        <v>0.28</v>
+        <v>-0.52</v>
       </c>
       <c r="E6">
         <v>248.91</v>
       </c>
       <c r="F6">
-        <v>121.67</v>
+        <v>121.74</v>
       </c>
       <c r="G6">
-        <v>-16.32</v>
+        <v>-16.76</v>
       </c>
       <c r="H6">
-        <v>71.19</v>
+        <v>70.2</v>
       </c>
       <c r="I6">
-        <v>-3.12</v>
+        <v>-2.55</v>
       </c>
       <c r="J6">
-        <v>-0.33</v>
+        <v>-0.44</v>
       </c>
       <c r="K6">
-        <v>-10.45</v>
+        <v>-8.26</v>
       </c>
       <c r="L6">
-        <v>71.62</v>
+        <v>70.3</v>
       </c>
       <c r="M6">
-        <v>58.8</v>
+        <v>60.35</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P6">
-        <v>206.2</v>
+        <v>205.11</v>
       </c>
       <c r="Q6">
-        <v>206.64</v>
+        <v>206.55</v>
       </c>
       <c r="R6">
-        <v>212.86</v>
+        <v>212.42</v>
       </c>
       <c r="S6">
-        <v>182.52</v>
+        <v>182.8</v>
       </c>
       <c r="T6">
-        <v>14.12</v>
+        <v>13.35</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1448,34 +1448,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>49.67</v>
+        <v>48.4</v>
       </c>
       <c r="Z6">
-        <v>-1.55</v>
+        <v>-1.41</v>
       </c>
       <c r="AA6">
-        <v>-2.14</v>
+        <v>-1.99</v>
       </c>
       <c r="AB6">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="AC6">
-        <v>53.77</v>
+        <v>57.19</v>
       </c>
       <c r="AD6">
-        <v>44.4</v>
+        <v>48.91</v>
       </c>
       <c r="AE6">
-        <v>6.04</v>
+        <v>5.76</v>
       </c>
       <c r="AF6">
-        <v>-13.56</v>
+        <v>-54.36</v>
       </c>
       <c r="AG6">
-        <v>213.95</v>
+        <v>213.78</v>
       </c>
       <c r="AH6">
-        <v>199.33</v>
+        <v>199.32</v>
       </c>
       <c r="AI6">
         <v>217.63</v>
@@ -1484,7 +1484,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>24.76</v>
+        <v>22.32</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1498,7 +1498,7 @@
         <v>405</v>
       </c>
       <c r="D7">
-        <v>0.57</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>588.6900000000001</v>
@@ -1513,19 +1513,19 @@
         <v>2.95</v>
       </c>
       <c r="I7">
-        <v>-1.47</v>
+        <v>-1.71</v>
       </c>
       <c r="J7">
-        <v>-8.99</v>
+        <v>-7.22</v>
       </c>
       <c r="K7">
-        <v>-2.52</v>
+        <v>-2</v>
       </c>
       <c r="L7">
-        <v>-28.23</v>
+        <v>-28.25</v>
       </c>
       <c r="M7">
-        <v>-0.75</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="N7">
         <v>34</v>
@@ -1534,19 +1534,19 @@
         <v>23</v>
       </c>
       <c r="P7">
-        <v>404.62</v>
+        <v>403.21</v>
       </c>
       <c r="Q7">
-        <v>414.13</v>
+        <v>412.68</v>
       </c>
       <c r="R7">
-        <v>425.09</v>
+        <v>424.71</v>
       </c>
       <c r="S7">
-        <v>469.24</v>
+        <v>468.49</v>
       </c>
       <c r="T7">
-        <v>-13.69</v>
+        <v>-13.55</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1564,31 +1564,31 @@
         <v>40.13</v>
       </c>
       <c r="Z7">
-        <v>-6.5</v>
+        <v>-6.37</v>
       </c>
       <c r="AA7">
-        <v>-5.66</v>
+        <v>-5.8</v>
       </c>
       <c r="AB7">
-        <v>-0.84</v>
+        <v>-0.57</v>
       </c>
       <c r="AC7">
-        <v>28.56</v>
+        <v>36</v>
       </c>
       <c r="AD7">
-        <v>26.26</v>
+        <v>27.7</v>
       </c>
       <c r="AE7">
-        <v>8.42</v>
+        <v>8.1</v>
       </c>
       <c r="AF7">
-        <v>-65.51000000000001</v>
+        <v>-66.84999999999999</v>
       </c>
       <c r="AG7">
-        <v>431.96</v>
+        <v>428.29</v>
       </c>
       <c r="AH7">
-        <v>396.3</v>
+        <v>397.07</v>
       </c>
       <c r="AI7">
         <v>425.32</v>
@@ -1597,7 +1597,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>27.03</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1608,10 +1608,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>614.05</v>
+        <v>612.35</v>
       </c>
       <c r="D8">
-        <v>-0.15</v>
+        <v>-0.28</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1620,46 +1620,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-24.03</v>
+        <v>-24.24</v>
       </c>
       <c r="H8">
-        <v>31.28</v>
+        <v>30.92</v>
       </c>
       <c r="I8">
-        <v>-4.85</v>
+        <v>-3.79</v>
       </c>
       <c r="J8">
-        <v>-7.01</v>
+        <v>-7.25</v>
       </c>
       <c r="K8">
-        <v>-19.41</v>
+        <v>-16.57</v>
       </c>
       <c r="L8">
-        <v>3.39</v>
+        <v>2.81</v>
       </c>
       <c r="M8">
-        <v>-16.08</v>
+        <v>-15.29</v>
       </c>
       <c r="N8">
         <v>55</v>
       </c>
       <c r="O8">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="P8">
-        <v>620.0700000000001</v>
+        <v>615.24</v>
       </c>
       <c r="Q8">
-        <v>644.23</v>
+        <v>641.97</v>
       </c>
       <c r="R8">
-        <v>674.34</v>
+        <v>672.1900000000001</v>
       </c>
       <c r="S8">
         <v>613.88</v>
       </c>
       <c r="T8">
-        <v>0.03</v>
+        <v>-0.25</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1671,46 +1671,46 @@
         <v>47</v>
       </c>
       <c r="X8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y8">
-        <v>29.39</v>
+        <v>28.8</v>
       </c>
       <c r="Z8">
-        <v>-14.93</v>
+        <v>-15.39</v>
       </c>
       <c r="AA8">
-        <v>-12.56</v>
+        <v>-13.13</v>
       </c>
       <c r="AB8">
-        <v>-2.37</v>
+        <v>-2.27</v>
       </c>
       <c r="AC8">
-        <v>2.99</v>
+        <v>3.14</v>
       </c>
       <c r="AD8">
-        <v>2.01</v>
+        <v>2.63</v>
       </c>
       <c r="AE8">
-        <v>16.14</v>
+        <v>15.65</v>
       </c>
       <c r="AF8">
-        <v>-49.55</v>
+        <v>-53.82</v>
       </c>
       <c r="AG8">
-        <v>677.6900000000001</v>
+        <v>677.67</v>
       </c>
       <c r="AH8">
-        <v>610.78</v>
+        <v>606.28</v>
       </c>
       <c r="AI8">
-        <v>664.6799999999999</v>
+        <v>662.12</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>27.69</v>
+        <v>30.48</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1721,10 +1721,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>190.79</v>
+        <v>187.29</v>
       </c>
       <c r="D9">
-        <v>-0.24</v>
+        <v>-1.83</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1733,46 +1733,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-31.27</v>
+        <v>-32.53</v>
       </c>
       <c r="H9">
-        <v>10.73</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I9">
-        <v>-4.48</v>
+        <v>-4.58</v>
       </c>
       <c r="J9">
-        <v>-1.42</v>
+        <v>-5.11</v>
       </c>
       <c r="K9">
-        <v>1.01</v>
+        <v>0.85</v>
       </c>
       <c r="L9">
-        <v>-23.67</v>
+        <v>-27.24</v>
       </c>
       <c r="M9">
-        <v>-7.19</v>
+        <v>-7.56</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P9">
-        <v>193.05</v>
+        <v>191.25</v>
       </c>
       <c r="Q9">
-        <v>193.7</v>
+        <v>193.19</v>
       </c>
       <c r="R9">
-        <v>190.45</v>
+        <v>190.55</v>
       </c>
       <c r="S9">
-        <v>203.78</v>
+        <v>203.38</v>
       </c>
       <c r="T9">
-        <v>-6.38</v>
+        <v>-7.91</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1787,34 +1787,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>46.4</v>
+        <v>41.39</v>
       </c>
       <c r="Z9">
-        <v>0.72</v>
+        <v>0.16</v>
       </c>
       <c r="AA9">
-        <v>1.19</v>
+        <v>0.99</v>
       </c>
       <c r="AB9">
-        <v>-0.47</v>
+        <v>-0.83</v>
       </c>
       <c r="AC9">
-        <v>20.67</v>
+        <v>8.82</v>
       </c>
       <c r="AD9">
-        <v>27.17</v>
+        <v>18.01</v>
       </c>
       <c r="AE9">
-        <v>4.99</v>
+        <v>5.04</v>
       </c>
       <c r="AF9">
-        <v>-70.05</v>
+        <v>-13.1</v>
       </c>
       <c r="AG9">
-        <v>201.63</v>
+        <v>201.4</v>
       </c>
       <c r="AH9">
-        <v>185.78</v>
+        <v>184.99</v>
       </c>
       <c r="AI9">
         <v>185.88</v>
@@ -1823,7 +1823,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>24.54</v>
+        <v>26.21</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1834,58 +1834,58 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>70.66</v>
+        <v>74.27</v>
       </c>
       <c r="D10">
-        <v>-0.25</v>
+        <v>5.11</v>
       </c>
       <c r="E10">
-        <v>139.7</v>
+        <v>131.73</v>
       </c>
       <c r="F10">
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-49.42</v>
+        <v>-43.62</v>
       </c>
       <c r="H10">
-        <v>19.2</v>
+        <v>25.29</v>
       </c>
       <c r="I10">
-        <v>-4.77</v>
+        <v>0.68</v>
       </c>
       <c r="J10">
-        <v>-8.44</v>
+        <v>-4.02</v>
       </c>
       <c r="K10">
-        <v>-16.62</v>
+        <v>-8.9</v>
       </c>
       <c r="L10">
-        <v>-49.71</v>
+        <v>-46.84</v>
       </c>
       <c r="M10">
-        <v>-1.47</v>
+        <v>0.25</v>
       </c>
       <c r="N10">
         <v>12</v>
       </c>
       <c r="O10">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P10">
-        <v>71.78</v>
+        <v>71.88</v>
       </c>
       <c r="Q10">
-        <v>74.64</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="R10">
-        <v>77.38</v>
+        <v>77.25</v>
       </c>
       <c r="S10">
-        <v>80.98999999999999</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="T10">
-        <v>-12.75</v>
+        <v>-8.23</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1900,31 +1900,31 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>26.19</v>
+        <v>47.42</v>
       </c>
       <c r="Z10">
-        <v>-1.67</v>
+        <v>-1.46</v>
       </c>
       <c r="AA10">
-        <v>-1.31</v>
+        <v>-1.34</v>
       </c>
       <c r="AB10">
-        <v>-0.37</v>
+        <v>-0.12</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>33.33</v>
       </c>
       <c r="AD10">
-        <v>4.4</v>
+        <v>11.11</v>
       </c>
       <c r="AE10">
-        <v>1.99</v>
+        <v>2.18</v>
       </c>
       <c r="AF10">
-        <v>-43.43</v>
+        <v>195.87</v>
       </c>
       <c r="AG10">
-        <v>78.67</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="AH10">
         <v>70.62</v>
@@ -1936,7 +1936,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>54.52</v>
+        <v>47.42</v>
       </c>
     </row>
   </sheetData>
@@ -2077,7 +2077,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2117,7 +2117,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2169,13 +2169,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>-8.529999999999999</v>
+        <v>-8.75</v>
       </c>
       <c r="D7" s="6">
-        <v>-8.75</v>
+        <v>-6.86</v>
       </c>
       <c r="E7" s="7">
-        <v>-0.22</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2186,13 +2186,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-5.19</v>
+        <v>-4.89</v>
       </c>
       <c r="D8" s="6">
-        <v>-4.89</v>
-      </c>
-      <c r="E8" s="8">
-        <v>0.3</v>
+        <v>-2.91</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.98</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2203,13 +2203,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-6.36</v>
+        <v>-7</v>
       </c>
       <c r="D9" s="6">
-        <v>-7</v>
+        <v>-5.12</v>
       </c>
       <c r="E9" s="7">
-        <v>-0.64</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2220,13 +2220,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-1.99</v>
+        <v>0.38</v>
       </c>
       <c r="D10" s="6">
-        <v>0.38</v>
-      </c>
-      <c r="E10" s="8">
-        <v>2.37</v>
+        <v>0.73</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.35</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2237,13 +2237,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-1.07</v>
+        <v>-0.33</v>
       </c>
       <c r="D11" s="6">
-        <v>-0.33</v>
+        <v>-0.44</v>
       </c>
       <c r="E11" s="8">
-        <v>0.74</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2254,13 +2254,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-7.65</v>
+        <v>-8.99</v>
       </c>
       <c r="D12" s="6">
-        <v>-8.99</v>
+        <v>-7.22</v>
       </c>
       <c r="E12" s="7">
-        <v>-1.34</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2271,13 +2271,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-7.8</v>
+        <v>-7.01</v>
       </c>
       <c r="D13" s="6">
-        <v>-7.01</v>
+        <v>-7.25</v>
       </c>
       <c r="E13" s="8">
-        <v>0.79</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2288,13 +2288,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>0.35</v>
+        <v>-1.42</v>
       </c>
       <c r="D14" s="6">
-        <v>-1.42</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-1.77</v>
+        <v>-5.11</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-3.69</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2305,13 +2305,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-7.59</v>
+        <v>-8.44</v>
       </c>
       <c r="D15" s="6">
-        <v>-8.44</v>
+        <v>-4.02</v>
       </c>
       <c r="E15" s="7">
-        <v>-0.85</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2322,13 +2322,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-4.89</v>
+        <v>-2.95</v>
       </c>
       <c r="D16" s="6">
-        <v>-2.95</v>
-      </c>
-      <c r="E16" s="8">
-        <v>1.94</v>
+        <v>-1.73</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1.22</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2339,13 +2339,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-7.08</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="D17" s="6">
-        <v>-8.460000000000001</v>
+        <v>-7.27</v>
       </c>
       <c r="E17" s="7">
-        <v>-1.38</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2356,13 +2356,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-0.55</v>
+        <v>-3.39</v>
       </c>
       <c r="D18" s="6">
-        <v>-3.39</v>
+        <v>-0.74</v>
       </c>
       <c r="E18" s="7">
-        <v>-2.84</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2373,13 +2373,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-1.11</v>
+        <v>-0.44</v>
       </c>
       <c r="D19" s="6">
-        <v>-0.44</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.67</v>
+        <v>-0.01</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.43</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2390,13 +2390,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>0.24</v>
+        <v>-3.12</v>
       </c>
       <c r="D20" s="6">
-        <v>-3.12</v>
+        <v>-2.55</v>
       </c>
       <c r="E20" s="7">
-        <v>-3.36</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2407,13 +2407,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-3.94</v>
+        <v>-1.47</v>
       </c>
       <c r="D21" s="6">
-        <v>-1.47</v>
+        <v>-1.71</v>
       </c>
       <c r="E21" s="8">
-        <v>2.47</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2424,13 +2424,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-4.47</v>
+        <v>-4.85</v>
       </c>
       <c r="D22" s="6">
-        <v>-4.85</v>
+        <v>-3.79</v>
       </c>
       <c r="E22" s="7">
-        <v>-0.38</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2441,13 +2441,13 @@
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>-5.27</v>
+        <v>-4.48</v>
       </c>
       <c r="D23" s="6">
-        <v>-4.48</v>
+        <v>-4.58</v>
       </c>
       <c r="E23" s="8">
-        <v>0.79</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2458,13 +2458,13 @@
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>-4.72</v>
+        <v>-4.77</v>
       </c>
       <c r="D24" s="6">
-        <v>-4.77</v>
+        <v>0.68</v>
       </c>
       <c r="E24" s="7">
-        <v>-0.05</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2475,13 +2475,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>-29.3</v>
+        <v>-29.64</v>
       </c>
       <c r="D25" s="6">
-        <v>-29.64</v>
+        <v>-29.13</v>
       </c>
       <c r="E25" s="7">
-        <v>-0.34</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2492,13 +2492,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>28.89</v>
+        <v>27.06</v>
       </c>
       <c r="D26" s="6">
-        <v>27.06</v>
+        <v>29.25</v>
       </c>
       <c r="E26" s="7">
-        <v>-1.83</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2509,13 +2509,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>41.87</v>
+        <v>37.77</v>
       </c>
       <c r="D27" s="6">
-        <v>37.77</v>
+        <v>39.35</v>
       </c>
       <c r="E27" s="7">
-        <v>-4.1</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2526,13 +2526,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>27.95</v>
+        <v>28.34</v>
       </c>
       <c r="D28" s="6">
-        <v>28.34</v>
+        <v>28.31</v>
       </c>
       <c r="E28" s="8">
-        <v>0.39</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2543,13 +2543,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>72.90000000000001</v>
+        <v>71.62</v>
       </c>
       <c r="D29" s="6">
-        <v>71.62</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-1.28</v>
+        <v>70.3</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-1.32</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2560,13 +2560,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>-28.14</v>
+        <v>-28.23</v>
       </c>
       <c r="D30" s="6">
-        <v>-28.23</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-0.09</v>
+        <v>-28.25</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2577,13 +2577,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>4.07</v>
+        <v>3.39</v>
       </c>
       <c r="D31" s="6">
-        <v>3.39</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-0.68</v>
+        <v>2.81</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-0.58</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2594,13 +2594,13 @@
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>-23.96</v>
+        <v>-23.67</v>
       </c>
       <c r="D32" s="6">
-        <v>-23.67</v>
+        <v>-27.24</v>
       </c>
       <c r="E32" s="8">
-        <v>0.29</v>
+        <v>-3.57</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2611,13 +2611,13 @@
         <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>-49.85</v>
+        <v>-49.71</v>
       </c>
       <c r="D33" s="6">
-        <v>-49.71</v>
-      </c>
-      <c r="E33" s="8">
-        <v>0.14</v>
+        <v>-46.84</v>
+      </c>
+      <c r="E33" s="7">
+        <v>2.87</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2628,13 +2628,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>-5.69</v>
+        <v>-3.79</v>
       </c>
       <c r="D34" s="6">
-        <v>-3.79</v>
-      </c>
-      <c r="E34" s="8">
-        <v>1.9</v>
+        <v>-2.16</v>
+      </c>
+      <c r="E34" s="7">
+        <v>1.63</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2645,13 +2645,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-2.68</v>
+        <v>-4.79</v>
       </c>
       <c r="D35" s="6">
-        <v>-4.79</v>
+        <v>-1.03</v>
       </c>
       <c r="E35" s="7">
-        <v>-2.11</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2662,13 +2662,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>-8.94</v>
+        <v>-15.88</v>
       </c>
       <c r="D36" s="6">
-        <v>-15.88</v>
+        <v>-12.69</v>
       </c>
       <c r="E36" s="7">
-        <v>-6.94</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2679,13 +2679,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>-6.21</v>
+        <v>-6.06</v>
       </c>
       <c r="D37" s="6">
-        <v>-6.06</v>
-      </c>
-      <c r="E37" s="8">
-        <v>0.15</v>
+        <v>-5.01</v>
+      </c>
+      <c r="E37" s="7">
+        <v>1.05</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2696,13 +2696,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>-9.710000000000001</v>
+        <v>-10.45</v>
       </c>
       <c r="D38" s="6">
-        <v>-10.45</v>
+        <v>-8.26</v>
       </c>
       <c r="E38" s="7">
-        <v>-0.74</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2713,13 +2713,13 @@
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>-5.08</v>
+        <v>-2.52</v>
       </c>
       <c r="D39" s="6">
-        <v>-2.52</v>
-      </c>
-      <c r="E39" s="8">
-        <v>2.56</v>
+        <v>-2</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.52</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2730,13 +2730,13 @@
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>-17.32</v>
+        <v>-19.41</v>
       </c>
       <c r="D40" s="6">
-        <v>-19.41</v>
+        <v>-16.57</v>
       </c>
       <c r="E40" s="7">
-        <v>-2.09</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2747,13 +2747,13 @@
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="D41" s="6">
-        <v>1.01</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-0.04</v>
+        <v>0.85</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2764,13 +2764,13 @@
         <v>10</v>
       </c>
       <c r="C42" s="6">
-        <v>-14.23</v>
+        <v>-16.62</v>
       </c>
       <c r="D42" s="6">
-        <v>-16.62</v>
+        <v>-8.9</v>
       </c>
       <c r="E42" s="7">
-        <v>-2.39</v>
+        <v>7.72</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2781,13 +2781,13 @@
         <v>6</v>
       </c>
       <c r="C43" s="6">
-        <v>-33.43</v>
+        <v>-33.15</v>
       </c>
       <c r="D43" s="6">
-        <v>-33.15</v>
-      </c>
-      <c r="E43" s="8">
-        <v>0.28</v>
+        <v>-32.53</v>
+      </c>
+      <c r="E43" s="7">
+        <v>0.62</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2798,13 +2798,13 @@
         <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-9.970000000000001</v>
+        <v>-9.69</v>
       </c>
       <c r="D44" s="6">
-        <v>-9.69</v>
-      </c>
-      <c r="E44" s="8">
-        <v>0.28</v>
+        <v>-8.529999999999999</v>
+      </c>
+      <c r="E44" s="7">
+        <v>1.16</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2815,13 +2815,13 @@
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-19.23</v>
+        <v>-20.01</v>
       </c>
       <c r="D45" s="6">
-        <v>-20.01</v>
+        <v>-18.9</v>
       </c>
       <c r="E45" s="7">
-        <v>-0.78</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2832,13 +2832,13 @@
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-11.18</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="D46" s="6">
-        <v>-9.380000000000001</v>
-      </c>
-      <c r="E46" s="8">
-        <v>1.8</v>
+        <v>-9.34</v>
+      </c>
+      <c r="E46" s="7">
+        <v>0.04</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2849,239 +2849,239 @@
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-16.56</v>
+        <v>-16.32</v>
       </c>
       <c r="D47" s="6">
-        <v>-16.32</v>
+        <v>-16.76</v>
       </c>
       <c r="E47" s="8">
-        <v>0.24</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-31.59</v>
+        <v>-24.03</v>
       </c>
       <c r="D48" s="6">
-        <v>-31.2</v>
+        <v>-24.24</v>
       </c>
       <c r="E48" s="8">
-        <v>0.39</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-23.92</v>
+        <v>-31.27</v>
       </c>
       <c r="D49" s="6">
-        <v>-24.03</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-0.11</v>
+        <v>-32.53</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-1.26</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-31.11</v>
+        <v>-49.42</v>
       </c>
       <c r="D50" s="6">
-        <v>-31.27</v>
+        <v>-43.62</v>
       </c>
       <c r="E50" s="7">
-        <v>-0.16</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C51" s="6">
-        <v>-49.58</v>
+        <v>1272</v>
       </c>
       <c r="D51" s="6">
-        <v>-49.42</v>
-      </c>
-      <c r="E51" s="8">
-        <v>0.16</v>
+        <v>1283.8</v>
+      </c>
+      <c r="E51" s="7">
+        <v>11.8</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C52" s="6">
-        <v>1266.6</v>
+        <v>2901</v>
       </c>
       <c r="D52" s="6">
-        <v>1272</v>
-      </c>
-      <c r="E52" s="8">
-        <v>5.4</v>
+        <v>2938</v>
+      </c>
+      <c r="E52" s="7">
+        <v>37</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>2891.8</v>
+        <v>1283.4</v>
       </c>
       <c r="D53" s="6">
-        <v>2901</v>
-      </c>
-      <c r="E53" s="8">
-        <v>9.199999999999999</v>
+        <v>1301.3</v>
+      </c>
+      <c r="E53" s="7">
+        <v>17.9</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>1296</v>
+        <v>1706.5</v>
       </c>
       <c r="D54" s="6">
-        <v>1283.4</v>
+        <v>1707.3</v>
       </c>
       <c r="E54" s="7">
-        <v>-12.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>1672.7</v>
+        <v>208.29</v>
       </c>
       <c r="D55" s="6">
-        <v>1706.5</v>
+        <v>207.2</v>
       </c>
       <c r="E55" s="8">
-        <v>33.8</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>207.7</v>
+        <v>614.05</v>
       </c>
       <c r="D56" s="6">
-        <v>208.29</v>
+        <v>612.35</v>
       </c>
       <c r="E56" s="8">
-        <v>0.59</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>402.7</v>
+        <v>190.79</v>
       </c>
       <c r="D57" s="6">
-        <v>405</v>
+        <v>187.29</v>
       </c>
       <c r="E57" s="8">
-        <v>2.3</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>614.95</v>
+        <v>70.66</v>
       </c>
       <c r="D58" s="6">
-        <v>614.05</v>
+        <v>74.27</v>
       </c>
       <c r="E58" s="7">
-        <v>-0.9</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C59" s="6">
-        <v>191.25</v>
+        <v>77</v>
       </c>
       <c r="D59" s="6">
-        <v>190.79</v>
+        <v>88</v>
       </c>
       <c r="E59" s="7">
-        <v>-0.46</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C60" s="6">
-        <v>70.84</v>
+        <v>66</v>
       </c>
       <c r="D60" s="6">
-        <v>70.66</v>
+        <v>77</v>
       </c>
       <c r="E60" s="7">
-        <v>-0.18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>13</v>
@@ -3092,331 +3092,297 @@
       <c r="D61" s="6">
         <v>66</v>
       </c>
-      <c r="E61" s="7">
+      <c r="E61" s="8">
         <v>-22</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C62" s="6">
-        <v>66</v>
+        <v>36.05</v>
       </c>
       <c r="D62" s="6">
-        <v>88</v>
-      </c>
-      <c r="E62" s="8">
-        <v>22</v>
+        <v>40.5</v>
+      </c>
+      <c r="E62" s="7">
+        <v>4.45</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C63" s="6">
-        <v>33.94</v>
+        <v>39.76</v>
       </c>
       <c r="D63" s="6">
-        <v>36.05</v>
-      </c>
-      <c r="E63" s="8">
-        <v>2.11</v>
+        <v>43.72</v>
+      </c>
+      <c r="E63" s="7">
+        <v>3.96</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C64" s="6">
-        <v>38.77</v>
+        <v>42.36</v>
       </c>
       <c r="D64" s="6">
-        <v>39.76</v>
-      </c>
-      <c r="E64" s="8">
-        <v>0.99</v>
+        <v>45.29</v>
+      </c>
+      <c r="E64" s="7">
+        <v>2.93</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C65" s="6">
-        <v>43.89</v>
+        <v>51.1</v>
       </c>
       <c r="D65" s="6">
-        <v>42.36</v>
+        <v>51.22</v>
       </c>
       <c r="E65" s="7">
-        <v>-1.53</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="6">
-        <v>45.97</v>
+        <v>49.67</v>
       </c>
       <c r="D66" s="6">
-        <v>51.1</v>
+        <v>48.4</v>
       </c>
       <c r="E66" s="8">
-        <v>5.13</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="6">
-        <v>49</v>
+        <v>29.39</v>
       </c>
       <c r="D67" s="6">
-        <v>49.67</v>
+        <v>28.8</v>
       </c>
       <c r="E67" s="8">
-        <v>0.67</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="6">
-        <v>37.8</v>
+        <v>46.4</v>
       </c>
       <c r="D68" s="6">
-        <v>40.13</v>
+        <v>41.39</v>
       </c>
       <c r="E68" s="8">
-        <v>2.33</v>
+        <v>-5.01</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="6">
-        <v>29.7</v>
+        <v>26.19</v>
       </c>
       <c r="D69" s="6">
-        <v>29.39</v>
+        <v>47.42</v>
       </c>
       <c r="E69" s="7">
-        <v>-0.31</v>
+        <v>21.23</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C70" s="6">
-        <v>47.1</v>
+        <v>-30.87</v>
       </c>
       <c r="D70" s="6">
-        <v>46.4</v>
+        <v>-18.96</v>
       </c>
       <c r="E70" s="7">
-        <v>-0.7</v>
+        <v>11.91</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C71" s="6">
-        <v>26.69</v>
+        <v>-55.37</v>
       </c>
       <c r="D71" s="6">
-        <v>26.19</v>
+        <v>-41.93</v>
       </c>
       <c r="E71" s="7">
-        <v>-0.5</v>
+        <v>13.44</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C72" s="6">
-        <v>4.04</v>
+        <v>-29.74</v>
       </c>
       <c r="D72" s="6">
-        <v>-30.87</v>
-      </c>
-      <c r="E72" s="7">
-        <v>-34.91</v>
+        <v>-52.26</v>
+      </c>
+      <c r="E72" s="8">
+        <v>-22.52</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C73" s="6">
-        <v>-8.369999999999999</v>
+        <v>48.56</v>
       </c>
       <c r="D73" s="6">
-        <v>-55.37</v>
-      </c>
-      <c r="E73" s="7">
-        <v>-47</v>
+        <v>-44.71</v>
+      </c>
+      <c r="E73" s="8">
+        <v>-93.27</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C74" s="6">
-        <v>67.36</v>
+        <v>-13.56</v>
       </c>
       <c r="D74" s="6">
-        <v>-29.74</v>
-      </c>
-      <c r="E74" s="7">
-        <v>-97.09999999999999</v>
+        <v>-54.36</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-40.8</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="6">
-        <v>5.85</v>
+        <v>-65.51000000000001</v>
       </c>
       <c r="D75" s="6">
-        <v>48.56</v>
+        <v>-66.84999999999999</v>
       </c>
       <c r="E75" s="8">
-        <v>42.71</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="6">
-        <v>-8.949999999999999</v>
+        <v>-49.55</v>
       </c>
       <c r="D76" s="6">
-        <v>-13.56</v>
-      </c>
-      <c r="E76" s="7">
-        <v>-4.61</v>
+        <v>-53.82</v>
+      </c>
+      <c r="E76" s="8">
+        <v>-4.27</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="6">
-        <v>-50.48</v>
+        <v>-70.05</v>
       </c>
       <c r="D77" s="6">
-        <v>-65.51000000000001</v>
+        <v>-13.1</v>
       </c>
       <c r="E77" s="7">
-        <v>-15.03</v>
+        <v>56.95</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="6">
-        <v>-18.71</v>
+        <v>-43.43</v>
       </c>
       <c r="D78" s="6">
-        <v>-49.55</v>
+        <v>195.87</v>
       </c>
       <c r="E78" s="7">
-        <v>-30.84</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>-15.7</v>
-      </c>
-      <c r="D79" s="6">
-        <v>-70.05</v>
-      </c>
-      <c r="E79" s="7">
-        <v>-54.35</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>-7.2</v>
-      </c>
-      <c r="D80" s="6">
-        <v>-43.43</v>
-      </c>
-      <c r="E80" s="7">
-        <v>-36.23</v>
+        <v>239.3</v>
       </c>
     </row>
   </sheetData>
@@ -3475,22 +3441,22 @@
         <v>46</v>
       </c>
       <c r="B2" s="11">
-        <v>56.16</v>
+        <v>48.16</v>
       </c>
       <c r="C2" s="12">
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>40.1</v>
+        <v>43</v>
       </c>
       <c r="E2" s="11">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F2" s="11">
-        <v>-5.2</v>
+        <v>-4.2</v>
       </c>
       <c r="G2" s="11">
-        <v>-8.699999999999999</v>
+        <v>-6.2</v>
       </c>
       <c r="H2" s="11">
         <v>55.4</v>
@@ -3610,10 +3576,10 @@
         <v>39</v>
       </c>
       <c r="E1" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" s="13" t="s">
         <v>42</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>45</v>
       </c>
       <c r="G1" s="13" t="s">
         <v>44</v>
@@ -3627,31 +3593,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.588</v>
+        <v>0.6035</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1836</v>
+        <v>0.1851</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1318</v>
+        <v>0.1325</v>
       </c>
       <c r="D2" s="14">
-        <v>0.0349</v>
+        <v>0.0318</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.0075</v>
+        <v>0.0025</v>
       </c>
       <c r="F2" s="14">
-        <v>-0.0147</v>
+        <v>-0.008100000000000001</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.07190000000000001</v>
+        <v>-0.0756</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.1163</v>
+        <v>-0.1151</v>
       </c>
       <c r="I2" s="14">
-        <v>-0.1608</v>
+        <v>-0.1529</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,19 +193,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>26.2 → 47.4</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>26.2</t>
-  </si>
-  <si>
-    <t>47.4</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>51.2 → 49.1</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>51.2</t>
+  </si>
+  <si>
+    <t>49.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -291,14 +291,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -331,13 +331,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -930,10 +930,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1283.8</v>
+        <v>1268.7</v>
       </c>
       <c r="D2">
-        <v>0.93</v>
+        <v>-1.18</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -942,46 +942,46 @@
         <v>1247.38</v>
       </c>
       <c r="G2">
-        <v>-32.53</v>
+        <v>-33.32</v>
       </c>
       <c r="H2">
-        <v>2.92</v>
+        <v>1.71</v>
       </c>
       <c r="I2">
-        <v>-1.73</v>
+        <v>-0.61</v>
       </c>
       <c r="J2">
-        <v>-6.86</v>
+        <v>-6.9</v>
       </c>
       <c r="K2">
-        <v>-2.16</v>
+        <v>-3.67</v>
       </c>
       <c r="L2">
-        <v>-29.13</v>
+        <v>-30.77</v>
       </c>
       <c r="M2">
-        <v>-11.51</v>
+        <v>-11.78</v>
       </c>
       <c r="N2">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="O2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="P2">
-        <v>1274.24</v>
+        <v>1272.68</v>
       </c>
       <c r="Q2">
-        <v>1306.03</v>
+        <v>1301.59</v>
       </c>
       <c r="R2">
-        <v>1342.03</v>
+        <v>1340.74</v>
       </c>
       <c r="S2">
-        <v>1492.01</v>
+        <v>1489.22</v>
       </c>
       <c r="T2">
-        <v>-13.95</v>
+        <v>-14.81</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -996,34 +996,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>40.5</v>
+        <v>36.95</v>
       </c>
       <c r="Z2">
-        <v>-19.7</v>
+        <v>-20.18</v>
       </c>
       <c r="AA2">
-        <v>-17.24</v>
+        <v>-17.83</v>
       </c>
       <c r="AB2">
-        <v>-2.46</v>
+        <v>-2.35</v>
       </c>
       <c r="AC2">
-        <v>22.63</v>
+        <v>28.99</v>
       </c>
       <c r="AD2">
-        <v>14.87</v>
+        <v>20.93</v>
       </c>
       <c r="AE2">
-        <v>22.68</v>
+        <v>22.7</v>
       </c>
       <c r="AF2">
-        <v>-18.96</v>
+        <v>-26.19</v>
       </c>
       <c r="AG2">
-        <v>1355.16</v>
+        <v>1347.02</v>
       </c>
       <c r="AH2">
-        <v>1256.9</v>
+        <v>1256.15</v>
       </c>
       <c r="AI2">
         <v>1334.07</v>
@@ -1032,7 +1032,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>31.78</v>
+        <v>31.27</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,10 +1043,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2938</v>
+        <v>2950</v>
       </c>
       <c r="D3">
-        <v>1.28</v>
+        <v>0.41</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1055,25 +1055,25 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-8.529999999999999</v>
+        <v>-8.16</v>
       </c>
       <c r="H3">
-        <v>67.12</v>
+        <v>67.8</v>
       </c>
       <c r="I3">
-        <v>-7.27</v>
+        <v>3.18</v>
       </c>
       <c r="J3">
-        <v>-2.91</v>
+        <v>-2.32</v>
       </c>
       <c r="K3">
-        <v>-1.03</v>
+        <v>-0.96</v>
       </c>
       <c r="L3">
-        <v>29.25</v>
+        <v>28.95</v>
       </c>
       <c r="M3">
-        <v>13.25</v>
+        <v>13.67</v>
       </c>
       <c r="N3">
         <v>88</v>
@@ -1082,19 +1082,19 @@
         <v>69</v>
       </c>
       <c r="P3">
-        <v>2890.76</v>
+        <v>2908.94</v>
       </c>
       <c r="Q3">
-        <v>2999.76</v>
+        <v>2996.76</v>
       </c>
       <c r="R3">
-        <v>3056.87</v>
+        <v>3056.62</v>
       </c>
       <c r="S3">
-        <v>2511.81</v>
+        <v>2514.4</v>
       </c>
       <c r="T3">
-        <v>16.97</v>
+        <v>17.32</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1109,34 +1109,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>43.72</v>
+        <v>44.98</v>
       </c>
       <c r="Z3">
-        <v>-29.03</v>
+        <v>-28.78</v>
       </c>
       <c r="AA3">
-        <v>-14.45</v>
+        <v>-17.31</v>
       </c>
       <c r="AB3">
-        <v>-14.58</v>
+        <v>-11.47</v>
       </c>
       <c r="AC3">
-        <v>17.46</v>
+        <v>24.08</v>
       </c>
       <c r="AD3">
-        <v>10.24</v>
+        <v>16.85</v>
       </c>
       <c r="AE3">
-        <v>78.73999999999999</v>
+        <v>76.39</v>
       </c>
       <c r="AF3">
-        <v>-41.93</v>
+        <v>-46.57</v>
       </c>
       <c r="AG3">
-        <v>3176.45</v>
+        <v>3174.75</v>
       </c>
       <c r="AH3">
-        <v>2823.06</v>
+        <v>2818.76</v>
       </c>
       <c r="AI3">
         <v>3113.12</v>
@@ -1145,7 +1145,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>37.05</v>
+        <v>35.06</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1156,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1301.3</v>
+        <v>1288</v>
       </c>
       <c r="D4">
-        <v>1.39</v>
+        <v>-1.02</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1168,46 +1168,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-18.9</v>
+        <v>-19.73</v>
       </c>
       <c r="H4">
-        <v>68.39</v>
+        <v>66.67</v>
       </c>
       <c r="I4">
-        <v>-0.74</v>
+        <v>6.02</v>
       </c>
       <c r="J4">
-        <v>-5.12</v>
+        <v>-6.15</v>
       </c>
       <c r="K4">
-        <v>-12.69</v>
+        <v>-16.06</v>
       </c>
       <c r="L4">
-        <v>39.35</v>
+        <v>37.65</v>
       </c>
       <c r="M4">
-        <v>3.18</v>
+        <v>3.02</v>
       </c>
       <c r="N4">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="O4">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="P4">
-        <v>1272.12</v>
+        <v>1286.74</v>
       </c>
       <c r="Q4">
-        <v>1311.3</v>
+        <v>1307.25</v>
       </c>
       <c r="R4">
-        <v>1406.83</v>
+        <v>1402.54</v>
       </c>
       <c r="S4">
-        <v>1176.75</v>
+        <v>1177.84</v>
       </c>
       <c r="T4">
-        <v>10.58</v>
+        <v>9.35</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1222,34 +1222,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>45.29</v>
+        <v>43.52</v>
       </c>
       <c r="Z4">
-        <v>-31.85</v>
+        <v>-30.3</v>
       </c>
       <c r="AA4">
-        <v>-35.16</v>
+        <v>-34.19</v>
       </c>
       <c r="AB4">
-        <v>3.3</v>
+        <v>3.88</v>
       </c>
       <c r="AC4">
-        <v>96.51000000000001</v>
+        <v>92.83</v>
       </c>
       <c r="AD4">
-        <v>79.38</v>
+        <v>91.69</v>
       </c>
       <c r="AE4">
-        <v>40.92</v>
+        <v>39.76</v>
       </c>
       <c r="AF4">
-        <v>-52.26</v>
+        <v>-57.33</v>
       </c>
       <c r="AG4">
-        <v>1379.69</v>
+        <v>1370.67</v>
       </c>
       <c r="AH4">
-        <v>1242.91</v>
+        <v>1243.83</v>
       </c>
       <c r="AI4">
         <v>1367.12</v>
@@ -1258,7 +1258,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>25.69</v>
+        <v>23.84</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1269,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1707.3</v>
+        <v>1694.3</v>
       </c>
       <c r="D5">
-        <v>0.05</v>
+        <v>-0.76</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1281,46 +1281,46 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-9.34</v>
+        <v>-10.03</v>
       </c>
       <c r="H5">
-        <v>31.52</v>
+        <v>30.52</v>
       </c>
       <c r="I5">
-        <v>-0.01</v>
+        <v>6.35</v>
       </c>
       <c r="J5">
-        <v>0.73</v>
+        <v>0.05</v>
       </c>
       <c r="K5">
-        <v>-5.01</v>
+        <v>-6.84</v>
       </c>
       <c r="L5">
-        <v>28.31</v>
+        <v>27.7</v>
       </c>
       <c r="M5">
-        <v>18.51</v>
+        <v>18.48</v>
       </c>
       <c r="N5">
+        <v>77</v>
+      </c>
+      <c r="O5">
         <v>66</v>
       </c>
-      <c r="O5">
-        <v>67</v>
-      </c>
       <c r="P5">
-        <v>1665.42</v>
+        <v>1685.66</v>
       </c>
       <c r="Q5">
-        <v>1682.37</v>
+        <v>1683.03</v>
       </c>
       <c r="R5">
-        <v>1745.22</v>
+        <v>1743.58</v>
       </c>
       <c r="S5">
-        <v>1601.94</v>
+        <v>1603.02</v>
       </c>
       <c r="T5">
-        <v>6.58</v>
+        <v>5.69</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1335,34 +1335,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>51.22</v>
+        <v>49.14</v>
       </c>
       <c r="Z5">
-        <v>-13.99</v>
+        <v>-12.18</v>
       </c>
       <c r="AA5">
-        <v>-19.53</v>
+        <v>-18.06</v>
       </c>
       <c r="AB5">
-        <v>5.54</v>
+        <v>5.88</v>
       </c>
       <c r="AC5">
-        <v>92.91</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AD5">
-        <v>73.04000000000001</v>
+        <v>89.52</v>
       </c>
       <c r="AE5">
-        <v>38.28</v>
+        <v>37.73</v>
       </c>
       <c r="AF5">
-        <v>-44.71</v>
+        <v>-49.33</v>
       </c>
       <c r="AG5">
-        <v>1738.44</v>
+        <v>1739.35</v>
       </c>
       <c r="AH5">
-        <v>1626.3</v>
+        <v>1626.72</v>
       </c>
       <c r="AI5">
         <v>1757.42</v>
@@ -1371,7 +1371,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>25.18</v>
+        <v>22.49</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,10 +1382,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>207.2</v>
+        <v>204.49</v>
       </c>
       <c r="D6">
-        <v>-0.52</v>
+        <v>-1.31</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1394,46 +1394,46 @@
         <v>121.74</v>
       </c>
       <c r="G6">
-        <v>-16.76</v>
+        <v>-17.85</v>
       </c>
       <c r="H6">
-        <v>70.2</v>
+        <v>67.97</v>
       </c>
       <c r="I6">
-        <v>-2.55</v>
+        <v>3.28</v>
       </c>
       <c r="J6">
-        <v>-0.44</v>
+        <v>-2.16</v>
       </c>
       <c r="K6">
-        <v>-8.26</v>
+        <v>-9.57</v>
       </c>
       <c r="L6">
-        <v>70.3</v>
+        <v>67.81</v>
       </c>
       <c r="M6">
-        <v>60.35</v>
+        <v>61.5</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="P6">
-        <v>205.11</v>
+        <v>206.41</v>
       </c>
       <c r="Q6">
-        <v>206.55</v>
+        <v>206.25</v>
       </c>
       <c r="R6">
-        <v>212.42</v>
+        <v>211.96</v>
       </c>
       <c r="S6">
-        <v>182.8</v>
+        <v>183.07</v>
       </c>
       <c r="T6">
-        <v>13.35</v>
+        <v>11.7</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1448,34 +1448,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>48.4</v>
+        <v>45.31</v>
       </c>
       <c r="Z6">
-        <v>-1.41</v>
+        <v>-1.5</v>
       </c>
       <c r="AA6">
-        <v>-1.99</v>
+        <v>-1.9</v>
       </c>
       <c r="AB6">
-        <v>0.58</v>
+        <v>0.4</v>
       </c>
       <c r="AC6">
-        <v>57.19</v>
+        <v>50.62</v>
       </c>
       <c r="AD6">
-        <v>48.91</v>
+        <v>53.86</v>
       </c>
       <c r="AE6">
-        <v>5.76</v>
+        <v>5.67</v>
       </c>
       <c r="AF6">
-        <v>-54.36</v>
+        <v>-51.08</v>
       </c>
       <c r="AG6">
-        <v>213.78</v>
+        <v>213.26</v>
       </c>
       <c r="AH6">
-        <v>199.32</v>
+        <v>199.23</v>
       </c>
       <c r="AI6">
         <v>217.63</v>
@@ -1484,7 +1484,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>22.32</v>
+        <v>20.43</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1495,10 +1495,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>405</v>
+        <v>398.6</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>-1.58</v>
       </c>
       <c r="E7">
         <v>588.6900000000001</v>
@@ -1507,46 +1507,46 @@
         <v>393.4</v>
       </c>
       <c r="G7">
-        <v>-31.2</v>
+        <v>-32.29</v>
       </c>
       <c r="H7">
-        <v>2.95</v>
+        <v>1.32</v>
       </c>
       <c r="I7">
-        <v>-1.71</v>
+        <v>-0.64</v>
       </c>
       <c r="J7">
-        <v>-7.22</v>
+        <v>-8.16</v>
       </c>
       <c r="K7">
-        <v>-2</v>
+        <v>-3.71</v>
       </c>
       <c r="L7">
-        <v>-28.25</v>
+        <v>-30.18</v>
       </c>
       <c r="M7">
-        <v>-0.8100000000000001</v>
+        <v>-1.27</v>
       </c>
       <c r="N7">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="O7">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="P7">
-        <v>403.21</v>
+        <v>402.7</v>
       </c>
       <c r="Q7">
-        <v>412.68</v>
+        <v>411.07</v>
       </c>
       <c r="R7">
-        <v>424.71</v>
+        <v>424.2</v>
       </c>
       <c r="S7">
-        <v>468.49</v>
+        <v>467.72</v>
       </c>
       <c r="T7">
-        <v>-13.55</v>
+        <v>-14.78</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1561,34 +1561,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>40.13</v>
+        <v>35.8</v>
       </c>
       <c r="Z7">
-        <v>-6.37</v>
+        <v>-6.7</v>
       </c>
       <c r="AA7">
-        <v>-5.8</v>
+        <v>-5.98</v>
       </c>
       <c r="AB7">
-        <v>-0.57</v>
+        <v>-0.72</v>
       </c>
       <c r="AC7">
-        <v>36</v>
+        <v>30.73</v>
       </c>
       <c r="AD7">
-        <v>27.7</v>
+        <v>31.76</v>
       </c>
       <c r="AE7">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="AF7">
-        <v>-66.84999999999999</v>
+        <v>-61.63</v>
       </c>
       <c r="AG7">
-        <v>428.29</v>
+        <v>425.38</v>
       </c>
       <c r="AH7">
-        <v>397.07</v>
+        <v>396.75</v>
       </c>
       <c r="AI7">
         <v>425.32</v>
@@ -1597,7 +1597,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>25.3</v>
+        <v>26.05</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1608,10 +1608,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>612.35</v>
+        <v>603.7</v>
       </c>
       <c r="D8">
-        <v>-0.28</v>
+        <v>-1.41</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1620,46 +1620,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-24.24</v>
+        <v>-25.31</v>
       </c>
       <c r="H8">
-        <v>30.92</v>
+        <v>29.07</v>
       </c>
       <c r="I8">
-        <v>-3.79</v>
+        <v>-2.82</v>
       </c>
       <c r="J8">
-        <v>-7.25</v>
+        <v>-8.19</v>
       </c>
       <c r="K8">
-        <v>-16.57</v>
+        <v>-19.71</v>
       </c>
       <c r="L8">
-        <v>2.81</v>
+        <v>1.13</v>
       </c>
       <c r="M8">
-        <v>-15.29</v>
+        <v>-14.64</v>
       </c>
       <c r="N8">
         <v>55</v>
       </c>
       <c r="O8">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="P8">
-        <v>615.24</v>
+        <v>611.74</v>
       </c>
       <c r="Q8">
-        <v>641.97</v>
+        <v>639.15</v>
       </c>
       <c r="R8">
-        <v>672.1900000000001</v>
+        <v>669.63</v>
       </c>
       <c r="S8">
-        <v>613.88</v>
+        <v>613.85</v>
       </c>
       <c r="T8">
-        <v>-0.25</v>
+        <v>-1.65</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1674,43 +1674,43 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>28.8</v>
+        <v>25.91</v>
       </c>
       <c r="Z8">
-        <v>-15.39</v>
+        <v>-16.27</v>
       </c>
       <c r="AA8">
-        <v>-13.13</v>
+        <v>-13.75</v>
       </c>
       <c r="AB8">
-        <v>-2.27</v>
+        <v>-2.51</v>
       </c>
       <c r="AC8">
-        <v>3.14</v>
+        <v>1.38</v>
       </c>
       <c r="AD8">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AE8">
-        <v>15.65</v>
+        <v>15.61</v>
       </c>
       <c r="AF8">
-        <v>-53.82</v>
+        <v>-57.05</v>
       </c>
       <c r="AG8">
-        <v>677.67</v>
+        <v>677.63</v>
       </c>
       <c r="AH8">
-        <v>606.28</v>
+        <v>600.6799999999999</v>
       </c>
       <c r="AI8">
-        <v>662.12</v>
+        <v>656.28</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>30.48</v>
+        <v>34.19</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1721,10 +1721,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>187.29</v>
+        <v>188.27</v>
       </c>
       <c r="D9">
-        <v>-1.83</v>
+        <v>0.52</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1733,46 +1733,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-32.53</v>
+        <v>-32.18</v>
       </c>
       <c r="H9">
-        <v>8.699999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="I9">
-        <v>-4.58</v>
+        <v>-2.22</v>
       </c>
       <c r="J9">
-        <v>-5.11</v>
+        <v>-4.67</v>
       </c>
       <c r="K9">
-        <v>0.85</v>
+        <v>-0.23</v>
       </c>
       <c r="L9">
-        <v>-27.24</v>
+        <v>-29.55</v>
       </c>
       <c r="M9">
-        <v>-7.56</v>
+        <v>-7.44</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P9">
-        <v>191.25</v>
+        <v>190.4</v>
       </c>
       <c r="Q9">
-        <v>193.19</v>
+        <v>192.8</v>
       </c>
       <c r="R9">
-        <v>190.55</v>
+        <v>190.66</v>
       </c>
       <c r="S9">
-        <v>203.38</v>
+        <v>202.94</v>
       </c>
       <c r="T9">
-        <v>-7.91</v>
+        <v>-7.23</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1787,34 +1787,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>41.39</v>
+        <v>43.24</v>
       </c>
       <c r="Z9">
-        <v>0.16</v>
+        <v>-0.2</v>
       </c>
       <c r="AA9">
-        <v>0.99</v>
+        <v>0.75</v>
       </c>
       <c r="AB9">
-        <v>-0.83</v>
+        <v>-0.95</v>
       </c>
       <c r="AC9">
-        <v>8.82</v>
+        <v>6.3</v>
       </c>
       <c r="AD9">
-        <v>18.01</v>
+        <v>11.93</v>
       </c>
       <c r="AE9">
-        <v>5.04</v>
+        <v>4.96</v>
       </c>
       <c r="AF9">
-        <v>-13.1</v>
+        <v>-58.4</v>
       </c>
       <c r="AG9">
-        <v>201.4</v>
+        <v>201.17</v>
       </c>
       <c r="AH9">
-        <v>184.99</v>
+        <v>184.44</v>
       </c>
       <c r="AI9">
         <v>185.88</v>
@@ -1823,7 +1823,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>26.21</v>
+        <v>28.23</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1834,10 +1834,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>74.27</v>
+        <v>72.87</v>
       </c>
       <c r="D10">
-        <v>5.11</v>
+        <v>-1.89</v>
       </c>
       <c r="E10">
         <v>131.73</v>
@@ -1846,46 +1846,46 @@
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-43.62</v>
+        <v>-44.68</v>
       </c>
       <c r="H10">
-        <v>25.29</v>
+        <v>22.93</v>
       </c>
       <c r="I10">
-        <v>0.68</v>
+        <v>0.93</v>
       </c>
       <c r="J10">
-        <v>-4.02</v>
+        <v>-5.2</v>
       </c>
       <c r="K10">
-        <v>-8.9</v>
+        <v>-11.04</v>
       </c>
       <c r="L10">
-        <v>-46.84</v>
+        <v>-34.31</v>
       </c>
       <c r="M10">
-        <v>0.25</v>
+        <v>-0.51</v>
       </c>
       <c r="N10">
         <v>12</v>
       </c>
       <c r="O10">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="P10">
-        <v>71.88</v>
+        <v>72.01000000000001</v>
       </c>
       <c r="Q10">
-        <v>74.51000000000001</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="R10">
-        <v>77.25</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="S10">
-        <v>80.93000000000001</v>
+        <v>80.86</v>
       </c>
       <c r="T10">
-        <v>-8.23</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1900,34 +1900,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>47.42</v>
+        <v>42.33</v>
       </c>
       <c r="Z10">
-        <v>-1.46</v>
+        <v>-1.39</v>
       </c>
       <c r="AA10">
-        <v>-1.34</v>
+        <v>-1.35</v>
       </c>
       <c r="AB10">
-        <v>-0.12</v>
+        <v>-0.04</v>
       </c>
       <c r="AC10">
-        <v>33.33</v>
+        <v>58.68</v>
       </c>
       <c r="AD10">
-        <v>11.11</v>
+        <v>30.67</v>
       </c>
       <c r="AE10">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="AF10">
-        <v>195.87</v>
+        <v>-7.46</v>
       </c>
       <c r="AG10">
-        <v>78.40000000000001</v>
+        <v>78.23</v>
       </c>
       <c r="AH10">
-        <v>70.62</v>
+        <v>70.47</v>
       </c>
       <c r="AI10">
         <v>76.63</v>
@@ -1936,7 +1936,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>47.42</v>
+        <v>41.26</v>
       </c>
     </row>
   </sheetData>
@@ -2077,7 +2077,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2117,7 +2117,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2169,13 +2169,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>-8.75</v>
+        <v>-6.86</v>
       </c>
       <c r="D7" s="6">
-        <v>-6.86</v>
+        <v>-6.9</v>
       </c>
       <c r="E7" s="7">
-        <v>1.89</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2186,13 +2186,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-4.89</v>
+        <v>-2.91</v>
       </c>
       <c r="D8" s="6">
-        <v>-2.91</v>
-      </c>
-      <c r="E8" s="7">
-        <v>1.98</v>
+        <v>-2.32</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0.59</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2203,13 +2203,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-7</v>
+        <v>-5.12</v>
       </c>
       <c r="D9" s="6">
-        <v>-5.12</v>
+        <v>-6.15</v>
       </c>
       <c r="E9" s="7">
-        <v>1.88</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2220,13 +2220,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>0.38</v>
+        <v>0.73</v>
       </c>
       <c r="D10" s="6">
-        <v>0.73</v>
+        <v>0.05</v>
       </c>
       <c r="E10" s="7">
-        <v>0.35</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2237,13 +2237,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-0.33</v>
+        <v>-0.44</v>
       </c>
       <c r="D11" s="6">
-        <v>-0.44</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-0.11</v>
+        <v>-2.16</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.72</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2254,13 +2254,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-8.99</v>
+        <v>-7.22</v>
       </c>
       <c r="D12" s="6">
-        <v>-7.22</v>
+        <v>-8.16</v>
       </c>
       <c r="E12" s="7">
-        <v>1.77</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2271,13 +2271,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-7.01</v>
+        <v>-7.25</v>
       </c>
       <c r="D13" s="6">
-        <v>-7.25</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-0.24</v>
+        <v>-8.19</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2288,13 +2288,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-1.42</v>
+        <v>-5.11</v>
       </c>
       <c r="D14" s="6">
-        <v>-5.11</v>
+        <v>-4.67</v>
       </c>
       <c r="E14" s="8">
-        <v>-3.69</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2305,13 +2305,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-8.44</v>
+        <v>-4.02</v>
       </c>
       <c r="D15" s="6">
-        <v>-4.02</v>
+        <v>-5.2</v>
       </c>
       <c r="E15" s="7">
-        <v>4.42</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2322,13 +2322,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-2.95</v>
+        <v>-1.73</v>
       </c>
       <c r="D16" s="6">
-        <v>-1.73</v>
-      </c>
-      <c r="E16" s="7">
-        <v>1.22</v>
+        <v>-0.61</v>
+      </c>
+      <c r="E16" s="8">
+        <v>1.12</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2339,13 +2339,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-8.460000000000001</v>
+        <v>-7.27</v>
       </c>
       <c r="D17" s="6">
-        <v>-7.27</v>
-      </c>
-      <c r="E17" s="7">
-        <v>1.19</v>
+        <v>3.18</v>
+      </c>
+      <c r="E17" s="8">
+        <v>10.45</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2356,13 +2356,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-3.39</v>
+        <v>-0.74</v>
       </c>
       <c r="D18" s="6">
-        <v>-0.74</v>
-      </c>
-      <c r="E18" s="7">
-        <v>2.65</v>
+        <v>6.02</v>
+      </c>
+      <c r="E18" s="8">
+        <v>6.76</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2373,13 +2373,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-0.44</v>
+        <v>-0.01</v>
       </c>
       <c r="D19" s="6">
-        <v>-0.01</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.43</v>
+        <v>6.35</v>
+      </c>
+      <c r="E19" s="8">
+        <v>6.36</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2390,13 +2390,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-3.12</v>
+        <v>-2.55</v>
       </c>
       <c r="D20" s="6">
-        <v>-2.55</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0.57</v>
+        <v>3.28</v>
+      </c>
+      <c r="E20" s="8">
+        <v>5.83</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2407,13 +2407,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-1.47</v>
+        <v>-1.71</v>
       </c>
       <c r="D21" s="6">
-        <v>-1.71</v>
+        <v>-0.64</v>
       </c>
       <c r="E21" s="8">
-        <v>-0.24</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2424,13 +2424,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-4.85</v>
+        <v>-3.79</v>
       </c>
       <c r="D22" s="6">
-        <v>-3.79</v>
-      </c>
-      <c r="E22" s="7">
-        <v>1.06</v>
+        <v>-2.82</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.97</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2441,13 +2441,13 @@
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>-4.48</v>
+        <v>-4.58</v>
       </c>
       <c r="D23" s="6">
-        <v>-4.58</v>
+        <v>-2.22</v>
       </c>
       <c r="E23" s="8">
-        <v>-0.1</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2458,13 +2458,13 @@
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>-4.77</v>
+        <v>0.68</v>
       </c>
       <c r="D24" s="6">
-        <v>0.68</v>
-      </c>
-      <c r="E24" s="7">
-        <v>5.45</v>
+        <v>0.93</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0.25</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2475,13 +2475,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>-29.64</v>
+        <v>-29.13</v>
       </c>
       <c r="D25" s="6">
-        <v>-29.13</v>
+        <v>-30.77</v>
       </c>
       <c r="E25" s="7">
-        <v>0.51</v>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2492,13 +2492,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>27.06</v>
+        <v>29.25</v>
       </c>
       <c r="D26" s="6">
-        <v>29.25</v>
+        <v>28.95</v>
       </c>
       <c r="E26" s="7">
-        <v>2.19</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2509,13 +2509,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>37.77</v>
+        <v>39.35</v>
       </c>
       <c r="D27" s="6">
-        <v>39.35</v>
+        <v>37.65</v>
       </c>
       <c r="E27" s="7">
-        <v>1.58</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2526,13 +2526,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>28.34</v>
+        <v>28.31</v>
       </c>
       <c r="D28" s="6">
-        <v>28.31</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-0.03</v>
+        <v>27.7</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-0.61</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2543,13 +2543,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>71.62</v>
+        <v>70.3</v>
       </c>
       <c r="D29" s="6">
-        <v>70.3</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-1.32</v>
+        <v>67.81</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-2.49</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2560,13 +2560,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>-28.23</v>
+        <v>-28.25</v>
       </c>
       <c r="D30" s="6">
-        <v>-28.25</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-0.02</v>
+        <v>-30.18</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-1.93</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2577,13 +2577,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>3.39</v>
+        <v>2.81</v>
       </c>
       <c r="D31" s="6">
-        <v>2.81</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-0.58</v>
+        <v>1.13</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-1.68</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2594,13 +2594,13 @@
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>-23.67</v>
+        <v>-27.24</v>
       </c>
       <c r="D32" s="6">
-        <v>-27.24</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-3.57</v>
+        <v>-29.55</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-2.31</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2611,13 +2611,13 @@
         <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>-49.71</v>
+        <v>-46.84</v>
       </c>
       <c r="D33" s="6">
-        <v>-46.84</v>
-      </c>
-      <c r="E33" s="7">
-        <v>2.87</v>
+        <v>-34.31</v>
+      </c>
+      <c r="E33" s="8">
+        <v>12.53</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2628,13 +2628,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>-3.79</v>
+        <v>-2.16</v>
       </c>
       <c r="D34" s="6">
-        <v>-2.16</v>
+        <v>-3.67</v>
       </c>
       <c r="E34" s="7">
-        <v>1.63</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2645,13 +2645,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-4.79</v>
+        <v>-1.03</v>
       </c>
       <c r="D35" s="6">
-        <v>-1.03</v>
-      </c>
-      <c r="E35" s="7">
-        <v>3.76</v>
+        <v>-0.96</v>
+      </c>
+      <c r="E35" s="8">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2662,13 +2662,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>-15.88</v>
+        <v>-12.69</v>
       </c>
       <c r="D36" s="6">
-        <v>-12.69</v>
+        <v>-16.06</v>
       </c>
       <c r="E36" s="7">
-        <v>3.19</v>
+        <v>-3.37</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2679,13 +2679,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>-6.06</v>
+        <v>-5.01</v>
       </c>
       <c r="D37" s="6">
-        <v>-5.01</v>
+        <v>-6.84</v>
       </c>
       <c r="E37" s="7">
-        <v>1.05</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2696,13 +2696,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>-10.45</v>
+        <v>-8.26</v>
       </c>
       <c r="D38" s="6">
-        <v>-8.26</v>
+        <v>-9.57</v>
       </c>
       <c r="E38" s="7">
-        <v>2.19</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2713,13 +2713,13 @@
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>-2.52</v>
+        <v>-2</v>
       </c>
       <c r="D39" s="6">
-        <v>-2</v>
+        <v>-3.71</v>
       </c>
       <c r="E39" s="7">
-        <v>0.52</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2730,13 +2730,13 @@
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>-19.41</v>
+        <v>-16.57</v>
       </c>
       <c r="D40" s="6">
-        <v>-16.57</v>
+        <v>-19.71</v>
       </c>
       <c r="E40" s="7">
-        <v>2.84</v>
+        <v>-3.14</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2747,13 +2747,13 @@
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>1.01</v>
+        <v>0.85</v>
       </c>
       <c r="D41" s="6">
-        <v>0.85</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-0.16</v>
+        <v>-0.23</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-1.08</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2764,13 +2764,13 @@
         <v>10</v>
       </c>
       <c r="C42" s="6">
-        <v>-16.62</v>
+        <v>-8.9</v>
       </c>
       <c r="D42" s="6">
-        <v>-8.9</v>
+        <v>-11.04</v>
       </c>
       <c r="E42" s="7">
-        <v>7.72</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2781,13 +2781,13 @@
         <v>6</v>
       </c>
       <c r="C43" s="6">
-        <v>-33.15</v>
+        <v>-32.53</v>
       </c>
       <c r="D43" s="6">
-        <v>-32.53</v>
+        <v>-33.32</v>
       </c>
       <c r="E43" s="7">
-        <v>0.62</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2798,13 +2798,13 @@
         <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-9.69</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="D44" s="6">
-        <v>-8.529999999999999</v>
-      </c>
-      <c r="E44" s="7">
-        <v>1.16</v>
+        <v>-8.16</v>
+      </c>
+      <c r="E44" s="8">
+        <v>0.37</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2815,13 +2815,13 @@
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-20.01</v>
+        <v>-18.9</v>
       </c>
       <c r="D45" s="6">
-        <v>-18.9</v>
+        <v>-19.73</v>
       </c>
       <c r="E45" s="7">
-        <v>1.11</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2832,13 +2832,13 @@
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-9.380000000000001</v>
+        <v>-9.34</v>
       </c>
       <c r="D46" s="6">
-        <v>-9.34</v>
+        <v>-10.03</v>
       </c>
       <c r="E46" s="7">
-        <v>0.04</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2849,540 +2849,608 @@
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-16.32</v>
+        <v>-16.76</v>
       </c>
       <c r="D47" s="6">
-        <v>-16.76</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-0.44</v>
+        <v>-17.85</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-1.09</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-24.03</v>
+        <v>-31.2</v>
       </c>
       <c r="D48" s="6">
-        <v>-24.24</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-0.21</v>
+        <v>-32.29</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-1.09</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-31.27</v>
+        <v>-24.24</v>
       </c>
       <c r="D49" s="6">
-        <v>-32.53</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-1.26</v>
+        <v>-25.31</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-1.07</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-49.42</v>
+        <v>-32.53</v>
       </c>
       <c r="D50" s="6">
-        <v>-43.62</v>
-      </c>
-      <c r="E50" s="7">
-        <v>5.8</v>
+        <v>-32.18</v>
+      </c>
+      <c r="E50" s="8">
+        <v>0.35</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C51" s="6">
-        <v>1272</v>
+        <v>-43.62</v>
       </c>
       <c r="D51" s="6">
-        <v>1283.8</v>
+        <v>-44.68</v>
       </c>
       <c r="E51" s="7">
-        <v>11.8</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C52" s="6">
-        <v>2901</v>
+        <v>1283.8</v>
       </c>
       <c r="D52" s="6">
-        <v>2938</v>
+        <v>1268.7</v>
       </c>
       <c r="E52" s="7">
-        <v>37</v>
+        <v>-15.1</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>1283.4</v>
+        <v>2938</v>
       </c>
       <c r="D53" s="6">
-        <v>1301.3</v>
-      </c>
-      <c r="E53" s="7">
-        <v>17.9</v>
+        <v>2950</v>
+      </c>
+      <c r="E53" s="8">
+        <v>12</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>1706.5</v>
+        <v>1301.3</v>
       </c>
       <c r="D54" s="6">
-        <v>1707.3</v>
+        <v>1288</v>
       </c>
       <c r="E54" s="7">
-        <v>0.8</v>
+        <v>-13.3</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>208.29</v>
+        <v>1707.3</v>
       </c>
       <c r="D55" s="6">
-        <v>207.2</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-1.09</v>
+        <v>1694.3</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-13</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>614.05</v>
+        <v>207.2</v>
       </c>
       <c r="D56" s="6">
-        <v>612.35</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-1.7</v>
+        <v>204.49</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-2.71</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>190.79</v>
+        <v>405</v>
       </c>
       <c r="D57" s="6">
-        <v>187.29</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-3.5</v>
+        <v>398.6</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-6.4</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>70.66</v>
+        <v>612.35</v>
       </c>
       <c r="D58" s="6">
-        <v>74.27</v>
+        <v>603.7</v>
       </c>
       <c r="E58" s="7">
-        <v>3.61</v>
+        <v>-8.65</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C59" s="6">
-        <v>77</v>
+        <v>187.29</v>
       </c>
       <c r="D59" s="6">
-        <v>88</v>
-      </c>
-      <c r="E59" s="7">
-        <v>11</v>
+        <v>188.27</v>
+      </c>
+      <c r="E59" s="8">
+        <v>0.98</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C60" s="6">
-        <v>66</v>
+        <v>74.27</v>
       </c>
       <c r="D60" s="6">
-        <v>77</v>
+        <v>72.87</v>
       </c>
       <c r="E60" s="7">
-        <v>11</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C61" s="6">
-        <v>88</v>
+        <v>23</v>
       </c>
       <c r="D61" s="6">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="E61" s="8">
-        <v>-22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C62" s="6">
-        <v>36.05</v>
+        <v>77</v>
       </c>
       <c r="D62" s="6">
-        <v>40.5</v>
+        <v>66</v>
       </c>
       <c r="E62" s="7">
-        <v>4.45</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C63" s="6">
-        <v>39.76</v>
+        <v>66</v>
       </c>
       <c r="D63" s="6">
-        <v>43.72</v>
-      </c>
-      <c r="E63" s="7">
-        <v>3.96</v>
+        <v>77</v>
+      </c>
+      <c r="E63" s="8">
+        <v>11</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C64" s="6">
-        <v>42.36</v>
+        <v>34</v>
       </c>
       <c r="D64" s="6">
-        <v>45.29</v>
+        <v>23</v>
       </c>
       <c r="E64" s="7">
-        <v>2.93</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C65" s="6">
-        <v>51.1</v>
+        <v>40.5</v>
       </c>
       <c r="D65" s="6">
-        <v>51.22</v>
+        <v>36.95</v>
       </c>
       <c r="E65" s="7">
-        <v>0.12</v>
+        <v>-3.55</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="6">
-        <v>49.67</v>
+        <v>43.72</v>
       </c>
       <c r="D66" s="6">
-        <v>48.4</v>
+        <v>44.98</v>
       </c>
       <c r="E66" s="8">
-        <v>-1.27</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="6">
-        <v>29.39</v>
+        <v>45.29</v>
       </c>
       <c r="D67" s="6">
-        <v>28.8</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-0.59</v>
+        <v>43.52</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-1.77</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="6">
-        <v>46.4</v>
+        <v>51.22</v>
       </c>
       <c r="D68" s="6">
-        <v>41.39</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-5.01</v>
+        <v>49.14</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-2.08</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="6">
-        <v>26.19</v>
+        <v>48.4</v>
       </c>
       <c r="D69" s="6">
-        <v>47.42</v>
+        <v>45.31</v>
       </c>
       <c r="E69" s="7">
-        <v>21.23</v>
+        <v>-3.09</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C70" s="6">
-        <v>-30.87</v>
+        <v>40.13</v>
       </c>
       <c r="D70" s="6">
-        <v>-18.96</v>
+        <v>35.8</v>
       </c>
       <c r="E70" s="7">
-        <v>11.91</v>
+        <v>-4.33</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C71" s="6">
-        <v>-55.37</v>
+        <v>28.8</v>
       </c>
       <c r="D71" s="6">
-        <v>-41.93</v>
+        <v>25.91</v>
       </c>
       <c r="E71" s="7">
-        <v>13.44</v>
+        <v>-2.89</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C72" s="6">
-        <v>-29.74</v>
+        <v>41.39</v>
       </c>
       <c r="D72" s="6">
-        <v>-52.26</v>
+        <v>43.24</v>
       </c>
       <c r="E72" s="8">
-        <v>-22.52</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C73" s="6">
-        <v>48.56</v>
+        <v>47.42</v>
       </c>
       <c r="D73" s="6">
-        <v>-44.71</v>
-      </c>
-      <c r="E73" s="8">
-        <v>-93.27</v>
+        <v>42.33</v>
+      </c>
+      <c r="E73" s="7">
+        <v>-5.09</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C74" s="6">
-        <v>-13.56</v>
+        <v>-18.96</v>
       </c>
       <c r="D74" s="6">
-        <v>-54.36</v>
-      </c>
-      <c r="E74" s="8">
-        <v>-40.8</v>
+        <v>-26.19</v>
+      </c>
+      <c r="E74" s="7">
+        <v>-7.23</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="6">
-        <v>-65.51000000000001</v>
+        <v>-41.93</v>
       </c>
       <c r="D75" s="6">
-        <v>-66.84999999999999</v>
-      </c>
-      <c r="E75" s="8">
-        <v>-1.34</v>
+        <v>-46.57</v>
+      </c>
+      <c r="E75" s="7">
+        <v>-4.64</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="6">
-        <v>-49.55</v>
+        <v>-52.26</v>
       </c>
       <c r="D76" s="6">
-        <v>-53.82</v>
-      </c>
-      <c r="E76" s="8">
-        <v>-4.27</v>
+        <v>-57.33</v>
+      </c>
+      <c r="E76" s="7">
+        <v>-5.07</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="6">
-        <v>-70.05</v>
+        <v>-44.71</v>
       </c>
       <c r="D77" s="6">
-        <v>-13.1</v>
+        <v>-49.33</v>
       </c>
       <c r="E77" s="7">
-        <v>56.95</v>
+        <v>-4.62</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="6">
-        <v>-43.43</v>
+        <v>-54.36</v>
       </c>
       <c r="D78" s="6">
+        <v>-51.08</v>
+      </c>
+      <c r="E78" s="8">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
+        <v>-66.84999999999999</v>
+      </c>
+      <c r="D79" s="6">
+        <v>-61.63</v>
+      </c>
+      <c r="E79" s="8">
+        <v>5.22</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="6">
+        <v>-53.82</v>
+      </c>
+      <c r="D80" s="6">
+        <v>-57.05</v>
+      </c>
+      <c r="E80" s="7">
+        <v>-3.23</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="6">
+        <v>-13.1</v>
+      </c>
+      <c r="D81" s="6">
+        <v>-58.4</v>
+      </c>
+      <c r="E81" s="7">
+        <v>-45.3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="6">
         <v>195.87</v>
       </c>
-      <c r="E78" s="7">
-        <v>239.3</v>
+      <c r="D82" s="6">
+        <v>-7.46</v>
+      </c>
+      <c r="E82" s="7">
+        <v>-203.33</v>
       </c>
     </row>
   </sheetData>
@@ -3447,16 +3515,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>43</v>
+        <v>40.8</v>
       </c>
       <c r="E2" s="11">
         <v>40</v>
       </c>
       <c r="F2" s="11">
-        <v>-4.2</v>
+        <v>-4.9</v>
       </c>
       <c r="G2" s="11">
-        <v>-6.2</v>
+        <v>-8</v>
       </c>
       <c r="H2" s="11">
         <v>55.4</v>
@@ -3593,31 +3661,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.6035</v>
+        <v>0.615</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1851</v>
+        <v>0.1848</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1325</v>
+        <v>0.1367</v>
       </c>
       <c r="D2" s="14">
-        <v>0.0318</v>
+        <v>0.0302</v>
       </c>
       <c r="E2" s="14">
-        <v>0.0025</v>
+        <v>-0.0051</v>
       </c>
       <c r="F2" s="14">
-        <v>-0.008100000000000001</v>
+        <v>-0.0127</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.0756</v>
+        <v>-0.07440000000000001</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.1151</v>
+        <v>-0.1178</v>
       </c>
       <c r="I2" s="14">
-        <v>-0.1529</v>
+        <v>-0.1464</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="82">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,16 +196,37 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>51.2 → 49.1</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>51.2</t>
+    <t>49.1 → 51.7</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
   </si>
   <si>
     <t>49.1</t>
+  </si>
+  <si>
+    <t>51.7</t>
+  </si>
+  <si>
+    <t>45.3 → 50.2</t>
+  </si>
+  <si>
+    <t>45.3</t>
+  </si>
+  <si>
+    <t>50.2</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>25.9 → 30.8</t>
+  </si>
+  <si>
+    <t>25.9</t>
+  </si>
+  <si>
+    <t>30.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -291,14 +312,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -331,13 +352,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -417,8 +438,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -930,10 +951,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1268.7</v>
+        <v>1262.8</v>
       </c>
       <c r="D2">
-        <v>-1.18</v>
+        <v>-0.47</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -942,46 +963,46 @@
         <v>1247.38</v>
       </c>
       <c r="G2">
-        <v>-33.32</v>
+        <v>-33.63</v>
       </c>
       <c r="H2">
-        <v>1.71</v>
+        <v>1.24</v>
       </c>
       <c r="I2">
-        <v>-0.61</v>
+        <v>-0.75</v>
       </c>
       <c r="J2">
-        <v>-6.9</v>
+        <v>-6.98</v>
       </c>
       <c r="K2">
-        <v>-3.67</v>
+        <v>-3.5</v>
       </c>
       <c r="L2">
-        <v>-30.77</v>
+        <v>-30.99</v>
       </c>
       <c r="M2">
-        <v>-11.78</v>
+        <v>-11.61</v>
       </c>
       <c r="N2">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="O2">
         <v>20</v>
       </c>
       <c r="P2">
-        <v>1272.68</v>
+        <v>1270.78</v>
       </c>
       <c r="Q2">
-        <v>1301.59</v>
+        <v>1297.74</v>
       </c>
       <c r="R2">
-        <v>1340.74</v>
+        <v>1339.45</v>
       </c>
       <c r="S2">
-        <v>1489.22</v>
+        <v>1486.33</v>
       </c>
       <c r="T2">
-        <v>-14.81</v>
+        <v>-15.04</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -996,43 +1017,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>36.95</v>
+        <v>35.64</v>
       </c>
       <c r="Z2">
-        <v>-20.18</v>
+        <v>-20.79</v>
       </c>
       <c r="AA2">
-        <v>-17.83</v>
+        <v>-18.42</v>
       </c>
       <c r="AB2">
-        <v>-2.35</v>
+        <v>-2.36</v>
       </c>
       <c r="AC2">
-        <v>28.99</v>
+        <v>26.86</v>
       </c>
       <c r="AD2">
-        <v>20.93</v>
+        <v>26.16</v>
       </c>
       <c r="AE2">
-        <v>22.7</v>
+        <v>22.01</v>
       </c>
       <c r="AF2">
-        <v>-26.19</v>
+        <v>-2.01</v>
       </c>
       <c r="AG2">
-        <v>1347.02</v>
+        <v>1342.58</v>
       </c>
       <c r="AH2">
-        <v>1256.15</v>
+        <v>1252.89</v>
       </c>
       <c r="AI2">
-        <v>1334.07</v>
+        <v>1327.88</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>31.27</v>
+        <v>32.07</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,10 +1064,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2950</v>
+        <v>2953.1</v>
       </c>
       <c r="D3">
-        <v>0.41</v>
+        <v>0.11</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1055,46 +1076,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-8.16</v>
+        <v>-8.06</v>
       </c>
       <c r="H3">
-        <v>67.8</v>
+        <v>67.98</v>
       </c>
       <c r="I3">
-        <v>3.18</v>
+        <v>3.11</v>
       </c>
       <c r="J3">
-        <v>-2.32</v>
+        <v>-1.89</v>
       </c>
       <c r="K3">
-        <v>-0.96</v>
+        <v>0.8</v>
       </c>
       <c r="L3">
-        <v>28.95</v>
+        <v>29.65</v>
       </c>
       <c r="M3">
-        <v>13.67</v>
+        <v>13.73</v>
       </c>
       <c r="N3">
         <v>88</v>
       </c>
       <c r="O3">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P3">
-        <v>2908.94</v>
+        <v>2926.78</v>
       </c>
       <c r="Q3">
-        <v>2996.76</v>
+        <v>2994.64</v>
       </c>
       <c r="R3">
-        <v>3056.62</v>
+        <v>3054.96</v>
       </c>
       <c r="S3">
-        <v>2514.4</v>
+        <v>2516.94</v>
       </c>
       <c r="T3">
-        <v>17.32</v>
+        <v>17.33</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1109,34 +1130,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>44.98</v>
+        <v>45.32</v>
       </c>
       <c r="Z3">
-        <v>-28.78</v>
+        <v>-28.01</v>
       </c>
       <c r="AA3">
-        <v>-17.31</v>
+        <v>-19.45</v>
       </c>
       <c r="AB3">
-        <v>-11.47</v>
+        <v>-8.56</v>
       </c>
       <c r="AC3">
-        <v>24.08</v>
+        <v>29.99</v>
       </c>
       <c r="AD3">
-        <v>16.85</v>
+        <v>23.84</v>
       </c>
       <c r="AE3">
-        <v>76.39</v>
+        <v>74.56</v>
       </c>
       <c r="AF3">
-        <v>-46.57</v>
+        <v>-47.38</v>
       </c>
       <c r="AG3">
-        <v>3174.75</v>
+        <v>3173.7</v>
       </c>
       <c r="AH3">
-        <v>2818.76</v>
+        <v>2815.57</v>
       </c>
       <c r="AI3">
         <v>3113.12</v>
@@ -1145,7 +1166,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>35.06</v>
+        <v>33.05</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1177,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="D4">
-        <v>-1.02</v>
+        <v>0.31</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1168,46 +1189,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-19.73</v>
+        <v>-19.48</v>
       </c>
       <c r="H4">
-        <v>66.67</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="I4">
-        <v>6.02</v>
+        <v>2.13</v>
       </c>
       <c r="J4">
-        <v>-6.15</v>
+        <v>-5.62</v>
       </c>
       <c r="K4">
-        <v>-16.06</v>
+        <v>-12.88</v>
       </c>
       <c r="L4">
-        <v>37.65</v>
+        <v>39.05</v>
       </c>
       <c r="M4">
-        <v>3.02</v>
+        <v>2.21</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P4">
-        <v>1286.74</v>
+        <v>1292.14</v>
       </c>
       <c r="Q4">
-        <v>1307.25</v>
+        <v>1303.55</v>
       </c>
       <c r="R4">
-        <v>1402.54</v>
+        <v>1398.54</v>
       </c>
       <c r="S4">
-        <v>1177.84</v>
+        <v>1179</v>
       </c>
       <c r="T4">
-        <v>9.35</v>
+        <v>9.58</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1222,34 +1243,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>43.52</v>
+        <v>44.22</v>
       </c>
       <c r="Z4">
-        <v>-30.3</v>
+        <v>-28.43</v>
       </c>
       <c r="AA4">
-        <v>-34.19</v>
+        <v>-33.03</v>
       </c>
       <c r="AB4">
-        <v>3.88</v>
+        <v>4.61</v>
       </c>
       <c r="AC4">
-        <v>92.83</v>
+        <v>94.12</v>
       </c>
       <c r="AD4">
-        <v>91.69</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="AE4">
-        <v>39.76</v>
+        <v>38.77</v>
       </c>
       <c r="AF4">
-        <v>-57.33</v>
+        <v>-57.04</v>
       </c>
       <c r="AG4">
-        <v>1370.67</v>
+        <v>1360.88</v>
       </c>
       <c r="AH4">
-        <v>1243.83</v>
+        <v>1246.22</v>
       </c>
       <c r="AI4">
         <v>1367.12</v>
@@ -1258,7 +1279,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>23.84</v>
+        <v>23.32</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1290,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1694.3</v>
+        <v>1710</v>
       </c>
       <c r="D5">
-        <v>-0.76</v>
+        <v>0.93</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1281,46 +1302,46 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-10.03</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="H5">
-        <v>30.52</v>
+        <v>31.73</v>
       </c>
       <c r="I5">
-        <v>6.35</v>
+        <v>3.79</v>
       </c>
       <c r="J5">
-        <v>0.05</v>
+        <v>1.73</v>
       </c>
       <c r="K5">
-        <v>-6.84</v>
+        <v>-5.71</v>
       </c>
       <c r="L5">
-        <v>27.7</v>
+        <v>29.29</v>
       </c>
       <c r="M5">
-        <v>18.48</v>
+        <v>18.66</v>
       </c>
       <c r="N5">
         <v>77</v>
       </c>
       <c r="O5">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P5">
-        <v>1685.66</v>
+        <v>1698.16</v>
       </c>
       <c r="Q5">
-        <v>1683.03</v>
+        <v>1685.12</v>
       </c>
       <c r="R5">
-        <v>1743.58</v>
+        <v>1741.58</v>
       </c>
       <c r="S5">
-        <v>1603.02</v>
+        <v>1604.15</v>
       </c>
       <c r="T5">
-        <v>5.69</v>
+        <v>6.6</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1335,34 +1356,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>49.14</v>
+        <v>51.69</v>
       </c>
       <c r="Z5">
-        <v>-12.18</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="AA5">
-        <v>-18.06</v>
+        <v>-16.32</v>
       </c>
       <c r="AB5">
-        <v>5.88</v>
+        <v>6.95</v>
       </c>
       <c r="AC5">
         <v>96.59999999999999</v>
       </c>
       <c r="AD5">
-        <v>89.52</v>
+        <v>95.37</v>
       </c>
       <c r="AE5">
-        <v>37.73</v>
+        <v>37.02</v>
       </c>
       <c r="AF5">
-        <v>-49.33</v>
+        <v>-46.19</v>
       </c>
       <c r="AG5">
-        <v>1739.35</v>
+        <v>1742.22</v>
       </c>
       <c r="AH5">
-        <v>1626.72</v>
+        <v>1628.03</v>
       </c>
       <c r="AI5">
         <v>1757.42</v>
@@ -1371,7 +1392,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>22.49</v>
+        <v>20.23</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,58 +1403,58 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>204.49</v>
+        <v>208.4</v>
       </c>
       <c r="D6">
-        <v>-1.31</v>
+        <v>1.91</v>
       </c>
       <c r="E6">
         <v>248.91</v>
       </c>
       <c r="F6">
-        <v>121.74</v>
+        <v>121.94</v>
       </c>
       <c r="G6">
-        <v>-17.85</v>
+        <v>-16.27</v>
       </c>
       <c r="H6">
-        <v>67.97</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I6">
-        <v>3.28</v>
+        <v>1.98</v>
       </c>
       <c r="J6">
-        <v>-2.16</v>
+        <v>-1.07</v>
       </c>
       <c r="K6">
-        <v>-9.57</v>
+        <v>-5.52</v>
       </c>
       <c r="L6">
-        <v>67.81</v>
+        <v>71.18000000000001</v>
       </c>
       <c r="M6">
-        <v>61.5</v>
+        <v>60.54</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="P6">
-        <v>206.41</v>
+        <v>207.22</v>
       </c>
       <c r="Q6">
-        <v>206.25</v>
+        <v>206.22</v>
       </c>
       <c r="R6">
-        <v>211.96</v>
+        <v>211.66</v>
       </c>
       <c r="S6">
-        <v>183.07</v>
+        <v>183.35</v>
       </c>
       <c r="T6">
-        <v>11.7</v>
+        <v>13.66</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1448,34 +1469,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>45.31</v>
+        <v>50.25</v>
       </c>
       <c r="Z6">
-        <v>-1.5</v>
+        <v>-1.24</v>
       </c>
       <c r="AA6">
-        <v>-1.9</v>
+        <v>-1.76</v>
       </c>
       <c r="AB6">
-        <v>0.4</v>
+        <v>0.52</v>
       </c>
       <c r="AC6">
-        <v>50.62</v>
+        <v>50.52</v>
       </c>
       <c r="AD6">
-        <v>53.86</v>
+        <v>52.78</v>
       </c>
       <c r="AE6">
-        <v>5.67</v>
+        <v>5.64</v>
       </c>
       <c r="AF6">
-        <v>-51.08</v>
+        <v>-10.34</v>
       </c>
       <c r="AG6">
-        <v>213.26</v>
+        <v>213.19</v>
       </c>
       <c r="AH6">
-        <v>199.23</v>
+        <v>199.24</v>
       </c>
       <c r="AI6">
         <v>217.63</v>
@@ -1484,7 +1505,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>20.43</v>
+        <v>18.16</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1495,10 +1516,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>398.6</v>
+        <v>398.3</v>
       </c>
       <c r="D7">
-        <v>-1.58</v>
+        <v>-0.08</v>
       </c>
       <c r="E7">
         <v>588.6900000000001</v>
@@ -1507,46 +1528,46 @@
         <v>393.4</v>
       </c>
       <c r="G7">
-        <v>-32.29</v>
+        <v>-32.34</v>
       </c>
       <c r="H7">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="I7">
-        <v>-0.64</v>
+        <v>-0.97</v>
       </c>
       <c r="J7">
-        <v>-8.16</v>
+        <v>-7.55</v>
       </c>
       <c r="K7">
-        <v>-3.71</v>
+        <v>-2.32</v>
       </c>
       <c r="L7">
-        <v>-30.18</v>
+        <v>-29.49</v>
       </c>
       <c r="M7">
-        <v>-1.27</v>
+        <v>-1.03</v>
       </c>
       <c r="N7">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="O7">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="P7">
-        <v>402.7</v>
+        <v>401.92</v>
       </c>
       <c r="Q7">
-        <v>411.07</v>
+        <v>409.78</v>
       </c>
       <c r="R7">
-        <v>424.2</v>
+        <v>423.73</v>
       </c>
       <c r="S7">
-        <v>467.72</v>
+        <v>466.95</v>
       </c>
       <c r="T7">
-        <v>-14.78</v>
+        <v>-14.7</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1561,43 +1582,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>35.8</v>
+        <v>35.61</v>
       </c>
       <c r="Z7">
-        <v>-6.7</v>
+        <v>-6.91</v>
       </c>
       <c r="AA7">
-        <v>-5.98</v>
+        <v>-6.17</v>
       </c>
       <c r="AB7">
-        <v>-0.72</v>
+        <v>-0.75</v>
       </c>
       <c r="AC7">
-        <v>30.73</v>
+        <v>16.69</v>
       </c>
       <c r="AD7">
-        <v>31.76</v>
+        <v>27.81</v>
       </c>
       <c r="AE7">
-        <v>8</v>
+        <v>7.85</v>
       </c>
       <c r="AF7">
-        <v>-61.63</v>
+        <v>-55.91</v>
       </c>
       <c r="AG7">
-        <v>425.38</v>
+        <v>423.82</v>
       </c>
       <c r="AH7">
-        <v>396.75</v>
+        <v>395.75</v>
       </c>
       <c r="AI7">
-        <v>425.32</v>
+        <v>421.59</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>26.05</v>
+        <v>27.82</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1608,10 +1629,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>603.7</v>
+        <v>609.4</v>
       </c>
       <c r="D8">
-        <v>-1.41</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1620,46 +1641,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-25.31</v>
+        <v>-24.6</v>
       </c>
       <c r="H8">
-        <v>29.07</v>
+        <v>30.29</v>
       </c>
       <c r="I8">
-        <v>-2.82</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="J8">
-        <v>-8.19</v>
+        <v>-7.68</v>
       </c>
       <c r="K8">
-        <v>-19.71</v>
+        <v>-16.31</v>
       </c>
       <c r="L8">
-        <v>1.13</v>
+        <v>2.28</v>
       </c>
       <c r="M8">
-        <v>-14.64</v>
+        <v>-15.28</v>
       </c>
       <c r="N8">
         <v>55</v>
       </c>
       <c r="O8">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P8">
-        <v>611.74</v>
+        <v>610.89</v>
       </c>
       <c r="Q8">
-        <v>639.15</v>
+        <v>636.3200000000001</v>
       </c>
       <c r="R8">
-        <v>669.63</v>
+        <v>667.1900000000001</v>
       </c>
       <c r="S8">
         <v>613.85</v>
       </c>
       <c r="T8">
-        <v>-1.65</v>
+        <v>-0.72</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1674,43 +1695,43 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>25.91</v>
+        <v>30.83</v>
       </c>
       <c r="Z8">
-        <v>-16.27</v>
+        <v>-16.32</v>
       </c>
       <c r="AA8">
-        <v>-13.75</v>
+        <v>-14.27</v>
       </c>
       <c r="AB8">
-        <v>-2.51</v>
+        <v>-2.05</v>
       </c>
       <c r="AC8">
-        <v>1.38</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AD8">
-        <v>2.5</v>
+        <v>4.55</v>
       </c>
       <c r="AE8">
-        <v>15.61</v>
+        <v>15.21</v>
       </c>
       <c r="AF8">
-        <v>-57.05</v>
+        <v>-52.63</v>
       </c>
       <c r="AG8">
-        <v>677.63</v>
+        <v>674.78</v>
       </c>
       <c r="AH8">
-        <v>600.6799999999999</v>
+        <v>597.86</v>
       </c>
       <c r="AI8">
-        <v>656.28</v>
+        <v>652.63</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>34.19</v>
+        <v>37.4</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1721,10 +1742,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>188.27</v>
+        <v>187.52</v>
       </c>
       <c r="D9">
-        <v>0.52</v>
+        <v>-0.4</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1733,25 +1754,25 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-32.18</v>
+        <v>-32.45</v>
       </c>
       <c r="H9">
-        <v>9.27</v>
+        <v>8.83</v>
       </c>
       <c r="I9">
-        <v>-2.22</v>
+        <v>-3.53</v>
       </c>
       <c r="J9">
-        <v>-4.67</v>
+        <v>-4.39</v>
       </c>
       <c r="K9">
-        <v>-0.23</v>
+        <v>0.2</v>
       </c>
       <c r="L9">
-        <v>-29.55</v>
+        <v>-29.46</v>
       </c>
       <c r="M9">
-        <v>-7.44</v>
+        <v>-7.52</v>
       </c>
       <c r="N9">
         <v>45</v>
@@ -1760,19 +1781,19 @@
         <v>25</v>
       </c>
       <c r="P9">
-        <v>190.4</v>
+        <v>189.02</v>
       </c>
       <c r="Q9">
-        <v>192.8</v>
+        <v>192.53</v>
       </c>
       <c r="R9">
-        <v>190.66</v>
+        <v>190.74</v>
       </c>
       <c r="S9">
-        <v>202.94</v>
+        <v>202.49</v>
       </c>
       <c r="T9">
-        <v>-7.23</v>
+        <v>-7.39</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1787,34 +1808,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>43.24</v>
+        <v>42.14</v>
       </c>
       <c r="Z9">
-        <v>-0.2</v>
+        <v>-0.54</v>
       </c>
       <c r="AA9">
-        <v>0.75</v>
+        <v>0.49</v>
       </c>
       <c r="AB9">
-        <v>-0.95</v>
+        <v>-1.03</v>
       </c>
       <c r="AC9">
-        <v>6.3</v>
+        <v>3.35</v>
       </c>
       <c r="AD9">
-        <v>11.93</v>
+        <v>6.16</v>
       </c>
       <c r="AE9">
-        <v>4.96</v>
+        <v>4.77</v>
       </c>
       <c r="AF9">
-        <v>-58.4</v>
+        <v>-75.05</v>
       </c>
       <c r="AG9">
-        <v>201.17</v>
+        <v>201.23</v>
       </c>
       <c r="AH9">
-        <v>184.44</v>
+        <v>183.84</v>
       </c>
       <c r="AI9">
         <v>185.88</v>
@@ -1823,7 +1844,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>28.23</v>
+        <v>29.98</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1834,10 +1855,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>72.87</v>
+        <v>73.03</v>
       </c>
       <c r="D10">
-        <v>-1.89</v>
+        <v>0.22</v>
       </c>
       <c r="E10">
         <v>131.73</v>
@@ -1846,46 +1867,46 @@
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-44.68</v>
+        <v>-44.56</v>
       </c>
       <c r="H10">
-        <v>22.93</v>
+        <v>23.2</v>
       </c>
       <c r="I10">
-        <v>0.93</v>
+        <v>2.25</v>
       </c>
       <c r="J10">
-        <v>-5.2</v>
+        <v>-4.08</v>
       </c>
       <c r="K10">
-        <v>-11.04</v>
+        <v>-6.79</v>
       </c>
       <c r="L10">
-        <v>-34.31</v>
+        <v>-34.93</v>
       </c>
       <c r="M10">
-        <v>-0.51</v>
+        <v>-0.25</v>
       </c>
       <c r="N10">
         <v>12</v>
       </c>
       <c r="O10">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P10">
-        <v>72.01000000000001</v>
+        <v>72.33</v>
       </c>
       <c r="Q10">
-        <v>74.34999999999999</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="R10">
-        <v>77.09999999999999</v>
+        <v>76.95</v>
       </c>
       <c r="S10">
-        <v>80.86</v>
+        <v>80.8</v>
       </c>
       <c r="T10">
-        <v>-9.890000000000001</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1900,34 +1921,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>42.33</v>
+        <v>43.09</v>
       </c>
       <c r="Z10">
-        <v>-1.39</v>
+        <v>-1.3</v>
       </c>
       <c r="AA10">
-        <v>-1.35</v>
+        <v>-1.34</v>
       </c>
       <c r="AB10">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="AC10">
-        <v>58.68</v>
+        <v>85.20999999999999</v>
       </c>
       <c r="AD10">
-        <v>30.67</v>
+        <v>59.08</v>
       </c>
       <c r="AE10">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="AF10">
-        <v>-7.46</v>
+        <v>-51.12</v>
       </c>
       <c r="AG10">
-        <v>78.23</v>
+        <v>77.87</v>
       </c>
       <c r="AH10">
-        <v>70.47</v>
+        <v>70.44</v>
       </c>
       <c r="AI10">
         <v>76.63</v>
@@ -1936,7 +1957,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>41.26</v>
+        <v>36.35</v>
       </c>
     </row>
   </sheetData>
@@ -2135,999 +2156,1005 @@
         <v>61</v>
       </c>
     </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-6.86</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-6.9</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-2.91</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-2.32</v>
-      </c>
-      <c r="E8" s="8">
-        <v>0.59</v>
+      <c r="B8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-5.12</v>
+        <v>-6.9</v>
       </c>
       <c r="D9" s="6">
-        <v>-6.15</v>
+        <v>-6.98</v>
       </c>
       <c r="E9" s="7">
-        <v>-1.03</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>0.73</v>
+        <v>-2.32</v>
       </c>
       <c r="D10" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-0.68</v>
+        <v>-1.89</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0.43</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-0.44</v>
+        <v>-6.15</v>
       </c>
       <c r="D11" s="6">
-        <v>-2.16</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-1.72</v>
+        <v>-5.62</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0.53</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-7.22</v>
+        <v>0.05</v>
       </c>
       <c r="D12" s="6">
-        <v>-8.16</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.9399999999999999</v>
+        <v>1.73</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1.68</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-7.25</v>
+        <v>-2.16</v>
       </c>
       <c r="D13" s="6">
-        <v>-8.19</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.9399999999999999</v>
+        <v>-1.07</v>
+      </c>
+      <c r="E13" s="8">
+        <v>1.09</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-5.11</v>
+        <v>-8.16</v>
       </c>
       <c r="D14" s="6">
-        <v>-4.67</v>
+        <v>-7.55</v>
       </c>
       <c r="E14" s="8">
-        <v>0.44</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-4.02</v>
+        <v>-8.19</v>
       </c>
       <c r="D15" s="6">
-        <v>-5.2</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-1.18</v>
+        <v>-7.68</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.51</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>-1.73</v>
+        <v>-4.67</v>
       </c>
       <c r="D16" s="6">
-        <v>-0.61</v>
+        <v>-4.39</v>
       </c>
       <c r="E16" s="8">
-        <v>1.12</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17" s="6">
-        <v>-7.27</v>
+        <v>-5.2</v>
       </c>
       <c r="D17" s="6">
-        <v>3.18</v>
+        <v>-4.08</v>
       </c>
       <c r="E17" s="8">
-        <v>10.45</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-0.74</v>
+        <v>-0.61</v>
       </c>
       <c r="D18" s="6">
-        <v>6.02</v>
-      </c>
-      <c r="E18" s="8">
-        <v>6.76</v>
+        <v>-0.75</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-0.14</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-0.01</v>
+        <v>3.18</v>
       </c>
       <c r="D19" s="6">
-        <v>6.35</v>
-      </c>
-      <c r="E19" s="8">
-        <v>6.36</v>
+        <v>3.11</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-2.55</v>
+        <v>6.02</v>
       </c>
       <c r="D20" s="6">
-        <v>3.28</v>
-      </c>
-      <c r="E20" s="8">
-        <v>5.83</v>
+        <v>2.13</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-3.89</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-1.71</v>
+        <v>6.35</v>
       </c>
       <c r="D21" s="6">
-        <v>-0.64</v>
-      </c>
-      <c r="E21" s="8">
-        <v>1.07</v>
+        <v>3.79</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-2.56</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-3.79</v>
+        <v>3.28</v>
       </c>
       <c r="D22" s="6">
-        <v>-2.82</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0.97</v>
+        <v>1.98</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-1.3</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>-4.58</v>
+        <v>-0.64</v>
       </c>
       <c r="D23" s="6">
-        <v>-2.22</v>
-      </c>
-      <c r="E23" s="8">
-        <v>2.36</v>
+        <v>-0.97</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.33</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>0.68</v>
+        <v>-2.82</v>
       </c>
       <c r="D24" s="6">
-        <v>0.93</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="E24" s="8">
-        <v>0.25</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C25" s="6">
-        <v>-29.13</v>
+        <v>-2.22</v>
       </c>
       <c r="D25" s="6">
-        <v>-30.77</v>
+        <v>-3.53</v>
       </c>
       <c r="E25" s="7">
-        <v>-1.64</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C26" s="6">
-        <v>29.25</v>
+        <v>0.93</v>
       </c>
       <c r="D26" s="6">
-        <v>28.95</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-0.3</v>
+        <v>2.25</v>
+      </c>
+      <c r="E26" s="8">
+        <v>1.32</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>39.35</v>
+        <v>-30.77</v>
       </c>
       <c r="D27" s="6">
-        <v>37.65</v>
+        <v>-30.99</v>
       </c>
       <c r="E27" s="7">
-        <v>-1.7</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>28.31</v>
+        <v>28.95</v>
       </c>
       <c r="D28" s="6">
-        <v>27.7</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-0.61</v>
+        <v>29.65</v>
+      </c>
+      <c r="E28" s="8">
+        <v>0.7</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>70.3</v>
+        <v>37.65</v>
       </c>
       <c r="D29" s="6">
-        <v>67.81</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-2.49</v>
+        <v>39.05</v>
+      </c>
+      <c r="E29" s="8">
+        <v>1.4</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>-28.25</v>
+        <v>27.7</v>
       </c>
       <c r="D30" s="6">
-        <v>-30.18</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-1.93</v>
+        <v>29.29</v>
+      </c>
+      <c r="E30" s="8">
+        <v>1.59</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>2.81</v>
+        <v>67.81</v>
       </c>
       <c r="D31" s="6">
-        <v>1.13</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-1.68</v>
+        <v>71.18000000000001</v>
+      </c>
+      <c r="E31" s="8">
+        <v>3.37</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>-27.24</v>
+        <v>-30.18</v>
       </c>
       <c r="D32" s="6">
-        <v>-29.55</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-2.31</v>
+        <v>-29.49</v>
+      </c>
+      <c r="E32" s="8">
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>-46.84</v>
+        <v>1.13</v>
       </c>
       <c r="D33" s="6">
-        <v>-34.31</v>
+        <v>2.28</v>
       </c>
       <c r="E33" s="8">
-        <v>12.53</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C34" s="6">
-        <v>-2.16</v>
+        <v>-29.55</v>
       </c>
       <c r="D34" s="6">
-        <v>-3.67</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-1.51</v>
+        <v>-29.46</v>
+      </c>
+      <c r="E34" s="8">
+        <v>0.09</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C35" s="6">
-        <v>-1.03</v>
+        <v>-34.31</v>
       </c>
       <c r="D35" s="6">
-        <v>-0.96</v>
-      </c>
-      <c r="E35" s="8">
-        <v>0.07000000000000001</v>
+        <v>-34.93</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-0.62</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>-12.69</v>
+        <v>-3.67</v>
       </c>
       <c r="D36" s="6">
-        <v>-16.06</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-3.37</v>
+        <v>-3.5</v>
+      </c>
+      <c r="E36" s="8">
+        <v>0.17</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>-5.01</v>
+        <v>-0.96</v>
       </c>
       <c r="D37" s="6">
-        <v>-6.84</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-1.83</v>
+        <v>0.8</v>
+      </c>
+      <c r="E37" s="8">
+        <v>1.76</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>-8.26</v>
+        <v>-16.06</v>
       </c>
       <c r="D38" s="6">
-        <v>-9.57</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-1.31</v>
+        <v>-12.88</v>
+      </c>
+      <c r="E38" s="8">
+        <v>3.18</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>-2</v>
+        <v>-6.84</v>
       </c>
       <c r="D39" s="6">
-        <v>-3.71</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-1.71</v>
+        <v>-5.71</v>
+      </c>
+      <c r="E39" s="8">
+        <v>1.13</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>-16.57</v>
+        <v>-9.57</v>
       </c>
       <c r="D40" s="6">
-        <v>-19.71</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-3.14</v>
+        <v>-5.52</v>
+      </c>
+      <c r="E40" s="8">
+        <v>4.05</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>0.85</v>
+        <v>-3.71</v>
       </c>
       <c r="D41" s="6">
-        <v>-0.23</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-1.08</v>
+        <v>-2.32</v>
+      </c>
+      <c r="E41" s="8">
+        <v>1.39</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="6">
-        <v>-8.9</v>
+        <v>-19.71</v>
       </c>
       <c r="D42" s="6">
-        <v>-11.04</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-2.14</v>
+        <v>-16.31</v>
+      </c>
+      <c r="E42" s="8">
+        <v>3.4</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C43" s="6">
-        <v>-32.53</v>
+        <v>-0.23</v>
       </c>
       <c r="D43" s="6">
-        <v>-33.32</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-0.79</v>
+        <v>0.2</v>
+      </c>
+      <c r="E43" s="8">
+        <v>0.43</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C44" s="6">
-        <v>-8.529999999999999</v>
+        <v>-11.04</v>
       </c>
       <c r="D44" s="6">
-        <v>-8.16</v>
+        <v>-6.79</v>
       </c>
       <c r="E44" s="8">
-        <v>0.37</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-18.9</v>
+        <v>-33.32</v>
       </c>
       <c r="D45" s="6">
-        <v>-19.73</v>
+        <v>-33.63</v>
       </c>
       <c r="E45" s="7">
-        <v>-0.83</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-9.34</v>
+        <v>-8.16</v>
       </c>
       <c r="D46" s="6">
-        <v>-10.03</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-0.6899999999999999</v>
+        <v>-8.06</v>
+      </c>
+      <c r="E46" s="8">
+        <v>0.1</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-16.76</v>
+        <v>-19.73</v>
       </c>
       <c r="D47" s="6">
-        <v>-17.85</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-1.09</v>
+        <v>-19.48</v>
+      </c>
+      <c r="E47" s="8">
+        <v>0.25</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-31.2</v>
+        <v>-10.03</v>
       </c>
       <c r="D48" s="6">
-        <v>-32.29</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-1.09</v>
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="E48" s="8">
+        <v>0.83</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-24.24</v>
+        <v>-17.85</v>
       </c>
       <c r="D49" s="6">
-        <v>-25.31</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-1.07</v>
+        <v>-16.27</v>
+      </c>
+      <c r="E49" s="8">
+        <v>1.58</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-32.53</v>
+        <v>-32.29</v>
       </c>
       <c r="D50" s="6">
-        <v>-32.18</v>
-      </c>
-      <c r="E50" s="8">
-        <v>0.35</v>
+        <v>-32.34</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="6">
-        <v>-43.62</v>
+        <v>-25.31</v>
       </c>
       <c r="D51" s="6">
-        <v>-44.68</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-1.06</v>
+        <v>-24.6</v>
+      </c>
+      <c r="E51" s="8">
+        <v>0.71</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C52" s="6">
-        <v>1283.8</v>
+        <v>-32.18</v>
       </c>
       <c r="D52" s="6">
-        <v>1268.7</v>
+        <v>-32.45</v>
       </c>
       <c r="E52" s="7">
-        <v>-15.1</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C53" s="6">
-        <v>2938</v>
+        <v>-44.68</v>
       </c>
       <c r="D53" s="6">
-        <v>2950</v>
+        <v>-44.56</v>
       </c>
       <c r="E53" s="8">
-        <v>12</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>1301.3</v>
+        <v>1268.7</v>
       </c>
       <c r="D54" s="6">
-        <v>1288</v>
+        <v>1262.8</v>
       </c>
       <c r="E54" s="7">
-        <v>-13.3</v>
+        <v>-5.9</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>1707.3</v>
+        <v>2950</v>
       </c>
       <c r="D55" s="6">
-        <v>1694.3</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-13</v>
+        <v>2953.1</v>
+      </c>
+      <c r="E55" s="8">
+        <v>3.1</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>207.2</v>
+        <v>1288</v>
       </c>
       <c r="D56" s="6">
-        <v>204.49</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-2.71</v>
+        <v>1292</v>
+      </c>
+      <c r="E56" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>405</v>
+        <v>1694.3</v>
       </c>
       <c r="D57" s="6">
-        <v>398.6</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-6.4</v>
+        <v>1710</v>
+      </c>
+      <c r="E57" s="8">
+        <v>15.7</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>612.35</v>
+        <v>204.49</v>
       </c>
       <c r="D58" s="6">
-        <v>603.7</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-8.65</v>
+        <v>208.4</v>
+      </c>
+      <c r="E58" s="8">
+        <v>3.91</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="6">
-        <v>187.29</v>
+        <v>398.6</v>
       </c>
       <c r="D59" s="6">
-        <v>188.27</v>
-      </c>
-      <c r="E59" s="8">
-        <v>0.98</v>
+        <v>398.3</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C60" s="6">
-        <v>74.27</v>
+        <v>603.7</v>
       </c>
       <c r="D60" s="6">
-        <v>72.87</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-1.4</v>
+        <v>609.4</v>
+      </c>
+      <c r="E60" s="8">
+        <v>5.7</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C61" s="6">
-        <v>23</v>
+        <v>188.27</v>
       </c>
       <c r="D61" s="6">
-        <v>34</v>
-      </c>
-      <c r="E61" s="8">
-        <v>11</v>
+        <v>187.52</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-0.75</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C62" s="6">
-        <v>77</v>
+        <v>72.87</v>
       </c>
       <c r="D62" s="6">
-        <v>66</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-11</v>
+        <v>73.03</v>
+      </c>
+      <c r="E62" s="8">
+        <v>0.16</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C63" s="6">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="D63" s="6">
-        <v>77</v>
-      </c>
-      <c r="E63" s="8">
-        <v>11</v>
+        <v>23</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-11</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -3138,13 +3165,13 @@
         <v>13</v>
       </c>
       <c r="C64" s="6">
+        <v>23</v>
+      </c>
+      <c r="D64" s="6">
         <v>34</v>
       </c>
-      <c r="D64" s="6">
-        <v>23</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-11</v>
+      <c r="E64" s="8">
+        <v>11</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -3155,13 +3182,13 @@
         <v>24</v>
       </c>
       <c r="C65" s="6">
-        <v>40.5</v>
+        <v>36.95</v>
       </c>
       <c r="D65" s="6">
-        <v>36.95</v>
+        <v>35.64</v>
       </c>
       <c r="E65" s="7">
-        <v>-3.55</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -3172,13 +3199,13 @@
         <v>24</v>
       </c>
       <c r="C66" s="6">
-        <v>43.72</v>
+        <v>44.98</v>
       </c>
       <c r="D66" s="6">
-        <v>44.98</v>
+        <v>45.32</v>
       </c>
       <c r="E66" s="8">
-        <v>1.26</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -3189,13 +3216,13 @@
         <v>24</v>
       </c>
       <c r="C67" s="6">
-        <v>45.29</v>
+        <v>43.52</v>
       </c>
       <c r="D67" s="6">
-        <v>43.52</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-1.77</v>
+        <v>44.22</v>
+      </c>
+      <c r="E67" s="8">
+        <v>0.7</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -3206,13 +3233,13 @@
         <v>24</v>
       </c>
       <c r="C68" s="6">
-        <v>51.22</v>
+        <v>49.14</v>
       </c>
       <c r="D68" s="6">
-        <v>49.14</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-2.08</v>
+        <v>51.69</v>
+      </c>
+      <c r="E68" s="8">
+        <v>2.55</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -3223,13 +3250,13 @@
         <v>24</v>
       </c>
       <c r="C69" s="6">
-        <v>48.4</v>
+        <v>45.31</v>
       </c>
       <c r="D69" s="6">
-        <v>45.31</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-3.09</v>
+        <v>50.25</v>
+      </c>
+      <c r="E69" s="8">
+        <v>4.94</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -3240,13 +3267,13 @@
         <v>24</v>
       </c>
       <c r="C70" s="6">
-        <v>40.13</v>
+        <v>35.8</v>
       </c>
       <c r="D70" s="6">
-        <v>35.8</v>
+        <v>35.61</v>
       </c>
       <c r="E70" s="7">
-        <v>-4.33</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -3257,13 +3284,13 @@
         <v>24</v>
       </c>
       <c r="C71" s="6">
-        <v>28.8</v>
+        <v>25.91</v>
       </c>
       <c r="D71" s="6">
-        <v>25.91</v>
-      </c>
-      <c r="E71" s="7">
-        <v>-2.89</v>
+        <v>30.83</v>
+      </c>
+      <c r="E71" s="8">
+        <v>4.92</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -3274,13 +3301,13 @@
         <v>24</v>
       </c>
       <c r="C72" s="6">
-        <v>41.39</v>
+        <v>43.24</v>
       </c>
       <c r="D72" s="6">
-        <v>43.24</v>
-      </c>
-      <c r="E72" s="8">
-        <v>1.85</v>
+        <v>42.14</v>
+      </c>
+      <c r="E72" s="7">
+        <v>-1.1</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -3291,13 +3318,13 @@
         <v>24</v>
       </c>
       <c r="C73" s="6">
-        <v>47.42</v>
+        <v>42.33</v>
       </c>
       <c r="D73" s="6">
-        <v>42.33</v>
-      </c>
-      <c r="E73" s="7">
-        <v>-5.09</v>
+        <v>43.09</v>
+      </c>
+      <c r="E73" s="8">
+        <v>0.76</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -3308,13 +3335,13 @@
         <v>31</v>
       </c>
       <c r="C74" s="6">
-        <v>-18.96</v>
+        <v>-26.19</v>
       </c>
       <c r="D74" s="6">
-        <v>-26.19</v>
-      </c>
-      <c r="E74" s="7">
-        <v>-7.23</v>
+        <v>-2.01</v>
+      </c>
+      <c r="E74" s="8">
+        <v>24.18</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -3325,13 +3352,13 @@
         <v>31</v>
       </c>
       <c r="C75" s="6">
-        <v>-41.93</v>
+        <v>-46.57</v>
       </c>
       <c r="D75" s="6">
-        <v>-46.57</v>
+        <v>-47.38</v>
       </c>
       <c r="E75" s="7">
-        <v>-4.64</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -3342,13 +3369,13 @@
         <v>31</v>
       </c>
       <c r="C76" s="6">
-        <v>-52.26</v>
+        <v>-57.33</v>
       </c>
       <c r="D76" s="6">
-        <v>-57.33</v>
-      </c>
-      <c r="E76" s="7">
-        <v>-5.07</v>
+        <v>-57.04</v>
+      </c>
+      <c r="E76" s="8">
+        <v>0.29</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -3359,13 +3386,13 @@
         <v>31</v>
       </c>
       <c r="C77" s="6">
-        <v>-44.71</v>
+        <v>-49.33</v>
       </c>
       <c r="D77" s="6">
-        <v>-49.33</v>
-      </c>
-      <c r="E77" s="7">
-        <v>-4.62</v>
+        <v>-46.19</v>
+      </c>
+      <c r="E77" s="8">
+        <v>3.14</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -3376,13 +3403,13 @@
         <v>31</v>
       </c>
       <c r="C78" s="6">
-        <v>-54.36</v>
+        <v>-51.08</v>
       </c>
       <c r="D78" s="6">
-        <v>-51.08</v>
+        <v>-10.34</v>
       </c>
       <c r="E78" s="8">
-        <v>3.28</v>
+        <v>40.74</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -3393,13 +3420,13 @@
         <v>31</v>
       </c>
       <c r="C79" s="6">
-        <v>-66.84999999999999</v>
+        <v>-61.63</v>
       </c>
       <c r="D79" s="6">
-        <v>-61.63</v>
+        <v>-55.91</v>
       </c>
       <c r="E79" s="8">
-        <v>5.22</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -3410,13 +3437,13 @@
         <v>31</v>
       </c>
       <c r="C80" s="6">
-        <v>-53.82</v>
+        <v>-57.05</v>
       </c>
       <c r="D80" s="6">
-        <v>-57.05</v>
-      </c>
-      <c r="E80" s="7">
-        <v>-3.23</v>
+        <v>-52.63</v>
+      </c>
+      <c r="E80" s="8">
+        <v>4.42</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -3427,13 +3454,13 @@
         <v>31</v>
       </c>
       <c r="C81" s="6">
-        <v>-13.1</v>
+        <v>-58.4</v>
       </c>
       <c r="D81" s="6">
-        <v>-58.4</v>
+        <v>-75.05</v>
       </c>
       <c r="E81" s="7">
-        <v>-45.3</v>
+        <v>-16.65</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -3444,19 +3471,19 @@
         <v>31</v>
       </c>
       <c r="C82" s="6">
-        <v>195.87</v>
+        <v>-7.46</v>
       </c>
       <c r="D82" s="6">
-        <v>-7.46</v>
+        <v>-51.12</v>
       </c>
       <c r="E82" s="7">
-        <v>-203.33</v>
+        <v>-43.66</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3480,28 +3507,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3515,16 +3542,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>40.8</v>
+        <v>42.1</v>
       </c>
       <c r="E2" s="11">
         <v>40</v>
       </c>
       <c r="F2" s="11">
-        <v>-4.9</v>
+        <v>-4.2</v>
       </c>
       <c r="G2" s="11">
-        <v>-8</v>
+        <v>-5.8</v>
       </c>
       <c r="H2" s="11">
         <v>55.4</v>
@@ -3661,31 +3688,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.615</v>
+        <v>0.6053999999999999</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1848</v>
+        <v>0.1866</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1367</v>
+        <v>0.1373</v>
       </c>
       <c r="D2" s="14">
-        <v>0.0302</v>
+        <v>0.0221</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.0051</v>
+        <v>-0.0025</v>
       </c>
       <c r="F2" s="14">
-        <v>-0.0127</v>
+        <v>-0.0103</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.07440000000000001</v>
+        <v>-0.07519999999999999</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.1178</v>
+        <v>-0.1161</v>
       </c>
       <c r="I2" s="14">
-        <v>-0.1464</v>
+        <v>-0.1528</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,37 +196,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>49.1 → 51.7</t>
+    <t>45.3 → 58.8</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>49.1</t>
-  </si>
-  <si>
-    <t>51.7</t>
-  </si>
-  <si>
-    <t>45.3 → 50.2</t>
-  </si>
-  <si>
     <t>45.3</t>
   </si>
   <si>
-    <t>50.2</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>25.9 → 30.8</t>
-  </si>
-  <si>
-    <t>25.9</t>
-  </si>
-  <si>
-    <t>30.8</t>
+    <t>58.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -438,8 +417,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -951,10 +930,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1262.8</v>
+        <v>1257.7</v>
       </c>
       <c r="D2">
-        <v>-0.47</v>
+        <v>-0.4</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -963,46 +942,46 @@
         <v>1247.38</v>
       </c>
       <c r="G2">
-        <v>-33.63</v>
+        <v>-33.9</v>
       </c>
       <c r="H2">
-        <v>1.24</v>
+        <v>0.83</v>
       </c>
       <c r="I2">
-        <v>-0.75</v>
+        <v>-0.7</v>
       </c>
       <c r="J2">
-        <v>-6.98</v>
+        <v>-6.13</v>
       </c>
       <c r="K2">
-        <v>-3.5</v>
+        <v>-2.97</v>
       </c>
       <c r="L2">
-        <v>-30.99</v>
+        <v>-30.84</v>
       </c>
       <c r="M2">
-        <v>-11.61</v>
+        <v>-11.76</v>
       </c>
       <c r="N2">
         <v>23</v>
       </c>
       <c r="O2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P2">
-        <v>1270.78</v>
+        <v>1269</v>
       </c>
       <c r="Q2">
-        <v>1297.74</v>
+        <v>1293.98</v>
       </c>
       <c r="R2">
-        <v>1339.45</v>
+        <v>1337.96</v>
       </c>
       <c r="S2">
-        <v>1486.33</v>
+        <v>1483.52</v>
       </c>
       <c r="T2">
-        <v>-15.04</v>
+        <v>-15.22</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1017,34 +996,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>35.64</v>
+        <v>34.5</v>
       </c>
       <c r="Z2">
-        <v>-20.79</v>
+        <v>-21.43</v>
       </c>
       <c r="AA2">
-        <v>-18.42</v>
+        <v>-19.02</v>
       </c>
       <c r="AB2">
-        <v>-2.36</v>
+        <v>-2.41</v>
       </c>
       <c r="AC2">
-        <v>26.86</v>
+        <v>12.78</v>
       </c>
       <c r="AD2">
-        <v>26.16</v>
+        <v>22.88</v>
       </c>
       <c r="AE2">
-        <v>22.01</v>
+        <v>21.65</v>
       </c>
       <c r="AF2">
-        <v>-2.01</v>
+        <v>4.64</v>
       </c>
       <c r="AG2">
-        <v>1342.58</v>
+        <v>1339.04</v>
       </c>
       <c r="AH2">
-        <v>1252.89</v>
+        <v>1248.92</v>
       </c>
       <c r="AI2">
         <v>1327.88</v>
@@ -1053,7 +1032,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>32.07</v>
+        <v>31.71</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1064,10 +1043,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2953.1</v>
+        <v>3104.7</v>
       </c>
       <c r="D3">
-        <v>0.11</v>
+        <v>5.13</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1076,46 +1055,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-8.06</v>
+        <v>-3.34</v>
       </c>
       <c r="H3">
-        <v>67.98</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I3">
-        <v>3.11</v>
+        <v>7.36</v>
       </c>
       <c r="J3">
-        <v>-1.89</v>
+        <v>3.65</v>
       </c>
       <c r="K3">
-        <v>0.8</v>
+        <v>6.78</v>
       </c>
       <c r="L3">
-        <v>29.65</v>
+        <v>36.15</v>
       </c>
       <c r="M3">
-        <v>13.73</v>
+        <v>15.03</v>
       </c>
       <c r="N3">
         <v>88</v>
       </c>
       <c r="O3">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="P3">
-        <v>2926.78</v>
+        <v>2969.36</v>
       </c>
       <c r="Q3">
-        <v>2994.64</v>
+        <v>3000.59</v>
       </c>
       <c r="R3">
-        <v>3054.96</v>
+        <v>3054.19</v>
       </c>
       <c r="S3">
-        <v>2516.94</v>
+        <v>2520.36</v>
       </c>
       <c r="T3">
-        <v>17.33</v>
+        <v>23.18</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1130,34 +1109,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>45.32</v>
+        <v>58.78</v>
       </c>
       <c r="Z3">
-        <v>-28.01</v>
+        <v>-15</v>
       </c>
       <c r="AA3">
-        <v>-19.45</v>
+        <v>-18.56</v>
       </c>
       <c r="AB3">
-        <v>-8.56</v>
+        <v>3.57</v>
       </c>
       <c r="AC3">
-        <v>29.99</v>
+        <v>46.03</v>
       </c>
       <c r="AD3">
-        <v>23.84</v>
+        <v>33.37</v>
       </c>
       <c r="AE3">
-        <v>74.56</v>
+        <v>84.01000000000001</v>
       </c>
       <c r="AF3">
-        <v>-47.38</v>
+        <v>187.11</v>
       </c>
       <c r="AG3">
-        <v>3173.7</v>
+        <v>3186.19</v>
       </c>
       <c r="AH3">
-        <v>2815.57</v>
+        <v>2814.98</v>
       </c>
       <c r="AI3">
         <v>3113.12</v>
@@ -1166,7 +1145,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>33.05</v>
+        <v>33.17</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1177,10 +1156,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1292</v>
+        <v>1315</v>
       </c>
       <c r="D4">
-        <v>0.31</v>
+        <v>1.78</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1189,46 +1168,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-19.48</v>
+        <v>-18.04</v>
       </c>
       <c r="H4">
-        <v>67.18000000000001</v>
+        <v>70.16</v>
       </c>
       <c r="I4">
-        <v>2.13</v>
+        <v>1.47</v>
       </c>
       <c r="J4">
-        <v>-5.62</v>
+        <v>-3.73</v>
       </c>
       <c r="K4">
-        <v>-12.88</v>
+        <v>-9.59</v>
       </c>
       <c r="L4">
-        <v>39.05</v>
+        <v>41.5</v>
       </c>
       <c r="M4">
-        <v>2.21</v>
+        <v>1.58</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="P4">
-        <v>1292.14</v>
+        <v>1295.94</v>
       </c>
       <c r="Q4">
-        <v>1303.55</v>
+        <v>1302.69</v>
       </c>
       <c r="R4">
-        <v>1398.54</v>
+        <v>1394.14</v>
       </c>
       <c r="S4">
-        <v>1179</v>
+        <v>1180.42</v>
       </c>
       <c r="T4">
-        <v>9.58</v>
+        <v>11.4</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1243,34 +1222,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>44.22</v>
+        <v>48.23</v>
       </c>
       <c r="Z4">
-        <v>-28.43</v>
+        <v>-24.8</v>
       </c>
       <c r="AA4">
-        <v>-33.03</v>
+        <v>-31.39</v>
       </c>
       <c r="AB4">
-        <v>4.61</v>
+        <v>6.59</v>
       </c>
       <c r="AC4">
         <v>94.12</v>
       </c>
       <c r="AD4">
-        <v>94.48999999999999</v>
+        <v>93.69</v>
       </c>
       <c r="AE4">
-        <v>38.77</v>
+        <v>39.55</v>
       </c>
       <c r="AF4">
-        <v>-57.04</v>
+        <v>57.79</v>
       </c>
       <c r="AG4">
-        <v>1360.88</v>
+        <v>1358.69</v>
       </c>
       <c r="AH4">
-        <v>1246.22</v>
+        <v>1246.68</v>
       </c>
       <c r="AI4">
         <v>1367.12</v>
@@ -1279,7 +1258,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>23.32</v>
+        <v>22.37</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1290,10 +1269,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1710</v>
+        <v>1775</v>
       </c>
       <c r="D5">
-        <v>0.93</v>
+        <v>3.8</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1302,46 +1281,46 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-9.199999999999999</v>
+        <v>-5.75</v>
       </c>
       <c r="H5">
-        <v>31.73</v>
+        <v>36.74</v>
       </c>
       <c r="I5">
-        <v>3.79</v>
+        <v>6.12</v>
       </c>
       <c r="J5">
-        <v>1.73</v>
+        <v>6.4</v>
       </c>
       <c r="K5">
-        <v>-5.71</v>
+        <v>-0.26</v>
       </c>
       <c r="L5">
-        <v>29.29</v>
+        <v>34.85</v>
       </c>
       <c r="M5">
-        <v>18.66</v>
+        <v>19.46</v>
       </c>
       <c r="N5">
         <v>77</v>
       </c>
       <c r="O5">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="P5">
-        <v>1698.16</v>
+        <v>1718.62</v>
       </c>
       <c r="Q5">
-        <v>1685.12</v>
+        <v>1690.62</v>
       </c>
       <c r="R5">
-        <v>1741.58</v>
+        <v>1740.11</v>
       </c>
       <c r="S5">
-        <v>1604.15</v>
+        <v>1605.66</v>
       </c>
       <c r="T5">
-        <v>6.6</v>
+        <v>10.55</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1356,43 +1335,43 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>51.69</v>
+        <v>60.5</v>
       </c>
       <c r="Z5">
-        <v>-9.369999999999999</v>
+        <v>-1.88</v>
       </c>
       <c r="AA5">
-        <v>-16.32</v>
+        <v>-13.43</v>
       </c>
       <c r="AB5">
-        <v>6.95</v>
+        <v>11.55</v>
       </c>
       <c r="AC5">
         <v>96.59999999999999</v>
       </c>
       <c r="AD5">
-        <v>95.37</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AE5">
-        <v>37.02</v>
+        <v>40.09</v>
       </c>
       <c r="AF5">
-        <v>-46.19</v>
+        <v>149.43</v>
       </c>
       <c r="AG5">
-        <v>1742.22</v>
+        <v>1759.53</v>
       </c>
       <c r="AH5">
-        <v>1628.03</v>
+        <v>1621.72</v>
       </c>
       <c r="AI5">
-        <v>1757.42</v>
+        <v>1625.69</v>
       </c>
       <c r="AJ5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AK5">
-        <v>20.23</v>
+        <v>22.84</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1403,58 +1382,58 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>208.4</v>
+        <v>214.9</v>
       </c>
       <c r="D6">
-        <v>1.91</v>
+        <v>3.12</v>
       </c>
       <c r="E6">
         <v>248.91</v>
       </c>
       <c r="F6">
-        <v>121.94</v>
+        <v>124.93</v>
       </c>
       <c r="G6">
-        <v>-16.27</v>
+        <v>-13.66</v>
       </c>
       <c r="H6">
-        <v>70.90000000000001</v>
+        <v>72.02</v>
       </c>
       <c r="I6">
-        <v>1.98</v>
+        <v>3.47</v>
       </c>
       <c r="J6">
-        <v>-1.07</v>
+        <v>2.82</v>
       </c>
       <c r="K6">
-        <v>-5.52</v>
+        <v>-0.28</v>
       </c>
       <c r="L6">
-        <v>71.18000000000001</v>
+        <v>76.23</v>
       </c>
       <c r="M6">
-        <v>60.54</v>
+        <v>59.99</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="P6">
-        <v>207.22</v>
+        <v>208.66</v>
       </c>
       <c r="Q6">
-        <v>206.22</v>
+        <v>206.61</v>
       </c>
       <c r="R6">
-        <v>211.66</v>
+        <v>211.42</v>
       </c>
       <c r="S6">
-        <v>183.35</v>
+        <v>183.68</v>
       </c>
       <c r="T6">
-        <v>13.66</v>
+        <v>17</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1469,34 +1448,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>50.25</v>
+        <v>57.18</v>
       </c>
       <c r="Z6">
-        <v>-1.24</v>
+        <v>-0.51</v>
       </c>
       <c r="AA6">
-        <v>-1.76</v>
+        <v>-1.51</v>
       </c>
       <c r="AB6">
-        <v>0.52</v>
+        <v>1.01</v>
       </c>
       <c r="AC6">
-        <v>50.52</v>
+        <v>63.64</v>
       </c>
       <c r="AD6">
-        <v>52.78</v>
+        <v>54.93</v>
       </c>
       <c r="AE6">
-        <v>5.64</v>
+        <v>5.93</v>
       </c>
       <c r="AF6">
-        <v>-10.34</v>
+        <v>65.16</v>
       </c>
       <c r="AG6">
-        <v>213.19</v>
+        <v>214.59</v>
       </c>
       <c r="AH6">
-        <v>199.24</v>
+        <v>198.63</v>
       </c>
       <c r="AI6">
         <v>217.63</v>
@@ -1505,7 +1484,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>18.16</v>
+        <v>19.57</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1516,10 +1495,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>398.3</v>
+        <v>397</v>
       </c>
       <c r="D7">
-        <v>-0.08</v>
+        <v>-0.33</v>
       </c>
       <c r="E7">
         <v>588.6900000000001</v>
@@ -1528,46 +1507,46 @@
         <v>393.4</v>
       </c>
       <c r="G7">
-        <v>-32.34</v>
+        <v>-32.56</v>
       </c>
       <c r="H7">
-        <v>1.25</v>
+        <v>0.92</v>
       </c>
       <c r="I7">
-        <v>-0.97</v>
+        <v>-1.42</v>
       </c>
       <c r="J7">
-        <v>-7.55</v>
+        <v>-6.37</v>
       </c>
       <c r="K7">
-        <v>-2.32</v>
+        <v>-1.74</v>
       </c>
       <c r="L7">
-        <v>-29.49</v>
+        <v>-29.6</v>
       </c>
       <c r="M7">
-        <v>-1.03</v>
+        <v>-1.21</v>
       </c>
       <c r="N7">
         <v>34</v>
       </c>
       <c r="O7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P7">
-        <v>401.92</v>
+        <v>400.78</v>
       </c>
       <c r="Q7">
-        <v>409.78</v>
+        <v>408.58</v>
       </c>
       <c r="R7">
-        <v>423.73</v>
+        <v>423.29</v>
       </c>
       <c r="S7">
-        <v>466.95</v>
+        <v>466.21</v>
       </c>
       <c r="T7">
-        <v>-14.7</v>
+        <v>-14.85</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1582,43 +1561,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>35.61</v>
+        <v>34.73</v>
       </c>
       <c r="Z7">
-        <v>-6.91</v>
+        <v>-7.1</v>
       </c>
       <c r="AA7">
-        <v>-6.17</v>
+        <v>-6.35</v>
       </c>
       <c r="AB7">
         <v>-0.75</v>
       </c>
       <c r="AC7">
+        <v>2.64</v>
+      </c>
+      <c r="AD7">
         <v>16.69</v>
       </c>
-      <c r="AD7">
-        <v>27.81</v>
-      </c>
       <c r="AE7">
-        <v>7.85</v>
+        <v>7.7</v>
       </c>
       <c r="AF7">
-        <v>-55.91</v>
+        <v>-60.77</v>
       </c>
       <c r="AG7">
-        <v>423.82</v>
+        <v>422.68</v>
       </c>
       <c r="AH7">
-        <v>395.75</v>
+        <v>394.48</v>
       </c>
       <c r="AI7">
-        <v>421.59</v>
+        <v>421</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>27.82</v>
+        <v>29.41</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1629,10 +1608,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>609.4</v>
+        <v>612.3</v>
       </c>
       <c r="D8">
-        <v>0.9399999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1641,46 +1620,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-24.6</v>
+        <v>-24.25</v>
       </c>
       <c r="H8">
-        <v>30.29</v>
+        <v>30.91</v>
       </c>
       <c r="I8">
-        <v>-0.6899999999999999</v>
+        <v>-0.43</v>
       </c>
       <c r="J8">
-        <v>-7.68</v>
+        <v>-8.08</v>
       </c>
       <c r="K8">
-        <v>-16.31</v>
+        <v>-14.47</v>
       </c>
       <c r="L8">
-        <v>2.28</v>
+        <v>3.75</v>
       </c>
       <c r="M8">
-        <v>-15.28</v>
+        <v>-15.12</v>
       </c>
       <c r="N8">
         <v>55</v>
       </c>
       <c r="O8">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="P8">
-        <v>610.89</v>
+        <v>610.36</v>
       </c>
       <c r="Q8">
-        <v>636.3200000000001</v>
+        <v>633.91</v>
       </c>
       <c r="R8">
-        <v>667.1900000000001</v>
+        <v>664.75</v>
       </c>
       <c r="S8">
-        <v>613.85</v>
+        <v>613.87</v>
       </c>
       <c r="T8">
-        <v>-0.72</v>
+        <v>-0.26</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1695,34 +1674,34 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>30.83</v>
+        <v>33.26</v>
       </c>
       <c r="Z8">
-        <v>-16.32</v>
+        <v>-15.94</v>
       </c>
       <c r="AA8">
-        <v>-14.27</v>
+        <v>-14.6</v>
       </c>
       <c r="AB8">
-        <v>-2.05</v>
+        <v>-1.34</v>
       </c>
       <c r="AC8">
-        <v>9.140000000000001</v>
+        <v>25.57</v>
       </c>
       <c r="AD8">
-        <v>4.55</v>
+        <v>12.03</v>
       </c>
       <c r="AE8">
-        <v>15.21</v>
+        <v>15.25</v>
       </c>
       <c r="AF8">
-        <v>-52.63</v>
+        <v>-9.9</v>
       </c>
       <c r="AG8">
-        <v>674.78</v>
+        <v>672.0599999999999</v>
       </c>
       <c r="AH8">
-        <v>597.86</v>
+        <v>595.77</v>
       </c>
       <c r="AI8">
         <v>652.63</v>
@@ -1731,7 +1710,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>37.4</v>
+        <v>34.62</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1745,7 +1724,7 @@
         <v>187.52</v>
       </c>
       <c r="D9">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1760,40 +1739,40 @@
         <v>8.83</v>
       </c>
       <c r="I9">
-        <v>-3.53</v>
+        <v>-1.95</v>
       </c>
       <c r="J9">
-        <v>-4.39</v>
+        <v>-2.77</v>
       </c>
       <c r="K9">
-        <v>0.2</v>
+        <v>1.13</v>
       </c>
       <c r="L9">
-        <v>-29.46</v>
+        <v>-28.63</v>
       </c>
       <c r="M9">
-        <v>-7.52</v>
+        <v>-7.51</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="P9">
-        <v>189.02</v>
+        <v>188.28</v>
       </c>
       <c r="Q9">
-        <v>192.53</v>
+        <v>192.2</v>
       </c>
       <c r="R9">
-        <v>190.74</v>
+        <v>190.81</v>
       </c>
       <c r="S9">
-        <v>202.49</v>
+        <v>202.06</v>
       </c>
       <c r="T9">
-        <v>-7.39</v>
+        <v>-7.2</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1811,31 +1790,31 @@
         <v>42.14</v>
       </c>
       <c r="Z9">
-        <v>-0.54</v>
+        <v>-0.8</v>
       </c>
       <c r="AA9">
-        <v>0.49</v>
+        <v>0.23</v>
       </c>
       <c r="AB9">
-        <v>-1.03</v>
+        <v>-1.04</v>
       </c>
       <c r="AC9">
-        <v>3.35</v>
+        <v>4.32</v>
       </c>
       <c r="AD9">
-        <v>6.16</v>
+        <v>4.66</v>
       </c>
       <c r="AE9">
-        <v>4.77</v>
+        <v>4.67</v>
       </c>
       <c r="AF9">
-        <v>-75.05</v>
+        <v>-51.41</v>
       </c>
       <c r="AG9">
-        <v>201.23</v>
+        <v>201.13</v>
       </c>
       <c r="AH9">
-        <v>183.84</v>
+        <v>183.27</v>
       </c>
       <c r="AI9">
         <v>185.88</v>
@@ -1844,7 +1823,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>29.98</v>
+        <v>32.08</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1855,10 +1834,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>73.03</v>
+        <v>73.73</v>
       </c>
       <c r="D10">
-        <v>0.22</v>
+        <v>0.96</v>
       </c>
       <c r="E10">
         <v>131.73</v>
@@ -1867,46 +1846,46 @@
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-44.56</v>
+        <v>-44.03</v>
       </c>
       <c r="H10">
-        <v>23.2</v>
+        <v>24.38</v>
       </c>
       <c r="I10">
-        <v>2.25</v>
+        <v>4.08</v>
       </c>
       <c r="J10">
-        <v>-4.08</v>
+        <v>-4.18</v>
       </c>
       <c r="K10">
-        <v>-6.79</v>
+        <v>-6.11</v>
       </c>
       <c r="L10">
-        <v>-34.93</v>
+        <v>-33.56</v>
       </c>
       <c r="M10">
-        <v>-0.25</v>
+        <v>0.01</v>
       </c>
       <c r="N10">
         <v>12</v>
       </c>
       <c r="O10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P10">
-        <v>72.33</v>
+        <v>72.91</v>
       </c>
       <c r="Q10">
-        <v>74.15000000000001</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="R10">
-        <v>76.95</v>
+        <v>76.81</v>
       </c>
       <c r="S10">
-        <v>80.8</v>
+        <v>80.73999999999999</v>
       </c>
       <c r="T10">
-        <v>-9.619999999999999</v>
+        <v>-8.69</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1921,34 +1900,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>43.09</v>
+        <v>46.38</v>
       </c>
       <c r="Z10">
+        <v>-1.17</v>
+      </c>
+      <c r="AA10">
         <v>-1.3</v>
       </c>
-      <c r="AA10">
-        <v>-1.34</v>
-      </c>
       <c r="AB10">
-        <v>0.04</v>
+        <v>0.14</v>
       </c>
       <c r="AC10">
-        <v>85.20999999999999</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="AD10">
-        <v>59.08</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="AE10">
         <v>2.26</v>
       </c>
       <c r="AF10">
-        <v>-51.12</v>
+        <v>-10.29</v>
       </c>
       <c r="AG10">
-        <v>77.87</v>
+        <v>77.64</v>
       </c>
       <c r="AH10">
-        <v>70.44</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="AI10">
         <v>76.63</v>
@@ -1957,7 +1936,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>36.35</v>
+        <v>32.09</v>
       </c>
     </row>
   </sheetData>
@@ -2098,7 +2077,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2138,7 +2117,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2156,1005 +2135,999 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>68</v>
-      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-6.98</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-6.13</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>73</v>
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-1.89</v>
+      </c>
+      <c r="D8" s="6">
+        <v>3.65</v>
+      </c>
+      <c r="E8" s="7">
+        <v>5.54</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-6.9</v>
+        <v>-5.62</v>
       </c>
       <c r="D9" s="6">
-        <v>-6.98</v>
+        <v>-3.73</v>
       </c>
       <c r="E9" s="7">
-        <v>-0.08</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-2.32</v>
+        <v>1.73</v>
       </c>
       <c r="D10" s="6">
-        <v>-1.89</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0.43</v>
+        <v>6.4</v>
+      </c>
+      <c r="E10" s="7">
+        <v>4.67</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-6.15</v>
+        <v>-1.07</v>
       </c>
       <c r="D11" s="6">
-        <v>-5.62</v>
-      </c>
-      <c r="E11" s="8">
-        <v>0.53</v>
+        <v>2.82</v>
+      </c>
+      <c r="E11" s="7">
+        <v>3.89</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>0.05</v>
+        <v>-7.55</v>
       </c>
       <c r="D12" s="6">
-        <v>1.73</v>
-      </c>
-      <c r="E12" s="8">
-        <v>1.68</v>
+        <v>-6.37</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1.18</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-2.16</v>
+        <v>-7.68</v>
       </c>
       <c r="D13" s="6">
-        <v>-1.07</v>
+        <v>-8.08</v>
       </c>
       <c r="E13" s="8">
-        <v>1.09</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-8.16</v>
+        <v>-4.39</v>
       </c>
       <c r="D14" s="6">
-        <v>-7.55</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0.61</v>
+        <v>-2.77</v>
+      </c>
+      <c r="E14" s="7">
+        <v>1.62</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-8.19</v>
+        <v>-4.08</v>
       </c>
       <c r="D15" s="6">
-        <v>-7.68</v>
+        <v>-4.18</v>
       </c>
       <c r="E15" s="8">
-        <v>0.51</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-4.67</v>
+        <v>-0.75</v>
       </c>
       <c r="D16" s="6">
-        <v>-4.39</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.28</v>
+        <v>-0.7</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.05</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-5.2</v>
+        <v>3.11</v>
       </c>
       <c r="D17" s="6">
-        <v>-4.08</v>
-      </c>
-      <c r="E17" s="8">
-        <v>1.12</v>
+        <v>7.36</v>
+      </c>
+      <c r="E17" s="7">
+        <v>4.25</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-0.61</v>
+        <v>2.13</v>
       </c>
       <c r="D18" s="6">
-        <v>-0.75</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-0.14</v>
+        <v>1.47</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-0.66</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>3.18</v>
+        <v>3.79</v>
       </c>
       <c r="D19" s="6">
-        <v>3.11</v>
+        <v>6.12</v>
       </c>
       <c r="E19" s="7">
-        <v>-0.07000000000000001</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>6.02</v>
+        <v>1.98</v>
       </c>
       <c r="D20" s="6">
-        <v>2.13</v>
+        <v>3.47</v>
       </c>
       <c r="E20" s="7">
-        <v>-3.89</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>6.35</v>
+        <v>-0.97</v>
       </c>
       <c r="D21" s="6">
-        <v>3.79</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-2.56</v>
+        <v>-1.42</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>3.28</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="D22" s="6">
-        <v>1.98</v>
+        <v>-0.43</v>
       </c>
       <c r="E22" s="7">
-        <v>-1.3</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>-0.64</v>
+        <v>-3.53</v>
       </c>
       <c r="D23" s="6">
-        <v>-0.97</v>
+        <v>-1.95</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.33</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>-2.82</v>
+        <v>2.25</v>
       </c>
       <c r="D24" s="6">
-        <v>-0.6899999999999999</v>
-      </c>
-      <c r="E24" s="8">
-        <v>2.13</v>
+        <v>4.08</v>
+      </c>
+      <c r="E24" s="7">
+        <v>1.83</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>-2.22</v>
+        <v>-30.99</v>
       </c>
       <c r="D25" s="6">
-        <v>-3.53</v>
+        <v>-30.84</v>
       </c>
       <c r="E25" s="7">
-        <v>-1.31</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>0.93</v>
+        <v>29.65</v>
       </c>
       <c r="D26" s="6">
-        <v>2.25</v>
-      </c>
-      <c r="E26" s="8">
-        <v>1.32</v>
+        <v>36.15</v>
+      </c>
+      <c r="E26" s="7">
+        <v>6.5</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>-30.77</v>
+        <v>39.05</v>
       </c>
       <c r="D27" s="6">
-        <v>-30.99</v>
+        <v>41.5</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.22</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>28.95</v>
+        <v>29.29</v>
       </c>
       <c r="D28" s="6">
-        <v>29.65</v>
-      </c>
-      <c r="E28" s="8">
-        <v>0.7</v>
+        <v>34.85</v>
+      </c>
+      <c r="E28" s="7">
+        <v>5.56</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>37.65</v>
+        <v>71.18000000000001</v>
       </c>
       <c r="D29" s="6">
-        <v>39.05</v>
-      </c>
-      <c r="E29" s="8">
-        <v>1.4</v>
+        <v>76.23</v>
+      </c>
+      <c r="E29" s="7">
+        <v>5.05</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>27.7</v>
+        <v>-29.49</v>
       </c>
       <c r="D30" s="6">
-        <v>29.29</v>
+        <v>-29.6</v>
       </c>
       <c r="E30" s="8">
-        <v>1.59</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>67.81</v>
+        <v>2.28</v>
       </c>
       <c r="D31" s="6">
-        <v>71.18000000000001</v>
-      </c>
-      <c r="E31" s="8">
-        <v>3.37</v>
+        <v>3.75</v>
+      </c>
+      <c r="E31" s="7">
+        <v>1.47</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>-30.18</v>
+        <v>-29.46</v>
       </c>
       <c r="D32" s="6">
-        <v>-29.49</v>
-      </c>
-      <c r="E32" s="8">
-        <v>0.6899999999999999</v>
+        <v>-28.63</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0.83</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>1.13</v>
+        <v>-34.93</v>
       </c>
       <c r="D33" s="6">
-        <v>2.28</v>
-      </c>
-      <c r="E33" s="8">
-        <v>1.15</v>
+        <v>-33.56</v>
+      </c>
+      <c r="E33" s="7">
+        <v>1.37</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>-29.55</v>
+        <v>-3.5</v>
       </c>
       <c r="D34" s="6">
-        <v>-29.46</v>
-      </c>
-      <c r="E34" s="8">
-        <v>0.09</v>
+        <v>-2.97</v>
+      </c>
+      <c r="E34" s="7">
+        <v>0.53</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-34.31</v>
+        <v>0.8</v>
       </c>
       <c r="D35" s="6">
-        <v>-34.93</v>
+        <v>6.78</v>
       </c>
       <c r="E35" s="7">
-        <v>-0.62</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>-3.67</v>
+        <v>-12.88</v>
       </c>
       <c r="D36" s="6">
-        <v>-3.5</v>
-      </c>
-      <c r="E36" s="8">
-        <v>0.17</v>
+        <v>-9.59</v>
+      </c>
+      <c r="E36" s="7">
+        <v>3.29</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>-0.96</v>
+        <v>-5.71</v>
       </c>
       <c r="D37" s="6">
-        <v>0.8</v>
-      </c>
-      <c r="E37" s="8">
-        <v>1.76</v>
+        <v>-0.26</v>
+      </c>
+      <c r="E37" s="7">
+        <v>5.45</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>-16.06</v>
+        <v>-5.52</v>
       </c>
       <c r="D38" s="6">
-        <v>-12.88</v>
-      </c>
-      <c r="E38" s="8">
-        <v>3.18</v>
+        <v>-0.28</v>
+      </c>
+      <c r="E38" s="7">
+        <v>5.24</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>-6.84</v>
+        <v>-2.32</v>
       </c>
       <c r="D39" s="6">
-        <v>-5.71</v>
-      </c>
-      <c r="E39" s="8">
-        <v>1.13</v>
+        <v>-1.74</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.58</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>-9.57</v>
+        <v>-16.31</v>
       </c>
       <c r="D40" s="6">
-        <v>-5.52</v>
-      </c>
-      <c r="E40" s="8">
-        <v>4.05</v>
+        <v>-14.47</v>
+      </c>
+      <c r="E40" s="7">
+        <v>1.84</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>-3.71</v>
+        <v>0.2</v>
       </c>
       <c r="D41" s="6">
-        <v>-2.32</v>
-      </c>
-      <c r="E41" s="8">
-        <v>1.39</v>
+        <v>1.13</v>
+      </c>
+      <c r="E41" s="7">
+        <v>0.93</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="6">
-        <v>-19.71</v>
+        <v>-6.79</v>
       </c>
       <c r="D42" s="6">
-        <v>-16.31</v>
-      </c>
-      <c r="E42" s="8">
-        <v>3.4</v>
+        <v>-6.11</v>
+      </c>
+      <c r="E42" s="7">
+        <v>0.68</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C43" s="6">
-        <v>-0.23</v>
+        <v>-33.63</v>
       </c>
       <c r="D43" s="6">
-        <v>0.2</v>
+        <v>-33.9</v>
       </c>
       <c r="E43" s="8">
-        <v>0.43</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-11.04</v>
+        <v>-8.06</v>
       </c>
       <c r="D44" s="6">
-        <v>-6.79</v>
-      </c>
-      <c r="E44" s="8">
-        <v>4.25</v>
+        <v>-3.34</v>
+      </c>
+      <c r="E44" s="7">
+        <v>4.72</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-33.32</v>
+        <v>-19.48</v>
       </c>
       <c r="D45" s="6">
-        <v>-33.63</v>
+        <v>-18.04</v>
       </c>
       <c r="E45" s="7">
-        <v>-0.31</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-8.16</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="D46" s="6">
-        <v>-8.06</v>
-      </c>
-      <c r="E46" s="8">
-        <v>0.1</v>
+        <v>-5.75</v>
+      </c>
+      <c r="E46" s="7">
+        <v>3.45</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-19.73</v>
+        <v>-16.27</v>
       </c>
       <c r="D47" s="6">
-        <v>-19.48</v>
-      </c>
-      <c r="E47" s="8">
-        <v>0.25</v>
+        <v>-13.66</v>
+      </c>
+      <c r="E47" s="7">
+        <v>2.61</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-10.03</v>
+        <v>-32.34</v>
       </c>
       <c r="D48" s="6">
-        <v>-9.199999999999999</v>
+        <v>-32.56</v>
       </c>
       <c r="E48" s="8">
-        <v>0.83</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-17.85</v>
+        <v>-24.6</v>
       </c>
       <c r="D49" s="6">
-        <v>-16.27</v>
-      </c>
-      <c r="E49" s="8">
-        <v>1.58</v>
+        <v>-24.25</v>
+      </c>
+      <c r="E49" s="7">
+        <v>0.35</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-32.29</v>
+        <v>-44.56</v>
       </c>
       <c r="D50" s="6">
-        <v>-32.34</v>
+        <v>-44.03</v>
       </c>
       <c r="E50" s="7">
-        <v>-0.05</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C51" s="6">
-        <v>-25.31</v>
+        <v>1262.8</v>
       </c>
       <c r="D51" s="6">
-        <v>-24.6</v>
+        <v>1257.7</v>
       </c>
       <c r="E51" s="8">
-        <v>0.71</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C52" s="6">
-        <v>-32.18</v>
+        <v>2953.1</v>
       </c>
       <c r="D52" s="6">
-        <v>-32.45</v>
+        <v>3104.7</v>
       </c>
       <c r="E52" s="7">
-        <v>-0.27</v>
+        <v>151.6</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>-44.68</v>
+        <v>1292</v>
       </c>
       <c r="D53" s="6">
-        <v>-44.56</v>
-      </c>
-      <c r="E53" s="8">
-        <v>0.12</v>
+        <v>1315</v>
+      </c>
+      <c r="E53" s="7">
+        <v>23</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>1268.7</v>
+        <v>1710</v>
       </c>
       <c r="D54" s="6">
-        <v>1262.8</v>
+        <v>1775</v>
       </c>
       <c r="E54" s="7">
-        <v>-5.9</v>
+        <v>65</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>2950</v>
+        <v>208.4</v>
       </c>
       <c r="D55" s="6">
-        <v>2953.1</v>
-      </c>
-      <c r="E55" s="8">
-        <v>3.1</v>
+        <v>214.9</v>
+      </c>
+      <c r="E55" s="7">
+        <v>6.5</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>1288</v>
+        <v>398.3</v>
       </c>
       <c r="D56" s="6">
-        <v>1292</v>
+        <v>397</v>
       </c>
       <c r="E56" s="8">
-        <v>4</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>1694.3</v>
+        <v>609.4</v>
       </c>
       <c r="D57" s="6">
-        <v>1710</v>
-      </c>
-      <c r="E57" s="8">
-        <v>15.7</v>
+        <v>612.3</v>
+      </c>
+      <c r="E57" s="7">
+        <v>2.9</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>204.49</v>
+        <v>73.03</v>
       </c>
       <c r="D58" s="6">
-        <v>208.4</v>
-      </c>
-      <c r="E58" s="8">
-        <v>3.91</v>
+        <v>73.73</v>
+      </c>
+      <c r="E58" s="7">
+        <v>0.7</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C59" s="6">
-        <v>398.6</v>
+        <v>35.64</v>
       </c>
       <c r="D59" s="6">
-        <v>398.3</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-0.3</v>
+        <v>34.5</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-1.14</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C60" s="6">
-        <v>603.7</v>
+        <v>45.32</v>
       </c>
       <c r="D60" s="6">
-        <v>609.4</v>
-      </c>
-      <c r="E60" s="8">
-        <v>5.7</v>
+        <v>58.78</v>
+      </c>
+      <c r="E60" s="7">
+        <v>13.46</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C61" s="6">
-        <v>188.27</v>
+        <v>44.22</v>
       </c>
       <c r="D61" s="6">
-        <v>187.52</v>
+        <v>48.23</v>
       </c>
       <c r="E61" s="7">
-        <v>-0.75</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C62" s="6">
-        <v>72.87</v>
+        <v>51.69</v>
       </c>
       <c r="D62" s="6">
-        <v>73.03</v>
-      </c>
-      <c r="E62" s="8">
-        <v>0.16</v>
+        <v>60.5</v>
+      </c>
+      <c r="E62" s="7">
+        <v>8.81</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C63" s="6">
-        <v>34</v>
+        <v>50.25</v>
       </c>
       <c r="D63" s="6">
-        <v>23</v>
+        <v>57.18</v>
       </c>
       <c r="E63" s="7">
-        <v>-11</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -3162,328 +3135,209 @@
         <v>42</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C64" s="6">
-        <v>23</v>
+        <v>35.61</v>
       </c>
       <c r="D64" s="6">
-        <v>34</v>
+        <v>34.73</v>
       </c>
       <c r="E64" s="8">
-        <v>11</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C65" s="6">
-        <v>36.95</v>
+        <v>30.83</v>
       </c>
       <c r="D65" s="6">
-        <v>35.64</v>
+        <v>33.26</v>
       </c>
       <c r="E65" s="7">
-        <v>-1.31</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="6">
-        <v>44.98</v>
+        <v>43.09</v>
       </c>
       <c r="D66" s="6">
-        <v>45.32</v>
-      </c>
-      <c r="E66" s="8">
-        <v>0.34</v>
+        <v>46.38</v>
+      </c>
+      <c r="E66" s="7">
+        <v>3.29</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C67" s="6">
-        <v>43.52</v>
+        <v>-2.01</v>
       </c>
       <c r="D67" s="6">
-        <v>44.22</v>
-      </c>
-      <c r="E67" s="8">
-        <v>0.7</v>
+        <v>4.64</v>
+      </c>
+      <c r="E67" s="7">
+        <v>6.65</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C68" s="6">
-        <v>49.14</v>
+        <v>-47.38</v>
       </c>
       <c r="D68" s="6">
-        <v>51.69</v>
-      </c>
-      <c r="E68" s="8">
-        <v>2.55</v>
+        <v>187.11</v>
+      </c>
+      <c r="E68" s="7">
+        <v>234.49</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C69" s="6">
-        <v>45.31</v>
+        <v>-57.04</v>
       </c>
       <c r="D69" s="6">
-        <v>50.25</v>
-      </c>
-      <c r="E69" s="8">
-        <v>4.94</v>
+        <v>57.79</v>
+      </c>
+      <c r="E69" s="7">
+        <v>114.83</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C70" s="6">
-        <v>35.8</v>
+        <v>-46.19</v>
       </c>
       <c r="D70" s="6">
-        <v>35.61</v>
+        <v>149.43</v>
       </c>
       <c r="E70" s="7">
-        <v>-0.19</v>
+        <v>195.62</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C71" s="6">
-        <v>25.91</v>
+        <v>-10.34</v>
       </c>
       <c r="D71" s="6">
-        <v>30.83</v>
-      </c>
-      <c r="E71" s="8">
-        <v>4.92</v>
+        <v>65.16</v>
+      </c>
+      <c r="E71" s="7">
+        <v>75.5</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C72" s="6">
-        <v>43.24</v>
+        <v>-55.91</v>
       </c>
       <c r="D72" s="6">
-        <v>42.14</v>
-      </c>
-      <c r="E72" s="7">
-        <v>-1.1</v>
+        <v>-60.77</v>
+      </c>
+      <c r="E72" s="8">
+        <v>-4.86</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C73" s="6">
-        <v>42.33</v>
+        <v>-52.63</v>
       </c>
       <c r="D73" s="6">
-        <v>43.09</v>
-      </c>
-      <c r="E73" s="8">
-        <v>0.76</v>
+        <v>-9.9</v>
+      </c>
+      <c r="E73" s="7">
+        <v>42.73</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C74" s="6">
-        <v>-26.19</v>
+        <v>-75.05</v>
       </c>
       <c r="D74" s="6">
-        <v>-2.01</v>
-      </c>
-      <c r="E74" s="8">
-        <v>24.18</v>
+        <v>-51.41</v>
+      </c>
+      <c r="E74" s="7">
+        <v>23.64</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="6">
-        <v>-46.57</v>
+        <v>-51.12</v>
       </c>
       <c r="D75" s="6">
-        <v>-47.38</v>
+        <v>-10.29</v>
       </c>
       <c r="E75" s="7">
-        <v>-0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>-57.33</v>
-      </c>
-      <c r="D76" s="6">
-        <v>-57.04</v>
-      </c>
-      <c r="E76" s="8">
-        <v>0.29</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>-49.33</v>
-      </c>
-      <c r="D77" s="6">
-        <v>-46.19</v>
-      </c>
-      <c r="E77" s="8">
-        <v>3.14</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>-51.08</v>
-      </c>
-      <c r="D78" s="6">
-        <v>-10.34</v>
-      </c>
-      <c r="E78" s="8">
-        <v>40.74</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>-61.63</v>
-      </c>
-      <c r="D79" s="6">
-        <v>-55.91</v>
-      </c>
-      <c r="E79" s="8">
-        <v>5.72</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>-57.05</v>
-      </c>
-      <c r="D80" s="6">
-        <v>-52.63</v>
-      </c>
-      <c r="E80" s="8">
-        <v>4.42</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="6">
-        <v>-58.4</v>
-      </c>
-      <c r="D81" s="6">
-        <v>-75.05</v>
-      </c>
-      <c r="E81" s="7">
-        <v>-16.65</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="6">
-        <v>-7.46</v>
-      </c>
-      <c r="D82" s="6">
-        <v>-51.12</v>
-      </c>
-      <c r="E82" s="7">
-        <v>-43.66</v>
+        <v>40.83</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3507,28 +3361,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3542,16 +3396,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>42.1</v>
+        <v>46.2</v>
       </c>
       <c r="E2" s="11">
         <v>40</v>
       </c>
       <c r="F2" s="11">
-        <v>-4.2</v>
+        <v>-2</v>
       </c>
       <c r="G2" s="11">
-        <v>-5.8</v>
+        <v>-3.1</v>
       </c>
       <c r="H2" s="11">
         <v>55.4</v>
@@ -3688,31 +3542,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.6053999999999999</v>
+        <v>0.5999</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1866</v>
+        <v>0.1946</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1373</v>
+        <v>0.1503</v>
       </c>
       <c r="D2" s="14">
-        <v>0.0221</v>
+        <v>0.0158</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.0025</v>
+        <v>0.0001</v>
       </c>
       <c r="F2" s="14">
-        <v>-0.0103</v>
+        <v>-0.0121</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.07519999999999999</v>
+        <v>-0.0751</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.1161</v>
+        <v>-0.1176</v>
       </c>
       <c r="I2" s="14">
-        <v>-0.1528</v>
+        <v>-0.1512</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="66">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,34 +178,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>45.3 → 58.8</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>45.3</t>
-  </si>
-  <si>
-    <t>58.8</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -407,15 +380,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -930,10 +902,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1257.7</v>
+        <v>1254.3</v>
       </c>
       <c r="D2">
-        <v>-0.4</v>
+        <v>-0.27</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -942,46 +914,46 @@
         <v>1247.38</v>
       </c>
       <c r="G2">
-        <v>-33.9</v>
+        <v>-34.08</v>
       </c>
       <c r="H2">
-        <v>0.83</v>
+        <v>0.55</v>
       </c>
       <c r="I2">
-        <v>-0.7</v>
+        <v>-1.39</v>
       </c>
       <c r="J2">
-        <v>-6.13</v>
+        <v>-5.89</v>
       </c>
       <c r="K2">
-        <v>-2.97</v>
+        <v>-6.16</v>
       </c>
       <c r="L2">
-        <v>-30.84</v>
+        <v>-31.37</v>
       </c>
       <c r="M2">
-        <v>-11.76</v>
+        <v>-11.91</v>
       </c>
       <c r="N2">
         <v>23</v>
       </c>
       <c r="O2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P2">
-        <v>1269</v>
+        <v>1265.46</v>
       </c>
       <c r="Q2">
-        <v>1293.98</v>
+        <v>1290.46</v>
       </c>
       <c r="R2">
-        <v>1337.96</v>
+        <v>1336.03</v>
       </c>
       <c r="S2">
-        <v>1483.52</v>
+        <v>1480.28</v>
       </c>
       <c r="T2">
-        <v>-15.22</v>
+        <v>-15.27</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -996,43 +968,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>34.5</v>
+        <v>33.72</v>
       </c>
       <c r="Z2">
-        <v>-21.43</v>
+        <v>-21.97</v>
       </c>
       <c r="AA2">
-        <v>-19.02</v>
+        <v>-19.61</v>
       </c>
       <c r="AB2">
-        <v>-2.41</v>
+        <v>-2.36</v>
       </c>
       <c r="AC2">
-        <v>12.78</v>
+        <v>4.97</v>
       </c>
       <c r="AD2">
-        <v>22.88</v>
+        <v>14.87</v>
       </c>
       <c r="AE2">
-        <v>21.65</v>
+        <v>20.83</v>
       </c>
       <c r="AF2">
-        <v>4.64</v>
+        <v>-5.64</v>
       </c>
       <c r="AG2">
-        <v>1339.04</v>
+        <v>1336.41</v>
       </c>
       <c r="AH2">
-        <v>1248.92</v>
+        <v>1244.51</v>
       </c>
       <c r="AI2">
-        <v>1327.88</v>
+        <v>1317.68</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>31.71</v>
+        <v>32.12</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,10 +1015,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3104.7</v>
+        <v>3077.2</v>
       </c>
       <c r="D3">
-        <v>5.13</v>
+        <v>-0.89</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1055,25 +1027,25 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-3.34</v>
+        <v>-4.2</v>
       </c>
       <c r="H3">
-        <v>76.59999999999999</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="I3">
-        <v>7.36</v>
+        <v>6.07</v>
       </c>
       <c r="J3">
-        <v>3.65</v>
+        <v>3.06</v>
       </c>
       <c r="K3">
-        <v>6.78</v>
+        <v>5.33</v>
       </c>
       <c r="L3">
-        <v>36.15</v>
+        <v>33.22</v>
       </c>
       <c r="M3">
-        <v>15.03</v>
+        <v>15.04</v>
       </c>
       <c r="N3">
         <v>88</v>
@@ -1082,19 +1054,19 @@
         <v>77</v>
       </c>
       <c r="P3">
-        <v>2969.36</v>
+        <v>3004.6</v>
       </c>
       <c r="Q3">
-        <v>3000.59</v>
+        <v>3006.2</v>
       </c>
       <c r="R3">
-        <v>3054.19</v>
+        <v>3052.18</v>
       </c>
       <c r="S3">
-        <v>2520.36</v>
+        <v>2523.75</v>
       </c>
       <c r="T3">
-        <v>23.18</v>
+        <v>21.93</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1109,34 +1081,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>58.78</v>
+        <v>56.08</v>
       </c>
       <c r="Z3">
-        <v>-15</v>
+        <v>-6.82</v>
       </c>
       <c r="AA3">
-        <v>-18.56</v>
+        <v>-16.21</v>
       </c>
       <c r="AB3">
-        <v>3.57</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="AC3">
-        <v>46.03</v>
+        <v>57.85</v>
       </c>
       <c r="AD3">
-        <v>33.37</v>
+        <v>44.62</v>
       </c>
       <c r="AE3">
-        <v>84.01000000000001</v>
+        <v>83.25</v>
       </c>
       <c r="AF3">
-        <v>187.11</v>
+        <v>-15.87</v>
       </c>
       <c r="AG3">
-        <v>3186.19</v>
+        <v>3194.04</v>
       </c>
       <c r="AH3">
-        <v>2814.98</v>
+        <v>2818.36</v>
       </c>
       <c r="AI3">
         <v>3113.12</v>
@@ -1145,7 +1117,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>33.17</v>
+        <v>33.27</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1128,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1315</v>
+        <v>1299.1</v>
       </c>
       <c r="D4">
-        <v>1.78</v>
+        <v>-1.21</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1168,46 +1140,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-18.04</v>
+        <v>-19.03</v>
       </c>
       <c r="H4">
-        <v>70.16</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="I4">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="J4">
-        <v>-3.73</v>
+        <v>-2.49</v>
       </c>
       <c r="K4">
-        <v>-9.59</v>
+        <v>-12.56</v>
       </c>
       <c r="L4">
-        <v>41.5</v>
+        <v>38.62</v>
       </c>
       <c r="M4">
-        <v>1.58</v>
+        <v>1.86</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P4">
-        <v>1295.94</v>
+        <v>1299.08</v>
       </c>
       <c r="Q4">
-        <v>1302.69</v>
+        <v>1301.69</v>
       </c>
       <c r="R4">
-        <v>1394.14</v>
+        <v>1389.01</v>
       </c>
       <c r="S4">
-        <v>1180.42</v>
+        <v>1181.87</v>
       </c>
       <c r="T4">
-        <v>11.4</v>
+        <v>9.92</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1222,34 +1194,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>48.23</v>
+        <v>45.78</v>
       </c>
       <c r="Z4">
-        <v>-24.8</v>
+        <v>-22.94</v>
       </c>
       <c r="AA4">
-        <v>-31.39</v>
+        <v>-29.7</v>
       </c>
       <c r="AB4">
-        <v>6.59</v>
+        <v>6.76</v>
       </c>
       <c r="AC4">
-        <v>94.12</v>
+        <v>93.48999999999999</v>
       </c>
       <c r="AD4">
-        <v>93.69</v>
+        <v>93.91</v>
       </c>
       <c r="AE4">
-        <v>39.55</v>
+        <v>38.87</v>
       </c>
       <c r="AF4">
-        <v>57.79</v>
+        <v>-24.63</v>
       </c>
       <c r="AG4">
-        <v>1358.69</v>
+        <v>1357.18</v>
       </c>
       <c r="AH4">
-        <v>1246.68</v>
+        <v>1246.2</v>
       </c>
       <c r="AI4">
         <v>1367.12</v>
@@ -1258,7 +1230,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>22.37</v>
+        <v>21.54</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1241,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1775</v>
+        <v>1768</v>
       </c>
       <c r="D5">
-        <v>3.8</v>
+        <v>-0.39</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1281,46 +1253,46 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-5.75</v>
+        <v>-6.12</v>
       </c>
       <c r="H5">
-        <v>36.74</v>
+        <v>36.2</v>
       </c>
       <c r="I5">
-        <v>6.12</v>
+        <v>3.6</v>
       </c>
       <c r="J5">
-        <v>6.4</v>
+        <v>6.19</v>
       </c>
       <c r="K5">
-        <v>-0.26</v>
+        <v>-2.48</v>
       </c>
       <c r="L5">
-        <v>34.85</v>
+        <v>31.68</v>
       </c>
       <c r="M5">
-        <v>19.46</v>
+        <v>19.55</v>
       </c>
       <c r="N5">
         <v>77</v>
       </c>
       <c r="O5">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P5">
-        <v>1718.62</v>
+        <v>1730.92</v>
       </c>
       <c r="Q5">
-        <v>1690.62</v>
+        <v>1696.12</v>
       </c>
       <c r="R5">
-        <v>1740.11</v>
+        <v>1737.81</v>
       </c>
       <c r="S5">
-        <v>1605.66</v>
+        <v>1607.1</v>
       </c>
       <c r="T5">
-        <v>10.55</v>
+        <v>10.01</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1335,43 +1307,43 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>60.5</v>
+        <v>59.25</v>
       </c>
       <c r="Z5">
-        <v>-1.88</v>
+        <v>3.45</v>
       </c>
       <c r="AA5">
-        <v>-13.43</v>
+        <v>-10.06</v>
       </c>
       <c r="AB5">
-        <v>11.55</v>
+        <v>13.51</v>
       </c>
       <c r="AC5">
-        <v>96.59999999999999</v>
+        <v>98.59</v>
       </c>
       <c r="AD5">
-        <v>96.59999999999999</v>
+        <v>97.26000000000001</v>
       </c>
       <c r="AE5">
-        <v>40.09</v>
+        <v>39.34</v>
       </c>
       <c r="AF5">
-        <v>149.43</v>
+        <v>17.1</v>
       </c>
       <c r="AG5">
-        <v>1759.53</v>
+        <v>1771.34</v>
       </c>
       <c r="AH5">
-        <v>1621.72</v>
+        <v>1620.91</v>
       </c>
       <c r="AI5">
-        <v>1625.69</v>
+        <v>1647.19</v>
       </c>
       <c r="AJ5" t="s">
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>22.84</v>
+        <v>25.09</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,10 +1354,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>214.9</v>
+        <v>213.5</v>
       </c>
       <c r="D6">
-        <v>3.12</v>
+        <v>-0.65</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1394,46 +1366,46 @@
         <v>124.93</v>
       </c>
       <c r="G6">
-        <v>-13.66</v>
+        <v>-14.23</v>
       </c>
       <c r="H6">
-        <v>72.02</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I6">
-        <v>3.47</v>
+        <v>2.5</v>
       </c>
       <c r="J6">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="K6">
-        <v>-0.28</v>
+        <v>-4.29</v>
       </c>
       <c r="L6">
-        <v>76.23</v>
+        <v>68.42</v>
       </c>
       <c r="M6">
-        <v>59.99</v>
+        <v>60.53</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="P6">
-        <v>208.66</v>
+        <v>209.7</v>
       </c>
       <c r="Q6">
-        <v>206.61</v>
+        <v>206.98</v>
       </c>
       <c r="R6">
-        <v>211.42</v>
+        <v>211.2</v>
       </c>
       <c r="S6">
-        <v>183.68</v>
+        <v>184.02</v>
       </c>
       <c r="T6">
-        <v>17</v>
+        <v>16.02</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1448,34 +1420,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>57.18</v>
+        <v>55.39</v>
       </c>
       <c r="Z6">
-        <v>-0.51</v>
+        <v>-0.03</v>
       </c>
       <c r="AA6">
-        <v>-1.51</v>
+        <v>-1.22</v>
       </c>
       <c r="AB6">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AC6">
-        <v>63.64</v>
+        <v>78.72</v>
       </c>
       <c r="AD6">
-        <v>54.93</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="AE6">
-        <v>5.93</v>
+        <v>5.7</v>
       </c>
       <c r="AF6">
-        <v>65.16</v>
+        <v>-10.28</v>
       </c>
       <c r="AG6">
-        <v>214.59</v>
+        <v>215.53</v>
       </c>
       <c r="AH6">
-        <v>198.63</v>
+        <v>198.43</v>
       </c>
       <c r="AI6">
         <v>217.63</v>
@@ -1484,7 +1456,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>19.57</v>
+        <v>20.79</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1495,10 +1467,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>397</v>
+        <v>395.6</v>
       </c>
       <c r="D7">
-        <v>-0.33</v>
+        <v>-0.35</v>
       </c>
       <c r="E7">
         <v>588.6900000000001</v>
@@ -1507,46 +1479,46 @@
         <v>393.4</v>
       </c>
       <c r="G7">
-        <v>-32.56</v>
+        <v>-32.8</v>
       </c>
       <c r="H7">
-        <v>0.92</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I7">
-        <v>-1.42</v>
+        <v>-2.32</v>
       </c>
       <c r="J7">
-        <v>-6.37</v>
+        <v>-6.03</v>
       </c>
       <c r="K7">
-        <v>-1.74</v>
+        <v>-6.5</v>
       </c>
       <c r="L7">
-        <v>-29.6</v>
+        <v>-30.29</v>
       </c>
       <c r="M7">
-        <v>-1.21</v>
+        <v>-1.18</v>
       </c>
       <c r="N7">
         <v>34</v>
       </c>
       <c r="O7">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="P7">
-        <v>400.78</v>
+        <v>398.9</v>
       </c>
       <c r="Q7">
-        <v>408.58</v>
+        <v>407.39</v>
       </c>
       <c r="R7">
-        <v>423.29</v>
+        <v>422.62</v>
       </c>
       <c r="S7">
-        <v>466.21</v>
+        <v>465.48</v>
       </c>
       <c r="T7">
-        <v>-14.85</v>
+        <v>-15.01</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1561,43 +1533,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>34.73</v>
+        <v>33.77</v>
       </c>
       <c r="Z7">
-        <v>-7.1</v>
+        <v>-7.28</v>
       </c>
       <c r="AA7">
-        <v>-6.35</v>
+        <v>-6.54</v>
       </c>
       <c r="AB7">
-        <v>-0.75</v>
+        <v>-0.74</v>
       </c>
       <c r="AC7">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AD7">
-        <v>16.69</v>
+        <v>6.44</v>
       </c>
       <c r="AE7">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="AF7">
-        <v>-60.77</v>
+        <v>-34.27</v>
       </c>
       <c r="AG7">
-        <v>422.68</v>
+        <v>421.67</v>
       </c>
       <c r="AH7">
-        <v>394.48</v>
+        <v>393.12</v>
       </c>
       <c r="AI7">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>29.41</v>
+        <v>31.12</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1608,10 +1580,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>612.3</v>
+        <v>602.7</v>
       </c>
       <c r="D8">
-        <v>0.48</v>
+        <v>-1.57</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1620,46 +1592,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-24.25</v>
+        <v>-25.43</v>
       </c>
       <c r="H8">
-        <v>30.91</v>
+        <v>28.85</v>
       </c>
       <c r="I8">
-        <v>-0.43</v>
+        <v>-1.85</v>
       </c>
       <c r="J8">
-        <v>-8.08</v>
+        <v>-8.73</v>
       </c>
       <c r="K8">
-        <v>-14.47</v>
+        <v>-17.27</v>
       </c>
       <c r="L8">
-        <v>3.75</v>
+        <v>1.79</v>
       </c>
       <c r="M8">
-        <v>-15.12</v>
+        <v>-15.22</v>
       </c>
       <c r="N8">
         <v>55</v>
       </c>
       <c r="O8">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="P8">
-        <v>610.36</v>
+        <v>608.09</v>
       </c>
       <c r="Q8">
-        <v>633.91</v>
+        <v>631.3</v>
       </c>
       <c r="R8">
-        <v>664.75</v>
+        <v>662.14</v>
       </c>
       <c r="S8">
-        <v>613.87</v>
+        <v>613.88</v>
       </c>
       <c r="T8">
-        <v>-0.26</v>
+        <v>-1.82</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1674,34 +1646,34 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>33.26</v>
+        <v>29.56</v>
       </c>
       <c r="Z8">
-        <v>-15.94</v>
+        <v>-16.22</v>
       </c>
       <c r="AA8">
-        <v>-14.6</v>
+        <v>-14.93</v>
       </c>
       <c r="AB8">
-        <v>-1.34</v>
+        <v>-1.3</v>
       </c>
       <c r="AC8">
-        <v>25.57</v>
+        <v>33.8</v>
       </c>
       <c r="AD8">
-        <v>12.03</v>
+        <v>22.84</v>
       </c>
       <c r="AE8">
-        <v>15.25</v>
+        <v>15.29</v>
       </c>
       <c r="AF8">
-        <v>-9.9</v>
+        <v>-52.04</v>
       </c>
       <c r="AG8">
-        <v>672.0599999999999</v>
+        <v>670.5</v>
       </c>
       <c r="AH8">
-        <v>595.77</v>
+        <v>592.09</v>
       </c>
       <c r="AI8">
         <v>652.63</v>
@@ -1710,7 +1682,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>34.62</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1721,10 +1693,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>187.52</v>
+        <v>185.7</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>-0.97</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1733,46 +1705,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-32.45</v>
+        <v>-33.11</v>
       </c>
       <c r="H9">
-        <v>8.83</v>
+        <v>7.78</v>
       </c>
       <c r="I9">
-        <v>-1.95</v>
+        <v>-2.67</v>
       </c>
       <c r="J9">
-        <v>-2.77</v>
+        <v>-4.4</v>
       </c>
       <c r="K9">
-        <v>1.13</v>
+        <v>-2.68</v>
       </c>
       <c r="L9">
-        <v>-28.63</v>
+        <v>-28.88</v>
       </c>
       <c r="M9">
-        <v>-7.51</v>
+        <v>-7.71</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P9">
-        <v>188.28</v>
+        <v>187.26</v>
       </c>
       <c r="Q9">
-        <v>192.2</v>
+        <v>191.88</v>
       </c>
       <c r="R9">
-        <v>190.81</v>
+        <v>190.84</v>
       </c>
       <c r="S9">
-        <v>202.06</v>
+        <v>201.6</v>
       </c>
       <c r="T9">
-        <v>-7.2</v>
+        <v>-7.89</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1787,43 +1759,43 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>42.14</v>
+        <v>39.34</v>
       </c>
       <c r="Z9">
-        <v>-0.8</v>
+        <v>-1.15</v>
       </c>
       <c r="AA9">
-        <v>0.23</v>
+        <v>-0.04</v>
       </c>
       <c r="AB9">
-        <v>-1.04</v>
+        <v>-1.1</v>
       </c>
       <c r="AC9">
-        <v>4.32</v>
+        <v>1.94</v>
       </c>
       <c r="AD9">
-        <v>4.66</v>
+        <v>3.21</v>
       </c>
       <c r="AE9">
-        <v>4.67</v>
+        <v>4.57</v>
       </c>
       <c r="AF9">
-        <v>-51.41</v>
+        <v>-76.33</v>
       </c>
       <c r="AG9">
-        <v>201.13</v>
+        <v>201.27</v>
       </c>
       <c r="AH9">
-        <v>183.27</v>
+        <v>182.49</v>
       </c>
       <c r="AI9">
-        <v>185.88</v>
+        <v>200.58</v>
       </c>
       <c r="AJ9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AK9">
-        <v>32.08</v>
+        <v>33.87</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1834,10 +1806,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>73.73</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="D10">
-        <v>0.96</v>
+        <v>-1.95</v>
       </c>
       <c r="E10">
         <v>131.73</v>
@@ -1846,46 +1818,46 @@
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-44.03</v>
+        <v>-45.12</v>
       </c>
       <c r="H10">
-        <v>24.38</v>
+        <v>21.95</v>
       </c>
       <c r="I10">
-        <v>4.08</v>
+        <v>2.31</v>
       </c>
       <c r="J10">
-        <v>-4.18</v>
+        <v>-5.02</v>
       </c>
       <c r="K10">
-        <v>-6.11</v>
+        <v>-11.03</v>
       </c>
       <c r="L10">
-        <v>-33.56</v>
+        <v>-35.81</v>
       </c>
       <c r="M10">
-        <v>0.01</v>
+        <v>-0.18</v>
       </c>
       <c r="N10">
         <v>12</v>
       </c>
       <c r="O10">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="P10">
-        <v>72.91</v>
+        <v>73.23999999999999</v>
       </c>
       <c r="Q10">
-        <v>74.04000000000001</v>
+        <v>73.83</v>
       </c>
       <c r="R10">
-        <v>76.81</v>
+        <v>76.62</v>
       </c>
       <c r="S10">
-        <v>80.73999999999999</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="T10">
-        <v>-8.69</v>
+        <v>-10.4</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1900,34 +1872,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>46.38</v>
+        <v>41.11</v>
       </c>
       <c r="Z10">
-        <v>-1.17</v>
+        <v>-1.16</v>
       </c>
       <c r="AA10">
-        <v>-1.3</v>
+        <v>-1.28</v>
       </c>
       <c r="AB10">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AC10">
-        <v>83.56999999999999</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="AD10">
-        <v>75.81999999999999</v>
+        <v>83.48</v>
       </c>
       <c r="AE10">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="AF10">
-        <v>-10.29</v>
+        <v>-43.47</v>
       </c>
       <c r="AG10">
-        <v>77.64</v>
+        <v>77.34</v>
       </c>
       <c r="AH10">
-        <v>70.43000000000001</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="AI10">
         <v>76.63</v>
@@ -1936,7 +1908,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>32.09</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -2077,7 +2049,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2097,47 +2069,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -2145,1193 +2082,1244 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>66</v>
+      <c r="B6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-6.98</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-6.13</v>
       </c>
-      <c r="E7" s="7">
-        <v>0.85</v>
+      <c r="D7" s="5">
+        <v>-5.89</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.24</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-1.89</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>3.65</v>
       </c>
+      <c r="D8" s="5">
+        <v>3.06</v>
+      </c>
       <c r="E8" s="7">
-        <v>5.54</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-5.62</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-3.73</v>
       </c>
-      <c r="E9" s="7">
-        <v>1.89</v>
+      <c r="D9" s="5">
+        <v>-2.49</v>
+      </c>
+      <c r="E9" s="6">
+        <v>1.24</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>1.73</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>6.4</v>
       </c>
+      <c r="D10" s="5">
+        <v>6.19</v>
+      </c>
       <c r="E10" s="7">
-        <v>4.67</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-1.07</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>2.82</v>
       </c>
-      <c r="E11" s="7">
-        <v>3.89</v>
+      <c r="D11" s="5">
+        <v>3.15</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0.33</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
-        <v>-7.55</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>-6.37</v>
       </c>
-      <c r="E12" s="7">
-        <v>1.18</v>
+      <c r="D12" s="5">
+        <v>-6.03</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0.34</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="6">
-        <v>-7.68</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>-8.08</v>
       </c>
-      <c r="E13" s="8">
-        <v>-0.4</v>
+      <c r="D13" s="5">
+        <v>-8.73</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.65</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="6">
-        <v>-4.39</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>-2.77</v>
       </c>
+      <c r="D14" s="5">
+        <v>-4.4</v>
+      </c>
       <c r="E14" s="7">
-        <v>1.62</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="6">
-        <v>-4.08</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>-4.18</v>
       </c>
-      <c r="E15" s="8">
-        <v>-0.1</v>
+      <c r="D15" s="5">
+        <v>-5.02</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.84</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="6">
-        <v>-0.75</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="5">
         <v>-0.7</v>
       </c>
+      <c r="D16" s="5">
+        <v>-1.39</v>
+      </c>
       <c r="E16" s="7">
-        <v>0.05</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="6">
-        <v>3.11</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C17" s="5">
         <v>7.36</v>
       </c>
+      <c r="D17" s="5">
+        <v>6.07</v>
+      </c>
       <c r="E17" s="7">
-        <v>4.25</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="6">
-        <v>2.13</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C18" s="5">
         <v>1.47</v>
       </c>
-      <c r="E18" s="8">
+      <c r="D18" s="5">
+        <v>1.22</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>6.12</v>
+      </c>
+      <c r="D19" s="5">
+        <v>3.6</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-2.52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>3.47</v>
+      </c>
+      <c r="D20" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-1.42</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-2.32</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-0.43</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-1.85</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-1.42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-1.95</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-2.67</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="5">
+        <v>4.08</v>
+      </c>
+      <c r="D24" s="5">
+        <v>2.31</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-1.77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-30.84</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-31.37</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>36.15</v>
+      </c>
+      <c r="D26" s="5">
+        <v>33.22</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-2.93</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>41.5</v>
+      </c>
+      <c r="D27" s="5">
+        <v>38.62</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-2.88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="5">
+        <v>34.85</v>
+      </c>
+      <c r="D28" s="5">
+        <v>31.68</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-3.17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="5">
+        <v>76.23</v>
+      </c>
+      <c r="D29" s="5">
+        <v>68.42</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-7.81</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-29.6</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-30.29</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="5">
+        <v>3.75</v>
+      </c>
+      <c r="D31" s="5">
+        <v>1.79</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-1.96</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-28.63</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-28.88</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="5">
+        <v>-33.56</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-35.81</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-2.25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-2.97</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-6.16</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-3.19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="5">
+        <v>6.78</v>
+      </c>
+      <c r="D35" s="5">
+        <v>5.33</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-1.45</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-9.59</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-12.56</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-2.97</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-0.26</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-2.48</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-2.22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-0.28</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-4.29</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-4.01</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-1.74</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-6.5</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-4.76</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-14.47</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-17.27</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-2.8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="5">
+        <v>1.13</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-2.68</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-3.81</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="5">
+        <v>-6.11</v>
+      </c>
+      <c r="D42" s="5">
+        <v>-11.03</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-4.92</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-33.9</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-34.08</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-3.34</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-4.2</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-18.04</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-19.03</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-0.99</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="5">
+        <v>-5.75</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-6.12</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="5">
+        <v>-13.66</v>
+      </c>
+      <c r="D47" s="5">
+        <v>-14.23</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="5">
+        <v>-32.56</v>
+      </c>
+      <c r="D48" s="5">
+        <v>-32.8</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="5">
+        <v>-24.25</v>
+      </c>
+      <c r="D49" s="5">
+        <v>-25.43</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-1.18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="5">
+        <v>-32.45</v>
+      </c>
+      <c r="D50" s="5">
+        <v>-33.11</v>
+      </c>
+      <c r="E50" s="7">
         <v>-0.66</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="5">
+        <v>-44.03</v>
+      </c>
+      <c r="D51" s="5">
+        <v>-45.12</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-1.09</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="5">
+        <v>1257.7</v>
+      </c>
+      <c r="D52" s="5">
+        <v>1254.3</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-3.4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="5">
+        <v>3104.7</v>
+      </c>
+      <c r="D53" s="5">
+        <v>3077.2</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-27.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="5">
+        <v>1315</v>
+      </c>
+      <c r="D54" s="5">
+        <v>1299.1</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-15.9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>3.79</v>
-      </c>
-      <c r="D19" s="6">
-        <v>6.12</v>
-      </c>
-      <c r="E19" s="7">
-        <v>2.33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B55" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="5">
+        <v>1775</v>
+      </c>
+      <c r="D55" s="5">
+        <v>1768</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>1.98</v>
-      </c>
-      <c r="D20" s="6">
-        <v>3.47</v>
-      </c>
-      <c r="E20" s="7">
-        <v>1.49</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B56" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="5">
+        <v>214.9</v>
+      </c>
+      <c r="D56" s="5">
+        <v>213.5</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-0.97</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-1.42</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-0.45</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B57" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="5">
+        <v>397</v>
+      </c>
+      <c r="D57" s="5">
+        <v>395.6</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-0.6899999999999999</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-0.43</v>
-      </c>
-      <c r="E22" s="7">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B58" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="5">
+        <v>612.3</v>
+      </c>
+      <c r="D58" s="5">
+        <v>602.7</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-9.6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-3.53</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-1.95</v>
-      </c>
-      <c r="E23" s="7">
-        <v>1.58</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B59" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="5">
+        <v>187.52</v>
+      </c>
+      <c r="D59" s="5">
+        <v>185.7</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-1.82</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>2.25</v>
-      </c>
-      <c r="D24" s="6">
-        <v>4.08</v>
-      </c>
-      <c r="E24" s="7">
-        <v>1.83</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B60" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="5">
+        <v>73.73</v>
+      </c>
+      <c r="D60" s="5">
+        <v>72.29000000000001</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-1.44</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-30.99</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-30.84</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B61" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="5">
+        <v>34.5</v>
+      </c>
+      <c r="D61" s="5">
+        <v>33.72</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-0.78</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>29.65</v>
-      </c>
-      <c r="D26" s="6">
-        <v>36.15</v>
-      </c>
-      <c r="E26" s="7">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="5">
+        <v>58.78</v>
+      </c>
+      <c r="D62" s="5">
+        <v>56.08</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-2.7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>39.05</v>
-      </c>
-      <c r="D27" s="6">
-        <v>41.5</v>
-      </c>
-      <c r="E27" s="7">
-        <v>2.45</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B63" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="5">
+        <v>48.23</v>
+      </c>
+      <c r="D63" s="5">
+        <v>45.78</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-2.45</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>29.29</v>
-      </c>
-      <c r="D28" s="6">
-        <v>34.85</v>
-      </c>
-      <c r="E28" s="7">
-        <v>5.56</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B64" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="5">
+        <v>60.5</v>
+      </c>
+      <c r="D64" s="5">
+        <v>59.25</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-1.25</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>71.18000000000001</v>
-      </c>
-      <c r="D29" s="6">
-        <v>76.23</v>
-      </c>
-      <c r="E29" s="7">
-        <v>5.05</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B65" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="5">
+        <v>57.18</v>
+      </c>
+      <c r="D65" s="5">
+        <v>55.39</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-1.79</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-29.49</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-29.6</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B66" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="5">
+        <v>34.73</v>
+      </c>
+      <c r="D66" s="5">
+        <v>33.77</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-0.96</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>2.28</v>
-      </c>
-      <c r="D31" s="6">
-        <v>3.75</v>
-      </c>
-      <c r="E31" s="7">
-        <v>1.47</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B67" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="5">
+        <v>33.26</v>
+      </c>
+      <c r="D67" s="5">
+        <v>29.56</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-3.7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-29.46</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-28.63</v>
-      </c>
-      <c r="E32" s="7">
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B68" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="5">
+        <v>42.14</v>
+      </c>
+      <c r="D68" s="5">
+        <v>39.34</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-2.8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-34.93</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-33.56</v>
-      </c>
-      <c r="E33" s="7">
-        <v>1.37</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B69" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="5">
+        <v>46.38</v>
+      </c>
+      <c r="D69" s="5">
+        <v>41.11</v>
+      </c>
+      <c r="E69" s="7">
+        <v>-5.27</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-3.5</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-2.97</v>
-      </c>
-      <c r="E34" s="7">
-        <v>0.53</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B70" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="5">
+        <v>4.64</v>
+      </c>
+      <c r="D70" s="5">
+        <v>-5.64</v>
+      </c>
+      <c r="E70" s="7">
+        <v>-10.28</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>0.8</v>
-      </c>
-      <c r="D35" s="6">
-        <v>6.78</v>
-      </c>
-      <c r="E35" s="7">
-        <v>5.98</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B71" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="5">
+        <v>187.11</v>
+      </c>
+      <c r="D71" s="5">
+        <v>-15.87</v>
+      </c>
+      <c r="E71" s="7">
+        <v>-202.98</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-12.88</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-9.59</v>
-      </c>
-      <c r="E36" s="7">
-        <v>3.29</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="B72" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="5">
+        <v>57.79</v>
+      </c>
+      <c r="D72" s="5">
+        <v>-24.63</v>
+      </c>
+      <c r="E72" s="7">
+        <v>-82.42</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-5.71</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-0.26</v>
-      </c>
-      <c r="E37" s="7">
-        <v>5.45</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="B73" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="5">
+        <v>149.43</v>
+      </c>
+      <c r="D73" s="5">
+        <v>17.1</v>
+      </c>
+      <c r="E73" s="7">
+        <v>-132.33</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-5.52</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-0.28</v>
-      </c>
-      <c r="E38" s="7">
-        <v>5.24</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="B74" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="5">
+        <v>65.16</v>
+      </c>
+      <c r="D74" s="5">
+        <v>-10.28</v>
+      </c>
+      <c r="E74" s="7">
+        <v>-75.44</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-2.32</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-1.74</v>
-      </c>
-      <c r="E39" s="7">
-        <v>0.58</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
+      <c r="B75" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="5">
+        <v>-60.77</v>
+      </c>
+      <c r="D75" s="5">
+        <v>-34.27</v>
+      </c>
+      <c r="E75" s="6">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-16.31</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-14.47</v>
-      </c>
-      <c r="E40" s="7">
-        <v>1.84</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
+      <c r="B76" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="5">
+        <v>-9.9</v>
+      </c>
+      <c r="D76" s="5">
+        <v>-52.04</v>
+      </c>
+      <c r="E76" s="7">
+        <v>-42.14</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="D41" s="6">
-        <v>1.13</v>
-      </c>
-      <c r="E41" s="7">
-        <v>0.93</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
+      <c r="B77" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="5">
+        <v>-51.41</v>
+      </c>
+      <c r="D77" s="5">
+        <v>-76.33</v>
+      </c>
+      <c r="E77" s="7">
+        <v>-24.92</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-6.79</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-6.11</v>
-      </c>
-      <c r="E42" s="7">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-33.63</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-33.9</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-8.06</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-3.34</v>
-      </c>
-      <c r="E44" s="7">
-        <v>4.72</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-19.48</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-18.04</v>
-      </c>
-      <c r="E45" s="7">
-        <v>1.44</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-9.199999999999999</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-5.75</v>
-      </c>
-      <c r="E46" s="7">
-        <v>3.45</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-16.27</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-13.66</v>
-      </c>
-      <c r="E47" s="7">
-        <v>2.61</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-32.34</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-32.56</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-0.22</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-24.6</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-24.25</v>
-      </c>
-      <c r="E49" s="7">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-44.56</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-44.03</v>
-      </c>
-      <c r="E50" s="7">
-        <v>0.53</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="6">
-        <v>1262.8</v>
-      </c>
-      <c r="D51" s="6">
-        <v>1257.7</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-5.1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="6">
-        <v>2953.1</v>
-      </c>
-      <c r="D52" s="6">
-        <v>3104.7</v>
-      </c>
-      <c r="E52" s="7">
-        <v>151.6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>1292</v>
-      </c>
-      <c r="D53" s="6">
-        <v>1315</v>
-      </c>
-      <c r="E53" s="7">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>1710</v>
-      </c>
-      <c r="D54" s="6">
-        <v>1775</v>
-      </c>
-      <c r="E54" s="7">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>208.4</v>
-      </c>
-      <c r="D55" s="6">
-        <v>214.9</v>
-      </c>
-      <c r="E55" s="7">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>398.3</v>
-      </c>
-      <c r="D56" s="6">
-        <v>397</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>609.4</v>
-      </c>
-      <c r="D57" s="6">
-        <v>612.3</v>
-      </c>
-      <c r="E57" s="7">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>73.03</v>
-      </c>
-      <c r="D58" s="6">
-        <v>73.73</v>
-      </c>
-      <c r="E58" s="7">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="6">
-        <v>35.64</v>
-      </c>
-      <c r="D59" s="6">
-        <v>34.5</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-1.14</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="6">
-        <v>45.32</v>
-      </c>
-      <c r="D60" s="6">
-        <v>58.78</v>
-      </c>
-      <c r="E60" s="7">
-        <v>13.46</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="6">
-        <v>44.22</v>
-      </c>
-      <c r="D61" s="6">
-        <v>48.23</v>
-      </c>
-      <c r="E61" s="7">
-        <v>4.01</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="6">
-        <v>51.69</v>
-      </c>
-      <c r="D62" s="6">
-        <v>60.5</v>
-      </c>
-      <c r="E62" s="7">
-        <v>8.81</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="6">
-        <v>50.25</v>
-      </c>
-      <c r="D63" s="6">
-        <v>57.18</v>
-      </c>
-      <c r="E63" s="7">
-        <v>6.93</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="6">
-        <v>35.61</v>
-      </c>
-      <c r="D64" s="6">
-        <v>34.73</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-0.88</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>30.83</v>
-      </c>
-      <c r="D65" s="6">
-        <v>33.26</v>
-      </c>
-      <c r="E65" s="7">
-        <v>2.43</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>43.09</v>
-      </c>
-      <c r="D66" s="6">
-        <v>46.38</v>
-      </c>
-      <c r="E66" s="7">
-        <v>3.29</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B67" s="5" t="s">
+      <c r="B78" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C67" s="6">
-        <v>-2.01</v>
-      </c>
-      <c r="D67" s="6">
-        <v>4.64</v>
-      </c>
-      <c r="E67" s="7">
-        <v>6.65</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="6">
-        <v>-47.38</v>
-      </c>
-      <c r="D68" s="6">
-        <v>187.11</v>
-      </c>
-      <c r="E68" s="7">
-        <v>234.49</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="6">
-        <v>-57.04</v>
-      </c>
-      <c r="D69" s="6">
-        <v>57.79</v>
-      </c>
-      <c r="E69" s="7">
-        <v>114.83</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="6">
-        <v>-46.19</v>
-      </c>
-      <c r="D70" s="6">
-        <v>149.43</v>
-      </c>
-      <c r="E70" s="7">
-        <v>195.62</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="6">
-        <v>-10.34</v>
-      </c>
-      <c r="D71" s="6">
-        <v>65.16</v>
-      </c>
-      <c r="E71" s="7">
-        <v>75.5</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="6">
-        <v>-55.91</v>
-      </c>
-      <c r="D72" s="6">
-        <v>-60.77</v>
-      </c>
-      <c r="E72" s="8">
-        <v>-4.86</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="6">
-        <v>-52.63</v>
-      </c>
-      <c r="D73" s="6">
-        <v>-9.9</v>
-      </c>
-      <c r="E73" s="7">
-        <v>42.73</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="6">
-        <v>-75.05</v>
-      </c>
-      <c r="D74" s="6">
-        <v>-51.41</v>
-      </c>
-      <c r="E74" s="7">
-        <v>23.64</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="6">
-        <v>-51.12</v>
-      </c>
-      <c r="D75" s="6">
+      <c r="C78" s="5">
         <v>-10.29</v>
       </c>
-      <c r="E75" s="7">
-        <v>40.83</v>
+      <c r="D78" s="5">
+        <v>-43.47</v>
+      </c>
+      <c r="E78" s="7">
+        <v>-33.18</v>
       </c>
     </row>
   </sheetData>
@@ -3357,60 +3345,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>74</v>
+      <c r="B1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>48.16</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
-        <v>46.2</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>43.8</v>
+      </c>
+      <c r="E2" s="10">
         <v>40</v>
       </c>
-      <c r="F2" s="11">
-        <v>-2</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-3.1</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-2.2</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-6.4</v>
+      </c>
+      <c r="H2" s="10">
         <v>55.4</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -3512,61 +3500,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="12" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>0.5999</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.1946</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1503</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.0158</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.0001</v>
-      </c>
-      <c r="F2" s="14">
-        <v>-0.0121</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.0751</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.1176</v>
-      </c>
-      <c r="I2" s="14">
-        <v>-0.1512</v>
+      <c r="A2" s="13">
+        <v>0.6053000000000001</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.1955</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.1504</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.0186</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.0018</v>
+      </c>
+      <c r="F2" s="13">
+        <v>-0.0118</v>
+      </c>
+      <c r="G2" s="13">
+        <v>-0.0771</v>
+      </c>
+      <c r="H2" s="13">
+        <v>-0.1191</v>
+      </c>
+      <c r="I2" s="13">
+        <v>-0.1522</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -264,14 +264,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -304,13 +304,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -902,58 +902,58 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1254.3</v>
+        <v>1246.5</v>
       </c>
       <c r="D2">
-        <v>-0.27</v>
+        <v>-0.62</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
       </c>
       <c r="F2">
-        <v>1247.38</v>
+        <v>1246.5</v>
       </c>
       <c r="G2">
-        <v>-34.08</v>
+        <v>-34.49</v>
       </c>
       <c r="H2">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>-1.39</v>
+        <v>-2.91</v>
       </c>
       <c r="J2">
-        <v>-5.89</v>
+        <v>-5.9</v>
       </c>
       <c r="K2">
-        <v>-6.16</v>
+        <v>-8.1</v>
       </c>
       <c r="L2">
-        <v>-31.37</v>
+        <v>-32.24</v>
       </c>
       <c r="M2">
-        <v>-11.91</v>
+        <v>-12.02</v>
       </c>
       <c r="N2">
         <v>23</v>
       </c>
       <c r="O2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P2">
-        <v>1265.46</v>
+        <v>1258</v>
       </c>
       <c r="Q2">
-        <v>1290.46</v>
+        <v>1286.72</v>
       </c>
       <c r="R2">
-        <v>1336.03</v>
+        <v>1333.09</v>
       </c>
       <c r="S2">
-        <v>1480.28</v>
+        <v>1477.22</v>
       </c>
       <c r="T2">
-        <v>-15.27</v>
+        <v>-15.62</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -968,43 +968,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>33.72</v>
+        <v>31.95</v>
       </c>
       <c r="Z2">
-        <v>-21.97</v>
+        <v>-22.76</v>
       </c>
       <c r="AA2">
-        <v>-19.61</v>
+        <v>-20.24</v>
       </c>
       <c r="AB2">
-        <v>-2.36</v>
+        <v>-2.52</v>
       </c>
       <c r="AC2">
-        <v>4.97</v>
+        <v>1.22</v>
       </c>
       <c r="AD2">
-        <v>14.87</v>
+        <v>6.32</v>
       </c>
       <c r="AE2">
-        <v>20.83</v>
+        <v>21.03</v>
       </c>
       <c r="AF2">
-        <v>-5.64</v>
+        <v>-3.12</v>
       </c>
       <c r="AG2">
-        <v>1336.41</v>
+        <v>1334.23</v>
       </c>
       <c r="AH2">
-        <v>1244.51</v>
+        <v>1239.2</v>
       </c>
       <c r="AI2">
-        <v>1317.68</v>
+        <v>1304.25</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>32.12</v>
+        <v>34.69</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1015,10 +1015,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3077.2</v>
+        <v>3060</v>
       </c>
       <c r="D3">
-        <v>-0.89</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1027,25 +1027,25 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-4.2</v>
+        <v>-4.74</v>
       </c>
       <c r="H3">
-        <v>75.04000000000001</v>
+        <v>74.06</v>
       </c>
       <c r="I3">
-        <v>6.07</v>
+        <v>4.15</v>
       </c>
       <c r="J3">
-        <v>3.06</v>
+        <v>3.21</v>
       </c>
       <c r="K3">
-        <v>5.33</v>
+        <v>3.99</v>
       </c>
       <c r="L3">
-        <v>33.22</v>
+        <v>32.43</v>
       </c>
       <c r="M3">
-        <v>15.04</v>
+        <v>14.9</v>
       </c>
       <c r="N3">
         <v>88</v>
@@ -1054,19 +1054,19 @@
         <v>77</v>
       </c>
       <c r="P3">
-        <v>3004.6</v>
+        <v>3029</v>
       </c>
       <c r="Q3">
-        <v>3006.2</v>
+        <v>3007.45</v>
       </c>
       <c r="R3">
-        <v>3052.18</v>
+        <v>3049.14</v>
       </c>
       <c r="S3">
-        <v>2523.75</v>
+        <v>2527.39</v>
       </c>
       <c r="T3">
-        <v>21.93</v>
+        <v>21.07</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1081,34 +1081,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>56.08</v>
+        <v>54.4</v>
       </c>
       <c r="Z3">
-        <v>-6.82</v>
+        <v>-1.71</v>
       </c>
       <c r="AA3">
-        <v>-16.21</v>
+        <v>-13.31</v>
       </c>
       <c r="AB3">
-        <v>9.390000000000001</v>
+        <v>11.6</v>
       </c>
       <c r="AC3">
-        <v>57.85</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="AD3">
-        <v>44.62</v>
+        <v>57.13</v>
       </c>
       <c r="AE3">
-        <v>83.25</v>
+        <v>82.89</v>
       </c>
       <c r="AF3">
-        <v>-15.87</v>
+        <v>-12.13</v>
       </c>
       <c r="AG3">
-        <v>3194.04</v>
+        <v>3196.42</v>
       </c>
       <c r="AH3">
-        <v>2818.36</v>
+        <v>2818.47</v>
       </c>
       <c r="AI3">
         <v>3113.12</v>
@@ -1117,7 +1117,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>33.27</v>
+        <v>31.09</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1128,10 +1128,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1299.1</v>
+        <v>1281.3</v>
       </c>
       <c r="D4">
-        <v>-1.21</v>
+        <v>-1.37</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1140,46 +1140,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-19.03</v>
+        <v>-20.14</v>
       </c>
       <c r="H4">
-        <v>68.09999999999999</v>
+        <v>65.8</v>
       </c>
       <c r="I4">
-        <v>1.22</v>
+        <v>-1.54</v>
       </c>
       <c r="J4">
-        <v>-2.49</v>
+        <v>-2.86</v>
       </c>
       <c r="K4">
-        <v>-12.56</v>
+        <v>-13.58</v>
       </c>
       <c r="L4">
-        <v>38.62</v>
+        <v>35.77</v>
       </c>
       <c r="M4">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P4">
-        <v>1299.08</v>
+        <v>1295.08</v>
       </c>
       <c r="Q4">
-        <v>1301.69</v>
+        <v>1298.36</v>
       </c>
       <c r="R4">
-        <v>1389.01</v>
+        <v>1383.52</v>
       </c>
       <c r="S4">
-        <v>1181.87</v>
+        <v>1183.22</v>
       </c>
       <c r="T4">
-        <v>9.92</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1194,34 +1194,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>45.78</v>
+        <v>43.14</v>
       </c>
       <c r="Z4">
-        <v>-22.94</v>
+        <v>-22.64</v>
       </c>
       <c r="AA4">
-        <v>-29.7</v>
+        <v>-28.29</v>
       </c>
       <c r="AB4">
-        <v>6.76</v>
+        <v>5.64</v>
       </c>
       <c r="AC4">
-        <v>93.48999999999999</v>
+        <v>86.77</v>
       </c>
       <c r="AD4">
-        <v>93.91</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="AE4">
-        <v>38.87</v>
+        <v>38.18</v>
       </c>
       <c r="AF4">
-        <v>-24.63</v>
+        <v>-33.36</v>
       </c>
       <c r="AG4">
-        <v>1357.18</v>
+        <v>1350.01</v>
       </c>
       <c r="AH4">
-        <v>1246.2</v>
+        <v>1246.7</v>
       </c>
       <c r="AI4">
         <v>1367.12</v>
@@ -1230,7 +1230,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>21.54</v>
+        <v>19.05</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1241,10 +1241,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1768</v>
+        <v>1764.6</v>
       </c>
       <c r="D5">
-        <v>-0.39</v>
+        <v>-0.19</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1253,25 +1253,25 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-6.12</v>
+        <v>-6.3</v>
       </c>
       <c r="H5">
-        <v>36.2</v>
+        <v>35.93</v>
       </c>
       <c r="I5">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="J5">
-        <v>6.19</v>
+        <v>6.43</v>
       </c>
       <c r="K5">
-        <v>-2.48</v>
+        <v>-2.23</v>
       </c>
       <c r="L5">
-        <v>31.68</v>
+        <v>28.33</v>
       </c>
       <c r="M5">
-        <v>19.55</v>
+        <v>19.49</v>
       </c>
       <c r="N5">
         <v>77</v>
@@ -1280,19 +1280,19 @@
         <v>73</v>
       </c>
       <c r="P5">
-        <v>1730.92</v>
+        <v>1742.38</v>
       </c>
       <c r="Q5">
-        <v>1696.12</v>
+        <v>1699.35</v>
       </c>
       <c r="R5">
-        <v>1737.81</v>
+        <v>1735.62</v>
       </c>
       <c r="S5">
-        <v>1607.1</v>
+        <v>1608.53</v>
       </c>
       <c r="T5">
-        <v>10.01</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1307,43 +1307,43 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>59.25</v>
+        <v>58.61</v>
       </c>
       <c r="Z5">
-        <v>3.45</v>
+        <v>7.32</v>
       </c>
       <c r="AA5">
-        <v>-10.06</v>
+        <v>-6.58</v>
       </c>
       <c r="AB5">
-        <v>13.51</v>
+        <v>13.9</v>
       </c>
       <c r="AC5">
-        <v>98.59</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="AD5">
-        <v>97.26000000000001</v>
+        <v>97.20999999999999</v>
       </c>
       <c r="AE5">
-        <v>39.34</v>
+        <v>38.03</v>
       </c>
       <c r="AF5">
-        <v>17.1</v>
+        <v>-31.15</v>
       </c>
       <c r="AG5">
-        <v>1771.34</v>
+        <v>1780.58</v>
       </c>
       <c r="AH5">
-        <v>1620.91</v>
+        <v>1618.13</v>
       </c>
       <c r="AI5">
-        <v>1647.19</v>
+        <v>1647.25</v>
       </c>
       <c r="AJ5" t="s">
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>25.09</v>
+        <v>27.05</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1354,10 +1354,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>213.5</v>
+        <v>209.97</v>
       </c>
       <c r="D6">
-        <v>-0.65</v>
+        <v>-1.65</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1366,25 +1366,25 @@
         <v>124.93</v>
       </c>
       <c r="G6">
-        <v>-14.23</v>
+        <v>-15.64</v>
       </c>
       <c r="H6">
-        <v>70.90000000000001</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="I6">
-        <v>2.5</v>
+        <v>1.34</v>
       </c>
       <c r="J6">
-        <v>3.15</v>
+        <v>1.88</v>
       </c>
       <c r="K6">
-        <v>-4.29</v>
+        <v>-4.78</v>
       </c>
       <c r="L6">
-        <v>68.42</v>
+        <v>63.11</v>
       </c>
       <c r="M6">
-        <v>60.53</v>
+        <v>59.96</v>
       </c>
       <c r="N6">
         <v>99</v>
@@ -1393,19 +1393,19 @@
         <v>84</v>
       </c>
       <c r="P6">
-        <v>209.7</v>
+        <v>210.25</v>
       </c>
       <c r="Q6">
-        <v>206.98</v>
+        <v>207.22</v>
       </c>
       <c r="R6">
-        <v>211.2</v>
+        <v>210.96</v>
       </c>
       <c r="S6">
-        <v>184.02</v>
+        <v>184.34</v>
       </c>
       <c r="T6">
-        <v>16.02</v>
+        <v>13.9</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1420,34 +1420,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>55.39</v>
+        <v>51.05</v>
       </c>
       <c r="Z6">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="AA6">
-        <v>-1.22</v>
+        <v>-0.96</v>
       </c>
       <c r="AB6">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="AC6">
-        <v>78.72</v>
+        <v>79.91</v>
       </c>
       <c r="AD6">
-        <v>64.29000000000001</v>
+        <v>74.09</v>
       </c>
       <c r="AE6">
-        <v>5.7</v>
+        <v>5.66</v>
       </c>
       <c r="AF6">
-        <v>-10.28</v>
+        <v>-51.31</v>
       </c>
       <c r="AG6">
-        <v>215.53</v>
+        <v>215.83</v>
       </c>
       <c r="AH6">
-        <v>198.43</v>
+        <v>198.61</v>
       </c>
       <c r="AI6">
         <v>217.63</v>
@@ -1456,7 +1456,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>20.79</v>
+        <v>18.39</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1467,37 +1467,37 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>395.6</v>
+        <v>391.85</v>
       </c>
       <c r="D7">
-        <v>-0.35</v>
+        <v>-0.95</v>
       </c>
       <c r="E7">
         <v>588.6900000000001</v>
       </c>
       <c r="F7">
-        <v>393.4</v>
+        <v>391.85</v>
       </c>
       <c r="G7">
-        <v>-32.8</v>
+        <v>-33.44</v>
       </c>
       <c r="H7">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>-2.32</v>
+        <v>-3.25</v>
       </c>
       <c r="J7">
-        <v>-6.03</v>
+        <v>-6.57</v>
       </c>
       <c r="K7">
-        <v>-6.5</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="L7">
-        <v>-30.29</v>
+        <v>-30.62</v>
       </c>
       <c r="M7">
-        <v>-1.18</v>
+        <v>-1.37</v>
       </c>
       <c r="N7">
         <v>34</v>
@@ -1506,19 +1506,19 @@
         <v>20</v>
       </c>
       <c r="P7">
-        <v>398.9</v>
+        <v>396.27</v>
       </c>
       <c r="Q7">
-        <v>407.39</v>
+        <v>406.11</v>
       </c>
       <c r="R7">
-        <v>422.62</v>
+        <v>421.59</v>
       </c>
       <c r="S7">
-        <v>465.48</v>
+        <v>464.72</v>
       </c>
       <c r="T7">
-        <v>-15.01</v>
+        <v>-15.68</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1533,43 +1533,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>33.77</v>
+        <v>31.26</v>
       </c>
       <c r="Z7">
-        <v>-7.28</v>
+        <v>-7.64</v>
       </c>
       <c r="AA7">
-        <v>-6.54</v>
+        <v>-6.76</v>
       </c>
       <c r="AB7">
-        <v>-0.74</v>
+        <v>-0.88</v>
       </c>
       <c r="AC7">
         <v>0</v>
       </c>
       <c r="AD7">
-        <v>6.44</v>
+        <v>0.88</v>
       </c>
       <c r="AE7">
-        <v>7.4</v>
+        <v>7.44</v>
       </c>
       <c r="AF7">
-        <v>-34.27</v>
+        <v>-33.88</v>
       </c>
       <c r="AG7">
-        <v>421.67</v>
+        <v>421.15</v>
       </c>
       <c r="AH7">
-        <v>393.12</v>
+        <v>391.07</v>
       </c>
       <c r="AI7">
-        <v>418</v>
+        <v>412.92</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>31.12</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1580,10 +1580,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>602.7</v>
+        <v>594.8</v>
       </c>
       <c r="D8">
-        <v>-1.57</v>
+        <v>-1.31</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1592,46 +1592,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-25.43</v>
+        <v>-26.41</v>
       </c>
       <c r="H8">
-        <v>28.85</v>
+        <v>27.16</v>
       </c>
       <c r="I8">
-        <v>-1.85</v>
+        <v>-2.87</v>
       </c>
       <c r="J8">
-        <v>-8.73</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="K8">
-        <v>-17.27</v>
+        <v>-17.39</v>
       </c>
       <c r="L8">
-        <v>1.79</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M8">
-        <v>-15.22</v>
+        <v>-15.43</v>
       </c>
       <c r="N8">
         <v>55</v>
       </c>
       <c r="O8">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="P8">
-        <v>608.09</v>
+        <v>604.58</v>
       </c>
       <c r="Q8">
-        <v>631.3</v>
+        <v>628.34</v>
       </c>
       <c r="R8">
-        <v>662.14</v>
+        <v>659.6</v>
       </c>
       <c r="S8">
-        <v>613.88</v>
+        <v>613.83</v>
       </c>
       <c r="T8">
-        <v>-1.82</v>
+        <v>-3.1</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1646,43 +1646,43 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>29.56</v>
+        <v>26.91</v>
       </c>
       <c r="Z8">
-        <v>-16.22</v>
+        <v>-16.89</v>
       </c>
       <c r="AA8">
-        <v>-14.93</v>
+        <v>-15.32</v>
       </c>
       <c r="AB8">
-        <v>-1.3</v>
+        <v>-1.57</v>
       </c>
       <c r="AC8">
-        <v>33.8</v>
+        <v>27.07</v>
       </c>
       <c r="AD8">
-        <v>22.84</v>
+        <v>28.81</v>
       </c>
       <c r="AE8">
-        <v>15.29</v>
+        <v>14.93</v>
       </c>
       <c r="AF8">
-        <v>-52.04</v>
+        <v>-53.64</v>
       </c>
       <c r="AG8">
-        <v>670.5</v>
+        <v>669.22</v>
       </c>
       <c r="AH8">
-        <v>592.09</v>
+        <v>587.45</v>
       </c>
       <c r="AI8">
-        <v>652.63</v>
+        <v>641.75</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>34.09</v>
+        <v>35.06</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1693,10 +1693,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>185.7</v>
+        <v>185.02</v>
       </c>
       <c r="D9">
-        <v>-0.97</v>
+        <v>-0.37</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1705,46 +1705,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-33.11</v>
+        <v>-33.35</v>
       </c>
       <c r="H9">
-        <v>7.78</v>
+        <v>7.38</v>
       </c>
       <c r="I9">
-        <v>-2.67</v>
+        <v>-1.21</v>
       </c>
       <c r="J9">
-        <v>-4.4</v>
+        <v>-3.69</v>
       </c>
       <c r="K9">
-        <v>-2.68</v>
+        <v>-3.21</v>
       </c>
       <c r="L9">
-        <v>-28.88</v>
+        <v>-27.98</v>
       </c>
       <c r="M9">
-        <v>-7.71</v>
+        <v>-7.78</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="P9">
-        <v>187.26</v>
+        <v>186.81</v>
       </c>
       <c r="Q9">
-        <v>191.88</v>
+        <v>191.52</v>
       </c>
       <c r="R9">
-        <v>190.84</v>
+        <v>190.72</v>
       </c>
       <c r="S9">
-        <v>201.6</v>
+        <v>201.17</v>
       </c>
       <c r="T9">
-        <v>-7.89</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1759,43 +1759,43 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>39.34</v>
+        <v>38.31</v>
       </c>
       <c r="Z9">
-        <v>-1.15</v>
+        <v>-1.45</v>
       </c>
       <c r="AA9">
-        <v>-0.04</v>
+        <v>-0.33</v>
       </c>
       <c r="AB9">
-        <v>-1.1</v>
+        <v>-1.13</v>
       </c>
       <c r="AC9">
-        <v>1.94</v>
+        <v>0.97</v>
       </c>
       <c r="AD9">
-        <v>3.21</v>
+        <v>2.41</v>
       </c>
       <c r="AE9">
-        <v>4.57</v>
+        <v>4.6</v>
       </c>
       <c r="AF9">
-        <v>-76.33</v>
+        <v>-47.28</v>
       </c>
       <c r="AG9">
-        <v>201.27</v>
+        <v>201.4</v>
       </c>
       <c r="AH9">
-        <v>182.49</v>
+        <v>181.64</v>
       </c>
       <c r="AI9">
-        <v>200.58</v>
+        <v>197.27</v>
       </c>
       <c r="AJ9" t="s">
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>33.87</v>
+        <v>37.75</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1806,10 +1806,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>72.29000000000001</v>
+        <v>72.02</v>
       </c>
       <c r="D10">
-        <v>-1.95</v>
+        <v>-0.37</v>
       </c>
       <c r="E10">
         <v>131.73</v>
@@ -1818,25 +1818,25 @@
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-45.12</v>
+        <v>-45.33</v>
       </c>
       <c r="H10">
-        <v>21.95</v>
+        <v>21.49</v>
       </c>
       <c r="I10">
-        <v>2.31</v>
+        <v>-3.03</v>
       </c>
       <c r="J10">
-        <v>-5.02</v>
+        <v>-5.7</v>
       </c>
       <c r="K10">
-        <v>-11.03</v>
+        <v>-11.99</v>
       </c>
       <c r="L10">
-        <v>-35.81</v>
+        <v>-37.3</v>
       </c>
       <c r="M10">
-        <v>-0.18</v>
+        <v>-0.26</v>
       </c>
       <c r="N10">
         <v>12</v>
@@ -1845,19 +1845,19 @@
         <v>13</v>
       </c>
       <c r="P10">
-        <v>73.23999999999999</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="Q10">
-        <v>73.83</v>
+        <v>73.61</v>
       </c>
       <c r="R10">
-        <v>76.62</v>
+        <v>76.44</v>
       </c>
       <c r="S10">
-        <v>80.68000000000001</v>
+        <v>80.62</v>
       </c>
       <c r="T10">
-        <v>-10.4</v>
+        <v>-10.67</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1872,34 +1872,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>41.11</v>
+        <v>40.19</v>
       </c>
       <c r="Z10">
         <v>-1.16</v>
       </c>
       <c r="AA10">
-        <v>-1.28</v>
+        <v>-1.25</v>
       </c>
       <c r="AB10">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="AC10">
-        <v>81.65000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="AD10">
-        <v>83.48</v>
+        <v>80.77</v>
       </c>
       <c r="AE10">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="AF10">
-        <v>-43.47</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG10">
-        <v>77.34</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="AH10">
-        <v>70.31999999999999</v>
+        <v>70.25</v>
       </c>
       <c r="AI10">
         <v>76.63</v>
@@ -1908,7 +1908,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>31</v>
+        <v>31.57</v>
       </c>
     </row>
   </sheetData>
@@ -2106,13 +2106,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-6.13</v>
+        <v>-5.89</v>
       </c>
       <c r="D7" s="5">
-        <v>-5.89</v>
+        <v>-5.9</v>
       </c>
       <c r="E7" s="6">
-        <v>0.24</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2123,13 +2123,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>3.65</v>
+        <v>3.06</v>
       </c>
       <c r="D8" s="5">
-        <v>3.06</v>
+        <v>3.21</v>
       </c>
       <c r="E8" s="7">
-        <v>-0.59</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2140,13 +2140,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-3.73</v>
+        <v>-2.49</v>
       </c>
       <c r="D9" s="5">
-        <v>-2.49</v>
+        <v>-2.86</v>
       </c>
       <c r="E9" s="6">
-        <v>1.24</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2157,13 +2157,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>6.4</v>
+        <v>6.19</v>
       </c>
       <c r="D10" s="5">
-        <v>6.19</v>
+        <v>6.43</v>
       </c>
       <c r="E10" s="7">
-        <v>-0.21</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2174,13 +2174,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="D11" s="5">
-        <v>3.15</v>
+        <v>1.88</v>
       </c>
       <c r="E11" s="6">
-        <v>0.33</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2191,13 +2191,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="5">
-        <v>-6.37</v>
+        <v>-6.03</v>
       </c>
       <c r="D12" s="5">
-        <v>-6.03</v>
+        <v>-6.57</v>
       </c>
       <c r="E12" s="6">
-        <v>0.34</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2208,13 +2208,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="5">
-        <v>-8.08</v>
+        <v>-8.73</v>
       </c>
       <c r="D13" s="5">
-        <v>-8.73</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.65</v>
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2225,13 +2225,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="5">
-        <v>-2.77</v>
+        <v>-4.4</v>
       </c>
       <c r="D14" s="5">
-        <v>-4.4</v>
+        <v>-3.69</v>
       </c>
       <c r="E14" s="7">
-        <v>-1.63</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2242,13 +2242,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="5">
-        <v>-4.18</v>
+        <v>-5.02</v>
       </c>
       <c r="D15" s="5">
-        <v>-5.02</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-0.84</v>
+        <v>-5.7</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2259,13 +2259,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>-0.7</v>
+        <v>-1.39</v>
       </c>
       <c r="D16" s="5">
-        <v>-1.39</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-0.6899999999999999</v>
+        <v>-2.91</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-1.52</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2276,13 +2276,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="5">
-        <v>7.36</v>
+        <v>6.07</v>
       </c>
       <c r="D17" s="5">
-        <v>6.07</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-1.29</v>
+        <v>4.15</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-1.92</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2293,13 +2293,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="5">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="D18" s="5">
-        <v>1.22</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-0.25</v>
+        <v>-1.54</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-2.76</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2310,13 +2310,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="5">
-        <v>6.12</v>
+        <v>3.6</v>
       </c>
       <c r="D19" s="5">
-        <v>3.6</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-2.52</v>
+        <v>3.36</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-0.24</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2327,13 +2327,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="5">
-        <v>3.47</v>
+        <v>2.5</v>
       </c>
       <c r="D20" s="5">
-        <v>2.5</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.97</v>
+        <v>1.34</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-1.16</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2344,13 +2344,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="5">
-        <v>-1.42</v>
+        <v>-2.32</v>
       </c>
       <c r="D21" s="5">
-        <v>-2.32</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.9</v>
+        <v>-3.25</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-0.93</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2361,13 +2361,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="5">
-        <v>-0.43</v>
+        <v>-1.85</v>
       </c>
       <c r="D22" s="5">
-        <v>-1.85</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-1.42</v>
+        <v>-2.87</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-1.02</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2378,13 +2378,13 @@
         <v>8</v>
       </c>
       <c r="C23" s="5">
-        <v>-1.95</v>
+        <v>-2.67</v>
       </c>
       <c r="D23" s="5">
-        <v>-2.67</v>
+        <v>-1.21</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.72</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2395,13 +2395,13 @@
         <v>8</v>
       </c>
       <c r="C24" s="5">
-        <v>4.08</v>
+        <v>2.31</v>
       </c>
       <c r="D24" s="5">
-        <v>2.31</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-1.77</v>
+        <v>-3.03</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-5.34</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2412,13 +2412,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="5">
-        <v>-30.84</v>
+        <v>-31.37</v>
       </c>
       <c r="D25" s="5">
-        <v>-31.37</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.53</v>
+        <v>-32.24</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-0.87</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2429,13 +2429,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="5">
-        <v>36.15</v>
+        <v>33.22</v>
       </c>
       <c r="D26" s="5">
-        <v>33.22</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-2.93</v>
+        <v>32.43</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-0.79</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2446,13 +2446,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="5">
-        <v>41.5</v>
+        <v>38.62</v>
       </c>
       <c r="D27" s="5">
-        <v>38.62</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-2.88</v>
+        <v>35.77</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-2.85</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2463,13 +2463,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="5">
-        <v>34.85</v>
+        <v>31.68</v>
       </c>
       <c r="D28" s="5">
-        <v>31.68</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-3.17</v>
+        <v>28.33</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-3.35</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2480,13 +2480,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="5">
-        <v>76.23</v>
+        <v>68.42</v>
       </c>
       <c r="D29" s="5">
-        <v>68.42</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-7.81</v>
+        <v>63.11</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-5.31</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2497,13 +2497,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="5">
-        <v>-29.6</v>
+        <v>-30.29</v>
       </c>
       <c r="D30" s="5">
-        <v>-30.29</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-0.6899999999999999</v>
+        <v>-30.62</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-0.33</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2514,13 +2514,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="5">
-        <v>3.75</v>
+        <v>1.79</v>
       </c>
       <c r="D31" s="5">
-        <v>1.79</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-1.96</v>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-1.72</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2531,13 +2531,13 @@
         <v>11</v>
       </c>
       <c r="C32" s="5">
-        <v>-28.63</v>
+        <v>-28.88</v>
       </c>
       <c r="D32" s="5">
-        <v>-28.88</v>
+        <v>-27.98</v>
       </c>
       <c r="E32" s="7">
-        <v>-0.25</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2548,13 +2548,13 @@
         <v>11</v>
       </c>
       <c r="C33" s="5">
-        <v>-33.56</v>
+        <v>-35.81</v>
       </c>
       <c r="D33" s="5">
-        <v>-35.81</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-2.25</v>
+        <v>-37.3</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-1.49</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2565,13 +2565,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="5">
-        <v>-2.97</v>
+        <v>-6.16</v>
       </c>
       <c r="D34" s="5">
-        <v>-6.16</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-3.19</v>
+        <v>-8.1</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-1.94</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2582,13 +2582,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="5">
-        <v>6.78</v>
+        <v>5.33</v>
       </c>
       <c r="D35" s="5">
-        <v>5.33</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-1.45</v>
+        <v>3.99</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-1.34</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2599,13 +2599,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="5">
-        <v>-9.59</v>
+        <v>-12.56</v>
       </c>
       <c r="D36" s="5">
-        <v>-12.56</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-2.97</v>
+        <v>-13.58</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-1.02</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2616,13 +2616,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="5">
-        <v>-0.26</v>
+        <v>-2.48</v>
       </c>
       <c r="D37" s="5">
-        <v>-2.48</v>
+        <v>-2.23</v>
       </c>
       <c r="E37" s="7">
-        <v>-2.22</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2633,13 +2633,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="5">
-        <v>-0.28</v>
+        <v>-4.29</v>
       </c>
       <c r="D38" s="5">
-        <v>-4.29</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-4.01</v>
+        <v>-4.78</v>
+      </c>
+      <c r="E38" s="6">
+        <v>-0.49</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2650,13 +2650,13 @@
         <v>10</v>
       </c>
       <c r="C39" s="5">
-        <v>-1.74</v>
+        <v>-6.5</v>
       </c>
       <c r="D39" s="5">
-        <v>-6.5</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-4.76</v>
+        <v>-8.630000000000001</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-2.13</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2667,13 +2667,13 @@
         <v>10</v>
       </c>
       <c r="C40" s="5">
-        <v>-14.47</v>
+        <v>-17.27</v>
       </c>
       <c r="D40" s="5">
-        <v>-17.27</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-2.8</v>
+        <v>-17.39</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-0.12</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2684,13 +2684,13 @@
         <v>10</v>
       </c>
       <c r="C41" s="5">
-        <v>1.13</v>
+        <v>-2.68</v>
       </c>
       <c r="D41" s="5">
-        <v>-2.68</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-3.81</v>
+        <v>-3.21</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-0.53</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2701,13 +2701,13 @@
         <v>10</v>
       </c>
       <c r="C42" s="5">
-        <v>-6.11</v>
+        <v>-11.03</v>
       </c>
       <c r="D42" s="5">
-        <v>-11.03</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-4.92</v>
+        <v>-11.99</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-0.96</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2718,13 +2718,13 @@
         <v>6</v>
       </c>
       <c r="C43" s="5">
-        <v>-33.9</v>
+        <v>-34.08</v>
       </c>
       <c r="D43" s="5">
-        <v>-34.08</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-0.18</v>
+        <v>-34.49</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2735,13 +2735,13 @@
         <v>6</v>
       </c>
       <c r="C44" s="5">
-        <v>-3.34</v>
+        <v>-4.2</v>
       </c>
       <c r="D44" s="5">
-        <v>-4.2</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-0.86</v>
+        <v>-4.74</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-0.54</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2752,13 +2752,13 @@
         <v>6</v>
       </c>
       <c r="C45" s="5">
-        <v>-18.04</v>
+        <v>-19.03</v>
       </c>
       <c r="D45" s="5">
-        <v>-19.03</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-0.99</v>
+        <v>-20.14</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-1.11</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2769,13 +2769,13 @@
         <v>6</v>
       </c>
       <c r="C46" s="5">
-        <v>-5.75</v>
+        <v>-6.12</v>
       </c>
       <c r="D46" s="5">
-        <v>-6.12</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-0.37</v>
+        <v>-6.3</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2786,13 +2786,13 @@
         <v>6</v>
       </c>
       <c r="C47" s="5">
-        <v>-13.66</v>
+        <v>-14.23</v>
       </c>
       <c r="D47" s="5">
-        <v>-14.23</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-0.57</v>
+        <v>-15.64</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-1.41</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2803,13 +2803,13 @@
         <v>6</v>
       </c>
       <c r="C48" s="5">
-        <v>-32.56</v>
+        <v>-32.8</v>
       </c>
       <c r="D48" s="5">
-        <v>-32.8</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-0.24</v>
+        <v>-33.44</v>
+      </c>
+      <c r="E48" s="6">
+        <v>-0.64</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2820,13 +2820,13 @@
         <v>6</v>
       </c>
       <c r="C49" s="5">
-        <v>-24.25</v>
+        <v>-25.43</v>
       </c>
       <c r="D49" s="5">
-        <v>-25.43</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-1.18</v>
+        <v>-26.41</v>
+      </c>
+      <c r="E49" s="6">
+        <v>-0.98</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2837,13 +2837,13 @@
         <v>6</v>
       </c>
       <c r="C50" s="5">
-        <v>-32.45</v>
+        <v>-33.11</v>
       </c>
       <c r="D50" s="5">
-        <v>-33.11</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-0.66</v>
+        <v>-33.35</v>
+      </c>
+      <c r="E50" s="6">
+        <v>-0.24</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2854,13 +2854,13 @@
         <v>6</v>
       </c>
       <c r="C51" s="5">
-        <v>-44.03</v>
+        <v>-45.12</v>
       </c>
       <c r="D51" s="5">
-        <v>-45.12</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-1.09</v>
+        <v>-45.33</v>
+      </c>
+      <c r="E51" s="6">
+        <v>-0.21</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2871,13 +2871,13 @@
         <v>2</v>
       </c>
       <c r="C52" s="5">
-        <v>1257.7</v>
+        <v>1254.3</v>
       </c>
       <c r="D52" s="5">
-        <v>1254.3</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-3.4</v>
+        <v>1246.5</v>
+      </c>
+      <c r="E52" s="6">
+        <v>-7.8</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2888,13 +2888,13 @@
         <v>2</v>
       </c>
       <c r="C53" s="5">
-        <v>3104.7</v>
+        <v>3077.2</v>
       </c>
       <c r="D53" s="5">
-        <v>3077.2</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-27.5</v>
+        <v>3060</v>
+      </c>
+      <c r="E53" s="6">
+        <v>-17.2</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2905,13 +2905,13 @@
         <v>2</v>
       </c>
       <c r="C54" s="5">
-        <v>1315</v>
+        <v>1299.1</v>
       </c>
       <c r="D54" s="5">
-        <v>1299.1</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-15.9</v>
+        <v>1281.3</v>
+      </c>
+      <c r="E54" s="6">
+        <v>-17.8</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2922,13 +2922,13 @@
         <v>2</v>
       </c>
       <c r="C55" s="5">
-        <v>1775</v>
+        <v>1768</v>
       </c>
       <c r="D55" s="5">
-        <v>1768</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-7</v>
+        <v>1764.6</v>
+      </c>
+      <c r="E55" s="6">
+        <v>-3.4</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2939,13 +2939,13 @@
         <v>2</v>
       </c>
       <c r="C56" s="5">
-        <v>214.9</v>
+        <v>213.5</v>
       </c>
       <c r="D56" s="5">
-        <v>213.5</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-1.4</v>
+        <v>209.97</v>
+      </c>
+      <c r="E56" s="6">
+        <v>-3.53</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2956,13 +2956,13 @@
         <v>2</v>
       </c>
       <c r="C57" s="5">
-        <v>397</v>
+        <v>395.6</v>
       </c>
       <c r="D57" s="5">
-        <v>395.6</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-1.4</v>
+        <v>391.85</v>
+      </c>
+      <c r="E57" s="6">
+        <v>-3.75</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2973,13 +2973,13 @@
         <v>2</v>
       </c>
       <c r="C58" s="5">
-        <v>612.3</v>
+        <v>602.7</v>
       </c>
       <c r="D58" s="5">
-        <v>602.7</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-9.6</v>
+        <v>594.8</v>
+      </c>
+      <c r="E58" s="6">
+        <v>-7.9</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2990,13 +2990,13 @@
         <v>2</v>
       </c>
       <c r="C59" s="5">
-        <v>187.52</v>
+        <v>185.7</v>
       </c>
       <c r="D59" s="5">
-        <v>185.7</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-1.82</v>
+        <v>185.02</v>
+      </c>
+      <c r="E59" s="6">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -3007,13 +3007,13 @@
         <v>2</v>
       </c>
       <c r="C60" s="5">
-        <v>73.73</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="D60" s="5">
-        <v>72.29000000000001</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-1.44</v>
+        <v>72.02</v>
+      </c>
+      <c r="E60" s="6">
+        <v>-0.27</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -3024,13 +3024,13 @@
         <v>24</v>
       </c>
       <c r="C61" s="5">
-        <v>34.5</v>
+        <v>33.72</v>
       </c>
       <c r="D61" s="5">
-        <v>33.72</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-0.78</v>
+        <v>31.95</v>
+      </c>
+      <c r="E61" s="6">
+        <v>-1.77</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -3041,13 +3041,13 @@
         <v>24</v>
       </c>
       <c r="C62" s="5">
-        <v>58.78</v>
+        <v>56.08</v>
       </c>
       <c r="D62" s="5">
-        <v>56.08</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-2.7</v>
+        <v>54.4</v>
+      </c>
+      <c r="E62" s="6">
+        <v>-1.68</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -3058,13 +3058,13 @@
         <v>24</v>
       </c>
       <c r="C63" s="5">
-        <v>48.23</v>
+        <v>45.78</v>
       </c>
       <c r="D63" s="5">
-        <v>45.78</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-2.45</v>
+        <v>43.14</v>
+      </c>
+      <c r="E63" s="6">
+        <v>-2.64</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -3075,13 +3075,13 @@
         <v>24</v>
       </c>
       <c r="C64" s="5">
-        <v>60.5</v>
+        <v>59.25</v>
       </c>
       <c r="D64" s="5">
-        <v>59.25</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-1.25</v>
+        <v>58.61</v>
+      </c>
+      <c r="E64" s="6">
+        <v>-0.64</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -3092,13 +3092,13 @@
         <v>24</v>
       </c>
       <c r="C65" s="5">
-        <v>57.18</v>
+        <v>55.39</v>
       </c>
       <c r="D65" s="5">
-        <v>55.39</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-1.79</v>
+        <v>51.05</v>
+      </c>
+      <c r="E65" s="6">
+        <v>-4.34</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -3109,13 +3109,13 @@
         <v>24</v>
       </c>
       <c r="C66" s="5">
-        <v>34.73</v>
+        <v>33.77</v>
       </c>
       <c r="D66" s="5">
-        <v>33.77</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-0.96</v>
+        <v>31.26</v>
+      </c>
+      <c r="E66" s="6">
+        <v>-2.51</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -3126,13 +3126,13 @@
         <v>24</v>
       </c>
       <c r="C67" s="5">
-        <v>33.26</v>
+        <v>29.56</v>
       </c>
       <c r="D67" s="5">
-        <v>29.56</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-3.7</v>
+        <v>26.91</v>
+      </c>
+      <c r="E67" s="6">
+        <v>-2.65</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -3143,13 +3143,13 @@
         <v>24</v>
       </c>
       <c r="C68" s="5">
-        <v>42.14</v>
+        <v>39.34</v>
       </c>
       <c r="D68" s="5">
-        <v>39.34</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-2.8</v>
+        <v>38.31</v>
+      </c>
+      <c r="E68" s="6">
+        <v>-1.03</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="C69" s="5">
-        <v>46.38</v>
+        <v>41.11</v>
       </c>
       <c r="D69" s="5">
-        <v>41.11</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-5.27</v>
+        <v>40.19</v>
+      </c>
+      <c r="E69" s="6">
+        <v>-0.92</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -3177,13 +3177,13 @@
         <v>31</v>
       </c>
       <c r="C70" s="5">
-        <v>4.64</v>
+        <v>-5.64</v>
       </c>
       <c r="D70" s="5">
-        <v>-5.64</v>
+        <v>-3.12</v>
       </c>
       <c r="E70" s="7">
-        <v>-10.28</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -3194,13 +3194,13 @@
         <v>31</v>
       </c>
       <c r="C71" s="5">
-        <v>187.11</v>
+        <v>-15.87</v>
       </c>
       <c r="D71" s="5">
-        <v>-15.87</v>
+        <v>-12.13</v>
       </c>
       <c r="E71" s="7">
-        <v>-202.98</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -3211,13 +3211,13 @@
         <v>31</v>
       </c>
       <c r="C72" s="5">
-        <v>57.79</v>
+        <v>-24.63</v>
       </c>
       <c r="D72" s="5">
-        <v>-24.63</v>
-      </c>
-      <c r="E72" s="7">
-        <v>-82.42</v>
+        <v>-33.36</v>
+      </c>
+      <c r="E72" s="6">
+        <v>-8.73</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -3228,13 +3228,13 @@
         <v>31</v>
       </c>
       <c r="C73" s="5">
-        <v>149.43</v>
+        <v>17.1</v>
       </c>
       <c r="D73" s="5">
-        <v>17.1</v>
-      </c>
-      <c r="E73" s="7">
-        <v>-132.33</v>
+        <v>-31.15</v>
+      </c>
+      <c r="E73" s="6">
+        <v>-48.25</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -3245,13 +3245,13 @@
         <v>31</v>
       </c>
       <c r="C74" s="5">
-        <v>65.16</v>
+        <v>-10.28</v>
       </c>
       <c r="D74" s="5">
-        <v>-10.28</v>
-      </c>
-      <c r="E74" s="7">
-        <v>-75.44</v>
+        <v>-51.31</v>
+      </c>
+      <c r="E74" s="6">
+        <v>-41.03</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -3262,13 +3262,13 @@
         <v>31</v>
       </c>
       <c r="C75" s="5">
-        <v>-60.77</v>
+        <v>-34.27</v>
       </c>
       <c r="D75" s="5">
-        <v>-34.27</v>
-      </c>
-      <c r="E75" s="6">
-        <v>26.5</v>
+        <v>-33.88</v>
+      </c>
+      <c r="E75" s="7">
+        <v>0.39</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -3279,13 +3279,13 @@
         <v>31</v>
       </c>
       <c r="C76" s="5">
-        <v>-9.9</v>
+        <v>-52.04</v>
       </c>
       <c r="D76" s="5">
-        <v>-52.04</v>
-      </c>
-      <c r="E76" s="7">
-        <v>-42.14</v>
+        <v>-53.64</v>
+      </c>
+      <c r="E76" s="6">
+        <v>-1.6</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -3296,13 +3296,13 @@
         <v>31</v>
       </c>
       <c r="C77" s="5">
-        <v>-51.41</v>
+        <v>-76.33</v>
       </c>
       <c r="D77" s="5">
-        <v>-76.33</v>
+        <v>-47.28</v>
       </c>
       <c r="E77" s="7">
-        <v>-24.92</v>
+        <v>29.05</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -3313,13 +3313,13 @@
         <v>31</v>
       </c>
       <c r="C78" s="5">
-        <v>-10.29</v>
+        <v>-43.47</v>
       </c>
       <c r="D78" s="5">
-        <v>-43.47</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E78" s="7">
-        <v>-33.18</v>
+        <v>51.67</v>
       </c>
     </row>
   </sheetData>
@@ -3384,16 +3384,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="10">
-        <v>43.8</v>
+        <v>41.8</v>
       </c>
       <c r="E2" s="10">
         <v>40</v>
       </c>
       <c r="F2" s="10">
-        <v>-2.2</v>
+        <v>-2.5</v>
       </c>
       <c r="G2" s="10">
-        <v>-6.4</v>
+        <v>-7.3</v>
       </c>
       <c r="H2" s="10">
         <v>55.4</v>
@@ -3530,31 +3530,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="13">
-        <v>0.6053000000000001</v>
+        <v>0.5996</v>
       </c>
       <c r="B2" s="13">
-        <v>0.1955</v>
+        <v>0.1949</v>
       </c>
       <c r="C2" s="13">
-        <v>0.1504</v>
+        <v>0.149</v>
       </c>
       <c r="D2" s="13">
-        <v>0.0186</v>
+        <v>0.0157</v>
       </c>
       <c r="E2" s="13">
-        <v>-0.0018</v>
+        <v>-0.0026</v>
       </c>
       <c r="F2" s="13">
-        <v>-0.0118</v>
+        <v>-0.0137</v>
       </c>
       <c r="G2" s="13">
-        <v>-0.0771</v>
+        <v>-0.07780000000000001</v>
       </c>
       <c r="H2" s="13">
-        <v>-0.1191</v>
+        <v>-0.1202</v>
       </c>
       <c r="I2" s="13">
-        <v>-0.1522</v>
+        <v>-0.1543</v>
       </c>
     </row>
   </sheetData>
